--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -2201,13 +2201,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46162.39149386574</v>
+        <v>46162.55816053241</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.70741635417</v>
+        <v>46175.87408302083</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.707430625</v>
+        <v>46175.87409729167</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2254,13 +2254,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46162.39156319444</v>
+        <v>46162.55822986111</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.707391689815</v>
+        <v>46175.87405835648</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.70741675926</v>
+        <v>46175.87408342592</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -2319,13 +2319,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46162.39156659722</v>
+        <v>46162.55823326389</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.70739228009</v>
+        <v>46175.87405894676</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.70741690972</v>
+        <v>46175.87408357639</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2384,13 +2384,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46162.39157100694</v>
+        <v>46162.55823767361</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.707392627315</v>
+        <v>46175.87405929399</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.70741699074</v>
+        <v>46175.87408365741</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -2449,13 +2449,13 @@
         <v>38</v>
       </c>
       <c r="B8" s="5">
-        <v>46162.39157511574</v>
+        <v>46162.558241782404</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.70739302083</v>
+        <v>46175.8740596875</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.70741724537</v>
+        <v>46175.87408391204</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>39</v>
@@ -2514,13 +2514,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="9">
-        <v>46162.3915787963</v>
+        <v>46162.55824546296</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.70739358796</v>
+        <v>46175.87406025463</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.70741747685</v>
+        <v>46175.87408414352</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>43</v>
@@ -2579,11 +2579,11 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46162.39149815972</v>
+        <v>46162.55816482639</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46162.41694712963</v>
+        <v>46162.5836137963</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2626,11 +2626,11 @@
         <v>48</v>
       </c>
       <c r="B11" s="9">
-        <v>46162.39158243056</v>
+        <v>46162.55824909722</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="9">
-        <v>46175.707422638894</v>
+        <v>46175.87408930555</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>49</v>
@@ -2689,11 +2689,11 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46162.3915878125</v>
+        <v>46162.55825447917</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46175.70742391204</v>
+        <v>46175.874090578705</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2752,11 +2752,11 @@
         <v>60</v>
       </c>
       <c r="B13" s="9">
-        <v>46162.39159321759</v>
+        <v>46162.55825988426</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46175.70742302084</v>
+        <v>46175.874089687495</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>61</v>
@@ -2815,11 +2815,11 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46162.391598229166</v>
+        <v>46162.55826489584</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46162.49793693287</v>
+        <v>46162.664603599536</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2878,11 +2878,11 @@
         <v>67</v>
       </c>
       <c r="B15" s="9">
-        <v>46162.39150253472</v>
+        <v>46162.55816920139</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46162.42608726852</v>
+        <v>46162.59275393518</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2925,11 +2925,11 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46162.39160631945</v>
+        <v>46162.55827298611</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46169.69577064815</v>
+        <v>46169.86243731482</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2988,11 +2988,11 @@
         <v>73</v>
       </c>
       <c r="B17" s="9">
-        <v>46162.39161152778</v>
+        <v>46162.55827819444</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46169.69578368055</v>
+        <v>46169.862450347224</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>74</v>
@@ -3051,11 +3051,11 @@
         <v>76</v>
       </c>
       <c r="B18" s="5">
-        <v>46162.39161695602</v>
+        <v>46162.55828362268</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46169.69579145833</v>
+        <v>46169.862458125004</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -3114,11 +3114,11 @@
         <v>80</v>
       </c>
       <c r="B19" s="9">
-        <v>46162.39162216435</v>
+        <v>46162.55828883102</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46182.01385185185</v>
+        <v>46182.18051851852</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>81</v>
@@ -3177,11 +3177,11 @@
         <v>87</v>
       </c>
       <c r="B20" s="5">
-        <v>46162.3916271412</v>
+        <v>46162.55829380787</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46182.01385133102</v>
+        <v>46182.18051799768</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>88</v>
@@ -3240,11 +3240,11 @@
         <v>90</v>
       </c>
       <c r="B21" s="9">
-        <v>46162.39163115741</v>
+        <v>46162.55829782407</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46182.01385158565</v>
+        <v>46182.18051825231</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>91</v>
@@ -3303,11 +3303,11 @@
         <v>93</v>
       </c>
       <c r="B22" s="5">
-        <v>46162.39163478009</v>
+        <v>46162.558301446756</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46182.013851400465</v>
+        <v>46182.18051806713</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>94</v>
@@ -3366,11 +3366,11 @@
         <v>96</v>
       </c>
       <c r="B23" s="9">
-        <v>46162.39150678241</v>
+        <v>46162.55817344907</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46162.43315896991</v>
+        <v>46162.59982563657</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>97</v>
@@ -3413,11 +3413,11 @@
         <v>99</v>
       </c>
       <c r="B24" s="5">
-        <v>46162.39163902777</v>
+        <v>46162.558305694445</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.69586019676</v>
+        <v>46169.86252686342</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>100</v>
@@ -3476,11 +3476,11 @@
         <v>104</v>
       </c>
       <c r="B25" s="9">
-        <v>46162.391643518524</v>
+        <v>46162.55831018518</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.696358437504</v>
+        <v>46169.86302510416</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>105</v>
@@ -3535,11 +3535,11 @@
         <v>107</v>
       </c>
       <c r="B26" s="5">
-        <v>46162.391648125005</v>
+        <v>46162.55831479166</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46169.69638149306</v>
+        <v>46169.86304815972</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>108</v>
@@ -3594,11 +3594,11 @@
         <v>110</v>
       </c>
       <c r="B27" s="9">
-        <v>46162.39165304398</v>
+        <v>46162.558319710646</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46169.695876909725</v>
+        <v>46169.86254357639</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>111</v>
@@ -3657,11 +3657,11 @@
         <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46162.39165748842</v>
+        <v>46162.55832415509</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46169.696302662036</v>
+        <v>46169.86296932871</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3716,11 +3716,11 @@
         <v>116</v>
       </c>
       <c r="B29" s="9">
-        <v>46162.39166703704</v>
+        <v>46162.5583337037</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46169.69631638889</v>
+        <v>46169.86298305556</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>117</v>
@@ -3775,11 +3775,11 @@
         <v>119</v>
       </c>
       <c r="B30" s="5">
-        <v>46162.391672094906</v>
+        <v>46162.55833876158</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46169.69589785879</v>
+        <v>46169.862564525465</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>120</v>
@@ -3838,11 +3838,11 @@
         <v>122</v>
       </c>
       <c r="B31" s="9">
-        <v>46162.39167703704</v>
+        <v>46162.5583437037</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46169.69623</v>
+        <v>46169.862896666666</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>123</v>
@@ -3897,11 +3897,11 @@
         <v>125</v>
       </c>
       <c r="B32" s="5">
-        <v>46162.39168206019</v>
+        <v>46162.55834872685</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46169.69624538194</v>
+        <v>46169.862912048615</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>126</v>
@@ -3956,11 +3956,11 @@
         <v>128</v>
       </c>
       <c r="B33" s="9">
-        <v>46162.39168685186</v>
+        <v>46162.558353518514</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46175.003680821756</v>
+        <v>46175.17034748843</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>129</v>
@@ -4015,11 +4015,11 @@
         <v>131</v>
       </c>
       <c r="B34" s="5">
-        <v>46162.3916915625</v>
+        <v>46162.558358229166</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46169.69590939815</v>
+        <v>46169.862576064814</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>132</v>
@@ -4078,11 +4078,11 @@
         <v>136</v>
       </c>
       <c r="B35" s="9">
-        <v>46162.39169614583</v>
+        <v>46162.5583628125</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46169.69617309028</v>
+        <v>46169.86283975694</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>137</v>
@@ -4137,11 +4137,11 @@
         <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46162.39174608796</v>
+        <v>46162.55841275463</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.69618954862</v>
+        <v>46169.86285621527</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>140</v>
@@ -4196,11 +4196,11 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46162.39175195602</v>
+        <v>46162.558418622684</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46169.69592395834</v>
+        <v>46169.862590625</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -4259,11 +4259,11 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46162.39175545139</v>
+        <v>46162.558422118054</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.6961208912</v>
+        <v>46169.86278755787</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>89</v>
@@ -4312,11 +4312,11 @@
         <v>147</v>
       </c>
       <c r="B39" s="9">
-        <v>46162.3917597338</v>
+        <v>46162.558426400465</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46171.00696226852</v>
+        <v>46171.17362893518</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>148</v>
@@ -4365,11 +4365,11 @@
         <v>150</v>
       </c>
       <c r="B40" s="5">
-        <v>46162.391767002315</v>
+        <v>46162.55843366898</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.69593177083</v>
+        <v>46169.862598437496</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>151</v>
@@ -4428,11 +4428,11 @@
         <v>155</v>
       </c>
       <c r="B41" s="9">
-        <v>46162.391770902774</v>
+        <v>46162.558437569445</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.69604415509</v>
+        <v>46169.86271082176</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>95</v>
@@ -4481,11 +4481,11 @@
         <v>157</v>
       </c>
       <c r="B42" s="5">
-        <v>46162.39177487268</v>
+        <v>46162.55844153935</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.69605724537</v>
+        <v>46169.86272391204</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>158</v>
@@ -4534,11 +4534,11 @@
         <v>160</v>
       </c>
       <c r="B43" s="9">
-        <v>46162.39177909722</v>
+        <v>46162.55844576389</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.69607568287</v>
+        <v>46169.862742349535</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>161</v>
@@ -4587,11 +4587,11 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46162.391781666665</v>
+        <v>46162.55844833334</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46169.69594810186</v>
+        <v>46169.86261476851</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -4650,11 +4650,11 @@
         <v>167</v>
       </c>
       <c r="B45" s="9">
-        <v>46162.391784479165</v>
+        <v>46162.55845114583</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46169.69599142361</v>
+        <v>46169.86265809028</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>92</v>
@@ -4703,11 +4703,11 @@
         <v>169</v>
       </c>
       <c r="B46" s="5">
-        <v>46162.39178854167</v>
+        <v>46162.55845520833</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.696003923615</v>
+        <v>46169.86267059028</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4756,11 +4756,11 @@
         <v>172</v>
       </c>
       <c r="B47" s="9">
-        <v>46162.39151100694</v>
+        <v>46162.55817767361</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46162.42564194444</v>
+        <v>46162.592308611114</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>173</v>
@@ -4803,11 +4803,11 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46162.391792905095</v>
+        <v>46162.55845957176</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46168.00518532407</v>
+        <v>46168.171851990744</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>176</v>
@@ -4866,11 +4866,11 @@
         <v>180</v>
       </c>
       <c r="B49" s="9">
-        <v>46162.391797731485</v>
+        <v>46162.55846439815</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46185.02548277778</v>
+        <v>46185.19214944444</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>181</v>
@@ -4929,11 +4929,11 @@
         <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46162.39180357639</v>
+        <v>46162.55847024306</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46185.004113773146</v>
+        <v>46185.17078043982</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>84</v>
@@ -4990,11 +4990,11 @@
         <v>186</v>
       </c>
       <c r="B51" s="9">
-        <v>46162.39181905093</v>
+        <v>46162.55848571759</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46162.505030671295</v>
+        <v>46162.671697337966</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>187</v>
@@ -5053,11 +5053,11 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46162.39182234954</v>
+        <v>46162.5584890162</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46162.48170163194</v>
+        <v>46162.648368298615</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -5102,11 +5102,11 @@
         <v>194</v>
       </c>
       <c r="B53" s="9">
-        <v>46162.39182628472</v>
+        <v>46162.558492951386</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46162.481713622685</v>
+        <v>46162.64838028935</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>192</v>
@@ -5151,11 +5151,11 @@
         <v>195</v>
       </c>
       <c r="B54" s="5">
-        <v>46162.391829942135</v>
+        <v>46162.55849660879</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46162.48172633102</v>
+        <v>46162.64839299768</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>192</v>
@@ -5200,11 +5200,11 @@
         <v>196</v>
       </c>
       <c r="B55" s="9">
-        <v>46162.3918325</v>
+        <v>46162.55849916667</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46162.48173832176</v>
+        <v>46162.64840498843</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>192</v>
@@ -5249,11 +5249,11 @@
         <v>197</v>
       </c>
       <c r="B56" s="5">
-        <v>46162.391835092596</v>
+        <v>46162.55850175926</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46162.48176515046</v>
+        <v>46162.64843181713</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>198</v>
@@ -5298,11 +5298,11 @@
         <v>199</v>
       </c>
       <c r="B57" s="9">
-        <v>46162.39544947917</v>
+        <v>46162.56211614583</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46162.481832731486</v>
+        <v>46162.64849939814</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>198</v>
@@ -5347,11 +5347,11 @@
         <v>200</v>
       </c>
       <c r="B58" s="5">
-        <v>46162.39545730324</v>
+        <v>46162.56212396991</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46162.48185784722</v>
+        <v>46162.64852451389</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>198</v>
@@ -5396,11 +5396,11 @@
         <v>201</v>
       </c>
       <c r="B59" s="9">
-        <v>46162.395468310184</v>
+        <v>46162.56213497685</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46162.481872743054</v>
+        <v>46162.648539409725</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>198</v>
@@ -5445,11 +5445,11 @@
         <v>202</v>
       </c>
       <c r="B60" s="5">
-        <v>46162.39548839121</v>
+        <v>46162.562155057865</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46162.48188298611</v>
+        <v>46162.648549652775</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>198</v>
@@ -5494,11 +5494,11 @@
         <v>203</v>
       </c>
       <c r="B61" s="9">
-        <v>46162.39549638889</v>
+        <v>46162.562163055554</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46162.48192523148</v>
+        <v>46162.64859189815</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>198</v>
@@ -5543,11 +5543,11 @@
         <v>204</v>
       </c>
       <c r="B62" s="5">
-        <v>46162.395504375</v>
+        <v>46162.56217104167</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46162.48193898148</v>
+        <v>46162.64860564815</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>198</v>
@@ -5592,11 +5592,11 @@
         <v>205</v>
       </c>
       <c r="B63" s="9">
-        <v>46162.395512268515</v>
+        <v>46162.562178935186</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46162.48196412037</v>
+        <v>46162.64863078704</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>198</v>
@@ -5641,11 +5641,11 @@
         <v>206</v>
       </c>
       <c r="B64" s="5">
-        <v>46162.391837766205</v>
+        <v>46162.55850443287</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46162.43817887732</v>
+        <v>46162.60484554398</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>207</v>
@@ -5688,11 +5688,11 @@
         <v>209</v>
       </c>
       <c r="B65" s="9">
-        <v>46162.39184087963</v>
+        <v>46162.558507546295</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46162.50513989583</v>
+        <v>46162.6718065625</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>210</v>
@@ -5751,11 +5751,11 @@
         <v>214</v>
       </c>
       <c r="B66" s="5">
-        <v>46162.391845474536</v>
+        <v>46162.5585121412</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46162.50521819445</v>
+        <v>46162.67188486111</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>215</v>
@@ -5814,11 +5814,11 @@
         <v>218</v>
       </c>
       <c r="B67" s="9">
-        <v>46162.39185197916</v>
+        <v>46162.558518645834</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46162.50513730324</v>
+        <v>46162.671803969904</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>219</v>
@@ -5877,11 +5877,11 @@
         <v>221</v>
       </c>
       <c r="B68" s="5">
-        <v>46162.391856574075</v>
+        <v>46162.55852324074</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46162.50521534722</v>
+        <v>46162.67188201389</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>222</v>
@@ -5940,11 +5940,11 @@
         <v>224</v>
       </c>
       <c r="B69" s="9">
-        <v>46162.39186078704</v>
+        <v>46162.5585274537</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46162.50513336806</v>
+        <v>46162.67180003472</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>225</v>
@@ -6003,11 +6003,11 @@
         <v>227</v>
       </c>
       <c r="B70" s="5">
-        <v>46162.3918647338</v>
+        <v>46162.558531400464</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46162.50521163194</v>
+        <v>46162.67187829861</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>226</v>
@@ -6066,11 +6066,11 @@
         <v>229</v>
       </c>
       <c r="B71" s="9">
-        <v>46162.391868900464</v>
+        <v>46162.55853556713</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46162.44473074074</v>
+        <v>46162.61139740741</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>230</v>
@@ -6113,11 +6113,11 @@
         <v>232</v>
       </c>
       <c r="B72" s="5">
-        <v>46162.39187140046</v>
+        <v>46162.558538067125</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46162.505567037035</v>
+        <v>46162.672233703706</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>233</v>
@@ -6176,11 +6176,11 @@
         <v>237</v>
       </c>
       <c r="B73" s="9">
-        <v>46162.391875891204</v>
+        <v>46162.558542557876</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46162.50557039352</v>
+        <v>46162.672237060186</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>192</v>
@@ -6229,11 +6229,11 @@
         <v>240</v>
       </c>
       <c r="B74" s="5">
-        <v>46162.39188173611</v>
+        <v>46162.558548402776</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46162.50556710648</v>
+        <v>46162.67223377315</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>192</v>
@@ -6282,11 +6282,11 @@
         <v>243</v>
       </c>
       <c r="B75" s="9">
-        <v>46162.391887453705</v>
+        <v>46162.55855412037</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46162.505563865736</v>
+        <v>46162.67223053241</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>192</v>
@@ -6335,11 +6335,11 @@
         <v>244</v>
       </c>
       <c r="B76" s="5">
-        <v>46162.39189333333</v>
+        <v>46162.558560000005</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46162.50556071759</v>
+        <v>46162.67222738426</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>192</v>
@@ -6388,11 +6388,11 @@
         <v>246</v>
       </c>
       <c r="B77" s="9">
-        <v>46162.39189900463</v>
+        <v>46162.558565671294</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46162.505556944445</v>
+        <v>46162.67222361111</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>198</v>
@@ -6441,11 +6441,11 @@
         <v>248</v>
       </c>
       <c r="B78" s="5">
-        <v>46162.393521122685</v>
+        <v>46162.56018778935</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46162.50555353009</v>
+        <v>46162.672220196764</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>198</v>
@@ -6494,11 +6494,11 @@
         <v>250</v>
       </c>
       <c r="B79" s="9">
-        <v>46162.393541122685</v>
+        <v>46162.560207789356</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46162.50555027778</v>
+        <v>46162.67221694444</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>198</v>
@@ -6547,11 +6547,11 @@
         <v>251</v>
       </c>
       <c r="B80" s="5">
-        <v>46162.39355087963</v>
+        <v>46162.5602175463</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46162.50554719908</v>
+        <v>46162.67221386574</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>198</v>
@@ -6600,11 +6600,11 @@
         <v>252</v>
       </c>
       <c r="B81" s="9">
-        <v>46162.39355974537</v>
+        <v>46162.56022641204</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46162.50554429398</v>
+        <v>46162.67221096065</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>198</v>
@@ -6653,11 +6653,11 @@
         <v>253</v>
       </c>
       <c r="B82" s="5">
-        <v>46162.393567928244</v>
+        <v>46162.56023459491</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46162.50553511574</v>
+        <v>46162.67220178241</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>198</v>
@@ -6706,11 +6706,11 @@
         <v>254</v>
       </c>
       <c r="B83" s="9">
-        <v>46162.393576180555</v>
+        <v>46162.56024284722</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46162.50553436343</v>
+        <v>46162.67220103009</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>198</v>
@@ -6759,11 +6759,11 @@
         <v>255</v>
       </c>
       <c r="B84" s="5">
-        <v>46162.39358395833</v>
+        <v>46162.560250625</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46162.50553359954</v>
+        <v>46162.6722002662</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>198</v>
@@ -6812,11 +6812,11 @@
         <v>256</v>
       </c>
       <c r="B85" s="9">
-        <v>46162.39195396991</v>
+        <v>46162.55862063657</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46162.50582612268</v>
+        <v>46162.67249278935</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>257</v>
@@ -6875,11 +6875,11 @@
         <v>259</v>
       </c>
       <c r="B86" s="5">
-        <v>46162.391959953704</v>
+        <v>46162.558626620375</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46162.505739409724</v>
+        <v>46162.67240607639</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>192</v>
@@ -6928,11 +6928,11 @@
         <v>262</v>
       </c>
       <c r="B87" s="9">
-        <v>46162.39196613426</v>
+        <v>46162.55863280092</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46162.5057364699</v>
+        <v>46162.672403136574</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>192</v>
@@ -6981,11 +6981,11 @@
         <v>263</v>
       </c>
       <c r="B88" s="5">
-        <v>46162.391971840276</v>
+        <v>46162.55863850695</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46162.50573309028</v>
+        <v>46162.67239975695</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>192</v>
@@ -7034,11 +7034,11 @@
         <v>265</v>
       </c>
       <c r="B89" s="9">
-        <v>46162.39197758102</v>
+        <v>46162.558644247685</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46162.5057303588</v>
+        <v>46162.67239702547</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>192</v>
@@ -7087,11 +7087,11 @@
         <v>266</v>
       </c>
       <c r="B90" s="5">
-        <v>46162.39198324074</v>
+        <v>46162.55864990741</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46162.50572736112</v>
+        <v>46162.67239402777</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>198</v>
@@ -7140,11 +7140,11 @@
         <v>268</v>
       </c>
       <c r="B91" s="9">
-        <v>46162.39481349537</v>
+        <v>46162.56148016204</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46162.50572439814</v>
+        <v>46162.672391064814</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>198</v>
@@ -7193,11 +7193,11 @@
         <v>269</v>
       </c>
       <c r="B92" s="5">
-        <v>46162.39482253473</v>
+        <v>46162.561489201384</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46162.50572107639</v>
+        <v>46162.672387743056</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>198</v>
@@ -7246,11 +7246,11 @@
         <v>270</v>
       </c>
       <c r="B93" s="9">
-        <v>46162.39483263889</v>
+        <v>46162.56149930556</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46162.50571813657</v>
+        <v>46162.67238480324</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>198</v>
@@ -7299,11 +7299,11 @@
         <v>271</v>
       </c>
       <c r="B94" s="5">
-        <v>46162.394840532404</v>
+        <v>46162.561507199076</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46162.50571546296</v>
+        <v>46162.67238212963</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>198</v>
@@ -7352,11 +7352,11 @@
         <v>272</v>
       </c>
       <c r="B95" s="9">
-        <v>46162.39484946759</v>
+        <v>46162.56151613426</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46162.505707268516</v>
+        <v>46162.67237393519</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>198</v>
@@ -7405,11 +7405,11 @@
         <v>273</v>
       </c>
       <c r="B96" s="5">
-        <v>46162.394857465275</v>
+        <v>46162.56152413195</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46162.5057065625</v>
+        <v>46162.67237322917</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>198</v>
@@ -7458,11 +7458,11 @@
         <v>274</v>
       </c>
       <c r="B97" s="9">
-        <v>46162.394864525464</v>
+        <v>46162.56153119213</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46162.505705902775</v>
+        <v>46162.67237256945</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>198</v>
@@ -7511,11 +7511,11 @@
         <v>275</v>
       </c>
       <c r="B98" s="5">
-        <v>46162.39198773148</v>
+        <v>46162.55865439815</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46162.50712538195</v>
+        <v>46162.67379204861</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>276</v>
@@ -7574,11 +7574,11 @@
         <v>278</v>
       </c>
       <c r="B99" s="9">
-        <v>46162.39199243055</v>
+        <v>46162.55865909722</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46162.50709849537</v>
+        <v>46162.673765162035</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>192</v>
@@ -7627,11 +7627,11 @@
         <v>280</v>
       </c>
       <c r="B100" s="5">
-        <v>46162.39199834491</v>
+        <v>46162.55866501157</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46162.50709784722</v>
+        <v>46162.67376451389</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>192</v>
@@ -7680,11 +7680,11 @@
         <v>282</v>
       </c>
       <c r="B101" s="9">
-        <v>46162.39200417824</v>
+        <v>46162.55867084491</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46162.50709716435</v>
+        <v>46162.673763831015</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>192</v>
@@ -7733,11 +7733,11 @@
         <v>284</v>
       </c>
       <c r="B102" s="5">
-        <v>46162.392009930554</v>
+        <v>46162.558676597226</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46162.50709648148</v>
+        <v>46162.67376314815</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>192</v>
@@ -7786,11 +7786,11 @@
         <v>286</v>
       </c>
       <c r="B103" s="9">
-        <v>46162.392015729165</v>
+        <v>46162.55868239583</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46162.507095810186</v>
+        <v>46162.67376247685</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>198</v>
@@ -7839,11 +7839,11 @@
         <v>288</v>
       </c>
       <c r="B104" s="5">
-        <v>46162.39510167824</v>
+        <v>46162.56176834491</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46162.50709515046</v>
+        <v>46162.67376181713</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>198</v>
@@ -7892,11 +7892,11 @@
         <v>289</v>
       </c>
       <c r="B105" s="9">
-        <v>46162.39511003472</v>
+        <v>46162.56177670139</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46162.50709424769</v>
+        <v>46162.67376091435</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>198</v>
@@ -7945,11 +7945,11 @@
         <v>291</v>
       </c>
       <c r="B106" s="5">
-        <v>46162.395118078704</v>
+        <v>46162.56178474537</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46162.50709356481</v>
+        <v>46162.67376023148</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>198</v>
@@ -7998,11 +7998,11 @@
         <v>292</v>
       </c>
       <c r="B107" s="9">
-        <v>46162.39512631945</v>
+        <v>46162.56179298611</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46162.50709290509</v>
+        <v>46162.67375957176</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>198</v>
@@ -8051,11 +8051,11 @@
         <v>293</v>
       </c>
       <c r="B108" s="5">
-        <v>46162.39513427083</v>
+        <v>46162.5618009375</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46162.50709221065</v>
+        <v>46162.67375887731</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>198</v>
@@ -8104,11 +8104,11 @@
         <v>294</v>
       </c>
       <c r="B109" s="9">
-        <v>46162.395142430556</v>
+        <v>46162.56180909723</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46162.507091527776</v>
+        <v>46162.67375819445</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>198</v>
@@ -8157,11 +8157,11 @@
         <v>295</v>
       </c>
       <c r="B110" s="5">
-        <v>46162.39515049769</v>
+        <v>46162.56181716435</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46162.50709084491</v>
+        <v>46162.67375751157</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>198</v>
@@ -8210,11 +8210,11 @@
         <v>296</v>
       </c>
       <c r="B111" s="9">
-        <v>46162.392019837964</v>
+        <v>46162.55868650463</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46162.44799885417</v>
+        <v>46162.61466552083</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>207</v>
@@ -8257,11 +8257,11 @@
         <v>298</v>
       </c>
       <c r="B112" s="5">
-        <v>46162.392023402776</v>
+        <v>46162.55869006945</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46162.507235694444</v>
+        <v>46162.673902361115</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>299</v>
@@ -8320,11 +8320,11 @@
         <v>301</v>
       </c>
       <c r="B113" s="9">
-        <v>46162.39203025463</v>
+        <v>46162.558696921296</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46162.50723224537</v>
+        <v>46162.673898912035</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>302</v>
@@ -8383,11 +8383,11 @@
         <v>304</v>
       </c>
       <c r="B114" s="5">
-        <v>46162.39203618055</v>
+        <v>46162.55870284722</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46162.50722951389</v>
+        <v>46162.67389618055</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>305</v>
@@ -8446,11 +8446,11 @@
         <v>307</v>
       </c>
       <c r="B115" s="9">
-        <v>46162.392042962965</v>
+        <v>46162.55870962963</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46162.50722515046</v>
+        <v>46162.67389181713</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>308</v>
@@ -8509,11 +8509,11 @@
         <v>310</v>
       </c>
       <c r="B116" s="5">
-        <v>46162.39205202546</v>
+        <v>46162.55871869213</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46162.481086562504</v>
+        <v>46162.64775322917</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>311</v>
@@ -8556,11 +8556,11 @@
         <v>313</v>
       </c>
       <c r="B117" s="9">
-        <v>46162.39205556713</v>
+        <v>46162.55872223379</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46162.507339918986</v>
+        <v>46162.67400658564</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>314</v>
@@ -8619,11 +8619,11 @@
         <v>316</v>
       </c>
       <c r="B118" s="5">
-        <v>46162.3920640162</v>
+        <v>46162.55873068287</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46162.5075959838</v>
+        <v>46162.674262650464</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>192</v>
@@ -8672,11 +8672,11 @@
         <v>318</v>
       </c>
       <c r="B119" s="9">
-        <v>46162.39206834491</v>
+        <v>46162.558735011575</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46162.507592546295</v>
+        <v>46162.67425921296</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>192</v>
@@ -8725,11 +8725,11 @@
         <v>319</v>
       </c>
       <c r="B120" s="5">
-        <v>46162.39207284722</v>
+        <v>46162.55873951389</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46162.507589664354</v>
+        <v>46162.67425633102</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>192</v>
@@ -8778,11 +8778,11 @@
         <v>321</v>
       </c>
       <c r="B121" s="9">
-        <v>46162.392077199074</v>
+        <v>46162.55874386574</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46162.50758671296</v>
+        <v>46162.674253379635</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>192</v>
@@ -8831,11 +8831,11 @@
         <v>322</v>
       </c>
       <c r="B122" s="5">
-        <v>46162.39208146991</v>
+        <v>46162.55874813657</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46162.50758333333</v>
+        <v>46162.67425</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>198</v>
@@ -8884,11 +8884,11 @@
         <v>323</v>
       </c>
       <c r="B123" s="9">
-        <v>46162.398500358795</v>
+        <v>46162.56516702546</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46162.5075803588</v>
+        <v>46162.67424702546</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>198</v>
@@ -8937,11 +8937,11 @@
         <v>324</v>
       </c>
       <c r="B124" s="5">
-        <v>46162.398507164355</v>
+        <v>46162.56517383102</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46162.507577627315</v>
+        <v>46162.67424429399</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>198</v>
@@ -8990,11 +8990,11 @@
         <v>325</v>
       </c>
       <c r="B125" s="9">
-        <v>46162.3985144676</v>
+        <v>46162.565181134254</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46162.50756665509</v>
+        <v>46162.674233321755</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>198</v>
@@ -9043,11 +9043,11 @@
         <v>326</v>
       </c>
       <c r="B126" s="5">
-        <v>46162.39852253472</v>
+        <v>46162.565189201385</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46162.50756597222</v>
+        <v>46162.67423263889</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>198</v>
@@ -9096,11 +9096,11 @@
         <v>327</v>
       </c>
       <c r="B127" s="9">
-        <v>46162.39853013889</v>
+        <v>46162.56519680556</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46162.507565277774</v>
+        <v>46162.674231944446</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>198</v>
@@ -9149,11 +9149,11 @@
         <v>328</v>
       </c>
       <c r="B128" s="5">
-        <v>46162.39853892361</v>
+        <v>46162.565205590276</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46162.50756459491</v>
+        <v>46162.674231261575</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>198</v>
@@ -9202,11 +9202,11 @@
         <v>329</v>
       </c>
       <c r="B129" s="9">
-        <v>46162.39854534723</v>
+        <v>46162.565212013884</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46162.507563935185</v>
+        <v>46162.67423060186</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>198</v>
@@ -9255,11 +9255,11 @@
         <v>330</v>
       </c>
       <c r="B130" s="5">
-        <v>46162.39208488426</v>
+        <v>46162.558751550925</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46162.50733674769</v>
+        <v>46162.67400341435</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>331</v>
@@ -9318,11 +9318,11 @@
         <v>332</v>
       </c>
       <c r="B131" s="9">
-        <v>46162.39208957176</v>
+        <v>46162.558756238424</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46162.50773142361</v>
+        <v>46162.67439809028</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>192</v>
@@ -9369,11 +9369,11 @@
         <v>335</v>
       </c>
       <c r="B132" s="5">
-        <v>46162.39209538195</v>
+        <v>46162.55876204861</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46162.5077284375</v>
+        <v>46162.67439510417</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>192</v>
@@ -9420,11 +9420,11 @@
         <v>337</v>
       </c>
       <c r="B133" s="9">
-        <v>46162.39210078704</v>
+        <v>46162.55876745371</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46162.50772525463</v>
+        <v>46162.6743919213</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>192</v>
@@ -9471,11 +9471,11 @@
         <v>340</v>
       </c>
       <c r="B134" s="5">
-        <v>46162.39210722222</v>
+        <v>46162.558773888886</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46162.50772170139</v>
+        <v>46162.674388368054</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>192</v>
@@ -9522,11 +9522,11 @@
         <v>341</v>
       </c>
       <c r="B135" s="9">
-        <v>46162.39216076389</v>
+        <v>46162.558827430556</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46162.50771856481</v>
+        <v>46162.67438523148</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>198</v>
@@ -9573,11 +9573,11 @@
         <v>343</v>
       </c>
       <c r="B136" s="5">
-        <v>46162.39881056713</v>
+        <v>46162.565477233795</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46162.50771523148</v>
+        <v>46162.67438189815</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>198</v>
@@ -9624,11 +9624,11 @@
         <v>345</v>
       </c>
       <c r="B137" s="9">
-        <v>46162.398818726855</v>
+        <v>46162.56548539352</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46162.50771204861</v>
+        <v>46162.67437871528</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>198</v>
@@ -9675,11 +9675,11 @@
         <v>347</v>
       </c>
       <c r="B138" s="5">
-        <v>46162.39882753472</v>
+        <v>46162.56549420139</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46162.507704131946</v>
+        <v>46162.67437079861</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>198</v>
@@ -9726,11 +9726,11 @@
         <v>348</v>
       </c>
       <c r="B139" s="9">
-        <v>46162.39883314815</v>
+        <v>46162.56549981482</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46162.50770346065</v>
+        <v>46162.674370127315</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>198</v>
@@ -9777,11 +9777,11 @@
         <v>350</v>
       </c>
       <c r="B140" s="5">
-        <v>46162.39884105324</v>
+        <v>46162.565507719904</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46162.50770244213</v>
+        <v>46162.6743691088</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>198</v>
@@ -9828,11 +9828,11 @@
         <v>351</v>
       </c>
       <c r="B141" s="9">
-        <v>46162.39884971065</v>
+        <v>46162.56551637732</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46162.50769734954</v>
+        <v>46162.6743640162</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>198</v>
@@ -9879,11 +9879,11 @@
         <v>353</v>
       </c>
       <c r="B142" s="5">
-        <v>46162.399315393515</v>
+        <v>46162.56598206019</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46162.507695636574</v>
+        <v>46162.67436230324</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>198</v>
@@ -9930,11 +9930,11 @@
         <v>354</v>
       </c>
       <c r="B143" s="9">
-        <v>46162.392166875</v>
+        <v>46162.55883354167</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46162.507333483794</v>
+        <v>46162.674000150466</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>355</v>
@@ -9993,11 +9993,11 @@
         <v>356</v>
       </c>
       <c r="B144" s="5">
-        <v>46162.392172314816</v>
+        <v>46162.55883898148</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46162.50787094908</v>
+        <v>46162.67453761574</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>192</v>
@@ -10046,11 +10046,11 @@
         <v>358</v>
       </c>
       <c r="B145" s="9">
-        <v>46162.39217951389</v>
+        <v>46162.55884618056</v>
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46162.507867939814</v>
+        <v>46162.674534606485</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>192</v>
@@ -10099,11 +10099,11 @@
         <v>360</v>
       </c>
       <c r="B146" s="5">
-        <v>46162.392186689816</v>
+        <v>46162.55885335648</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46162.507864907406</v>
+        <v>46162.67453157407</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>192</v>
@@ -10152,11 +10152,11 @@
         <v>362</v>
       </c>
       <c r="B147" s="9">
-        <v>46162.39219395834</v>
+        <v>46162.558860624995</v>
       </c>
       <c r="C147" s="10"/>
       <c r="D147" s="9">
-        <v>46162.50786150463</v>
+        <v>46162.674528171294</v>
       </c>
       <c r="E147" s="10" t="s">
         <v>192</v>
@@ -10205,11 +10205,11 @@
         <v>364</v>
       </c>
       <c r="B148" s="5">
-        <v>46162.39220072917</v>
+        <v>46162.558867395834</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46162.50785829861</v>
+        <v>46162.674524965274</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>198</v>
@@ -10258,11 +10258,11 @@
         <v>366</v>
       </c>
       <c r="B149" s="9">
-        <v>46162.399479699074</v>
+        <v>46162.566146365745</v>
       </c>
       <c r="C149" s="10"/>
       <c r="D149" s="9">
-        <v>46162.5078546875</v>
+        <v>46162.674521354165</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>198</v>
@@ -10311,11 +10311,11 @@
         <v>368</v>
       </c>
       <c r="B150" s="5">
-        <v>46162.399486435184</v>
+        <v>46162.566153101856</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46162.5078512037</v>
+        <v>46162.67451787037</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>198</v>
@@ -10364,11 +10364,11 @@
         <v>369</v>
       </c>
       <c r="B151" s="9">
-        <v>46162.399504444445</v>
+        <v>46162.56617111111</v>
       </c>
       <c r="C151" s="10"/>
       <c r="D151" s="9">
-        <v>46162.50784835649</v>
+        <v>46162.67451502314</v>
       </c>
       <c r="E151" s="10" t="s">
         <v>198</v>
@@ -10417,11 +10417,11 @@
         <v>370</v>
       </c>
       <c r="B152" s="5">
-        <v>46162.399514386576</v>
+        <v>46162.56618105324</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46162.50784576389</v>
+        <v>46162.67451243056</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>349</v>
@@ -10470,11 +10470,11 @@
         <v>371</v>
       </c>
       <c r="B153" s="9">
-        <v>46162.39952320602</v>
+        <v>46162.56618987268</v>
       </c>
       <c r="C153" s="10"/>
       <c r="D153" s="9">
-        <v>46162.507836689816</v>
+        <v>46162.67450335648</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>198</v>
@@ -10523,11 +10523,11 @@
         <v>372</v>
       </c>
       <c r="B154" s="5">
-        <v>46162.39953605324</v>
+        <v>46162.56620271991</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46162.507835972225</v>
+        <v>46162.67450263889</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>198</v>
@@ -10576,11 +10576,11 @@
         <v>373</v>
       </c>
       <c r="B155" s="9">
-        <v>46162.39954006944</v>
+        <v>46162.56620673611</v>
       </c>
       <c r="C155" s="10"/>
       <c r="D155" s="9">
-        <v>46162.507835219905</v>
+        <v>46162.67450188658</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>198</v>
@@ -10629,11 +10629,11 @@
         <v>374</v>
       </c>
       <c r="B156" s="5">
-        <v>46162.3922049074</v>
+        <v>46162.558871574074</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46162.507330532404</v>
+        <v>46162.673997199076</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>375</v>
@@ -10692,11 +10692,11 @@
         <v>377</v>
       </c>
       <c r="B157" s="9">
-        <v>46162.39220956019</v>
+        <v>46162.55887622685</v>
       </c>
       <c r="C157" s="10"/>
       <c r="D157" s="9">
-        <v>46162.50802770833</v>
+        <v>46162.674694375004</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>192</v>
@@ -10745,11 +10745,11 @@
         <v>380</v>
       </c>
       <c r="B158" s="5">
-        <v>46162.39221634259</v>
+        <v>46162.55888300926</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46162.50802435185</v>
+        <v>46162.67469101852</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>192</v>
@@ -10798,11 +10798,11 @@
         <v>381</v>
       </c>
       <c r="B159" s="9">
-        <v>46162.39222591435</v>
+        <v>46162.558892581015</v>
       </c>
       <c r="C159" s="10"/>
       <c r="D159" s="9">
-        <v>46162.50802126157</v>
+        <v>46162.674687928244</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>192</v>
@@ -10851,11 +10851,11 @@
         <v>383</v>
       </c>
       <c r="B160" s="5">
-        <v>46162.3922319213</v>
+        <v>46162.55889858796</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46162.50801846065</v>
+        <v>46162.67468512732</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>192</v>
@@ -10904,11 +10904,11 @@
         <v>385</v>
       </c>
       <c r="B161" s="9">
-        <v>46162.39223795139</v>
+        <v>46162.558904618054</v>
       </c>
       <c r="C161" s="10"/>
       <c r="D161" s="9">
-        <v>46162.50801568287</v>
+        <v>46162.674682349534</v>
       </c>
       <c r="E161" s="10" t="s">
         <v>198</v>
@@ -10957,11 +10957,11 @@
         <v>387</v>
       </c>
       <c r="B162" s="5">
-        <v>46162.399712708335</v>
+        <v>46162.566379375</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46162.50801222222</v>
+        <v>46162.674678888885</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>198</v>
@@ -11010,11 +11010,11 @@
         <v>390</v>
       </c>
       <c r="B163" s="9">
-        <v>46162.39972028935</v>
+        <v>46162.56638695602</v>
       </c>
       <c r="C163" s="10"/>
       <c r="D163" s="9">
-        <v>46162.50800920139</v>
+        <v>46162.67467586805</v>
       </c>
       <c r="E163" s="10" t="s">
         <v>198</v>
@@ -11063,11 +11063,11 @@
         <v>391</v>
       </c>
       <c r="B164" s="5">
-        <v>46162.39972865741</v>
+        <v>46162.56639532407</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46162.50800648148</v>
+        <v>46162.67467314815</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>198</v>
@@ -11116,11 +11116,11 @@
         <v>393</v>
       </c>
       <c r="B165" s="9">
-        <v>46162.39973752315</v>
+        <v>46162.56640418981</v>
       </c>
       <c r="C165" s="10"/>
       <c r="D165" s="9">
-        <v>46162.508003634255</v>
+        <v>46162.67467030093</v>
       </c>
       <c r="E165" s="10" t="s">
         <v>198</v>
@@ -11169,11 +11169,11 @@
         <v>396</v>
       </c>
       <c r="B166" s="5">
-        <v>46162.39974574074</v>
+        <v>46162.56641240741</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46162.50799572917</v>
+        <v>46162.67466239583</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>198</v>
@@ -11222,11 +11222,11 @@
         <v>397</v>
       </c>
       <c r="B167" s="9">
-        <v>46162.399753668986</v>
+        <v>46162.56642033564</v>
       </c>
       <c r="C167" s="10"/>
       <c r="D167" s="9">
-        <v>46162.507994988424</v>
+        <v>46162.674661655095</v>
       </c>
       <c r="E167" s="10" t="s">
         <v>198</v>
@@ -11275,11 +11275,11 @@
         <v>398</v>
       </c>
       <c r="B168" s="5">
-        <v>46162.39976104167</v>
+        <v>46162.566427708334</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46162.50799430556</v>
+        <v>46162.67466097222</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>198</v>
@@ -11328,11 +11328,11 @@
         <v>399</v>
       </c>
       <c r="B169" s="9">
-        <v>46162.3922422801</v>
+        <v>46162.558908946754</v>
       </c>
       <c r="C169" s="10"/>
       <c r="D169" s="9">
-        <v>46162.50732726852</v>
+        <v>46162.67399393518</v>
       </c>
       <c r="E169" s="10" t="s">
         <v>400</v>
@@ -11391,11 +11391,11 @@
         <v>401</v>
       </c>
       <c r="B170" s="5">
-        <v>46162.39224702546</v>
+        <v>46162.55891369213</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46162.508169189816</v>
+        <v>46162.67483585648</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>192</v>
@@ -11442,11 +11442,11 @@
         <v>403</v>
       </c>
       <c r="B171" s="9">
-        <v>46162.39225263889</v>
+        <v>46162.55891930556</v>
       </c>
       <c r="C171" s="10"/>
       <c r="D171" s="9">
-        <v>46162.50816618056</v>
+        <v>46162.674832847224</v>
       </c>
       <c r="E171" s="10" t="s">
         <v>192</v>
@@ -11493,11 +11493,11 @@
         <v>404</v>
       </c>
       <c r="B172" s="5">
-        <v>46162.39225826389</v>
+        <v>46162.558924930556</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46162.508162962964</v>
+        <v>46162.67482962963</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>192</v>
@@ -11544,11 +11544,11 @@
         <v>406</v>
       </c>
       <c r="B173" s="9">
-        <v>46162.392264375</v>
+        <v>46162.55893104167</v>
       </c>
       <c r="C173" s="10"/>
       <c r="D173" s="9">
-        <v>46162.5081602662</v>
+        <v>46162.67482693287</v>
       </c>
       <c r="E173" s="10" t="s">
         <v>192</v>
@@ -11595,11 +11595,11 @@
         <v>407</v>
       </c>
       <c r="B174" s="5">
-        <v>46162.39226980324</v>
+        <v>46162.55893646991</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46162.508157476856</v>
+        <v>46162.67482414352</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>198</v>
@@ -11646,11 +11646,11 @@
         <v>409</v>
       </c>
       <c r="B175" s="9">
-        <v>46162.40065422453</v>
+        <v>46162.567320891205</v>
       </c>
       <c r="C175" s="10"/>
       <c r="D175" s="9">
-        <v>46162.50815461806</v>
+        <v>46162.67482128472</v>
       </c>
       <c r="E175" s="10" t="s">
         <v>198</v>
@@ -11697,11 +11697,11 @@
         <v>410</v>
       </c>
       <c r="B176" s="5">
-        <v>46162.400663368055</v>
+        <v>46162.567330034726</v>
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46162.5081515162</v>
+        <v>46162.67481818287</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>198</v>
@@ -11748,11 +11748,11 @@
         <v>411</v>
       </c>
       <c r="B177" s="9">
-        <v>46162.40067101852</v>
+        <v>46162.567337685185</v>
       </c>
       <c r="C177" s="10"/>
       <c r="D177" s="9">
-        <v>46162.508148877314</v>
+        <v>46162.674815543985</v>
       </c>
       <c r="E177" s="10" t="s">
         <v>198</v>
@@ -11799,11 +11799,11 @@
         <v>412</v>
       </c>
       <c r="B178" s="5">
-        <v>46162.4006775</v>
+        <v>46162.567344166666</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46162.50814607639</v>
+        <v>46162.674812743055</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>198</v>
@@ -11850,11 +11850,11 @@
         <v>413</v>
       </c>
       <c r="B179" s="9">
-        <v>46162.4006846875</v>
+        <v>46162.56735135417</v>
       </c>
       <c r="C179" s="10"/>
       <c r="D179" s="9">
-        <v>46162.508138310186</v>
+        <v>46162.67480497685</v>
       </c>
       <c r="E179" s="10" t="s">
         <v>198</v>
@@ -11901,11 +11901,11 @@
         <v>414</v>
       </c>
       <c r="B180" s="5">
-        <v>46162.40069239584</v>
+        <v>46162.5673590625</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46162.50813765047</v>
+        <v>46162.674804317125</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>198</v>
@@ -11952,11 +11952,11 @@
         <v>415</v>
       </c>
       <c r="B181" s="9">
-        <v>46162.400699618054</v>
+        <v>46162.567366284726</v>
       </c>
       <c r="C181" s="10"/>
       <c r="D181" s="9">
-        <v>46162.5081369213</v>
+        <v>46162.674803587965</v>
       </c>
       <c r="E181" s="10" t="s">
         <v>198</v>
@@ -12003,11 +12003,11 @@
         <v>416</v>
       </c>
       <c r="B182" s="5">
-        <v>46162.392275011574</v>
+        <v>46162.558941678246</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46162.507321122685</v>
+        <v>46162.673987789356</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>417</v>
@@ -12066,11 +12066,11 @@
         <v>419</v>
       </c>
       <c r="B183" s="9">
-        <v>46162.392280520835</v>
+        <v>46162.5589471875</v>
       </c>
       <c r="C183" s="10"/>
       <c r="D183" s="9">
-        <v>46162.50841818287</v>
+        <v>46162.675084849536</v>
       </c>
       <c r="E183" s="10" t="s">
         <v>192</v>
@@ -12117,11 +12117,11 @@
         <v>421</v>
       </c>
       <c r="B184" s="5">
-        <v>46162.39228517361</v>
+        <v>46162.55895184028</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46162.5084152662</v>
+        <v>46162.67508193287</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>192</v>
@@ -12168,11 +12168,11 @@
         <v>422</v>
       </c>
       <c r="B185" s="9">
-        <v>46162.39228988426</v>
+        <v>46162.55895655093</v>
       </c>
       <c r="C185" s="10"/>
       <c r="D185" s="9">
-        <v>46162.50841202546</v>
+        <v>46162.67507869213</v>
       </c>
       <c r="E185" s="10" t="s">
         <v>192</v>
@@ -12219,11 +12219,11 @@
         <v>424</v>
       </c>
       <c r="B186" s="5">
-        <v>46162.392329270835</v>
+        <v>46162.5589959375</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46162.50840944445</v>
+        <v>46162.67507611111</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>192</v>
@@ -12270,11 +12270,11 @@
         <v>425</v>
       </c>
       <c r="B187" s="9">
-        <v>46162.39233469908</v>
+        <v>46162.55900136574</v>
       </c>
       <c r="C187" s="10"/>
       <c r="D187" s="9">
-        <v>46162.50840641204</v>
+        <v>46162.6750730787</v>
       </c>
       <c r="E187" s="10" t="s">
         <v>198</v>
@@ -12321,11 +12321,11 @@
         <v>427</v>
       </c>
       <c r="B188" s="5">
-        <v>46162.40092486111</v>
+        <v>46162.56759152778</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46162.50840348379</v>
+        <v>46162.675070150464</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>198</v>
@@ -12372,11 +12372,11 @@
         <v>428</v>
       </c>
       <c r="B189" s="9">
-        <v>46162.40093179398</v>
+        <v>46162.56759846065</v>
       </c>
       <c r="C189" s="10"/>
       <c r="D189" s="9">
-        <v>46162.50840078703</v>
+        <v>46162.6750674537</v>
       </c>
       <c r="E189" s="10" t="s">
         <v>198</v>
@@ -12423,11 +12423,11 @@
         <v>429</v>
       </c>
       <c r="B190" s="5">
-        <v>46162.4009400463</v>
+        <v>46162.56760671297</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46162.50839821759</v>
+        <v>46162.67506488426</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>198</v>
@@ -12474,11 +12474,11 @@
         <v>430</v>
       </c>
       <c r="B191" s="9">
-        <v>46162.4009475</v>
+        <v>46162.56761416666</v>
       </c>
       <c r="C191" s="10"/>
       <c r="D191" s="9">
-        <v>46162.50839497685</v>
+        <v>46162.67506164352</v>
       </c>
       <c r="E191" s="10" t="s">
         <v>198</v>
@@ -12525,11 +12525,11 @@
         <v>431</v>
       </c>
       <c r="B192" s="5">
-        <v>46162.400955543984</v>
+        <v>46162.56762221065</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46162.508387800925</v>
+        <v>46162.67505446759</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>198</v>
@@ -12576,11 +12576,11 @@
         <v>432</v>
       </c>
       <c r="B193" s="9">
-        <v>46162.400961886575</v>
+        <v>46162.56762855324</v>
       </c>
       <c r="C193" s="10"/>
       <c r="D193" s="9">
-        <v>46162.50838708333</v>
+        <v>46162.675053750005</v>
       </c>
       <c r="E193" s="10" t="s">
         <v>198</v>
@@ -12627,11 +12627,11 @@
         <v>433</v>
       </c>
       <c r="B194" s="5">
-        <v>46162.40096748843</v>
+        <v>46162.56763415509</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46162.508386354166</v>
+        <v>46162.67505302084</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>198</v>
@@ -12678,11 +12678,11 @@
         <v>434</v>
       </c>
       <c r="B195" s="9">
-        <v>46162.39233899306</v>
+        <v>46162.55900565972</v>
       </c>
       <c r="C195" s="10"/>
       <c r="D195" s="9">
-        <v>46162.49727244213</v>
+        <v>46162.663939108796</v>
       </c>
       <c r="E195" s="10" t="s">
         <v>435</v>
@@ -12725,11 +12725,11 @@
         <v>437</v>
       </c>
       <c r="B196" s="5">
-        <v>46162.392342743056</v>
+        <v>46162.55900940972</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46162.508735625</v>
+        <v>46162.67540229167</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>438</v>
@@ -12788,11 +12788,11 @@
         <v>442</v>
       </c>
       <c r="B197" s="9">
-        <v>46162.39234835649</v>
+        <v>46162.559015023144</v>
       </c>
       <c r="C197" s="10"/>
       <c r="D197" s="9">
-        <v>46162.508718391204</v>
+        <v>46162.67538505787</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>192</v>
@@ -12839,11 +12839,11 @@
         <v>444</v>
       </c>
       <c r="B198" s="5">
-        <v>46162.39235273148</v>
+        <v>46162.55901939815</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46162.508715868054</v>
+        <v>46162.675382534726</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>192</v>
@@ -12890,11 +12890,11 @@
         <v>445</v>
       </c>
       <c r="B199" s="9">
-        <v>46162.39235722223</v>
+        <v>46162.55902388888</v>
       </c>
       <c r="C199" s="10"/>
       <c r="D199" s="9">
-        <v>46162.50871324074</v>
+        <v>46162.67537990741</v>
       </c>
       <c r="E199" s="10" t="s">
         <v>192</v>
@@ -12941,11 +12941,11 @@
         <v>446</v>
       </c>
       <c r="B200" s="5">
-        <v>46162.39236142361</v>
+        <v>46162.559028090276</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46162.508710486116</v>
+        <v>46162.67537715277</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>192</v>
@@ -12992,11 +12992,11 @@
         <v>447</v>
       </c>
       <c r="B201" s="9">
-        <v>46162.39236539352</v>
+        <v>46162.559032060184</v>
       </c>
       <c r="C201" s="10"/>
       <c r="D201" s="9">
-        <v>46162.50870751157</v>
+        <v>46162.675374178245</v>
       </c>
       <c r="E201" s="10" t="s">
         <v>198</v>
@@ -13043,11 +13043,11 @@
         <v>449</v>
       </c>
       <c r="B202" s="5">
-        <v>46162.40180416667</v>
+        <v>46162.56847083333</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46162.508704629625</v>
+        <v>46162.675371296296</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>198</v>
@@ -13094,11 +13094,11 @@
         <v>450</v>
       </c>
       <c r="B203" s="9">
-        <v>46162.40181119213</v>
+        <v>46162.5684778588</v>
       </c>
       <c r="C203" s="10"/>
       <c r="D203" s="9">
-        <v>46162.5087016551</v>
+        <v>46162.675368321754</v>
       </c>
       <c r="E203" s="10" t="s">
         <v>198</v>
@@ -13145,11 +13145,11 @@
         <v>451</v>
       </c>
       <c r="B204" s="5">
-        <v>46162.40181916667</v>
+        <v>46162.56848583333</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46162.50869899306</v>
+        <v>46162.67536565972</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>198</v>
@@ -13196,11 +13196,11 @@
         <v>452</v>
       </c>
       <c r="B205" s="9">
-        <v>46162.40182649306</v>
+        <v>46162.56849315972</v>
       </c>
       <c r="C205" s="10"/>
       <c r="D205" s="9">
-        <v>46162.508696296296</v>
+        <v>46162.67536296297</v>
       </c>
       <c r="E205" s="10" t="s">
         <v>198</v>
@@ -13247,11 +13247,11 @@
         <v>453</v>
       </c>
       <c r="B206" s="5">
-        <v>46162.4018324537</v>
+        <v>46162.568499120374</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46162.50868840278</v>
+        <v>46162.67535506944</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>198</v>
@@ -13298,11 +13298,11 @@
         <v>454</v>
       </c>
       <c r="B207" s="9">
-        <v>46162.40184034722</v>
+        <v>46162.568507013886</v>
       </c>
       <c r="C207" s="10"/>
       <c r="D207" s="9">
-        <v>46162.50868773148</v>
+        <v>46162.67535439815</v>
       </c>
       <c r="E207" s="10" t="s">
         <v>198</v>
@@ -13349,11 +13349,11 @@
         <v>455</v>
       </c>
       <c r="B208" s="5">
-        <v>46162.40184909722</v>
+        <v>46162.56851576389</v>
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46162.508687071764</v>
+        <v>46162.67535373842</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>198</v>
@@ -13400,11 +13400,11 @@
         <v>456</v>
       </c>
       <c r="B209" s="9">
-        <v>46162.39236931713</v>
+        <v>46162.559035983795</v>
       </c>
       <c r="C209" s="10"/>
       <c r="D209" s="9">
-        <v>46162.50893476851</v>
+        <v>46162.675601435185</v>
       </c>
       <c r="E209" s="10" t="s">
         <v>457</v>
@@ -13463,11 +13463,11 @@
         <v>458</v>
       </c>
       <c r="B210" s="5">
-        <v>46162.39237339121</v>
+        <v>46162.559040057866</v>
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46162.50892731482</v>
+        <v>46162.67559398148</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>192</v>
@@ -13514,11 +13514,11 @@
         <v>460</v>
       </c>
       <c r="B211" s="9">
-        <v>46162.392377638884</v>
+        <v>46162.559044305555</v>
       </c>
       <c r="C211" s="10"/>
       <c r="D211" s="9">
-        <v>46162.50892451389</v>
+        <v>46162.67559118055</v>
       </c>
       <c r="E211" s="10" t="s">
         <v>192</v>
@@ -13565,11 +13565,11 @@
         <v>461</v>
       </c>
       <c r="B212" s="5">
-        <v>46162.39238175926</v>
+        <v>46162.55904842593</v>
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46162.50892172454</v>
+        <v>46162.675588391205</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>192</v>
@@ -13616,11 +13616,11 @@
         <v>462</v>
       </c>
       <c r="B213" s="9">
-        <v>46162.39238575232</v>
+        <v>46162.55905241898</v>
       </c>
       <c r="C213" s="10"/>
       <c r="D213" s="9">
-        <v>46162.508918935186</v>
+        <v>46162.67558560186</v>
       </c>
       <c r="E213" s="10" t="s">
         <v>192</v>
@@ -13667,11 +13667,11 @@
         <v>463</v>
       </c>
       <c r="B214" s="5">
-        <v>46162.392389768516</v>
+        <v>46162.55905643519</v>
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46162.50891618055</v>
+        <v>46162.67558284722</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>198</v>
@@ -13718,11 +13718,11 @@
         <v>465</v>
       </c>
       <c r="B215" s="9">
-        <v>46162.40212766203</v>
+        <v>46162.568794328705</v>
       </c>
       <c r="C215" s="10"/>
       <c r="D215" s="9">
-        <v>46162.508913067126</v>
+        <v>46162.6755797338</v>
       </c>
       <c r="E215" s="10" t="s">
         <v>198</v>
@@ -13769,11 +13769,11 @@
         <v>466</v>
       </c>
       <c r="B216" s="5">
-        <v>46162.40213472222</v>
+        <v>46162.56880138889</v>
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46162.50891030092</v>
+        <v>46162.675576967595</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>198</v>
@@ -13820,11 +13820,11 @@
         <v>467</v>
       </c>
       <c r="B217" s="9">
-        <v>46162.402141412036</v>
+        <v>46162.56880807871</v>
       </c>
       <c r="C217" s="10"/>
       <c r="D217" s="9">
-        <v>46162.50890765047</v>
+        <v>46162.67557431713</v>
       </c>
       <c r="E217" s="10" t="s">
         <v>198</v>
@@ -13871,11 +13871,11 @@
         <v>469</v>
       </c>
       <c r="B218" s="5">
-        <v>46162.40214881944</v>
+        <v>46162.56881548611</v>
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46162.508904953705</v>
+        <v>46162.67557162037</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>198</v>
@@ -13922,11 +13922,11 @@
         <v>470</v>
       </c>
       <c r="B219" s="9">
-        <v>46162.402155821765</v>
+        <v>46162.56882248842</v>
       </c>
       <c r="C219" s="10"/>
       <c r="D219" s="9">
-        <v>46162.50889708333</v>
+        <v>46162.67556375</v>
       </c>
       <c r="E219" s="10" t="s">
         <v>198</v>
@@ -13973,11 +13973,11 @@
         <v>471</v>
       </c>
       <c r="B220" s="5">
-        <v>46162.40216304398</v>
+        <v>46162.56882971065</v>
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46162.508896354164</v>
+        <v>46162.675563020835</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>198</v>
@@ -14024,11 +14024,11 @@
         <v>472</v>
       </c>
       <c r="B221" s="9">
-        <v>46162.40217094908</v>
+        <v>46162.56883761574</v>
       </c>
       <c r="C221" s="10"/>
       <c r="D221" s="9">
-        <v>46162.50889563657</v>
+        <v>46162.67556230324</v>
       </c>
       <c r="E221" s="10" t="s">
         <v>198</v>
@@ -14075,11 +14075,11 @@
         <v>473</v>
       </c>
       <c r="B222" s="5">
-        <v>46162.39239400463</v>
+        <v>46162.559060671294</v>
       </c>
       <c r="C222" s="6"/>
       <c r="D222" s="5">
-        <v>46162.50912635417</v>
+        <v>46162.67579302083</v>
       </c>
       <c r="E222" s="6" t="s">
         <v>474</v>
@@ -14138,11 +14138,11 @@
         <v>475</v>
       </c>
       <c r="B223" s="9">
-        <v>46162.392398055556</v>
+        <v>46162.55906472223</v>
       </c>
       <c r="C223" s="10"/>
       <c r="D223" s="9">
-        <v>46162.50912783565</v>
+        <v>46162.67579450231</v>
       </c>
       <c r="E223" s="10" t="s">
         <v>192</v>
@@ -14189,11 +14189,11 @@
         <v>477</v>
       </c>
       <c r="B224" s="5">
-        <v>46162.392405694445</v>
+        <v>46162.55907236111</v>
       </c>
       <c r="C224" s="6"/>
       <c r="D224" s="5">
-        <v>46162.50912484954</v>
+        <v>46162.6757915162</v>
       </c>
       <c r="E224" s="6" t="s">
         <v>192</v>
@@ -14240,11 +14240,11 @@
         <v>478</v>
       </c>
       <c r="B225" s="9">
-        <v>46162.39241195602</v>
+        <v>46162.55907862268</v>
       </c>
       <c r="C225" s="10"/>
       <c r="D225" s="9">
-        <v>46162.509121967596</v>
+        <v>46162.67578863426</v>
       </c>
       <c r="E225" s="10" t="s">
         <v>192</v>
@@ -14291,11 +14291,11 @@
         <v>480</v>
       </c>
       <c r="B226" s="5">
-        <v>46162.39241637732</v>
+        <v>46162.55908304398</v>
       </c>
       <c r="C226" s="6"/>
       <c r="D226" s="5">
-        <v>46162.509119236114</v>
+        <v>46162.67578590278</v>
       </c>
       <c r="E226" s="6" t="s">
         <v>192</v>
@@ -14342,11 +14342,11 @@
         <v>481</v>
       </c>
       <c r="B227" s="9">
-        <v>46162.39242053241</v>
+        <v>46162.55908719907</v>
       </c>
       <c r="C227" s="10"/>
       <c r="D227" s="9">
-        <v>46162.50911622685</v>
+        <v>46162.67578289352</v>
       </c>
       <c r="E227" s="10" t="s">
         <v>198</v>
@@ -14393,11 +14393,11 @@
         <v>483</v>
       </c>
       <c r="B228" s="5">
-        <v>46162.40234565972</v>
+        <v>46162.56901232639</v>
       </c>
       <c r="C228" s="6"/>
       <c r="D228" s="5">
-        <v>46162.50911296296</v>
+        <v>46162.67577962963</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>198</v>
@@ -14444,11 +14444,11 @@
         <v>484</v>
       </c>
       <c r="B229" s="9">
-        <v>46162.40235222223</v>
+        <v>46162.569018888884</v>
       </c>
       <c r="C229" s="10"/>
       <c r="D229" s="9">
-        <v>46162.50911028935</v>
+        <v>46162.67577695602</v>
       </c>
       <c r="E229" s="10" t="s">
         <v>198</v>
@@ -14495,11 +14495,11 @@
         <v>485</v>
       </c>
       <c r="B230" s="5">
-        <v>46162.40236021991</v>
+        <v>46162.56902688657</v>
       </c>
       <c r="C230" s="6"/>
       <c r="D230" s="5">
-        <v>46162.50910744213</v>
+        <v>46162.67577410879</v>
       </c>
       <c r="E230" s="6" t="s">
         <v>468</v>
@@ -14546,11 +14546,11 @@
         <v>486</v>
       </c>
       <c r="B231" s="9">
-        <v>46162.40236625</v>
+        <v>46162.56903291667</v>
       </c>
       <c r="C231" s="10"/>
       <c r="D231" s="9">
-        <v>46162.5091049537</v>
+        <v>46162.67577162037</v>
       </c>
       <c r="E231" s="10" t="s">
         <v>198</v>
@@ -14597,11 +14597,11 @@
         <v>487</v>
       </c>
       <c r="B232" s="5">
-        <v>46162.40237322917</v>
+        <v>46162.56903989583</v>
       </c>
       <c r="C232" s="6"/>
       <c r="D232" s="5">
-        <v>46162.509097256945</v>
+        <v>46162.67576392361</v>
       </c>
       <c r="E232" s="6" t="s">
         <v>198</v>
@@ -14648,11 +14648,11 @@
         <v>488</v>
       </c>
       <c r="B233" s="9">
-        <v>46162.4023796875</v>
+        <v>46162.56904635417</v>
       </c>
       <c r="C233" s="10"/>
       <c r="D233" s="9">
-        <v>46162.5090965625</v>
+        <v>46162.67576322917</v>
       </c>
       <c r="E233" s="10" t="s">
         <v>198</v>
@@ -14699,11 +14699,11 @@
         <v>489</v>
       </c>
       <c r="B234" s="5">
-        <v>46162.40238680555</v>
+        <v>46162.56905347222</v>
       </c>
       <c r="C234" s="6"/>
       <c r="D234" s="5">
-        <v>46162.50909585648</v>
+        <v>46162.67576252315</v>
       </c>
       <c r="E234" s="6" t="s">
         <v>198</v>
@@ -14750,11 +14750,11 @@
         <v>490</v>
       </c>
       <c r="B235" s="9">
-        <v>46162.392424618054</v>
+        <v>46162.559091284726</v>
       </c>
       <c r="C235" s="10"/>
       <c r="D235" s="9">
-        <v>46162.509191770834</v>
+        <v>46162.6758584375</v>
       </c>
       <c r="E235" s="10" t="s">
         <v>491</v>
@@ -14813,11 +14813,11 @@
         <v>493</v>
       </c>
       <c r="B236" s="5">
-        <v>46162.392429467596</v>
+        <v>46162.55909613426</v>
       </c>
       <c r="C236" s="6"/>
       <c r="D236" s="5">
-        <v>46162.509360208336</v>
+        <v>46162.676026875</v>
       </c>
       <c r="E236" s="6" t="s">
         <v>192</v>
@@ -14866,11 +14866,11 @@
         <v>494</v>
       </c>
       <c r="B237" s="9">
-        <v>46162.39243346065</v>
+        <v>46162.55910012731</v>
       </c>
       <c r="C237" s="10"/>
       <c r="D237" s="9">
-        <v>46162.509355891205</v>
+        <v>46162.67602255787</v>
       </c>
       <c r="E237" s="10" t="s">
         <v>192</v>
@@ -14919,11 +14919,11 @@
         <v>495</v>
       </c>
       <c r="B238" s="5">
-        <v>46162.39243740741</v>
+        <v>46162.55910407407</v>
       </c>
       <c r="C238" s="6"/>
       <c r="D238" s="5">
-        <v>46162.509352442125</v>
+        <v>46162.676019108796</v>
       </c>
       <c r="E238" s="6" t="s">
         <v>192</v>
@@ -14972,11 +14972,11 @@
         <v>496</v>
       </c>
       <c r="B239" s="9">
-        <v>46162.39244145833</v>
+        <v>46162.559108125</v>
       </c>
       <c r="C239" s="10"/>
       <c r="D239" s="9">
-        <v>46162.50934950232</v>
+        <v>46162.67601616898</v>
       </c>
       <c r="E239" s="10" t="s">
         <v>192</v>
@@ -15025,11 +15025,11 @@
         <v>497</v>
       </c>
       <c r="B240" s="5">
-        <v>46162.392477430556</v>
+        <v>46162.55914409722</v>
       </c>
       <c r="C240" s="6"/>
       <c r="D240" s="5">
-        <v>46162.5093466088</v>
+        <v>46162.676013275464</v>
       </c>
       <c r="E240" s="6" t="s">
         <v>198</v>
@@ -15078,11 +15078,11 @@
         <v>498</v>
       </c>
       <c r="B241" s="9">
-        <v>46162.40292248843</v>
+        <v>46162.56958915509</v>
       </c>
       <c r="C241" s="10"/>
       <c r="D241" s="9">
-        <v>46162.50934305556</v>
+        <v>46162.67600972222</v>
       </c>
       <c r="E241" s="10" t="s">
         <v>198</v>
@@ -15131,11 +15131,11 @@
         <v>499</v>
       </c>
       <c r="B242" s="5">
-        <v>46162.40292921296</v>
+        <v>46162.56959587963</v>
       </c>
       <c r="C242" s="6"/>
       <c r="D242" s="5">
-        <v>46162.509340335644</v>
+        <v>46162.676007002316</v>
       </c>
       <c r="E242" s="6" t="s">
         <v>198</v>
@@ -15184,11 +15184,11 @@
         <v>500</v>
       </c>
       <c r="B243" s="9">
-        <v>46162.40293847222</v>
+        <v>46162.56960513889</v>
       </c>
       <c r="C243" s="10"/>
       <c r="D243" s="9">
-        <v>46162.50933702546</v>
+        <v>46162.67600369213</v>
       </c>
       <c r="E243" s="10" t="s">
         <v>198</v>
@@ -15237,11 +15237,11 @@
         <v>501</v>
       </c>
       <c r="B244" s="5">
-        <v>46162.40294539352</v>
+        <v>46162.569612060186</v>
       </c>
       <c r="C244" s="6"/>
       <c r="D244" s="5">
-        <v>46162.50932924768</v>
+        <v>46162.67599591435</v>
       </c>
       <c r="E244" s="6" t="s">
         <v>198</v>
@@ -15290,11 +15290,11 @@
         <v>502</v>
       </c>
       <c r="B245" s="9">
-        <v>46162.40295333334</v>
+        <v>46162.569619999995</v>
       </c>
       <c r="C245" s="10"/>
       <c r="D245" s="9">
-        <v>46162.50932591435</v>
+        <v>46162.67599258102</v>
       </c>
       <c r="E245" s="10" t="s">
         <v>198</v>
@@ -15343,11 +15343,11 @@
         <v>503</v>
       </c>
       <c r="B246" s="5">
-        <v>46162.40296114583</v>
+        <v>46162.569627812496</v>
       </c>
       <c r="C246" s="6"/>
       <c r="D246" s="5">
-        <v>46162.50932474537</v>
+        <v>46162.675991412034</v>
       </c>
       <c r="E246" s="6" t="s">
         <v>198</v>
@@ -15396,11 +15396,11 @@
         <v>504</v>
       </c>
       <c r="B247" s="9">
-        <v>46162.40296784722</v>
+        <v>46162.569634513886</v>
       </c>
       <c r="C247" s="10"/>
       <c r="D247" s="9">
-        <v>46162.50932394676</v>
+        <v>46162.675990613425</v>
       </c>
       <c r="E247" s="10" t="s">
         <v>198</v>
@@ -15449,11 +15449,11 @@
         <v>505</v>
       </c>
       <c r="B248" s="5">
-        <v>46162.39248275463</v>
+        <v>46162.5591494213</v>
       </c>
       <c r="C248" s="6"/>
       <c r="D248" s="5">
-        <v>46162.49748135416</v>
+        <v>46162.664148020835</v>
       </c>
       <c r="E248" s="6" t="s">
         <v>506</v>
@@ -15496,11 +15496,11 @@
         <v>508</v>
       </c>
       <c r="B249" s="9">
-        <v>46162.39248613426</v>
+        <v>46162.559152800924</v>
       </c>
       <c r="C249" s="10"/>
       <c r="D249" s="9">
-        <v>46162.50939471065</v>
+        <v>46162.676061377315</v>
       </c>
       <c r="E249" s="10" t="s">
         <v>509</v>
@@ -15559,11 +15559,11 @@
         <v>512</v>
       </c>
       <c r="B250" s="5">
-        <v>46162.39249060185</v>
+        <v>46162.55915726852</v>
       </c>
       <c r="C250" s="6"/>
       <c r="D250" s="5">
-        <v>46162.50946783565</v>
+        <v>46162.67613450231</v>
       </c>
       <c r="E250" s="6" t="s">
         <v>513</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -4933,7 +4933,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46185.17078043982</v>
+        <v>46186.20479532407</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>84</v>
@@ -4975,8 +4975,8 @@
       <c r="R50" s="5">
         <v>46185</v>
       </c>
-      <c r="S50" s="12" t="s">
-        <v>86</v>
+      <c r="S50" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -3779,7 +3779,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46169.862564525465</v>
+        <v>46188.194889942126</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>120</v>
@@ -3823,8 +3823,8 @@
       <c r="R30" s="5">
         <v>46195</v>
       </c>
-      <c r="S30" s="7" t="s">
-        <v>54</v>
+      <c r="S30" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -3118,7 +3118,7 @@
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46182.18051851852</v>
+        <v>46189.16936002315</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>81</v>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46182.18051799768</v>
+        <v>46189.16936251157</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>88</v>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46182.18051825231</v>
+        <v>46189.169364050926</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>91</v>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46182.18051806713</v>
+        <v>46189.16936587963</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>94</v>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46162.67389618055</v>
+        <v>46189.19912201389</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>305</v>
@@ -8431,8 +8431,8 @@
       <c r="R114" s="5">
         <v>46196</v>
       </c>
-      <c r="S114" s="7" t="s">
-        <v>54</v>
+      <c r="S114" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="T114" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -290,112 +290,112 @@
     <t>Propuesta compras:,Generación OC materiales corte Laser OT 4324 4325</t>
   </si>
   <si>
+    <t>1214969335271801</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma  OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969466331109</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969466331119</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa  OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969284200801</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>rodete OT 4324 4325,Materiales corte Laser OT 4324 4325,Alabe OT 4324 4325,Motor OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969466331129</t>
+  </si>
+  <si>
+    <t>Alabe OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe OT 4324 4325,Generación OC Alabe OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969379038319</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe OT 4324 4325,Alabe OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969379038337</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Alabe OT 4324 4325,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214969287532633</t>
+  </si>
+  <si>
+    <t>rodete OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete OT 4324 4325,Fabricación Rodete OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969287532648</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete OT 4324 4325</t>
+  </si>
+  <si>
+    <t>rodete OT 4324 4325,Fabricación Rodete OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969503994817</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete,rodete OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969504007335</t>
+  </si>
+  <si>
+    <t>Motor OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Generación OC motor OT 4324 4325,Fabricación motor OT 4324 4325,Planos motor proveedor OT 4324 4325</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214969335271801</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma  OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969466331109</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969466331119</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa  OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969284200801</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>rodete OT 4324 4325,Materiales corte Laser OT 4324 4325,Alabe OT 4324 4325,Motor OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969466331129</t>
-  </si>
-  <si>
-    <t>Alabe OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe OT 4324 4325,Generación OC Alabe OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969379038319</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe OT 4324 4325,Alabe OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969379038337</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Alabe OT 4324 4325,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214969287532633</t>
-  </si>
-  <si>
-    <t>rodete OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete OT 4324 4325,Fabricación Rodete OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969287532648</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete OT 4324 4325</t>
-  </si>
-  <si>
-    <t>rodete OT 4324 4325,Fabricación Rodete OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969503994817</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete,rodete OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969504007335</t>
-  </si>
-  <si>
-    <t>Motor OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Generación OC motor OT 4324 4325,Fabricación motor OT 4324 4325,Planos motor proveedor OT 4324 4325</t>
   </si>
   <si>
     <t>1214969504007350</t>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46189.16936002315</v>
+        <v>46190.20507244213</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>81</v>
@@ -3162,8 +3162,8 @@
       <c r="R19" s="9">
         <v>46189</v>
       </c>
-      <c r="S19" s="12" t="s">
-        <v>86</v>
+      <c r="S19" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T19" s="10">
         <v>0</v>
@@ -3174,17 +3174,17 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B20" s="5">
         <v>46162.55829380787</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46189.16936251157</v>
+        <v>46190.205072453704</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -3217,7 +3217,7 @@
         <v>84</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q20" s="5">
         <v>46188</v>
@@ -3225,8 +3225,8 @@
       <c r="R20" s="5">
         <v>46189</v>
       </c>
-      <c r="S20" s="12" t="s">
-        <v>86</v>
+      <c r="S20" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T20" s="6">
         <v>0</v>
@@ -3237,17 +3237,17 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B21" s="9">
         <v>46162.55829782407</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46189.169364050926</v>
+        <v>46190.20507252315</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -3280,7 +3280,7 @@
         <v>84</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q21" s="9">
         <v>46188</v>
@@ -3288,8 +3288,8 @@
       <c r="R21" s="9">
         <v>46189</v>
       </c>
-      <c r="S21" s="12" t="s">
-        <v>86</v>
+      <c r="S21" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T21" s="10">
         <v>0</v>
@@ -3300,17 +3300,17 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B22" s="5">
         <v>46162.558301446756</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46189.16936587963</v>
+        <v>46190.20507293982</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -3343,7 +3343,7 @@
         <v>84</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q22" s="5">
         <v>46188</v>
@@ -3351,8 +3351,8 @@
       <c r="R22" s="5">
         <v>46189</v>
       </c>
-      <c r="S22" s="12" t="s">
-        <v>86</v>
+      <c r="S22" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
@@ -3363,7 +3363,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B23" s="9">
         <v>46162.55817344907</v>
@@ -3373,7 +3373,7 @@
         <v>46162.59982563657</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>25</v>
@@ -3397,7 +3397,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>26</v>
@@ -3410,7 +3410,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B24" s="5">
         <v>46162.558305694445</v>
@@ -3420,16 +3420,16 @@
         <v>46169.86252686342</v>
       </c>
       <c r="E24" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24" s="6" t="s">
+      <c r="H24" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="I24" s="5">
         <v>46155</v>
@@ -3447,13 +3447,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q24" s="5">
         <v>46155</v>
@@ -3473,7 +3473,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B25" s="9">
         <v>46162.55831018518</v>
@@ -3483,16 +3483,16 @@
         <v>46169.86302510416</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>101</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>102</v>
       </c>
       <c r="I25" s="9">
         <v>46155</v>
@@ -3510,13 +3510,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>74</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3532,7 +3532,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B26" s="5">
         <v>46162.55831479166</v>
@@ -3542,16 +3542,16 @@
         <v>46169.86304815972</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="I26" s="5">
         <v>46157</v>
@@ -3569,13 +3569,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -3591,7 +3591,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B27" s="9">
         <v>46162.558319710646</v>
@@ -3601,16 +3601,16 @@
         <v>46169.86254357639</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>101</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>102</v>
       </c>
       <c r="I27" s="9">
         <v>46155</v>
@@ -3628,13 +3628,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q27" s="9">
         <v>46155</v>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46162.55832415509</v>
@@ -3664,16 +3664,16 @@
         <v>46169.86296932871</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="I28" s="5">
         <v>46155</v>
@@ -3691,13 +3691,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3713,7 +3713,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B29" s="9">
         <v>46162.5583337037</v>
@@ -3723,16 +3723,16 @@
         <v>46169.86298305556</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>101</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>102</v>
       </c>
       <c r="I29" s="9">
         <v>46157</v>
@@ -3750,13 +3750,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3772,7 +3772,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5">
         <v>46162.55833876158</v>
@@ -3782,16 +3782,16 @@
         <v>46188.194889942126</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="I30" s="5">
         <v>46155</v>
@@ -3809,13 +3809,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q30" s="5">
         <v>46155</v>
@@ -3824,7 +3824,7 @@
         <v>46195</v>
       </c>
       <c r="S30" s="12" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
@@ -3851,10 +3851,10 @@
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>101</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>102</v>
       </c>
       <c r="I31" s="9">
         <v>46155</v>
@@ -3872,7 +3872,7 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O31" s="10" t="s">
         <v>71</v>
@@ -3910,10 +3910,10 @@
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="I32" s="5">
         <v>46167</v>
@@ -3931,7 +3931,7 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>123</v>
@@ -3969,10 +3969,10 @@
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>101</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>102</v>
       </c>
       <c r="I33" s="9">
         <v>46167</v>
@@ -3990,7 +3990,7 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O33" s="10" t="s">
         <v>123</v>
@@ -4049,13 +4049,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>135</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q34" s="5">
         <v>46190</v>
@@ -4230,7 +4230,7 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>144</v>
@@ -4266,7 +4266,7 @@
         <v>46169.86278755787</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -4296,7 +4296,7 @@
         <v>143</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>146</v>
@@ -4349,7 +4349,7 @@
         <v>143</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>149</v>
@@ -4399,7 +4399,7 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>154</v>
@@ -4435,7 +4435,7 @@
         <v>46169.86271082176</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
@@ -4465,7 +4465,7 @@
         <v>151</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>156</v>
@@ -4518,7 +4518,7 @@
         <v>151</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>159</v>
@@ -4621,7 +4621,7 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>166</v>
@@ -4657,7 +4657,7 @@
         <v>46169.86265809028</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -4687,7 +4687,7 @@
         <v>165</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>168</v>
@@ -4740,7 +4740,7 @@
         <v>165</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>171</v>
@@ -8294,7 +8294,7 @@
         <v>207</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>300</v>
@@ -8357,7 +8357,7 @@
         <v>207</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>303</v>
@@ -8432,7 +8432,7 @@
         <v>46196</v>
       </c>
       <c r="S114" s="12" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="T114" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -4082,7 +4082,7 @@
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46169.86283975694</v>
+        <v>46191.16929601852</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>137</v>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.86278755787</v>
+        <v>46191.169293900464</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>88</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46169.86265809028</v>
+        <v>46191.169297465276</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>91</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2840" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2852" uniqueCount="515">
   <si>
     <t xml:space="preserve">50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT 4324 4325 </t>
   </si>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46162.648368298615</v>
+        <v>46191.68638508102</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -5066,9 +5066,11 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H52" s="6"/>
+        <v>188</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>189</v>
+      </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
         <v>46225</v>
@@ -5106,7 +5108,7 @@
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46162.64838028935</v>
+        <v>46191.68638201389</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>192</v>
@@ -5115,9 +5117,11 @@
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H53" s="10"/>
+        <v>188</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>189</v>
+      </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
         <v>46225</v>
@@ -5155,7 +5159,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46162.64839299768</v>
+        <v>46191.68637913195</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>192</v>
@@ -5164,9 +5168,11 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H54" s="6"/>
+        <v>188</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>189</v>
+      </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
         <v>46225</v>
@@ -5204,7 +5210,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46162.64840498843</v>
+        <v>46191.68637614584</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>192</v>
@@ -5213,9 +5219,11 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H55" s="10"/>
+        <v>188</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>189</v>
+      </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
         <v>46225</v>
@@ -5253,7 +5261,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46162.64843181713</v>
+        <v>46191.6863727662</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>198</v>
@@ -5262,9 +5270,11 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H56" s="6"/>
+        <v>188</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>189</v>
+      </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
         <v>46225</v>
@@ -5302,7 +5312,7 @@
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46162.64849939814</v>
+        <v>46191.686369641204</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>198</v>
@@ -5311,9 +5321,11 @@
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H57" s="10"/>
+        <v>188</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>189</v>
+      </c>
       <c r="I57" s="10"/>
       <c r="J57" s="9">
         <v>46225</v>
@@ -5351,7 +5363,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46162.64852451389</v>
+        <v>46191.68636637731</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>198</v>
@@ -5360,9 +5372,11 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H58" s="6"/>
+        <v>188</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>189</v>
+      </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
         <v>46225</v>
@@ -5400,7 +5414,7 @@
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46162.648539409725</v>
+        <v>46191.686363761575</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>198</v>
@@ -5409,9 +5423,11 @@
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H59" s="10"/>
+        <v>188</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>189</v>
+      </c>
       <c r="I59" s="10"/>
       <c r="J59" s="9">
         <v>46225</v>
@@ -5449,7 +5465,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46162.648549652775</v>
+        <v>46191.6863608912</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>198</v>
@@ -5458,9 +5474,11 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H60" s="6"/>
+        <v>188</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>189</v>
+      </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
         <v>46225</v>
@@ -5498,7 +5516,7 @@
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46162.64859189815</v>
+        <v>46191.68635278935</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>198</v>
@@ -5507,9 +5525,11 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H61" s="10"/>
+        <v>188</v>
+      </c>
+      <c r="H61" s="10" t="s">
+        <v>189</v>
+      </c>
       <c r="I61" s="10"/>
       <c r="J61" s="9">
         <v>46225</v>
@@ -5547,7 +5567,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46162.64860564815</v>
+        <v>46191.68635209491</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>198</v>
@@ -5556,9 +5576,11 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H62" s="6"/>
+        <v>188</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>189</v>
+      </c>
       <c r="I62" s="6"/>
       <c r="J62" s="5">
         <v>46225</v>
@@ -5596,7 +5618,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46162.64863078704</v>
+        <v>46191.686351412034</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>198</v>
@@ -5605,9 +5627,11 @@
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H63" s="10"/>
+        <v>188</v>
+      </c>
+      <c r="H63" s="10" t="s">
+        <v>189</v>
+      </c>
       <c r="I63" s="10"/>
       <c r="J63" s="9">
         <v>46225</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -3779,7 +3779,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46188.194889942126</v>
+        <v>46195.169887048614</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46169.862912048615</v>
+        <v>46195.16988916667</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>126</v>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46169.862576064814</v>
+        <v>46195.184916620376</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>132</v>
@@ -4063,8 +4063,8 @@
       <c r="R34" s="5">
         <v>46202</v>
       </c>
-      <c r="S34" s="7" t="s">
-        <v>54</v>
+      <c r="S34" s="12" t="s">
+        <v>121</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46169.862590625</v>
+        <v>46195.18491644676</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -4244,8 +4244,8 @@
       <c r="R37" s="9">
         <v>46202</v>
       </c>
-      <c r="S37" s="7" t="s">
-        <v>54</v>
+      <c r="S37" s="12" t="s">
+        <v>121</v>
       </c>
       <c r="T37" s="10">
         <v>0</v>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46169.86261476851</v>
+        <v>46195.18491668982</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -4635,8 +4635,8 @@
       <c r="R44" s="5">
         <v>46202</v>
       </c>
-      <c r="S44" s="7" t="s">
-        <v>54</v>
+      <c r="S44" s="12" t="s">
+        <v>121</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -2630,7 +2630,7 @@
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="9">
-        <v>46175.87408930555</v>
+        <v>46195.59154087963</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>49</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -395,49 +395,49 @@
     <t>Generación OC motor OT 4324 4325,Fabricación motor OT 4324 4325,Planos motor proveedor OT 4324 4325</t>
   </si>
   <si>
+    <t>1214969504007350</t>
+  </si>
+  <si>
+    <t>Generación OC motor OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Motor OT 4324 4325,Fabricación motor OT 4324 4325,Planos motor proveedor OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969504023948</t>
+  </si>
+  <si>
+    <t>Fabricación motor OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Recepcion motor,Motor OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969504023966</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Motor OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969335368176</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser  OT 4324 4325,Generación OC materiales corte Laser OT 4324 4325</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214969504007350</t>
-  </si>
-  <si>
-    <t>Generación OC motor OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Motor OT 4324 4325,Fabricación motor OT 4324 4325,Planos motor proveedor OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969504023948</t>
-  </si>
-  <si>
-    <t>Fabricación motor OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Recepcion motor,Motor OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969504023966</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Motor OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969335368176</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser  OT 4324 4325,Generación OC materiales corte Laser OT 4324 4325</t>
   </si>
   <si>
     <t>1214969335368191</t>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46195.169887048614</v>
+        <v>46196.17404179398</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3823,8 +3823,8 @@
       <c r="R30" s="5">
         <v>46195</v>
       </c>
-      <c r="S30" s="12" t="s">
-        <v>121</v>
+      <c r="S30" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
@@ -3835,7 +3835,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B31" s="9">
         <v>46162.5583437037</v>
@@ -3845,7 +3845,7 @@
         <v>46169.862896666666</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
@@ -3878,7 +3878,7 @@
         <v>71</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B32" s="5">
         <v>46162.55834872685</v>
@@ -3904,7 +3904,7 @@
         <v>46195.16988916667</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3934,10 +3934,10 @@
         <v>119</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3953,7 +3953,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B33" s="9">
         <v>46162.558353518514</v>
@@ -3963,7 +3963,7 @@
         <v>46175.17034748843</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
@@ -3993,10 +3993,10 @@
         <v>119</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -4012,7 +4012,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B34" s="5">
         <v>46162.558358229166</v>
@@ -4022,16 +4022,16 @@
         <v>46195.184916620376</v>
       </c>
       <c r="E34" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G34" s="6" t="s">
+      <c r="H34" s="6" t="s">
         <v>133</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>134</v>
       </c>
       <c r="I34" s="5">
         <v>46190</v>
@@ -4052,7 +4052,7 @@
         <v>96</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>96</v>
@@ -4064,7 +4064,7 @@
         <v>46202</v>
       </c>
       <c r="S34" s="12" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
@@ -4091,10 +4091,10 @@
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>133</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>134</v>
       </c>
       <c r="I35" s="9">
         <v>46190</v>
@@ -4112,7 +4112,7 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>81</v>
@@ -4150,10 +4150,10 @@
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>133</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>134</v>
       </c>
       <c r="I36" s="5">
         <v>46192</v>
@@ -4171,7 +4171,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>137</v>
@@ -4209,10 +4209,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>133</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>134</v>
       </c>
       <c r="I37" s="9">
         <v>46190</v>
@@ -4245,7 +4245,7 @@
         <v>46202</v>
       </c>
       <c r="S37" s="12" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="T37" s="10">
         <v>0</v>
@@ -4272,10 +4272,10 @@
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>133</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>134</v>
       </c>
       <c r="I38" s="5">
         <v>46190</v>
@@ -4325,10 +4325,10 @@
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>133</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>134</v>
       </c>
       <c r="I39" s="9">
         <v>46161</v>
@@ -4600,10 +4600,10 @@
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>133</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>134</v>
       </c>
       <c r="I44" s="5">
         <v>46190</v>
@@ -4636,7 +4636,7 @@
         <v>46202</v>
       </c>
       <c r="S44" s="12" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
@@ -4663,10 +4663,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>133</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>134</v>
       </c>
       <c r="I45" s="9">
         <v>46190</v>
@@ -4716,10 +4716,10 @@
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>133</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>134</v>
       </c>
       <c r="I46" s="5">
         <v>46192</v>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46162.6718065625</v>
+        <v>46196.16939501157</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>210</v>
@@ -5760,8 +5760,8 @@
       <c r="R65" s="9">
         <v>46203</v>
       </c>
-      <c r="S65" s="7" t="s">
-        <v>54</v>
+      <c r="S65" s="12" t="s">
+        <v>135</v>
       </c>
       <c r="T65" s="10">
         <v>0</v>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46162.671803969904</v>
+        <v>46196.16939498842</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>219</v>
@@ -5886,8 +5886,8 @@
       <c r="R67" s="9">
         <v>46203</v>
       </c>
-      <c r="S67" s="7" t="s">
-        <v>54</v>
+      <c r="S67" s="12" t="s">
+        <v>135</v>
       </c>
       <c r="T67" s="10">
         <v>0</v>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46162.67180003472</v>
+        <v>46196.16939524305</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>225</v>
@@ -6012,8 +6012,8 @@
       <c r="R69" s="9">
         <v>46203</v>
       </c>
-      <c r="S69" s="7" t="s">
-        <v>54</v>
+      <c r="S69" s="12" t="s">
+        <v>135</v>
       </c>
       <c r="T69" s="10">
         <v>0</v>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46189.19912201389</v>
+        <v>46196.16906886574</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>305</v>
@@ -8444,7 +8444,7 @@
         <v>207</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>306</v>
@@ -8456,7 +8456,7 @@
         <v>46196</v>
       </c>
       <c r="S114" s="12" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="T114" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -2630,7 +2630,7 @@
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="9">
-        <v>46195.59154087963</v>
+        <v>46196.60226733796</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>49</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -902,7 +902,7 @@
     <t>1214969047720351</t>
   </si>
   <si>
-    <t xml:space="preserve">OT7 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">OT7 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214969047720352</t>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -5779,7 +5779,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46162.67188486111</v>
+        <v>46197.168534537035</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>215</v>
@@ -5823,8 +5823,8 @@
       <c r="R66" s="5">
         <v>46204</v>
       </c>
-      <c r="S66" s="7" t="s">
-        <v>54</v>
+      <c r="S66" s="12" t="s">
+        <v>135</v>
       </c>
       <c r="T66" s="6">
         <v>0</v>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46162.67188201389</v>
+        <v>46197.168534571756</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>222</v>
@@ -5949,8 +5949,8 @@
       <c r="R68" s="5">
         <v>46204</v>
       </c>
-      <c r="S68" s="7" t="s">
-        <v>54</v>
+      <c r="S68" s="12" t="s">
+        <v>135</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46162.67187829861</v>
+        <v>46197.16853431713</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>226</v>
@@ -6075,8 +6075,8 @@
       <c r="R70" s="5">
         <v>46204</v>
       </c>
-      <c r="S70" s="7" t="s">
-        <v>54</v>
+      <c r="S70" s="12" t="s">
+        <v>135</v>
       </c>
       <c r="T70" s="6">
         <v>0</v>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46196.16906886574</v>
+        <v>46197.17582074074</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>305</v>
@@ -8455,8 +8455,8 @@
       <c r="R114" s="5">
         <v>46196</v>
       </c>
-      <c r="S114" s="12" t="s">
-        <v>135</v>
+      <c r="S114" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T114" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46162.59275393518</v>
+        <v>46197.58811732639</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -3053,9 +3053,11 @@
       <c r="B18" s="5">
         <v>46162.55828362268</v>
       </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="5">
+        <v>46197.58811052083</v>
+      </c>
       <c r="D18" s="5">
-        <v>46169.862458125004</v>
+        <v>46197.588127407405</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -3103,10 +3105,10 @@
         <v>54</v>
       </c>
       <c r="T18" s="6">
-        <v>0</v>
-      </c>
-      <c r="U18" s="11" t="s">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="U18" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -3661,7 +3663,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46169.86296932871</v>
+        <v>46197.58811881945</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -182,7 +182,10 @@
     <t>cperez@zitron.com</t>
   </si>
   <si>
-    <t>MOTOR DE STOCK WEG - 02 POLOS - IE3 FRAME 280</t>
+    <t xml:space="preserve">Motores
+        OT 4324 — ZVN 1-7-37/2 – COD 350004
+        OT 4325 — ZVN 1-7-63/2 -- COD 350007
+</t>
   </si>
   <si>
     <t>Ingenieria Jefe de proyecto:,Analisis de costeo,propuesta motor OT 4324 4325</t>
@@ -191,34 +194,31 @@
     <t>Baja</t>
   </si>
   <si>
+    <t>1214969466296328</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Selección de Rodete:
+        OT 4324 - Ventilador ZVN 1-7-37/2 --- COD. RODETE: 300059
+        OT 4325 - Ventilador ZVN 1-7-63/2 --- COD. RODETE: 300065
+</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodete OT 4324 4325,Ingenieria Jefe de proyecto:,Analisis de costeo,propuesta alabes OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969335257867</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,Analisis de costeo,Planos preliminar</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1214969466296328</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Selección de Rodete:
-        Rodete de placas s/plano 3073.00
-        Alabe s/ plano 3073.01
-        Z8 N600
-        Código 300003
-        hgutierrez@zitron.com, tu apoyo con la definición de calaje.
-</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodete OT 4324 4325,Ingenieria Jefe de proyecto:,Analisis de costeo,propuesta alabes OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969335257867</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Analisis de costeo,Planos preliminar</t>
   </si>
   <si>
     <t>1214969335257887</t>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46162.5836137963</v>
+        <v>46197.654548402774</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2628,9 +2628,11 @@
       <c r="B11" s="9">
         <v>46162.55824909722</v>
       </c>
-      <c r="C11" s="10"/>
+      <c r="C11" s="9">
+        <v>46197.65242402778</v>
+      </c>
       <c r="D11" s="9">
-        <v>46196.60226733796</v>
+        <v>46197.65244247685</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>49</v>
@@ -2678,25 +2680,27 @@
         <v>54</v>
       </c>
       <c r="T11" s="10">
-        <v>0</v>
-      </c>
-      <c r="U11" s="12" t="s">
-        <v>55</v>
+        <v>1</v>
+      </c>
+      <c r="U11" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B12" s="5">
         <v>46162.55825447917</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="5">
+        <v>46197.65454083333</v>
+      </c>
       <c r="D12" s="5">
-        <v>46175.874090578705</v>
+        <v>46197.654557013884</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
@@ -2717,7 +2721,7 @@
         <v>26</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>26</v>
@@ -2729,7 +2733,7 @@
         <v>39</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q12" s="5">
         <v>46149</v>
@@ -2741,15 +2745,15 @@
         <v>54</v>
       </c>
       <c r="T12" s="6">
-        <v>0</v>
-      </c>
-      <c r="U12" s="12" t="s">
-        <v>55</v>
+        <v>1</v>
+      </c>
+      <c r="U12" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13" s="9">
         <v>46162.55825988426</v>
@@ -2759,7 +2763,7 @@
         <v>46175.874089687495</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
@@ -2792,7 +2796,7 @@
         <v>39</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q13" s="9">
         <v>46149</v>
@@ -2807,7 +2811,7 @@
         <v>0</v>
       </c>
       <c r="U13" s="12" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -2819,7 +2823,7 @@
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46162.664603599536</v>
+        <v>46197.65454884259</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2929,7 +2933,7 @@
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46169.86243731482</v>
+        <v>46197.65244157407</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2979,8 +2983,8 @@
       <c r="T16" s="6">
         <v>0</v>
       </c>
-      <c r="U16" s="11" t="s">
-        <v>66</v>
+      <c r="U16" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
@@ -2992,7 +2996,7 @@
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46169.862450347224</v>
+        <v>46197.654558842594</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>74</v>
@@ -3025,7 +3029,7 @@
         <v>68</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P17" s="10" t="s">
         <v>75</v>
@@ -3042,8 +3046,8 @@
       <c r="T17" s="10">
         <v>0</v>
       </c>
-      <c r="U17" s="11" t="s">
-        <v>66</v>
+      <c r="U17" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -3057,7 +3061,7 @@
         <v>46197.58811052083</v>
       </c>
       <c r="D18" s="5">
-        <v>46197.588127407405</v>
+        <v>46197.654558912036</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -3090,7 +3094,7 @@
         <v>68</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>79</v>
@@ -3107,8 +3111,8 @@
       <c r="T18" s="6">
         <v>1</v>
       </c>
-      <c r="U18" s="7" t="s">
-        <v>27</v>
+      <c r="U18" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -4842,7 +4846,7 @@
         <v>173</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>179</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2852" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2852" uniqueCount="516">
   <si>
     <t xml:space="preserve">50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT 4324 4325 </t>
   </si>
@@ -215,79 +215,98 @@
     <t>Ingenieria Detalle</t>
   </si>
   <si>
+    <t xml:space="preserve"> P.1553
+        OT 4323: 4 ventiladores ZVN 1-7-37/2,
+        OT 4325 : 8 ventiladores ZVN 1-7-63/2,
+    Planos para:
+        Ventilador ZVN 1-7-37/2 con motor WEG o similar – Alcance: TOBERA + REJILLA + FAR 70/100 + VENT + FAR 70/100 + TIPO A
+        Ventilador ZVN 1-7-63/2 con motor WEG o similar – Alcance: TOBERA + REJILLA + FAR 70/100 + VENT + FAR 70/100 + TIPO A
+        Alcance Chile: TOBERA + REJILLA + VENT
+        Alcance Colombia: FAR + TIPO A + DIFUSOR
+    Rodete:
+        Ventilador ZVN 1-7-37/2 --- RODETE: 300059
+        Ventilador ZVN 1-7-63/2 --- RODETE: 300065
+    Tratamiento superficial:
+        Estándar Zitrón con 2 capas y color de terminación Blanco RAL 9001.
+    Datos eléctricos para el motor:
+        440V, 60HZ, IP55, IE-3, 1000 MSNM.
+        Incluye: Sensor de vibraciones VKV 021 y Graseras automáticas con protección mecánica.
+</t>
+  </si>
+  <si>
     <t>Ingenieria Jefe de proyecto:,Analisis de costeo,Planos preliminar</t>
   </si>
   <si>
+    <t>1214969335257887</t>
+  </si>
+  <si>
+    <t>Analisis de costeo</t>
+  </si>
+  <si>
+    <t>Costos,Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
   </si>
   <si>
-    <t>1214969335257887</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Costos,Ingenieria Jefe de proyecto:</t>
+    <t>1214969284200799</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodete OT 4324 4325,propuesta Corte Laser OT 4324 4325,propuesta motor OT 4324 4325,propuesta alabes OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969466305909</t>
+  </si>
+  <si>
+    <t>propuesta motor OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC motor OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969503938685</t>
+  </si>
+  <si>
+    <t>propuesta alabes OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe OT 4324 4325,Propuesta compras:</t>
+  </si>
+  <si>
+    <t>1214969503938705</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodete OT 4324 4325</t>
+  </si>
+  <si>
+    <t>benjamin.bustos@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Rodete OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969335271786</t>
+  </si>
+  <si>
+    <t>propuesta Corte Laser OT 4324 4325</t>
+  </si>
+  <si>
+    <t>hugo isla martinez</t>
+  </si>
+  <si>
+    <t>hugo.isla@zitron.com</t>
+  </si>
+  <si>
+    <t>check planos</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC materiales corte Laser OT 4324 4325</t>
   </si>
   <si>
     <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1214969284200799</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodete OT 4324 4325,propuesta Corte Laser OT 4324 4325,propuesta motor OT 4324 4325,propuesta alabes OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969466305909</t>
-  </si>
-  <si>
-    <t>propuesta motor OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC motor OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969503938685</t>
-  </si>
-  <si>
-    <t>propuesta alabes OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe OT 4324 4325,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>1214969503938705</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodete OT 4324 4325</t>
-  </si>
-  <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Rodete OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969335271786</t>
-  </si>
-  <si>
-    <t>propuesta Corte Laser OT 4324 4325</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
-  </si>
-  <si>
-    <t>check planos</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC materiales corte Laser OT 4324 4325</t>
   </si>
   <si>
     <t>1214969335271801</t>
@@ -2583,7 +2602,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46197.654548402774</v>
+        <v>46197.65648712963</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2758,9 +2777,11 @@
       <c r="B13" s="9">
         <v>46162.55825988426</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="9">
+        <v>46197.65648178241</v>
+      </c>
       <c r="D13" s="9">
-        <v>46175.874089687495</v>
+        <v>46197.65649844907</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>60</v>
@@ -2784,7 +2805,7 @@
         <v>26</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="M13" s="10" t="s">
         <v>26</v>
@@ -2796,7 +2817,7 @@
         <v>39</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q13" s="9">
         <v>46149</v>
@@ -2808,10 +2829,10 @@
         <v>54</v>
       </c>
       <c r="T13" s="10">
-        <v>0</v>
-      </c>
-      <c r="U13" s="12" t="s">
-        <v>62</v>
+        <v>1</v>
+      </c>
+      <c r="U13" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -2823,7 +2844,7 @@
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46197.65454884259</v>
+        <v>46197.65650109954</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2873,7 +2894,7 @@
       <c r="T14" s="6">
         <v>0</v>
       </c>
-      <c r="U14" s="11" t="s">
+      <c r="U14" s="12" t="s">
         <v>66</v>
       </c>
     </row>
@@ -2984,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="U16" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
@@ -3047,7 +3068,7 @@
         <v>0</v>
       </c>
       <c r="U17" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -3112,7 +3133,7 @@
         <v>1</v>
       </c>
       <c r="U18" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -3175,12 +3196,12 @@
         <v>0</v>
       </c>
       <c r="U19" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B20" s="5">
         <v>46162.55829380787</v>
@@ -3190,7 +3211,7 @@
         <v>46190.205072453704</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -3223,7 +3244,7 @@
         <v>84</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q20" s="5">
         <v>46188</v>
@@ -3238,12 +3259,12 @@
         <v>0</v>
       </c>
       <c r="U20" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B21" s="9">
         <v>46162.55829782407</v>
@@ -3253,7 +3274,7 @@
         <v>46190.20507252315</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -3286,7 +3307,7 @@
         <v>84</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q21" s="9">
         <v>46188</v>
@@ -3301,12 +3322,12 @@
         <v>0</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B22" s="5">
         <v>46162.558301446756</v>
@@ -3316,7 +3337,7 @@
         <v>46190.20507293982</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -3349,7 +3370,7 @@
         <v>84</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q22" s="5">
         <v>46188</v>
@@ -3364,12 +3385,12 @@
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B23" s="9">
         <v>46162.55817344907</v>
@@ -3379,7 +3400,7 @@
         <v>46162.59982563657</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>25</v>
@@ -3403,7 +3424,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>26</v>
@@ -3416,7 +3437,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B24" s="5">
         <v>46162.558305694445</v>
@@ -3426,16 +3447,16 @@
         <v>46169.86252686342</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I24" s="5">
         <v>46155</v>
@@ -3453,13 +3474,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q24" s="5">
         <v>46155</v>
@@ -3474,12 +3495,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B25" s="9">
         <v>46162.55831018518</v>
@@ -3489,16 +3510,16 @@
         <v>46169.86302510416</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I25" s="9">
         <v>46155</v>
@@ -3516,13 +3537,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>74</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3533,12 +3554,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B26" s="5">
         <v>46162.55831479166</v>
@@ -3548,16 +3569,16 @@
         <v>46169.86304815972</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I26" s="5">
         <v>46157</v>
@@ -3575,13 +3596,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -3592,12 +3613,12 @@
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B27" s="9">
         <v>46162.558319710646</v>
@@ -3607,16 +3628,16 @@
         <v>46169.86254357639</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I27" s="9">
         <v>46155</v>
@@ -3634,13 +3655,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q27" s="9">
         <v>46155</v>
@@ -3655,12 +3676,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B28" s="5">
         <v>46162.55832415509</v>
@@ -3670,16 +3691,16 @@
         <v>46197.58811881945</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I28" s="5">
         <v>46155</v>
@@ -3697,13 +3718,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3714,12 +3735,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B29" s="9">
         <v>46162.5583337037</v>
@@ -3729,16 +3750,16 @@
         <v>46169.86298305556</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I29" s="9">
         <v>46157</v>
@@ -3756,13 +3777,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3773,12 +3794,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B30" s="5">
         <v>46162.55833876158</v>
@@ -3788,16 +3809,16 @@
         <v>46196.17404179398</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I30" s="5">
         <v>46155</v>
@@ -3815,13 +3836,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q30" s="5">
         <v>46155</v>
@@ -3836,12 +3857,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B31" s="9">
         <v>46162.5583437037</v>
@@ -3851,16 +3872,16 @@
         <v>46169.862896666666</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I31" s="9">
         <v>46155</v>
@@ -3878,13 +3899,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O31" s="10" t="s">
         <v>71</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3895,12 +3916,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B32" s="5">
         <v>46162.55834872685</v>
@@ -3910,16 +3931,16 @@
         <v>46195.16988916667</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I32" s="5">
         <v>46167</v>
@@ -3937,13 +3958,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3954,12 +3975,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B33" s="9">
         <v>46162.558353518514</v>
@@ -3969,16 +3990,16 @@
         <v>46175.17034748843</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I33" s="9">
         <v>46167</v>
@@ -3996,13 +4017,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -4013,12 +4034,12 @@
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
         <v>46162.558358229166</v>
@@ -4028,16 +4049,16 @@
         <v>46195.184916620376</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I34" s="5">
         <v>46190</v>
@@ -4055,13 +4076,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q34" s="5">
         <v>46190</v>
@@ -4070,18 +4091,18 @@
         <v>46202</v>
       </c>
       <c r="S34" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B35" s="9">
         <v>46162.5583628125</v>
@@ -4091,16 +4112,16 @@
         <v>46191.16929601852</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I35" s="9">
         <v>46190</v>
@@ -4118,13 +4139,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>81</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -4135,12 +4156,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B36" s="5">
         <v>46162.55841275463</v>
@@ -4150,16 +4171,16 @@
         <v>46169.86285621527</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I36" s="5">
         <v>46192</v>
@@ -4177,13 +4198,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -4194,12 +4215,12 @@
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B37" s="9">
         <v>46162.558418622684</v>
@@ -4209,16 +4230,16 @@
         <v>46195.18491644676</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I37" s="9">
         <v>46190</v>
@@ -4236,10 +4257,10 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>26</v>
@@ -4251,18 +4272,18 @@
         <v>46202</v>
       </c>
       <c r="S37" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="T37" s="10">
         <v>0</v>
       </c>
       <c r="U37" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B38" s="5">
         <v>46162.558422118054</v>
@@ -4272,16 +4293,16 @@
         <v>46191.169293900464</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I38" s="5">
         <v>46190</v>
@@ -4299,13 +4320,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -4315,7 +4336,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B39" s="9">
         <v>46162.558426400465</v>
@@ -4325,16 +4346,16 @@
         <v>46171.17362893518</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I39" s="9">
         <v>46161</v>
@@ -4352,13 +4373,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4368,7 +4389,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46162.55843366898</v>
@@ -4378,16 +4399,16 @@
         <v>46169.862598437496</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I40" s="5">
         <v>46190</v>
@@ -4405,10 +4426,10 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>26</v>
@@ -4426,12 +4447,12 @@
         <v>0</v>
       </c>
       <c r="U40" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B41" s="9">
         <v>46162.558437569445</v>
@@ -4441,16 +4462,16 @@
         <v>46169.86271082176</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I41" s="9">
         <v>46190</v>
@@ -4468,13 +4489,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4484,7 +4505,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B42" s="5">
         <v>46162.55844153935</v>
@@ -4494,16 +4515,16 @@
         <v>46169.86272391204</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I42" s="5">
         <v>46199</v>
@@ -4521,13 +4542,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4537,7 +4558,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B43" s="9">
         <v>46162.55844576389</v>
@@ -4547,16 +4568,16 @@
         <v>46169.862742349535</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I43" s="9">
         <v>46230</v>
@@ -4574,10 +4595,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4590,7 +4611,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B44" s="5">
         <v>46162.55844833334</v>
@@ -4600,16 +4621,16 @@
         <v>46195.18491668982</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I44" s="5">
         <v>46190</v>
@@ -4627,10 +4648,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4642,18 +4663,18 @@
         <v>46202</v>
       </c>
       <c r="S44" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
       </c>
       <c r="U44" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B45" s="9">
         <v>46162.55845114583</v>
@@ -4663,16 +4684,16 @@
         <v>46191.169297465276</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I45" s="9">
         <v>46190</v>
@@ -4690,13 +4711,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4706,7 +4727,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5">
         <v>46162.55845520833</v>
@@ -4716,16 +4737,16 @@
         <v>46169.86267059028</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I46" s="5">
         <v>46192</v>
@@ -4743,13 +4764,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4759,7 +4780,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B47" s="9">
         <v>46162.55817767361</v>
@@ -4769,7 +4790,7 @@
         <v>46162.592308611114</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>25</v>
@@ -4793,7 +4814,7 @@
         <v>26</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4806,26 +4827,26 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46162.55845957176</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46168.171851990744</v>
+        <v>46197.656501307865</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I48" s="5">
         <v>46160</v>
@@ -4843,13 +4864,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>60</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46160</v>
@@ -4863,13 +4884,13 @@
       <c r="T48" s="6">
         <v>0</v>
       </c>
-      <c r="U48" s="11" t="s">
+      <c r="U48" s="12" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <v>46162.55846439815</v>
@@ -4879,16 +4900,16 @@
         <v>46185.19214944444</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I49" s="9">
         <v>46176</v>
@@ -4906,13 +4927,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="9">
         <v>46176</v>
@@ -4927,12 +4948,12 @@
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46162.55847024306</v>
@@ -4948,10 +4969,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I50" s="6"/>
       <c r="J50" s="5">
@@ -4967,13 +4988,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q50" s="5">
         <v>46185</v>
@@ -4988,12 +5009,12 @@
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B51" s="9">
         <v>46162.55848571759</v>
@@ -5003,16 +5024,16 @@
         <v>46162.671697337966</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I51" s="9">
         <v>46225</v>
@@ -5030,10 +5051,10 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>26</v>
@@ -5051,12 +5072,12 @@
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46162.5584890162</v>
@@ -5066,16 +5087,16 @@
         <v>46191.68638508102</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -5091,13 +5112,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -5107,7 +5128,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B53" s="9">
         <v>46162.558492951386</v>
@@ -5117,16 +5138,16 @@
         <v>46191.68638201389</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
@@ -5142,13 +5163,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -5158,7 +5179,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B54" s="5">
         <v>46162.55849660879</v>
@@ -5168,16 +5189,16 @@
         <v>46191.68637913195</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -5193,13 +5214,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5209,7 +5230,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B55" s="9">
         <v>46162.55849916667</v>
@@ -5219,16 +5240,16 @@
         <v>46191.68637614584</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -5244,13 +5265,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5260,7 +5281,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B56" s="5">
         <v>46162.55850175926</v>
@@ -5270,16 +5291,16 @@
         <v>46191.6863727662</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -5295,13 +5316,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5311,7 +5332,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B57" s="9">
         <v>46162.56211614583</v>
@@ -5321,16 +5342,16 @@
         <v>46191.686369641204</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="9">
@@ -5346,10 +5367,10 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -5362,7 +5383,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B58" s="5">
         <v>46162.56212396991</v>
@@ -5372,16 +5393,16 @@
         <v>46191.68636637731</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -5397,13 +5418,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5413,7 +5434,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B59" s="9">
         <v>46162.56213497685</v>
@@ -5423,16 +5444,16 @@
         <v>46191.686363761575</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="9">
@@ -5448,13 +5469,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5464,7 +5485,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B60" s="5">
         <v>46162.562155057865</v>
@@ -5474,16 +5495,16 @@
         <v>46191.6863608912</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5499,10 +5520,10 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5515,7 +5536,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B61" s="9">
         <v>46162.562163055554</v>
@@ -5525,16 +5546,16 @@
         <v>46191.68635278935</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="9">
@@ -5550,10 +5571,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5566,7 +5587,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B62" s="5">
         <v>46162.56217104167</v>
@@ -5576,16 +5597,16 @@
         <v>46191.68635209491</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I62" s="6"/>
       <c r="J62" s="5">
@@ -5601,10 +5622,10 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5617,7 +5638,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B63" s="9">
         <v>46162.562178935186</v>
@@ -5627,16 +5648,16 @@
         <v>46191.686351412034</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="9">
@@ -5652,13 +5673,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5668,7 +5689,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B64" s="5">
         <v>46162.55850443287</v>
@@ -5678,7 +5699,7 @@
         <v>46162.60484554398</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>25</v>
@@ -5702,7 +5723,7 @@
         <v>26</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>26</v>
@@ -5715,7 +5736,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B65" s="9">
         <v>46162.558507546295</v>
@@ -5725,16 +5746,16 @@
         <v>46196.16939501157</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I65" s="9">
         <v>46203</v>
@@ -5752,13 +5773,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q65" s="9">
         <v>46203</v>
@@ -5767,18 +5788,18 @@
         <v>46203</v>
       </c>
       <c r="S65" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="T65" s="10">
         <v>0</v>
       </c>
       <c r="U65" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B66" s="5">
         <v>46162.5585121412</v>
@@ -5788,16 +5809,16 @@
         <v>46197.168534537035</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I66" s="5">
         <v>46204</v>
@@ -5815,13 +5836,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q66" s="5">
         <v>46204</v>
@@ -5830,18 +5851,18 @@
         <v>46204</v>
       </c>
       <c r="S66" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="T66" s="6">
         <v>0</v>
       </c>
       <c r="U66" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B67" s="9">
         <v>46162.558518645834</v>
@@ -5851,16 +5872,16 @@
         <v>46196.16939498842</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I67" s="9">
         <v>46203</v>
@@ -5878,13 +5899,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q67" s="9">
         <v>46203</v>
@@ -5893,18 +5914,18 @@
         <v>46203</v>
       </c>
       <c r="S67" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="T67" s="10">
         <v>0</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B68" s="5">
         <v>46162.55852324074</v>
@@ -5914,16 +5935,16 @@
         <v>46197.168534571756</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I68" s="5">
         <v>46204</v>
@@ -5941,13 +5962,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q68" s="5">
         <v>46204</v>
@@ -5956,18 +5977,18 @@
         <v>46204</v>
       </c>
       <c r="S68" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
       </c>
       <c r="U68" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B69" s="9">
         <v>46162.5585274537</v>
@@ -5977,16 +5998,16 @@
         <v>46196.16939524305</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I69" s="9">
         <v>46203</v>
@@ -6004,13 +6025,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q69" s="9">
         <v>46203</v>
@@ -6019,18 +6040,18 @@
         <v>46203</v>
       </c>
       <c r="S69" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="T69" s="10">
         <v>0</v>
       </c>
       <c r="U69" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B70" s="5">
         <v>46162.558531400464</v>
@@ -6040,16 +6061,16 @@
         <v>46197.16853431713</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I70" s="5">
         <v>46204</v>
@@ -6067,13 +6088,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q70" s="5">
         <v>46204</v>
@@ -6082,18 +6103,18 @@
         <v>46204</v>
       </c>
       <c r="S70" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="T70" s="6">
         <v>0</v>
       </c>
       <c r="U70" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B71" s="9">
         <v>46162.55853556713</v>
@@ -6103,7 +6124,7 @@
         <v>46162.61139740741</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -6127,7 +6148,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -6140,7 +6161,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B72" s="5">
         <v>46162.558538067125</v>
@@ -6150,16 +6171,16 @@
         <v>46162.672233703706</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I72" s="5">
         <v>46205</v>
@@ -6177,13 +6198,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q72" s="5">
         <v>46205</v>
@@ -6198,12 +6219,12 @@
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B73" s="9">
         <v>46162.558542557876</v>
@@ -6213,16 +6234,16 @@
         <v>46162.672237060186</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I73" s="9">
         <v>46205</v>
@@ -6240,13 +6261,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -6256,7 +6277,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B74" s="5">
         <v>46162.558548402776</v>
@@ -6266,16 +6287,16 @@
         <v>46162.67223377315</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I74" s="5">
         <v>46205</v>
@@ -6293,13 +6314,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6309,7 +6330,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B75" s="9">
         <v>46162.55855412037</v>
@@ -6319,16 +6340,16 @@
         <v>46162.67223053241</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I75" s="9">
         <v>46205</v>
@@ -6346,13 +6367,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6362,7 +6383,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B76" s="5">
         <v>46162.558560000005</v>
@@ -6372,16 +6393,16 @@
         <v>46162.67222738426</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I76" s="5">
         <v>46205</v>
@@ -6399,13 +6420,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6415,7 +6436,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B77" s="9">
         <v>46162.558565671294</v>
@@ -6425,16 +6446,16 @@
         <v>46162.67222361111</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I77" s="9">
         <v>46205</v>
@@ -6452,13 +6473,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6468,7 +6489,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B78" s="5">
         <v>46162.56018778935</v>
@@ -6478,16 +6499,16 @@
         <v>46162.672220196764</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I78" s="5">
         <v>46205</v>
@@ -6505,13 +6526,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6521,7 +6542,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B79" s="9">
         <v>46162.560207789356</v>
@@ -6531,16 +6552,16 @@
         <v>46162.67221694444</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I79" s="9">
         <v>46205</v>
@@ -6558,13 +6579,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6574,7 +6595,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B80" s="5">
         <v>46162.5602175463</v>
@@ -6584,16 +6605,16 @@
         <v>46162.67221386574</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I80" s="5">
         <v>46205</v>
@@ -6611,13 +6632,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6627,7 +6648,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B81" s="9">
         <v>46162.56022641204</v>
@@ -6637,16 +6658,16 @@
         <v>46162.67221096065</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I81" s="9">
         <v>46205</v>
@@ -6664,13 +6685,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6680,7 +6701,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B82" s="5">
         <v>46162.56023459491</v>
@@ -6690,16 +6711,16 @@
         <v>46162.67220178241</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I82" s="5">
         <v>46205</v>
@@ -6717,13 +6738,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6733,7 +6754,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B83" s="9">
         <v>46162.56024284722</v>
@@ -6743,16 +6764,16 @@
         <v>46162.67220103009</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I83" s="9">
         <v>46205</v>
@@ -6770,13 +6791,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6786,7 +6807,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B84" s="5">
         <v>46162.560250625</v>
@@ -6796,16 +6817,16 @@
         <v>46162.6722002662</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I84" s="5">
         <v>46205</v>
@@ -6823,13 +6844,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6839,7 +6860,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B85" s="9">
         <v>46162.55862063657</v>
@@ -6849,16 +6870,16 @@
         <v>46162.67249278935</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I85" s="9">
         <v>46210</v>
@@ -6876,13 +6897,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q85" s="9">
         <v>46210</v>
@@ -6897,12 +6918,12 @@
         <v>0</v>
       </c>
       <c r="U85" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B86" s="5">
         <v>46162.558626620375</v>
@@ -6912,16 +6933,16 @@
         <v>46162.67240607639</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I86" s="5">
         <v>46210</v>
@@ -6939,13 +6960,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6955,7 +6976,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B87" s="9">
         <v>46162.55863280092</v>
@@ -6965,16 +6986,16 @@
         <v>46162.672403136574</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I87" s="9">
         <v>46210</v>
@@ -6992,13 +7013,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -7008,7 +7029,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B88" s="5">
         <v>46162.55863850695</v>
@@ -7018,16 +7039,16 @@
         <v>46162.67239975695</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I88" s="5">
         <v>46210</v>
@@ -7045,13 +7066,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7061,7 +7082,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B89" s="9">
         <v>46162.558644247685</v>
@@ -7071,16 +7092,16 @@
         <v>46162.67239702547</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I89" s="9">
         <v>46210</v>
@@ -7098,13 +7119,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -7114,7 +7135,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B90" s="5">
         <v>46162.55864990741</v>
@@ -7124,16 +7145,16 @@
         <v>46162.67239402777</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I90" s="5">
         <v>46210</v>
@@ -7151,13 +7172,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7167,7 +7188,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B91" s="9">
         <v>46162.56148016204</v>
@@ -7177,16 +7198,16 @@
         <v>46162.672391064814</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I91" s="9">
         <v>46210</v>
@@ -7204,13 +7225,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7220,7 +7241,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B92" s="5">
         <v>46162.561489201384</v>
@@ -7230,16 +7251,16 @@
         <v>46162.672387743056</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I92" s="5">
         <v>46210</v>
@@ -7257,10 +7278,10 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>26</v>
@@ -7273,7 +7294,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B93" s="9">
         <v>46162.56149930556</v>
@@ -7283,16 +7304,16 @@
         <v>46162.67238480324</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I93" s="9">
         <v>46210</v>
@@ -7310,13 +7331,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7326,7 +7347,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B94" s="5">
         <v>46162.561507199076</v>
@@ -7336,16 +7357,16 @@
         <v>46162.67238212963</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I94" s="5">
         <v>46210</v>
@@ -7363,13 +7384,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7379,7 +7400,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B95" s="9">
         <v>46162.56151613426</v>
@@ -7389,16 +7410,16 @@
         <v>46162.67237393519</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I95" s="9">
         <v>46210</v>
@@ -7416,13 +7437,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7432,7 +7453,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B96" s="5">
         <v>46162.56152413195</v>
@@ -7442,16 +7463,16 @@
         <v>46162.67237322917</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I96" s="5">
         <v>46210</v>
@@ -7469,13 +7490,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7485,7 +7506,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B97" s="9">
         <v>46162.56153119213</v>
@@ -7495,16 +7516,16 @@
         <v>46162.67237256945</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I97" s="9">
         <v>46210</v>
@@ -7522,13 +7543,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7538,7 +7559,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B98" s="5">
         <v>46162.55865439815</v>
@@ -7548,16 +7569,16 @@
         <v>46162.67379204861</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I98" s="5">
         <v>46217</v>
@@ -7575,13 +7596,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q98" s="5">
         <v>46217</v>
@@ -7596,12 +7617,12 @@
         <v>0</v>
       </c>
       <c r="U98" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B99" s="9">
         <v>46162.55865909722</v>
@@ -7611,16 +7632,16 @@
         <v>46162.673765162035</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I99" s="9">
         <v>46217</v>
@@ -7638,13 +7659,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7654,7 +7675,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B100" s="5">
         <v>46162.55866501157</v>
@@ -7664,16 +7685,16 @@
         <v>46162.67376451389</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I100" s="5">
         <v>46217</v>
@@ -7691,13 +7712,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7707,7 +7728,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B101" s="9">
         <v>46162.55867084491</v>
@@ -7717,16 +7738,16 @@
         <v>46162.673763831015</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I101" s="9">
         <v>46217</v>
@@ -7744,13 +7765,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7760,7 +7781,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B102" s="5">
         <v>46162.558676597226</v>
@@ -7770,16 +7791,16 @@
         <v>46162.67376314815</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I102" s="5">
         <v>46217</v>
@@ -7797,13 +7818,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7813,7 +7834,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B103" s="9">
         <v>46162.55868239583</v>
@@ -7823,16 +7844,16 @@
         <v>46162.67376247685</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I103" s="9">
         <v>46217</v>
@@ -7850,13 +7871,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7866,7 +7887,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B104" s="5">
         <v>46162.56176834491</v>
@@ -7876,16 +7897,16 @@
         <v>46162.67376181713</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I104" s="5">
         <v>46217</v>
@@ -7903,13 +7924,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7919,7 +7940,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B105" s="9">
         <v>46162.56177670139</v>
@@ -7929,16 +7950,16 @@
         <v>46162.67376091435</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I105" s="9">
         <v>46217</v>
@@ -7956,13 +7977,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7972,7 +7993,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B106" s="5">
         <v>46162.56178474537</v>
@@ -7982,16 +8003,16 @@
         <v>46162.67376023148</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I106" s="5">
         <v>46217</v>
@@ -8009,13 +8030,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8025,7 +8046,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B107" s="9">
         <v>46162.56179298611</v>
@@ -8035,16 +8056,16 @@
         <v>46162.67375957176</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I107" s="9">
         <v>46217</v>
@@ -8062,13 +8083,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -8078,7 +8099,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B108" s="5">
         <v>46162.5618009375</v>
@@ -8088,16 +8109,16 @@
         <v>46162.67375887731</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I108" s="5">
         <v>46217</v>
@@ -8115,13 +8136,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8131,7 +8152,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B109" s="9">
         <v>46162.56180909723</v>
@@ -8141,16 +8162,16 @@
         <v>46162.67375819445</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I109" s="9">
         <v>46217</v>
@@ -8168,13 +8189,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8184,7 +8205,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B110" s="5">
         <v>46162.56181716435</v>
@@ -8194,16 +8215,16 @@
         <v>46162.67375751157</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I110" s="5">
         <v>46217</v>
@@ -8221,13 +8242,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8237,7 +8258,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B111" s="9">
         <v>46162.55868650463</v>
@@ -8247,7 +8268,7 @@
         <v>46162.61466552083</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>25</v>
@@ -8271,7 +8292,7 @@
         <v>26</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>26</v>
@@ -8284,7 +8305,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B112" s="5">
         <v>46162.55869006945</v>
@@ -8294,16 +8315,16 @@
         <v>46162.673902361115</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I112" s="5">
         <v>46161</v>
@@ -8321,13 +8342,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q112" s="5">
         <v>46161</v>
@@ -8342,12 +8363,12 @@
         <v>0</v>
       </c>
       <c r="U112" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B113" s="9">
         <v>46162.558696921296</v>
@@ -8357,16 +8378,16 @@
         <v>46162.673898912035</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I113" s="9">
         <v>46161</v>
@@ -8384,13 +8405,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q113" s="9">
         <v>46161</v>
@@ -8405,12 +8426,12 @@
         <v>0</v>
       </c>
       <c r="U113" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B114" s="5">
         <v>46162.55870284722</v>
@@ -8420,16 +8441,16 @@
         <v>46197.17582074074</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I114" s="5">
         <v>46196</v>
@@ -8447,13 +8468,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q114" s="5">
         <v>46196</v>
@@ -8468,12 +8489,12 @@
         <v>0</v>
       </c>
       <c r="U114" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B115" s="9">
         <v>46162.55870962963</v>
@@ -8483,16 +8504,16 @@
         <v>46162.67389181713</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I115" s="9">
         <v>46232</v>
@@ -8510,13 +8531,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q115" s="9">
         <v>46232</v>
@@ -8531,12 +8552,12 @@
         <v>0</v>
       </c>
       <c r="U115" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B116" s="5">
         <v>46162.55871869213</v>
@@ -8546,7 +8567,7 @@
         <v>46162.64775322917</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>25</v>
@@ -8570,7 +8591,7 @@
         <v>26</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>26</v>
@@ -8583,7 +8604,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B117" s="9">
         <v>46162.55872223379</v>
@@ -8593,7 +8614,7 @@
         <v>46162.67400658564</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8620,13 +8641,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q117" s="9">
         <v>46218</v>
@@ -8641,12 +8662,12 @@
         <v>0</v>
       </c>
       <c r="U117" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B118" s="5">
         <v>46162.55873068287</v>
@@ -8656,7 +8677,7 @@
         <v>46162.674262650464</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8683,10 +8704,10 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>26</v>
@@ -8699,7 +8720,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B119" s="9">
         <v>46162.558735011575</v>
@@ -8709,7 +8730,7 @@
         <v>46162.67425921296</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8736,10 +8757,10 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P119" s="10" t="s">
         <v>26</v>
@@ -8752,7 +8773,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B120" s="5">
         <v>46162.55873951389</v>
@@ -8762,7 +8783,7 @@
         <v>46162.67425633102</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8789,13 +8810,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8805,7 +8826,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B121" s="9">
         <v>46162.55874386574</v>
@@ -8815,7 +8836,7 @@
         <v>46162.674253379635</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8842,13 +8863,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8858,7 +8879,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B122" s="5">
         <v>46162.55874813657</v>
@@ -8868,7 +8889,7 @@
         <v>46162.67425</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8895,13 +8916,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8911,7 +8932,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B123" s="9">
         <v>46162.56516702546</v>
@@ -8921,7 +8942,7 @@
         <v>46162.67424702546</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8948,13 +8969,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8964,7 +8985,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B124" s="5">
         <v>46162.56517383102</v>
@@ -8974,7 +8995,7 @@
         <v>46162.67424429399</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -9001,13 +9022,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9017,7 +9038,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B125" s="9">
         <v>46162.565181134254</v>
@@ -9027,7 +9048,7 @@
         <v>46162.674233321755</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -9054,13 +9075,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -9070,7 +9091,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B126" s="5">
         <v>46162.565189201385</v>
@@ -9080,7 +9101,7 @@
         <v>46162.67423263889</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9107,13 +9128,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9123,7 +9144,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B127" s="9">
         <v>46162.56519680556</v>
@@ -9133,7 +9154,7 @@
         <v>46162.674231944446</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -9160,13 +9181,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9176,7 +9197,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B128" s="5">
         <v>46162.565205590276</v>
@@ -9186,7 +9207,7 @@
         <v>46162.674231261575</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9213,13 +9234,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9229,7 +9250,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B129" s="9">
         <v>46162.565212013884</v>
@@ -9239,7 +9260,7 @@
         <v>46162.67423060186</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -9266,13 +9287,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9282,7 +9303,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B130" s="5">
         <v>46162.558751550925</v>
@@ -9292,7 +9313,7 @@
         <v>46162.67400341435</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9319,13 +9340,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q130" s="5">
         <v>46219</v>
@@ -9340,12 +9361,12 @@
         <v>0</v>
       </c>
       <c r="U130" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B131" s="9">
         <v>46162.558756238424</v>
@@ -9355,7 +9376,7 @@
         <v>46162.67439809028</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9380,13 +9401,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9396,7 +9417,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B132" s="5">
         <v>46162.55876204861</v>
@@ -9406,7 +9427,7 @@
         <v>46162.67439510417</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9431,13 +9452,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9447,7 +9468,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B133" s="9">
         <v>46162.55876745371</v>
@@ -9457,7 +9478,7 @@
         <v>46162.6743919213</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9482,13 +9503,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9498,7 +9519,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B134" s="5">
         <v>46162.558773888886</v>
@@ -9508,7 +9529,7 @@
         <v>46162.674388368054</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9533,13 +9554,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9549,7 +9570,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B135" s="9">
         <v>46162.558827430556</v>
@@ -9559,7 +9580,7 @@
         <v>46162.67438523148</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9584,13 +9605,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9600,7 +9621,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B136" s="5">
         <v>46162.565477233795</v>
@@ -9610,7 +9631,7 @@
         <v>46162.67438189815</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9635,13 +9656,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9651,7 +9672,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B137" s="9">
         <v>46162.56548539352</v>
@@ -9661,7 +9682,7 @@
         <v>46162.67437871528</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9686,13 +9707,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9702,7 +9723,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B138" s="5">
         <v>46162.56549420139</v>
@@ -9712,7 +9733,7 @@
         <v>46162.67437079861</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9737,13 +9758,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9753,7 +9774,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B139" s="9">
         <v>46162.56549981482</v>
@@ -9763,7 +9784,7 @@
         <v>46162.674370127315</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -9788,13 +9809,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9804,7 +9825,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B140" s="5">
         <v>46162.565507719904</v>
@@ -9814,7 +9835,7 @@
         <v>46162.6743691088</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9839,13 +9860,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9855,7 +9876,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B141" s="9">
         <v>46162.56551637732</v>
@@ -9865,7 +9886,7 @@
         <v>46162.6743640162</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -9890,13 +9911,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9906,7 +9927,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B142" s="5">
         <v>46162.56598206019</v>
@@ -9916,7 +9937,7 @@
         <v>46162.67436230324</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9941,13 +9962,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9957,7 +9978,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B143" s="9">
         <v>46162.55883354167</v>
@@ -9967,7 +9988,7 @@
         <v>46162.674000150466</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -9994,13 +10015,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q143" s="9">
         <v>46220</v>
@@ -10015,12 +10036,12 @@
         <v>0</v>
       </c>
       <c r="U143" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B144" s="5">
         <v>46162.55883898148</v>
@@ -10030,7 +10051,7 @@
         <v>46162.67453761574</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -10057,13 +10078,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10073,7 +10094,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B145" s="9">
         <v>46162.55884618056</v>
@@ -10083,7 +10104,7 @@
         <v>46162.674534606485</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -10110,13 +10131,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -10126,7 +10147,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B146" s="5">
         <v>46162.55885335648</v>
@@ -10136,7 +10157,7 @@
         <v>46162.67453157407</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10163,13 +10184,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10179,7 +10200,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B147" s="9">
         <v>46162.558860624995</v>
@@ -10189,7 +10210,7 @@
         <v>46162.674528171294</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -10216,13 +10237,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10232,7 +10253,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B148" s="5">
         <v>46162.558867395834</v>
@@ -10242,7 +10263,7 @@
         <v>46162.674524965274</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10269,13 +10290,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10285,7 +10306,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B149" s="9">
         <v>46162.566146365745</v>
@@ -10295,7 +10316,7 @@
         <v>46162.674521354165</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -10322,13 +10343,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10338,7 +10359,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B150" s="5">
         <v>46162.566153101856</v>
@@ -10348,7 +10369,7 @@
         <v>46162.67451787037</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10375,13 +10396,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10391,7 +10412,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B151" s="9">
         <v>46162.56617111111</v>
@@ -10401,7 +10422,7 @@
         <v>46162.67451502314</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
@@ -10428,13 +10449,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10444,7 +10465,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B152" s="5">
         <v>46162.56618105324</v>
@@ -10454,7 +10475,7 @@
         <v>46162.67451243056</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10481,13 +10502,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10497,7 +10518,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B153" s="9">
         <v>46162.56618987268</v>
@@ -10507,7 +10528,7 @@
         <v>46162.67450335648</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10534,13 +10555,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q153" s="10"/>
       <c r="R153" s="10"/>
@@ -10550,7 +10571,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B154" s="5">
         <v>46162.56620271991</v>
@@ -10560,7 +10581,7 @@
         <v>46162.67450263889</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10587,13 +10608,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10603,7 +10624,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B155" s="9">
         <v>46162.56620673611</v>
@@ -10613,7 +10634,7 @@
         <v>46162.67450188658</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -10640,13 +10661,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q155" s="10"/>
       <c r="R155" s="10"/>
@@ -10656,7 +10677,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B156" s="5">
         <v>46162.558871574074</v>
@@ -10666,7 +10687,7 @@
         <v>46162.673997199076</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10693,13 +10714,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q156" s="5">
         <v>46223</v>
@@ -10714,12 +10735,12 @@
         <v>0</v>
       </c>
       <c r="U156" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B157" s="9">
         <v>46162.55887622685</v>
@@ -10729,7 +10750,7 @@
         <v>46162.674694375004</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
@@ -10756,13 +10777,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q157" s="10"/>
       <c r="R157" s="10"/>
@@ -10772,7 +10793,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B158" s="5">
         <v>46162.55888300926</v>
@@ -10782,7 +10803,7 @@
         <v>46162.67469101852</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10809,13 +10830,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10825,7 +10846,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B159" s="9">
         <v>46162.558892581015</v>
@@ -10835,7 +10856,7 @@
         <v>46162.674687928244</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
@@ -10862,13 +10883,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P159" s="10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q159" s="10"/>
       <c r="R159" s="10"/>
@@ -10878,7 +10899,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B160" s="5">
         <v>46162.55889858796</v>
@@ -10888,7 +10909,7 @@
         <v>46162.67468512732</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -10915,13 +10936,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -10931,7 +10952,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B161" s="9">
         <v>46162.558904618054</v>
@@ -10941,7 +10962,7 @@
         <v>46162.674682349534</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
@@ -10968,13 +10989,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P161" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q161" s="10"/>
       <c r="R161" s="10"/>
@@ -10984,7 +11005,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B162" s="5">
         <v>46162.566379375</v>
@@ -10994,7 +11015,7 @@
         <v>46162.674678888885</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -11021,13 +11042,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11037,7 +11058,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B163" s="9">
         <v>46162.56638695602</v>
@@ -11047,7 +11068,7 @@
         <v>46162.67467586805</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
@@ -11074,13 +11095,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -11090,7 +11111,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B164" s="5">
         <v>46162.56639532407</v>
@@ -11100,7 +11121,7 @@
         <v>46162.67467314815</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11127,13 +11148,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11143,7 +11164,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B165" s="9">
         <v>46162.56640418981</v>
@@ -11153,7 +11174,7 @@
         <v>46162.67467030093</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
@@ -11180,13 +11201,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -11196,7 +11217,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B166" s="5">
         <v>46162.56641240741</v>
@@ -11206,7 +11227,7 @@
         <v>46162.67466239583</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11233,13 +11254,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q166" s="6"/>
       <c r="R166" s="6"/>
@@ -11249,7 +11270,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B167" s="9">
         <v>46162.56642033564</v>
@@ -11259,7 +11280,7 @@
         <v>46162.674661655095</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
@@ -11286,13 +11307,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q167" s="10"/>
       <c r="R167" s="10"/>
@@ -11302,7 +11323,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B168" s="5">
         <v>46162.566427708334</v>
@@ -11312,7 +11333,7 @@
         <v>46162.67466097222</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11339,13 +11360,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
@@ -11355,7 +11376,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B169" s="9">
         <v>46162.558908946754</v>
@@ -11365,7 +11386,7 @@
         <v>46162.67399393518</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
@@ -11392,13 +11413,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P169" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q169" s="9">
         <v>46224</v>
@@ -11413,12 +11434,12 @@
         <v>0</v>
       </c>
       <c r="U169" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B170" s="5">
         <v>46162.55891369213</v>
@@ -11428,7 +11449,7 @@
         <v>46162.67483585648</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11453,13 +11474,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
@@ -11469,7 +11490,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B171" s="9">
         <v>46162.55891930556</v>
@@ -11479,7 +11500,7 @@
         <v>46162.674832847224</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11504,13 +11525,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q171" s="10"/>
       <c r="R171" s="10"/>
@@ -11520,7 +11541,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B172" s="5">
         <v>46162.558924930556</v>
@@ -11530,7 +11551,7 @@
         <v>46162.67482962963</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11555,13 +11576,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11571,7 +11592,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B173" s="9">
         <v>46162.55893104167</v>
@@ -11581,7 +11602,7 @@
         <v>46162.67482693287</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
@@ -11606,13 +11627,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11622,7 +11643,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B174" s="5">
         <v>46162.55893646991</v>
@@ -11632,7 +11653,7 @@
         <v>46162.67482414352</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
@@ -11657,13 +11678,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -11673,7 +11694,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B175" s="9">
         <v>46162.567320891205</v>
@@ -11683,7 +11704,7 @@
         <v>46162.67482128472</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
@@ -11708,10 +11729,10 @@
         <v>26</v>
       </c>
       <c r="N175" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P175" s="10" t="s">
         <v>26</v>
@@ -11724,7 +11745,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B176" s="5">
         <v>46162.567330034726</v>
@@ -11734,7 +11755,7 @@
         <v>46162.67481818287</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
@@ -11759,13 +11780,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
@@ -11775,7 +11796,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B177" s="9">
         <v>46162.567337685185</v>
@@ -11785,7 +11806,7 @@
         <v>46162.674815543985</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
@@ -11810,10 +11831,10 @@
         <v>26</v>
       </c>
       <c r="N177" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O177" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P177" s="10" t="s">
         <v>26</v>
@@ -11826,7 +11847,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B178" s="5">
         <v>46162.567344166666</v>
@@ -11836,7 +11857,7 @@
         <v>46162.674812743055</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
@@ -11861,10 +11882,10 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P178" s="6" t="s">
         <v>26</v>
@@ -11877,7 +11898,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B179" s="9">
         <v>46162.56735135417</v>
@@ -11887,7 +11908,7 @@
         <v>46162.67480497685</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
@@ -11912,10 +11933,10 @@
         <v>26</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O179" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P179" s="10" t="s">
         <v>26</v>
@@ -11928,7 +11949,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B180" s="5">
         <v>46162.5673590625</v>
@@ -11938,7 +11959,7 @@
         <v>46162.674804317125</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
@@ -11963,10 +11984,10 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P180" s="6" t="s">
         <v>26</v>
@@ -11979,7 +12000,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B181" s="9">
         <v>46162.567366284726</v>
@@ -11989,7 +12010,7 @@
         <v>46162.674803587965</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>26</v>
@@ -12014,13 +12035,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O181" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P181" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q181" s="10"/>
       <c r="R181" s="10"/>
@@ -12030,7 +12051,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B182" s="5">
         <v>46162.558941678246</v>
@@ -12040,7 +12061,7 @@
         <v>46162.673987789356</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
@@ -12067,13 +12088,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q182" s="5">
         <v>46226</v>
@@ -12088,12 +12109,12 @@
         <v>0</v>
       </c>
       <c r="U182" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B183" s="9">
         <v>46162.5589471875</v>
@@ -12103,7 +12124,7 @@
         <v>46162.675084849536</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>26</v>
@@ -12128,13 +12149,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O183" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P183" s="10" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q183" s="10"/>
       <c r="R183" s="10"/>
@@ -12144,7 +12165,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B184" s="5">
         <v>46162.55895184028</v>
@@ -12154,7 +12175,7 @@
         <v>46162.67508193287</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
@@ -12179,13 +12200,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12195,7 +12216,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B185" s="9">
         <v>46162.55895655093</v>
@@ -12205,7 +12226,7 @@
         <v>46162.67507869213</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
@@ -12230,13 +12251,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -12246,7 +12267,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B186" s="5">
         <v>46162.5589959375</v>
@@ -12256,7 +12277,7 @@
         <v>46162.67507611111</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
@@ -12281,13 +12302,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12297,7 +12318,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B187" s="9">
         <v>46162.55900136574</v>
@@ -12307,7 +12328,7 @@
         <v>46162.6750730787</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
@@ -12332,13 +12353,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P187" s="10" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q187" s="10"/>
       <c r="R187" s="10"/>
@@ -12348,7 +12369,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B188" s="5">
         <v>46162.56759152778</v>
@@ -12358,7 +12379,7 @@
         <v>46162.675070150464</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12383,10 +12404,10 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P188" s="6" t="s">
         <v>26</v>
@@ -12399,7 +12420,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B189" s="9">
         <v>46162.56759846065</v>
@@ -12409,7 +12430,7 @@
         <v>46162.6750674537</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
@@ -12434,13 +12455,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12450,7 +12471,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B190" s="5">
         <v>46162.56760671297</v>
@@ -12460,7 +12481,7 @@
         <v>46162.67506488426</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12485,13 +12506,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12501,7 +12522,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B191" s="9">
         <v>46162.56761416666</v>
@@ -12511,7 +12532,7 @@
         <v>46162.67506164352</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
@@ -12536,13 +12557,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12552,7 +12573,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B192" s="5">
         <v>46162.56762221065</v>
@@ -12562,7 +12583,7 @@
         <v>46162.67505446759</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -12587,13 +12608,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12603,7 +12624,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B193" s="9">
         <v>46162.56762855324</v>
@@ -12613,7 +12634,7 @@
         <v>46162.675053750005</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>26</v>
@@ -12638,13 +12659,13 @@
         <v>26</v>
       </c>
       <c r="N193" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O193" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P193" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q193" s="10"/>
       <c r="R193" s="10"/>
@@ -12654,7 +12675,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B194" s="5">
         <v>46162.56763415509</v>
@@ -12664,7 +12685,7 @@
         <v>46162.67505302084</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
@@ -12689,13 +12710,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -12705,7 +12726,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B195" s="9">
         <v>46162.55900565972</v>
@@ -12715,7 +12736,7 @@
         <v>46162.663939108796</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>25</v>
@@ -12739,7 +12760,7 @@
         <v>26</v>
       </c>
       <c r="O195" s="10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P195" s="10" t="s">
         <v>26</v>
@@ -12752,7 +12773,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B196" s="5">
         <v>46162.55900940972</v>
@@ -12762,16 +12783,16 @@
         <v>46162.67540229167</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G196" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H196" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I196" s="5">
         <v>46227</v>
@@ -12789,13 +12810,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q196" s="5">
         <v>46227</v>
@@ -12810,12 +12831,12 @@
         <v>0</v>
       </c>
       <c r="U196" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B197" s="9">
         <v>46162.559015023144</v>
@@ -12825,16 +12846,16 @@
         <v>46162.67538505787</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G197" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H197" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I197" s="10"/>
       <c r="J197" s="9">
@@ -12850,13 +12871,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O197" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P197" s="10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q197" s="10"/>
       <c r="R197" s="10"/>
@@ -12866,7 +12887,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B198" s="5">
         <v>46162.55901939815</v>
@@ -12876,16 +12897,16 @@
         <v>46162.675382534726</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I198" s="6"/>
       <c r="J198" s="5">
@@ -12901,13 +12922,13 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q198" s="6"/>
       <c r="R198" s="6"/>
@@ -12917,7 +12938,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B199" s="9">
         <v>46162.55902388888</v>
@@ -12927,16 +12948,16 @@
         <v>46162.67537990741</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G199" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H199" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I199" s="10"/>
       <c r="J199" s="9">
@@ -12952,13 +12973,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O199" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P199" s="10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q199" s="10"/>
       <c r="R199" s="10"/>
@@ -12968,7 +12989,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B200" s="5">
         <v>46162.559028090276</v>
@@ -12978,16 +12999,16 @@
         <v>46162.67537715277</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H200" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I200" s="6"/>
       <c r="J200" s="5">
@@ -13003,13 +13024,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -13019,7 +13040,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B201" s="9">
         <v>46162.559032060184</v>
@@ -13029,16 +13050,16 @@
         <v>46162.675374178245</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G201" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H201" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I201" s="10"/>
       <c r="J201" s="9">
@@ -13054,13 +13075,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O201" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P201" s="10" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Q201" s="10"/>
       <c r="R201" s="10"/>
@@ -13070,7 +13091,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B202" s="5">
         <v>46162.56847083333</v>
@@ -13080,16 +13101,16 @@
         <v>46162.675371296296</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H202" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I202" s="6"/>
       <c r="J202" s="5">
@@ -13105,13 +13126,13 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q202" s="6"/>
       <c r="R202" s="6"/>
@@ -13121,7 +13142,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B203" s="9">
         <v>46162.5684778588</v>
@@ -13131,16 +13152,16 @@
         <v>46162.675368321754</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H203" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I203" s="10"/>
       <c r="J203" s="9">
@@ -13156,10 +13177,10 @@
         <v>26</v>
       </c>
       <c r="N203" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P203" s="10" t="s">
         <v>26</v>
@@ -13172,7 +13193,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B204" s="5">
         <v>46162.56848583333</v>
@@ -13182,16 +13203,16 @@
         <v>46162.67536565972</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H204" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I204" s="6"/>
       <c r="J204" s="5">
@@ -13207,13 +13228,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13223,7 +13244,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B205" s="9">
         <v>46162.56849315972</v>
@@ -13233,16 +13254,16 @@
         <v>46162.67536296297</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G205" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H205" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I205" s="10"/>
       <c r="J205" s="9">
@@ -13258,13 +13279,13 @@
         <v>26</v>
       </c>
       <c r="N205" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q205" s="10"/>
       <c r="R205" s="10"/>
@@ -13274,7 +13295,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B206" s="5">
         <v>46162.568499120374</v>
@@ -13284,16 +13305,16 @@
         <v>46162.67535506944</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H206" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I206" s="6"/>
       <c r="J206" s="5">
@@ -13309,13 +13330,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13325,7 +13346,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B207" s="9">
         <v>46162.568507013886</v>
@@ -13335,16 +13356,16 @@
         <v>46162.67535439815</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H207" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I207" s="10"/>
       <c r="J207" s="9">
@@ -13360,13 +13381,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q207" s="10"/>
       <c r="R207" s="10"/>
@@ -13376,7 +13397,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B208" s="5">
         <v>46162.56851576389</v>
@@ -13386,16 +13407,16 @@
         <v>46162.67535373842</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H208" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I208" s="6"/>
       <c r="J208" s="5">
@@ -13411,13 +13432,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q208" s="6"/>
       <c r="R208" s="6"/>
@@ -13427,7 +13448,7 @@
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B209" s="9">
         <v>46162.559035983795</v>
@@ -13437,7 +13458,7 @@
         <v>46162.675601435185</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
@@ -13464,13 +13485,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P209" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q209" s="9">
         <v>46230</v>
@@ -13485,12 +13506,12 @@
         <v>0</v>
       </c>
       <c r="U209" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B210" s="5">
         <v>46162.559040057866</v>
@@ -13500,7 +13521,7 @@
         <v>46162.67559398148</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
@@ -13525,13 +13546,13 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O210" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P210" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Q210" s="6"/>
       <c r="R210" s="6"/>
@@ -13541,7 +13562,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B211" s="9">
         <v>46162.559044305555</v>
@@ -13551,7 +13572,7 @@
         <v>46162.67559118055</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>26</v>
@@ -13576,13 +13597,13 @@
         <v>26</v>
       </c>
       <c r="N211" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O211" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P211" s="10" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Q211" s="10"/>
       <c r="R211" s="10"/>
@@ -13592,7 +13613,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B212" s="5">
         <v>46162.55904842593</v>
@@ -13602,7 +13623,7 @@
         <v>46162.675588391205</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
@@ -13627,13 +13648,13 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P212" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Q212" s="6"/>
       <c r="R212" s="6"/>
@@ -13643,7 +13664,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B213" s="9">
         <v>46162.55905241898</v>
@@ -13653,7 +13674,7 @@
         <v>46162.67558560186</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>26</v>
@@ -13678,13 +13699,13 @@
         <v>26</v>
       </c>
       <c r="N213" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O213" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P213" s="10" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Q213" s="10"/>
       <c r="R213" s="10"/>
@@ -13694,7 +13715,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B214" s="5">
         <v>46162.55905643519</v>
@@ -13704,7 +13725,7 @@
         <v>46162.67558284722</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
@@ -13729,13 +13750,13 @@
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P214" s="6" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Q214" s="6"/>
       <c r="R214" s="6"/>
@@ -13745,7 +13766,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B215" s="9">
         <v>46162.568794328705</v>
@@ -13755,7 +13776,7 @@
         <v>46162.6755797338</v>
       </c>
       <c r="E215" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F215" s="10" t="s">
         <v>26</v>
@@ -13780,10 +13801,10 @@
         <v>26</v>
       </c>
       <c r="N215" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O215" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P215" s="10" t="s">
         <v>26</v>
@@ -13796,7 +13817,7 @@
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B216" s="5">
         <v>46162.56880138889</v>
@@ -13806,7 +13827,7 @@
         <v>46162.675576967595</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
@@ -13831,13 +13852,13 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P216" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q216" s="6"/>
       <c r="R216" s="6"/>
@@ -13847,7 +13868,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B217" s="9">
         <v>46162.56880807871</v>
@@ -13857,7 +13878,7 @@
         <v>46162.67557431713</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>26</v>
@@ -13882,13 +13903,13 @@
         <v>26</v>
       </c>
       <c r="N217" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O217" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P217" s="10" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Q217" s="10"/>
       <c r="R217" s="10"/>
@@ -13898,7 +13919,7 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B218" s="5">
         <v>46162.56881548611</v>
@@ -13908,7 +13929,7 @@
         <v>46162.67557162037</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
@@ -13933,13 +13954,13 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P218" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q218" s="6"/>
       <c r="R218" s="6"/>
@@ -13949,7 +13970,7 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B219" s="9">
         <v>46162.56882248842</v>
@@ -13959,7 +13980,7 @@
         <v>46162.67556375</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>26</v>
@@ -13984,13 +14005,13 @@
         <v>26</v>
       </c>
       <c r="N219" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O219" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P219" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q219" s="10"/>
       <c r="R219" s="10"/>
@@ -14000,7 +14021,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B220" s="5">
         <v>46162.56882971065</v>
@@ -14010,7 +14031,7 @@
         <v>46162.675563020835</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
@@ -14035,13 +14056,13 @@
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P220" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q220" s="6"/>
       <c r="R220" s="6"/>
@@ -14051,7 +14072,7 @@
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B221" s="9">
         <v>46162.56883761574</v>
@@ -14061,7 +14082,7 @@
         <v>46162.67556230324</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
@@ -14086,13 +14107,13 @@
         <v>26</v>
       </c>
       <c r="N221" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P221" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q221" s="10"/>
       <c r="R221" s="10"/>
@@ -14102,7 +14123,7 @@
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B222" s="5">
         <v>46162.559060671294</v>
@@ -14112,16 +14133,16 @@
         <v>46162.67579302083</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H222" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I222" s="5">
         <v>46231</v>
@@ -14139,13 +14160,13 @@
         <v>26</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O222" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P222" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q222" s="5">
         <v>46231</v>
@@ -14160,12 +14181,12 @@
         <v>0</v>
       </c>
       <c r="U222" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="223" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" s="8" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B223" s="9">
         <v>46162.55906472223</v>
@@ -14175,16 +14196,16 @@
         <v>46162.67579450231</v>
       </c>
       <c r="E223" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G223" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H223" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I223" s="10"/>
       <c r="J223" s="9">
@@ -14200,13 +14221,13 @@
         <v>26</v>
       </c>
       <c r="N223" s="10" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O223" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P223" s="10" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="Q223" s="10"/>
       <c r="R223" s="10"/>
@@ -14216,7 +14237,7 @@
     </row>
     <row r="224" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B224" s="5">
         <v>46162.55907236111</v>
@@ -14226,16 +14247,16 @@
         <v>46162.6757915162</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H224" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I224" s="6"/>
       <c r="J224" s="5">
@@ -14251,13 +14272,13 @@
         <v>26</v>
       </c>
       <c r="N224" s="6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O224" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P224" s="6" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="Q224" s="6"/>
       <c r="R224" s="6"/>
@@ -14267,7 +14288,7 @@
     </row>
     <row r="225" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" s="8" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B225" s="9">
         <v>46162.55907862268</v>
@@ -14277,16 +14298,16 @@
         <v>46162.67578863426</v>
       </c>
       <c r="E225" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F225" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G225" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H225" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I225" s="10"/>
       <c r="J225" s="9">
@@ -14302,13 +14323,13 @@
         <v>26</v>
       </c>
       <c r="N225" s="10" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O225" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P225" s="10" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Q225" s="10"/>
       <c r="R225" s="10"/>
@@ -14318,7 +14339,7 @@
     </row>
     <row r="226" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B226" s="5">
         <v>46162.55908304398</v>
@@ -14328,16 +14349,16 @@
         <v>46162.67578590278</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F226" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H226" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I226" s="6"/>
       <c r="J226" s="5">
@@ -14353,13 +14374,13 @@
         <v>26</v>
       </c>
       <c r="N226" s="6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O226" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P226" s="6" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Q226" s="6"/>
       <c r="R226" s="6"/>
@@ -14369,7 +14390,7 @@
     </row>
     <row r="227" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" s="8" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B227" s="9">
         <v>46162.55908719907</v>
@@ -14379,16 +14400,16 @@
         <v>46162.67578289352</v>
       </c>
       <c r="E227" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F227" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G227" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H227" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I227" s="10"/>
       <c r="J227" s="9">
@@ -14404,13 +14425,13 @@
         <v>26</v>
       </c>
       <c r="N227" s="10" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O227" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P227" s="10" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="Q227" s="10"/>
       <c r="R227" s="10"/>
@@ -14420,7 +14441,7 @@
     </row>
     <row r="228" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B228" s="5">
         <v>46162.56901232639</v>
@@ -14430,16 +14451,16 @@
         <v>46162.67577962963</v>
       </c>
       <c r="E228" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F228" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G228" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H228" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I228" s="6"/>
       <c r="J228" s="5">
@@ -14455,13 +14476,13 @@
         <v>26</v>
       </c>
       <c r="N228" s="6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O228" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P228" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q228" s="6"/>
       <c r="R228" s="6"/>
@@ -14471,7 +14492,7 @@
     </row>
     <row r="229" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" s="8" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B229" s="9">
         <v>46162.569018888884</v>
@@ -14481,16 +14502,16 @@
         <v>46162.67577695602</v>
       </c>
       <c r="E229" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F229" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G229" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H229" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I229" s="10"/>
       <c r="J229" s="9">
@@ -14506,13 +14527,13 @@
         <v>26</v>
       </c>
       <c r="N229" s="10" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O229" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P229" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q229" s="10"/>
       <c r="R229" s="10"/>
@@ -14522,7 +14543,7 @@
     </row>
     <row r="230" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B230" s="5">
         <v>46162.56902688657</v>
@@ -14532,16 +14553,16 @@
         <v>46162.67577410879</v>
       </c>
       <c r="E230" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F230" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G230" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H230" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I230" s="6"/>
       <c r="J230" s="5">
@@ -14557,13 +14578,13 @@
         <v>26</v>
       </c>
       <c r="N230" s="6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O230" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P230" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q230" s="6"/>
       <c r="R230" s="6"/>
@@ -14573,7 +14594,7 @@
     </row>
     <row r="231" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A231" s="8" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B231" s="9">
         <v>46162.56903291667</v>
@@ -14583,16 +14604,16 @@
         <v>46162.67577162037</v>
       </c>
       <c r="E231" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F231" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G231" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H231" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I231" s="10"/>
       <c r="J231" s="9">
@@ -14608,13 +14629,13 @@
         <v>26</v>
       </c>
       <c r="N231" s="10" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O231" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P231" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q231" s="10"/>
       <c r="R231" s="10"/>
@@ -14624,7 +14645,7 @@
     </row>
     <row r="232" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B232" s="5">
         <v>46162.56903989583</v>
@@ -14634,16 +14655,16 @@
         <v>46162.67576392361</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F232" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G232" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H232" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I232" s="6"/>
       <c r="J232" s="5">
@@ -14659,13 +14680,13 @@
         <v>26</v>
       </c>
       <c r="N232" s="6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O232" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P232" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q232" s="6"/>
       <c r="R232" s="6"/>
@@ -14675,7 +14696,7 @@
     </row>
     <row r="233" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B233" s="9">
         <v>46162.56904635417</v>
@@ -14685,16 +14706,16 @@
         <v>46162.67576322917</v>
       </c>
       <c r="E233" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F233" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G233" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H233" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I233" s="10"/>
       <c r="J233" s="9">
@@ -14710,13 +14731,13 @@
         <v>26</v>
       </c>
       <c r="N233" s="10" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O233" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P233" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q233" s="10"/>
       <c r="R233" s="10"/>
@@ -14726,7 +14747,7 @@
     </row>
     <row r="234" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B234" s="5">
         <v>46162.56905347222</v>
@@ -14736,16 +14757,16 @@
         <v>46162.67576252315</v>
       </c>
       <c r="E234" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F234" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G234" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H234" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I234" s="6"/>
       <c r="J234" s="5">
@@ -14761,13 +14782,13 @@
         <v>26</v>
       </c>
       <c r="N234" s="6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O234" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P234" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q234" s="6"/>
       <c r="R234" s="6"/>
@@ -14777,7 +14798,7 @@
     </row>
     <row r="235" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A235" s="8" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B235" s="9">
         <v>46162.559091284726</v>
@@ -14787,16 +14808,16 @@
         <v>46162.6758584375</v>
       </c>
       <c r="E235" s="10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F235" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G235" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H235" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I235" s="9">
         <v>46232</v>
@@ -14814,13 +14835,13 @@
         <v>26</v>
       </c>
       <c r="N235" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O235" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P235" s="10" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Q235" s="9">
         <v>46232</v>
@@ -14835,12 +14856,12 @@
         <v>0</v>
       </c>
       <c r="U235" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="236" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B236" s="5">
         <v>46162.55909613426</v>
@@ -14850,16 +14871,16 @@
         <v>46162.676026875</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F236" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G236" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H236" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I236" s="5">
         <v>46232</v>
@@ -14877,13 +14898,13 @@
         <v>26</v>
       </c>
       <c r="N236" s="6" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O236" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P236" s="6" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="Q236" s="6"/>
       <c r="R236" s="6"/>
@@ -14893,7 +14914,7 @@
     </row>
     <row r="237" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A237" s="8" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B237" s="9">
         <v>46162.55910012731</v>
@@ -14903,16 +14924,16 @@
         <v>46162.67602255787</v>
       </c>
       <c r="E237" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F237" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G237" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H237" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I237" s="9">
         <v>46232</v>
@@ -14930,13 +14951,13 @@
         <v>26</v>
       </c>
       <c r="N237" s="10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O237" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P237" s="10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="Q237" s="10"/>
       <c r="R237" s="10"/>
@@ -14946,7 +14967,7 @@
     </row>
     <row r="238" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B238" s="5">
         <v>46162.55910407407</v>
@@ -14956,16 +14977,16 @@
         <v>46162.676019108796</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F238" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G238" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H238" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I238" s="5">
         <v>46232</v>
@@ -14983,13 +15004,13 @@
         <v>26</v>
       </c>
       <c r="N238" s="6" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O238" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P238" s="6" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="Q238" s="6"/>
       <c r="R238" s="6"/>
@@ -14999,7 +15020,7 @@
     </row>
     <row r="239" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A239" s="8" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B239" s="9">
         <v>46162.559108125</v>
@@ -15009,16 +15030,16 @@
         <v>46162.67601616898</v>
       </c>
       <c r="E239" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F239" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G239" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H239" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I239" s="9">
         <v>46232</v>
@@ -15036,13 +15057,13 @@
         <v>26</v>
       </c>
       <c r="N239" s="10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O239" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P239" s="10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="Q239" s="10"/>
       <c r="R239" s="10"/>
@@ -15052,7 +15073,7 @@
     </row>
     <row r="240" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B240" s="5">
         <v>46162.55914409722</v>
@@ -15062,16 +15083,16 @@
         <v>46162.676013275464</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F240" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G240" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H240" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I240" s="5">
         <v>46232</v>
@@ -15089,13 +15110,13 @@
         <v>26</v>
       </c>
       <c r="N240" s="6" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O240" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P240" s="6" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="Q240" s="6"/>
       <c r="R240" s="6"/>
@@ -15105,7 +15126,7 @@
     </row>
     <row r="241" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A241" s="8" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B241" s="9">
         <v>46162.56958915509</v>
@@ -15115,16 +15136,16 @@
         <v>46162.67600972222</v>
       </c>
       <c r="E241" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F241" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G241" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H241" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I241" s="9">
         <v>46232</v>
@@ -15142,10 +15163,10 @@
         <v>26</v>
       </c>
       <c r="N241" s="10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O241" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P241" s="10" t="s">
         <v>26</v>
@@ -15158,7 +15179,7 @@
     </row>
     <row r="242" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B242" s="5">
         <v>46162.56959587963</v>
@@ -15168,16 +15189,16 @@
         <v>46162.676007002316</v>
       </c>
       <c r="E242" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F242" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G242" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H242" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I242" s="5">
         <v>46232</v>
@@ -15195,10 +15216,10 @@
         <v>26</v>
       </c>
       <c r="N242" s="6" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O242" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P242" s="6" t="s">
         <v>26</v>
@@ -15211,7 +15232,7 @@
     </row>
     <row r="243" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A243" s="8" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B243" s="9">
         <v>46162.56960513889</v>
@@ -15221,16 +15242,16 @@
         <v>46162.67600369213</v>
       </c>
       <c r="E243" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F243" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G243" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H243" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I243" s="9">
         <v>46232</v>
@@ -15248,10 +15269,10 @@
         <v>26</v>
       </c>
       <c r="N243" s="10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O243" s="10" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="P243" s="10" t="s">
         <v>26</v>
@@ -15264,7 +15285,7 @@
     </row>
     <row r="244" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B244" s="5">
         <v>46162.569612060186</v>
@@ -15274,16 +15295,16 @@
         <v>46162.67599591435</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F244" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G244" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H244" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I244" s="5">
         <v>46232</v>
@@ -15301,10 +15322,10 @@
         <v>26</v>
       </c>
       <c r="N244" s="6" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O244" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P244" s="6" t="s">
         <v>26</v>
@@ -15317,7 +15338,7 @@
     </row>
     <row r="245" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A245" s="8" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B245" s="9">
         <v>46162.569619999995</v>
@@ -15327,16 +15348,16 @@
         <v>46162.67599258102</v>
       </c>
       <c r="E245" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F245" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G245" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H245" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I245" s="9">
         <v>46232</v>
@@ -15354,10 +15375,10 @@
         <v>26</v>
       </c>
       <c r="N245" s="10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O245" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P245" s="10" t="s">
         <v>26</v>
@@ -15370,7 +15391,7 @@
     </row>
     <row r="246" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B246" s="5">
         <v>46162.569627812496</v>
@@ -15380,16 +15401,16 @@
         <v>46162.675991412034</v>
       </c>
       <c r="E246" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F246" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G246" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H246" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I246" s="5">
         <v>46232</v>
@@ -15407,10 +15428,10 @@
         <v>26</v>
       </c>
       <c r="N246" s="6" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O246" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P246" s="6" t="s">
         <v>26</v>
@@ -15423,7 +15444,7 @@
     </row>
     <row r="247" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A247" s="8" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B247" s="9">
         <v>46162.569634513886</v>
@@ -15433,16 +15454,16 @@
         <v>46162.675990613425</v>
       </c>
       <c r="E247" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F247" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G247" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H247" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I247" s="9">
         <v>46232</v>
@@ -15460,10 +15481,10 @@
         <v>26</v>
       </c>
       <c r="N247" s="10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O247" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P247" s="10" t="s">
         <v>26</v>
@@ -15476,7 +15497,7 @@
     </row>
     <row r="248" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B248" s="5">
         <v>46162.5591494213</v>
@@ -15486,7 +15507,7 @@
         <v>46162.664148020835</v>
       </c>
       <c r="E248" s="6" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F248" s="6" t="s">
         <v>25</v>
@@ -15510,7 +15531,7 @@
         <v>26</v>
       </c>
       <c r="O248" s="6" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P248" s="6" t="s">
         <v>26</v>
@@ -15523,7 +15544,7 @@
     </row>
     <row r="249" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A249" s="8" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B249" s="9">
         <v>46162.559152800924</v>
@@ -15533,16 +15554,16 @@
         <v>46162.676061377315</v>
       </c>
       <c r="E249" s="10" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F249" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G249" s="10" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H249" s="10" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="I249" s="9">
         <v>46233</v>
@@ -15560,13 +15581,13 @@
         <v>26</v>
       </c>
       <c r="N249" s="10" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O249" s="10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="P249" s="10" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="Q249" s="9">
         <v>46233</v>
@@ -15581,12 +15602,12 @@
         <v>0</v>
       </c>
       <c r="U249" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="250" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B250" s="5">
         <v>46162.55915726852</v>
@@ -15596,7 +15617,7 @@
         <v>46162.67613450231</v>
       </c>
       <c r="E250" s="6" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F250" s="6" t="s">
         <v>26</v>
@@ -15623,13 +15644,13 @@
         <v>26</v>
       </c>
       <c r="N250" s="6" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O250" s="6" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="P250" s="6" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="Q250" s="5">
         <v>46233</v>
@@ -15644,7 +15665,7 @@
         <v>0</v>
       </c>
       <c r="U250" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2852" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2852" uniqueCount="518">
   <si>
     <t xml:space="preserve">50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT 4324 4325 </t>
   </si>
@@ -582,28 +582,34 @@
     <t>Planos preliminar</t>
   </si>
   <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214969466529004</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos motor proveedor OT 4324 4325</t>
+  </si>
+  <si>
+    <t>check planos,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>1214969379162030</t>
+  </si>
+  <si>
     <t>Hernan Roberto Gutierrez Barrientos</t>
   </si>
   <si>
     <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214969466529004</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos motor proveedor OT 4324 4325</t>
-  </si>
-  <si>
-    <t>check planos,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>1214969379162030</t>
   </si>
   <si>
     <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,Propuesta Mecanizado OT 4324 4325,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,Propuesta Fabricación externa  OT 4324 4325,propuesta Corte Laser OT 4324 4325,Propuesta Corte plasma  OT 4324 4325,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
@@ -3987,7 +3993,7 @@
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46175.17034748843</v>
+        <v>46197.676590358795</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>129</v>
@@ -4787,7 +4793,7 @@
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46162.592308611114</v>
+        <v>46197.674966516206</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>174</v>
@@ -4832,9 +4838,11 @@
       <c r="B48" s="5">
         <v>46162.55845957176</v>
       </c>
-      <c r="C48" s="6"/>
+      <c r="C48" s="5">
+        <v>46197.674961006946</v>
+      </c>
       <c r="D48" s="5">
-        <v>46197.656501307865</v>
+        <v>46197.67690475694</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4882,10 +4890,10 @@
         <v>33</v>
       </c>
       <c r="T48" s="6">
-        <v>0</v>
-      </c>
-      <c r="U48" s="12" t="s">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="U48" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4897,7 +4905,7 @@
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46185.19214944444</v>
+        <v>46197.680058750004</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>182</v>
@@ -4969,10 +4977,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="I50" s="6"/>
       <c r="J50" s="5">
@@ -4994,7 +5002,7 @@
         <v>182</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q50" s="5">
         <v>46185</v>
@@ -5014,7 +5022,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
         <v>46162.55848571759</v>
@@ -5024,16 +5032,16 @@
         <v>46162.671697337966</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I51" s="9">
         <v>46225</v>
@@ -5054,7 +5062,7 @@
         <v>174</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>26</v>
@@ -5077,7 +5085,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B52" s="5">
         <v>46162.5584890162</v>
@@ -5087,16 +5095,16 @@
         <v>46191.68638508102</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -5112,13 +5120,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -5128,7 +5136,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B53" s="9">
         <v>46162.558492951386</v>
@@ -5138,16 +5146,16 @@
         <v>46191.68638201389</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
@@ -5163,13 +5171,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -5179,7 +5187,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B54" s="5">
         <v>46162.55849660879</v>
@@ -5189,16 +5197,16 @@
         <v>46191.68637913195</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -5214,13 +5222,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5230,7 +5238,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B55" s="9">
         <v>46162.55849916667</v>
@@ -5240,16 +5248,16 @@
         <v>46191.68637614584</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -5265,13 +5273,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5281,7 +5289,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B56" s="5">
         <v>46162.55850175926</v>
@@ -5291,16 +5299,16 @@
         <v>46191.6863727662</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -5316,13 +5324,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5332,7 +5340,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B57" s="9">
         <v>46162.56211614583</v>
@@ -5342,16 +5350,16 @@
         <v>46191.686369641204</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="9">
@@ -5367,10 +5375,10 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -5383,7 +5391,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B58" s="5">
         <v>46162.56212396991</v>
@@ -5393,16 +5401,16 @@
         <v>46191.68636637731</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -5418,13 +5426,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5434,7 +5442,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B59" s="9">
         <v>46162.56213497685</v>
@@ -5444,16 +5452,16 @@
         <v>46191.686363761575</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="9">
@@ -5469,13 +5477,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5485,7 +5493,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B60" s="5">
         <v>46162.562155057865</v>
@@ -5495,16 +5503,16 @@
         <v>46191.6863608912</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5520,10 +5528,10 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5536,7 +5544,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B61" s="9">
         <v>46162.562163055554</v>
@@ -5546,16 +5554,16 @@
         <v>46191.68635278935</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="9">
@@ -5571,10 +5579,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5587,7 +5595,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B62" s="5">
         <v>46162.56217104167</v>
@@ -5597,16 +5605,16 @@
         <v>46191.68635209491</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I62" s="6"/>
       <c r="J62" s="5">
@@ -5622,10 +5630,10 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5638,7 +5646,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B63" s="9">
         <v>46162.562178935186</v>
@@ -5648,16 +5656,16 @@
         <v>46191.686351412034</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="9">
@@ -5673,13 +5681,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5689,7 +5697,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B64" s="5">
         <v>46162.55850443287</v>
@@ -5699,7 +5707,7 @@
         <v>46162.60484554398</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>25</v>
@@ -5723,7 +5731,7 @@
         <v>26</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>26</v>
@@ -5736,7 +5744,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B65" s="9">
         <v>46162.558507546295</v>
@@ -5746,16 +5754,16 @@
         <v>46196.16939501157</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I65" s="9">
         <v>46203</v>
@@ -5773,13 +5781,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="O65" s="10" t="s">
         <v>141</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q65" s="9">
         <v>46203</v>
@@ -5799,7 +5807,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B66" s="5">
         <v>46162.5585121412</v>
@@ -5809,7 +5817,7 @@
         <v>46197.168534537035</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5836,13 +5844,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q66" s="5">
         <v>46204</v>
@@ -5862,7 +5870,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B67" s="9">
         <v>46162.558518645834</v>
@@ -5872,16 +5880,16 @@
         <v>46196.16939498842</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I67" s="9">
         <v>46203</v>
@@ -5899,13 +5907,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>149</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q67" s="9">
         <v>46203</v>
@@ -5925,7 +5933,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B68" s="5">
         <v>46162.55852324074</v>
@@ -5935,7 +5943,7 @@
         <v>46197.168534571756</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5962,13 +5970,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q68" s="5">
         <v>46204</v>
@@ -5988,7 +5996,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B69" s="9">
         <v>46162.5585274537</v>
@@ -5998,16 +6006,16 @@
         <v>46196.16939524305</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I69" s="9">
         <v>46203</v>
@@ -6025,13 +6033,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>171</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q69" s="9">
         <v>46203</v>
@@ -6051,7 +6059,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B70" s="5">
         <v>46162.558531400464</v>
@@ -6061,7 +6069,7 @@
         <v>46197.16853431713</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -6088,13 +6096,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q70" s="5">
         <v>46204</v>
@@ -6114,7 +6122,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B71" s="9">
         <v>46162.55853556713</v>
@@ -6124,7 +6132,7 @@
         <v>46162.61139740741</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -6148,7 +6156,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -6161,7 +6169,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B72" s="5">
         <v>46162.558538067125</v>
@@ -6171,16 +6179,16 @@
         <v>46162.672233703706</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I72" s="5">
         <v>46205</v>
@@ -6198,13 +6206,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q72" s="5">
         <v>46205</v>
@@ -6224,7 +6232,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B73" s="9">
         <v>46162.558542557876</v>
@@ -6234,16 +6242,16 @@
         <v>46162.672237060186</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I73" s="9">
         <v>46205</v>
@@ -6261,13 +6269,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -6277,7 +6285,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B74" s="5">
         <v>46162.558548402776</v>
@@ -6287,16 +6295,16 @@
         <v>46162.67223377315</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I74" s="5">
         <v>46205</v>
@@ -6314,13 +6322,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6330,7 +6338,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B75" s="9">
         <v>46162.55855412037</v>
@@ -6340,16 +6348,16 @@
         <v>46162.67223053241</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I75" s="9">
         <v>46205</v>
@@ -6367,13 +6375,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O75" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="P75" s="10" t="s">
         <v>242</v>
-      </c>
-      <c r="P75" s="10" t="s">
-        <v>240</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6383,7 +6391,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B76" s="5">
         <v>46162.558560000005</v>
@@ -6393,16 +6401,16 @@
         <v>46162.67222738426</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I76" s="5">
         <v>46205</v>
@@ -6420,13 +6428,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6436,7 +6444,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B77" s="9">
         <v>46162.558565671294</v>
@@ -6446,16 +6454,16 @@
         <v>46162.67222361111</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I77" s="9">
         <v>46205</v>
@@ -6473,13 +6481,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6489,7 +6497,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B78" s="5">
         <v>46162.56018778935</v>
@@ -6499,16 +6507,16 @@
         <v>46162.672220196764</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I78" s="5">
         <v>46205</v>
@@ -6526,13 +6534,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6542,7 +6550,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B79" s="9">
         <v>46162.560207789356</v>
@@ -6552,16 +6560,16 @@
         <v>46162.67221694444</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I79" s="9">
         <v>46205</v>
@@ -6579,13 +6587,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6595,7 +6603,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B80" s="5">
         <v>46162.5602175463</v>
@@ -6605,16 +6613,16 @@
         <v>46162.67221386574</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I80" s="5">
         <v>46205</v>
@@ -6632,13 +6640,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6648,7 +6656,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B81" s="9">
         <v>46162.56022641204</v>
@@ -6658,16 +6666,16 @@
         <v>46162.67221096065</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I81" s="9">
         <v>46205</v>
@@ -6685,13 +6693,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6701,7 +6709,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B82" s="5">
         <v>46162.56023459491</v>
@@ -6711,16 +6719,16 @@
         <v>46162.67220178241</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I82" s="5">
         <v>46205</v>
@@ -6738,13 +6746,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6754,7 +6762,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B83" s="9">
         <v>46162.56024284722</v>
@@ -6764,16 +6772,16 @@
         <v>46162.67220103009</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I83" s="9">
         <v>46205</v>
@@ -6791,13 +6799,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6807,7 +6815,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B84" s="5">
         <v>46162.560250625</v>
@@ -6817,16 +6825,16 @@
         <v>46162.6722002662</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I84" s="5">
         <v>46205</v>
@@ -6844,13 +6852,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6860,7 +6868,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B85" s="9">
         <v>46162.55862063657</v>
@@ -6870,16 +6878,16 @@
         <v>46162.67249278935</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I85" s="9">
         <v>46210</v>
@@ -6897,13 +6905,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q85" s="9">
         <v>46210</v>
@@ -6923,7 +6931,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B86" s="5">
         <v>46162.558626620375</v>
@@ -6933,16 +6941,16 @@
         <v>46162.67240607639</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I86" s="5">
         <v>46210</v>
@@ -6960,13 +6968,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6976,7 +6984,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B87" s="9">
         <v>46162.55863280092</v>
@@ -6986,16 +6994,16 @@
         <v>46162.672403136574</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I87" s="9">
         <v>46210</v>
@@ -7013,13 +7021,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -7029,7 +7037,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B88" s="5">
         <v>46162.55863850695</v>
@@ -7039,16 +7047,16 @@
         <v>46162.67239975695</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I88" s="5">
         <v>46210</v>
@@ -7066,13 +7074,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7082,7 +7090,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B89" s="9">
         <v>46162.558644247685</v>
@@ -7092,16 +7100,16 @@
         <v>46162.67239702547</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I89" s="9">
         <v>46210</v>
@@ -7119,13 +7127,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -7135,7 +7143,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B90" s="5">
         <v>46162.55864990741</v>
@@ -7145,16 +7153,16 @@
         <v>46162.67239402777</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I90" s="5">
         <v>46210</v>
@@ -7172,13 +7180,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7188,7 +7196,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B91" s="9">
         <v>46162.56148016204</v>
@@ -7198,16 +7206,16 @@
         <v>46162.672391064814</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I91" s="9">
         <v>46210</v>
@@ -7225,13 +7233,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7241,7 +7249,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B92" s="5">
         <v>46162.561489201384</v>
@@ -7251,16 +7259,16 @@
         <v>46162.672387743056</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I92" s="5">
         <v>46210</v>
@@ -7278,10 +7286,10 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>26</v>
@@ -7294,7 +7302,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B93" s="9">
         <v>46162.56149930556</v>
@@ -7304,16 +7312,16 @@
         <v>46162.67238480324</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I93" s="9">
         <v>46210</v>
@@ -7331,13 +7339,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7347,7 +7355,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B94" s="5">
         <v>46162.561507199076</v>
@@ -7357,16 +7365,16 @@
         <v>46162.67238212963</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I94" s="5">
         <v>46210</v>
@@ -7384,13 +7392,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7400,7 +7408,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B95" s="9">
         <v>46162.56151613426</v>
@@ -7410,16 +7418,16 @@
         <v>46162.67237393519</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I95" s="9">
         <v>46210</v>
@@ -7437,13 +7445,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7453,7 +7461,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B96" s="5">
         <v>46162.56152413195</v>
@@ -7463,16 +7471,16 @@
         <v>46162.67237322917</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I96" s="5">
         <v>46210</v>
@@ -7490,13 +7498,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7506,7 +7514,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B97" s="9">
         <v>46162.56153119213</v>
@@ -7516,16 +7524,16 @@
         <v>46162.67237256945</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I97" s="9">
         <v>46210</v>
@@ -7543,13 +7551,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7559,7 +7567,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B98" s="5">
         <v>46162.55865439815</v>
@@ -7569,7 +7577,7 @@
         <v>46162.67379204861</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7596,13 +7604,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q98" s="5">
         <v>46217</v>
@@ -7622,7 +7630,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B99" s="9">
         <v>46162.55865909722</v>
@@ -7632,7 +7640,7 @@
         <v>46162.673765162035</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7659,13 +7667,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7675,7 +7683,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B100" s="5">
         <v>46162.55866501157</v>
@@ -7685,7 +7693,7 @@
         <v>46162.67376451389</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7712,13 +7720,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7728,7 +7736,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B101" s="9">
         <v>46162.55867084491</v>
@@ -7738,7 +7746,7 @@
         <v>46162.673763831015</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7765,13 +7773,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7781,7 +7789,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B102" s="5">
         <v>46162.558676597226</v>
@@ -7791,7 +7799,7 @@
         <v>46162.67376314815</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7818,13 +7826,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7834,7 +7842,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B103" s="9">
         <v>46162.55868239583</v>
@@ -7844,7 +7852,7 @@
         <v>46162.67376247685</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7871,13 +7879,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7887,7 +7895,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B104" s="5">
         <v>46162.56176834491</v>
@@ -7897,7 +7905,7 @@
         <v>46162.67376181713</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7924,13 +7932,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7940,7 +7948,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B105" s="9">
         <v>46162.56177670139</v>
@@ -7950,7 +7958,7 @@
         <v>46162.67376091435</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7977,13 +7985,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7993,7 +8001,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B106" s="5">
         <v>46162.56178474537</v>
@@ -8003,7 +8011,7 @@
         <v>46162.67376023148</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -8030,13 +8038,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8046,7 +8054,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B107" s="9">
         <v>46162.56179298611</v>
@@ -8056,7 +8064,7 @@
         <v>46162.67375957176</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -8083,13 +8091,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -8099,7 +8107,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B108" s="5">
         <v>46162.5618009375</v>
@@ -8109,7 +8117,7 @@
         <v>46162.67375887731</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8136,13 +8144,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8152,7 +8160,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B109" s="9">
         <v>46162.56180909723</v>
@@ -8162,7 +8170,7 @@
         <v>46162.67375819445</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -8189,13 +8197,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8205,7 +8213,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B110" s="5">
         <v>46162.56181716435</v>
@@ -8215,7 +8223,7 @@
         <v>46162.67375751157</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8242,13 +8250,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8258,7 +8266,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B111" s="9">
         <v>46162.55868650463</v>
@@ -8268,7 +8276,7 @@
         <v>46162.61466552083</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>25</v>
@@ -8292,7 +8300,7 @@
         <v>26</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>26</v>
@@ -8305,7 +8313,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B112" s="5">
         <v>46162.55869006945</v>
@@ -8315,16 +8323,16 @@
         <v>46162.673902361115</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I112" s="5">
         <v>46161</v>
@@ -8342,13 +8350,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>117</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q112" s="5">
         <v>46161</v>
@@ -8368,7 +8376,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B113" s="9">
         <v>46162.558696921296</v>
@@ -8378,16 +8386,16 @@
         <v>46162.673898912035</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I113" s="9">
         <v>46161</v>
@@ -8405,13 +8413,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="O113" s="10" t="s">
         <v>108</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q113" s="9">
         <v>46161</v>
@@ -8431,7 +8439,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B114" s="5">
         <v>46162.55870284722</v>
@@ -8441,16 +8449,16 @@
         <v>46197.17582074074</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I114" s="5">
         <v>46196</v>
@@ -8468,13 +8476,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>126</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q114" s="5">
         <v>46196</v>
@@ -8494,7 +8502,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B115" s="9">
         <v>46162.55870962963</v>
@@ -8504,16 +8512,16 @@
         <v>46162.67389181713</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I115" s="9">
         <v>46232</v>
@@ -8531,13 +8539,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="O115" s="10" t="s">
         <v>159</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q115" s="9">
         <v>46232</v>
@@ -8557,7 +8565,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B116" s="5">
         <v>46162.55871869213</v>
@@ -8567,7 +8575,7 @@
         <v>46162.64775322917</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>25</v>
@@ -8591,7 +8599,7 @@
         <v>26</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>26</v>
@@ -8604,7 +8612,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B117" s="9">
         <v>46162.55872223379</v>
@@ -8614,7 +8622,7 @@
         <v>46162.67400658564</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8641,13 +8649,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q117" s="9">
         <v>46218</v>
@@ -8667,7 +8675,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B118" s="5">
         <v>46162.55873068287</v>
@@ -8677,7 +8685,7 @@
         <v>46162.674262650464</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8704,10 +8712,10 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>26</v>
@@ -8720,7 +8728,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B119" s="9">
         <v>46162.558735011575</v>
@@ -8730,7 +8738,7 @@
         <v>46162.67425921296</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8757,10 +8765,10 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P119" s="10" t="s">
         <v>26</v>
@@ -8773,7 +8781,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B120" s="5">
         <v>46162.55873951389</v>
@@ -8783,7 +8791,7 @@
         <v>46162.67425633102</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8810,13 +8818,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8826,7 +8834,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B121" s="9">
         <v>46162.55874386574</v>
@@ -8836,7 +8844,7 @@
         <v>46162.674253379635</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8863,13 +8871,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8879,7 +8887,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B122" s="5">
         <v>46162.55874813657</v>
@@ -8889,7 +8897,7 @@
         <v>46162.67425</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8916,13 +8924,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8932,7 +8940,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B123" s="9">
         <v>46162.56516702546</v>
@@ -8942,7 +8950,7 @@
         <v>46162.67424702546</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8969,13 +8977,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8985,7 +8993,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B124" s="5">
         <v>46162.56517383102</v>
@@ -8995,7 +9003,7 @@
         <v>46162.67424429399</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -9022,13 +9030,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9038,7 +9046,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B125" s="9">
         <v>46162.565181134254</v>
@@ -9048,7 +9056,7 @@
         <v>46162.674233321755</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -9075,13 +9083,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -9091,7 +9099,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B126" s="5">
         <v>46162.565189201385</v>
@@ -9101,7 +9109,7 @@
         <v>46162.67423263889</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9128,13 +9136,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9144,7 +9152,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B127" s="9">
         <v>46162.56519680556</v>
@@ -9154,7 +9162,7 @@
         <v>46162.674231944446</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -9181,13 +9189,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9197,7 +9205,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B128" s="5">
         <v>46162.565205590276</v>
@@ -9207,7 +9215,7 @@
         <v>46162.674231261575</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9234,13 +9242,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9250,7 +9258,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B129" s="9">
         <v>46162.565212013884</v>
@@ -9260,7 +9268,7 @@
         <v>46162.67423060186</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -9287,13 +9295,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9303,7 +9311,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B130" s="5">
         <v>46162.558751550925</v>
@@ -9313,7 +9321,7 @@
         <v>46162.67400341435</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9340,13 +9348,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q130" s="5">
         <v>46219</v>
@@ -9366,7 +9374,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B131" s="9">
         <v>46162.558756238424</v>
@@ -9376,7 +9384,7 @@
         <v>46162.67439809028</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9401,13 +9409,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9417,7 +9425,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B132" s="5">
         <v>46162.55876204861</v>
@@ -9427,7 +9435,7 @@
         <v>46162.67439510417</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9452,13 +9460,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O132" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="P132" s="6" t="s">
         <v>337</v>
-      </c>
-      <c r="P132" s="6" t="s">
-        <v>335</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9468,7 +9476,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B133" s="9">
         <v>46162.55876745371</v>
@@ -9478,7 +9486,7 @@
         <v>46162.6743919213</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9503,13 +9511,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9519,7 +9527,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B134" s="5">
         <v>46162.558773888886</v>
@@ -9529,7 +9537,7 @@
         <v>46162.674388368054</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9554,13 +9562,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9570,7 +9578,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B135" s="9">
         <v>46162.558827430556</v>
@@ -9580,7 +9588,7 @@
         <v>46162.67438523148</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9605,13 +9613,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9621,7 +9629,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B136" s="5">
         <v>46162.565477233795</v>
@@ -9631,7 +9639,7 @@
         <v>46162.67438189815</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9656,13 +9664,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9672,7 +9680,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B137" s="9">
         <v>46162.56548539352</v>
@@ -9682,7 +9690,7 @@
         <v>46162.67437871528</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9707,13 +9715,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9723,7 +9731,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B138" s="5">
         <v>46162.56549420139</v>
@@ -9733,7 +9741,7 @@
         <v>46162.67437079861</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9758,13 +9766,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9774,7 +9782,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B139" s="9">
         <v>46162.56549981482</v>
@@ -9784,7 +9792,7 @@
         <v>46162.674370127315</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -9809,13 +9817,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9825,7 +9833,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B140" s="5">
         <v>46162.565507719904</v>
@@ -9835,7 +9843,7 @@
         <v>46162.6743691088</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9860,13 +9868,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9876,7 +9884,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B141" s="9">
         <v>46162.56551637732</v>
@@ -9886,7 +9894,7 @@
         <v>46162.6743640162</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -9911,13 +9919,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9927,7 +9935,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B142" s="5">
         <v>46162.56598206019</v>
@@ -9937,7 +9945,7 @@
         <v>46162.67436230324</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9962,13 +9970,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9978,7 +9986,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B143" s="9">
         <v>46162.55883354167</v>
@@ -9988,7 +9996,7 @@
         <v>46162.674000150466</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -10015,13 +10023,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q143" s="9">
         <v>46220</v>
@@ -10041,7 +10049,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B144" s="5">
         <v>46162.55883898148</v>
@@ -10051,7 +10059,7 @@
         <v>46162.67453761574</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -10078,13 +10086,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O144" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="P144" s="6" t="s">
         <v>358</v>
-      </c>
-      <c r="P144" s="6" t="s">
-        <v>356</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10094,7 +10102,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B145" s="9">
         <v>46162.55884618056</v>
@@ -10104,7 +10112,7 @@
         <v>46162.674534606485</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -10131,13 +10139,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -10147,7 +10155,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B146" s="5">
         <v>46162.55885335648</v>
@@ -10157,7 +10165,7 @@
         <v>46162.67453157407</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10184,13 +10192,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10200,7 +10208,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B147" s="9">
         <v>46162.558860624995</v>
@@ -10210,7 +10218,7 @@
         <v>46162.674528171294</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -10237,13 +10245,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O147" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="P147" s="10" t="s">
         <v>364</v>
-      </c>
-      <c r="P147" s="10" t="s">
-        <v>362</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10253,7 +10261,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B148" s="5">
         <v>46162.558867395834</v>
@@ -10263,7 +10271,7 @@
         <v>46162.674524965274</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10290,13 +10298,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10306,7 +10314,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B149" s="9">
         <v>46162.566146365745</v>
@@ -10316,7 +10324,7 @@
         <v>46162.674521354165</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -10343,13 +10351,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10359,7 +10367,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B150" s="5">
         <v>46162.566153101856</v>
@@ -10369,7 +10377,7 @@
         <v>46162.67451787037</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10396,13 +10404,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10412,7 +10420,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B151" s="9">
         <v>46162.56617111111</v>
@@ -10422,7 +10430,7 @@
         <v>46162.67451502314</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
@@ -10449,13 +10457,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10465,7 +10473,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B152" s="5">
         <v>46162.56618105324</v>
@@ -10475,7 +10483,7 @@
         <v>46162.67451243056</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10502,13 +10510,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10518,7 +10526,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B153" s="9">
         <v>46162.56618987268</v>
@@ -10528,7 +10536,7 @@
         <v>46162.67450335648</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10555,13 +10563,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q153" s="10"/>
       <c r="R153" s="10"/>
@@ -10571,7 +10579,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B154" s="5">
         <v>46162.56620271991</v>
@@ -10581,7 +10589,7 @@
         <v>46162.67450263889</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10608,13 +10616,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10624,7 +10632,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B155" s="9">
         <v>46162.56620673611</v>
@@ -10634,7 +10642,7 @@
         <v>46162.67450188658</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -10661,13 +10669,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q155" s="10"/>
       <c r="R155" s="10"/>
@@ -10677,7 +10685,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B156" s="5">
         <v>46162.558871574074</v>
@@ -10687,7 +10695,7 @@
         <v>46162.673997199076</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10714,13 +10722,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q156" s="5">
         <v>46223</v>
@@ -10740,7 +10748,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B157" s="9">
         <v>46162.55887622685</v>
@@ -10750,7 +10758,7 @@
         <v>46162.674694375004</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
@@ -10777,13 +10785,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q157" s="10"/>
       <c r="R157" s="10"/>
@@ -10793,7 +10801,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B158" s="5">
         <v>46162.55888300926</v>
@@ -10803,7 +10811,7 @@
         <v>46162.67469101852</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10830,13 +10838,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10846,7 +10854,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B159" s="9">
         <v>46162.558892581015</v>
@@ -10856,7 +10864,7 @@
         <v>46162.674687928244</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
@@ -10883,13 +10891,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="P159" s="10" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q159" s="10"/>
       <c r="R159" s="10"/>
@@ -10899,7 +10907,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B160" s="5">
         <v>46162.55889858796</v>
@@ -10909,7 +10917,7 @@
         <v>46162.67468512732</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -10936,13 +10944,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -10952,7 +10960,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B161" s="9">
         <v>46162.558904618054</v>
@@ -10962,7 +10970,7 @@
         <v>46162.674682349534</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
@@ -10989,13 +10997,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P161" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Q161" s="10"/>
       <c r="R161" s="10"/>
@@ -11005,7 +11013,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B162" s="5">
         <v>46162.566379375</v>
@@ -11015,7 +11023,7 @@
         <v>46162.674678888885</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -11042,13 +11050,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11058,7 +11066,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B163" s="9">
         <v>46162.56638695602</v>
@@ -11068,7 +11076,7 @@
         <v>46162.67467586805</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
@@ -11095,13 +11103,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -11111,7 +11119,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B164" s="5">
         <v>46162.56639532407</v>
@@ -11121,7 +11129,7 @@
         <v>46162.67467314815</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11148,13 +11156,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11164,7 +11172,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B165" s="9">
         <v>46162.56640418981</v>
@@ -11174,7 +11182,7 @@
         <v>46162.67467030093</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
@@ -11201,13 +11209,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -11217,7 +11225,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B166" s="5">
         <v>46162.56641240741</v>
@@ -11227,7 +11235,7 @@
         <v>46162.67466239583</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11254,13 +11262,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Q166" s="6"/>
       <c r="R166" s="6"/>
@@ -11270,7 +11278,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B167" s="9">
         <v>46162.56642033564</v>
@@ -11280,7 +11288,7 @@
         <v>46162.674661655095</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
@@ -11307,13 +11315,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Q167" s="10"/>
       <c r="R167" s="10"/>
@@ -11323,7 +11331,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B168" s="5">
         <v>46162.566427708334</v>
@@ -11333,7 +11341,7 @@
         <v>46162.67466097222</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11360,13 +11368,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
@@ -11376,7 +11384,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B169" s="9">
         <v>46162.558908946754</v>
@@ -11386,7 +11394,7 @@
         <v>46162.67399393518</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
@@ -11413,13 +11421,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P169" s="10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q169" s="9">
         <v>46224</v>
@@ -11439,7 +11447,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B170" s="5">
         <v>46162.55891369213</v>
@@ -11449,7 +11457,7 @@
         <v>46162.67483585648</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11474,13 +11482,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
@@ -11490,7 +11498,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B171" s="9">
         <v>46162.55891930556</v>
@@ -11500,7 +11508,7 @@
         <v>46162.674832847224</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11525,13 +11533,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Q171" s="10"/>
       <c r="R171" s="10"/>
@@ -11541,7 +11549,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B172" s="5">
         <v>46162.558924930556</v>
@@ -11551,7 +11559,7 @@
         <v>46162.67482962963</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11576,13 +11584,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11592,7 +11600,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B173" s="9">
         <v>46162.55893104167</v>
@@ -11602,7 +11610,7 @@
         <v>46162.67482693287</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
@@ -11627,13 +11635,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="10" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11643,7 +11651,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B174" s="5">
         <v>46162.55893646991</v>
@@ -11653,7 +11661,7 @@
         <v>46162.67482414352</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
@@ -11678,13 +11686,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -11694,7 +11702,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B175" s="9">
         <v>46162.567320891205</v>
@@ -11704,7 +11712,7 @@
         <v>46162.67482128472</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
@@ -11729,10 +11737,10 @@
         <v>26</v>
       </c>
       <c r="N175" s="10" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P175" s="10" t="s">
         <v>26</v>
@@ -11745,7 +11753,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B176" s="5">
         <v>46162.567330034726</v>
@@ -11755,7 +11763,7 @@
         <v>46162.67481818287</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
@@ -11780,13 +11788,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
@@ -11796,7 +11804,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B177" s="9">
         <v>46162.567337685185</v>
@@ -11806,7 +11814,7 @@
         <v>46162.674815543985</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
@@ -11831,10 +11839,10 @@
         <v>26</v>
       </c>
       <c r="N177" s="10" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="O177" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P177" s="10" t="s">
         <v>26</v>
@@ -11847,7 +11855,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B178" s="5">
         <v>46162.567344166666</v>
@@ -11857,7 +11865,7 @@
         <v>46162.674812743055</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
@@ -11882,10 +11890,10 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P178" s="6" t="s">
         <v>26</v>
@@ -11898,7 +11906,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B179" s="9">
         <v>46162.56735135417</v>
@@ -11908,7 +11916,7 @@
         <v>46162.67480497685</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
@@ -11933,10 +11941,10 @@
         <v>26</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="O179" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P179" s="10" t="s">
         <v>26</v>
@@ -11949,7 +11957,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B180" s="5">
         <v>46162.5673590625</v>
@@ -11959,7 +11967,7 @@
         <v>46162.674804317125</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
@@ -11984,10 +11992,10 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P180" s="6" t="s">
         <v>26</v>
@@ -12000,7 +12008,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B181" s="9">
         <v>46162.567366284726</v>
@@ -12010,7 +12018,7 @@
         <v>46162.674803587965</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>26</v>
@@ -12035,13 +12043,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="10" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="O181" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P181" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q181" s="10"/>
       <c r="R181" s="10"/>
@@ -12051,7 +12059,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B182" s="5">
         <v>46162.558941678246</v>
@@ -12061,7 +12069,7 @@
         <v>46162.673987789356</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
@@ -12088,13 +12096,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="Q182" s="5">
         <v>46226</v>
@@ -12114,7 +12122,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B183" s="9">
         <v>46162.5589471875</v>
@@ -12124,7 +12132,7 @@
         <v>46162.675084849536</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>26</v>
@@ -12149,13 +12157,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="10" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="O183" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P183" s="10" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="Q183" s="10"/>
       <c r="R183" s="10"/>
@@ -12165,7 +12173,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B184" s="5">
         <v>46162.55895184028</v>
@@ -12175,7 +12183,7 @@
         <v>46162.67508193287</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
@@ -12200,13 +12208,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12216,7 +12224,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B185" s="9">
         <v>46162.55895655093</v>
@@ -12226,7 +12234,7 @@
         <v>46162.67507869213</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
@@ -12251,13 +12259,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="10" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -12267,7 +12275,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B186" s="5">
         <v>46162.5589959375</v>
@@ -12277,7 +12285,7 @@
         <v>46162.67507611111</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
@@ -12302,13 +12310,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12318,7 +12326,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B187" s="9">
         <v>46162.55900136574</v>
@@ -12328,7 +12336,7 @@
         <v>46162.6750730787</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
@@ -12353,13 +12361,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="10" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P187" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="Q187" s="10"/>
       <c r="R187" s="10"/>
@@ -12369,7 +12377,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B188" s="5">
         <v>46162.56759152778</v>
@@ -12379,7 +12387,7 @@
         <v>46162.675070150464</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12404,10 +12412,10 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P188" s="6" t="s">
         <v>26</v>
@@ -12420,7 +12428,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B189" s="9">
         <v>46162.56759846065</v>
@@ -12430,7 +12438,7 @@
         <v>46162.6750674537</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
@@ -12455,13 +12463,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="10" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12471,7 +12479,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B190" s="5">
         <v>46162.56760671297</v>
@@ -12481,7 +12489,7 @@
         <v>46162.67506488426</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12506,13 +12514,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12522,7 +12530,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B191" s="9">
         <v>46162.56761416666</v>
@@ -12532,7 +12540,7 @@
         <v>46162.67506164352</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
@@ -12557,13 +12565,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="10" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12573,7 +12581,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B192" s="5">
         <v>46162.56762221065</v>
@@ -12583,7 +12591,7 @@
         <v>46162.67505446759</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -12608,13 +12616,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12624,7 +12632,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B193" s="9">
         <v>46162.56762855324</v>
@@ -12634,7 +12642,7 @@
         <v>46162.675053750005</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>26</v>
@@ -12659,13 +12667,13 @@
         <v>26</v>
       </c>
       <c r="N193" s="10" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="O193" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P193" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q193" s="10"/>
       <c r="R193" s="10"/>
@@ -12675,7 +12683,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B194" s="5">
         <v>46162.56763415509</v>
@@ -12685,7 +12693,7 @@
         <v>46162.67505302084</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
@@ -12710,13 +12718,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -12726,7 +12734,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B195" s="9">
         <v>46162.55900565972</v>
@@ -12736,7 +12744,7 @@
         <v>46162.663939108796</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>25</v>
@@ -12760,7 +12768,7 @@
         <v>26</v>
       </c>
       <c r="O195" s="10" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="P195" s="10" t="s">
         <v>26</v>
@@ -12773,7 +12781,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B196" s="5">
         <v>46162.55900940972</v>
@@ -12783,16 +12791,16 @@
         <v>46162.67540229167</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G196" s="6" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H196" s="6" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="I196" s="5">
         <v>46227</v>
@@ -12810,13 +12818,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="Q196" s="5">
         <v>46227</v>
@@ -12836,7 +12844,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B197" s="9">
         <v>46162.559015023144</v>
@@ -12846,16 +12854,16 @@
         <v>46162.67538505787</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G197" s="10" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H197" s="10" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="I197" s="10"/>
       <c r="J197" s="9">
@@ -12871,13 +12879,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="10" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O197" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P197" s="10" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="Q197" s="10"/>
       <c r="R197" s="10"/>
@@ -12887,7 +12895,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B198" s="5">
         <v>46162.55901939815</v>
@@ -12897,16 +12905,16 @@
         <v>46162.675382534726</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="I198" s="6"/>
       <c r="J198" s="5">
@@ -12922,13 +12930,13 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="Q198" s="6"/>
       <c r="R198" s="6"/>
@@ -12938,7 +12946,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B199" s="9">
         <v>46162.55902388888</v>
@@ -12948,16 +12956,16 @@
         <v>46162.67537990741</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G199" s="10" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H199" s="10" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="I199" s="10"/>
       <c r="J199" s="9">
@@ -12973,13 +12981,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="10" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O199" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P199" s="10" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="Q199" s="10"/>
       <c r="R199" s="10"/>
@@ -12989,7 +12997,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B200" s="5">
         <v>46162.559028090276</v>
@@ -12999,16 +13007,16 @@
         <v>46162.67537715277</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H200" s="6" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="I200" s="6"/>
       <c r="J200" s="5">
@@ -13024,13 +13032,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -13040,7 +13048,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B201" s="9">
         <v>46162.559032060184</v>
@@ -13050,16 +13058,16 @@
         <v>46162.675374178245</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G201" s="10" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H201" s="10" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="I201" s="10"/>
       <c r="J201" s="9">
@@ -13075,13 +13083,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="10" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O201" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P201" s="10" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="Q201" s="10"/>
       <c r="R201" s="10"/>
@@ -13091,7 +13099,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B202" s="5">
         <v>46162.56847083333</v>
@@ -13101,16 +13109,16 @@
         <v>46162.675371296296</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H202" s="6" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="I202" s="6"/>
       <c r="J202" s="5">
@@ -13126,13 +13134,13 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Q202" s="6"/>
       <c r="R202" s="6"/>
@@ -13142,7 +13150,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B203" s="9">
         <v>46162.5684778588</v>
@@ -13152,16 +13160,16 @@
         <v>46162.675368321754</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="10" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H203" s="10" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="I203" s="10"/>
       <c r="J203" s="9">
@@ -13177,10 +13185,10 @@
         <v>26</v>
       </c>
       <c r="N203" s="10" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P203" s="10" t="s">
         <v>26</v>
@@ -13193,7 +13201,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B204" s="5">
         <v>46162.56848583333</v>
@@ -13203,16 +13211,16 @@
         <v>46162.67536565972</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H204" s="6" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="I204" s="6"/>
       <c r="J204" s="5">
@@ -13228,13 +13236,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13244,7 +13252,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B205" s="9">
         <v>46162.56849315972</v>
@@ -13254,16 +13262,16 @@
         <v>46162.67536296297</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G205" s="10" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H205" s="10" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="I205" s="10"/>
       <c r="J205" s="9">
@@ -13279,13 +13287,13 @@
         <v>26</v>
       </c>
       <c r="N205" s="10" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q205" s="10"/>
       <c r="R205" s="10"/>
@@ -13295,7 +13303,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B206" s="5">
         <v>46162.568499120374</v>
@@ -13305,16 +13313,16 @@
         <v>46162.67535506944</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H206" s="6" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="I206" s="6"/>
       <c r="J206" s="5">
@@ -13330,13 +13338,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13346,7 +13354,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B207" s="9">
         <v>46162.568507013886</v>
@@ -13356,16 +13364,16 @@
         <v>46162.67535439815</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="10" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H207" s="10" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="I207" s="10"/>
       <c r="J207" s="9">
@@ -13381,13 +13389,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="10" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q207" s="10"/>
       <c r="R207" s="10"/>
@@ -13397,7 +13405,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B208" s="5">
         <v>46162.56851576389</v>
@@ -13407,16 +13415,16 @@
         <v>46162.67535373842</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H208" s="6" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="I208" s="6"/>
       <c r="J208" s="5">
@@ -13432,13 +13440,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q208" s="6"/>
       <c r="R208" s="6"/>
@@ -13448,7 +13456,7 @@
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B209" s="9">
         <v>46162.559035983795</v>
@@ -13458,7 +13466,7 @@
         <v>46162.675601435185</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
@@ -13485,13 +13493,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="10" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P209" s="10" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="Q209" s="9">
         <v>46230</v>
@@ -13511,7 +13519,7 @@
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B210" s="5">
         <v>46162.559040057866</v>
@@ -13521,7 +13529,7 @@
         <v>46162.67559398148</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
@@ -13546,13 +13554,13 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O210" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P210" s="6" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="Q210" s="6"/>
       <c r="R210" s="6"/>
@@ -13562,7 +13570,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B211" s="9">
         <v>46162.559044305555</v>
@@ -13572,7 +13580,7 @@
         <v>46162.67559118055</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>26</v>
@@ -13597,13 +13605,13 @@
         <v>26</v>
       </c>
       <c r="N211" s="10" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O211" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P211" s="10" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="Q211" s="10"/>
       <c r="R211" s="10"/>
@@ -13613,7 +13621,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B212" s="5">
         <v>46162.55904842593</v>
@@ -13623,7 +13631,7 @@
         <v>46162.675588391205</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
@@ -13648,13 +13656,13 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P212" s="6" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="Q212" s="6"/>
       <c r="R212" s="6"/>
@@ -13664,7 +13672,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B213" s="9">
         <v>46162.55905241898</v>
@@ -13674,7 +13682,7 @@
         <v>46162.67558560186</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>26</v>
@@ -13699,13 +13707,13 @@
         <v>26</v>
       </c>
       <c r="N213" s="10" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O213" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P213" s="10" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="Q213" s="10"/>
       <c r="R213" s="10"/>
@@ -13715,7 +13723,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B214" s="5">
         <v>46162.55905643519</v>
@@ -13725,7 +13733,7 @@
         <v>46162.67558284722</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
@@ -13750,13 +13758,13 @@
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P214" s="6" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="Q214" s="6"/>
       <c r="R214" s="6"/>
@@ -13766,7 +13774,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B215" s="9">
         <v>46162.568794328705</v>
@@ -13776,7 +13784,7 @@
         <v>46162.6755797338</v>
       </c>
       <c r="E215" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F215" s="10" t="s">
         <v>26</v>
@@ -13801,10 +13809,10 @@
         <v>26</v>
       </c>
       <c r="N215" s="10" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O215" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P215" s="10" t="s">
         <v>26</v>
@@ -13817,7 +13825,7 @@
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B216" s="5">
         <v>46162.56880138889</v>
@@ -13827,7 +13835,7 @@
         <v>46162.675576967595</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
@@ -13852,13 +13860,13 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P216" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q216" s="6"/>
       <c r="R216" s="6"/>
@@ -13868,7 +13876,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B217" s="9">
         <v>46162.56880807871</v>
@@ -13878,7 +13886,7 @@
         <v>46162.67557431713</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>26</v>
@@ -13903,13 +13911,13 @@
         <v>26</v>
       </c>
       <c r="N217" s="10" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O217" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P217" s="10" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="Q217" s="10"/>
       <c r="R217" s="10"/>
@@ -13919,7 +13927,7 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B218" s="5">
         <v>46162.56881548611</v>
@@ -13929,7 +13937,7 @@
         <v>46162.67557162037</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
@@ -13954,13 +13962,13 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P218" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q218" s="6"/>
       <c r="R218" s="6"/>
@@ -13970,7 +13978,7 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B219" s="9">
         <v>46162.56882248842</v>
@@ -13980,7 +13988,7 @@
         <v>46162.67556375</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>26</v>
@@ -14005,13 +14013,13 @@
         <v>26</v>
       </c>
       <c r="N219" s="10" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O219" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P219" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q219" s="10"/>
       <c r="R219" s="10"/>
@@ -14021,7 +14029,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B220" s="5">
         <v>46162.56882971065</v>
@@ -14031,7 +14039,7 @@
         <v>46162.675563020835</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
@@ -14056,13 +14064,13 @@
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P220" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q220" s="6"/>
       <c r="R220" s="6"/>
@@ -14072,7 +14080,7 @@
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B221" s="9">
         <v>46162.56883761574</v>
@@ -14082,7 +14090,7 @@
         <v>46162.67556230324</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
@@ -14107,13 +14115,13 @@
         <v>26</v>
       </c>
       <c r="N221" s="10" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P221" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q221" s="10"/>
       <c r="R221" s="10"/>
@@ -14123,7 +14131,7 @@
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B222" s="5">
         <v>46162.559060671294</v>
@@ -14133,16 +14141,16 @@
         <v>46162.67579302083</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H222" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I222" s="5">
         <v>46231</v>
@@ -14160,13 +14168,13 @@
         <v>26</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O222" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P222" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="Q222" s="5">
         <v>46231</v>
@@ -14186,7 +14194,7 @@
     </row>
     <row r="223" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" s="8" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B223" s="9">
         <v>46162.55906472223</v>
@@ -14196,16 +14204,16 @@
         <v>46162.67579450231</v>
       </c>
       <c r="E223" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G223" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H223" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I223" s="10"/>
       <c r="J223" s="9">
@@ -14221,13 +14229,13 @@
         <v>26</v>
       </c>
       <c r="N223" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O223" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P223" s="10" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="Q223" s="10"/>
       <c r="R223" s="10"/>
@@ -14237,7 +14245,7 @@
     </row>
     <row r="224" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B224" s="5">
         <v>46162.55907236111</v>
@@ -14247,16 +14255,16 @@
         <v>46162.6757915162</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H224" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I224" s="6"/>
       <c r="J224" s="5">
@@ -14272,13 +14280,13 @@
         <v>26</v>
       </c>
       <c r="N224" s="6" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O224" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P224" s="6" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="Q224" s="6"/>
       <c r="R224" s="6"/>
@@ -14288,7 +14296,7 @@
     </row>
     <row r="225" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" s="8" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B225" s="9">
         <v>46162.55907862268</v>
@@ -14298,16 +14306,16 @@
         <v>46162.67578863426</v>
       </c>
       <c r="E225" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F225" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G225" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H225" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I225" s="10"/>
       <c r="J225" s="9">
@@ -14323,13 +14331,13 @@
         <v>26</v>
       </c>
       <c r="N225" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O225" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P225" s="10" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="Q225" s="10"/>
       <c r="R225" s="10"/>
@@ -14339,7 +14347,7 @@
     </row>
     <row r="226" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B226" s="5">
         <v>46162.55908304398</v>
@@ -14349,16 +14357,16 @@
         <v>46162.67578590278</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F226" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H226" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I226" s="6"/>
       <c r="J226" s="5">
@@ -14374,13 +14382,13 @@
         <v>26</v>
       </c>
       <c r="N226" s="6" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O226" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P226" s="6" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="Q226" s="6"/>
       <c r="R226" s="6"/>
@@ -14390,7 +14398,7 @@
     </row>
     <row r="227" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" s="8" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B227" s="9">
         <v>46162.55908719907</v>
@@ -14400,16 +14408,16 @@
         <v>46162.67578289352</v>
       </c>
       <c r="E227" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F227" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G227" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H227" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I227" s="10"/>
       <c r="J227" s="9">
@@ -14425,13 +14433,13 @@
         <v>26</v>
       </c>
       <c r="N227" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O227" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P227" s="10" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="Q227" s="10"/>
       <c r="R227" s="10"/>
@@ -14441,7 +14449,7 @@
     </row>
     <row r="228" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B228" s="5">
         <v>46162.56901232639</v>
@@ -14451,16 +14459,16 @@
         <v>46162.67577962963</v>
       </c>
       <c r="E228" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F228" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G228" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H228" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I228" s="6"/>
       <c r="J228" s="5">
@@ -14476,13 +14484,13 @@
         <v>26</v>
       </c>
       <c r="N228" s="6" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O228" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P228" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q228" s="6"/>
       <c r="R228" s="6"/>
@@ -14492,7 +14500,7 @@
     </row>
     <row r="229" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" s="8" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B229" s="9">
         <v>46162.569018888884</v>
@@ -14502,16 +14510,16 @@
         <v>46162.67577695602</v>
       </c>
       <c r="E229" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F229" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G229" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H229" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I229" s="10"/>
       <c r="J229" s="9">
@@ -14527,13 +14535,13 @@
         <v>26</v>
       </c>
       <c r="N229" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O229" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P229" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q229" s="10"/>
       <c r="R229" s="10"/>
@@ -14543,7 +14551,7 @@
     </row>
     <row r="230" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B230" s="5">
         <v>46162.56902688657</v>
@@ -14553,16 +14561,16 @@
         <v>46162.67577410879</v>
       </c>
       <c r="E230" s="6" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F230" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G230" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H230" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I230" s="6"/>
       <c r="J230" s="5">
@@ -14578,13 +14586,13 @@
         <v>26</v>
       </c>
       <c r="N230" s="6" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O230" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P230" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q230" s="6"/>
       <c r="R230" s="6"/>
@@ -14594,7 +14602,7 @@
     </row>
     <row r="231" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A231" s="8" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B231" s="9">
         <v>46162.56903291667</v>
@@ -14604,16 +14612,16 @@
         <v>46162.67577162037</v>
       </c>
       <c r="E231" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F231" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G231" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H231" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I231" s="10"/>
       <c r="J231" s="9">
@@ -14629,13 +14637,13 @@
         <v>26</v>
       </c>
       <c r="N231" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O231" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P231" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q231" s="10"/>
       <c r="R231" s="10"/>
@@ -14645,7 +14653,7 @@
     </row>
     <row r="232" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B232" s="5">
         <v>46162.56903989583</v>
@@ -14655,16 +14663,16 @@
         <v>46162.67576392361</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F232" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G232" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H232" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I232" s="6"/>
       <c r="J232" s="5">
@@ -14680,13 +14688,13 @@
         <v>26</v>
       </c>
       <c r="N232" s="6" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O232" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P232" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q232" s="6"/>
       <c r="R232" s="6"/>
@@ -14696,7 +14704,7 @@
     </row>
     <row r="233" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B233" s="9">
         <v>46162.56904635417</v>
@@ -14706,16 +14714,16 @@
         <v>46162.67576322917</v>
       </c>
       <c r="E233" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F233" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G233" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H233" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I233" s="10"/>
       <c r="J233" s="9">
@@ -14731,13 +14739,13 @@
         <v>26</v>
       </c>
       <c r="N233" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O233" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P233" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q233" s="10"/>
       <c r="R233" s="10"/>
@@ -14747,7 +14755,7 @@
     </row>
     <row r="234" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B234" s="5">
         <v>46162.56905347222</v>
@@ -14757,16 +14765,16 @@
         <v>46162.67576252315</v>
       </c>
       <c r="E234" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F234" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G234" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H234" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I234" s="6"/>
       <c r="J234" s="5">
@@ -14782,13 +14790,13 @@
         <v>26</v>
       </c>
       <c r="N234" s="6" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O234" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P234" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q234" s="6"/>
       <c r="R234" s="6"/>
@@ -14798,7 +14806,7 @@
     </row>
     <row r="235" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A235" s="8" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B235" s="9">
         <v>46162.559091284726</v>
@@ -14808,16 +14816,16 @@
         <v>46162.6758584375</v>
       </c>
       <c r="E235" s="10" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F235" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G235" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H235" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I235" s="9">
         <v>46232</v>
@@ -14835,13 +14843,13 @@
         <v>26</v>
       </c>
       <c r="N235" s="10" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O235" s="10" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P235" s="10" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="Q235" s="9">
         <v>46232</v>
@@ -14861,7 +14869,7 @@
     </row>
     <row r="236" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B236" s="5">
         <v>46162.55909613426</v>
@@ -14871,16 +14879,16 @@
         <v>46162.676026875</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F236" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G236" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H236" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I236" s="5">
         <v>46232</v>
@@ -14898,13 +14906,13 @@
         <v>26</v>
       </c>
       <c r="N236" s="6" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="O236" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P236" s="6" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="Q236" s="6"/>
       <c r="R236" s="6"/>
@@ -14914,7 +14922,7 @@
     </row>
     <row r="237" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A237" s="8" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B237" s="9">
         <v>46162.55910012731</v>
@@ -14924,16 +14932,16 @@
         <v>46162.67602255787</v>
       </c>
       <c r="E237" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F237" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G237" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H237" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I237" s="9">
         <v>46232</v>
@@ -14951,13 +14959,13 @@
         <v>26</v>
       </c>
       <c r="N237" s="10" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="O237" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P237" s="10" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="Q237" s="10"/>
       <c r="R237" s="10"/>
@@ -14967,7 +14975,7 @@
     </row>
     <row r="238" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B238" s="5">
         <v>46162.55910407407</v>
@@ -14977,16 +14985,16 @@
         <v>46162.676019108796</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F238" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G238" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H238" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I238" s="5">
         <v>46232</v>
@@ -15004,13 +15012,13 @@
         <v>26</v>
       </c>
       <c r="N238" s="6" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="O238" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P238" s="6" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="Q238" s="6"/>
       <c r="R238" s="6"/>
@@ -15020,7 +15028,7 @@
     </row>
     <row r="239" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A239" s="8" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B239" s="9">
         <v>46162.559108125</v>
@@ -15030,16 +15038,16 @@
         <v>46162.67601616898</v>
       </c>
       <c r="E239" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F239" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G239" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H239" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I239" s="9">
         <v>46232</v>
@@ -15057,13 +15065,13 @@
         <v>26</v>
       </c>
       <c r="N239" s="10" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="O239" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P239" s="10" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="Q239" s="10"/>
       <c r="R239" s="10"/>
@@ -15073,7 +15081,7 @@
     </row>
     <row r="240" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B240" s="5">
         <v>46162.55914409722</v>
@@ -15083,16 +15091,16 @@
         <v>46162.676013275464</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F240" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G240" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H240" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I240" s="5">
         <v>46232</v>
@@ -15110,13 +15118,13 @@
         <v>26</v>
       </c>
       <c r="N240" s="6" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="O240" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P240" s="6" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="Q240" s="6"/>
       <c r="R240" s="6"/>
@@ -15126,7 +15134,7 @@
     </row>
     <row r="241" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A241" s="8" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B241" s="9">
         <v>46162.56958915509</v>
@@ -15136,16 +15144,16 @@
         <v>46162.67600972222</v>
       </c>
       <c r="E241" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F241" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G241" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H241" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I241" s="9">
         <v>46232</v>
@@ -15163,10 +15171,10 @@
         <v>26</v>
       </c>
       <c r="N241" s="10" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="O241" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P241" s="10" t="s">
         <v>26</v>
@@ -15179,7 +15187,7 @@
     </row>
     <row r="242" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B242" s="5">
         <v>46162.56959587963</v>
@@ -15189,16 +15197,16 @@
         <v>46162.676007002316</v>
       </c>
       <c r="E242" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F242" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G242" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H242" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I242" s="5">
         <v>46232</v>
@@ -15216,10 +15224,10 @@
         <v>26</v>
       </c>
       <c r="N242" s="6" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="O242" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P242" s="6" t="s">
         <v>26</v>
@@ -15232,7 +15240,7 @@
     </row>
     <row r="243" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A243" s="8" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B243" s="9">
         <v>46162.56960513889</v>
@@ -15242,16 +15250,16 @@
         <v>46162.67600369213</v>
       </c>
       <c r="E243" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F243" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G243" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H243" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I243" s="9">
         <v>46232</v>
@@ -15269,10 +15277,10 @@
         <v>26</v>
       </c>
       <c r="N243" s="10" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="O243" s="10" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="P243" s="10" t="s">
         <v>26</v>
@@ -15285,7 +15293,7 @@
     </row>
     <row r="244" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B244" s="5">
         <v>46162.569612060186</v>
@@ -15295,16 +15303,16 @@
         <v>46162.67599591435</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F244" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G244" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H244" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I244" s="5">
         <v>46232</v>
@@ -15322,10 +15330,10 @@
         <v>26</v>
       </c>
       <c r="N244" s="6" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="O244" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P244" s="6" t="s">
         <v>26</v>
@@ -15338,7 +15346,7 @@
     </row>
     <row r="245" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A245" s="8" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B245" s="9">
         <v>46162.569619999995</v>
@@ -15348,16 +15356,16 @@
         <v>46162.67599258102</v>
       </c>
       <c r="E245" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F245" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G245" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H245" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I245" s="9">
         <v>46232</v>
@@ -15375,10 +15383,10 @@
         <v>26</v>
       </c>
       <c r="N245" s="10" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="O245" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P245" s="10" t="s">
         <v>26</v>
@@ -15391,7 +15399,7 @@
     </row>
     <row r="246" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B246" s="5">
         <v>46162.569627812496</v>
@@ -15401,16 +15409,16 @@
         <v>46162.675991412034</v>
       </c>
       <c r="E246" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F246" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G246" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H246" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I246" s="5">
         <v>46232</v>
@@ -15428,10 +15436,10 @@
         <v>26</v>
       </c>
       <c r="N246" s="6" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="O246" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P246" s="6" t="s">
         <v>26</v>
@@ -15444,7 +15452,7 @@
     </row>
     <row r="247" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A247" s="8" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B247" s="9">
         <v>46162.569634513886</v>
@@ -15454,16 +15462,16 @@
         <v>46162.675990613425</v>
       </c>
       <c r="E247" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F247" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G247" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H247" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I247" s="9">
         <v>46232</v>
@@ -15481,10 +15489,10 @@
         <v>26</v>
       </c>
       <c r="N247" s="10" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="O247" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P247" s="10" t="s">
         <v>26</v>
@@ -15497,7 +15505,7 @@
     </row>
     <row r="248" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B248" s="5">
         <v>46162.5591494213</v>
@@ -15507,7 +15515,7 @@
         <v>46162.664148020835</v>
       </c>
       <c r="E248" s="6" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="F248" s="6" t="s">
         <v>25</v>
@@ -15531,7 +15539,7 @@
         <v>26</v>
       </c>
       <c r="O248" s="6" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="P248" s="6" t="s">
         <v>26</v>
@@ -15544,7 +15552,7 @@
     </row>
     <row r="249" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A249" s="8" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B249" s="9">
         <v>46162.559152800924</v>
@@ -15554,16 +15562,16 @@
         <v>46162.676061377315</v>
       </c>
       <c r="E249" s="10" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F249" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G249" s="10" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="H249" s="10" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="I249" s="9">
         <v>46233</v>
@@ -15581,13 +15589,13 @@
         <v>26</v>
       </c>
       <c r="N249" s="10" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="O249" s="10" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="P249" s="10" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="Q249" s="9">
         <v>46233</v>
@@ -15607,7 +15615,7 @@
     </row>
     <row r="250" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B250" s="5">
         <v>46162.55915726852</v>
@@ -15617,7 +15625,7 @@
         <v>46162.67613450231</v>
       </c>
       <c r="E250" s="6" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F250" s="6" t="s">
         <v>26</v>
@@ -15644,13 +15652,13 @@
         <v>26</v>
       </c>
       <c r="N250" s="6" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="O250" s="6" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="P250" s="6" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="Q250" s="5">
         <v>46233</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -3012,7 +3012,7 @@
         <v>46197.58811052083</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.654558912036</v>
+        <v>46197.77760189815</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>73</v>
@@ -3062,8 +3062,8 @@
       <c r="T17" s="10">
         <v>1</v>
       </c>
-      <c r="U17" s="12" t="s">
-        <v>47</v>
+      <c r="U17" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -4389,7 +4389,7 @@
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.86271082176</v>
+        <v>46198.16910141204</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>91</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -2837,7 +2837,7 @@
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46197.58811732639</v>
+        <v>46198.68393108796</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2882,9 +2882,11 @@
       <c r="B15" s="9">
         <v>46162.55827298611</v>
       </c>
-      <c r="C15" s="10"/>
+      <c r="C15" s="9">
+        <v>46198.683924930556</v>
+      </c>
       <c r="D15" s="9">
-        <v>46197.65244157407</v>
+        <v>46198.683943310185</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>67</v>
@@ -2932,10 +2934,10 @@
         <v>54</v>
       </c>
       <c r="T15" s="10">
-        <v>0</v>
-      </c>
-      <c r="U15" s="12" t="s">
-        <v>47</v>
+        <v>1</v>
+      </c>
+      <c r="U15" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -3327,7 +3329,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46162.59982563657</v>
+        <v>46198.68470386574</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>93</v>
@@ -3553,9 +3555,11 @@
       <c r="B26" s="5">
         <v>46162.558319710646</v>
       </c>
-      <c r="C26" s="6"/>
+      <c r="C26" s="5">
+        <v>46198.68469451389</v>
+      </c>
       <c r="D26" s="5">
-        <v>46169.86254357639</v>
+        <v>46198.684707002314</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>107</v>
@@ -3603,10 +3607,10 @@
         <v>54</v>
       </c>
       <c r="T26" s="6">
-        <v>0</v>
-      </c>
-      <c r="U26" s="11" t="s">
-        <v>82</v>
+        <v>1</v>
+      </c>
+      <c r="U26" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -3616,9 +3620,11 @@
       <c r="B27" s="9">
         <v>46162.55832415509</v>
       </c>
-      <c r="C27" s="10"/>
+      <c r="C27" s="9">
+        <v>46198.684641087966</v>
+      </c>
       <c r="D27" s="9">
-        <v>46197.58811881945</v>
+        <v>46198.68464270834</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>110</v>
@@ -3675,9 +3681,11 @@
       <c r="B28" s="5">
         <v>46162.5583337037</v>
       </c>
-      <c r="C28" s="6"/>
+      <c r="C28" s="5">
+        <v>46198.68467929398</v>
+      </c>
       <c r="D28" s="5">
-        <v>46169.86298305556</v>
+        <v>46198.68468228009</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3734,9 +3742,11 @@
       <c r="B29" s="9">
         <v>46162.55833876158</v>
       </c>
-      <c r="C29" s="10"/>
+      <c r="C29" s="9">
+        <v>46198.684322326386</v>
+      </c>
       <c r="D29" s="9">
-        <v>46196.17404179398</v>
+        <v>46198.684341354165</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>116</v>
@@ -3784,10 +3794,10 @@
         <v>33</v>
       </c>
       <c r="T29" s="10">
-        <v>0</v>
-      </c>
-      <c r="U29" s="11" t="s">
-        <v>82</v>
+        <v>1</v>
+      </c>
+      <c r="U29" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3797,9 +3807,11 @@
       <c r="B30" s="5">
         <v>46162.5583437037</v>
       </c>
-      <c r="C30" s="6"/>
+      <c r="C30" s="5">
+        <v>46198.68413635417</v>
+      </c>
       <c r="D30" s="5">
-        <v>46169.862896666666</v>
+        <v>46198.684137696764</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3856,9 +3868,11 @@
       <c r="B31" s="9">
         <v>46162.55834872685</v>
       </c>
-      <c r="C31" s="10"/>
+      <c r="C31" s="9">
+        <v>46198.68430692129</v>
+      </c>
       <c r="D31" s="9">
-        <v>46195.16988916667</v>
+        <v>46198.68430833334</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>122</v>
@@ -3915,9 +3929,11 @@
       <c r="B32" s="5">
         <v>46162.558353518514</v>
       </c>
-      <c r="C32" s="6"/>
+      <c r="C32" s="5">
+        <v>46198.68417550926</v>
+      </c>
       <c r="D32" s="5">
-        <v>46197.676590358795</v>
+        <v>46198.68417709491</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -4829,7 +4845,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46197.680058750004</v>
+        <v>46198.68419076389</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>178</v>
@@ -4879,8 +4895,8 @@
       <c r="T48" s="6">
         <v>0</v>
       </c>
-      <c r="U48" s="11" t="s">
-        <v>82</v>
+      <c r="U48" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -8244,7 +8260,7 @@
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46162.673902361115</v>
+        <v>46198.68469991898</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>298</v>
@@ -8294,8 +8310,8 @@
       <c r="T111" s="10">
         <v>0</v>
       </c>
-      <c r="U111" s="11" t="s">
-        <v>82</v>
+      <c r="U111" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
@@ -8370,7 +8386,7 @@
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46197.17582074074</v>
+        <v>46198.684325486116</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>304</v>
@@ -8420,8 +8436,8 @@
       <c r="T113" s="10">
         <v>0</v>
       </c>
-      <c r="U113" s="11" t="s">
-        <v>82</v>
+      <c r="U113" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2840" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2841" uniqueCount="513">
   <si>
     <t xml:space="preserve">50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT 4324 4325 </t>
   </si>
@@ -294,58 +294,58 @@
     <t>Propuesta compras:,Generación OC materiales corte Laser OT 4324 4325</t>
   </si>
   <si>
+    <t>1214969335271801</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma  OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969466331109</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969466331119</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa  OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969284200801</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>rodete OT 4324 4325,Materiales corte Laser OT 4324 4325,Alabe OT 4324 4325,Motor OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969466331129</t>
+  </si>
+  <si>
+    <t>Alabe OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe OT 4324 4325,Generación OC Alabe OT 4324 4325</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1214969335271801</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma  OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969466331109</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969466331119</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa  OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969284200801</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>rodete OT 4324 4325,Materiales corte Laser OT 4324 4325,Alabe OT 4324 4325,Motor OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969466331129</t>
-  </si>
-  <si>
-    <t>Alabe OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe OT 4324 4325,Generación OC Alabe OT 4324 4325</t>
   </si>
   <si>
     <t>1214969379038319</t>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46190.20507244213</v>
+        <v>46198.79339923611</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -3127,23 +3127,23 @@
       <c r="T18" s="6">
         <v>0</v>
       </c>
-      <c r="U18" s="11" t="s">
-        <v>82</v>
+      <c r="U18" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B19" s="9">
         <v>46162.55829380787</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46190.205072453704</v>
+        <v>46198.79340429398</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -3176,7 +3176,7 @@
         <v>80</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q19" s="9">
         <v>46188</v>
@@ -3190,23 +3190,23 @@
       <c r="T19" s="10">
         <v>0</v>
       </c>
-      <c r="U19" s="11" t="s">
-        <v>82</v>
+      <c r="U19" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B20" s="5">
         <v>46162.55829782407</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46190.20507252315</v>
+        <v>46198.793399999995</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -3239,7 +3239,7 @@
         <v>80</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q20" s="5">
         <v>46188</v>
@@ -3253,23 +3253,23 @@
       <c r="T20" s="6">
         <v>0</v>
       </c>
-      <c r="U20" s="11" t="s">
-        <v>82</v>
+      <c r="U20" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B21" s="9">
         <v>46162.558301446756</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46190.20507293982</v>
+        <v>46198.793400509254</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -3302,7 +3302,7 @@
         <v>80</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q21" s="9">
         <v>46188</v>
@@ -3316,13 +3316,13 @@
       <c r="T21" s="10">
         <v>0</v>
       </c>
-      <c r="U21" s="11" t="s">
-        <v>82</v>
+      <c r="U21" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B22" s="5">
         <v>46162.55817344907</v>
@@ -3332,7 +3332,7 @@
         <v>46198.68470386574</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -3356,7 +3356,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -3369,7 +3369,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B23" s="9">
         <v>46162.558305694445</v>
@@ -3379,16 +3379,16 @@
         <v>46169.86252686342</v>
       </c>
       <c r="E23" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="10" t="s">
+      <c r="H23" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="I23" s="9">
         <v>46155</v>
@@ -3406,13 +3406,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q23" s="9">
         <v>46155</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -3448,10 +3448,10 @@
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="I24" s="5">
         <v>46155</v>
@@ -3469,7 +3469,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>70</v>
@@ -3486,7 +3486,7 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -3507,10 +3507,10 @@
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="I25" s="9">
         <v>46157</v>
@@ -3528,7 +3528,7 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>101</v>
@@ -3545,7 +3545,7 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -3568,10 +3568,10 @@
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="I26" s="5">
         <v>46155</v>
@@ -3589,13 +3589,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>108</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q26" s="5">
         <v>46155</v>
@@ -3633,10 +3633,10 @@
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="I27" s="9">
         <v>46155</v>
@@ -3671,7 +3671,7 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3694,10 +3694,10 @@
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="I28" s="5">
         <v>46157</v>
@@ -3732,7 +3732,7 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3755,10 +3755,10 @@
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="I29" s="9">
         <v>46155</v>
@@ -3776,13 +3776,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>117</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q29" s="9">
         <v>46155</v>
@@ -3820,10 +3820,10 @@
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="I30" s="5">
         <v>46155</v>
@@ -3858,7 +3858,7 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3881,10 +3881,10 @@
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="I31" s="9">
         <v>46167</v>
@@ -3919,7 +3919,7 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -3942,10 +3942,10 @@
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="I32" s="5">
         <v>46167</v>
@@ -3980,7 +3980,7 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -4022,13 +4022,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O33" s="10" t="s">
         <v>131</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q33" s="9">
         <v>46190</v>
@@ -4043,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -4161,7 +4161,7 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -4203,7 +4203,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>141</v>
@@ -4224,7 +4224,7 @@
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -4239,7 +4239,7 @@
         <v>46191.169293900464</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
@@ -4269,7 +4269,7 @@
         <v>140</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>143</v>
@@ -4322,7 +4322,7 @@
         <v>140</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>146</v>
@@ -4372,7 +4372,7 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>151</v>
@@ -4393,7 +4393,7 @@
         <v>0</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -4408,7 +4408,7 @@
         <v>46198.16910141204</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
@@ -4438,7 +4438,7 @@
         <v>148</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>153</v>
@@ -4491,7 +4491,7 @@
         <v>148</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>156</v>
@@ -4594,7 +4594,7 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>163</v>
@@ -4615,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="U43" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -4630,7 +4630,7 @@
         <v>46191.169297465276</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
@@ -4660,7 +4660,7 @@
         <v>162</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>165</v>
@@ -4713,7 +4713,7 @@
         <v>162</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>168</v>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46197.674966516206</v>
+        <v>46198.79333590278</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4769,7 +4769,9 @@
       <c r="R46" s="6"/>
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
+      <c r="U46" s="12" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
@@ -4843,9 +4845,11 @@
       <c r="B48" s="5">
         <v>46162.55846439815</v>
       </c>
-      <c r="C48" s="6"/>
+      <c r="C48" s="5">
+        <v>46198.79331645834</v>
+      </c>
       <c r="D48" s="5">
-        <v>46198.68419076389</v>
+        <v>46198.79333422454</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>178</v>
@@ -4893,10 +4897,10 @@
         <v>33</v>
       </c>
       <c r="T48" s="6">
-        <v>0</v>
-      </c>
-      <c r="U48" s="12" t="s">
-        <v>47</v>
+        <v>1</v>
+      </c>
+      <c r="U48" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4906,9 +4910,11 @@
       <c r="B49" s="9">
         <v>46162.55847024306</v>
       </c>
-      <c r="C49" s="10"/>
+      <c r="C49" s="9">
+        <v>46198.79336401621</v>
+      </c>
       <c r="D49" s="9">
-        <v>46186.20479532407</v>
+        <v>46198.793379675924</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>80</v>
@@ -4954,10 +4960,10 @@
         <v>33</v>
       </c>
       <c r="T49" s="10">
-        <v>0</v>
-      </c>
-      <c r="U49" s="11" t="s">
-        <v>82</v>
+        <v>1</v>
+      </c>
+      <c r="U49" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -5020,7 +5026,7 @@
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -5742,7 +5748,7 @@
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5805,7 +5811,7 @@
         <v>0</v>
       </c>
       <c r="U65" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5868,7 +5874,7 @@
         <v>0</v>
       </c>
       <c r="U66" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5931,7 +5937,7 @@
         <v>0</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5994,7 +6000,7 @@
         <v>0</v>
       </c>
       <c r="U68" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -6057,7 +6063,7 @@
         <v>0</v>
       </c>
       <c r="U69" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -6167,7 +6173,7 @@
         <v>0</v>
       </c>
       <c r="U71" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -6866,7 +6872,7 @@
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6878,7 +6884,7 @@
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46162.67240607639</v>
+        <v>46198.79338525463</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>191</v>
@@ -6931,7 +6937,7 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46162.672403136574</v>
+        <v>46198.79338199074</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>191</v>
@@ -6984,7 +6990,7 @@
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46162.67239975695</v>
+        <v>46198.79338243055</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>191</v>
@@ -7037,7 +7043,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46162.67239702547</v>
+        <v>46198.79338296296</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>191</v>
@@ -7565,7 +7571,7 @@
         <v>0</v>
       </c>
       <c r="U97" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7577,7 +7583,7 @@
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46162.673765162035</v>
+        <v>46198.7933840162</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>191</v>
@@ -7630,7 +7636,7 @@
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46162.67376451389</v>
+        <v>46198.79338457176</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>191</v>
@@ -7683,7 +7689,7 @@
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46162.673763831015</v>
+        <v>46198.79337287037</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>191</v>
@@ -7736,7 +7742,7 @@
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46162.67376314815</v>
+        <v>46198.793388391205</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>191</v>
@@ -8374,7 +8380,7 @@
         <v>0</v>
       </c>
       <c r="U112" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
@@ -8500,7 +8506,7 @@
         <v>0</v>
       </c>
       <c r="U114" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
@@ -8610,7 +8616,7 @@
         <v>0</v>
       </c>
       <c r="U116" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
@@ -9309,7 +9315,7 @@
         <v>0</v>
       </c>
       <c r="U129" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
@@ -9321,7 +9327,7 @@
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46162.67439809028</v>
+        <v>46198.79338591435</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>191</v>
@@ -9372,7 +9378,7 @@
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46162.67439510417</v>
+        <v>46198.79338641204</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>191</v>
@@ -9423,7 +9429,7 @@
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46162.6743919213</v>
+        <v>46198.79338869213</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>191</v>
@@ -9474,7 +9480,7 @@
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46162.674388368054</v>
+        <v>46198.793389004626</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>191</v>
@@ -9576,7 +9582,7 @@
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46162.67438189815</v>
+        <v>46198.79336980324</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>197</v>
@@ -9627,7 +9633,7 @@
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46162.67437871528</v>
+        <v>46198.79337046296</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>197</v>
@@ -9678,7 +9684,7 @@
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46162.67437079861</v>
+        <v>46198.79337111111</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>197</v>
@@ -9729,7 +9735,7 @@
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46162.674370127315</v>
+        <v>46198.79337171296</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>197</v>
@@ -9780,7 +9786,7 @@
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46162.6743691088</v>
+        <v>46198.79337225694</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>197</v>
@@ -9984,7 +9990,7 @@
         <v>0</v>
       </c>
       <c r="U142" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
@@ -9996,7 +10002,7 @@
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46162.67453761574</v>
+        <v>46198.79338673611</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>191</v>
@@ -10049,7 +10055,7 @@
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46162.674534606485</v>
+        <v>46198.793387094905</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>191</v>
@@ -10102,7 +10108,7 @@
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46162.67453157407</v>
+        <v>46198.79338740741</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>191</v>
@@ -10155,7 +10161,7 @@
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46162.674528171294</v>
+        <v>46198.793387858794</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>191</v>
@@ -10683,7 +10689,7 @@
         <v>0</v>
       </c>
       <c r="U155" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
@@ -10695,7 +10701,7 @@
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46162.674694375004</v>
+        <v>46198.7933762037</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>191</v>
@@ -10748,7 +10754,7 @@
       </c>
       <c r="C157" s="10"/>
       <c r="D157" s="9">
-        <v>46162.67469101852</v>
+        <v>46198.79337655092</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>191</v>
@@ -10801,7 +10807,7 @@
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46162.674687928244</v>
+        <v>46198.793389375</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>191</v>
@@ -10854,7 +10860,7 @@
       </c>
       <c r="C159" s="10"/>
       <c r="D159" s="9">
-        <v>46162.67468512732</v>
+        <v>46198.79338491899</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>191</v>
@@ -11382,7 +11388,7 @@
         <v>0</v>
       </c>
       <c r="U168" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
@@ -12057,7 +12063,7 @@
         <v>0</v>
       </c>
       <c r="U181" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
@@ -12779,7 +12785,7 @@
         <v>0</v>
       </c>
       <c r="U195" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
@@ -13454,7 +13460,7 @@
         <v>0</v>
       </c>
       <c r="U208" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
@@ -14129,7 +14135,7 @@
         <v>0</v>
       </c>
       <c r="U221" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
@@ -14804,7 +14810,7 @@
         <v>0</v>
       </c>
       <c r="U234" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="235" spans="1:21" x14ac:dyDescent="0.25">
@@ -15550,7 +15556,7 @@
         <v>0</v>
       </c>
       <c r="U248" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="249" spans="1:21" x14ac:dyDescent="0.25">
@@ -15613,7 +15619,7 @@
         <v>0</v>
       </c>
       <c r="U249" s="11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -3992,7 +3992,7 @@
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46195.184916620376</v>
+        <v>46202.16935228009</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46169.86285621527</v>
+        <v>46202.16929391204</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>137</v>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46195.18491644676</v>
+        <v>46202.16929586805</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>140</v>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46195.18491668982</v>
+        <v>46202.169298692126</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>162</v>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46169.86267059028</v>
+        <v>46202.16929168982</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>167</v>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46162.672233703706</v>
+        <v>46202.191681435186</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>232</v>
@@ -6166,8 +6166,8 @@
       <c r="R71" s="9">
         <v>46209</v>
       </c>
-      <c r="S71" s="7" t="s">
-        <v>54</v>
+      <c r="S71" s="12" t="s">
+        <v>132</v>
       </c>
       <c r="T71" s="10">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -444,247 +444,247 @@
     <t>Fabricacion Corte Laser  OT 4324 4325,Generación OC materiales corte Laser OT 4324 4325</t>
   </si>
   <si>
+    <t>1214969335368191</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser  OT 4324 4325,Materiales corte Laser OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969379077262</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser  OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Materiales corte Laser OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969379077280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales Corte Plasma OT 4324 4325 </t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  OT 4324 4325,Fabricación Corte Plasma  OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969287605397</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma OT 4324 4325 ,Fabricación Corte Plasma  OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969287605412</t>
+  </si>
+  <si>
+    <t>Fabricación Corte Plasma  OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma OT 4324 4325 ,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>1214969287605814</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4324 4325,Fabricación estructura proveedor externo OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969287605824</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4324 4325,Fabricación estructura proveedor externo OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969287605839</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Recepcion fabricación externa ,Fabricación Externa  OT 4324 4325,Control de calidad fabricación externa  OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969466515947</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1214969466515957</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4324 4325,Fabricación Mecanizado OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969466515967</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4324 4325,Fabricación Mecanizado OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969335445666</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado,Mecanizado OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969284200803</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214969335445681</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214969466529004</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos motor proveedor OT 4324 4325</t>
+  </si>
+  <si>
+    <t>check planos,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>1214969379162030</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,Propuesta Mecanizado OT 4324 4325,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,Propuesta Fabricación externa  OT 4324 4325,propuesta Corte Laser OT 4324 4325,Propuesta Corte plasma  OT 4324 4325,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
+    <t>1214969335458365</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
+    <t>1214969335458375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">check pruebas FAT,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
+    <t>1214969335458385</t>
+  </si>
+  <si>
+    <t>1214969379177095</t>
+  </si>
+  <si>
+    <t>1214969379177100</t>
+  </si>
+  <si>
+    <t>1214969379177105</t>
+  </si>
+  <si>
+    <t>OT 4325- ZVN 1-7-63/2</t>
+  </si>
+  <si>
+    <t>1214969047720357</t>
+  </si>
+  <si>
+    <t>1214969047720358</t>
+  </si>
+  <si>
+    <t>1214969047720359</t>
+  </si>
+  <si>
+    <t>1214969047720360</t>
+  </si>
+  <si>
+    <t>1214969047720361</t>
+  </si>
+  <si>
+    <t>1214969047720362</t>
+  </si>
+  <si>
+    <t>1214969047720363</t>
+  </si>
+  <si>
+    <t>1214969379177110</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214969287656726</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214969335368191</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser  OT 4324 4325,Materiales corte Laser OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969379077262</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser  OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Materiales corte Laser OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969379077280</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales Corte Plasma OT 4324 4325 </t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  OT 4324 4325,Fabricación Corte Plasma  OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969287605397</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma OT 4324 4325 ,Fabricación Corte Plasma  OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969287605412</t>
-  </si>
-  <si>
-    <t>Fabricación Corte Plasma  OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma OT 4324 4325 ,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>1214969287605814</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4324 4325,Fabricación estructura proveedor externo OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969287605824</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4324 4325,Fabricación estructura proveedor externo OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969287605839</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Recepcion fabricación externa ,Fabricación Externa  OT 4324 4325,Control de calidad fabricación externa  OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969466515947</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1214969466515957</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4324 4325,Fabricación Mecanizado OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969466515967</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4324 4325,Fabricación Mecanizado OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969335445666</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado,Mecanizado OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969284200803</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214969335445681</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214969466529004</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos motor proveedor OT 4324 4325</t>
-  </si>
-  <si>
-    <t>check planos,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>1214969379162030</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,Propuesta Mecanizado OT 4324 4325,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,Propuesta Fabricación externa  OT 4324 4325,propuesta Corte Laser OT 4324 4325,Propuesta Corte plasma  OT 4324 4325,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t>1214969335458365</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t>1214969335458375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">check pruebas FAT,OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t>1214969335458385</t>
-  </si>
-  <si>
-    <t>1214969379177095</t>
-  </si>
-  <si>
-    <t>1214969379177100</t>
-  </si>
-  <si>
-    <t>1214969379177105</t>
-  </si>
-  <si>
-    <t>OT 4325- ZVN 1-7-63/2</t>
-  </si>
-  <si>
-    <t>1214969047720357</t>
-  </si>
-  <si>
-    <t>1214969047720358</t>
-  </si>
-  <si>
-    <t>1214969047720359</t>
-  </si>
-  <si>
-    <t>1214969047720360</t>
-  </si>
-  <si>
-    <t>1214969047720361</t>
-  </si>
-  <si>
-    <t>1214969047720362</t>
-  </si>
-  <si>
-    <t>1214969047720363</t>
-  </si>
-  <si>
-    <t>1214969379177110</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214969287656726</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
   </si>
   <si>
     <t>1214969287656746</t>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46202.16935228009</v>
+        <v>46203.186885787036</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -4036,8 +4036,8 @@
       <c r="R33" s="9">
         <v>46202</v>
       </c>
-      <c r="S33" s="12" t="s">
-        <v>132</v>
+      <c r="S33" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T33" s="10">
         <v>0</v>
@@ -4048,7 +4048,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5">
         <v>46162.5583628125</v>
@@ -4058,7 +4058,7 @@
         <v>46191.16929601852</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -4091,7 +4091,7 @@
         <v>77</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -4107,7 +4107,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B35" s="9">
         <v>46162.55841275463</v>
@@ -4117,7 +4117,7 @@
         <v>46202.16929391204</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
@@ -4147,10 +4147,10 @@
         <v>128</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -4166,17 +4166,17 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B36" s="5">
         <v>46162.558418622684</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46202.16929586805</v>
+        <v>46203.186885821764</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -4206,7 +4206,7 @@
         <v>92</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -4217,8 +4217,8 @@
       <c r="R36" s="5">
         <v>46202</v>
       </c>
-      <c r="S36" s="12" t="s">
-        <v>132</v>
+      <c r="S36" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
@@ -4229,7 +4229,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B37" s="9">
         <v>46162.558422118054</v>
@@ -4266,13 +4266,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>83</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -4282,7 +4282,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46162.558426400465</v>
@@ -4292,7 +4292,7 @@
         <v>46171.17362893518</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -4319,13 +4319,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -4335,7 +4335,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B39" s="9">
         <v>46162.55843366898</v>
@@ -4345,16 +4345,16 @@
         <v>46169.862598437496</v>
       </c>
       <c r="E39" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>149</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>150</v>
       </c>
       <c r="I39" s="9">
         <v>46190</v>
@@ -4375,7 +4375,7 @@
         <v>92</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -4398,7 +4398,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46162.558437569445</v>
@@ -4414,10 +4414,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>150</v>
       </c>
       <c r="I40" s="5">
         <v>46190</v>
@@ -4435,13 +4435,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>89</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4451,7 +4451,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B41" s="9">
         <v>46162.55844153935</v>
@@ -4461,16 +4461,16 @@
         <v>46169.86272391204</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>149</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>150</v>
       </c>
       <c r="I41" s="9">
         <v>46199</v>
@@ -4488,13 +4488,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>90</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46162.55844576389</v>
@@ -4514,16 +4514,16 @@
         <v>46169.862742349535</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I42" s="5">
         <v>46230</v>
@@ -4541,10 +4541,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4557,17 +4557,17 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B43" s="9">
         <v>46162.55844833334</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46202.169298692126</v>
+        <v>46203.186886435185</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
@@ -4597,7 +4597,7 @@
         <v>92</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4608,8 +4608,8 @@
       <c r="R43" s="9">
         <v>46202</v>
       </c>
-      <c r="S43" s="12" t="s">
-        <v>132</v>
+      <c r="S43" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T43" s="10">
         <v>0</v>
@@ -4620,7 +4620,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46162.55845114583</v>
@@ -4657,13 +4657,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4673,7 +4673,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B45" s="9">
         <v>46162.55845520833</v>
@@ -4683,7 +4683,7 @@
         <v>46202.16929168982</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -4710,13 +4710,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>87</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46162.55817767361</v>
@@ -4736,7 +4736,7 @@
         <v>46198.79333590278</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4760,7 +4760,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4775,7 +4775,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B47" s="9">
         <v>46162.55845957176</v>
@@ -4787,16 +4787,16 @@
         <v>46197.67690475694</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>174</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>175</v>
       </c>
       <c r="I47" s="9">
         <v>46160</v>
@@ -4814,13 +4814,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="9">
         <v>46160</v>
@@ -4840,7 +4840,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46162.55846439815</v>
@@ -4852,16 +4852,16 @@
         <v>46198.79333422454</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46176</v>
@@ -4879,13 +4879,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46176</v>
@@ -4905,7 +4905,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B49" s="9">
         <v>46162.55847024306</v>
@@ -4923,10 +4923,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4942,13 +4942,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="9">
         <v>46185</v>
@@ -4968,7 +4968,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46162.55848571759</v>
@@ -4978,16 +4978,16 @@
         <v>46162.671697337966</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46225</v>
@@ -5005,10 +5005,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -5031,7 +5031,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
         <v>46162.5584890162</v>
@@ -5041,16 +5041,16 @@
         <v>46191.68638508102</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -5066,13 +5066,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O51" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="P51" s="10" t="s">
         <v>191</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>192</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -5082,7 +5082,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46162.558492951386</v>
@@ -5092,16 +5092,16 @@
         <v>46191.68638201389</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -5117,13 +5117,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="P52" s="6" t="s">
         <v>191</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>192</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -5133,7 +5133,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B53" s="9">
         <v>46162.55849660879</v>
@@ -5143,16 +5143,16 @@
         <v>46191.68637913195</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
@@ -5168,13 +5168,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -5184,7 +5184,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B54" s="5">
         <v>46162.55849916667</v>
@@ -5194,16 +5194,16 @@
         <v>46191.68637614584</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -5219,13 +5219,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5235,7 +5235,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B55" s="9">
         <v>46162.55850175926</v>
@@ -5245,16 +5245,16 @@
         <v>46191.6863727662</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -5270,13 +5270,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5286,7 +5286,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B56" s="5">
         <v>46162.56211614583</v>
@@ -5296,16 +5296,16 @@
         <v>46191.686369641204</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -5321,10 +5321,10 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -5337,7 +5337,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B57" s="9">
         <v>46162.56212396991</v>
@@ -5347,16 +5347,16 @@
         <v>46191.68636637731</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="9">
@@ -5372,13 +5372,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5388,7 +5388,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B58" s="5">
         <v>46162.56213497685</v>
@@ -5398,16 +5398,16 @@
         <v>46191.686363761575</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -5423,13 +5423,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5439,7 +5439,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B59" s="9">
         <v>46162.562155057865</v>
@@ -5449,16 +5449,16 @@
         <v>46191.6863608912</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="9">
@@ -5474,10 +5474,10 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>26</v>
@@ -5490,7 +5490,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B60" s="5">
         <v>46162.562163055554</v>
@@ -5500,16 +5500,16 @@
         <v>46191.68635278935</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5525,10 +5525,10 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5541,7 +5541,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B61" s="9">
         <v>46162.56217104167</v>
@@ -5551,16 +5551,16 @@
         <v>46191.68635209491</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="9">
@@ -5576,10 +5576,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5592,7 +5592,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B62" s="5">
         <v>46162.562178935186</v>
@@ -5602,16 +5602,16 @@
         <v>46191.686351412034</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I62" s="6"/>
       <c r="J62" s="5">
@@ -5627,13 +5627,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5643,7 +5643,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B63" s="9">
         <v>46162.55850443287</v>
@@ -5653,7 +5653,7 @@
         <v>46162.60484554398</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>25</v>
@@ -5677,7 +5677,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>26</v>
@@ -5690,26 +5690,26 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B64" s="5">
         <v>46162.558507546295</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46196.16939501157</v>
+        <v>46203.170544444445</v>
       </c>
       <c r="E64" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G64" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="F64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G64" s="6" t="s">
+      <c r="H64" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I64" s="5">
         <v>46203</v>
@@ -5727,13 +5727,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q64" s="5">
         <v>46203</v>
@@ -5742,7 +5742,7 @@
         <v>46203</v>
       </c>
       <c r="S64" s="12" t="s">
-        <v>132</v>
+        <v>212</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
@@ -5769,10 +5769,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I65" s="9">
         <v>46204</v>
@@ -5790,7 +5790,7 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O65" s="10" t="s">
         <v>215</v>
@@ -5805,7 +5805,7 @@
         <v>46204</v>
       </c>
       <c r="S65" s="12" t="s">
-        <v>132</v>
+        <v>212</v>
       </c>
       <c r="T65" s="10">
         <v>0</v>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46196.16939498842</v>
+        <v>46203.17054697916</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>218</v>
@@ -5832,10 +5832,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I66" s="5">
         <v>46203</v>
@@ -5853,10 +5853,10 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>219</v>
@@ -5868,7 +5868,7 @@
         <v>46203</v>
       </c>
       <c r="S66" s="12" t="s">
-        <v>132</v>
+        <v>212</v>
       </c>
       <c r="T66" s="6">
         <v>0</v>
@@ -5895,10 +5895,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I67" s="9">
         <v>46204</v>
@@ -5916,7 +5916,7 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>218</v>
@@ -5931,7 +5931,7 @@
         <v>46204</v>
       </c>
       <c r="S67" s="12" t="s">
-        <v>132</v>
+        <v>212</v>
       </c>
       <c r="T67" s="10">
         <v>0</v>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46196.16939524305</v>
+        <v>46203.170548298614</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>224</v>
@@ -5958,10 +5958,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I68" s="5">
         <v>46203</v>
@@ -5979,10 +5979,10 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>225</v>
@@ -5994,7 +5994,7 @@
         <v>46203</v>
       </c>
       <c r="S68" s="12" t="s">
-        <v>132</v>
+        <v>212</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
@@ -6021,10 +6021,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I69" s="9">
         <v>46204</v>
@@ -6042,7 +6042,7 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>224</v>
@@ -6057,7 +6057,7 @@
         <v>46204</v>
       </c>
       <c r="S69" s="12" t="s">
-        <v>132</v>
+        <v>212</v>
       </c>
       <c r="T69" s="10">
         <v>0</v>
@@ -6167,7 +6167,7 @@
         <v>46209</v>
       </c>
       <c r="S71" s="12" t="s">
-        <v>132</v>
+        <v>212</v>
       </c>
       <c r="T71" s="10">
         <v>0</v>
@@ -6188,7 +6188,7 @@
         <v>46162.672237060186</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -6241,7 +6241,7 @@
         <v>46162.67223377315</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -6294,7 +6294,7 @@
         <v>46162.67223053241</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -6347,7 +6347,7 @@
         <v>46162.67222738426</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -6400,7 +6400,7 @@
         <v>46162.67222361111</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6453,7 +6453,7 @@
         <v>46162.672220196764</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6486,7 +6486,7 @@
         <v>248</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6506,7 +6506,7 @@
         <v>46162.67221694444</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6539,7 +6539,7 @@
         <v>237</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6559,7 +6559,7 @@
         <v>46162.67221386574</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6592,7 +6592,7 @@
         <v>244</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6612,7 +6612,7 @@
         <v>46162.67221096065</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6645,7 +6645,7 @@
         <v>244</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6665,7 +6665,7 @@
         <v>46162.67220178241</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6698,7 +6698,7 @@
         <v>244</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6718,7 +6718,7 @@
         <v>46162.67220103009</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6751,7 +6751,7 @@
         <v>248</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6771,7 +6771,7 @@
         <v>46162.6722002662</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6804,7 +6804,7 @@
         <v>240</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6887,7 +6887,7 @@
         <v>46198.79338525463</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6940,7 +6940,7 @@
         <v>46198.79338199074</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6993,7 +6993,7 @@
         <v>46198.79338243055</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -7046,7 +7046,7 @@
         <v>46198.79338296296</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -7099,7 +7099,7 @@
         <v>46162.67239402777</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -7129,7 +7129,7 @@
         <v>256</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>266</v>
@@ -7152,7 +7152,7 @@
         <v>46162.672391064814</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -7182,10 +7182,10 @@
         <v>256</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7205,7 +7205,7 @@
         <v>46162.672387743056</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -7235,7 +7235,7 @@
         <v>256</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P91" s="10" t="s">
         <v>26</v>
@@ -7258,7 +7258,7 @@
         <v>46162.67238480324</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7288,10 +7288,10 @@
         <v>256</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7311,7 +7311,7 @@
         <v>46162.67238212963</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7341,10 +7341,10 @@
         <v>256</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7364,7 +7364,7 @@
         <v>46162.67237393519</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7394,10 +7394,10 @@
         <v>256</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7417,7 +7417,7 @@
         <v>46162.67237322917</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7447,10 +7447,10 @@
         <v>256</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7470,7 +7470,7 @@
         <v>46162.67237256945</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7500,10 +7500,10 @@
         <v>256</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7529,10 +7529,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H97" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I97" s="9">
         <v>46217</v>
@@ -7586,16 +7586,16 @@
         <v>46198.7933840162</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I98" s="5">
         <v>46217</v>
@@ -7639,16 +7639,16 @@
         <v>46198.79338457176</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H99" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I99" s="9">
         <v>46217</v>
@@ -7692,16 +7692,16 @@
         <v>46198.79337287037</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I100" s="5">
         <v>46217</v>
@@ -7745,16 +7745,16 @@
         <v>46198.793388391205</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I101" s="9">
         <v>46217</v>
@@ -7798,16 +7798,16 @@
         <v>46162.67376247685</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I102" s="5">
         <v>46217</v>
@@ -7828,7 +7828,7 @@
         <v>275</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>286</v>
@@ -7851,16 +7851,16 @@
         <v>46162.67376181713</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H103" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I103" s="9">
         <v>46217</v>
@@ -7881,10 +7881,10 @@
         <v>275</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7904,16 +7904,16 @@
         <v>46162.67376091435</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I104" s="5">
         <v>46217</v>
@@ -7937,7 +7937,7 @@
         <v>289</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7957,16 +7957,16 @@
         <v>46162.67376023148</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H105" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I105" s="9">
         <v>46217</v>
@@ -7987,10 +7987,10 @@
         <v>275</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -8010,16 +8010,16 @@
         <v>46162.67375957176</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I106" s="5">
         <v>46217</v>
@@ -8040,10 +8040,10 @@
         <v>275</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8063,16 +8063,16 @@
         <v>46162.67375887731</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H107" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I107" s="9">
         <v>46217</v>
@@ -8093,10 +8093,10 @@
         <v>275</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -8116,16 +8116,16 @@
         <v>46162.67375819445</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H108" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I108" s="5">
         <v>46217</v>
@@ -8146,10 +8146,10 @@
         <v>275</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8169,16 +8169,16 @@
         <v>46162.67375751157</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H109" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I109" s="9">
         <v>46217</v>
@@ -8199,10 +8199,10 @@
         <v>275</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8222,7 +8222,7 @@
         <v>46162.61466552083</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>25</v>
@@ -8275,10 +8275,10 @@
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H111" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H111" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I111" s="9">
         <v>46161</v>
@@ -8296,7 +8296,7 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O111" s="10" t="s">
         <v>113</v>
@@ -8338,10 +8338,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H112" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I112" s="5">
         <v>46161</v>
@@ -8359,7 +8359,7 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>104</v>
@@ -8401,10 +8401,10 @@
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H113" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H113" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I113" s="9">
         <v>46196</v>
@@ -8422,7 +8422,7 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O113" s="10" t="s">
         <v>122</v>
@@ -8464,10 +8464,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H114" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I114" s="5">
         <v>46232</v>
@@ -8485,10 +8485,10 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>308</v>
@@ -8631,7 +8631,7 @@
         <v>46162.674262650464</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8684,7 +8684,7 @@
         <v>46162.67425921296</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8737,7 +8737,7 @@
         <v>46162.67425633102</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8767,7 +8767,7 @@
         <v>313</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P119" s="10" t="s">
         <v>319</v>
@@ -8790,7 +8790,7 @@
         <v>46162.674253379635</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8820,7 +8820,7 @@
         <v>313</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>319</v>
@@ -8843,7 +8843,7 @@
         <v>46162.67425</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8873,10 +8873,10 @@
         <v>313</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8896,7 +8896,7 @@
         <v>46162.67424702546</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8926,10 +8926,10 @@
         <v>313</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8949,7 +8949,7 @@
         <v>46162.67424429399</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8979,10 +8979,10 @@
         <v>313</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -9002,7 +9002,7 @@
         <v>46162.674233321755</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -9032,10 +9032,10 @@
         <v>313</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9055,7 +9055,7 @@
         <v>46162.67423263889</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -9085,10 +9085,10 @@
         <v>313</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -9108,7 +9108,7 @@
         <v>46162.674231944446</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9138,10 +9138,10 @@
         <v>313</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9161,7 +9161,7 @@
         <v>46162.674231261575</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -9191,10 +9191,10 @@
         <v>313</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9214,7 +9214,7 @@
         <v>46162.67423060186</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9244,10 +9244,10 @@
         <v>313</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9330,7 +9330,7 @@
         <v>46198.79338591435</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9381,7 +9381,7 @@
         <v>46198.79338641204</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9432,7 +9432,7 @@
         <v>46198.79338869213</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9483,7 +9483,7 @@
         <v>46198.793389004626</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9534,7 +9534,7 @@
         <v>46162.67438523148</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9562,7 +9562,7 @@
         <v>330</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>341</v>
@@ -9585,7 +9585,7 @@
         <v>46198.79336980324</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9616,7 +9616,7 @@
         <v>343</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9636,7 +9636,7 @@
         <v>46198.79337046296</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9667,7 +9667,7 @@
         <v>345</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9687,7 +9687,7 @@
         <v>46198.79337111111</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9718,7 +9718,7 @@
         <v>343</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9738,7 +9738,7 @@
         <v>46198.79337171296</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9789,7 +9789,7 @@
         <v>46198.79337225694</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -9820,7 +9820,7 @@
         <v>343</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9840,7 +9840,7 @@
         <v>46162.6743640162</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9871,7 +9871,7 @@
         <v>351</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9891,7 +9891,7 @@
         <v>46162.67436230324</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -9922,7 +9922,7 @@
         <v>351</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -10005,7 +10005,7 @@
         <v>46198.79338673611</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -10058,7 +10058,7 @@
         <v>46198.793387094905</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -10111,7 +10111,7 @@
         <v>46198.79338740741</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -10164,7 +10164,7 @@
         <v>46198.793387858794</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10217,7 +10217,7 @@
         <v>46162.674524965274</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -10247,7 +10247,7 @@
         <v>354</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P147" s="10" t="s">
         <v>364</v>
@@ -10270,7 +10270,7 @@
         <v>46162.674521354165</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10303,7 +10303,7 @@
         <v>366</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10323,7 +10323,7 @@
         <v>46162.67451787037</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -10353,10 +10353,10 @@
         <v>354</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10376,7 +10376,7 @@
         <v>46162.67451502314</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10409,7 +10409,7 @@
         <v>366</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10462,7 +10462,7 @@
         <v>366</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10482,7 +10482,7 @@
         <v>46162.67450335648</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10515,7 +10515,7 @@
         <v>366</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10535,7 +10535,7 @@
         <v>46162.67450263889</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10568,7 +10568,7 @@
         <v>366</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q153" s="10"/>
       <c r="R153" s="10"/>
@@ -10588,7 +10588,7 @@
         <v>46162.67450188658</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10621,7 +10621,7 @@
         <v>366</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10704,7 +10704,7 @@
         <v>46198.7933762037</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10757,7 +10757,7 @@
         <v>46198.79337655092</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
@@ -10810,7 +10810,7 @@
         <v>46198.793389375</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10863,7 +10863,7 @@
         <v>46198.79338491899</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
@@ -10916,7 +10916,7 @@
         <v>46162.674682349534</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -10946,7 +10946,7 @@
         <v>374</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P160" s="6" t="s">
         <v>385</v>
@@ -10969,7 +10969,7 @@
         <v>46162.674678888885</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
@@ -11022,7 +11022,7 @@
         <v>46162.67467586805</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -11055,7 +11055,7 @@
         <v>387</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11075,7 +11075,7 @@
         <v>46162.67467314815</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
@@ -11128,7 +11128,7 @@
         <v>46162.67467030093</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11181,7 +11181,7 @@
         <v>46162.67466239583</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
@@ -11234,7 +11234,7 @@
         <v>46162.674661655095</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11287,7 +11287,7 @@
         <v>46162.67466097222</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
@@ -11320,7 +11320,7 @@
         <v>387</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q167" s="10"/>
       <c r="R167" s="10"/>
@@ -11403,7 +11403,7 @@
         <v>46162.67483585648</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
@@ -11431,7 +11431,7 @@
         <v>399</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P169" s="10" t="s">
         <v>401</v>
@@ -11454,7 +11454,7 @@
         <v>46162.674832847224</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11482,7 +11482,7 @@
         <v>399</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P170" s="6" t="s">
         <v>401</v>
@@ -11505,7 +11505,7 @@
         <v>46162.67482962963</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11533,7 +11533,7 @@
         <v>399</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P171" s="10" t="s">
         <v>404</v>
@@ -11556,7 +11556,7 @@
         <v>46162.67482693287</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11584,7 +11584,7 @@
         <v>399</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P172" s="6" t="s">
         <v>404</v>
@@ -11607,7 +11607,7 @@
         <v>46162.67482414352</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
@@ -11635,7 +11635,7 @@
         <v>399</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P173" s="10" t="s">
         <v>407</v>
@@ -11658,7 +11658,7 @@
         <v>46162.67482128472</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
@@ -11686,7 +11686,7 @@
         <v>399</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P174" s="6" t="s">
         <v>26</v>
@@ -11709,7 +11709,7 @@
         <v>46162.67481818287</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
@@ -11737,10 +11737,10 @@
         <v>399</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q175" s="10"/>
       <c r="R175" s="10"/>
@@ -11760,7 +11760,7 @@
         <v>46162.674815543985</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
@@ -11788,7 +11788,7 @@
         <v>399</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P176" s="6" t="s">
         <v>26</v>
@@ -11811,7 +11811,7 @@
         <v>46162.674812743055</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
@@ -11839,7 +11839,7 @@
         <v>399</v>
       </c>
       <c r="O177" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P177" s="10" t="s">
         <v>26</v>
@@ -11862,7 +11862,7 @@
         <v>46162.67480497685</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
@@ -11890,7 +11890,7 @@
         <v>399</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P178" s="6" t="s">
         <v>26</v>
@@ -11913,7 +11913,7 @@
         <v>46162.674804317125</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
@@ -11941,7 +11941,7 @@
         <v>399</v>
       </c>
       <c r="O179" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P179" s="10" t="s">
         <v>26</v>
@@ -11964,7 +11964,7 @@
         <v>46162.674803587965</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
@@ -11992,10 +11992,10 @@
         <v>399</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -12078,7 +12078,7 @@
         <v>46162.675084849536</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
@@ -12106,7 +12106,7 @@
         <v>416</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P182" s="6" t="s">
         <v>419</v>
@@ -12129,7 +12129,7 @@
         <v>46162.67508193287</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>26</v>
@@ -12157,7 +12157,7 @@
         <v>416</v>
       </c>
       <c r="O183" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P183" s="10" t="s">
         <v>419</v>
@@ -12180,7 +12180,7 @@
         <v>46162.67507869213</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
@@ -12208,7 +12208,7 @@
         <v>416</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P184" s="6" t="s">
         <v>422</v>
@@ -12231,7 +12231,7 @@
         <v>46162.67507611111</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
@@ -12259,7 +12259,7 @@
         <v>416</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P185" s="10" t="s">
         <v>419</v>
@@ -12282,7 +12282,7 @@
         <v>46162.6750730787</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
@@ -12310,7 +12310,7 @@
         <v>416</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P186" s="6" t="s">
         <v>425</v>
@@ -12333,7 +12333,7 @@
         <v>46162.675070150464</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
@@ -12361,7 +12361,7 @@
         <v>416</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P187" s="10" t="s">
         <v>26</v>
@@ -12384,7 +12384,7 @@
         <v>46162.6750674537</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12412,7 +12412,7 @@
         <v>416</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P188" s="6" t="s">
         <v>391</v>
@@ -12435,7 +12435,7 @@
         <v>46162.67506488426</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
@@ -12463,10 +12463,10 @@
         <v>416</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12486,7 +12486,7 @@
         <v>46162.67506164352</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12514,10 +12514,10 @@
         <v>416</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12537,7 +12537,7 @@
         <v>46162.67505446759</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
@@ -12565,10 +12565,10 @@
         <v>416</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12588,7 +12588,7 @@
         <v>46162.675053750005</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -12616,10 +12616,10 @@
         <v>416</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12639,7 +12639,7 @@
         <v>46162.67505302084</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>26</v>
@@ -12667,10 +12667,10 @@
         <v>416</v>
       </c>
       <c r="O193" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P193" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q193" s="10"/>
       <c r="R193" s="10"/>
@@ -12800,7 +12800,7 @@
         <v>46162.67538505787</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
@@ -12828,7 +12828,7 @@
         <v>437</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P196" s="6" t="s">
         <v>442</v>
@@ -12851,7 +12851,7 @@
         <v>46162.675382534726</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>26</v>
@@ -12879,7 +12879,7 @@
         <v>437</v>
       </c>
       <c r="O197" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P197" s="10" t="s">
         <v>442</v>
@@ -12902,7 +12902,7 @@
         <v>46162.67537990741</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
@@ -12930,7 +12930,7 @@
         <v>437</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P198" s="6" t="s">
         <v>442</v>
@@ -12953,7 +12953,7 @@
         <v>46162.67537715277</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>26</v>
@@ -12981,7 +12981,7 @@
         <v>437</v>
       </c>
       <c r="O199" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P199" s="10" t="s">
         <v>442</v>
@@ -13004,7 +13004,7 @@
         <v>46162.675374178245</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
@@ -13032,7 +13032,7 @@
         <v>437</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P200" s="6" t="s">
         <v>447</v>
@@ -13055,7 +13055,7 @@
         <v>46162.675371296296</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
@@ -13083,7 +13083,7 @@
         <v>437</v>
       </c>
       <c r="O201" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P201" s="10" t="s">
         <v>391</v>
@@ -13106,7 +13106,7 @@
         <v>46162.675368321754</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
@@ -13134,7 +13134,7 @@
         <v>437</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P202" s="6" t="s">
         <v>26</v>
@@ -13157,7 +13157,7 @@
         <v>46162.67536565972</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
@@ -13185,10 +13185,10 @@
         <v>437</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P203" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q203" s="10"/>
       <c r="R203" s="10"/>
@@ -13208,7 +13208,7 @@
         <v>46162.67536296297</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
@@ -13236,10 +13236,10 @@
         <v>437</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13259,7 +13259,7 @@
         <v>46162.67535506944</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
@@ -13287,10 +13287,10 @@
         <v>437</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q205" s="10"/>
       <c r="R205" s="10"/>
@@ -13310,7 +13310,7 @@
         <v>46162.67535439815</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
@@ -13338,10 +13338,10 @@
         <v>437</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13361,7 +13361,7 @@
         <v>46162.67535373842</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
@@ -13389,10 +13389,10 @@
         <v>437</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q207" s="10"/>
       <c r="R207" s="10"/>
@@ -13475,7 +13475,7 @@
         <v>46162.67559398148</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
@@ -13503,7 +13503,7 @@
         <v>456</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P209" s="10" t="s">
         <v>458</v>
@@ -13526,7 +13526,7 @@
         <v>46162.67559118055</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
@@ -13554,7 +13554,7 @@
         <v>456</v>
       </c>
       <c r="O210" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P210" s="6" t="s">
         <v>458</v>
@@ -13577,7 +13577,7 @@
         <v>46162.675588391205</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>26</v>
@@ -13605,7 +13605,7 @@
         <v>456</v>
       </c>
       <c r="O211" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P211" s="10" t="s">
         <v>458</v>
@@ -13628,7 +13628,7 @@
         <v>46162.67558560186</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
@@ -13656,7 +13656,7 @@
         <v>456</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P212" s="6" t="s">
         <v>458</v>
@@ -13679,7 +13679,7 @@
         <v>46162.67558284722</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>26</v>
@@ -13707,7 +13707,7 @@
         <v>456</v>
       </c>
       <c r="O213" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P213" s="10" t="s">
         <v>463</v>
@@ -13730,7 +13730,7 @@
         <v>46162.6755797338</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
@@ -13758,7 +13758,7 @@
         <v>456</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P214" s="6" t="s">
         <v>26</v>
@@ -13781,7 +13781,7 @@
         <v>46162.675576967595</v>
       </c>
       <c r="E215" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F215" s="10" t="s">
         <v>26</v>
@@ -13809,10 +13809,10 @@
         <v>456</v>
       </c>
       <c r="O215" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P215" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q215" s="10"/>
       <c r="R215" s="10"/>
@@ -13832,7 +13832,7 @@
         <v>46162.67557431713</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
@@ -13860,7 +13860,7 @@
         <v>456</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P216" s="6" t="s">
         <v>467</v>
@@ -13883,7 +13883,7 @@
         <v>46162.67557162037</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>26</v>
@@ -13911,10 +13911,10 @@
         <v>456</v>
       </c>
       <c r="O217" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P217" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q217" s="10"/>
       <c r="R217" s="10"/>
@@ -13934,7 +13934,7 @@
         <v>46162.67556375</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
@@ -13962,10 +13962,10 @@
         <v>456</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P218" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q218" s="6"/>
       <c r="R218" s="6"/>
@@ -13985,7 +13985,7 @@
         <v>46162.675563020835</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>26</v>
@@ -14013,10 +14013,10 @@
         <v>456</v>
       </c>
       <c r="O219" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P219" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q219" s="10"/>
       <c r="R219" s="10"/>
@@ -14036,7 +14036,7 @@
         <v>46162.67556230324</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
@@ -14064,10 +14064,10 @@
         <v>456</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P220" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q220" s="6"/>
       <c r="R220" s="6"/>
@@ -14150,7 +14150,7 @@
         <v>46162.67579450231</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
@@ -14178,7 +14178,7 @@
         <v>473</v>
       </c>
       <c r="O222" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P222" s="6" t="s">
         <v>475</v>
@@ -14201,7 +14201,7 @@
         <v>46162.6757915162</v>
       </c>
       <c r="E223" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>26</v>
@@ -14229,7 +14229,7 @@
         <v>473</v>
       </c>
       <c r="O223" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P223" s="10" t="s">
         <v>475</v>
@@ -14252,7 +14252,7 @@
         <v>46162.67578863426</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>26</v>
@@ -14280,7 +14280,7 @@
         <v>473</v>
       </c>
       <c r="O224" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P224" s="6" t="s">
         <v>478</v>
@@ -14303,7 +14303,7 @@
         <v>46162.67578590278</v>
       </c>
       <c r="E225" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F225" s="10" t="s">
         <v>26</v>
@@ -14331,7 +14331,7 @@
         <v>473</v>
       </c>
       <c r="O225" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P225" s="10" t="s">
         <v>478</v>
@@ -14354,7 +14354,7 @@
         <v>46162.67578289352</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F226" s="6" t="s">
         <v>26</v>
@@ -14382,7 +14382,7 @@
         <v>473</v>
       </c>
       <c r="O226" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P226" s="6" t="s">
         <v>481</v>
@@ -14405,7 +14405,7 @@
         <v>46162.67577962963</v>
       </c>
       <c r="E227" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F227" s="10" t="s">
         <v>26</v>
@@ -14433,10 +14433,10 @@
         <v>473</v>
       </c>
       <c r="O227" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P227" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q227" s="10"/>
       <c r="R227" s="10"/>
@@ -14456,7 +14456,7 @@
         <v>46162.67577695602</v>
       </c>
       <c r="E228" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F228" s="6" t="s">
         <v>26</v>
@@ -14484,10 +14484,10 @@
         <v>473</v>
       </c>
       <c r="O228" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P228" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q228" s="6"/>
       <c r="R228" s="6"/>
@@ -14535,10 +14535,10 @@
         <v>473</v>
       </c>
       <c r="O229" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P229" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q229" s="10"/>
       <c r="R229" s="10"/>
@@ -14558,7 +14558,7 @@
         <v>46162.67577162037</v>
       </c>
       <c r="E230" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F230" s="6" t="s">
         <v>26</v>
@@ -14586,10 +14586,10 @@
         <v>473</v>
       </c>
       <c r="O230" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P230" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q230" s="6"/>
       <c r="R230" s="6"/>
@@ -14609,7 +14609,7 @@
         <v>46162.67576392361</v>
       </c>
       <c r="E231" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F231" s="10" t="s">
         <v>26</v>
@@ -14637,10 +14637,10 @@
         <v>473</v>
       </c>
       <c r="O231" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P231" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q231" s="10"/>
       <c r="R231" s="10"/>
@@ -14660,7 +14660,7 @@
         <v>46162.67576322917</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F232" s="6" t="s">
         <v>26</v>
@@ -14688,10 +14688,10 @@
         <v>473</v>
       </c>
       <c r="O232" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P232" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q232" s="6"/>
       <c r="R232" s="6"/>
@@ -14711,7 +14711,7 @@
         <v>46162.67576252315</v>
       </c>
       <c r="E233" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F233" s="10" t="s">
         <v>26</v>
@@ -14739,10 +14739,10 @@
         <v>473</v>
       </c>
       <c r="O233" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P233" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q233" s="10"/>
       <c r="R233" s="10"/>
@@ -14825,7 +14825,7 @@
         <v>46162.676026875</v>
       </c>
       <c r="E235" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F235" s="10" t="s">
         <v>26</v>
@@ -14855,7 +14855,7 @@
         <v>490</v>
       </c>
       <c r="O235" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P235" s="10" t="s">
         <v>490</v>
@@ -14878,7 +14878,7 @@
         <v>46162.67602255787</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F236" s="6" t="s">
         <v>26</v>
@@ -14908,7 +14908,7 @@
         <v>490</v>
       </c>
       <c r="O236" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P236" s="6" t="s">
         <v>490</v>
@@ -14931,7 +14931,7 @@
         <v>46162.676019108796</v>
       </c>
       <c r="E237" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F237" s="10" t="s">
         <v>26</v>
@@ -14961,7 +14961,7 @@
         <v>490</v>
       </c>
       <c r="O237" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P237" s="10" t="s">
         <v>490</v>
@@ -14984,7 +14984,7 @@
         <v>46162.67601616898</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F238" s="6" t="s">
         <v>26</v>
@@ -15014,7 +15014,7 @@
         <v>490</v>
       </c>
       <c r="O238" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P238" s="6" t="s">
         <v>490</v>
@@ -15037,7 +15037,7 @@
         <v>46162.676013275464</v>
       </c>
       <c r="E239" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F239" s="10" t="s">
         <v>26</v>
@@ -15067,7 +15067,7 @@
         <v>490</v>
       </c>
       <c r="O239" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P239" s="10" t="s">
         <v>490</v>
@@ -15090,7 +15090,7 @@
         <v>46162.67600972222</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F240" s="6" t="s">
         <v>26</v>
@@ -15120,7 +15120,7 @@
         <v>490</v>
       </c>
       <c r="O240" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P240" s="6" t="s">
         <v>26</v>
@@ -15143,7 +15143,7 @@
         <v>46162.676007002316</v>
       </c>
       <c r="E241" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F241" s="10" t="s">
         <v>26</v>
@@ -15173,7 +15173,7 @@
         <v>490</v>
       </c>
       <c r="O241" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P241" s="10" t="s">
         <v>26</v>
@@ -15196,7 +15196,7 @@
         <v>46162.67600369213</v>
       </c>
       <c r="E242" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F242" s="6" t="s">
         <v>26</v>
@@ -15249,7 +15249,7 @@
         <v>46162.67599591435</v>
       </c>
       <c r="E243" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F243" s="10" t="s">
         <v>26</v>
@@ -15279,7 +15279,7 @@
         <v>490</v>
       </c>
       <c r="O243" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P243" s="10" t="s">
         <v>26</v>
@@ -15302,7 +15302,7 @@
         <v>46162.67599258102</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F244" s="6" t="s">
         <v>26</v>
@@ -15332,7 +15332,7 @@
         <v>490</v>
       </c>
       <c r="O244" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P244" s="6" t="s">
         <v>26</v>
@@ -15355,7 +15355,7 @@
         <v>46162.675991412034</v>
       </c>
       <c r="E245" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F245" s="10" t="s">
         <v>26</v>
@@ -15385,7 +15385,7 @@
         <v>490</v>
       </c>
       <c r="O245" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P245" s="10" t="s">
         <v>26</v>
@@ -15408,7 +15408,7 @@
         <v>46162.675990613425</v>
       </c>
       <c r="E246" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F246" s="6" t="s">
         <v>26</v>
@@ -15438,7 +15438,7 @@
         <v>490</v>
       </c>
       <c r="O246" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P246" s="6" t="s">
         <v>26</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -684,19 +684,19 @@
     <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
   </si>
   <si>
+    <t>1214969287656746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,Bodega:,OT 4324- ZVN 1-7-37/2 ,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214969287656746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,Bodega:,OT 4324- ZVN 1-7-37/2 ,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
   </si>
   <si>
     <t>1214969287656971</t>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46203.170544444445</v>
+        <v>46204.167069814815</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>208</v>
@@ -5741,8 +5741,8 @@
       <c r="R64" s="5">
         <v>46203</v>
       </c>
-      <c r="S64" s="12" t="s">
-        <v>212</v>
+      <c r="S64" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
@@ -5753,17 +5753,17 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B65" s="9">
         <v>46162.5585121412</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46197.168534537035</v>
+        <v>46204.16969789352</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5793,10 +5793,10 @@
         <v>205</v>
       </c>
       <c r="O65" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="P65" s="10" t="s">
         <v>215</v>
-      </c>
-      <c r="P65" s="10" t="s">
-        <v>216</v>
       </c>
       <c r="Q65" s="9">
         <v>46204</v>
@@ -5805,7 +5805,7 @@
         <v>46204</v>
       </c>
       <c r="S65" s="12" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="T65" s="10">
         <v>0</v>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46203.17054697916</v>
+        <v>46204.16707040509</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>218</v>
@@ -5867,8 +5867,8 @@
       <c r="R66" s="5">
         <v>46203</v>
       </c>
-      <c r="S66" s="12" t="s">
-        <v>212</v>
+      <c r="S66" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T66" s="6">
         <v>0</v>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46197.168534571756</v>
+        <v>46204.1696995949</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>221</v>
@@ -5931,7 +5931,7 @@
         <v>46204</v>
       </c>
       <c r="S67" s="12" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="T67" s="10">
         <v>0</v>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46203.170548298614</v>
+        <v>46204.1670715162</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>224</v>
@@ -5993,8 +5993,8 @@
       <c r="R68" s="5">
         <v>46203</v>
       </c>
-      <c r="S68" s="12" t="s">
-        <v>212</v>
+      <c r="S68" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46197.16853431713</v>
+        <v>46204.169700983795</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>225</v>
@@ -6057,7 +6057,7 @@
         <v>46204</v>
       </c>
       <c r="S69" s="12" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="T69" s="10">
         <v>0</v>
@@ -6167,7 +6167,7 @@
         <v>46209</v>
       </c>
       <c r="S71" s="12" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="T71" s="10">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -696,64 +696,64 @@
     <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,Bodega:,OT 4324- ZVN 1-7-37/2 ,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
   </si>
   <si>
+    <t>1214969287656971</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1214969287656991</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
+    <t>1214969287665511</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1214969287665526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
+    <t>1214969504173515</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,Armado,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1214969504173525</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214969287656971</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1214969287656991</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t>1214969287665511</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1214969287665526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t>1214969504173515</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,Armado,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1214969504173525</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
   </si>
   <si>
     <t>1214969379214241</t>
@@ -2211,13 +2211,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46162.55816053241</v>
+        <v>46162.39149386574</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.87408302083</v>
+        <v>46175.70741635417</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.87409729167</v>
+        <v>46175.707430625</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2264,13 +2264,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46162.55822986111</v>
+        <v>46162.39156319444</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.87405835648</v>
+        <v>46175.707391689815</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.87408342592</v>
+        <v>46175.70741675926</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -2329,13 +2329,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46162.55823326389</v>
+        <v>46162.39156659722</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.87405894676</v>
+        <v>46175.70739228009</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.87408357639</v>
+        <v>46175.70741690972</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2394,13 +2394,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46162.55823767361</v>
+        <v>46162.39157100694</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.87405929399</v>
+        <v>46175.707392627315</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.87408365741</v>
+        <v>46175.70741699074</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -2459,13 +2459,13 @@
         <v>38</v>
       </c>
       <c r="B8" s="5">
-        <v>46162.558241782404</v>
+        <v>46162.39157511574</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.8740596875</v>
+        <v>46175.70739302083</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.87408391204</v>
+        <v>46175.70741724537</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>39</v>
@@ -2524,13 +2524,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="9">
-        <v>46162.55824546296</v>
+        <v>46162.3915787963</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.87406025463</v>
+        <v>46175.70739358796</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.87408414352</v>
+        <v>46175.70741747685</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>43</v>
@@ -2589,11 +2589,11 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46162.55816482639</v>
+        <v>46162.39149815972</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46197.69419108796</v>
+        <v>46197.5275244213</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2638,13 +2638,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="9">
-        <v>46162.55824909722</v>
+        <v>46162.39158243056</v>
       </c>
       <c r="C11" s="9">
-        <v>46197.65242402778</v>
+        <v>46197.48575736111</v>
       </c>
       <c r="D11" s="9">
-        <v>46197.69418131944</v>
+        <v>46197.52751465278</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>49</v>
@@ -2703,13 +2703,13 @@
         <v>55</v>
       </c>
       <c r="B12" s="5">
-        <v>46162.55825447917</v>
+        <v>46162.3915878125</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.65454083333</v>
+        <v>46197.48787416666</v>
       </c>
       <c r="D12" s="5">
-        <v>46197.69418155093</v>
+        <v>46197.52751488426</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2768,13 +2768,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="9">
-        <v>46162.55825988426</v>
+        <v>46162.39159321759</v>
       </c>
       <c r="C13" s="9">
-        <v>46197.65648178241</v>
+        <v>46197.48981511574</v>
       </c>
       <c r="D13" s="9">
-        <v>46197.6941815162</v>
+        <v>46197.52751484954</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>60</v>
@@ -2833,11 +2833,11 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46162.55816920139</v>
+        <v>46162.39150253472</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46198.68393108796</v>
+        <v>46198.5172644213</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2880,13 +2880,13 @@
         <v>66</v>
       </c>
       <c r="B15" s="9">
-        <v>46162.55827298611</v>
+        <v>46162.39160631945</v>
       </c>
       <c r="C15" s="9">
-        <v>46198.683924930556</v>
+        <v>46198.51725826389</v>
       </c>
       <c r="D15" s="9">
-        <v>46198.683943310185</v>
+        <v>46198.51727664351</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>67</v>
@@ -2945,11 +2945,11 @@
         <v>69</v>
       </c>
       <c r="B16" s="5">
-        <v>46162.55827819444</v>
+        <v>46162.39161152778</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46197.654558842594</v>
+        <v>46197.48789217592</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>70</v>
@@ -3008,13 +3008,13 @@
         <v>72</v>
       </c>
       <c r="B17" s="9">
-        <v>46162.55828362268</v>
+        <v>46162.39161695602</v>
       </c>
       <c r="C17" s="9">
-        <v>46197.58811052083</v>
+        <v>46197.42144385417</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.77760189815</v>
+        <v>46197.61093523148</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>73</v>
@@ -3073,11 +3073,11 @@
         <v>76</v>
       </c>
       <c r="B18" s="5">
-        <v>46162.55828883102</v>
+        <v>46162.39162216435</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46198.79339923611</v>
+        <v>46198.62673256945</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -3136,11 +3136,11 @@
         <v>82</v>
       </c>
       <c r="B19" s="9">
-        <v>46162.55829380787</v>
+        <v>46162.3916271412</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46198.79340429398</v>
+        <v>46198.62673762732</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>83</v>
@@ -3199,11 +3199,11 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46162.55829782407</v>
+        <v>46162.39163115741</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46198.793399999995</v>
+        <v>46198.62673333334</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -3262,11 +3262,11 @@
         <v>88</v>
       </c>
       <c r="B21" s="9">
-        <v>46162.558301446756</v>
+        <v>46162.39163478009</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46198.793400509254</v>
+        <v>46198.6267338426</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>89</v>
@@ -3325,11 +3325,11 @@
         <v>91</v>
       </c>
       <c r="B22" s="5">
-        <v>46162.55817344907</v>
+        <v>46162.39150678241</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46198.68470386574</v>
+        <v>46198.51803719907</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -3372,11 +3372,11 @@
         <v>94</v>
       </c>
       <c r="B23" s="9">
-        <v>46162.558305694445</v>
+        <v>46162.39163902777</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46169.86252686342</v>
+        <v>46169.69586019676</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>95</v>
@@ -3435,11 +3435,11 @@
         <v>100</v>
       </c>
       <c r="B24" s="5">
-        <v>46162.55831018518</v>
+        <v>46162.391643518524</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.86302510416</v>
+        <v>46169.696358437504</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>101</v>
@@ -3494,11 +3494,11 @@
         <v>103</v>
       </c>
       <c r="B25" s="9">
-        <v>46162.55831479166</v>
+        <v>46162.391648125005</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.86304815972</v>
+        <v>46169.69638149306</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>104</v>
@@ -3553,13 +3553,13 @@
         <v>106</v>
       </c>
       <c r="B26" s="5">
-        <v>46162.558319710646</v>
+        <v>46162.39165304398</v>
       </c>
       <c r="C26" s="5">
-        <v>46198.68469451389</v>
+        <v>46198.518027847225</v>
       </c>
       <c r="D26" s="5">
-        <v>46198.684707002314</v>
+        <v>46198.51804033565</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>107</v>
@@ -3618,13 +3618,13 @@
         <v>109</v>
       </c>
       <c r="B27" s="9">
-        <v>46162.55832415509</v>
+        <v>46162.39165748842</v>
       </c>
       <c r="C27" s="9">
-        <v>46198.684641087966</v>
+        <v>46198.517974421295</v>
       </c>
       <c r="D27" s="9">
-        <v>46198.68464270834</v>
+        <v>46198.517976041665</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>110</v>
@@ -3679,13 +3679,13 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46162.5583337037</v>
+        <v>46162.39166703704</v>
       </c>
       <c r="C28" s="5">
-        <v>46198.68467929398</v>
+        <v>46198.51801262732</v>
       </c>
       <c r="D28" s="5">
-        <v>46198.68468228009</v>
+        <v>46198.51801561343</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3740,13 +3740,13 @@
         <v>115</v>
       </c>
       <c r="B29" s="9">
-        <v>46162.55833876158</v>
+        <v>46162.391672094906</v>
       </c>
       <c r="C29" s="9">
-        <v>46198.684322326386</v>
+        <v>46198.51765565972</v>
       </c>
       <c r="D29" s="9">
-        <v>46198.684341354165</v>
+        <v>46198.5176746875</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>116</v>
@@ -3805,13 +3805,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46162.5583437037</v>
+        <v>46162.39167703704</v>
       </c>
       <c r="C30" s="5">
-        <v>46198.68413635417</v>
+        <v>46198.517469687504</v>
       </c>
       <c r="D30" s="5">
-        <v>46198.684137696764</v>
+        <v>46198.51747103009</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3866,13 +3866,13 @@
         <v>121</v>
       </c>
       <c r="B31" s="9">
-        <v>46162.55834872685</v>
+        <v>46162.39168206019</v>
       </c>
       <c r="C31" s="9">
-        <v>46198.68430692129</v>
+        <v>46198.517640254635</v>
       </c>
       <c r="D31" s="9">
-        <v>46198.68430833334</v>
+        <v>46198.517641666665</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>122</v>
@@ -3927,13 +3927,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46162.558353518514</v>
+        <v>46162.39168685186</v>
       </c>
       <c r="C32" s="5">
-        <v>46198.68417550926</v>
+        <v>46198.51750884259</v>
       </c>
       <c r="D32" s="5">
-        <v>46198.68417709491</v>
+        <v>46198.51751042824</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3988,11 +3988,11 @@
         <v>127</v>
       </c>
       <c r="B33" s="9">
-        <v>46162.558358229166</v>
+        <v>46162.3916915625</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46203.186885787036</v>
+        <v>46203.02021912037</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -4051,11 +4051,11 @@
         <v>132</v>
       </c>
       <c r="B34" s="5">
-        <v>46162.5583628125</v>
+        <v>46162.39169614583</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46191.16929601852</v>
+        <v>46191.00262935185</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -4110,11 +4110,11 @@
         <v>135</v>
       </c>
       <c r="B35" s="9">
-        <v>46162.55841275463</v>
+        <v>46162.39174608796</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46202.16929391204</v>
+        <v>46202.00262724537</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>136</v>
@@ -4169,11 +4169,11 @@
         <v>138</v>
       </c>
       <c r="B36" s="5">
-        <v>46162.558418622684</v>
+        <v>46162.39175195602</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46203.186885821764</v>
+        <v>46203.02021915509</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>139</v>
@@ -4232,11 +4232,11 @@
         <v>141</v>
       </c>
       <c r="B37" s="9">
-        <v>46162.558422118054</v>
+        <v>46162.39175545139</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46191.169293900464</v>
+        <v>46191.0026272338</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>84</v>
@@ -4285,11 +4285,11 @@
         <v>143</v>
       </c>
       <c r="B38" s="5">
-        <v>46162.558426400465</v>
+        <v>46162.3917597338</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46171.17362893518</v>
+        <v>46171.00696226852</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>144</v>
@@ -4338,11 +4338,11 @@
         <v>146</v>
       </c>
       <c r="B39" s="9">
-        <v>46162.55843366898</v>
+        <v>46162.391767002315</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.862598437496</v>
+        <v>46169.69593177083</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>147</v>
@@ -4401,11 +4401,11 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46162.558437569445</v>
+        <v>46162.391770902774</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46198.16910141204</v>
+        <v>46198.00243474537</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>90</v>
@@ -4454,11 +4454,11 @@
         <v>153</v>
       </c>
       <c r="B41" s="9">
-        <v>46162.55844153935</v>
+        <v>46162.39177487268</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.86272391204</v>
+        <v>46169.69605724537</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>154</v>
@@ -4507,11 +4507,11 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46162.55844576389</v>
+        <v>46162.39177909722</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.862742349535</v>
+        <v>46169.69607568287</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -4560,11 +4560,11 @@
         <v>160</v>
       </c>
       <c r="B43" s="9">
-        <v>46162.55844833334</v>
+        <v>46162.391781666665</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46203.186886435185</v>
+        <v>46203.020219768514</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>161</v>
@@ -4623,11 +4623,11 @@
         <v>163</v>
       </c>
       <c r="B44" s="5">
-        <v>46162.55845114583</v>
+        <v>46162.391784479165</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46191.169297465276</v>
+        <v>46191.00263079861</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>87</v>
@@ -4676,11 +4676,11 @@
         <v>165</v>
       </c>
       <c r="B45" s="9">
-        <v>46162.55845520833</v>
+        <v>46162.39178854167</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46202.16929168982</v>
+        <v>46202.002625023146</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>166</v>
@@ -4729,11 +4729,11 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46162.55817767361</v>
+        <v>46162.39151100694</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46198.79333590278</v>
+        <v>46198.62666923611</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4778,13 +4778,13 @@
         <v>171</v>
       </c>
       <c r="B47" s="9">
-        <v>46162.55845957176</v>
+        <v>46162.391792905095</v>
       </c>
       <c r="C47" s="9">
-        <v>46197.674961006946</v>
+        <v>46197.50829434028</v>
       </c>
       <c r="D47" s="9">
-        <v>46197.67690475694</v>
+        <v>46197.51023809028</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>172</v>
@@ -4843,13 +4843,13 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46162.55846439815</v>
+        <v>46162.391797731485</v>
       </c>
       <c r="C48" s="5">
-        <v>46198.79331645834</v>
+        <v>46198.626649791666</v>
       </c>
       <c r="D48" s="5">
-        <v>46198.79333422454</v>
+        <v>46198.626667557866</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4908,13 +4908,13 @@
         <v>180</v>
       </c>
       <c r="B49" s="9">
-        <v>46162.55847024306</v>
+        <v>46162.39180357639</v>
       </c>
       <c r="C49" s="9">
-        <v>46198.79336401621</v>
+        <v>46198.62669734954</v>
       </c>
       <c r="D49" s="9">
-        <v>46198.793379675924</v>
+        <v>46198.62671300926</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>80</v>
@@ -4971,11 +4971,11 @@
         <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46162.55848571759</v>
+        <v>46162.39181905093</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46162.671697337966</v>
+        <v>46162.505030671295</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -5034,11 +5034,11 @@
         <v>189</v>
       </c>
       <c r="B51" s="9">
-        <v>46162.5584890162</v>
+        <v>46162.39182234954</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46191.68638508102</v>
+        <v>46191.51971841435</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>190</v>
@@ -5085,11 +5085,11 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46162.558492951386</v>
+        <v>46162.39182628472</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46191.68638201389</v>
+        <v>46191.519715347225</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>190</v>
@@ -5136,11 +5136,11 @@
         <v>193</v>
       </c>
       <c r="B53" s="9">
-        <v>46162.55849660879</v>
+        <v>46162.391829942135</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46191.68637913195</v>
+        <v>46191.51971246528</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>190</v>
@@ -5187,11 +5187,11 @@
         <v>194</v>
       </c>
       <c r="B54" s="5">
-        <v>46162.55849916667</v>
+        <v>46162.3918325</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46191.68637614584</v>
+        <v>46191.519709479166</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -5238,11 +5238,11 @@
         <v>195</v>
       </c>
       <c r="B55" s="9">
-        <v>46162.55850175926</v>
+        <v>46162.391835092596</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46191.6863727662</v>
+        <v>46191.51970609954</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>196</v>
@@ -5289,11 +5289,11 @@
         <v>197</v>
       </c>
       <c r="B56" s="5">
-        <v>46162.56211614583</v>
+        <v>46162.39544947917</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46191.686369641204</v>
+        <v>46191.51970297453</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>196</v>
@@ -5340,11 +5340,11 @@
         <v>198</v>
       </c>
       <c r="B57" s="9">
-        <v>46162.56212396991</v>
+        <v>46162.39545730324</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46191.68636637731</v>
+        <v>46191.51969971065</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>196</v>
@@ -5391,11 +5391,11 @@
         <v>199</v>
       </c>
       <c r="B58" s="5">
-        <v>46162.56213497685</v>
+        <v>46162.395468310184</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46191.686363761575</v>
+        <v>46191.519697094904</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>196</v>
@@ -5442,11 +5442,11 @@
         <v>200</v>
       </c>
       <c r="B59" s="9">
-        <v>46162.562155057865</v>
+        <v>46162.39548839121</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46191.6863608912</v>
+        <v>46191.51969422454</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>196</v>
@@ -5493,11 +5493,11 @@
         <v>201</v>
       </c>
       <c r="B60" s="5">
-        <v>46162.562163055554</v>
+        <v>46162.39549638889</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46191.68635278935</v>
+        <v>46191.51968612269</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>196</v>
@@ -5544,11 +5544,11 @@
         <v>202</v>
       </c>
       <c r="B61" s="9">
-        <v>46162.56217104167</v>
+        <v>46162.395504375</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46191.68635209491</v>
+        <v>46191.51968542824</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>196</v>
@@ -5595,11 +5595,11 @@
         <v>203</v>
       </c>
       <c r="B62" s="5">
-        <v>46162.562178935186</v>
+        <v>46162.395512268515</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46191.686351412034</v>
+        <v>46191.51968474537</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>196</v>
@@ -5646,11 +5646,11 @@
         <v>204</v>
       </c>
       <c r="B63" s="9">
-        <v>46162.55850443287</v>
+        <v>46162.391837766205</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46162.60484554398</v>
+        <v>46162.43817887732</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>205</v>
@@ -5693,11 +5693,11 @@
         <v>207</v>
       </c>
       <c r="B64" s="5">
-        <v>46162.558507546295</v>
+        <v>46162.39184087963</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46204.167069814815</v>
+        <v>46204.00040314815</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>208</v>
@@ -5756,11 +5756,11 @@
         <v>212</v>
       </c>
       <c r="B65" s="9">
-        <v>46162.5585121412</v>
+        <v>46162.391845474536</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46204.16969789352</v>
+        <v>46205.00828016204</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>213</v>
@@ -5804,8 +5804,8 @@
       <c r="R65" s="9">
         <v>46204</v>
       </c>
-      <c r="S65" s="12" t="s">
-        <v>216</v>
+      <c r="S65" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T65" s="10">
         <v>0</v>
@@ -5816,17 +5816,17 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B66" s="5">
-        <v>46162.558518645834</v>
+        <v>46162.39185197916</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46204.16707040509</v>
+        <v>46204.00040373842</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5859,7 +5859,7 @@
         <v>144</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q66" s="5">
         <v>46203</v>
@@ -5879,17 +5879,17 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B67" s="9">
-        <v>46162.55852324074</v>
+        <v>46162.391856574075</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46204.1696995949</v>
+        <v>46205.00828008102</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5919,10 +5919,10 @@
         <v>205</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q67" s="9">
         <v>46204</v>
@@ -5930,8 +5930,8 @@
       <c r="R67" s="9">
         <v>46204</v>
       </c>
-      <c r="S67" s="12" t="s">
-        <v>216</v>
+      <c r="S67" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T67" s="10">
         <v>0</v>
@@ -5942,17 +5942,17 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B68" s="5">
-        <v>46162.5585274537</v>
+        <v>46162.39186078704</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46204.1670715162</v>
+        <v>46204.00040484953</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5985,7 +5985,7 @@
         <v>166</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q68" s="5">
         <v>46203</v>
@@ -6005,17 +6005,17 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B69" s="9">
-        <v>46162.558531400464</v>
+        <v>46162.3918647338</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46204.169700983795</v>
+        <v>46205.00828006944</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -6045,10 +6045,10 @@
         <v>205</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q69" s="9">
         <v>46204</v>
@@ -6056,8 +6056,8 @@
       <c r="R69" s="9">
         <v>46204</v>
       </c>
-      <c r="S69" s="12" t="s">
-        <v>216</v>
+      <c r="S69" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T69" s="10">
         <v>0</v>
@@ -6068,17 +6068,17 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B70" s="5">
-        <v>46162.55853556713</v>
+        <v>46162.391868900464</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46162.61139740741</v>
+        <v>46162.44473074074</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -6102,7 +6102,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -6115,26 +6115,26 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B71" s="9">
-        <v>46162.558538067125</v>
+        <v>46162.39187140046</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46202.191681435186</v>
+        <v>46202.025014768515</v>
       </c>
       <c r="E71" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="F71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="F71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="10" t="s">
+      <c r="H71" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I71" s="9">
         <v>46205</v>
@@ -6152,13 +6152,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q71" s="9">
         <v>46205</v>
@@ -6167,7 +6167,7 @@
         <v>46209</v>
       </c>
       <c r="S71" s="12" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="T71" s="10">
         <v>0</v>
@@ -6181,11 +6181,11 @@
         <v>236</v>
       </c>
       <c r="B72" s="5">
-        <v>46162.558542557876</v>
+        <v>46162.391875891204</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46162.672237060186</v>
+        <v>46162.50557039352</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>190</v>
@@ -6194,10 +6194,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I72" s="5">
         <v>46205</v>
@@ -6215,7 +6215,7 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>237</v>
@@ -6234,11 +6234,11 @@
         <v>239</v>
       </c>
       <c r="B73" s="9">
-        <v>46162.558548402776</v>
+        <v>46162.39188173611</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46162.67223377315</v>
+        <v>46162.50556710648</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>190</v>
@@ -6247,10 +6247,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I73" s="9">
         <v>46205</v>
@@ -6268,7 +6268,7 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O73" s="10" t="s">
         <v>240</v>
@@ -6287,11 +6287,11 @@
         <v>242</v>
       </c>
       <c r="B74" s="5">
-        <v>46162.55855412037</v>
+        <v>46162.391887453705</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46162.67223053241</v>
+        <v>46162.505563865736</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>190</v>
@@ -6300,10 +6300,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I74" s="5">
         <v>46205</v>
@@ -6321,7 +6321,7 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>240</v>
@@ -6340,11 +6340,11 @@
         <v>243</v>
       </c>
       <c r="B75" s="9">
-        <v>46162.558560000005</v>
+        <v>46162.39189333333</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46162.67222738426</v>
+        <v>46162.50556071759</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>190</v>
@@ -6353,10 +6353,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I75" s="9">
         <v>46205</v>
@@ -6374,7 +6374,7 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O75" s="10" t="s">
         <v>244</v>
@@ -6393,11 +6393,11 @@
         <v>245</v>
       </c>
       <c r="B76" s="5">
-        <v>46162.558565671294</v>
+        <v>46162.39189900463</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46162.67222361111</v>
+        <v>46162.505556944445</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>196</v>
@@ -6406,10 +6406,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I76" s="5">
         <v>46205</v>
@@ -6427,7 +6427,7 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>244</v>
@@ -6446,11 +6446,11 @@
         <v>247</v>
       </c>
       <c r="B77" s="9">
-        <v>46162.56018778935</v>
+        <v>46162.393521122685</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46162.672220196764</v>
+        <v>46162.50555353009</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>196</v>
@@ -6459,10 +6459,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H77" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I77" s="9">
         <v>46205</v>
@@ -6480,7 +6480,7 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O77" s="10" t="s">
         <v>248</v>
@@ -6499,11 +6499,11 @@
         <v>249</v>
       </c>
       <c r="B78" s="5">
-        <v>46162.560207789356</v>
+        <v>46162.393541122685</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46162.67221694444</v>
+        <v>46162.50555027778</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>196</v>
@@ -6512,10 +6512,10 @@
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I78" s="5">
         <v>46205</v>
@@ -6533,7 +6533,7 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>237</v>
@@ -6552,11 +6552,11 @@
         <v>250</v>
       </c>
       <c r="B79" s="9">
-        <v>46162.5602175463</v>
+        <v>46162.39355087963</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46162.67221386574</v>
+        <v>46162.50554719908</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>196</v>
@@ -6565,10 +6565,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I79" s="9">
         <v>46205</v>
@@ -6586,7 +6586,7 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>244</v>
@@ -6605,11 +6605,11 @@
         <v>251</v>
       </c>
       <c r="B80" s="5">
-        <v>46162.56022641204</v>
+        <v>46162.39355974537</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46162.67221096065</v>
+        <v>46162.50554429398</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>196</v>
@@ -6618,10 +6618,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I80" s="5">
         <v>46205</v>
@@ -6639,7 +6639,7 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>244</v>
@@ -6658,11 +6658,11 @@
         <v>252</v>
       </c>
       <c r="B81" s="9">
-        <v>46162.56023459491</v>
+        <v>46162.393567928244</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46162.67220178241</v>
+        <v>46162.50553511574</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>196</v>
@@ -6671,10 +6671,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I81" s="9">
         <v>46205</v>
@@ -6692,7 +6692,7 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>244</v>
@@ -6711,11 +6711,11 @@
         <v>253</v>
       </c>
       <c r="B82" s="5">
-        <v>46162.56024284722</v>
+        <v>46162.393576180555</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46162.67220103009</v>
+        <v>46162.50553436343</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>196</v>
@@ -6724,10 +6724,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I82" s="5">
         <v>46205</v>
@@ -6745,7 +6745,7 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>248</v>
@@ -6764,11 +6764,11 @@
         <v>254</v>
       </c>
       <c r="B83" s="9">
-        <v>46162.560250625</v>
+        <v>46162.39358395833</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46162.6722002662</v>
+        <v>46162.50553359954</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>196</v>
@@ -6777,10 +6777,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I83" s="9">
         <v>46205</v>
@@ -6798,7 +6798,7 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O83" s="10" t="s">
         <v>240</v>
@@ -6817,11 +6817,11 @@
         <v>255</v>
       </c>
       <c r="B84" s="5">
-        <v>46162.55862063657</v>
+        <v>46162.39195396991</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46162.67249278935</v>
+        <v>46162.50582612268</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>256</v>
@@ -6830,10 +6830,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I84" s="5">
         <v>46210</v>
@@ -6851,13 +6851,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>257</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q84" s="5">
         <v>46210</v>
@@ -6880,11 +6880,11 @@
         <v>258</v>
       </c>
       <c r="B85" s="9">
-        <v>46162.558626620375</v>
+        <v>46162.391959953704</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46198.79338525463</v>
+        <v>46198.62671858796</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>190</v>
@@ -6893,10 +6893,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H85" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I85" s="9">
         <v>46210</v>
@@ -6933,11 +6933,11 @@
         <v>261</v>
       </c>
       <c r="B86" s="5">
-        <v>46162.55863280092</v>
+        <v>46162.39196613426</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46198.79338199074</v>
+        <v>46198.62671532408</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>190</v>
@@ -6946,10 +6946,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I86" s="5">
         <v>46210</v>
@@ -6986,11 +6986,11 @@
         <v>262</v>
       </c>
       <c r="B87" s="9">
-        <v>46162.55863850695</v>
+        <v>46162.391971840276</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46198.79338243055</v>
+        <v>46198.626715763894</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>190</v>
@@ -6999,10 +6999,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H87" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I87" s="9">
         <v>46210</v>
@@ -7039,11 +7039,11 @@
         <v>264</v>
       </c>
       <c r="B88" s="5">
-        <v>46162.558644247685</v>
+        <v>46162.39197758102</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46198.79338296296</v>
+        <v>46198.6267162963</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>190</v>
@@ -7052,10 +7052,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I88" s="5">
         <v>46210</v>
@@ -7092,11 +7092,11 @@
         <v>265</v>
       </c>
       <c r="B89" s="9">
-        <v>46162.55864990741</v>
+        <v>46162.39198324074</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46162.67239402777</v>
+        <v>46162.50572736112</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>196</v>
@@ -7105,10 +7105,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I89" s="9">
         <v>46210</v>
@@ -7145,11 +7145,11 @@
         <v>267</v>
       </c>
       <c r="B90" s="5">
-        <v>46162.56148016204</v>
+        <v>46162.39481349537</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46162.672391064814</v>
+        <v>46162.50572439814</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>196</v>
@@ -7158,10 +7158,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I90" s="5">
         <v>46210</v>
@@ -7198,11 +7198,11 @@
         <v>268</v>
       </c>
       <c r="B91" s="9">
-        <v>46162.561489201384</v>
+        <v>46162.39482253473</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46162.672387743056</v>
+        <v>46162.50572107639</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>196</v>
@@ -7211,10 +7211,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H91" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I91" s="9">
         <v>46210</v>
@@ -7251,11 +7251,11 @@
         <v>269</v>
       </c>
       <c r="B92" s="5">
-        <v>46162.56149930556</v>
+        <v>46162.39483263889</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46162.67238480324</v>
+        <v>46162.50571813657</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>196</v>
@@ -7264,10 +7264,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I92" s="5">
         <v>46210</v>
@@ -7304,11 +7304,11 @@
         <v>270</v>
       </c>
       <c r="B93" s="9">
-        <v>46162.561507199076</v>
+        <v>46162.394840532404</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46162.67238212963</v>
+        <v>46162.50571546296</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>196</v>
@@ -7317,10 +7317,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H93" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I93" s="9">
         <v>46210</v>
@@ -7357,11 +7357,11 @@
         <v>271</v>
       </c>
       <c r="B94" s="5">
-        <v>46162.56151613426</v>
+        <v>46162.39484946759</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46162.67237393519</v>
+        <v>46162.505707268516</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>196</v>
@@ -7370,10 +7370,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I94" s="5">
         <v>46210</v>
@@ -7410,11 +7410,11 @@
         <v>272</v>
       </c>
       <c r="B95" s="9">
-        <v>46162.56152413195</v>
+        <v>46162.394857465275</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46162.67237322917</v>
+        <v>46162.5057065625</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>196</v>
@@ -7423,10 +7423,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H95" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I95" s="9">
         <v>46210</v>
@@ -7463,11 +7463,11 @@
         <v>273</v>
       </c>
       <c r="B96" s="5">
-        <v>46162.56153119213</v>
+        <v>46162.394864525464</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46162.67237256945</v>
+        <v>46162.505705902775</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>196</v>
@@ -7476,10 +7476,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I96" s="5">
         <v>46210</v>
@@ -7516,11 +7516,11 @@
         <v>274</v>
       </c>
       <c r="B97" s="9">
-        <v>46162.55865439815</v>
+        <v>46162.39198773148</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46162.67379204861</v>
+        <v>46162.50712538195</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>275</v>
@@ -7550,13 +7550,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O97" s="10" t="s">
         <v>276</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q97" s="9">
         <v>46217</v>
@@ -7579,11 +7579,11 @@
         <v>277</v>
       </c>
       <c r="B98" s="5">
-        <v>46162.55865909722</v>
+        <v>46162.39199243055</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46198.7933840162</v>
+        <v>46198.626717349536</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>190</v>
@@ -7632,11 +7632,11 @@
         <v>279</v>
       </c>
       <c r="B99" s="9">
-        <v>46162.55866501157</v>
+        <v>46162.39199834491</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46198.79338457176</v>
+        <v>46198.62671790509</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>190</v>
@@ -7685,11 +7685,11 @@
         <v>281</v>
       </c>
       <c r="B100" s="5">
-        <v>46162.55867084491</v>
+        <v>46162.39200417824</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46198.79337287037</v>
+        <v>46198.62670620371</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>190</v>
@@ -7738,11 +7738,11 @@
         <v>283</v>
       </c>
       <c r="B101" s="9">
-        <v>46162.558676597226</v>
+        <v>46162.392009930554</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46198.793388391205</v>
+        <v>46198.62672172453</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>190</v>
@@ -7791,11 +7791,11 @@
         <v>285</v>
       </c>
       <c r="B102" s="5">
-        <v>46162.55868239583</v>
+        <v>46162.392015729165</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46162.67376247685</v>
+        <v>46162.507095810186</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>196</v>
@@ -7844,11 +7844,11 @@
         <v>287</v>
       </c>
       <c r="B103" s="9">
-        <v>46162.56176834491</v>
+        <v>46162.39510167824</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46162.67376181713</v>
+        <v>46162.50709515046</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>196</v>
@@ -7897,11 +7897,11 @@
         <v>288</v>
       </c>
       <c r="B104" s="5">
-        <v>46162.56177670139</v>
+        <v>46162.39511003472</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46162.67376091435</v>
+        <v>46162.50709424769</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>196</v>
@@ -7950,11 +7950,11 @@
         <v>290</v>
       </c>
       <c r="B105" s="9">
-        <v>46162.56178474537</v>
+        <v>46162.395118078704</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46162.67376023148</v>
+        <v>46162.50709356481</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>196</v>
@@ -8003,11 +8003,11 @@
         <v>291</v>
       </c>
       <c r="B106" s="5">
-        <v>46162.56179298611</v>
+        <v>46162.39512631945</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46162.67375957176</v>
+        <v>46162.50709290509</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>196</v>
@@ -8056,11 +8056,11 @@
         <v>292</v>
       </c>
       <c r="B107" s="9">
-        <v>46162.5618009375</v>
+        <v>46162.39513427083</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46162.67375887731</v>
+        <v>46162.50709221065</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>196</v>
@@ -8109,11 +8109,11 @@
         <v>293</v>
       </c>
       <c r="B108" s="5">
-        <v>46162.56180909723</v>
+        <v>46162.395142430556</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46162.67375819445</v>
+        <v>46162.507091527776</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>196</v>
@@ -8162,11 +8162,11 @@
         <v>294</v>
       </c>
       <c r="B109" s="9">
-        <v>46162.56181716435</v>
+        <v>46162.39515049769</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46162.67375751157</v>
+        <v>46162.50709084491</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>196</v>
@@ -8215,11 +8215,11 @@
         <v>295</v>
       </c>
       <c r="B110" s="5">
-        <v>46162.55868650463</v>
+        <v>46162.392019837964</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46162.61466552083</v>
+        <v>46162.44799885417</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>205</v>
@@ -8262,11 +8262,11 @@
         <v>297</v>
       </c>
       <c r="B111" s="9">
-        <v>46162.55869006945</v>
+        <v>46162.392023402776</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46198.68469991898</v>
+        <v>46198.518033252316</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>298</v>
@@ -8325,11 +8325,11 @@
         <v>300</v>
       </c>
       <c r="B112" s="5">
-        <v>46162.558696921296</v>
+        <v>46162.39203025463</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46162.673898912035</v>
+        <v>46162.50723224537</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>301</v>
@@ -8388,11 +8388,11 @@
         <v>303</v>
       </c>
       <c r="B113" s="9">
-        <v>46162.55870284722</v>
+        <v>46162.39203618055</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46198.684325486116</v>
+        <v>46198.517658819444</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>304</v>
@@ -8451,11 +8451,11 @@
         <v>306</v>
       </c>
       <c r="B114" s="5">
-        <v>46162.55870962963</v>
+        <v>46162.392042962965</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46162.67389181713</v>
+        <v>46162.50722515046</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>307</v>
@@ -8514,11 +8514,11 @@
         <v>309</v>
       </c>
       <c r="B115" s="9">
-        <v>46162.55871869213</v>
+        <v>46162.39205202546</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46162.64775322917</v>
+        <v>46162.481086562504</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>310</v>
@@ -8561,11 +8561,11 @@
         <v>312</v>
       </c>
       <c r="B116" s="5">
-        <v>46162.55872223379</v>
+        <v>46162.39205556713</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46162.67400658564</v>
+        <v>46162.507339918986</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>313</v>
@@ -8624,11 +8624,11 @@
         <v>315</v>
       </c>
       <c r="B117" s="9">
-        <v>46162.55873068287</v>
+        <v>46162.3920640162</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46162.674262650464</v>
+        <v>46162.5075959838</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>190</v>
@@ -8677,11 +8677,11 @@
         <v>317</v>
       </c>
       <c r="B118" s="5">
-        <v>46162.558735011575</v>
+        <v>46162.39206834491</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46162.67425921296</v>
+        <v>46162.507592546295</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>190</v>
@@ -8730,11 +8730,11 @@
         <v>318</v>
       </c>
       <c r="B119" s="9">
-        <v>46162.55873951389</v>
+        <v>46162.39207284722</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46162.67425633102</v>
+        <v>46162.507589664354</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>190</v>
@@ -8783,11 +8783,11 @@
         <v>320</v>
       </c>
       <c r="B120" s="5">
-        <v>46162.55874386574</v>
+        <v>46162.392077199074</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46162.674253379635</v>
+        <v>46162.50758671296</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>190</v>
@@ -8836,11 +8836,11 @@
         <v>321</v>
       </c>
       <c r="B121" s="9">
-        <v>46162.55874813657</v>
+        <v>46162.39208146991</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46162.67425</v>
+        <v>46162.50758333333</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>196</v>
@@ -8889,11 +8889,11 @@
         <v>322</v>
       </c>
       <c r="B122" s="5">
-        <v>46162.56516702546</v>
+        <v>46162.398500358795</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46162.67424702546</v>
+        <v>46162.5075803588</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>196</v>
@@ -8942,11 +8942,11 @@
         <v>323</v>
       </c>
       <c r="B123" s="9">
-        <v>46162.56517383102</v>
+        <v>46162.398507164355</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46162.67424429399</v>
+        <v>46162.507577627315</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>196</v>
@@ -8995,11 +8995,11 @@
         <v>324</v>
       </c>
       <c r="B124" s="5">
-        <v>46162.565181134254</v>
+        <v>46162.3985144676</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46162.674233321755</v>
+        <v>46162.50756665509</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>196</v>
@@ -9048,11 +9048,11 @@
         <v>325</v>
       </c>
       <c r="B125" s="9">
-        <v>46162.565189201385</v>
+        <v>46162.39852253472</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46162.67423263889</v>
+        <v>46162.50756597222</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>196</v>
@@ -9101,11 +9101,11 @@
         <v>326</v>
       </c>
       <c r="B126" s="5">
-        <v>46162.56519680556</v>
+        <v>46162.39853013889</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46162.674231944446</v>
+        <v>46162.507565277774</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>196</v>
@@ -9154,11 +9154,11 @@
         <v>327</v>
       </c>
       <c r="B127" s="9">
-        <v>46162.565205590276</v>
+        <v>46162.39853892361</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46162.674231261575</v>
+        <v>46162.50756459491</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>196</v>
@@ -9207,11 +9207,11 @@
         <v>328</v>
       </c>
       <c r="B128" s="5">
-        <v>46162.565212013884</v>
+        <v>46162.39854534723</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46162.67423060186</v>
+        <v>46162.507563935185</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>196</v>
@@ -9260,11 +9260,11 @@
         <v>329</v>
       </c>
       <c r="B129" s="9">
-        <v>46162.558751550925</v>
+        <v>46162.39208488426</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46162.67400341435</v>
+        <v>46162.50733674769</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>330</v>
@@ -9323,11 +9323,11 @@
         <v>331</v>
       </c>
       <c r="B130" s="5">
-        <v>46162.558756238424</v>
+        <v>46162.39208957176</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46198.79338591435</v>
+        <v>46198.62671924768</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>190</v>
@@ -9374,11 +9374,11 @@
         <v>334</v>
       </c>
       <c r="B131" s="9">
-        <v>46162.55876204861</v>
+        <v>46162.39209538195</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46198.79338641204</v>
+        <v>46198.62671974537</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>190</v>
@@ -9425,11 +9425,11 @@
         <v>336</v>
       </c>
       <c r="B132" s="5">
-        <v>46162.55876745371</v>
+        <v>46162.39210078704</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46198.79338869213</v>
+        <v>46198.62672202547</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>190</v>
@@ -9476,11 +9476,11 @@
         <v>339</v>
       </c>
       <c r="B133" s="9">
-        <v>46162.558773888886</v>
+        <v>46162.39210722222</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46198.793389004626</v>
+        <v>46198.62672233796</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>190</v>
@@ -9527,11 +9527,11 @@
         <v>340</v>
       </c>
       <c r="B134" s="5">
-        <v>46162.558827430556</v>
+        <v>46162.39216076389</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46162.67438523148</v>
+        <v>46162.50771856481</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>196</v>
@@ -9578,11 +9578,11 @@
         <v>342</v>
       </c>
       <c r="B135" s="9">
-        <v>46162.565477233795</v>
+        <v>46162.39881056713</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46198.79336980324</v>
+        <v>46198.62670313657</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>196</v>
@@ -9629,11 +9629,11 @@
         <v>344</v>
       </c>
       <c r="B136" s="5">
-        <v>46162.56548539352</v>
+        <v>46162.398818726855</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46198.79337046296</v>
+        <v>46198.6267037963</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>196</v>
@@ -9680,11 +9680,11 @@
         <v>346</v>
       </c>
       <c r="B137" s="9">
-        <v>46162.56549420139</v>
+        <v>46162.39882753472</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46198.79337111111</v>
+        <v>46198.62670444444</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>196</v>
@@ -9731,11 +9731,11 @@
         <v>347</v>
       </c>
       <c r="B138" s="5">
-        <v>46162.56549981482</v>
+        <v>46162.39883314815</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46198.79337171296</v>
+        <v>46198.62670504629</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>196</v>
@@ -9782,11 +9782,11 @@
         <v>349</v>
       </c>
       <c r="B139" s="9">
-        <v>46162.565507719904</v>
+        <v>46162.39884105324</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46198.79337225694</v>
+        <v>46198.62670559028</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>196</v>
@@ -9833,11 +9833,11 @@
         <v>350</v>
       </c>
       <c r="B140" s="5">
-        <v>46162.56551637732</v>
+        <v>46162.39884971065</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46162.6743640162</v>
+        <v>46162.50769734954</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>196</v>
@@ -9884,11 +9884,11 @@
         <v>352</v>
       </c>
       <c r="B141" s="9">
-        <v>46162.56598206019</v>
+        <v>46162.399315393515</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46162.67436230324</v>
+        <v>46162.507695636574</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>196</v>
@@ -9935,11 +9935,11 @@
         <v>353</v>
       </c>
       <c r="B142" s="5">
-        <v>46162.55883354167</v>
+        <v>46162.392166875</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46162.674000150466</v>
+        <v>46162.507333483794</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>354</v>
@@ -9998,11 +9998,11 @@
         <v>355</v>
       </c>
       <c r="B143" s="9">
-        <v>46162.55883898148</v>
+        <v>46162.392172314816</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46198.79338673611</v>
+        <v>46198.62672006944</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>190</v>
@@ -10051,11 +10051,11 @@
         <v>357</v>
       </c>
       <c r="B144" s="5">
-        <v>46162.55884618056</v>
+        <v>46162.39217951389</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46198.793387094905</v>
+        <v>46198.62672042824</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>190</v>
@@ -10104,11 +10104,11 @@
         <v>359</v>
       </c>
       <c r="B145" s="9">
-        <v>46162.55885335648</v>
+        <v>46162.392186689816</v>
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46198.79338740741</v>
+        <v>46198.626720740736</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>190</v>
@@ -10157,11 +10157,11 @@
         <v>361</v>
       </c>
       <c r="B146" s="5">
-        <v>46162.558860624995</v>
+        <v>46162.39219395834</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46198.793387858794</v>
+        <v>46198.62672119213</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>190</v>
@@ -10210,11 +10210,11 @@
         <v>363</v>
       </c>
       <c r="B147" s="9">
-        <v>46162.558867395834</v>
+        <v>46162.39220072917</v>
       </c>
       <c r="C147" s="10"/>
       <c r="D147" s="9">
-        <v>46162.674524965274</v>
+        <v>46162.50785829861</v>
       </c>
       <c r="E147" s="10" t="s">
         <v>196</v>
@@ -10263,11 +10263,11 @@
         <v>365</v>
       </c>
       <c r="B148" s="5">
-        <v>46162.566146365745</v>
+        <v>46162.399479699074</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46162.674521354165</v>
+        <v>46162.5078546875</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>196</v>
@@ -10316,11 +10316,11 @@
         <v>367</v>
       </c>
       <c r="B149" s="9">
-        <v>46162.566153101856</v>
+        <v>46162.399486435184</v>
       </c>
       <c r="C149" s="10"/>
       <c r="D149" s="9">
-        <v>46162.67451787037</v>
+        <v>46162.5078512037</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>196</v>
@@ -10369,11 +10369,11 @@
         <v>368</v>
       </c>
       <c r="B150" s="5">
-        <v>46162.56617111111</v>
+        <v>46162.399504444445</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46162.67451502314</v>
+        <v>46162.50784835649</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>196</v>
@@ -10422,11 +10422,11 @@
         <v>369</v>
       </c>
       <c r="B151" s="9">
-        <v>46162.56618105324</v>
+        <v>46162.399514386576</v>
       </c>
       <c r="C151" s="10"/>
       <c r="D151" s="9">
-        <v>46162.67451243056</v>
+        <v>46162.50784576389</v>
       </c>
       <c r="E151" s="10" t="s">
         <v>348</v>
@@ -10475,11 +10475,11 @@
         <v>370</v>
       </c>
       <c r="B152" s="5">
-        <v>46162.56618987268</v>
+        <v>46162.39952320602</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46162.67450335648</v>
+        <v>46162.507836689816</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>196</v>
@@ -10528,11 +10528,11 @@
         <v>371</v>
       </c>
       <c r="B153" s="9">
-        <v>46162.56620271991</v>
+        <v>46162.39953605324</v>
       </c>
       <c r="C153" s="10"/>
       <c r="D153" s="9">
-        <v>46162.67450263889</v>
+        <v>46162.507835972225</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>196</v>
@@ -10581,11 +10581,11 @@
         <v>372</v>
       </c>
       <c r="B154" s="5">
-        <v>46162.56620673611</v>
+        <v>46162.39954006944</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46162.67450188658</v>
+        <v>46162.507835219905</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>196</v>
@@ -10634,11 +10634,11 @@
         <v>373</v>
       </c>
       <c r="B155" s="9">
-        <v>46162.558871574074</v>
+        <v>46162.3922049074</v>
       </c>
       <c r="C155" s="10"/>
       <c r="D155" s="9">
-        <v>46162.673997199076</v>
+        <v>46162.507330532404</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>374</v>
@@ -10697,11 +10697,11 @@
         <v>376</v>
       </c>
       <c r="B156" s="5">
-        <v>46162.55887622685</v>
+        <v>46162.39220956019</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46198.7933762037</v>
+        <v>46198.62670953704</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>190</v>
@@ -10750,11 +10750,11 @@
         <v>379</v>
       </c>
       <c r="B157" s="9">
-        <v>46162.55888300926</v>
+        <v>46162.39221634259</v>
       </c>
       <c r="C157" s="10"/>
       <c r="D157" s="9">
-        <v>46198.79337655092</v>
+        <v>46198.62670988426</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>190</v>
@@ -10803,11 +10803,11 @@
         <v>380</v>
       </c>
       <c r="B158" s="5">
-        <v>46162.558892581015</v>
+        <v>46162.39222591435</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46198.793389375</v>
+        <v>46198.62672270833</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>190</v>
@@ -10856,11 +10856,11 @@
         <v>382</v>
       </c>
       <c r="B159" s="9">
-        <v>46162.55889858796</v>
+        <v>46162.3922319213</v>
       </c>
       <c r="C159" s="10"/>
       <c r="D159" s="9">
-        <v>46198.79338491899</v>
+        <v>46198.626718252315</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>190</v>
@@ -10909,11 +10909,11 @@
         <v>384</v>
       </c>
       <c r="B160" s="5">
-        <v>46162.558904618054</v>
+        <v>46162.39223795139</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46162.674682349534</v>
+        <v>46162.50801568287</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>196</v>
@@ -10962,11 +10962,11 @@
         <v>386</v>
       </c>
       <c r="B161" s="9">
-        <v>46162.566379375</v>
+        <v>46162.399712708335</v>
       </c>
       <c r="C161" s="10"/>
       <c r="D161" s="9">
-        <v>46162.674678888885</v>
+        <v>46162.50801222222</v>
       </c>
       <c r="E161" s="10" t="s">
         <v>196</v>
@@ -11015,11 +11015,11 @@
         <v>389</v>
       </c>
       <c r="B162" s="5">
-        <v>46162.56638695602</v>
+        <v>46162.39972028935</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46162.67467586805</v>
+        <v>46162.50800920139</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>196</v>
@@ -11068,11 +11068,11 @@
         <v>390</v>
       </c>
       <c r="B163" s="9">
-        <v>46162.56639532407</v>
+        <v>46162.39972865741</v>
       </c>
       <c r="C163" s="10"/>
       <c r="D163" s="9">
-        <v>46162.67467314815</v>
+        <v>46162.50800648148</v>
       </c>
       <c r="E163" s="10" t="s">
         <v>196</v>
@@ -11121,11 +11121,11 @@
         <v>392</v>
       </c>
       <c r="B164" s="5">
-        <v>46162.56640418981</v>
+        <v>46162.39973752315</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46162.67467030093</v>
+        <v>46162.508003634255</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>196</v>
@@ -11174,11 +11174,11 @@
         <v>395</v>
       </c>
       <c r="B165" s="9">
-        <v>46162.56641240741</v>
+        <v>46162.39974574074</v>
       </c>
       <c r="C165" s="10"/>
       <c r="D165" s="9">
-        <v>46162.67466239583</v>
+        <v>46162.50799572917</v>
       </c>
       <c r="E165" s="10" t="s">
         <v>196</v>
@@ -11227,11 +11227,11 @@
         <v>396</v>
       </c>
       <c r="B166" s="5">
-        <v>46162.56642033564</v>
+        <v>46162.399753668986</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46162.674661655095</v>
+        <v>46162.507994988424</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>196</v>
@@ -11280,11 +11280,11 @@
         <v>397</v>
       </c>
       <c r="B167" s="9">
-        <v>46162.566427708334</v>
+        <v>46162.39976104167</v>
       </c>
       <c r="C167" s="10"/>
       <c r="D167" s="9">
-        <v>46162.67466097222</v>
+        <v>46162.50799430556</v>
       </c>
       <c r="E167" s="10" t="s">
         <v>196</v>
@@ -11333,11 +11333,11 @@
         <v>398</v>
       </c>
       <c r="B168" s="5">
-        <v>46162.558908946754</v>
+        <v>46162.3922422801</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46162.67399393518</v>
+        <v>46162.50732726852</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>399</v>
@@ -11396,11 +11396,11 @@
         <v>400</v>
       </c>
       <c r="B169" s="9">
-        <v>46162.55891369213</v>
+        <v>46162.39224702546</v>
       </c>
       <c r="C169" s="10"/>
       <c r="D169" s="9">
-        <v>46162.67483585648</v>
+        <v>46162.508169189816</v>
       </c>
       <c r="E169" s="10" t="s">
         <v>190</v>
@@ -11447,11 +11447,11 @@
         <v>402</v>
       </c>
       <c r="B170" s="5">
-        <v>46162.55891930556</v>
+        <v>46162.39225263889</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46162.674832847224</v>
+        <v>46162.50816618056</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>190</v>
@@ -11498,11 +11498,11 @@
         <v>403</v>
       </c>
       <c r="B171" s="9">
-        <v>46162.558924930556</v>
+        <v>46162.39225826389</v>
       </c>
       <c r="C171" s="10"/>
       <c r="D171" s="9">
-        <v>46162.67482962963</v>
+        <v>46162.508162962964</v>
       </c>
       <c r="E171" s="10" t="s">
         <v>190</v>
@@ -11549,11 +11549,11 @@
         <v>405</v>
       </c>
       <c r="B172" s="5">
-        <v>46162.55893104167</v>
+        <v>46162.392264375</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46162.67482693287</v>
+        <v>46162.5081602662</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>190</v>
@@ -11600,11 +11600,11 @@
         <v>406</v>
       </c>
       <c r="B173" s="9">
-        <v>46162.55893646991</v>
+        <v>46162.39226980324</v>
       </c>
       <c r="C173" s="10"/>
       <c r="D173" s="9">
-        <v>46162.67482414352</v>
+        <v>46162.508157476856</v>
       </c>
       <c r="E173" s="10" t="s">
         <v>196</v>
@@ -11651,11 +11651,11 @@
         <v>408</v>
       </c>
       <c r="B174" s="5">
-        <v>46162.567320891205</v>
+        <v>46162.40065422453</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46162.67482128472</v>
+        <v>46162.50815461806</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>196</v>
@@ -11702,11 +11702,11 @@
         <v>409</v>
       </c>
       <c r="B175" s="9">
-        <v>46162.567330034726</v>
+        <v>46162.400663368055</v>
       </c>
       <c r="C175" s="10"/>
       <c r="D175" s="9">
-        <v>46162.67481818287</v>
+        <v>46162.5081515162</v>
       </c>
       <c r="E175" s="10" t="s">
         <v>196</v>
@@ -11753,11 +11753,11 @@
         <v>410</v>
       </c>
       <c r="B176" s="5">
-        <v>46162.567337685185</v>
+        <v>46162.40067101852</v>
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46162.674815543985</v>
+        <v>46162.508148877314</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>196</v>
@@ -11804,11 +11804,11 @@
         <v>411</v>
       </c>
       <c r="B177" s="9">
-        <v>46162.567344166666</v>
+        <v>46162.4006775</v>
       </c>
       <c r="C177" s="10"/>
       <c r="D177" s="9">
-        <v>46162.674812743055</v>
+        <v>46162.50814607639</v>
       </c>
       <c r="E177" s="10" t="s">
         <v>196</v>
@@ -11855,11 +11855,11 @@
         <v>412</v>
       </c>
       <c r="B178" s="5">
-        <v>46162.56735135417</v>
+        <v>46162.4006846875</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46162.67480497685</v>
+        <v>46162.508138310186</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>196</v>
@@ -11906,11 +11906,11 @@
         <v>413</v>
       </c>
       <c r="B179" s="9">
-        <v>46162.5673590625</v>
+        <v>46162.40069239584</v>
       </c>
       <c r="C179" s="10"/>
       <c r="D179" s="9">
-        <v>46162.674804317125</v>
+        <v>46162.50813765047</v>
       </c>
       <c r="E179" s="10" t="s">
         <v>196</v>
@@ -11957,11 +11957,11 @@
         <v>414</v>
       </c>
       <c r="B180" s="5">
-        <v>46162.567366284726</v>
+        <v>46162.400699618054</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46162.674803587965</v>
+        <v>46162.5081369213</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>196</v>
@@ -12008,11 +12008,11 @@
         <v>415</v>
       </c>
       <c r="B181" s="9">
-        <v>46162.558941678246</v>
+        <v>46162.392275011574</v>
       </c>
       <c r="C181" s="10"/>
       <c r="D181" s="9">
-        <v>46162.673987789356</v>
+        <v>46162.507321122685</v>
       </c>
       <c r="E181" s="10" t="s">
         <v>416</v>
@@ -12071,11 +12071,11 @@
         <v>418</v>
       </c>
       <c r="B182" s="5">
-        <v>46162.5589471875</v>
+        <v>46162.392280520835</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46162.675084849536</v>
+        <v>46162.50841818287</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>190</v>
@@ -12122,11 +12122,11 @@
         <v>420</v>
       </c>
       <c r="B183" s="9">
-        <v>46162.55895184028</v>
+        <v>46162.39228517361</v>
       </c>
       <c r="C183" s="10"/>
       <c r="D183" s="9">
-        <v>46162.67508193287</v>
+        <v>46162.5084152662</v>
       </c>
       <c r="E183" s="10" t="s">
         <v>190</v>
@@ -12173,11 +12173,11 @@
         <v>421</v>
       </c>
       <c r="B184" s="5">
-        <v>46162.55895655093</v>
+        <v>46162.39228988426</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46162.67507869213</v>
+        <v>46162.50841202546</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>190</v>
@@ -12224,11 +12224,11 @@
         <v>423</v>
       </c>
       <c r="B185" s="9">
-        <v>46162.5589959375</v>
+        <v>46162.392329270835</v>
       </c>
       <c r="C185" s="10"/>
       <c r="D185" s="9">
-        <v>46162.67507611111</v>
+        <v>46162.50840944445</v>
       </c>
       <c r="E185" s="10" t="s">
         <v>190</v>
@@ -12275,11 +12275,11 @@
         <v>424</v>
       </c>
       <c r="B186" s="5">
-        <v>46162.55900136574</v>
+        <v>46162.39233469908</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46162.6750730787</v>
+        <v>46162.50840641204</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>196</v>
@@ -12326,11 +12326,11 @@
         <v>426</v>
       </c>
       <c r="B187" s="9">
-        <v>46162.56759152778</v>
+        <v>46162.40092486111</v>
       </c>
       <c r="C187" s="10"/>
       <c r="D187" s="9">
-        <v>46162.675070150464</v>
+        <v>46162.50840348379</v>
       </c>
       <c r="E187" s="10" t="s">
         <v>196</v>
@@ -12377,11 +12377,11 @@
         <v>427</v>
       </c>
       <c r="B188" s="5">
-        <v>46162.56759846065</v>
+        <v>46162.40093179398</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46162.6750674537</v>
+        <v>46162.50840078703</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>196</v>
@@ -12428,11 +12428,11 @@
         <v>428</v>
       </c>
       <c r="B189" s="9">
-        <v>46162.56760671297</v>
+        <v>46162.4009400463</v>
       </c>
       <c r="C189" s="10"/>
       <c r="D189" s="9">
-        <v>46162.67506488426</v>
+        <v>46162.50839821759</v>
       </c>
       <c r="E189" s="10" t="s">
         <v>196</v>
@@ -12479,11 +12479,11 @@
         <v>429</v>
       </c>
       <c r="B190" s="5">
-        <v>46162.56761416666</v>
+        <v>46162.4009475</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46162.67506164352</v>
+        <v>46162.50839497685</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>196</v>
@@ -12530,11 +12530,11 @@
         <v>430</v>
       </c>
       <c r="B191" s="9">
-        <v>46162.56762221065</v>
+        <v>46162.400955543984</v>
       </c>
       <c r="C191" s="10"/>
       <c r="D191" s="9">
-        <v>46162.67505446759</v>
+        <v>46162.508387800925</v>
       </c>
       <c r="E191" s="10" t="s">
         <v>196</v>
@@ -12581,11 +12581,11 @@
         <v>431</v>
       </c>
       <c r="B192" s="5">
-        <v>46162.56762855324</v>
+        <v>46162.400961886575</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46162.675053750005</v>
+        <v>46162.50838708333</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>196</v>
@@ -12632,11 +12632,11 @@
         <v>432</v>
       </c>
       <c r="B193" s="9">
-        <v>46162.56763415509</v>
+        <v>46162.40096748843</v>
       </c>
       <c r="C193" s="10"/>
       <c r="D193" s="9">
-        <v>46162.67505302084</v>
+        <v>46162.508386354166</v>
       </c>
       <c r="E193" s="10" t="s">
         <v>196</v>
@@ -12683,11 +12683,11 @@
         <v>433</v>
       </c>
       <c r="B194" s="5">
-        <v>46162.55900565972</v>
+        <v>46162.39233899306</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46162.663939108796</v>
+        <v>46162.49727244213</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>434</v>
@@ -12730,11 +12730,11 @@
         <v>436</v>
       </c>
       <c r="B195" s="9">
-        <v>46162.55900940972</v>
+        <v>46162.392342743056</v>
       </c>
       <c r="C195" s="10"/>
       <c r="D195" s="9">
-        <v>46162.67540229167</v>
+        <v>46162.508735625</v>
       </c>
       <c r="E195" s="10" t="s">
         <v>437</v>
@@ -12793,11 +12793,11 @@
         <v>441</v>
       </c>
       <c r="B196" s="5">
-        <v>46162.559015023144</v>
+        <v>46162.39234835649</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46162.67538505787</v>
+        <v>46162.508718391204</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>190</v>
@@ -12844,11 +12844,11 @@
         <v>443</v>
       </c>
       <c r="B197" s="9">
-        <v>46162.55901939815</v>
+        <v>46162.39235273148</v>
       </c>
       <c r="C197" s="10"/>
       <c r="D197" s="9">
-        <v>46162.675382534726</v>
+        <v>46162.508715868054</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>190</v>
@@ -12895,11 +12895,11 @@
         <v>444</v>
       </c>
       <c r="B198" s="5">
-        <v>46162.55902388888</v>
+        <v>46162.39235722223</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46162.67537990741</v>
+        <v>46162.50871324074</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>190</v>
@@ -12946,11 +12946,11 @@
         <v>445</v>
       </c>
       <c r="B199" s="9">
-        <v>46162.559028090276</v>
+        <v>46162.39236142361</v>
       </c>
       <c r="C199" s="10"/>
       <c r="D199" s="9">
-        <v>46162.67537715277</v>
+        <v>46162.508710486116</v>
       </c>
       <c r="E199" s="10" t="s">
         <v>190</v>
@@ -12997,11 +12997,11 @@
         <v>446</v>
       </c>
       <c r="B200" s="5">
-        <v>46162.559032060184</v>
+        <v>46162.39236539352</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46162.675374178245</v>
+        <v>46162.50870751157</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>196</v>
@@ -13048,11 +13048,11 @@
         <v>448</v>
       </c>
       <c r="B201" s="9">
-        <v>46162.56847083333</v>
+        <v>46162.40180416667</v>
       </c>
       <c r="C201" s="10"/>
       <c r="D201" s="9">
-        <v>46162.675371296296</v>
+        <v>46162.508704629625</v>
       </c>
       <c r="E201" s="10" t="s">
         <v>196</v>
@@ -13099,11 +13099,11 @@
         <v>449</v>
       </c>
       <c r="B202" s="5">
-        <v>46162.5684778588</v>
+        <v>46162.40181119213</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46162.675368321754</v>
+        <v>46162.5087016551</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>196</v>
@@ -13150,11 +13150,11 @@
         <v>450</v>
       </c>
       <c r="B203" s="9">
-        <v>46162.56848583333</v>
+        <v>46162.40181916667</v>
       </c>
       <c r="C203" s="10"/>
       <c r="D203" s="9">
-        <v>46162.67536565972</v>
+        <v>46162.50869899306</v>
       </c>
       <c r="E203" s="10" t="s">
         <v>196</v>
@@ -13201,11 +13201,11 @@
         <v>451</v>
       </c>
       <c r="B204" s="5">
-        <v>46162.56849315972</v>
+        <v>46162.40182649306</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46162.67536296297</v>
+        <v>46162.508696296296</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>196</v>
@@ -13252,11 +13252,11 @@
         <v>452</v>
       </c>
       <c r="B205" s="9">
-        <v>46162.568499120374</v>
+        <v>46162.4018324537</v>
       </c>
       <c r="C205" s="10"/>
       <c r="D205" s="9">
-        <v>46162.67535506944</v>
+        <v>46162.50868840278</v>
       </c>
       <c r="E205" s="10" t="s">
         <v>196</v>
@@ -13303,11 +13303,11 @@
         <v>453</v>
       </c>
       <c r="B206" s="5">
-        <v>46162.568507013886</v>
+        <v>46162.40184034722</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46162.67535439815</v>
+        <v>46162.50868773148</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>196</v>
@@ -13354,11 +13354,11 @@
         <v>454</v>
       </c>
       <c r="B207" s="9">
-        <v>46162.56851576389</v>
+        <v>46162.40184909722</v>
       </c>
       <c r="C207" s="10"/>
       <c r="D207" s="9">
-        <v>46162.67535373842</v>
+        <v>46162.508687071764</v>
       </c>
       <c r="E207" s="10" t="s">
         <v>196</v>
@@ -13405,11 +13405,11 @@
         <v>455</v>
       </c>
       <c r="B208" s="5">
-        <v>46162.559035983795</v>
+        <v>46162.39236931713</v>
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46162.675601435185</v>
+        <v>46162.50893476851</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>456</v>
@@ -13468,11 +13468,11 @@
         <v>457</v>
       </c>
       <c r="B209" s="9">
-        <v>46162.559040057866</v>
+        <v>46162.39237339121</v>
       </c>
       <c r="C209" s="10"/>
       <c r="D209" s="9">
-        <v>46162.67559398148</v>
+        <v>46162.50892731482</v>
       </c>
       <c r="E209" s="10" t="s">
         <v>190</v>
@@ -13519,11 +13519,11 @@
         <v>459</v>
       </c>
       <c r="B210" s="5">
-        <v>46162.559044305555</v>
+        <v>46162.392377638884</v>
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46162.67559118055</v>
+        <v>46162.50892451389</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>190</v>
@@ -13570,11 +13570,11 @@
         <v>460</v>
       </c>
       <c r="B211" s="9">
-        <v>46162.55904842593</v>
+        <v>46162.39238175926</v>
       </c>
       <c r="C211" s="10"/>
       <c r="D211" s="9">
-        <v>46162.675588391205</v>
+        <v>46162.50892172454</v>
       </c>
       <c r="E211" s="10" t="s">
         <v>190</v>
@@ -13621,11 +13621,11 @@
         <v>461</v>
       </c>
       <c r="B212" s="5">
-        <v>46162.55905241898</v>
+        <v>46162.39238575232</v>
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46162.67558560186</v>
+        <v>46162.508918935186</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>190</v>
@@ -13672,11 +13672,11 @@
         <v>462</v>
       </c>
       <c r="B213" s="9">
-        <v>46162.55905643519</v>
+        <v>46162.392389768516</v>
       </c>
       <c r="C213" s="10"/>
       <c r="D213" s="9">
-        <v>46162.67558284722</v>
+        <v>46162.50891618055</v>
       </c>
       <c r="E213" s="10" t="s">
         <v>196</v>
@@ -13723,11 +13723,11 @@
         <v>464</v>
       </c>
       <c r="B214" s="5">
-        <v>46162.568794328705</v>
+        <v>46162.40212766203</v>
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46162.6755797338</v>
+        <v>46162.508913067126</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>196</v>
@@ -13774,11 +13774,11 @@
         <v>465</v>
       </c>
       <c r="B215" s="9">
-        <v>46162.56880138889</v>
+        <v>46162.40213472222</v>
       </c>
       <c r="C215" s="10"/>
       <c r="D215" s="9">
-        <v>46162.675576967595</v>
+        <v>46162.50891030092</v>
       </c>
       <c r="E215" s="10" t="s">
         <v>196</v>
@@ -13825,11 +13825,11 @@
         <v>466</v>
       </c>
       <c r="B216" s="5">
-        <v>46162.56880807871</v>
+        <v>46162.402141412036</v>
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46162.67557431713</v>
+        <v>46162.50890765047</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>196</v>
@@ -13876,11 +13876,11 @@
         <v>468</v>
       </c>
       <c r="B217" s="9">
-        <v>46162.56881548611</v>
+        <v>46162.40214881944</v>
       </c>
       <c r="C217" s="10"/>
       <c r="D217" s="9">
-        <v>46162.67557162037</v>
+        <v>46162.508904953705</v>
       </c>
       <c r="E217" s="10" t="s">
         <v>196</v>
@@ -13927,11 +13927,11 @@
         <v>469</v>
       </c>
       <c r="B218" s="5">
-        <v>46162.56882248842</v>
+        <v>46162.402155821765</v>
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46162.67556375</v>
+        <v>46162.50889708333</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>196</v>
@@ -13978,11 +13978,11 @@
         <v>470</v>
       </c>
       <c r="B219" s="9">
-        <v>46162.56882971065</v>
+        <v>46162.40216304398</v>
       </c>
       <c r="C219" s="10"/>
       <c r="D219" s="9">
-        <v>46162.675563020835</v>
+        <v>46162.508896354164</v>
       </c>
       <c r="E219" s="10" t="s">
         <v>196</v>
@@ -14029,11 +14029,11 @@
         <v>471</v>
       </c>
       <c r="B220" s="5">
-        <v>46162.56883761574</v>
+        <v>46162.40217094908</v>
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46162.67556230324</v>
+        <v>46162.50889563657</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>196</v>
@@ -14080,11 +14080,11 @@
         <v>472</v>
       </c>
       <c r="B221" s="9">
-        <v>46162.559060671294</v>
+        <v>46162.39239400463</v>
       </c>
       <c r="C221" s="10"/>
       <c r="D221" s="9">
-        <v>46162.67579302083</v>
+        <v>46162.50912635417</v>
       </c>
       <c r="E221" s="10" t="s">
         <v>473</v>
@@ -14093,10 +14093,10 @@
         <v>26</v>
       </c>
       <c r="G221" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H221" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H221" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I221" s="9">
         <v>46231</v>
@@ -14143,11 +14143,11 @@
         <v>474</v>
       </c>
       <c r="B222" s="5">
-        <v>46162.55906472223</v>
+        <v>46162.392398055556</v>
       </c>
       <c r="C222" s="6"/>
       <c r="D222" s="5">
-        <v>46162.67579450231</v>
+        <v>46162.50912783565</v>
       </c>
       <c r="E222" s="6" t="s">
         <v>190</v>
@@ -14156,10 +14156,10 @@
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H222" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H222" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I222" s="6"/>
       <c r="J222" s="5">
@@ -14194,11 +14194,11 @@
         <v>476</v>
       </c>
       <c r="B223" s="9">
-        <v>46162.55907236111</v>
+        <v>46162.392405694445</v>
       </c>
       <c r="C223" s="10"/>
       <c r="D223" s="9">
-        <v>46162.6757915162</v>
+        <v>46162.50912484954</v>
       </c>
       <c r="E223" s="10" t="s">
         <v>190</v>
@@ -14207,10 +14207,10 @@
         <v>26</v>
       </c>
       <c r="G223" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H223" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H223" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I223" s="10"/>
       <c r="J223" s="9">
@@ -14245,11 +14245,11 @@
         <v>477</v>
       </c>
       <c r="B224" s="5">
-        <v>46162.55907862268</v>
+        <v>46162.39241195602</v>
       </c>
       <c r="C224" s="6"/>
       <c r="D224" s="5">
-        <v>46162.67578863426</v>
+        <v>46162.509121967596</v>
       </c>
       <c r="E224" s="6" t="s">
         <v>190</v>
@@ -14258,10 +14258,10 @@
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H224" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H224" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I224" s="6"/>
       <c r="J224" s="5">
@@ -14296,11 +14296,11 @@
         <v>479</v>
       </c>
       <c r="B225" s="9">
-        <v>46162.55908304398</v>
+        <v>46162.39241637732</v>
       </c>
       <c r="C225" s="10"/>
       <c r="D225" s="9">
-        <v>46162.67578590278</v>
+        <v>46162.509119236114</v>
       </c>
       <c r="E225" s="10" t="s">
         <v>190</v>
@@ -14309,10 +14309,10 @@
         <v>26</v>
       </c>
       <c r="G225" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H225" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H225" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I225" s="10"/>
       <c r="J225" s="9">
@@ -14347,11 +14347,11 @@
         <v>480</v>
       </c>
       <c r="B226" s="5">
-        <v>46162.55908719907</v>
+        <v>46162.39242053241</v>
       </c>
       <c r="C226" s="6"/>
       <c r="D226" s="5">
-        <v>46162.67578289352</v>
+        <v>46162.50911622685</v>
       </c>
       <c r="E226" s="6" t="s">
         <v>196</v>
@@ -14360,10 +14360,10 @@
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H226" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H226" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I226" s="6"/>
       <c r="J226" s="5">
@@ -14398,11 +14398,11 @@
         <v>482</v>
       </c>
       <c r="B227" s="9">
-        <v>46162.56901232639</v>
+        <v>46162.40234565972</v>
       </c>
       <c r="C227" s="10"/>
       <c r="D227" s="9">
-        <v>46162.67577962963</v>
+        <v>46162.50911296296</v>
       </c>
       <c r="E227" s="10" t="s">
         <v>196</v>
@@ -14411,10 +14411,10 @@
         <v>26</v>
       </c>
       <c r="G227" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H227" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H227" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I227" s="10"/>
       <c r="J227" s="9">
@@ -14449,11 +14449,11 @@
         <v>483</v>
       </c>
       <c r="B228" s="5">
-        <v>46162.569018888884</v>
+        <v>46162.40235222223</v>
       </c>
       <c r="C228" s="6"/>
       <c r="D228" s="5">
-        <v>46162.67577695602</v>
+        <v>46162.50911028935</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>196</v>
@@ -14462,10 +14462,10 @@
         <v>26</v>
       </c>
       <c r="G228" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H228" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H228" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I228" s="6"/>
       <c r="J228" s="5">
@@ -14500,11 +14500,11 @@
         <v>484</v>
       </c>
       <c r="B229" s="9">
-        <v>46162.56902688657</v>
+        <v>46162.40236021991</v>
       </c>
       <c r="C229" s="10"/>
       <c r="D229" s="9">
-        <v>46162.67577410879</v>
+        <v>46162.50910744213</v>
       </c>
       <c r="E229" s="10" t="s">
         <v>467</v>
@@ -14513,10 +14513,10 @@
         <v>26</v>
       </c>
       <c r="G229" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H229" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H229" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I229" s="10"/>
       <c r="J229" s="9">
@@ -14551,11 +14551,11 @@
         <v>485</v>
       </c>
       <c r="B230" s="5">
-        <v>46162.56903291667</v>
+        <v>46162.40236625</v>
       </c>
       <c r="C230" s="6"/>
       <c r="D230" s="5">
-        <v>46162.67577162037</v>
+        <v>46162.5091049537</v>
       </c>
       <c r="E230" s="6" t="s">
         <v>196</v>
@@ -14564,10 +14564,10 @@
         <v>26</v>
       </c>
       <c r="G230" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H230" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H230" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I230" s="6"/>
       <c r="J230" s="5">
@@ -14602,11 +14602,11 @@
         <v>486</v>
       </c>
       <c r="B231" s="9">
-        <v>46162.56903989583</v>
+        <v>46162.40237322917</v>
       </c>
       <c r="C231" s="10"/>
       <c r="D231" s="9">
-        <v>46162.67576392361</v>
+        <v>46162.509097256945</v>
       </c>
       <c r="E231" s="10" t="s">
         <v>196</v>
@@ -14615,10 +14615,10 @@
         <v>26</v>
       </c>
       <c r="G231" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H231" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H231" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I231" s="10"/>
       <c r="J231" s="9">
@@ -14653,11 +14653,11 @@
         <v>487</v>
       </c>
       <c r="B232" s="5">
-        <v>46162.56904635417</v>
+        <v>46162.4023796875</v>
       </c>
       <c r="C232" s="6"/>
       <c r="D232" s="5">
-        <v>46162.67576322917</v>
+        <v>46162.5090965625</v>
       </c>
       <c r="E232" s="6" t="s">
         <v>196</v>
@@ -14666,10 +14666,10 @@
         <v>26</v>
       </c>
       <c r="G232" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H232" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H232" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I232" s="6"/>
       <c r="J232" s="5">
@@ -14704,11 +14704,11 @@
         <v>488</v>
       </c>
       <c r="B233" s="9">
-        <v>46162.56905347222</v>
+        <v>46162.40238680555</v>
       </c>
       <c r="C233" s="10"/>
       <c r="D233" s="9">
-        <v>46162.67576252315</v>
+        <v>46162.50909585648</v>
       </c>
       <c r="E233" s="10" t="s">
         <v>196</v>
@@ -14717,10 +14717,10 @@
         <v>26</v>
       </c>
       <c r="G233" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H233" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H233" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I233" s="10"/>
       <c r="J233" s="9">
@@ -14755,11 +14755,11 @@
         <v>489</v>
       </c>
       <c r="B234" s="5">
-        <v>46162.559091284726</v>
+        <v>46162.392424618054</v>
       </c>
       <c r="C234" s="6"/>
       <c r="D234" s="5">
-        <v>46162.6758584375</v>
+        <v>46162.509191770834</v>
       </c>
       <c r="E234" s="6" t="s">
         <v>490</v>
@@ -14768,10 +14768,10 @@
         <v>26</v>
       </c>
       <c r="G234" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H234" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H234" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I234" s="5">
         <v>46232</v>
@@ -14818,11 +14818,11 @@
         <v>492</v>
       </c>
       <c r="B235" s="9">
-        <v>46162.55909613426</v>
+        <v>46162.392429467596</v>
       </c>
       <c r="C235" s="10"/>
       <c r="D235" s="9">
-        <v>46162.676026875</v>
+        <v>46162.509360208336</v>
       </c>
       <c r="E235" s="10" t="s">
         <v>190</v>
@@ -14831,10 +14831,10 @@
         <v>26</v>
       </c>
       <c r="G235" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H235" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H235" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I235" s="9">
         <v>46232</v>
@@ -14871,11 +14871,11 @@
         <v>493</v>
       </c>
       <c r="B236" s="5">
-        <v>46162.55910012731</v>
+        <v>46162.39243346065</v>
       </c>
       <c r="C236" s="6"/>
       <c r="D236" s="5">
-        <v>46162.67602255787</v>
+        <v>46162.509355891205</v>
       </c>
       <c r="E236" s="6" t="s">
         <v>190</v>
@@ -14884,10 +14884,10 @@
         <v>26</v>
       </c>
       <c r="G236" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H236" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H236" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I236" s="5">
         <v>46232</v>
@@ -14924,11 +14924,11 @@
         <v>494</v>
       </c>
       <c r="B237" s="9">
-        <v>46162.55910407407</v>
+        <v>46162.39243740741</v>
       </c>
       <c r="C237" s="10"/>
       <c r="D237" s="9">
-        <v>46162.676019108796</v>
+        <v>46162.509352442125</v>
       </c>
       <c r="E237" s="10" t="s">
         <v>190</v>
@@ -14937,10 +14937,10 @@
         <v>26</v>
       </c>
       <c r="G237" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H237" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H237" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I237" s="9">
         <v>46232</v>
@@ -14977,11 +14977,11 @@
         <v>495</v>
       </c>
       <c r="B238" s="5">
-        <v>46162.559108125</v>
+        <v>46162.39244145833</v>
       </c>
       <c r="C238" s="6"/>
       <c r="D238" s="5">
-        <v>46162.67601616898</v>
+        <v>46162.50934950232</v>
       </c>
       <c r="E238" s="6" t="s">
         <v>190</v>
@@ -14990,10 +14990,10 @@
         <v>26</v>
       </c>
       <c r="G238" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H238" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H238" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I238" s="5">
         <v>46232</v>
@@ -15030,11 +15030,11 @@
         <v>496</v>
       </c>
       <c r="B239" s="9">
-        <v>46162.55914409722</v>
+        <v>46162.392477430556</v>
       </c>
       <c r="C239" s="10"/>
       <c r="D239" s="9">
-        <v>46162.676013275464</v>
+        <v>46162.5093466088</v>
       </c>
       <c r="E239" s="10" t="s">
         <v>196</v>
@@ -15043,10 +15043,10 @@
         <v>26</v>
       </c>
       <c r="G239" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H239" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H239" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I239" s="9">
         <v>46232</v>
@@ -15083,11 +15083,11 @@
         <v>497</v>
       </c>
       <c r="B240" s="5">
-        <v>46162.56958915509</v>
+        <v>46162.40292248843</v>
       </c>
       <c r="C240" s="6"/>
       <c r="D240" s="5">
-        <v>46162.67600972222</v>
+        <v>46162.50934305556</v>
       </c>
       <c r="E240" s="6" t="s">
         <v>196</v>
@@ -15096,10 +15096,10 @@
         <v>26</v>
       </c>
       <c r="G240" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H240" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H240" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I240" s="5">
         <v>46232</v>
@@ -15136,11 +15136,11 @@
         <v>498</v>
       </c>
       <c r="B241" s="9">
-        <v>46162.56959587963</v>
+        <v>46162.40292921296</v>
       </c>
       <c r="C241" s="10"/>
       <c r="D241" s="9">
-        <v>46162.676007002316</v>
+        <v>46162.509340335644</v>
       </c>
       <c r="E241" s="10" t="s">
         <v>196</v>
@@ -15149,10 +15149,10 @@
         <v>26</v>
       </c>
       <c r="G241" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H241" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H241" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I241" s="9">
         <v>46232</v>
@@ -15189,11 +15189,11 @@
         <v>499</v>
       </c>
       <c r="B242" s="5">
-        <v>46162.56960513889</v>
+        <v>46162.40293847222</v>
       </c>
       <c r="C242" s="6"/>
       <c r="D242" s="5">
-        <v>46162.67600369213</v>
+        <v>46162.50933702546</v>
       </c>
       <c r="E242" s="6" t="s">
         <v>196</v>
@@ -15202,10 +15202,10 @@
         <v>26</v>
       </c>
       <c r="G242" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H242" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H242" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I242" s="5">
         <v>46232</v>
@@ -15242,11 +15242,11 @@
         <v>500</v>
       </c>
       <c r="B243" s="9">
-        <v>46162.569612060186</v>
+        <v>46162.40294539352</v>
       </c>
       <c r="C243" s="10"/>
       <c r="D243" s="9">
-        <v>46162.67599591435</v>
+        <v>46162.50932924768</v>
       </c>
       <c r="E243" s="10" t="s">
         <v>196</v>
@@ -15255,10 +15255,10 @@
         <v>26</v>
       </c>
       <c r="G243" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H243" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H243" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I243" s="9">
         <v>46232</v>
@@ -15295,11 +15295,11 @@
         <v>501</v>
       </c>
       <c r="B244" s="5">
-        <v>46162.569619999995</v>
+        <v>46162.40295333334</v>
       </c>
       <c r="C244" s="6"/>
       <c r="D244" s="5">
-        <v>46162.67599258102</v>
+        <v>46162.50932591435</v>
       </c>
       <c r="E244" s="6" t="s">
         <v>196</v>
@@ -15308,10 +15308,10 @@
         <v>26</v>
       </c>
       <c r="G244" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H244" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H244" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I244" s="5">
         <v>46232</v>
@@ -15348,11 +15348,11 @@
         <v>502</v>
       </c>
       <c r="B245" s="9">
-        <v>46162.569627812496</v>
+        <v>46162.40296114583</v>
       </c>
       <c r="C245" s="10"/>
       <c r="D245" s="9">
-        <v>46162.675991412034</v>
+        <v>46162.50932474537</v>
       </c>
       <c r="E245" s="10" t="s">
         <v>196</v>
@@ -15361,10 +15361,10 @@
         <v>26</v>
       </c>
       <c r="G245" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H245" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H245" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I245" s="9">
         <v>46232</v>
@@ -15401,11 +15401,11 @@
         <v>503</v>
       </c>
       <c r="B246" s="5">
-        <v>46162.569634513886</v>
+        <v>46162.40296784722</v>
       </c>
       <c r="C246" s="6"/>
       <c r="D246" s="5">
-        <v>46162.675990613425</v>
+        <v>46162.50932394676</v>
       </c>
       <c r="E246" s="6" t="s">
         <v>196</v>
@@ -15414,10 +15414,10 @@
         <v>26</v>
       </c>
       <c r="G246" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H246" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H246" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I246" s="5">
         <v>46232</v>
@@ -15454,11 +15454,11 @@
         <v>504</v>
       </c>
       <c r="B247" s="9">
-        <v>46162.5591494213</v>
+        <v>46162.39248275463</v>
       </c>
       <c r="C247" s="10"/>
       <c r="D247" s="9">
-        <v>46162.664148020835</v>
+        <v>46162.49748135416</v>
       </c>
       <c r="E247" s="10" t="s">
         <v>505</v>
@@ -15501,11 +15501,11 @@
         <v>507</v>
       </c>
       <c r="B248" s="5">
-        <v>46162.559152800924</v>
+        <v>46162.39248613426</v>
       </c>
       <c r="C248" s="6"/>
       <c r="D248" s="5">
-        <v>46162.676061377315</v>
+        <v>46162.50939471065</v>
       </c>
       <c r="E248" s="6" t="s">
         <v>508</v>
@@ -15564,11 +15564,11 @@
         <v>511</v>
       </c>
       <c r="B249" s="9">
-        <v>46162.55915726852</v>
+        <v>46162.39249060185</v>
       </c>
       <c r="C249" s="10"/>
       <c r="D249" s="9">
-        <v>46197.69418131944</v>
+        <v>46197.52751465278</v>
       </c>
       <c r="E249" s="10" t="s">
         <v>512</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -2211,13 +2211,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46162.39149386574</v>
+        <v>46162.55816053241</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.70741635417</v>
+        <v>46175.87408302083</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.707430625</v>
+        <v>46175.87409729167</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2264,13 +2264,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46162.39156319444</v>
+        <v>46162.55822986111</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.707391689815</v>
+        <v>46175.87405835648</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.70741675926</v>
+        <v>46175.87408342592</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -2329,13 +2329,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46162.39156659722</v>
+        <v>46162.55823326389</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.70739228009</v>
+        <v>46175.87405894676</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.70741690972</v>
+        <v>46175.87408357639</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2394,13 +2394,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46162.39157100694</v>
+        <v>46162.55823767361</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.707392627315</v>
+        <v>46175.87405929399</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.70741699074</v>
+        <v>46175.87408365741</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -2459,13 +2459,13 @@
         <v>38</v>
       </c>
       <c r="B8" s="5">
-        <v>46162.39157511574</v>
+        <v>46162.558241782404</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.70739302083</v>
+        <v>46175.8740596875</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.70741724537</v>
+        <v>46175.87408391204</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>39</v>
@@ -2524,13 +2524,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="9">
-        <v>46162.3915787963</v>
+        <v>46162.55824546296</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.70739358796</v>
+        <v>46175.87406025463</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.70741747685</v>
+        <v>46175.87408414352</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>43</v>
@@ -2589,11 +2589,11 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46162.39149815972</v>
+        <v>46162.55816482639</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46197.5275244213</v>
+        <v>46197.69419108796</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2638,13 +2638,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="9">
-        <v>46162.39158243056</v>
+        <v>46162.55824909722</v>
       </c>
       <c r="C11" s="9">
-        <v>46197.48575736111</v>
+        <v>46197.65242402778</v>
       </c>
       <c r="D11" s="9">
-        <v>46197.52751465278</v>
+        <v>46197.69418131944</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>49</v>
@@ -2703,13 +2703,13 @@
         <v>55</v>
       </c>
       <c r="B12" s="5">
-        <v>46162.3915878125</v>
+        <v>46162.55825447917</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.48787416666</v>
+        <v>46197.65454083333</v>
       </c>
       <c r="D12" s="5">
-        <v>46197.52751488426</v>
+        <v>46197.69418155093</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2768,13 +2768,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="9">
-        <v>46162.39159321759</v>
+        <v>46162.55825988426</v>
       </c>
       <c r="C13" s="9">
-        <v>46197.48981511574</v>
+        <v>46197.65648178241</v>
       </c>
       <c r="D13" s="9">
-        <v>46197.52751484954</v>
+        <v>46197.6941815162</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>60</v>
@@ -2833,11 +2833,11 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46162.39150253472</v>
+        <v>46162.55816920139</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46198.5172644213</v>
+        <v>46198.68393108796</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2880,13 +2880,13 @@
         <v>66</v>
       </c>
       <c r="B15" s="9">
-        <v>46162.39160631945</v>
+        <v>46162.55827298611</v>
       </c>
       <c r="C15" s="9">
-        <v>46198.51725826389</v>
+        <v>46198.683924930556</v>
       </c>
       <c r="D15" s="9">
-        <v>46198.51727664351</v>
+        <v>46198.683943310185</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>67</v>
@@ -2945,11 +2945,11 @@
         <v>69</v>
       </c>
       <c r="B16" s="5">
-        <v>46162.39161152778</v>
+        <v>46162.55827819444</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46197.48789217592</v>
+        <v>46197.654558842594</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>70</v>
@@ -3008,13 +3008,13 @@
         <v>72</v>
       </c>
       <c r="B17" s="9">
-        <v>46162.39161695602</v>
+        <v>46162.55828362268</v>
       </c>
       <c r="C17" s="9">
-        <v>46197.42144385417</v>
+        <v>46197.58811052083</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.61093523148</v>
+        <v>46197.77760189815</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>73</v>
@@ -3073,11 +3073,11 @@
         <v>76</v>
       </c>
       <c r="B18" s="5">
-        <v>46162.39162216435</v>
+        <v>46162.55828883102</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46198.62673256945</v>
+        <v>46198.79339923611</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -3136,11 +3136,11 @@
         <v>82</v>
       </c>
       <c r="B19" s="9">
-        <v>46162.3916271412</v>
+        <v>46162.55829380787</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46198.62673762732</v>
+        <v>46198.79340429398</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>83</v>
@@ -3199,11 +3199,11 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46162.39163115741</v>
+        <v>46162.55829782407</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46198.62673333334</v>
+        <v>46198.793399999995</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -3262,11 +3262,11 @@
         <v>88</v>
       </c>
       <c r="B21" s="9">
-        <v>46162.39163478009</v>
+        <v>46162.558301446756</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46198.6267338426</v>
+        <v>46198.793400509254</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>89</v>
@@ -3325,11 +3325,11 @@
         <v>91</v>
       </c>
       <c r="B22" s="5">
-        <v>46162.39150678241</v>
+        <v>46162.55817344907</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46198.51803719907</v>
+        <v>46198.68470386574</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -3372,11 +3372,11 @@
         <v>94</v>
       </c>
       <c r="B23" s="9">
-        <v>46162.39163902777</v>
+        <v>46162.558305694445</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46169.69586019676</v>
+        <v>46169.86252686342</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>95</v>
@@ -3435,11 +3435,11 @@
         <v>100</v>
       </c>
       <c r="B24" s="5">
-        <v>46162.391643518524</v>
+        <v>46162.55831018518</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.696358437504</v>
+        <v>46169.86302510416</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>101</v>
@@ -3494,11 +3494,11 @@
         <v>103</v>
       </c>
       <c r="B25" s="9">
-        <v>46162.391648125005</v>
+        <v>46162.55831479166</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.69638149306</v>
+        <v>46169.86304815972</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>104</v>
@@ -3553,13 +3553,13 @@
         <v>106</v>
       </c>
       <c r="B26" s="5">
-        <v>46162.39165304398</v>
+        <v>46162.558319710646</v>
       </c>
       <c r="C26" s="5">
-        <v>46198.518027847225</v>
+        <v>46198.68469451389</v>
       </c>
       <c r="D26" s="5">
-        <v>46198.51804033565</v>
+        <v>46198.684707002314</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>107</v>
@@ -3618,13 +3618,13 @@
         <v>109</v>
       </c>
       <c r="B27" s="9">
-        <v>46162.39165748842</v>
+        <v>46162.55832415509</v>
       </c>
       <c r="C27" s="9">
-        <v>46198.517974421295</v>
+        <v>46198.684641087966</v>
       </c>
       <c r="D27" s="9">
-        <v>46198.517976041665</v>
+        <v>46198.68464270834</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>110</v>
@@ -3679,13 +3679,13 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46162.39166703704</v>
+        <v>46162.5583337037</v>
       </c>
       <c r="C28" s="5">
-        <v>46198.51801262732</v>
+        <v>46198.68467929398</v>
       </c>
       <c r="D28" s="5">
-        <v>46198.51801561343</v>
+        <v>46198.68468228009</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3740,13 +3740,13 @@
         <v>115</v>
       </c>
       <c r="B29" s="9">
-        <v>46162.391672094906</v>
+        <v>46162.55833876158</v>
       </c>
       <c r="C29" s="9">
-        <v>46198.51765565972</v>
+        <v>46198.684322326386</v>
       </c>
       <c r="D29" s="9">
-        <v>46198.5176746875</v>
+        <v>46198.684341354165</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>116</v>
@@ -3805,13 +3805,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46162.39167703704</v>
+        <v>46162.5583437037</v>
       </c>
       <c r="C30" s="5">
-        <v>46198.517469687504</v>
+        <v>46198.68413635417</v>
       </c>
       <c r="D30" s="5">
-        <v>46198.51747103009</v>
+        <v>46198.684137696764</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3866,13 +3866,13 @@
         <v>121</v>
       </c>
       <c r="B31" s="9">
-        <v>46162.39168206019</v>
+        <v>46162.55834872685</v>
       </c>
       <c r="C31" s="9">
-        <v>46198.517640254635</v>
+        <v>46198.68430692129</v>
       </c>
       <c r="D31" s="9">
-        <v>46198.517641666665</v>
+        <v>46198.68430833334</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>122</v>
@@ -3927,13 +3927,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46162.39168685186</v>
+        <v>46162.558353518514</v>
       </c>
       <c r="C32" s="5">
-        <v>46198.51750884259</v>
+        <v>46198.68417550926</v>
       </c>
       <c r="D32" s="5">
-        <v>46198.51751042824</v>
+        <v>46198.68417709491</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3988,11 +3988,11 @@
         <v>127</v>
       </c>
       <c r="B33" s="9">
-        <v>46162.3916915625</v>
+        <v>46162.558358229166</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46203.02021912037</v>
+        <v>46203.186885787036</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -4051,11 +4051,11 @@
         <v>132</v>
       </c>
       <c r="B34" s="5">
-        <v>46162.39169614583</v>
+        <v>46162.5583628125</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46191.00262935185</v>
+        <v>46191.16929601852</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -4110,11 +4110,11 @@
         <v>135</v>
       </c>
       <c r="B35" s="9">
-        <v>46162.39174608796</v>
+        <v>46162.55841275463</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46202.00262724537</v>
+        <v>46202.16929391204</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>136</v>
@@ -4169,11 +4169,11 @@
         <v>138</v>
       </c>
       <c r="B36" s="5">
-        <v>46162.39175195602</v>
+        <v>46162.558418622684</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46203.02021915509</v>
+        <v>46203.186885821764</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>139</v>
@@ -4232,11 +4232,11 @@
         <v>141</v>
       </c>
       <c r="B37" s="9">
-        <v>46162.39175545139</v>
+        <v>46162.558422118054</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46191.0026272338</v>
+        <v>46191.169293900464</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>84</v>
@@ -4285,11 +4285,11 @@
         <v>143</v>
       </c>
       <c r="B38" s="5">
-        <v>46162.3917597338</v>
+        <v>46162.558426400465</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46171.00696226852</v>
+        <v>46171.17362893518</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>144</v>
@@ -4338,11 +4338,11 @@
         <v>146</v>
       </c>
       <c r="B39" s="9">
-        <v>46162.391767002315</v>
+        <v>46162.55843366898</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.69593177083</v>
+        <v>46169.862598437496</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>147</v>
@@ -4401,11 +4401,11 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46162.391770902774</v>
+        <v>46162.558437569445</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46198.00243474537</v>
+        <v>46198.16910141204</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>90</v>
@@ -4454,11 +4454,11 @@
         <v>153</v>
       </c>
       <c r="B41" s="9">
-        <v>46162.39177487268</v>
+        <v>46162.55844153935</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.69605724537</v>
+        <v>46169.86272391204</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>154</v>
@@ -4507,11 +4507,11 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46162.39177909722</v>
+        <v>46162.55844576389</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.69607568287</v>
+        <v>46169.862742349535</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -4560,11 +4560,11 @@
         <v>160</v>
       </c>
       <c r="B43" s="9">
-        <v>46162.391781666665</v>
+        <v>46162.55844833334</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46203.020219768514</v>
+        <v>46203.186886435185</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>161</v>
@@ -4623,11 +4623,11 @@
         <v>163</v>
       </c>
       <c r="B44" s="5">
-        <v>46162.391784479165</v>
+        <v>46162.55845114583</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46191.00263079861</v>
+        <v>46191.169297465276</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>87</v>
@@ -4676,11 +4676,11 @@
         <v>165</v>
       </c>
       <c r="B45" s="9">
-        <v>46162.39178854167</v>
+        <v>46162.55845520833</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46202.002625023146</v>
+        <v>46202.16929168982</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>166</v>
@@ -4729,11 +4729,11 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46162.39151100694</v>
+        <v>46162.55817767361</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46198.62666923611</v>
+        <v>46198.79333590278</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4778,13 +4778,13 @@
         <v>171</v>
       </c>
       <c r="B47" s="9">
-        <v>46162.391792905095</v>
+        <v>46162.55845957176</v>
       </c>
       <c r="C47" s="9">
-        <v>46197.50829434028</v>
+        <v>46197.674961006946</v>
       </c>
       <c r="D47" s="9">
-        <v>46197.51023809028</v>
+        <v>46197.67690475694</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>172</v>
@@ -4843,13 +4843,13 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46162.391797731485</v>
+        <v>46162.55846439815</v>
       </c>
       <c r="C48" s="5">
-        <v>46198.626649791666</v>
+        <v>46198.79331645834</v>
       </c>
       <c r="D48" s="5">
-        <v>46198.626667557866</v>
+        <v>46198.79333422454</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4908,13 +4908,13 @@
         <v>180</v>
       </c>
       <c r="B49" s="9">
-        <v>46162.39180357639</v>
+        <v>46162.55847024306</v>
       </c>
       <c r="C49" s="9">
-        <v>46198.62669734954</v>
+        <v>46198.79336401621</v>
       </c>
       <c r="D49" s="9">
-        <v>46198.62671300926</v>
+        <v>46198.793379675924</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>80</v>
@@ -4971,11 +4971,11 @@
         <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46162.39181905093</v>
+        <v>46162.55848571759</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46162.505030671295</v>
+        <v>46162.671697337966</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -5034,11 +5034,11 @@
         <v>189</v>
       </c>
       <c r="B51" s="9">
-        <v>46162.39182234954</v>
+        <v>46162.5584890162</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46191.51971841435</v>
+        <v>46191.68638508102</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>190</v>
@@ -5085,11 +5085,11 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46162.39182628472</v>
+        <v>46162.558492951386</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46191.519715347225</v>
+        <v>46191.68638201389</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>190</v>
@@ -5136,11 +5136,11 @@
         <v>193</v>
       </c>
       <c r="B53" s="9">
-        <v>46162.391829942135</v>
+        <v>46162.55849660879</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46191.51971246528</v>
+        <v>46191.68637913195</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>190</v>
@@ -5187,11 +5187,11 @@
         <v>194</v>
       </c>
       <c r="B54" s="5">
-        <v>46162.3918325</v>
+        <v>46162.55849916667</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46191.519709479166</v>
+        <v>46191.68637614584</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -5238,11 +5238,11 @@
         <v>195</v>
       </c>
       <c r="B55" s="9">
-        <v>46162.391835092596</v>
+        <v>46162.55850175926</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46191.51970609954</v>
+        <v>46191.6863727662</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>196</v>
@@ -5289,11 +5289,11 @@
         <v>197</v>
       </c>
       <c r="B56" s="5">
-        <v>46162.39544947917</v>
+        <v>46162.56211614583</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46191.51970297453</v>
+        <v>46191.686369641204</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>196</v>
@@ -5340,11 +5340,11 @@
         <v>198</v>
       </c>
       <c r="B57" s="9">
-        <v>46162.39545730324</v>
+        <v>46162.56212396991</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46191.51969971065</v>
+        <v>46191.68636637731</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>196</v>
@@ -5391,11 +5391,11 @@
         <v>199</v>
       </c>
       <c r="B58" s="5">
-        <v>46162.395468310184</v>
+        <v>46162.56213497685</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46191.519697094904</v>
+        <v>46191.686363761575</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>196</v>
@@ -5442,11 +5442,11 @@
         <v>200</v>
       </c>
       <c r="B59" s="9">
-        <v>46162.39548839121</v>
+        <v>46162.562155057865</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46191.51969422454</v>
+        <v>46191.6863608912</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>196</v>
@@ -5493,11 +5493,11 @@
         <v>201</v>
       </c>
       <c r="B60" s="5">
-        <v>46162.39549638889</v>
+        <v>46162.562163055554</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46191.51968612269</v>
+        <v>46191.68635278935</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>196</v>
@@ -5544,11 +5544,11 @@
         <v>202</v>
       </c>
       <c r="B61" s="9">
-        <v>46162.395504375</v>
+        <v>46162.56217104167</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46191.51968542824</v>
+        <v>46191.68635209491</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>196</v>
@@ -5595,11 +5595,11 @@
         <v>203</v>
       </c>
       <c r="B62" s="5">
-        <v>46162.395512268515</v>
+        <v>46162.562178935186</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46191.51968474537</v>
+        <v>46191.686351412034</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>196</v>
@@ -5646,11 +5646,11 @@
         <v>204</v>
       </c>
       <c r="B63" s="9">
-        <v>46162.391837766205</v>
+        <v>46162.55850443287</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46162.43817887732</v>
+        <v>46162.60484554398</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>205</v>
@@ -5693,11 +5693,11 @@
         <v>207</v>
       </c>
       <c r="B64" s="5">
-        <v>46162.39184087963</v>
+        <v>46162.558507546295</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46204.00040314815</v>
+        <v>46204.167069814815</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>208</v>
@@ -5756,11 +5756,11 @@
         <v>212</v>
       </c>
       <c r="B65" s="9">
-        <v>46162.391845474536</v>
+        <v>46162.5585121412</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46205.00828016204</v>
+        <v>46205.1749468287</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>213</v>
@@ -5819,11 +5819,11 @@
         <v>216</v>
       </c>
       <c r="B66" s="5">
-        <v>46162.39185197916</v>
+        <v>46162.558518645834</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46204.00040373842</v>
+        <v>46204.16707040509</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>217</v>
@@ -5882,11 +5882,11 @@
         <v>219</v>
       </c>
       <c r="B67" s="9">
-        <v>46162.391856574075</v>
+        <v>46162.55852324074</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46205.00828008102</v>
+        <v>46205.174946747684</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>220</v>
@@ -5945,11 +5945,11 @@
         <v>222</v>
       </c>
       <c r="B68" s="5">
-        <v>46162.39186078704</v>
+        <v>46162.5585274537</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46204.00040484953</v>
+        <v>46204.1670715162</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>223</v>
@@ -6008,11 +6008,11 @@
         <v>225</v>
       </c>
       <c r="B69" s="9">
-        <v>46162.3918647338</v>
+        <v>46162.558531400464</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46205.00828006944</v>
+        <v>46205.17494673611</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>224</v>
@@ -6071,11 +6071,11 @@
         <v>227</v>
       </c>
       <c r="B70" s="5">
-        <v>46162.391868900464</v>
+        <v>46162.55853556713</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46162.44473074074</v>
+        <v>46162.61139740741</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>228</v>
@@ -6118,11 +6118,11 @@
         <v>230</v>
       </c>
       <c r="B71" s="9">
-        <v>46162.39187140046</v>
+        <v>46162.558538067125</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46202.025014768515</v>
+        <v>46202.191681435186</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>231</v>
@@ -6181,11 +6181,11 @@
         <v>236</v>
       </c>
       <c r="B72" s="5">
-        <v>46162.391875891204</v>
+        <v>46162.558542557876</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46162.50557039352</v>
+        <v>46162.672237060186</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>190</v>
@@ -6234,11 +6234,11 @@
         <v>239</v>
       </c>
       <c r="B73" s="9">
-        <v>46162.39188173611</v>
+        <v>46162.558548402776</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46162.50556710648</v>
+        <v>46162.67223377315</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>190</v>
@@ -6287,11 +6287,11 @@
         <v>242</v>
       </c>
       <c r="B74" s="5">
-        <v>46162.391887453705</v>
+        <v>46162.55855412037</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46162.505563865736</v>
+        <v>46162.67223053241</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>190</v>
@@ -6340,11 +6340,11 @@
         <v>243</v>
       </c>
       <c r="B75" s="9">
-        <v>46162.39189333333</v>
+        <v>46162.558560000005</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46162.50556071759</v>
+        <v>46162.67222738426</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>190</v>
@@ -6393,11 +6393,11 @@
         <v>245</v>
       </c>
       <c r="B76" s="5">
-        <v>46162.39189900463</v>
+        <v>46162.558565671294</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46162.505556944445</v>
+        <v>46162.67222361111</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>196</v>
@@ -6446,11 +6446,11 @@
         <v>247</v>
       </c>
       <c r="B77" s="9">
-        <v>46162.393521122685</v>
+        <v>46162.56018778935</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46162.50555353009</v>
+        <v>46162.672220196764</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>196</v>
@@ -6499,11 +6499,11 @@
         <v>249</v>
       </c>
       <c r="B78" s="5">
-        <v>46162.393541122685</v>
+        <v>46162.560207789356</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46162.50555027778</v>
+        <v>46162.67221694444</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>196</v>
@@ -6552,11 +6552,11 @@
         <v>250</v>
       </c>
       <c r="B79" s="9">
-        <v>46162.39355087963</v>
+        <v>46162.5602175463</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46162.50554719908</v>
+        <v>46162.67221386574</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>196</v>
@@ -6605,11 +6605,11 @@
         <v>251</v>
       </c>
       <c r="B80" s="5">
-        <v>46162.39355974537</v>
+        <v>46162.56022641204</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46162.50554429398</v>
+        <v>46162.67221096065</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>196</v>
@@ -6658,11 +6658,11 @@
         <v>252</v>
       </c>
       <c r="B81" s="9">
-        <v>46162.393567928244</v>
+        <v>46162.56023459491</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46162.50553511574</v>
+        <v>46162.67220178241</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>196</v>
@@ -6711,11 +6711,11 @@
         <v>253</v>
       </c>
       <c r="B82" s="5">
-        <v>46162.393576180555</v>
+        <v>46162.56024284722</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46162.50553436343</v>
+        <v>46162.67220103009</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>196</v>
@@ -6764,11 +6764,11 @@
         <v>254</v>
       </c>
       <c r="B83" s="9">
-        <v>46162.39358395833</v>
+        <v>46162.560250625</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46162.50553359954</v>
+        <v>46162.6722002662</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>196</v>
@@ -6817,11 +6817,11 @@
         <v>255</v>
       </c>
       <c r="B84" s="5">
-        <v>46162.39195396991</v>
+        <v>46162.55862063657</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46162.50582612268</v>
+        <v>46162.67249278935</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>256</v>
@@ -6880,11 +6880,11 @@
         <v>258</v>
       </c>
       <c r="B85" s="9">
-        <v>46162.391959953704</v>
+        <v>46162.558626620375</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46198.62671858796</v>
+        <v>46198.79338525463</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>190</v>
@@ -6933,11 +6933,11 @@
         <v>261</v>
       </c>
       <c r="B86" s="5">
-        <v>46162.39196613426</v>
+        <v>46162.55863280092</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46198.62671532408</v>
+        <v>46198.79338199074</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>190</v>
@@ -6986,11 +6986,11 @@
         <v>262</v>
       </c>
       <c r="B87" s="9">
-        <v>46162.391971840276</v>
+        <v>46162.55863850695</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46198.626715763894</v>
+        <v>46198.79338243055</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>190</v>
@@ -7039,11 +7039,11 @@
         <v>264</v>
       </c>
       <c r="B88" s="5">
-        <v>46162.39197758102</v>
+        <v>46162.558644247685</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46198.6267162963</v>
+        <v>46198.79338296296</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>190</v>
@@ -7092,11 +7092,11 @@
         <v>265</v>
       </c>
       <c r="B89" s="9">
-        <v>46162.39198324074</v>
+        <v>46162.55864990741</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46162.50572736112</v>
+        <v>46162.67239402777</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>196</v>
@@ -7145,11 +7145,11 @@
         <v>267</v>
       </c>
       <c r="B90" s="5">
-        <v>46162.39481349537</v>
+        <v>46162.56148016204</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46162.50572439814</v>
+        <v>46162.672391064814</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>196</v>
@@ -7198,11 +7198,11 @@
         <v>268</v>
       </c>
       <c r="B91" s="9">
-        <v>46162.39482253473</v>
+        <v>46162.561489201384</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46162.50572107639</v>
+        <v>46162.672387743056</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>196</v>
@@ -7251,11 +7251,11 @@
         <v>269</v>
       </c>
       <c r="B92" s="5">
-        <v>46162.39483263889</v>
+        <v>46162.56149930556</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46162.50571813657</v>
+        <v>46162.67238480324</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>196</v>
@@ -7304,11 +7304,11 @@
         <v>270</v>
       </c>
       <c r="B93" s="9">
-        <v>46162.394840532404</v>
+        <v>46162.561507199076</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46162.50571546296</v>
+        <v>46162.67238212963</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>196</v>
@@ -7357,11 +7357,11 @@
         <v>271</v>
       </c>
       <c r="B94" s="5">
-        <v>46162.39484946759</v>
+        <v>46162.56151613426</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46162.505707268516</v>
+        <v>46162.67237393519</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>196</v>
@@ -7410,11 +7410,11 @@
         <v>272</v>
       </c>
       <c r="B95" s="9">
-        <v>46162.394857465275</v>
+        <v>46162.56152413195</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46162.5057065625</v>
+        <v>46162.67237322917</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>196</v>
@@ -7463,11 +7463,11 @@
         <v>273</v>
       </c>
       <c r="B96" s="5">
-        <v>46162.394864525464</v>
+        <v>46162.56153119213</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46162.505705902775</v>
+        <v>46162.67237256945</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>196</v>
@@ -7516,11 +7516,11 @@
         <v>274</v>
       </c>
       <c r="B97" s="9">
-        <v>46162.39198773148</v>
+        <v>46162.55865439815</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46162.50712538195</v>
+        <v>46162.67379204861</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>275</v>
@@ -7579,11 +7579,11 @@
         <v>277</v>
       </c>
       <c r="B98" s="5">
-        <v>46162.39199243055</v>
+        <v>46162.55865909722</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46198.626717349536</v>
+        <v>46198.7933840162</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>190</v>
@@ -7632,11 +7632,11 @@
         <v>279</v>
       </c>
       <c r="B99" s="9">
-        <v>46162.39199834491</v>
+        <v>46162.55866501157</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46198.62671790509</v>
+        <v>46198.79338457176</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>190</v>
@@ -7685,11 +7685,11 @@
         <v>281</v>
       </c>
       <c r="B100" s="5">
-        <v>46162.39200417824</v>
+        <v>46162.55867084491</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46198.62670620371</v>
+        <v>46198.79337287037</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>190</v>
@@ -7738,11 +7738,11 @@
         <v>283</v>
       </c>
       <c r="B101" s="9">
-        <v>46162.392009930554</v>
+        <v>46162.558676597226</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46198.62672172453</v>
+        <v>46198.793388391205</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>190</v>
@@ -7791,11 +7791,11 @@
         <v>285</v>
       </c>
       <c r="B102" s="5">
-        <v>46162.392015729165</v>
+        <v>46162.55868239583</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46162.507095810186</v>
+        <v>46162.67376247685</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>196</v>
@@ -7844,11 +7844,11 @@
         <v>287</v>
       </c>
       <c r="B103" s="9">
-        <v>46162.39510167824</v>
+        <v>46162.56176834491</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46162.50709515046</v>
+        <v>46162.67376181713</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>196</v>
@@ -7897,11 +7897,11 @@
         <v>288</v>
       </c>
       <c r="B104" s="5">
-        <v>46162.39511003472</v>
+        <v>46162.56177670139</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46162.50709424769</v>
+        <v>46162.67376091435</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>196</v>
@@ -7950,11 +7950,11 @@
         <v>290</v>
       </c>
       <c r="B105" s="9">
-        <v>46162.395118078704</v>
+        <v>46162.56178474537</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46162.50709356481</v>
+        <v>46162.67376023148</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>196</v>
@@ -8003,11 +8003,11 @@
         <v>291</v>
       </c>
       <c r="B106" s="5">
-        <v>46162.39512631945</v>
+        <v>46162.56179298611</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46162.50709290509</v>
+        <v>46162.67375957176</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>196</v>
@@ -8056,11 +8056,11 @@
         <v>292</v>
       </c>
       <c r="B107" s="9">
-        <v>46162.39513427083</v>
+        <v>46162.5618009375</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46162.50709221065</v>
+        <v>46162.67375887731</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>196</v>
@@ -8109,11 +8109,11 @@
         <v>293</v>
       </c>
       <c r="B108" s="5">
-        <v>46162.395142430556</v>
+        <v>46162.56180909723</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46162.507091527776</v>
+        <v>46162.67375819445</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>196</v>
@@ -8162,11 +8162,11 @@
         <v>294</v>
       </c>
       <c r="B109" s="9">
-        <v>46162.39515049769</v>
+        <v>46162.56181716435</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46162.50709084491</v>
+        <v>46162.67375751157</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>196</v>
@@ -8215,11 +8215,11 @@
         <v>295</v>
       </c>
       <c r="B110" s="5">
-        <v>46162.392019837964</v>
+        <v>46162.55868650463</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46162.44799885417</v>
+        <v>46162.61466552083</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>205</v>
@@ -8262,11 +8262,11 @@
         <v>297</v>
       </c>
       <c r="B111" s="9">
-        <v>46162.392023402776</v>
+        <v>46162.55869006945</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46198.518033252316</v>
+        <v>46198.68469991898</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>298</v>
@@ -8325,11 +8325,11 @@
         <v>300</v>
       </c>
       <c r="B112" s="5">
-        <v>46162.39203025463</v>
+        <v>46162.558696921296</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46162.50723224537</v>
+        <v>46162.673898912035</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>301</v>
@@ -8388,11 +8388,11 @@
         <v>303</v>
       </c>
       <c r="B113" s="9">
-        <v>46162.39203618055</v>
+        <v>46162.55870284722</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46198.517658819444</v>
+        <v>46198.684325486116</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>304</v>
@@ -8451,11 +8451,11 @@
         <v>306</v>
       </c>
       <c r="B114" s="5">
-        <v>46162.392042962965</v>
+        <v>46162.55870962963</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46162.50722515046</v>
+        <v>46162.67389181713</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>307</v>
@@ -8514,11 +8514,11 @@
         <v>309</v>
       </c>
       <c r="B115" s="9">
-        <v>46162.39205202546</v>
+        <v>46162.55871869213</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46162.481086562504</v>
+        <v>46162.64775322917</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>310</v>
@@ -8561,11 +8561,11 @@
         <v>312</v>
       </c>
       <c r="B116" s="5">
-        <v>46162.39205556713</v>
+        <v>46162.55872223379</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46162.507339918986</v>
+        <v>46162.67400658564</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>313</v>
@@ -8624,11 +8624,11 @@
         <v>315</v>
       </c>
       <c r="B117" s="9">
-        <v>46162.3920640162</v>
+        <v>46162.55873068287</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46162.5075959838</v>
+        <v>46162.674262650464</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>190</v>
@@ -8677,11 +8677,11 @@
         <v>317</v>
       </c>
       <c r="B118" s="5">
-        <v>46162.39206834491</v>
+        <v>46162.558735011575</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46162.507592546295</v>
+        <v>46162.67425921296</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>190</v>
@@ -8730,11 +8730,11 @@
         <v>318</v>
       </c>
       <c r="B119" s="9">
-        <v>46162.39207284722</v>
+        <v>46162.55873951389</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46162.507589664354</v>
+        <v>46162.67425633102</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>190</v>
@@ -8783,11 +8783,11 @@
         <v>320</v>
       </c>
       <c r="B120" s="5">
-        <v>46162.392077199074</v>
+        <v>46162.55874386574</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46162.50758671296</v>
+        <v>46162.674253379635</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>190</v>
@@ -8836,11 +8836,11 @@
         <v>321</v>
       </c>
       <c r="B121" s="9">
-        <v>46162.39208146991</v>
+        <v>46162.55874813657</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46162.50758333333</v>
+        <v>46162.67425</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>196</v>
@@ -8889,11 +8889,11 @@
         <v>322</v>
       </c>
       <c r="B122" s="5">
-        <v>46162.398500358795</v>
+        <v>46162.56516702546</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46162.5075803588</v>
+        <v>46162.67424702546</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>196</v>
@@ -8942,11 +8942,11 @@
         <v>323</v>
       </c>
       <c r="B123" s="9">
-        <v>46162.398507164355</v>
+        <v>46162.56517383102</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46162.507577627315</v>
+        <v>46162.67424429399</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>196</v>
@@ -8995,11 +8995,11 @@
         <v>324</v>
       </c>
       <c r="B124" s="5">
-        <v>46162.3985144676</v>
+        <v>46162.565181134254</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46162.50756665509</v>
+        <v>46162.674233321755</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>196</v>
@@ -9048,11 +9048,11 @@
         <v>325</v>
       </c>
       <c r="B125" s="9">
-        <v>46162.39852253472</v>
+        <v>46162.565189201385</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46162.50756597222</v>
+        <v>46162.67423263889</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>196</v>
@@ -9101,11 +9101,11 @@
         <v>326</v>
       </c>
       <c r="B126" s="5">
-        <v>46162.39853013889</v>
+        <v>46162.56519680556</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46162.507565277774</v>
+        <v>46162.674231944446</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>196</v>
@@ -9154,11 +9154,11 @@
         <v>327</v>
       </c>
       <c r="B127" s="9">
-        <v>46162.39853892361</v>
+        <v>46162.565205590276</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46162.50756459491</v>
+        <v>46162.674231261575</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>196</v>
@@ -9207,11 +9207,11 @@
         <v>328</v>
       </c>
       <c r="B128" s="5">
-        <v>46162.39854534723</v>
+        <v>46162.565212013884</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46162.507563935185</v>
+        <v>46162.67423060186</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>196</v>
@@ -9260,11 +9260,11 @@
         <v>329</v>
       </c>
       <c r="B129" s="9">
-        <v>46162.39208488426</v>
+        <v>46162.558751550925</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46162.50733674769</v>
+        <v>46162.67400341435</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>330</v>
@@ -9323,11 +9323,11 @@
         <v>331</v>
       </c>
       <c r="B130" s="5">
-        <v>46162.39208957176</v>
+        <v>46162.558756238424</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46198.62671924768</v>
+        <v>46198.79338591435</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>190</v>
@@ -9374,11 +9374,11 @@
         <v>334</v>
       </c>
       <c r="B131" s="9">
-        <v>46162.39209538195</v>
+        <v>46162.55876204861</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46198.62671974537</v>
+        <v>46198.79338641204</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>190</v>
@@ -9425,11 +9425,11 @@
         <v>336</v>
       </c>
       <c r="B132" s="5">
-        <v>46162.39210078704</v>
+        <v>46162.55876745371</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46198.62672202547</v>
+        <v>46198.79338869213</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>190</v>
@@ -9476,11 +9476,11 @@
         <v>339</v>
       </c>
       <c r="B133" s="9">
-        <v>46162.39210722222</v>
+        <v>46162.558773888886</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46198.62672233796</v>
+        <v>46198.793389004626</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>190</v>
@@ -9527,11 +9527,11 @@
         <v>340</v>
       </c>
       <c r="B134" s="5">
-        <v>46162.39216076389</v>
+        <v>46162.558827430556</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46162.50771856481</v>
+        <v>46162.67438523148</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>196</v>
@@ -9578,11 +9578,11 @@
         <v>342</v>
       </c>
       <c r="B135" s="9">
-        <v>46162.39881056713</v>
+        <v>46162.565477233795</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46198.62670313657</v>
+        <v>46198.79336980324</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>196</v>
@@ -9629,11 +9629,11 @@
         <v>344</v>
       </c>
       <c r="B136" s="5">
-        <v>46162.398818726855</v>
+        <v>46162.56548539352</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46198.6267037963</v>
+        <v>46198.79337046296</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>196</v>
@@ -9680,11 +9680,11 @@
         <v>346</v>
       </c>
       <c r="B137" s="9">
-        <v>46162.39882753472</v>
+        <v>46162.56549420139</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46198.62670444444</v>
+        <v>46198.79337111111</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>196</v>
@@ -9731,11 +9731,11 @@
         <v>347</v>
       </c>
       <c r="B138" s="5">
-        <v>46162.39883314815</v>
+        <v>46162.56549981482</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46198.62670504629</v>
+        <v>46198.79337171296</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>196</v>
@@ -9782,11 +9782,11 @@
         <v>349</v>
       </c>
       <c r="B139" s="9">
-        <v>46162.39884105324</v>
+        <v>46162.565507719904</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46198.62670559028</v>
+        <v>46198.79337225694</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>196</v>
@@ -9833,11 +9833,11 @@
         <v>350</v>
       </c>
       <c r="B140" s="5">
-        <v>46162.39884971065</v>
+        <v>46162.56551637732</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46162.50769734954</v>
+        <v>46162.6743640162</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>196</v>
@@ -9884,11 +9884,11 @@
         <v>352</v>
       </c>
       <c r="B141" s="9">
-        <v>46162.399315393515</v>
+        <v>46162.56598206019</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46162.507695636574</v>
+        <v>46162.67436230324</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>196</v>
@@ -9935,11 +9935,11 @@
         <v>353</v>
       </c>
       <c r="B142" s="5">
-        <v>46162.392166875</v>
+        <v>46162.55883354167</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46162.507333483794</v>
+        <v>46162.674000150466</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>354</v>
@@ -9998,11 +9998,11 @@
         <v>355</v>
       </c>
       <c r="B143" s="9">
-        <v>46162.392172314816</v>
+        <v>46162.55883898148</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46198.62672006944</v>
+        <v>46198.79338673611</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>190</v>
@@ -10051,11 +10051,11 @@
         <v>357</v>
       </c>
       <c r="B144" s="5">
-        <v>46162.39217951389</v>
+        <v>46162.55884618056</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46198.62672042824</v>
+        <v>46198.793387094905</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>190</v>
@@ -10104,11 +10104,11 @@
         <v>359</v>
       </c>
       <c r="B145" s="9">
-        <v>46162.392186689816</v>
+        <v>46162.55885335648</v>
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46198.626720740736</v>
+        <v>46198.79338740741</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>190</v>
@@ -10157,11 +10157,11 @@
         <v>361</v>
       </c>
       <c r="B146" s="5">
-        <v>46162.39219395834</v>
+        <v>46162.558860624995</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46198.62672119213</v>
+        <v>46198.793387858794</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>190</v>
@@ -10210,11 +10210,11 @@
         <v>363</v>
       </c>
       <c r="B147" s="9">
-        <v>46162.39220072917</v>
+        <v>46162.558867395834</v>
       </c>
       <c r="C147" s="10"/>
       <c r="D147" s="9">
-        <v>46162.50785829861</v>
+        <v>46162.674524965274</v>
       </c>
       <c r="E147" s="10" t="s">
         <v>196</v>
@@ -10263,11 +10263,11 @@
         <v>365</v>
       </c>
       <c r="B148" s="5">
-        <v>46162.399479699074</v>
+        <v>46162.566146365745</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46162.5078546875</v>
+        <v>46162.674521354165</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>196</v>
@@ -10316,11 +10316,11 @@
         <v>367</v>
       </c>
       <c r="B149" s="9">
-        <v>46162.399486435184</v>
+        <v>46162.566153101856</v>
       </c>
       <c r="C149" s="10"/>
       <c r="D149" s="9">
-        <v>46162.5078512037</v>
+        <v>46162.67451787037</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>196</v>
@@ -10369,11 +10369,11 @@
         <v>368</v>
       </c>
       <c r="B150" s="5">
-        <v>46162.399504444445</v>
+        <v>46162.56617111111</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46162.50784835649</v>
+        <v>46162.67451502314</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>196</v>
@@ -10422,11 +10422,11 @@
         <v>369</v>
       </c>
       <c r="B151" s="9">
-        <v>46162.399514386576</v>
+        <v>46162.56618105324</v>
       </c>
       <c r="C151" s="10"/>
       <c r="D151" s="9">
-        <v>46162.50784576389</v>
+        <v>46162.67451243056</v>
       </c>
       <c r="E151" s="10" t="s">
         <v>348</v>
@@ -10475,11 +10475,11 @@
         <v>370</v>
       </c>
       <c r="B152" s="5">
-        <v>46162.39952320602</v>
+        <v>46162.56618987268</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46162.507836689816</v>
+        <v>46162.67450335648</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>196</v>
@@ -10528,11 +10528,11 @@
         <v>371</v>
       </c>
       <c r="B153" s="9">
-        <v>46162.39953605324</v>
+        <v>46162.56620271991</v>
       </c>
       <c r="C153" s="10"/>
       <c r="D153" s="9">
-        <v>46162.507835972225</v>
+        <v>46162.67450263889</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>196</v>
@@ -10581,11 +10581,11 @@
         <v>372</v>
       </c>
       <c r="B154" s="5">
-        <v>46162.39954006944</v>
+        <v>46162.56620673611</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46162.507835219905</v>
+        <v>46162.67450188658</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>196</v>
@@ -10634,11 +10634,11 @@
         <v>373</v>
       </c>
       <c r="B155" s="9">
-        <v>46162.3922049074</v>
+        <v>46162.558871574074</v>
       </c>
       <c r="C155" s="10"/>
       <c r="D155" s="9">
-        <v>46162.507330532404</v>
+        <v>46162.673997199076</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>374</v>
@@ -10697,11 +10697,11 @@
         <v>376</v>
       </c>
       <c r="B156" s="5">
-        <v>46162.39220956019</v>
+        <v>46162.55887622685</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46198.62670953704</v>
+        <v>46198.7933762037</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>190</v>
@@ -10750,11 +10750,11 @@
         <v>379</v>
       </c>
       <c r="B157" s="9">
-        <v>46162.39221634259</v>
+        <v>46162.55888300926</v>
       </c>
       <c r="C157" s="10"/>
       <c r="D157" s="9">
-        <v>46198.62670988426</v>
+        <v>46198.79337655092</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>190</v>
@@ -10803,11 +10803,11 @@
         <v>380</v>
       </c>
       <c r="B158" s="5">
-        <v>46162.39222591435</v>
+        <v>46162.558892581015</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46198.62672270833</v>
+        <v>46198.793389375</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>190</v>
@@ -10856,11 +10856,11 @@
         <v>382</v>
       </c>
       <c r="B159" s="9">
-        <v>46162.3922319213</v>
+        <v>46162.55889858796</v>
       </c>
       <c r="C159" s="10"/>
       <c r="D159" s="9">
-        <v>46198.626718252315</v>
+        <v>46198.79338491899</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>190</v>
@@ -10909,11 +10909,11 @@
         <v>384</v>
       </c>
       <c r="B160" s="5">
-        <v>46162.39223795139</v>
+        <v>46162.558904618054</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46162.50801568287</v>
+        <v>46162.674682349534</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>196</v>
@@ -10962,11 +10962,11 @@
         <v>386</v>
       </c>
       <c r="B161" s="9">
-        <v>46162.399712708335</v>
+        <v>46162.566379375</v>
       </c>
       <c r="C161" s="10"/>
       <c r="D161" s="9">
-        <v>46162.50801222222</v>
+        <v>46162.674678888885</v>
       </c>
       <c r="E161" s="10" t="s">
         <v>196</v>
@@ -11015,11 +11015,11 @@
         <v>389</v>
       </c>
       <c r="B162" s="5">
-        <v>46162.39972028935</v>
+        <v>46162.56638695602</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46162.50800920139</v>
+        <v>46162.67467586805</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>196</v>
@@ -11068,11 +11068,11 @@
         <v>390</v>
       </c>
       <c r="B163" s="9">
-        <v>46162.39972865741</v>
+        <v>46162.56639532407</v>
       </c>
       <c r="C163" s="10"/>
       <c r="D163" s="9">
-        <v>46162.50800648148</v>
+        <v>46162.67467314815</v>
       </c>
       <c r="E163" s="10" t="s">
         <v>196</v>
@@ -11121,11 +11121,11 @@
         <v>392</v>
       </c>
       <c r="B164" s="5">
-        <v>46162.39973752315</v>
+        <v>46162.56640418981</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46162.508003634255</v>
+        <v>46162.67467030093</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>196</v>
@@ -11174,11 +11174,11 @@
         <v>395</v>
       </c>
       <c r="B165" s="9">
-        <v>46162.39974574074</v>
+        <v>46162.56641240741</v>
       </c>
       <c r="C165" s="10"/>
       <c r="D165" s="9">
-        <v>46162.50799572917</v>
+        <v>46162.67466239583</v>
       </c>
       <c r="E165" s="10" t="s">
         <v>196</v>
@@ -11227,11 +11227,11 @@
         <v>396</v>
       </c>
       <c r="B166" s="5">
-        <v>46162.399753668986</v>
+        <v>46162.56642033564</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46162.507994988424</v>
+        <v>46162.674661655095</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>196</v>
@@ -11280,11 +11280,11 @@
         <v>397</v>
       </c>
       <c r="B167" s="9">
-        <v>46162.39976104167</v>
+        <v>46162.566427708334</v>
       </c>
       <c r="C167" s="10"/>
       <c r="D167" s="9">
-        <v>46162.50799430556</v>
+        <v>46162.67466097222</v>
       </c>
       <c r="E167" s="10" t="s">
         <v>196</v>
@@ -11333,11 +11333,11 @@
         <v>398</v>
       </c>
       <c r="B168" s="5">
-        <v>46162.3922422801</v>
+        <v>46162.558908946754</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46162.50732726852</v>
+        <v>46162.67399393518</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>399</v>
@@ -11396,11 +11396,11 @@
         <v>400</v>
       </c>
       <c r="B169" s="9">
-        <v>46162.39224702546</v>
+        <v>46162.55891369213</v>
       </c>
       <c r="C169" s="10"/>
       <c r="D169" s="9">
-        <v>46162.508169189816</v>
+        <v>46162.67483585648</v>
       </c>
       <c r="E169" s="10" t="s">
         <v>190</v>
@@ -11447,11 +11447,11 @@
         <v>402</v>
       </c>
       <c r="B170" s="5">
-        <v>46162.39225263889</v>
+        <v>46162.55891930556</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46162.50816618056</v>
+        <v>46162.674832847224</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>190</v>
@@ -11498,11 +11498,11 @@
         <v>403</v>
       </c>
       <c r="B171" s="9">
-        <v>46162.39225826389</v>
+        <v>46162.558924930556</v>
       </c>
       <c r="C171" s="10"/>
       <c r="D171" s="9">
-        <v>46162.508162962964</v>
+        <v>46162.67482962963</v>
       </c>
       <c r="E171" s="10" t="s">
         <v>190</v>
@@ -11549,11 +11549,11 @@
         <v>405</v>
       </c>
       <c r="B172" s="5">
-        <v>46162.392264375</v>
+        <v>46162.55893104167</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46162.5081602662</v>
+        <v>46162.67482693287</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>190</v>
@@ -11600,11 +11600,11 @@
         <v>406</v>
       </c>
       <c r="B173" s="9">
-        <v>46162.39226980324</v>
+        <v>46162.55893646991</v>
       </c>
       <c r="C173" s="10"/>
       <c r="D173" s="9">
-        <v>46162.508157476856</v>
+        <v>46162.67482414352</v>
       </c>
       <c r="E173" s="10" t="s">
         <v>196</v>
@@ -11651,11 +11651,11 @@
         <v>408</v>
       </c>
       <c r="B174" s="5">
-        <v>46162.40065422453</v>
+        <v>46162.567320891205</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46162.50815461806</v>
+        <v>46162.67482128472</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>196</v>
@@ -11702,11 +11702,11 @@
         <v>409</v>
       </c>
       <c r="B175" s="9">
-        <v>46162.400663368055</v>
+        <v>46162.567330034726</v>
       </c>
       <c r="C175" s="10"/>
       <c r="D175" s="9">
-        <v>46162.5081515162</v>
+        <v>46162.67481818287</v>
       </c>
       <c r="E175" s="10" t="s">
         <v>196</v>
@@ -11753,11 +11753,11 @@
         <v>410</v>
       </c>
       <c r="B176" s="5">
-        <v>46162.40067101852</v>
+        <v>46162.567337685185</v>
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46162.508148877314</v>
+        <v>46162.674815543985</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>196</v>
@@ -11804,11 +11804,11 @@
         <v>411</v>
       </c>
       <c r="B177" s="9">
-        <v>46162.4006775</v>
+        <v>46162.567344166666</v>
       </c>
       <c r="C177" s="10"/>
       <c r="D177" s="9">
-        <v>46162.50814607639</v>
+        <v>46162.674812743055</v>
       </c>
       <c r="E177" s="10" t="s">
         <v>196</v>
@@ -11855,11 +11855,11 @@
         <v>412</v>
       </c>
       <c r="B178" s="5">
-        <v>46162.4006846875</v>
+        <v>46162.56735135417</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46162.508138310186</v>
+        <v>46162.67480497685</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>196</v>
@@ -11906,11 +11906,11 @@
         <v>413</v>
       </c>
       <c r="B179" s="9">
-        <v>46162.40069239584</v>
+        <v>46162.5673590625</v>
       </c>
       <c r="C179" s="10"/>
       <c r="D179" s="9">
-        <v>46162.50813765047</v>
+        <v>46162.674804317125</v>
       </c>
       <c r="E179" s="10" t="s">
         <v>196</v>
@@ -11957,11 +11957,11 @@
         <v>414</v>
       </c>
       <c r="B180" s="5">
-        <v>46162.400699618054</v>
+        <v>46162.567366284726</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46162.5081369213</v>
+        <v>46162.674803587965</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>196</v>
@@ -12008,11 +12008,11 @@
         <v>415</v>
       </c>
       <c r="B181" s="9">
-        <v>46162.392275011574</v>
+        <v>46162.558941678246</v>
       </c>
       <c r="C181" s="10"/>
       <c r="D181" s="9">
-        <v>46162.507321122685</v>
+        <v>46162.673987789356</v>
       </c>
       <c r="E181" s="10" t="s">
         <v>416</v>
@@ -12071,11 +12071,11 @@
         <v>418</v>
       </c>
       <c r="B182" s="5">
-        <v>46162.392280520835</v>
+        <v>46162.5589471875</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46162.50841818287</v>
+        <v>46162.675084849536</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>190</v>
@@ -12122,11 +12122,11 @@
         <v>420</v>
       </c>
       <c r="B183" s="9">
-        <v>46162.39228517361</v>
+        <v>46162.55895184028</v>
       </c>
       <c r="C183" s="10"/>
       <c r="D183" s="9">
-        <v>46162.5084152662</v>
+        <v>46162.67508193287</v>
       </c>
       <c r="E183" s="10" t="s">
         <v>190</v>
@@ -12173,11 +12173,11 @@
         <v>421</v>
       </c>
       <c r="B184" s="5">
-        <v>46162.39228988426</v>
+        <v>46162.55895655093</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46162.50841202546</v>
+        <v>46162.67507869213</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>190</v>
@@ -12224,11 +12224,11 @@
         <v>423</v>
       </c>
       <c r="B185" s="9">
-        <v>46162.392329270835</v>
+        <v>46162.5589959375</v>
       </c>
       <c r="C185" s="10"/>
       <c r="D185" s="9">
-        <v>46162.50840944445</v>
+        <v>46162.67507611111</v>
       </c>
       <c r="E185" s="10" t="s">
         <v>190</v>
@@ -12275,11 +12275,11 @@
         <v>424</v>
       </c>
       <c r="B186" s="5">
-        <v>46162.39233469908</v>
+        <v>46162.55900136574</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46162.50840641204</v>
+        <v>46162.6750730787</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>196</v>
@@ -12326,11 +12326,11 @@
         <v>426</v>
       </c>
       <c r="B187" s="9">
-        <v>46162.40092486111</v>
+        <v>46162.56759152778</v>
       </c>
       <c r="C187" s="10"/>
       <c r="D187" s="9">
-        <v>46162.50840348379</v>
+        <v>46162.675070150464</v>
       </c>
       <c r="E187" s="10" t="s">
         <v>196</v>
@@ -12377,11 +12377,11 @@
         <v>427</v>
       </c>
       <c r="B188" s="5">
-        <v>46162.40093179398</v>
+        <v>46162.56759846065</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46162.50840078703</v>
+        <v>46162.6750674537</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>196</v>
@@ -12428,11 +12428,11 @@
         <v>428</v>
       </c>
       <c r="B189" s="9">
-        <v>46162.4009400463</v>
+        <v>46162.56760671297</v>
       </c>
       <c r="C189" s="10"/>
       <c r="D189" s="9">
-        <v>46162.50839821759</v>
+        <v>46162.67506488426</v>
       </c>
       <c r="E189" s="10" t="s">
         <v>196</v>
@@ -12479,11 +12479,11 @@
         <v>429</v>
       </c>
       <c r="B190" s="5">
-        <v>46162.4009475</v>
+        <v>46162.56761416666</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46162.50839497685</v>
+        <v>46162.67506164352</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>196</v>
@@ -12530,11 +12530,11 @@
         <v>430</v>
       </c>
       <c r="B191" s="9">
-        <v>46162.400955543984</v>
+        <v>46162.56762221065</v>
       </c>
       <c r="C191" s="10"/>
       <c r="D191" s="9">
-        <v>46162.508387800925</v>
+        <v>46162.67505446759</v>
       </c>
       <c r="E191" s="10" t="s">
         <v>196</v>
@@ -12581,11 +12581,11 @@
         <v>431</v>
       </c>
       <c r="B192" s="5">
-        <v>46162.400961886575</v>
+        <v>46162.56762855324</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46162.50838708333</v>
+        <v>46162.675053750005</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>196</v>
@@ -12632,11 +12632,11 @@
         <v>432</v>
       </c>
       <c r="B193" s="9">
-        <v>46162.40096748843</v>
+        <v>46162.56763415509</v>
       </c>
       <c r="C193" s="10"/>
       <c r="D193" s="9">
-        <v>46162.508386354166</v>
+        <v>46162.67505302084</v>
       </c>
       <c r="E193" s="10" t="s">
         <v>196</v>
@@ -12683,11 +12683,11 @@
         <v>433</v>
       </c>
       <c r="B194" s="5">
-        <v>46162.39233899306</v>
+        <v>46162.55900565972</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46162.49727244213</v>
+        <v>46162.663939108796</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>434</v>
@@ -12730,11 +12730,11 @@
         <v>436</v>
       </c>
       <c r="B195" s="9">
-        <v>46162.392342743056</v>
+        <v>46162.55900940972</v>
       </c>
       <c r="C195" s="10"/>
       <c r="D195" s="9">
-        <v>46162.508735625</v>
+        <v>46162.67540229167</v>
       </c>
       <c r="E195" s="10" t="s">
         <v>437</v>
@@ -12793,11 +12793,11 @@
         <v>441</v>
       </c>
       <c r="B196" s="5">
-        <v>46162.39234835649</v>
+        <v>46162.559015023144</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46162.508718391204</v>
+        <v>46162.67538505787</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>190</v>
@@ -12844,11 +12844,11 @@
         <v>443</v>
       </c>
       <c r="B197" s="9">
-        <v>46162.39235273148</v>
+        <v>46162.55901939815</v>
       </c>
       <c r="C197" s="10"/>
       <c r="D197" s="9">
-        <v>46162.508715868054</v>
+        <v>46162.675382534726</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>190</v>
@@ -12895,11 +12895,11 @@
         <v>444</v>
       </c>
       <c r="B198" s="5">
-        <v>46162.39235722223</v>
+        <v>46162.55902388888</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46162.50871324074</v>
+        <v>46162.67537990741</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>190</v>
@@ -12946,11 +12946,11 @@
         <v>445</v>
       </c>
       <c r="B199" s="9">
-        <v>46162.39236142361</v>
+        <v>46162.559028090276</v>
       </c>
       <c r="C199" s="10"/>
       <c r="D199" s="9">
-        <v>46162.508710486116</v>
+        <v>46162.67537715277</v>
       </c>
       <c r="E199" s="10" t="s">
         <v>190</v>
@@ -12997,11 +12997,11 @@
         <v>446</v>
       </c>
       <c r="B200" s="5">
-        <v>46162.39236539352</v>
+        <v>46162.559032060184</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46162.50870751157</v>
+        <v>46162.675374178245</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>196</v>
@@ -13048,11 +13048,11 @@
         <v>448</v>
       </c>
       <c r="B201" s="9">
-        <v>46162.40180416667</v>
+        <v>46162.56847083333</v>
       </c>
       <c r="C201" s="10"/>
       <c r="D201" s="9">
-        <v>46162.508704629625</v>
+        <v>46162.675371296296</v>
       </c>
       <c r="E201" s="10" t="s">
         <v>196</v>
@@ -13099,11 +13099,11 @@
         <v>449</v>
       </c>
       <c r="B202" s="5">
-        <v>46162.40181119213</v>
+        <v>46162.5684778588</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46162.5087016551</v>
+        <v>46162.675368321754</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>196</v>
@@ -13150,11 +13150,11 @@
         <v>450</v>
       </c>
       <c r="B203" s="9">
-        <v>46162.40181916667</v>
+        <v>46162.56848583333</v>
       </c>
       <c r="C203" s="10"/>
       <c r="D203" s="9">
-        <v>46162.50869899306</v>
+        <v>46162.67536565972</v>
       </c>
       <c r="E203" s="10" t="s">
         <v>196</v>
@@ -13201,11 +13201,11 @@
         <v>451</v>
       </c>
       <c r="B204" s="5">
-        <v>46162.40182649306</v>
+        <v>46162.56849315972</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46162.508696296296</v>
+        <v>46162.67536296297</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>196</v>
@@ -13252,11 +13252,11 @@
         <v>452</v>
       </c>
       <c r="B205" s="9">
-        <v>46162.4018324537</v>
+        <v>46162.568499120374</v>
       </c>
       <c r="C205" s="10"/>
       <c r="D205" s="9">
-        <v>46162.50868840278</v>
+        <v>46162.67535506944</v>
       </c>
       <c r="E205" s="10" t="s">
         <v>196</v>
@@ -13303,11 +13303,11 @@
         <v>453</v>
       </c>
       <c r="B206" s="5">
-        <v>46162.40184034722</v>
+        <v>46162.568507013886</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46162.50868773148</v>
+        <v>46162.67535439815</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>196</v>
@@ -13354,11 +13354,11 @@
         <v>454</v>
       </c>
       <c r="B207" s="9">
-        <v>46162.40184909722</v>
+        <v>46162.56851576389</v>
       </c>
       <c r="C207" s="10"/>
       <c r="D207" s="9">
-        <v>46162.508687071764</v>
+        <v>46162.67535373842</v>
       </c>
       <c r="E207" s="10" t="s">
         <v>196</v>
@@ -13405,11 +13405,11 @@
         <v>455</v>
       </c>
       <c r="B208" s="5">
-        <v>46162.39236931713</v>
+        <v>46162.559035983795</v>
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46162.50893476851</v>
+        <v>46162.675601435185</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>456</v>
@@ -13468,11 +13468,11 @@
         <v>457</v>
       </c>
       <c r="B209" s="9">
-        <v>46162.39237339121</v>
+        <v>46162.559040057866</v>
       </c>
       <c r="C209" s="10"/>
       <c r="D209" s="9">
-        <v>46162.50892731482</v>
+        <v>46162.67559398148</v>
       </c>
       <c r="E209" s="10" t="s">
         <v>190</v>
@@ -13519,11 +13519,11 @@
         <v>459</v>
       </c>
       <c r="B210" s="5">
-        <v>46162.392377638884</v>
+        <v>46162.559044305555</v>
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46162.50892451389</v>
+        <v>46162.67559118055</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>190</v>
@@ -13570,11 +13570,11 @@
         <v>460</v>
       </c>
       <c r="B211" s="9">
-        <v>46162.39238175926</v>
+        <v>46162.55904842593</v>
       </c>
       <c r="C211" s="10"/>
       <c r="D211" s="9">
-        <v>46162.50892172454</v>
+        <v>46162.675588391205</v>
       </c>
       <c r="E211" s="10" t="s">
         <v>190</v>
@@ -13621,11 +13621,11 @@
         <v>461</v>
       </c>
       <c r="B212" s="5">
-        <v>46162.39238575232</v>
+        <v>46162.55905241898</v>
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46162.508918935186</v>
+        <v>46162.67558560186</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>190</v>
@@ -13672,11 +13672,11 @@
         <v>462</v>
       </c>
       <c r="B213" s="9">
-        <v>46162.392389768516</v>
+        <v>46162.55905643519</v>
       </c>
       <c r="C213" s="10"/>
       <c r="D213" s="9">
-        <v>46162.50891618055</v>
+        <v>46162.67558284722</v>
       </c>
       <c r="E213" s="10" t="s">
         <v>196</v>
@@ -13723,11 +13723,11 @@
         <v>464</v>
       </c>
       <c r="B214" s="5">
-        <v>46162.40212766203</v>
+        <v>46162.568794328705</v>
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46162.508913067126</v>
+        <v>46162.6755797338</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>196</v>
@@ -13774,11 +13774,11 @@
         <v>465</v>
       </c>
       <c r="B215" s="9">
-        <v>46162.40213472222</v>
+        <v>46162.56880138889</v>
       </c>
       <c r="C215" s="10"/>
       <c r="D215" s="9">
-        <v>46162.50891030092</v>
+        <v>46162.675576967595</v>
       </c>
       <c r="E215" s="10" t="s">
         <v>196</v>
@@ -13825,11 +13825,11 @@
         <v>466</v>
       </c>
       <c r="B216" s="5">
-        <v>46162.402141412036</v>
+        <v>46162.56880807871</v>
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46162.50890765047</v>
+        <v>46162.67557431713</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>196</v>
@@ -13876,11 +13876,11 @@
         <v>468</v>
       </c>
       <c r="B217" s="9">
-        <v>46162.40214881944</v>
+        <v>46162.56881548611</v>
       </c>
       <c r="C217" s="10"/>
       <c r="D217" s="9">
-        <v>46162.508904953705</v>
+        <v>46162.67557162037</v>
       </c>
       <c r="E217" s="10" t="s">
         <v>196</v>
@@ -13927,11 +13927,11 @@
         <v>469</v>
       </c>
       <c r="B218" s="5">
-        <v>46162.402155821765</v>
+        <v>46162.56882248842</v>
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46162.50889708333</v>
+        <v>46162.67556375</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>196</v>
@@ -13978,11 +13978,11 @@
         <v>470</v>
       </c>
       <c r="B219" s="9">
-        <v>46162.40216304398</v>
+        <v>46162.56882971065</v>
       </c>
       <c r="C219" s="10"/>
       <c r="D219" s="9">
-        <v>46162.508896354164</v>
+        <v>46162.675563020835</v>
       </c>
       <c r="E219" s="10" t="s">
         <v>196</v>
@@ -14029,11 +14029,11 @@
         <v>471</v>
       </c>
       <c r="B220" s="5">
-        <v>46162.40217094908</v>
+        <v>46162.56883761574</v>
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46162.50889563657</v>
+        <v>46162.67556230324</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>196</v>
@@ -14080,11 +14080,11 @@
         <v>472</v>
       </c>
       <c r="B221" s="9">
-        <v>46162.39239400463</v>
+        <v>46162.559060671294</v>
       </c>
       <c r="C221" s="10"/>
       <c r="D221" s="9">
-        <v>46162.50912635417</v>
+        <v>46162.67579302083</v>
       </c>
       <c r="E221" s="10" t="s">
         <v>473</v>
@@ -14143,11 +14143,11 @@
         <v>474</v>
       </c>
       <c r="B222" s="5">
-        <v>46162.392398055556</v>
+        <v>46162.55906472223</v>
       </c>
       <c r="C222" s="6"/>
       <c r="D222" s="5">
-        <v>46162.50912783565</v>
+        <v>46162.67579450231</v>
       </c>
       <c r="E222" s="6" t="s">
         <v>190</v>
@@ -14194,11 +14194,11 @@
         <v>476</v>
       </c>
       <c r="B223" s="9">
-        <v>46162.392405694445</v>
+        <v>46162.55907236111</v>
       </c>
       <c r="C223" s="10"/>
       <c r="D223" s="9">
-        <v>46162.50912484954</v>
+        <v>46162.6757915162</v>
       </c>
       <c r="E223" s="10" t="s">
         <v>190</v>
@@ -14245,11 +14245,11 @@
         <v>477</v>
       </c>
       <c r="B224" s="5">
-        <v>46162.39241195602</v>
+        <v>46162.55907862268</v>
       </c>
       <c r="C224" s="6"/>
       <c r="D224" s="5">
-        <v>46162.509121967596</v>
+        <v>46162.67578863426</v>
       </c>
       <c r="E224" s="6" t="s">
         <v>190</v>
@@ -14296,11 +14296,11 @@
         <v>479</v>
       </c>
       <c r="B225" s="9">
-        <v>46162.39241637732</v>
+        <v>46162.55908304398</v>
       </c>
       <c r="C225" s="10"/>
       <c r="D225" s="9">
-        <v>46162.509119236114</v>
+        <v>46162.67578590278</v>
       </c>
       <c r="E225" s="10" t="s">
         <v>190</v>
@@ -14347,11 +14347,11 @@
         <v>480</v>
       </c>
       <c r="B226" s="5">
-        <v>46162.39242053241</v>
+        <v>46162.55908719907</v>
       </c>
       <c r="C226" s="6"/>
       <c r="D226" s="5">
-        <v>46162.50911622685</v>
+        <v>46162.67578289352</v>
       </c>
       <c r="E226" s="6" t="s">
         <v>196</v>
@@ -14398,11 +14398,11 @@
         <v>482</v>
       </c>
       <c r="B227" s="9">
-        <v>46162.40234565972</v>
+        <v>46162.56901232639</v>
       </c>
       <c r="C227" s="10"/>
       <c r="D227" s="9">
-        <v>46162.50911296296</v>
+        <v>46162.67577962963</v>
       </c>
       <c r="E227" s="10" t="s">
         <v>196</v>
@@ -14449,11 +14449,11 @@
         <v>483</v>
       </c>
       <c r="B228" s="5">
-        <v>46162.40235222223</v>
+        <v>46162.569018888884</v>
       </c>
       <c r="C228" s="6"/>
       <c r="D228" s="5">
-        <v>46162.50911028935</v>
+        <v>46162.67577695602</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>196</v>
@@ -14500,11 +14500,11 @@
         <v>484</v>
       </c>
       <c r="B229" s="9">
-        <v>46162.40236021991</v>
+        <v>46162.56902688657</v>
       </c>
       <c r="C229" s="10"/>
       <c r="D229" s="9">
-        <v>46162.50910744213</v>
+        <v>46162.67577410879</v>
       </c>
       <c r="E229" s="10" t="s">
         <v>467</v>
@@ -14551,11 +14551,11 @@
         <v>485</v>
       </c>
       <c r="B230" s="5">
-        <v>46162.40236625</v>
+        <v>46162.56903291667</v>
       </c>
       <c r="C230" s="6"/>
       <c r="D230" s="5">
-        <v>46162.5091049537</v>
+        <v>46162.67577162037</v>
       </c>
       <c r="E230" s="6" t="s">
         <v>196</v>
@@ -14602,11 +14602,11 @@
         <v>486</v>
       </c>
       <c r="B231" s="9">
-        <v>46162.40237322917</v>
+        <v>46162.56903989583</v>
       </c>
       <c r="C231" s="10"/>
       <c r="D231" s="9">
-        <v>46162.509097256945</v>
+        <v>46162.67576392361</v>
       </c>
       <c r="E231" s="10" t="s">
         <v>196</v>
@@ -14653,11 +14653,11 @@
         <v>487</v>
       </c>
       <c r="B232" s="5">
-        <v>46162.4023796875</v>
+        <v>46162.56904635417</v>
       </c>
       <c r="C232" s="6"/>
       <c r="D232" s="5">
-        <v>46162.5090965625</v>
+        <v>46162.67576322917</v>
       </c>
       <c r="E232" s="6" t="s">
         <v>196</v>
@@ -14704,11 +14704,11 @@
         <v>488</v>
       </c>
       <c r="B233" s="9">
-        <v>46162.40238680555</v>
+        <v>46162.56905347222</v>
       </c>
       <c r="C233" s="10"/>
       <c r="D233" s="9">
-        <v>46162.50909585648</v>
+        <v>46162.67576252315</v>
       </c>
       <c r="E233" s="10" t="s">
         <v>196</v>
@@ -14755,11 +14755,11 @@
         <v>489</v>
       </c>
       <c r="B234" s="5">
-        <v>46162.392424618054</v>
+        <v>46162.559091284726</v>
       </c>
       <c r="C234" s="6"/>
       <c r="D234" s="5">
-        <v>46162.509191770834</v>
+        <v>46162.6758584375</v>
       </c>
       <c r="E234" s="6" t="s">
         <v>490</v>
@@ -14818,11 +14818,11 @@
         <v>492</v>
       </c>
       <c r="B235" s="9">
-        <v>46162.392429467596</v>
+        <v>46162.55909613426</v>
       </c>
       <c r="C235" s="10"/>
       <c r="D235" s="9">
-        <v>46162.509360208336</v>
+        <v>46162.676026875</v>
       </c>
       <c r="E235" s="10" t="s">
         <v>190</v>
@@ -14871,11 +14871,11 @@
         <v>493</v>
       </c>
       <c r="B236" s="5">
-        <v>46162.39243346065</v>
+        <v>46162.55910012731</v>
       </c>
       <c r="C236" s="6"/>
       <c r="D236" s="5">
-        <v>46162.509355891205</v>
+        <v>46162.67602255787</v>
       </c>
       <c r="E236" s="6" t="s">
         <v>190</v>
@@ -14924,11 +14924,11 @@
         <v>494</v>
       </c>
       <c r="B237" s="9">
-        <v>46162.39243740741</v>
+        <v>46162.55910407407</v>
       </c>
       <c r="C237" s="10"/>
       <c r="D237" s="9">
-        <v>46162.509352442125</v>
+        <v>46162.676019108796</v>
       </c>
       <c r="E237" s="10" t="s">
         <v>190</v>
@@ -14977,11 +14977,11 @@
         <v>495</v>
       </c>
       <c r="B238" s="5">
-        <v>46162.39244145833</v>
+        <v>46162.559108125</v>
       </c>
       <c r="C238" s="6"/>
       <c r="D238" s="5">
-        <v>46162.50934950232</v>
+        <v>46162.67601616898</v>
       </c>
       <c r="E238" s="6" t="s">
         <v>190</v>
@@ -15030,11 +15030,11 @@
         <v>496</v>
       </c>
       <c r="B239" s="9">
-        <v>46162.392477430556</v>
+        <v>46162.55914409722</v>
       </c>
       <c r="C239" s="10"/>
       <c r="D239" s="9">
-        <v>46162.5093466088</v>
+        <v>46162.676013275464</v>
       </c>
       <c r="E239" s="10" t="s">
         <v>196</v>
@@ -15083,11 +15083,11 @@
         <v>497</v>
       </c>
       <c r="B240" s="5">
-        <v>46162.40292248843</v>
+        <v>46162.56958915509</v>
       </c>
       <c r="C240" s="6"/>
       <c r="D240" s="5">
-        <v>46162.50934305556</v>
+        <v>46162.67600972222</v>
       </c>
       <c r="E240" s="6" t="s">
         <v>196</v>
@@ -15136,11 +15136,11 @@
         <v>498</v>
       </c>
       <c r="B241" s="9">
-        <v>46162.40292921296</v>
+        <v>46162.56959587963</v>
       </c>
       <c r="C241" s="10"/>
       <c r="D241" s="9">
-        <v>46162.509340335644</v>
+        <v>46162.676007002316</v>
       </c>
       <c r="E241" s="10" t="s">
         <v>196</v>
@@ -15189,11 +15189,11 @@
         <v>499</v>
       </c>
       <c r="B242" s="5">
-        <v>46162.40293847222</v>
+        <v>46162.56960513889</v>
       </c>
       <c r="C242" s="6"/>
       <c r="D242" s="5">
-        <v>46162.50933702546</v>
+        <v>46162.67600369213</v>
       </c>
       <c r="E242" s="6" t="s">
         <v>196</v>
@@ -15242,11 +15242,11 @@
         <v>500</v>
       </c>
       <c r="B243" s="9">
-        <v>46162.40294539352</v>
+        <v>46162.569612060186</v>
       </c>
       <c r="C243" s="10"/>
       <c r="D243" s="9">
-        <v>46162.50932924768</v>
+        <v>46162.67599591435</v>
       </c>
       <c r="E243" s="10" t="s">
         <v>196</v>
@@ -15295,11 +15295,11 @@
         <v>501</v>
       </c>
       <c r="B244" s="5">
-        <v>46162.40295333334</v>
+        <v>46162.569619999995</v>
       </c>
       <c r="C244" s="6"/>
       <c r="D244" s="5">
-        <v>46162.50932591435</v>
+        <v>46162.67599258102</v>
       </c>
       <c r="E244" s="6" t="s">
         <v>196</v>
@@ -15348,11 +15348,11 @@
         <v>502</v>
       </c>
       <c r="B245" s="9">
-        <v>46162.40296114583</v>
+        <v>46162.569627812496</v>
       </c>
       <c r="C245" s="10"/>
       <c r="D245" s="9">
-        <v>46162.50932474537</v>
+        <v>46162.675991412034</v>
       </c>
       <c r="E245" s="10" t="s">
         <v>196</v>
@@ -15401,11 +15401,11 @@
         <v>503</v>
       </c>
       <c r="B246" s="5">
-        <v>46162.40296784722</v>
+        <v>46162.569634513886</v>
       </c>
       <c r="C246" s="6"/>
       <c r="D246" s="5">
-        <v>46162.50932394676</v>
+        <v>46162.675990613425</v>
       </c>
       <c r="E246" s="6" t="s">
         <v>196</v>
@@ -15454,11 +15454,11 @@
         <v>504</v>
       </c>
       <c r="B247" s="9">
-        <v>46162.39248275463</v>
+        <v>46162.5591494213</v>
       </c>
       <c r="C247" s="10"/>
       <c r="D247" s="9">
-        <v>46162.49748135416</v>
+        <v>46162.664148020835</v>
       </c>
       <c r="E247" s="10" t="s">
         <v>505</v>
@@ -15501,11 +15501,11 @@
         <v>507</v>
       </c>
       <c r="B248" s="5">
-        <v>46162.39248613426</v>
+        <v>46162.559152800924</v>
       </c>
       <c r="C248" s="6"/>
       <c r="D248" s="5">
-        <v>46162.50939471065</v>
+        <v>46162.676061377315</v>
       </c>
       <c r="E248" s="6" t="s">
         <v>508</v>
@@ -15564,11 +15564,11 @@
         <v>511</v>
       </c>
       <c r="B249" s="9">
-        <v>46162.39249060185</v>
+        <v>46162.55915726852</v>
       </c>
       <c r="C249" s="10"/>
       <c r="D249" s="9">
-        <v>46197.52751465278</v>
+        <v>46197.69418131944</v>
       </c>
       <c r="E249" s="10" t="s">
         <v>512</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -2837,7 +2837,7 @@
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46198.68393108796</v>
+        <v>46206.5583869213</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -3075,9 +3075,11 @@
       <c r="B18" s="5">
         <v>46162.55828883102</v>
       </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="5">
+        <v>46206.558380381946</v>
+      </c>
       <c r="D18" s="5">
-        <v>46198.79339923611</v>
+        <v>46206.558396238426</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -3125,10 +3127,10 @@
         <v>33</v>
       </c>
       <c r="T18" s="6">
-        <v>0</v>
-      </c>
-      <c r="U18" s="12" t="s">
-        <v>47</v>
+        <v>1</v>
+      </c>
+      <c r="U18" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -3138,9 +3140,11 @@
       <c r="B19" s="9">
         <v>46162.55829380787</v>
       </c>
-      <c r="C19" s="10"/>
+      <c r="C19" s="9">
+        <v>46206.55904466435</v>
+      </c>
       <c r="D19" s="9">
-        <v>46198.79340429398</v>
+        <v>46206.55905884259</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>83</v>
@@ -3188,10 +3192,10 @@
         <v>33</v>
       </c>
       <c r="T19" s="10">
-        <v>0</v>
-      </c>
-      <c r="U19" s="12" t="s">
-        <v>47</v>
+        <v>1</v>
+      </c>
+      <c r="U19" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -3201,9 +3205,11 @@
       <c r="B20" s="5">
         <v>46162.55829782407</v>
       </c>
-      <c r="C20" s="6"/>
+      <c r="C20" s="5">
+        <v>46206.559481261575</v>
+      </c>
       <c r="D20" s="5">
-        <v>46198.793399999995</v>
+        <v>46206.55949671296</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -3251,10 +3257,10 @@
         <v>33</v>
       </c>
       <c r="T20" s="6">
-        <v>0</v>
-      </c>
-      <c r="U20" s="12" t="s">
-        <v>47</v>
+        <v>1</v>
+      </c>
+      <c r="U20" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
@@ -3264,9 +3270,11 @@
       <c r="B21" s="9">
         <v>46162.558301446756</v>
       </c>
-      <c r="C21" s="10"/>
+      <c r="C21" s="9">
+        <v>46206.55996136574</v>
+      </c>
       <c r="D21" s="9">
-        <v>46198.793400509254</v>
+        <v>46206.55997537037</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>89</v>
@@ -3314,10 +3322,10 @@
         <v>33</v>
       </c>
       <c r="T21" s="10">
-        <v>0</v>
-      </c>
-      <c r="U21" s="12" t="s">
-        <v>47</v>
+        <v>1</v>
+      </c>
+      <c r="U21" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -4055,7 +4063,7 @@
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46191.16929601852</v>
+        <v>46206.55838853009</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -4236,7 +4244,7 @@
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46191.169293900464</v>
+        <v>46206.559050254626</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>84</v>
@@ -4405,7 +4413,7 @@
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46198.16910141204</v>
+        <v>46206.55996775463</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>90</v>
@@ -4627,7 +4635,7 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46191.169297465276</v>
+        <v>46206.559488425926</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>87</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46202.191681435186</v>
+        <v>46209.16939314815</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>231</v>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46162.672237060186</v>
+        <v>46209.16938944445</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>190</v>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46162.67223377315</v>
+        <v>46209.169390752315</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>190</v>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46162.67223053241</v>
+        <v>46209.169391944444</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>190</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46162.67222738426</v>
+        <v>46209.16938706019</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>190</v>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46162.67222361111</v>
+        <v>46209.16938824074</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>196</v>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46162.672220196764</v>
+        <v>46209.169375474536</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>196</v>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46162.67221694444</v>
+        <v>46209.16937722222</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>196</v>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46162.67221386574</v>
+        <v>46209.169378391205</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>196</v>
@@ -6617,7 +6617,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46162.67221096065</v>
+        <v>46209.1693796412</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>196</v>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46162.67220178241</v>
+        <v>46209.169380775464</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>196</v>
@@ -6723,7 +6723,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46162.67220103009</v>
+        <v>46209.169382175925</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>196</v>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46162.6722002662</v>
+        <v>46209.169383437504</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>196</v>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46162.67249278935</v>
+        <v>46209.17865288194</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>256</v>
@@ -6873,8 +6873,8 @@
       <c r="R84" s="5">
         <v>46216</v>
       </c>
-      <c r="S84" s="7" t="s">
-        <v>54</v>
+      <c r="S84" s="12" t="s">
+        <v>235</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2841" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2842" uniqueCount="513">
   <si>
     <t xml:space="preserve">50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT 4324 4325 </t>
   </si>
@@ -345,16 +345,16 @@
     <t>Fabricación Alabe OT 4324 4325,Generación OC Alabe OT 4324 4325</t>
   </si>
   <si>
+    <t>1214969379038319</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe OT 4324 4325,Alabe OT 4324 4325</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1214969379038319</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe OT 4324 4325,Alabe OT 4324 4325</t>
   </si>
   <si>
     <t>1214969379038337</t>
@@ -2835,9 +2835,11 @@
       <c r="B14" s="5">
         <v>46162.55816920139</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="5">
+        <v>46209.561731678245</v>
+      </c>
       <c r="D14" s="5">
-        <v>46206.5583869213</v>
+        <v>46209.56174483796</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2872,8 +2874,12 @@
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
+      <c r="T14" s="6">
+        <v>1</v>
+      </c>
+      <c r="U14" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
@@ -2947,9 +2953,11 @@
       <c r="B16" s="5">
         <v>46162.55827819444</v>
       </c>
-      <c r="C16" s="6"/>
+      <c r="C16" s="5">
+        <v>46209.56171221065</v>
+      </c>
       <c r="D16" s="5">
-        <v>46197.654558842594</v>
+        <v>46209.56277344907</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>70</v>
@@ -2997,10 +3005,10 @@
         <v>54</v>
       </c>
       <c r="T16" s="6">
-        <v>0</v>
-      </c>
-      <c r="U16" s="12" t="s">
-        <v>47</v>
+        <v>1</v>
+      </c>
+      <c r="U16" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
@@ -3014,7 +3022,7 @@
         <v>46197.58811052083</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.77760189815</v>
+        <v>46209.5628121412</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>73</v>
@@ -3337,7 +3345,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46198.68470386574</v>
+        <v>46209.56216927084</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -3382,9 +3390,11 @@
       <c r="B23" s="9">
         <v>46162.558305694445</v>
       </c>
-      <c r="C23" s="10"/>
+      <c r="C23" s="9">
+        <v>46209.562155300926</v>
+      </c>
       <c r="D23" s="9">
-        <v>46169.86252686342</v>
+        <v>46209.563062939815</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>95</v>
@@ -3432,25 +3442,27 @@
         <v>54</v>
       </c>
       <c r="T23" s="10">
-        <v>0</v>
-      </c>
-      <c r="U23" s="11" t="s">
-        <v>99</v>
+        <v>1</v>
+      </c>
+      <c r="U23" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B24" s="5">
         <v>46162.55831018518</v>
       </c>
-      <c r="C24" s="6"/>
+      <c r="C24" s="5">
+        <v>46209.562107129634</v>
+      </c>
       <c r="D24" s="5">
-        <v>46169.86302510416</v>
+        <v>46209.56210862269</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -3483,7 +3495,7 @@
         <v>70</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -3494,7 +3506,7 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -3504,9 +3516,11 @@
       <c r="B25" s="9">
         <v>46162.55831479166</v>
       </c>
-      <c r="C25" s="10"/>
+      <c r="C25" s="9">
+        <v>46209.562140995375</v>
+      </c>
       <c r="D25" s="9">
-        <v>46169.86304815972</v>
+        <v>46209.56214238426</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>104</v>
@@ -3539,7 +3553,7 @@
         <v>95</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>105</v>
@@ -3553,7 +3567,7 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -3567,7 +3581,7 @@
         <v>46198.68469451389</v>
       </c>
       <c r="D26" s="5">
-        <v>46198.684707002314</v>
+        <v>46209.563100486106</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>107</v>
@@ -3679,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3740,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3866,7 +3880,7 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3927,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -3988,7 +4002,7 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -4051,7 +4065,7 @@
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -4110,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -4169,7 +4183,7 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -4232,7 +4246,7 @@
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -4401,7 +4415,7 @@
         <v>0</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -4623,7 +4637,7 @@
         <v>0</v>
       </c>
       <c r="U43" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -5034,7 +5048,7 @@
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -5756,7 +5770,7 @@
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5819,7 +5833,7 @@
         <v>0</v>
       </c>
       <c r="U65" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5882,7 +5896,7 @@
         <v>0</v>
       </c>
       <c r="U66" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5945,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -6008,7 +6022,7 @@
         <v>0</v>
       </c>
       <c r="U68" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -6071,7 +6085,7 @@
         <v>0</v>
       </c>
       <c r="U69" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -6181,7 +6195,7 @@
         <v>0</v>
       </c>
       <c r="U71" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -6880,7 +6894,7 @@
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -7579,7 +7593,7 @@
         <v>0</v>
       </c>
       <c r="U97" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -8337,7 +8351,7 @@
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46162.673898912035</v>
+        <v>46209.562158773144</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>301</v>
@@ -8387,8 +8401,8 @@
       <c r="T112" s="6">
         <v>0</v>
       </c>
-      <c r="U112" s="11" t="s">
-        <v>99</v>
+      <c r="U112" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
@@ -8514,7 +8528,7 @@
         <v>0</v>
       </c>
       <c r="U114" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
@@ -8624,7 +8638,7 @@
         <v>0</v>
       </c>
       <c r="U116" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
@@ -9323,7 +9337,7 @@
         <v>0</v>
       </c>
       <c r="U129" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
@@ -9998,7 +10012,7 @@
         <v>0</v>
       </c>
       <c r="U142" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
@@ -10697,7 +10711,7 @@
         <v>0</v>
       </c>
       <c r="U155" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
@@ -11396,7 +11410,7 @@
         <v>0</v>
       </c>
       <c r="U168" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
@@ -12071,7 +12085,7 @@
         <v>0</v>
       </c>
       <c r="U181" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
@@ -12793,7 +12807,7 @@
         <v>0</v>
       </c>
       <c r="U195" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
@@ -13468,7 +13482,7 @@
         <v>0</v>
       </c>
       <c r="U208" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
@@ -14143,7 +14157,7 @@
         <v>0</v>
       </c>
       <c r="U221" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
@@ -14818,7 +14832,7 @@
         <v>0</v>
       </c>
       <c r="U234" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="235" spans="1:21" x14ac:dyDescent="0.25">
@@ -15564,7 +15578,7 @@
         <v>0</v>
       </c>
       <c r="U248" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="249" spans="1:21" x14ac:dyDescent="0.25">
@@ -15627,7 +15641,7 @@
         <v>0</v>
       </c>
       <c r="U249" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -4362,9 +4362,11 @@
       <c r="B39" s="9">
         <v>46162.55843366898</v>
       </c>
-      <c r="C39" s="10"/>
+      <c r="C39" s="9">
+        <v>46209.612930856485</v>
+      </c>
       <c r="D39" s="9">
-        <v>46169.862598437496</v>
+        <v>46209.61294594908</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>147</v>
@@ -4412,10 +4414,10 @@
         <v>54</v>
       </c>
       <c r="T39" s="10">
-        <v>0</v>
-      </c>
-      <c r="U39" s="11" t="s">
-        <v>102</v>
+        <v>1</v>
+      </c>
+      <c r="U39" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -4425,9 +4427,11 @@
       <c r="B40" s="5">
         <v>46162.558437569445</v>
       </c>
-      <c r="C40" s="6"/>
+      <c r="C40" s="5">
+        <v>46209.6120780787</v>
+      </c>
       <c r="D40" s="5">
-        <v>46206.55996775463</v>
+        <v>46209.612079687504</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>90</v>
@@ -4478,9 +4482,11 @@
       <c r="B41" s="9">
         <v>46162.55844153935</v>
       </c>
-      <c r="C41" s="10"/>
+      <c r="C41" s="9">
+        <v>46209.61288494213</v>
+      </c>
       <c r="D41" s="9">
-        <v>46169.86272391204</v>
+        <v>46209.612886620365</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>154</v>
@@ -4533,7 +4539,7 @@
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.862742349535</v>
+        <v>46209.612896307866</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -8477,7 +8483,7 @@
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46162.67389181713</v>
+        <v>46209.61290208333</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>307</v>
@@ -8527,8 +8533,8 @@
       <c r="T114" s="6">
         <v>0</v>
       </c>
-      <c r="U114" s="11" t="s">
-        <v>102</v>
+      <c r="U114" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2842" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2843" uniqueCount="513">
   <si>
     <t xml:space="preserve">50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT 4324 4325 </t>
   </si>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46209.56216927084</v>
+        <v>46209.81432671296</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -3381,7 +3381,9 @@
       <c r="R22" s="6"/>
       <c r="S22" s="6"/>
       <c r="T22" s="6"/>
-      <c r="U22" s="6"/>
+      <c r="U22" s="12" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
@@ -4012,9 +4014,11 @@
       <c r="B33" s="9">
         <v>46162.558358229166</v>
       </c>
-      <c r="C33" s="10"/>
+      <c r="C33" s="9">
+        <v>46209.81430680555</v>
+      </c>
       <c r="D33" s="9">
-        <v>46203.186885787036</v>
+        <v>46209.81431997685</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -4062,10 +4066,10 @@
         <v>33</v>
       </c>
       <c r="T33" s="10">
-        <v>0</v>
-      </c>
-      <c r="U33" s="11" t="s">
-        <v>102</v>
+        <v>1</v>
+      </c>
+      <c r="U33" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -4075,9 +4079,11 @@
       <c r="B34" s="5">
         <v>46162.5583628125</v>
       </c>
-      <c r="C34" s="6"/>
+      <c r="C34" s="5">
+        <v>46209.814144421296</v>
+      </c>
       <c r="D34" s="5">
-        <v>46206.55838853009</v>
+        <v>46209.814146226854</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -4134,9 +4140,11 @@
       <c r="B35" s="9">
         <v>46162.55841275463</v>
       </c>
-      <c r="C35" s="10"/>
+      <c r="C35" s="9">
+        <v>46209.814290752314</v>
+      </c>
       <c r="D35" s="9">
-        <v>46202.16929391204</v>
+        <v>46209.8142920949</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>136</v>
@@ -4193,9 +4201,11 @@
       <c r="B36" s="5">
         <v>46162.558418622684</v>
       </c>
-      <c r="C36" s="6"/>
+      <c r="C36" s="5">
+        <v>46209.81447261574</v>
+      </c>
       <c r="D36" s="5">
-        <v>46203.186885821764</v>
+        <v>46209.81449996528</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>139</v>
@@ -4243,10 +4253,10 @@
         <v>33</v>
       </c>
       <c r="T36" s="6">
-        <v>0</v>
-      </c>
-      <c r="U36" s="11" t="s">
-        <v>102</v>
+        <v>1</v>
+      </c>
+      <c r="U36" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -4256,9 +4266,11 @@
       <c r="B37" s="9">
         <v>46162.558422118054</v>
       </c>
-      <c r="C37" s="10"/>
+      <c r="C37" s="9">
+        <v>46209.81440701389</v>
+      </c>
       <c r="D37" s="9">
-        <v>46206.559050254626</v>
+        <v>46209.81440909722</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>84</v>
@@ -4309,9 +4321,11 @@
       <c r="B38" s="5">
         <v>46162.558426400465</v>
       </c>
-      <c r="C38" s="6"/>
+      <c r="C38" s="5">
+        <v>46209.81445883102</v>
+      </c>
       <c r="D38" s="5">
-        <v>46171.17362893518</v>
+        <v>46209.81446026621</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>144</v>
@@ -4590,9 +4604,11 @@
       <c r="B43" s="9">
         <v>46162.55844833334</v>
       </c>
-      <c r="C43" s="10"/>
+      <c r="C43" s="9">
+        <v>46209.814689583334</v>
+      </c>
       <c r="D43" s="9">
-        <v>46203.186886435185</v>
+        <v>46209.81470094908</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>161</v>
@@ -4640,10 +4656,10 @@
         <v>33</v>
       </c>
       <c r="T43" s="10">
-        <v>0</v>
-      </c>
-      <c r="U43" s="11" t="s">
-        <v>102</v>
+        <v>1</v>
+      </c>
+      <c r="U43" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -4653,9 +4669,11 @@
       <c r="B44" s="5">
         <v>46162.55845114583</v>
       </c>
-      <c r="C44" s="6"/>
+      <c r="C44" s="5">
+        <v>46209.814636689815</v>
+      </c>
       <c r="D44" s="5">
-        <v>46206.559488425926</v>
+        <v>46209.814638090276</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>87</v>
@@ -4706,9 +4724,11 @@
       <c r="B45" s="9">
         <v>46162.55845520833</v>
       </c>
-      <c r="C45" s="10"/>
+      <c r="C45" s="9">
+        <v>46209.81467625</v>
+      </c>
       <c r="D45" s="9">
-        <v>46202.16929168982</v>
+        <v>46209.81467782408</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>166</v>
@@ -5725,7 +5745,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46204.167069814815</v>
+        <v>46209.81431027778</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>208</v>
@@ -5775,8 +5795,8 @@
       <c r="T64" s="6">
         <v>0</v>
       </c>
-      <c r="U64" s="11" t="s">
-        <v>102</v>
+      <c r="U64" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5851,7 +5871,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46204.16707040509</v>
+        <v>46209.814479583336</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>217</v>
@@ -5901,8 +5921,8 @@
       <c r="T66" s="6">
         <v>0</v>
       </c>
-      <c r="U66" s="11" t="s">
-        <v>102</v>
+      <c r="U66" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5977,7 +5997,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46204.1670715162</v>
+        <v>46209.814692500004</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>223</v>
@@ -6027,8 +6047,8 @@
       <c r="T68" s="6">
         <v>0</v>
       </c>
-      <c r="U68" s="11" t="s">
-        <v>102</v>
+      <c r="U68" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -753,73 +753,73 @@
     <t xml:space="preserve">OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
   </si>
   <si>
+    <t>1214969379214241</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparación Materiales,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
+    <t>1214969379214266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>OT 4324- ZVN 1-7-37/2 ,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1214969466635588</t>
+  </si>
+  <si>
+    <t>1214969287690629</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado,Control de calidad corte laser ,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1214969335506636</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,OT 4325- ZVN 1-7-63/2</t>
+  </si>
+  <si>
+    <t>1214969047720336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Mecanizado,Control de calidad Corte plasma,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214969047720337</t>
+  </si>
+  <si>
+    <t>1214969047720338</t>
+  </si>
+  <si>
+    <t>1214969047720339</t>
+  </si>
+  <si>
+    <t>1214969047720340</t>
+  </si>
+  <si>
+    <t>1214969047720341</t>
+  </si>
+  <si>
+    <t>1214969047720342</t>
+  </si>
+  <si>
+    <t>1214969466610535</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214969379214241</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preparación Materiales,OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t>1214969379214266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>OT 4324- ZVN 1-7-37/2 ,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1214969466635588</t>
-  </si>
-  <si>
-    <t>1214969287690629</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado,Control de calidad corte laser ,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1214969335506636</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,OT 4325- ZVN 1-7-63/2</t>
-  </si>
-  <si>
-    <t>1214969047720336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Mecanizado,Control de calidad Corte plasma,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214969047720337</t>
-  </si>
-  <si>
-    <t>1214969047720338</t>
-  </si>
-  <si>
-    <t>1214969047720339</t>
-  </si>
-  <si>
-    <t>1214969047720340</t>
-  </si>
-  <si>
-    <t>1214969047720341</t>
-  </si>
-  <si>
-    <t>1214969047720342</t>
-  </si>
-  <si>
-    <t>1214969466610535</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
   </si>
   <si>
     <t>1214969466610550</t>
@@ -4779,9 +4779,11 @@
       <c r="B46" s="5">
         <v>46162.55817767361</v>
       </c>
-      <c r="C46" s="6"/>
+      <c r="C46" s="5">
+        <v>46210.528908935186</v>
+      </c>
       <c r="D46" s="5">
-        <v>46198.79333590278</v>
+        <v>46210.528923819445</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4816,9 +4818,11 @@
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
       <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="12" t="s">
-        <v>47</v>
+      <c r="T46" s="6">
+        <v>1</v>
+      </c>
+      <c r="U46" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -6170,7 +6174,7 @@
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46209.16939314815</v>
+        <v>46210.17224337963</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>231</v>
@@ -6214,8 +6218,8 @@
       <c r="R71" s="9">
         <v>46209</v>
       </c>
-      <c r="S71" s="12" t="s">
-        <v>235</v>
+      <c r="S71" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T71" s="10">
         <v>0</v>
@@ -6226,7 +6230,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B72" s="5">
         <v>46162.558542557876</v>
@@ -6266,10 +6270,10 @@
         <v>231</v>
       </c>
       <c r="O72" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="P72" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="P72" s="6" t="s">
-        <v>238</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6279,7 +6283,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B73" s="9">
         <v>46162.558548402776</v>
@@ -6319,10 +6323,10 @@
         <v>231</v>
       </c>
       <c r="O73" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="P73" s="10" t="s">
         <v>240</v>
-      </c>
-      <c r="P73" s="10" t="s">
-        <v>241</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -6332,7 +6336,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B74" s="5">
         <v>46162.55855412037</v>
@@ -6372,10 +6376,10 @@
         <v>231</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6385,7 +6389,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B75" s="9">
         <v>46162.558560000005</v>
@@ -6425,10 +6429,10 @@
         <v>231</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6438,7 +6442,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B76" s="5">
         <v>46162.558565671294</v>
@@ -6478,10 +6482,10 @@
         <v>231</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6491,7 +6495,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B77" s="9">
         <v>46162.56018778935</v>
@@ -6531,7 +6535,7 @@
         <v>231</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>196</v>
@@ -6544,7 +6548,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B78" s="5">
         <v>46162.560207789356</v>
@@ -6584,7 +6588,7 @@
         <v>231</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>196</v>
@@ -6597,7 +6601,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B79" s="9">
         <v>46162.5602175463</v>
@@ -6637,7 +6641,7 @@
         <v>231</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>196</v>
@@ -6650,7 +6654,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B80" s="5">
         <v>46162.56022641204</v>
@@ -6690,7 +6694,7 @@
         <v>231</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>196</v>
@@ -6703,7 +6707,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B81" s="9">
         <v>46162.56023459491</v>
@@ -6743,7 +6747,7 @@
         <v>231</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>196</v>
@@ -6756,7 +6760,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B82" s="5">
         <v>46162.56024284722</v>
@@ -6796,7 +6800,7 @@
         <v>231</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>196</v>
@@ -6809,7 +6813,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B83" s="9">
         <v>46162.560250625</v>
@@ -6849,7 +6853,7 @@
         <v>231</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>196</v>
@@ -6862,7 +6866,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B84" s="5">
         <v>46162.55862063657</v>
@@ -6872,7 +6876,7 @@
         <v>46209.17865288194</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6902,7 +6906,7 @@
         <v>228</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>228</v>
@@ -6914,7 +6918,7 @@
         <v>46216</v>
       </c>
       <c r="S84" s="12" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
@@ -6962,7 +6966,7 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O85" s="10" t="s">
         <v>259</v>
@@ -7015,7 +7019,7 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>259</v>
@@ -7068,7 +7072,7 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>259</v>
@@ -7121,7 +7125,7 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>259</v>
@@ -7174,7 +7178,7 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O89" s="10" t="s">
         <v>196</v>
@@ -7227,7 +7231,7 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>196</v>
@@ -7280,7 +7284,7 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O91" s="10" t="s">
         <v>196</v>
@@ -7333,7 +7337,7 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>196</v>
@@ -7386,7 +7390,7 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O93" s="10" t="s">
         <v>196</v>
@@ -7439,7 +7443,7 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>196</v>
@@ -7492,7 +7496,7 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O95" s="10" t="s">
         <v>196</v>
@@ -7545,7 +7549,7 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>196</v>
@@ -7568,7 +7572,7 @@
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46162.67379204861</v>
+        <v>46210.17988293982</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>275</v>
@@ -7612,8 +7616,8 @@
       <c r="R97" s="9">
         <v>46217</v>
       </c>
-      <c r="S97" s="7" t="s">
-        <v>54</v>
+      <c r="S97" s="12" t="s">
+        <v>257</v>
       </c>
       <c r="T97" s="10">
         <v>0</v>
@@ -10020,7 +10024,7 @@
         <v>310</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>310</v>
@@ -11418,7 +11422,7 @@
         <v>310</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P168" s="6" t="s">
         <v>310</v>
@@ -13490,7 +13494,7 @@
         <v>434</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P208" s="6" t="s">
         <v>434</v>
@@ -14840,7 +14844,7 @@
         <v>434</v>
       </c>
       <c r="O234" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P234" s="6" t="s">
         <v>491</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -9316,7 +9316,7 @@
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46162.67400341435</v>
+        <v>46212.180082453706</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>330</v>
@@ -9360,8 +9360,8 @@
       <c r="R129" s="9">
         <v>46219</v>
       </c>
-      <c r="S129" s="7" t="s">
-        <v>54</v>
+      <c r="S129" s="12" t="s">
+        <v>257</v>
       </c>
       <c r="T129" s="10">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -9991,7 +9991,7 @@
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46162.674000150466</v>
+        <v>46213.173677557876</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>354</v>
@@ -10035,8 +10035,8 @@
       <c r="R142" s="5">
         <v>46220</v>
       </c>
-      <c r="S142" s="7" t="s">
-        <v>54</v>
+      <c r="S142" s="12" t="s">
+        <v>257</v>
       </c>
       <c r="T142" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -6906,7 +6906,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46209.17865288194</v>
+        <v>46216.16904840278</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>256</v>
@@ -6969,7 +6969,7 @@
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46198.79338525463</v>
+        <v>46216.16902931713</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>191</v>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46198.79338199074</v>
+        <v>46216.169044270835</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>191</v>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46198.79338243055</v>
+        <v>46216.16904583333</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>191</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46198.79338296296</v>
+        <v>46216.1690471412</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>191</v>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46162.67239402777</v>
+        <v>46216.16904278935</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>197</v>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46162.672391064814</v>
+        <v>46216.169030324076</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>197</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46162.672387743056</v>
+        <v>46216.169031840276</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>197</v>
@@ -7340,7 +7340,7 @@
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46162.67238480324</v>
+        <v>46216.16903329861</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>197</v>
@@ -7393,7 +7393,7 @@
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46162.67238212963</v>
+        <v>46216.16903479167</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>197</v>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46162.67237393519</v>
+        <v>46216.16903612269</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>197</v>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46162.67237322917</v>
+        <v>46216.16903741898</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>197</v>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46162.67237256945</v>
+        <v>46216.16903872685</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>197</v>
@@ -10723,7 +10723,7 @@
       </c>
       <c r="C155" s="10"/>
       <c r="D155" s="9">
-        <v>46162.673997199076</v>
+        <v>46216.16880238426</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>375</v>
@@ -10767,8 +10767,8 @@
       <c r="R155" s="9">
         <v>46223</v>
       </c>
-      <c r="S155" s="7" t="s">
-        <v>55</v>
+      <c r="S155" s="12" t="s">
+        <v>258</v>
       </c>
       <c r="T155" s="10">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2843" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2844" uniqueCount="513">
   <si>
     <t xml:space="preserve">50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT 4324 4325 </t>
   </si>
@@ -723,7 +723,7 @@
     <t xml:space="preserve">Control de calidad corte laser </t>
   </si>
   <si>
-    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
+    <t>Recepcion materiales corte laser,Recepcion materiales corte laser,Recepcion materiales corte laser</t>
   </si>
   <si>
     <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,Bodega:,OT 4324- ZVN 1-7-37/2 ,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
@@ -735,13 +735,10 @@
     <t>Recepcion Materiales corte plasma</t>
   </si>
   <si>
-    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
+    <t>Control de calidad Corte plasma</t>
   </si>
   <si>
     <t>1214969287656991</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
   </si>
   <si>
     <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
@@ -4413,7 +4410,7 @@
         <v>46209.612930856485</v>
       </c>
       <c r="D39" s="9">
-        <v>46209.61294594908</v>
+        <v>46216.544503425925</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>148</v>
@@ -4584,9 +4581,11 @@
       <c r="B42" s="5">
         <v>46162.55844576389</v>
       </c>
-      <c r="C42" s="6"/>
+      <c r="C42" s="5">
+        <v>46216.544432256946</v>
+      </c>
       <c r="D42" s="5">
-        <v>46209.612896307866</v>
+        <v>46216.54443384259</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>158</v>
@@ -5733,9 +5732,11 @@
       <c r="B63" s="9">
         <v>46162.55850443287</v>
       </c>
-      <c r="C63" s="10"/>
+      <c r="C63" s="9">
+        <v>46216.60851976852</v>
+      </c>
       <c r="D63" s="9">
-        <v>46162.60484554398</v>
+        <v>46216.608532638886</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>206</v>
@@ -5770,8 +5771,12 @@
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
       <c r="S63" s="10"/>
-      <c r="T63" s="10"/>
-      <c r="U63" s="10"/>
+      <c r="T63" s="10">
+        <v>1</v>
+      </c>
+      <c r="U63" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
@@ -5780,9 +5785,11 @@
       <c r="B64" s="5">
         <v>46162.558507546295</v>
       </c>
-      <c r="C64" s="6"/>
+      <c r="C64" s="5">
+        <v>46216.60233902778</v>
+      </c>
       <c r="D64" s="5">
-        <v>46209.81431027778</v>
+        <v>46216.60235340278</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>209</v>
@@ -5830,10 +5837,10 @@
         <v>33</v>
       </c>
       <c r="T64" s="6">
-        <v>0</v>
-      </c>
-      <c r="U64" s="12" t="s">
-        <v>48</v>
+        <v>1</v>
+      </c>
+      <c r="U64" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5843,9 +5850,11 @@
       <c r="B65" s="9">
         <v>46162.5585121412</v>
       </c>
-      <c r="C65" s="10"/>
+      <c r="C65" s="9">
+        <v>46216.603007384256</v>
+      </c>
       <c r="D65" s="9">
-        <v>46205.1749468287</v>
+        <v>46216.603024375</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>214</v>
@@ -5893,10 +5902,10 @@
         <v>33</v>
       </c>
       <c r="T65" s="10">
-        <v>0</v>
-      </c>
-      <c r="U65" s="11" t="s">
-        <v>103</v>
+        <v>1</v>
+      </c>
+      <c r="U65" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5906,9 +5915,11 @@
       <c r="B66" s="5">
         <v>46162.558518645834</v>
       </c>
-      <c r="C66" s="6"/>
+      <c r="C66" s="5">
+        <v>46216.603305358796</v>
+      </c>
       <c r="D66" s="5">
-        <v>46209.814479583336</v>
+        <v>46216.60332174768</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>218</v>
@@ -5956,10 +5967,10 @@
         <v>33</v>
       </c>
       <c r="T66" s="6">
-        <v>0</v>
-      </c>
-      <c r="U66" s="12" t="s">
-        <v>48</v>
+        <v>1</v>
+      </c>
+      <c r="U66" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5969,12 +5980,14 @@
       <c r="B67" s="9">
         <v>46162.55852324074</v>
       </c>
-      <c r="C67" s="10"/>
+      <c r="C67" s="9">
+        <v>46216.603357071755</v>
+      </c>
       <c r="D67" s="9">
-        <v>46205.174946747684</v>
+        <v>46216.603370682875</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -6007,7 +6020,7 @@
         <v>218</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q67" s="9">
         <v>46204</v>
@@ -6019,25 +6032,27 @@
         <v>33</v>
       </c>
       <c r="T67" s="10">
-        <v>0</v>
-      </c>
-      <c r="U67" s="11" t="s">
-        <v>103</v>
+        <v>1</v>
+      </c>
+      <c r="U67" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B68" s="5">
         <v>46162.5585274537</v>
       </c>
-      <c r="C68" s="6"/>
+      <c r="C68" s="5">
+        <v>46216.60846390046</v>
+      </c>
       <c r="D68" s="5">
-        <v>46209.814692500004</v>
+        <v>46216.60848061343</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -6070,7 +6085,7 @@
         <v>167</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q68" s="5">
         <v>46203</v>
@@ -6082,25 +6097,27 @@
         <v>33</v>
       </c>
       <c r="T68" s="6">
-        <v>0</v>
-      </c>
-      <c r="U68" s="12" t="s">
-        <v>48</v>
+        <v>1</v>
+      </c>
+      <c r="U68" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B69" s="9">
         <v>46162.558531400464</v>
       </c>
-      <c r="C69" s="10"/>
+      <c r="C69" s="9">
+        <v>46216.60850371528</v>
+      </c>
       <c r="D69" s="9">
-        <v>46205.17494673611</v>
+        <v>46216.60852013889</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -6130,10 +6147,10 @@
         <v>206</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q69" s="9">
         <v>46204</v>
@@ -6145,15 +6162,15 @@
         <v>33</v>
       </c>
       <c r="T69" s="10">
-        <v>0</v>
-      </c>
-      <c r="U69" s="11" t="s">
-        <v>103</v>
+        <v>1</v>
+      </c>
+      <c r="U69" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B70" s="5">
         <v>46162.55853556713</v>
@@ -6163,7 +6180,7 @@
         <v>46162.61139740741</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -6187,7 +6204,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -6200,7 +6217,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B71" s="9">
         <v>46162.558538067125</v>
@@ -6210,16 +6227,16 @@
         <v>46210.17224337963</v>
       </c>
       <c r="E71" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="F71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="F71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="10" t="s">
+      <c r="H71" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I71" s="9">
         <v>46205</v>
@@ -6237,13 +6254,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q71" s="9">
         <v>46205</v>
@@ -6263,14 +6280,14 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B72" s="5">
         <v>46162.558542557876</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46209.16938944445</v>
+        <v>46216.60851978009</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>191</v>
@@ -6279,10 +6296,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I72" s="5">
         <v>46205</v>
@@ -6300,13 +6317,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O72" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="P72" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="P72" s="6" t="s">
-        <v>238</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6316,14 +6333,14 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B73" s="9">
         <v>46162.558548402776</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46209.169390752315</v>
+        <v>46216.608520821756</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>191</v>
@@ -6332,10 +6349,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I73" s="9">
         <v>46205</v>
@@ -6353,13 +6370,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O73" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="P73" s="10" t="s">
         <v>240</v>
-      </c>
-      <c r="P73" s="10" t="s">
-        <v>241</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -6369,14 +6386,14 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B74" s="5">
         <v>46162.55855412037</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46209.169391944444</v>
+        <v>46216.608521828704</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>191</v>
@@ -6385,10 +6402,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I74" s="5">
         <v>46205</v>
@@ -6406,13 +6423,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6422,14 +6439,14 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B75" s="9">
         <v>46162.558560000005</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46209.16938706019</v>
+        <v>46216.6085178125</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>191</v>
@@ -6438,10 +6455,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I75" s="9">
         <v>46205</v>
@@ -6459,13 +6476,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6475,14 +6492,14 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B76" s="5">
         <v>46162.558565671294</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46209.16938824074</v>
+        <v>46216.60851880787</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>197</v>
@@ -6491,10 +6508,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I76" s="5">
         <v>46205</v>
@@ -6512,13 +6529,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6528,14 +6545,14 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B77" s="9">
         <v>46162.56018778935</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46209.169375474536</v>
+        <v>46216.60851089121</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>197</v>
@@ -6544,10 +6561,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H77" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I77" s="9">
         <v>46205</v>
@@ -6565,10 +6582,10 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>197</v>
@@ -6581,14 +6598,14 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B78" s="5">
         <v>46162.560207789356</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46209.16937722222</v>
+        <v>46216.60851201389</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>197</v>
@@ -6597,10 +6614,10 @@
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I78" s="5">
         <v>46205</v>
@@ -6618,10 +6635,10 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>197</v>
@@ -6634,14 +6651,14 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B79" s="9">
         <v>46162.5602175463</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46209.169378391205</v>
+        <v>46216.608512997685</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>197</v>
@@ -6650,10 +6667,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I79" s="9">
         <v>46205</v>
@@ -6671,10 +6688,10 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>197</v>
@@ -6687,14 +6704,14 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B80" s="5">
         <v>46162.56022641204</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46209.1693796412</v>
+        <v>46216.608513900464</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>197</v>
@@ -6703,10 +6720,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I80" s="5">
         <v>46205</v>
@@ -6724,10 +6741,10 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>197</v>
@@ -6740,14 +6757,14 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B81" s="9">
         <v>46162.56023459491</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46209.169380775464</v>
+        <v>46216.60851494213</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>197</v>
@@ -6756,10 +6773,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I81" s="9">
         <v>46205</v>
@@ -6777,10 +6794,10 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>197</v>
@@ -6793,14 +6810,14 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B82" s="5">
         <v>46162.56024284722</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46209.169382175925</v>
+        <v>46216.6085158912</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>197</v>
@@ -6809,10 +6826,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I82" s="5">
         <v>46205</v>
@@ -6830,10 +6847,10 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>197</v>
@@ -6846,14 +6863,14 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B83" s="9">
         <v>46162.560250625</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46209.169383437504</v>
+        <v>46216.60851681713</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>197</v>
@@ -6862,10 +6879,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I83" s="9">
         <v>46205</v>
@@ -6883,10 +6900,10 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>197</v>
@@ -6899,7 +6916,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B84" s="5">
         <v>46162.55862063657</v>
@@ -6909,16 +6926,16 @@
         <v>46216.16904840278</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I84" s="5">
         <v>46210</v>
@@ -6936,13 +6953,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q84" s="5">
         <v>46210</v>
@@ -6951,7 +6968,7 @@
         <v>46216</v>
       </c>
       <c r="S84" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
@@ -6962,7 +6979,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B85" s="9">
         <v>46162.558626620375</v>
@@ -6978,10 +6995,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H85" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I85" s="9">
         <v>46210</v>
@@ -6999,13 +7016,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O85" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="P85" s="10" t="s">
         <v>260</v>
-      </c>
-      <c r="P85" s="10" t="s">
-        <v>261</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -7015,7 +7032,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B86" s="5">
         <v>46162.55863280092</v>
@@ -7031,10 +7048,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I86" s="5">
         <v>46210</v>
@@ -7052,13 +7069,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O86" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="P86" s="6" t="s">
         <v>260</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>261</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -7068,7 +7085,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B87" s="9">
         <v>46162.55863850695</v>
@@ -7084,10 +7101,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H87" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I87" s="9">
         <v>46210</v>
@@ -7105,13 +7122,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -7121,7 +7138,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B88" s="5">
         <v>46162.558644247685</v>
@@ -7137,10 +7154,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I88" s="5">
         <v>46210</v>
@@ -7158,13 +7175,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O88" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="P88" s="6" t="s">
         <v>260</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>261</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7174,7 +7191,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B89" s="9">
         <v>46162.55864990741</v>
@@ -7190,10 +7207,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I89" s="9">
         <v>46210</v>
@@ -7211,13 +7228,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O89" s="10" t="s">
         <v>197</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -7227,7 +7244,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B90" s="5">
         <v>46162.56148016204</v>
@@ -7243,10 +7260,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I90" s="5">
         <v>46210</v>
@@ -7264,7 +7281,7 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>197</v>
@@ -7280,7 +7297,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B91" s="9">
         <v>46162.561489201384</v>
@@ -7296,10 +7313,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H91" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I91" s="9">
         <v>46210</v>
@@ -7317,7 +7334,7 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O91" s="10" t="s">
         <v>197</v>
@@ -7333,7 +7350,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B92" s="5">
         <v>46162.56149930556</v>
@@ -7349,10 +7366,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I92" s="5">
         <v>46210</v>
@@ -7370,7 +7387,7 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>197</v>
@@ -7386,7 +7403,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B93" s="9">
         <v>46162.561507199076</v>
@@ -7402,10 +7419,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H93" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I93" s="9">
         <v>46210</v>
@@ -7423,7 +7440,7 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O93" s="10" t="s">
         <v>197</v>
@@ -7439,7 +7456,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B94" s="5">
         <v>46162.56151613426</v>
@@ -7455,10 +7472,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I94" s="5">
         <v>46210</v>
@@ -7476,7 +7493,7 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>197</v>
@@ -7492,7 +7509,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B95" s="9">
         <v>46162.56152413195</v>
@@ -7508,10 +7525,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H95" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I95" s="9">
         <v>46210</v>
@@ -7529,7 +7546,7 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O95" s="10" t="s">
         <v>197</v>
@@ -7545,7 +7562,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B96" s="5">
         <v>46162.56153119213</v>
@@ -7561,10 +7578,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I96" s="5">
         <v>46210</v>
@@ -7582,7 +7599,7 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>197</v>
@@ -7598,7 +7615,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B97" s="9">
         <v>46162.55865439815</v>
@@ -7608,7 +7625,7 @@
         <v>46210.17988293982</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7635,13 +7652,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q97" s="9">
         <v>46217</v>
@@ -7650,7 +7667,7 @@
         <v>46217</v>
       </c>
       <c r="S97" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T97" s="10">
         <v>0</v>
@@ -7661,7 +7678,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B98" s="5">
         <v>46162.55865909722</v>
@@ -7698,13 +7715,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7714,7 +7731,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B99" s="9">
         <v>46162.55866501157</v>
@@ -7751,13 +7768,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7767,7 +7784,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B100" s="5">
         <v>46162.55867084491</v>
@@ -7804,13 +7821,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7820,7 +7837,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B101" s="9">
         <v>46162.558676597226</v>
@@ -7857,13 +7874,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7873,7 +7890,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B102" s="5">
         <v>46162.55868239583</v>
@@ -7910,13 +7927,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>197</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7926,7 +7943,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B103" s="9">
         <v>46162.56176834491</v>
@@ -7963,7 +7980,7 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O103" s="10" t="s">
         <v>197</v>
@@ -7979,7 +7996,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B104" s="5">
         <v>46162.56177670139</v>
@@ -8016,10 +8033,10 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>197</v>
@@ -8032,7 +8049,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B105" s="9">
         <v>46162.56178474537</v>
@@ -8069,7 +8086,7 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O105" s="10" t="s">
         <v>197</v>
@@ -8085,7 +8102,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B106" s="5">
         <v>46162.56179298611</v>
@@ -8122,7 +8139,7 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>197</v>
@@ -8138,7 +8155,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B107" s="9">
         <v>46162.5618009375</v>
@@ -8175,7 +8192,7 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O107" s="10" t="s">
         <v>197</v>
@@ -8191,7 +8208,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B108" s="5">
         <v>46162.56180909723</v>
@@ -8228,7 +8245,7 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>197</v>
@@ -8244,7 +8261,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B109" s="9">
         <v>46162.56181716435</v>
@@ -8281,7 +8298,7 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O109" s="10" t="s">
         <v>197</v>
@@ -8297,14 +8314,14 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B110" s="5">
         <v>46162.55868650463</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46162.61466552083</v>
+        <v>46216.54541798611</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>206</v>
@@ -8331,7 +8348,7 @@
         <v>26</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>26</v>
@@ -8344,17 +8361,19 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B111" s="9">
         <v>46162.55869006945</v>
       </c>
-      <c r="C111" s="10"/>
+      <c r="C111" s="9">
+        <v>46216.54540293981</v>
+      </c>
       <c r="D111" s="9">
-        <v>46198.68469991898</v>
+        <v>46216.54541784722</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -8387,7 +8406,7 @@
         <v>114</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q111" s="9">
         <v>46161</v>
@@ -8399,25 +8418,27 @@
         <v>55</v>
       </c>
       <c r="T111" s="10">
-        <v>0</v>
-      </c>
-      <c r="U111" s="12" t="s">
-        <v>48</v>
+        <v>1</v>
+      </c>
+      <c r="U111" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B112" s="5">
         <v>46162.558696921296</v>
       </c>
-      <c r="C112" s="6"/>
+      <c r="C112" s="5">
+        <v>46216.54540828704</v>
+      </c>
       <c r="D112" s="5">
-        <v>46209.562158773144</v>
+        <v>46216.54542513889</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8450,7 +8471,7 @@
         <v>105</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q112" s="5">
         <v>46161</v>
@@ -8462,15 +8483,15 @@
         <v>55</v>
       </c>
       <c r="T112" s="6">
-        <v>0</v>
-      </c>
-      <c r="U112" s="12" t="s">
-        <v>48</v>
+        <v>1</v>
+      </c>
+      <c r="U112" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B113" s="9">
         <v>46162.55870284722</v>
@@ -8480,7 +8501,7 @@
         <v>46198.684325486116</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8513,7 +8534,7 @@
         <v>123</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q113" s="9">
         <v>46196</v>
@@ -8533,17 +8554,19 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B114" s="5">
         <v>46162.55870962963</v>
       </c>
-      <c r="C114" s="6"/>
+      <c r="C114" s="5">
+        <v>46216.54425189814</v>
+      </c>
       <c r="D114" s="5">
-        <v>46209.61290208333</v>
+        <v>46216.544359340274</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8576,7 +8599,7 @@
         <v>155</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q114" s="5">
         <v>46232</v>
@@ -8588,15 +8611,15 @@
         <v>55</v>
       </c>
       <c r="T114" s="6">
-        <v>0</v>
-      </c>
-      <c r="U114" s="12" t="s">
-        <v>48</v>
+        <v>1</v>
+      </c>
+      <c r="U114" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B115" s="9">
         <v>46162.55871869213</v>
@@ -8606,7 +8629,7 @@
         <v>46162.64775322917</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>25</v>
@@ -8630,7 +8653,7 @@
         <v>26</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>26</v>
@@ -8643,17 +8666,17 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B116" s="5">
         <v>46162.55872223379</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46162.67400658564</v>
+        <v>46216.544257754635</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8680,13 +8703,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q116" s="5">
         <v>46218</v>
@@ -8706,14 +8729,14 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B117" s="9">
         <v>46162.55873068287</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46162.674262650464</v>
+        <v>46216.544258368056</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>191</v>
@@ -8743,10 +8766,10 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P117" s="10" t="s">
         <v>26</v>
@@ -8759,14 +8782,14 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B118" s="5">
         <v>46162.558735011575</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46162.67425921296</v>
+        <v>46216.54425895833</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>191</v>
@@ -8796,10 +8819,10 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>26</v>
@@ -8812,7 +8835,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B119" s="9">
         <v>46162.55873951389</v>
@@ -8849,13 +8872,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O119" s="10" t="s">
         <v>191</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8865,7 +8888,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B120" s="5">
         <v>46162.55874386574</v>
@@ -8902,13 +8925,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>191</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8918,7 +8941,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B121" s="9">
         <v>46162.55874813657</v>
@@ -8955,7 +8978,7 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O121" s="10" t="s">
         <v>197</v>
@@ -8971,7 +8994,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B122" s="5">
         <v>46162.56516702546</v>
@@ -9008,7 +9031,7 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>197</v>
@@ -9024,7 +9047,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B123" s="9">
         <v>46162.56517383102</v>
@@ -9061,7 +9084,7 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O123" s="10" t="s">
         <v>197</v>
@@ -9077,7 +9100,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B124" s="5">
         <v>46162.565181134254</v>
@@ -9114,7 +9137,7 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>197</v>
@@ -9130,7 +9153,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B125" s="9">
         <v>46162.565189201385</v>
@@ -9167,7 +9190,7 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O125" s="10" t="s">
         <v>197</v>
@@ -9183,7 +9206,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B126" s="5">
         <v>46162.56519680556</v>
@@ -9220,7 +9243,7 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>197</v>
@@ -9236,7 +9259,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B127" s="9">
         <v>46162.565205590276</v>
@@ -9273,7 +9296,7 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O127" s="10" t="s">
         <v>197</v>
@@ -9289,7 +9312,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B128" s="5">
         <v>46162.565212013884</v>
@@ -9326,7 +9349,7 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>197</v>
@@ -9342,7 +9365,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B129" s="9">
         <v>46162.558751550925</v>
@@ -9352,7 +9375,7 @@
         <v>46212.180082453706</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -9379,13 +9402,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q129" s="9">
         <v>46219</v>
@@ -9394,7 +9417,7 @@
         <v>46219</v>
       </c>
       <c r="S129" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T129" s="10">
         <v>0</v>
@@ -9405,14 +9428,14 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B130" s="5">
         <v>46162.558756238424</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46198.79338591435</v>
+        <v>46216.545420497685</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>191</v>
@@ -9440,13 +9463,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O130" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="P130" s="6" t="s">
         <v>333</v>
-      </c>
-      <c r="P130" s="6" t="s">
-        <v>334</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9456,14 +9479,14 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B131" s="9">
         <v>46162.55876204861</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46198.79338641204</v>
+        <v>46216.54541923611</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>191</v>
@@ -9491,13 +9514,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9507,14 +9530,14 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B132" s="5">
         <v>46162.55876745371</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46198.79338869213</v>
+        <v>46216.54542087963</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>191</v>
@@ -9542,13 +9565,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O132" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="P132" s="6" t="s">
         <v>338</v>
-      </c>
-      <c r="P132" s="6" t="s">
-        <v>339</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9558,14 +9581,14 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B133" s="9">
         <v>46162.558773888886</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46198.793389004626</v>
+        <v>46216.545421400464</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>191</v>
@@ -9593,13 +9616,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O133" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="P133" s="10" t="s">
         <v>338</v>
-      </c>
-      <c r="P133" s="10" t="s">
-        <v>339</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9609,7 +9632,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B134" s="5">
         <v>46162.558827430556</v>
@@ -9644,13 +9667,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>197</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9660,14 +9683,14 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B135" s="9">
         <v>46162.565477233795</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46198.79336980324</v>
+        <v>46216.545414016204</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>197</v>
@@ -9695,10 +9718,10 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P135" s="10" t="s">
         <v>197</v>
@@ -9711,14 +9734,14 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B136" s="5">
         <v>46162.56548539352</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46198.79337046296</v>
+        <v>46216.54541466435</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>197</v>
@@ -9746,10 +9769,10 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>197</v>
@@ -9762,14 +9785,14 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B137" s="9">
         <v>46162.56549420139</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46198.79337111111</v>
+        <v>46216.54541517361</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>197</v>
@@ -9797,10 +9820,10 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P137" s="10" t="s">
         <v>197</v>
@@ -9813,14 +9836,14 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B138" s="5">
         <v>46162.56549981482</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46198.79337171296</v>
+        <v>46216.545415636574</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>197</v>
@@ -9848,13 +9871,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9864,14 +9887,14 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B139" s="9">
         <v>46162.565507719904</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46198.79337225694</v>
+        <v>46216.54541619213</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>197</v>
@@ -9899,10 +9922,10 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P139" s="10" t="s">
         <v>197</v>
@@ -9915,14 +9938,14 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B140" s="5">
         <v>46162.56551637732</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46162.6743640162</v>
+        <v>46216.545416747686</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>197</v>
@@ -9950,10 +9973,10 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>197</v>
@@ -9966,14 +9989,14 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B141" s="9">
         <v>46162.56598206019</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46162.67436230324</v>
+        <v>46216.54541722222</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>197</v>
@@ -10001,10 +10024,10 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P141" s="10" t="s">
         <v>197</v>
@@ -10017,7 +10040,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B142" s="5">
         <v>46162.55883354167</v>
@@ -10027,7 +10050,7 @@
         <v>46213.173677557876</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -10054,13 +10077,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q142" s="5">
         <v>46220</v>
@@ -10069,7 +10092,7 @@
         <v>46220</v>
       </c>
       <c r="S142" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T142" s="6">
         <v>0</v>
@@ -10080,14 +10103,14 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B143" s="9">
         <v>46162.55883898148</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46198.79338673611</v>
+        <v>46216.545412060186</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>191</v>
@@ -10117,13 +10140,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -10133,14 +10156,14 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B144" s="5">
         <v>46162.55884618056</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46198.793387094905</v>
+        <v>46216.54541274306</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>191</v>
@@ -10170,13 +10193,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10186,14 +10209,14 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B145" s="9">
         <v>46162.55885335648</v>
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46198.79338740741</v>
+        <v>46216.54541334491</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>191</v>
@@ -10223,13 +10246,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -10239,14 +10262,14 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B146" s="5">
         <v>46162.558860624995</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46198.793387858794</v>
+        <v>46216.545413935186</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>191</v>
@@ -10276,13 +10299,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10292,7 +10315,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B147" s="9">
         <v>46162.558867395834</v>
@@ -10329,13 +10352,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O147" s="10" t="s">
         <v>197</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10345,14 +10368,14 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B148" s="5">
         <v>46162.566146365745</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46162.674521354165</v>
+        <v>46216.54540832176</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>197</v>
@@ -10382,10 +10405,10 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>197</v>
@@ -10398,7 +10421,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B149" s="9">
         <v>46162.566153101856</v>
@@ -10435,7 +10458,7 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O149" s="10" t="s">
         <v>197</v>
@@ -10451,14 +10474,14 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B150" s="5">
         <v>46162.56617111111</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46162.67451502314</v>
+        <v>46216.54540890046</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>197</v>
@@ -10488,10 +10511,10 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>197</v>
@@ -10504,17 +10527,17 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B151" s="9">
         <v>46162.56618105324</v>
       </c>
       <c r="C151" s="10"/>
       <c r="D151" s="9">
-        <v>46162.67451243056</v>
+        <v>46216.545409432874</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
@@ -10541,10 +10564,10 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="P151" s="10" t="s">
         <v>197</v>
@@ -10557,14 +10580,14 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B152" s="5">
         <v>46162.56618987268</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46162.67450335648</v>
+        <v>46216.545409976854</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>197</v>
@@ -10594,10 +10617,10 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="P152" s="6" t="s">
         <v>197</v>
@@ -10610,14 +10633,14 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B153" s="9">
         <v>46162.56620271991</v>
       </c>
       <c r="C153" s="10"/>
       <c r="D153" s="9">
-        <v>46162.67450263889</v>
+        <v>46216.54541050926</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>197</v>
@@ -10647,10 +10670,10 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="P153" s="10" t="s">
         <v>197</v>
@@ -10663,14 +10686,14 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B154" s="5">
         <v>46162.56620673611</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46162.67450188658</v>
+        <v>46216.545411099534</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>197</v>
@@ -10700,10 +10723,10 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="P154" s="6" t="s">
         <v>197</v>
@@ -10716,7 +10739,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B155" s="9">
         <v>46162.558871574074</v>
@@ -10726,7 +10749,7 @@
         <v>46216.16880238426</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -10753,13 +10776,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q155" s="9">
         <v>46223</v>
@@ -10768,7 +10791,7 @@
         <v>46223</v>
       </c>
       <c r="S155" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T155" s="10">
         <v>0</v>
@@ -10779,7 +10802,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B156" s="5">
         <v>46162.55887622685</v>
@@ -10816,13 +10839,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O156" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="P156" s="6" t="s">
         <v>378</v>
-      </c>
-      <c r="P156" s="6" t="s">
-        <v>379</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10832,7 +10855,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B157" s="9">
         <v>46162.55888300926</v>
@@ -10869,13 +10892,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O157" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="P157" s="10" t="s">
         <v>378</v>
-      </c>
-      <c r="P157" s="10" t="s">
-        <v>379</v>
       </c>
       <c r="Q157" s="10"/>
       <c r="R157" s="10"/>
@@ -10885,7 +10908,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B158" s="5">
         <v>46162.558892581015</v>
@@ -10922,13 +10945,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10938,7 +10961,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B159" s="9">
         <v>46162.55889858796</v>
@@ -10975,13 +10998,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="P159" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q159" s="10"/>
       <c r="R159" s="10"/>
@@ -10991,7 +11014,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B160" s="5">
         <v>46162.558904618054</v>
@@ -11028,13 +11051,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O160" s="6" t="s">
         <v>197</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -11044,7 +11067,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B161" s="9">
         <v>46162.566379375</v>
@@ -11081,13 +11104,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O161" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="P161" s="10" t="s">
         <v>388</v>
-      </c>
-      <c r="P161" s="10" t="s">
-        <v>389</v>
       </c>
       <c r="Q161" s="10"/>
       <c r="R161" s="10"/>
@@ -11097,7 +11120,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B162" s="5">
         <v>46162.56638695602</v>
@@ -11134,10 +11157,10 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="P162" s="6" t="s">
         <v>197</v>
@@ -11150,7 +11173,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B163" s="9">
         <v>46162.56639532407</v>
@@ -11187,13 +11210,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -11203,7 +11226,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B164" s="5">
         <v>46162.56640418981</v>
@@ -11240,13 +11263,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O164" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="P164" s="6" t="s">
         <v>394</v>
-      </c>
-      <c r="P164" s="6" t="s">
-        <v>395</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11256,7 +11279,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B165" s="9">
         <v>46162.56641240741</v>
@@ -11293,13 +11316,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -11309,7 +11332,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B166" s="5">
         <v>46162.56642033564</v>
@@ -11346,13 +11369,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="Q166" s="6"/>
       <c r="R166" s="6"/>
@@ -11362,7 +11385,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B167" s="9">
         <v>46162.566427708334</v>
@@ -11399,10 +11422,10 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="P167" s="10" t="s">
         <v>197</v>
@@ -11415,7 +11438,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B168" s="5">
         <v>46162.558908946754</v>
@@ -11425,7 +11448,7 @@
         <v>46162.67399393518</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11452,13 +11475,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q168" s="5">
         <v>46224</v>
@@ -11478,7 +11501,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B169" s="9">
         <v>46162.55891369213</v>
@@ -11513,13 +11536,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="10" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O169" s="10" t="s">
         <v>191</v>
       </c>
       <c r="P169" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q169" s="10"/>
       <c r="R169" s="10"/>
@@ -11529,7 +11552,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B170" s="5">
         <v>46162.55891930556</v>
@@ -11564,13 +11587,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O170" s="6" t="s">
         <v>191</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
@@ -11580,7 +11603,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B171" s="9">
         <v>46162.558924930556</v>
@@ -11615,13 +11638,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O171" s="10" t="s">
         <v>191</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q171" s="10"/>
       <c r="R171" s="10"/>
@@ -11631,7 +11654,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B172" s="5">
         <v>46162.55893104167</v>
@@ -11666,13 +11689,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O172" s="6" t="s">
         <v>191</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11682,7 +11705,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B173" s="9">
         <v>46162.55893646991</v>
@@ -11717,13 +11740,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="10" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O173" s="10" t="s">
         <v>197</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11733,7 +11756,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B174" s="5">
         <v>46162.567320891205</v>
@@ -11768,7 +11791,7 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O174" s="6" t="s">
         <v>197</v>
@@ -11784,7 +11807,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B175" s="9">
         <v>46162.567330034726</v>
@@ -11819,7 +11842,7 @@
         <v>26</v>
       </c>
       <c r="N175" s="10" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O175" s="10" t="s">
         <v>197</v>
@@ -11835,7 +11858,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B176" s="5">
         <v>46162.567337685185</v>
@@ -11870,7 +11893,7 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O176" s="6" t="s">
         <v>197</v>
@@ -11886,7 +11909,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B177" s="9">
         <v>46162.567344166666</v>
@@ -11921,7 +11944,7 @@
         <v>26</v>
       </c>
       <c r="N177" s="10" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O177" s="10" t="s">
         <v>197</v>
@@ -11937,7 +11960,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B178" s="5">
         <v>46162.56735135417</v>
@@ -11972,7 +11995,7 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O178" s="6" t="s">
         <v>197</v>
@@ -11988,7 +12011,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B179" s="9">
         <v>46162.5673590625</v>
@@ -12023,7 +12046,7 @@
         <v>26</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O179" s="10" t="s">
         <v>197</v>
@@ -12039,7 +12062,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B180" s="5">
         <v>46162.567366284726</v>
@@ -12074,7 +12097,7 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O180" s="6" t="s">
         <v>197</v>
@@ -12090,7 +12113,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B181" s="9">
         <v>46162.558941678246</v>
@@ -12100,7 +12123,7 @@
         <v>46162.673987789356</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>26</v>
@@ -12127,13 +12150,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="O181" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="P181" s="10" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Q181" s="9">
         <v>46226</v>
@@ -12153,7 +12176,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B182" s="5">
         <v>46162.5589471875</v>
@@ -12188,13 +12211,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O182" s="6" t="s">
         <v>191</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -12204,7 +12227,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B183" s="9">
         <v>46162.55895184028</v>
@@ -12239,13 +12262,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O183" s="10" t="s">
         <v>191</v>
       </c>
       <c r="P183" s="10" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Q183" s="10"/>
       <c r="R183" s="10"/>
@@ -12255,7 +12278,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B184" s="5">
         <v>46162.55895655093</v>
@@ -12290,13 +12313,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O184" s="6" t="s">
         <v>191</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12306,7 +12329,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B185" s="9">
         <v>46162.5589959375</v>
@@ -12341,13 +12364,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O185" s="10" t="s">
         <v>191</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -12357,7 +12380,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B186" s="5">
         <v>46162.55900136574</v>
@@ -12392,13 +12415,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O186" s="6" t="s">
         <v>197</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12408,7 +12431,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B187" s="9">
         <v>46162.56759152778</v>
@@ -12443,7 +12466,7 @@
         <v>26</v>
       </c>
       <c r="N187" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O187" s="10" t="s">
         <v>197</v>
@@ -12459,7 +12482,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B188" s="5">
         <v>46162.56759846065</v>
@@ -12494,13 +12517,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O188" s="6" t="s">
         <v>197</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12510,7 +12533,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B189" s="9">
         <v>46162.56760671297</v>
@@ -12545,7 +12568,7 @@
         <v>26</v>
       </c>
       <c r="N189" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O189" s="10" t="s">
         <v>197</v>
@@ -12561,7 +12584,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B190" s="5">
         <v>46162.56761416666</v>
@@ -12596,7 +12619,7 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O190" s="6" t="s">
         <v>197</v>
@@ -12612,7 +12635,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B191" s="9">
         <v>46162.56762221065</v>
@@ -12647,7 +12670,7 @@
         <v>26</v>
       </c>
       <c r="N191" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O191" s="10" t="s">
         <v>197</v>
@@ -12663,7 +12686,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B192" s="5">
         <v>46162.56762855324</v>
@@ -12698,7 +12721,7 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O192" s="6" t="s">
         <v>197</v>
@@ -12714,7 +12737,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B193" s="9">
         <v>46162.56763415509</v>
@@ -12749,7 +12772,7 @@
         <v>26</v>
       </c>
       <c r="N193" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O193" s="10" t="s">
         <v>197</v>
@@ -12765,7 +12788,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B194" s="5">
         <v>46162.55900565972</v>
@@ -12775,7 +12798,7 @@
         <v>46162.663939108796</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>25</v>
@@ -12799,7 +12822,7 @@
         <v>26</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P194" s="6" t="s">
         <v>26</v>
@@ -12812,7 +12835,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B195" s="9">
         <v>46162.55900940972</v>
@@ -12822,16 +12845,16 @@
         <v>46162.67540229167</v>
       </c>
       <c r="E195" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="F195" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G195" s="10" t="s">
         <v>438</v>
       </c>
-      <c r="F195" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G195" s="10" t="s">
+      <c r="H195" s="10" t="s">
         <v>439</v>
-      </c>
-      <c r="H195" s="10" t="s">
-        <v>440</v>
       </c>
       <c r="I195" s="9">
         <v>46227</v>
@@ -12849,13 +12872,13 @@
         <v>26</v>
       </c>
       <c r="N195" s="10" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="O195" s="10" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="P195" s="10" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q195" s="9">
         <v>46227</v>
@@ -12875,7 +12898,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B196" s="5">
         <v>46162.559015023144</v>
@@ -12891,10 +12914,10 @@
         <v>26</v>
       </c>
       <c r="G196" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="H196" s="6" t="s">
         <v>439</v>
-      </c>
-      <c r="H196" s="6" t="s">
-        <v>440</v>
       </c>
       <c r="I196" s="6"/>
       <c r="J196" s="5">
@@ -12910,13 +12933,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O196" s="6" t="s">
         <v>191</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -12926,7 +12949,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B197" s="9">
         <v>46162.55901939815</v>
@@ -12942,10 +12965,10 @@
         <v>26</v>
       </c>
       <c r="G197" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="H197" s="10" t="s">
         <v>439</v>
-      </c>
-      <c r="H197" s="10" t="s">
-        <v>440</v>
       </c>
       <c r="I197" s="10"/>
       <c r="J197" s="9">
@@ -12961,13 +12984,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="10" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O197" s="10" t="s">
         <v>191</v>
       </c>
       <c r="P197" s="10" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="Q197" s="10"/>
       <c r="R197" s="10"/>
@@ -12977,7 +13000,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B198" s="5">
         <v>46162.55902388888</v>
@@ -12993,10 +13016,10 @@
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="H198" s="6" t="s">
         <v>439</v>
-      </c>
-      <c r="H198" s="6" t="s">
-        <v>440</v>
       </c>
       <c r="I198" s="6"/>
       <c r="J198" s="5">
@@ -13012,13 +13035,13 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O198" s="6" t="s">
         <v>191</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="Q198" s="6"/>
       <c r="R198" s="6"/>
@@ -13028,7 +13051,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B199" s="9">
         <v>46162.559028090276</v>
@@ -13044,10 +13067,10 @@
         <v>26</v>
       </c>
       <c r="G199" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="H199" s="10" t="s">
         <v>439</v>
-      </c>
-      <c r="H199" s="10" t="s">
-        <v>440</v>
       </c>
       <c r="I199" s="10"/>
       <c r="J199" s="9">
@@ -13063,13 +13086,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="10" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O199" s="10" t="s">
         <v>191</v>
       </c>
       <c r="P199" s="10" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="Q199" s="10"/>
       <c r="R199" s="10"/>
@@ -13079,7 +13102,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B200" s="5">
         <v>46162.559032060184</v>
@@ -13095,10 +13118,10 @@
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="H200" s="6" t="s">
         <v>439</v>
-      </c>
-      <c r="H200" s="6" t="s">
-        <v>440</v>
       </c>
       <c r="I200" s="6"/>
       <c r="J200" s="5">
@@ -13114,13 +13137,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O200" s="6" t="s">
         <v>197</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -13130,7 +13153,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B201" s="9">
         <v>46162.56847083333</v>
@@ -13146,10 +13169,10 @@
         <v>26</v>
       </c>
       <c r="G201" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="H201" s="10" t="s">
         <v>439</v>
-      </c>
-      <c r="H201" s="10" t="s">
-        <v>440</v>
       </c>
       <c r="I201" s="10"/>
       <c r="J201" s="9">
@@ -13165,13 +13188,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="10" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O201" s="10" t="s">
         <v>197</v>
       </c>
       <c r="P201" s="10" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="Q201" s="10"/>
       <c r="R201" s="10"/>
@@ -13181,7 +13204,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B202" s="5">
         <v>46162.5684778588</v>
@@ -13197,10 +13220,10 @@
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="H202" s="6" t="s">
         <v>439</v>
-      </c>
-      <c r="H202" s="6" t="s">
-        <v>440</v>
       </c>
       <c r="I202" s="6"/>
       <c r="J202" s="5">
@@ -13216,7 +13239,7 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O202" s="6" t="s">
         <v>197</v>
@@ -13232,7 +13255,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B203" s="9">
         <v>46162.56848583333</v>
@@ -13248,10 +13271,10 @@
         <v>26</v>
       </c>
       <c r="G203" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="H203" s="10" t="s">
         <v>439</v>
-      </c>
-      <c r="H203" s="10" t="s">
-        <v>440</v>
       </c>
       <c r="I203" s="10"/>
       <c r="J203" s="9">
@@ -13267,7 +13290,7 @@
         <v>26</v>
       </c>
       <c r="N203" s="10" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O203" s="10" t="s">
         <v>197</v>
@@ -13283,7 +13306,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B204" s="5">
         <v>46162.56849315972</v>
@@ -13299,10 +13322,10 @@
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="H204" s="6" t="s">
         <v>439</v>
-      </c>
-      <c r="H204" s="6" t="s">
-        <v>440</v>
       </c>
       <c r="I204" s="6"/>
       <c r="J204" s="5">
@@ -13318,7 +13341,7 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O204" s="6" t="s">
         <v>197</v>
@@ -13334,7 +13357,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B205" s="9">
         <v>46162.568499120374</v>
@@ -13350,10 +13373,10 @@
         <v>26</v>
       </c>
       <c r="G205" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="H205" s="10" t="s">
         <v>439</v>
-      </c>
-      <c r="H205" s="10" t="s">
-        <v>440</v>
       </c>
       <c r="I205" s="10"/>
       <c r="J205" s="9">
@@ -13369,7 +13392,7 @@
         <v>26</v>
       </c>
       <c r="N205" s="10" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O205" s="10" t="s">
         <v>197</v>
@@ -13385,7 +13408,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B206" s="5">
         <v>46162.568507013886</v>
@@ -13401,10 +13424,10 @@
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="H206" s="6" t="s">
         <v>439</v>
-      </c>
-      <c r="H206" s="6" t="s">
-        <v>440</v>
       </c>
       <c r="I206" s="6"/>
       <c r="J206" s="5">
@@ -13420,7 +13443,7 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O206" s="6" t="s">
         <v>197</v>
@@ -13436,7 +13459,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B207" s="9">
         <v>46162.56851576389</v>
@@ -13452,10 +13475,10 @@
         <v>26</v>
       </c>
       <c r="G207" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="H207" s="10" t="s">
         <v>439</v>
-      </c>
-      <c r="H207" s="10" t="s">
-        <v>440</v>
       </c>
       <c r="I207" s="10"/>
       <c r="J207" s="9">
@@ -13471,7 +13494,7 @@
         <v>26</v>
       </c>
       <c r="N207" s="10" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O207" s="10" t="s">
         <v>197</v>
@@ -13487,7 +13510,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B208" s="5">
         <v>46162.559035983795</v>
@@ -13497,7 +13520,7 @@
         <v>46162.675601435185</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
@@ -13524,13 +13547,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q208" s="5">
         <v>46230</v>
@@ -13550,7 +13573,7 @@
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B209" s="9">
         <v>46162.559040057866</v>
@@ -13585,13 +13608,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O209" s="10" t="s">
         <v>191</v>
       </c>
       <c r="P209" s="10" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q209" s="10"/>
       <c r="R209" s="10"/>
@@ -13601,7 +13624,7 @@
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B210" s="5">
         <v>46162.559044305555</v>
@@ -13636,13 +13659,13 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O210" s="6" t="s">
         <v>191</v>
       </c>
       <c r="P210" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q210" s="6"/>
       <c r="R210" s="6"/>
@@ -13652,7 +13675,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B211" s="9">
         <v>46162.55904842593</v>
@@ -13687,13 +13710,13 @@
         <v>26</v>
       </c>
       <c r="N211" s="10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O211" s="10" t="s">
         <v>191</v>
       </c>
       <c r="P211" s="10" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q211" s="10"/>
       <c r="R211" s="10"/>
@@ -13703,7 +13726,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B212" s="5">
         <v>46162.55905241898</v>
@@ -13738,13 +13761,13 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O212" s="6" t="s">
         <v>191</v>
       </c>
       <c r="P212" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q212" s="6"/>
       <c r="R212" s="6"/>
@@ -13754,7 +13777,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B213" s="9">
         <v>46162.55905643519</v>
@@ -13789,13 +13812,13 @@
         <v>26</v>
       </c>
       <c r="N213" s="10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O213" s="10" t="s">
         <v>197</v>
       </c>
       <c r="P213" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="Q213" s="10"/>
       <c r="R213" s="10"/>
@@ -13805,7 +13828,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B214" s="5">
         <v>46162.568794328705</v>
@@ -13840,7 +13863,7 @@
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O214" s="6" t="s">
         <v>197</v>
@@ -13856,7 +13879,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B215" s="9">
         <v>46162.56880138889</v>
@@ -13891,7 +13914,7 @@
         <v>26</v>
       </c>
       <c r="N215" s="10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O215" s="10" t="s">
         <v>197</v>
@@ -13907,7 +13930,7 @@
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B216" s="5">
         <v>46162.56880807871</v>
@@ -13942,13 +13965,13 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O216" s="6" t="s">
         <v>197</v>
       </c>
       <c r="P216" s="6" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="Q216" s="6"/>
       <c r="R216" s="6"/>
@@ -13958,7 +13981,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B217" s="9">
         <v>46162.56881548611</v>
@@ -13993,7 +14016,7 @@
         <v>26</v>
       </c>
       <c r="N217" s="10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O217" s="10" t="s">
         <v>197</v>
@@ -14009,7 +14032,7 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B218" s="5">
         <v>46162.56882248842</v>
@@ -14044,7 +14067,7 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O218" s="6" t="s">
         <v>197</v>
@@ -14060,7 +14083,7 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B219" s="9">
         <v>46162.56882971065</v>
@@ -14095,7 +14118,7 @@
         <v>26</v>
       </c>
       <c r="N219" s="10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O219" s="10" t="s">
         <v>197</v>
@@ -14111,7 +14134,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B220" s="5">
         <v>46162.56883761574</v>
@@ -14146,7 +14169,7 @@
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O220" s="6" t="s">
         <v>197</v>
@@ -14162,7 +14185,7 @@
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B221" s="9">
         <v>46162.559060671294</v>
@@ -14172,16 +14195,16 @@
         <v>46162.67579302083</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G221" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H221" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H221" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I221" s="9">
         <v>46231</v>
@@ -14199,13 +14222,13 @@
         <v>26</v>
       </c>
       <c r="N221" s="10" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P221" s="10" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q221" s="9">
         <v>46231</v>
@@ -14225,7 +14248,7 @@
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B222" s="5">
         <v>46162.55906472223</v>
@@ -14241,10 +14264,10 @@
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H222" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H222" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I222" s="6"/>
       <c r="J222" s="5">
@@ -14260,13 +14283,13 @@
         <v>26</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O222" s="6" t="s">
         <v>191</v>
       </c>
       <c r="P222" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="Q222" s="6"/>
       <c r="R222" s="6"/>
@@ -14276,7 +14299,7 @@
     </row>
     <row r="223" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B223" s="9">
         <v>46162.55907236111</v>
@@ -14292,10 +14315,10 @@
         <v>26</v>
       </c>
       <c r="G223" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H223" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H223" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I223" s="10"/>
       <c r="J223" s="9">
@@ -14311,13 +14334,13 @@
         <v>26</v>
       </c>
       <c r="N223" s="10" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O223" s="10" t="s">
         <v>191</v>
       </c>
       <c r="P223" s="10" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="Q223" s="10"/>
       <c r="R223" s="10"/>
@@ -14327,7 +14350,7 @@
     </row>
     <row r="224" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B224" s="5">
         <v>46162.55907862268</v>
@@ -14343,10 +14366,10 @@
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H224" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H224" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I224" s="6"/>
       <c r="J224" s="5">
@@ -14362,13 +14385,13 @@
         <v>26</v>
       </c>
       <c r="N224" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O224" s="6" t="s">
         <v>191</v>
       </c>
       <c r="P224" s="6" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="Q224" s="6"/>
       <c r="R224" s="6"/>
@@ -14378,7 +14401,7 @@
     </row>
     <row r="225" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B225" s="9">
         <v>46162.55908304398</v>
@@ -14394,10 +14417,10 @@
         <v>26</v>
       </c>
       <c r="G225" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H225" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H225" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I225" s="10"/>
       <c r="J225" s="9">
@@ -14413,13 +14436,13 @@
         <v>26</v>
       </c>
       <c r="N225" s="10" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O225" s="10" t="s">
         <v>191</v>
       </c>
       <c r="P225" s="10" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="Q225" s="10"/>
       <c r="R225" s="10"/>
@@ -14429,7 +14452,7 @@
     </row>
     <row r="226" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B226" s="5">
         <v>46162.55908719907</v>
@@ -14445,10 +14468,10 @@
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H226" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H226" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I226" s="6"/>
       <c r="J226" s="5">
@@ -14464,13 +14487,13 @@
         <v>26</v>
       </c>
       <c r="N226" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O226" s="6" t="s">
         <v>197</v>
       </c>
       <c r="P226" s="6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="Q226" s="6"/>
       <c r="R226" s="6"/>
@@ -14480,7 +14503,7 @@
     </row>
     <row r="227" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" s="8" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B227" s="9">
         <v>46162.56901232639</v>
@@ -14496,10 +14519,10 @@
         <v>26</v>
       </c>
       <c r="G227" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H227" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H227" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I227" s="10"/>
       <c r="J227" s="9">
@@ -14515,7 +14538,7 @@
         <v>26</v>
       </c>
       <c r="N227" s="10" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O227" s="10" t="s">
         <v>197</v>
@@ -14531,7 +14554,7 @@
     </row>
     <row r="228" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B228" s="5">
         <v>46162.569018888884</v>
@@ -14547,10 +14570,10 @@
         <v>26</v>
       </c>
       <c r="G228" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H228" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H228" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I228" s="6"/>
       <c r="J228" s="5">
@@ -14566,7 +14589,7 @@
         <v>26</v>
       </c>
       <c r="N228" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O228" s="6" t="s">
         <v>197</v>
@@ -14582,7 +14605,7 @@
     </row>
     <row r="229" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" s="8" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B229" s="9">
         <v>46162.56902688657</v>
@@ -14592,16 +14615,16 @@
         <v>46162.67577410879</v>
       </c>
       <c r="E229" s="10" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F229" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G229" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H229" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H229" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I229" s="10"/>
       <c r="J229" s="9">
@@ -14617,7 +14640,7 @@
         <v>26</v>
       </c>
       <c r="N229" s="10" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O229" s="10" t="s">
         <v>197</v>
@@ -14633,7 +14656,7 @@
     </row>
     <row r="230" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B230" s="5">
         <v>46162.56903291667</v>
@@ -14649,10 +14672,10 @@
         <v>26</v>
       </c>
       <c r="G230" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H230" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H230" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I230" s="6"/>
       <c r="J230" s="5">
@@ -14668,7 +14691,7 @@
         <v>26</v>
       </c>
       <c r="N230" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O230" s="6" t="s">
         <v>197</v>
@@ -14684,7 +14707,7 @@
     </row>
     <row r="231" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A231" s="8" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B231" s="9">
         <v>46162.56903989583</v>
@@ -14700,10 +14723,10 @@
         <v>26</v>
       </c>
       <c r="G231" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H231" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H231" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I231" s="10"/>
       <c r="J231" s="9">
@@ -14719,7 +14742,7 @@
         <v>26</v>
       </c>
       <c r="N231" s="10" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O231" s="10" t="s">
         <v>197</v>
@@ -14735,7 +14758,7 @@
     </row>
     <row r="232" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B232" s="5">
         <v>46162.56904635417</v>
@@ -14751,10 +14774,10 @@
         <v>26</v>
       </c>
       <c r="G232" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H232" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H232" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I232" s="6"/>
       <c r="J232" s="5">
@@ -14770,7 +14793,7 @@
         <v>26</v>
       </c>
       <c r="N232" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O232" s="6" t="s">
         <v>197</v>
@@ -14786,7 +14809,7 @@
     </row>
     <row r="233" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B233" s="9">
         <v>46162.56905347222</v>
@@ -14802,10 +14825,10 @@
         <v>26</v>
       </c>
       <c r="G233" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H233" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H233" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I233" s="10"/>
       <c r="J233" s="9">
@@ -14821,7 +14844,7 @@
         <v>26</v>
       </c>
       <c r="N233" s="10" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O233" s="10" t="s">
         <v>197</v>
@@ -14837,7 +14860,7 @@
     </row>
     <row r="234" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B234" s="5">
         <v>46162.559091284726</v>
@@ -14847,16 +14870,16 @@
         <v>46162.6758584375</v>
       </c>
       <c r="E234" s="6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F234" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G234" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H234" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H234" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I234" s="5">
         <v>46232</v>
@@ -14874,13 +14897,13 @@
         <v>26</v>
       </c>
       <c r="N234" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="O234" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P234" s="6" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="Q234" s="5">
         <v>46232</v>
@@ -14900,7 +14923,7 @@
     </row>
     <row r="235" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A235" s="8" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B235" s="9">
         <v>46162.55909613426</v>
@@ -14916,10 +14939,10 @@
         <v>26</v>
       </c>
       <c r="G235" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H235" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H235" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I235" s="9">
         <v>46232</v>
@@ -14937,13 +14960,13 @@
         <v>26</v>
       </c>
       <c r="N235" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="O235" s="10" t="s">
         <v>191</v>
       </c>
       <c r="P235" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q235" s="10"/>
       <c r="R235" s="10"/>
@@ -14953,7 +14976,7 @@
     </row>
     <row r="236" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B236" s="5">
         <v>46162.55910012731</v>
@@ -14969,10 +14992,10 @@
         <v>26</v>
       </c>
       <c r="G236" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H236" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H236" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I236" s="5">
         <v>46232</v>
@@ -14990,13 +15013,13 @@
         <v>26</v>
       </c>
       <c r="N236" s="6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="O236" s="6" t="s">
         <v>191</v>
       </c>
       <c r="P236" s="6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q236" s="6"/>
       <c r="R236" s="6"/>
@@ -15006,7 +15029,7 @@
     </row>
     <row r="237" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A237" s="8" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B237" s="9">
         <v>46162.55910407407</v>
@@ -15022,10 +15045,10 @@
         <v>26</v>
       </c>
       <c r="G237" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H237" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H237" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I237" s="9">
         <v>46232</v>
@@ -15043,13 +15066,13 @@
         <v>26</v>
       </c>
       <c r="N237" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="O237" s="10" t="s">
         <v>191</v>
       </c>
       <c r="P237" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q237" s="10"/>
       <c r="R237" s="10"/>
@@ -15059,7 +15082,7 @@
     </row>
     <row r="238" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B238" s="5">
         <v>46162.559108125</v>
@@ -15075,10 +15098,10 @@
         <v>26</v>
       </c>
       <c r="G238" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H238" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H238" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I238" s="5">
         <v>46232</v>
@@ -15096,13 +15119,13 @@
         <v>26</v>
       </c>
       <c r="N238" s="6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="O238" s="6" t="s">
         <v>191</v>
       </c>
       <c r="P238" s="6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q238" s="6"/>
       <c r="R238" s="6"/>
@@ -15112,7 +15135,7 @@
     </row>
     <row r="239" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A239" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B239" s="9">
         <v>46162.55914409722</v>
@@ -15128,10 +15151,10 @@
         <v>26</v>
       </c>
       <c r="G239" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H239" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H239" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I239" s="9">
         <v>46232</v>
@@ -15149,13 +15172,13 @@
         <v>26</v>
       </c>
       <c r="N239" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="O239" s="10" t="s">
         <v>197</v>
       </c>
       <c r="P239" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q239" s="10"/>
       <c r="R239" s="10"/>
@@ -15165,7 +15188,7 @@
     </row>
     <row r="240" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B240" s="5">
         <v>46162.56958915509</v>
@@ -15181,10 +15204,10 @@
         <v>26</v>
       </c>
       <c r="G240" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H240" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H240" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I240" s="5">
         <v>46232</v>
@@ -15202,7 +15225,7 @@
         <v>26</v>
       </c>
       <c r="N240" s="6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="O240" s="6" t="s">
         <v>197</v>
@@ -15218,7 +15241,7 @@
     </row>
     <row r="241" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A241" s="8" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B241" s="9">
         <v>46162.56959587963</v>
@@ -15234,10 +15257,10 @@
         <v>26</v>
       </c>
       <c r="G241" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H241" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H241" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I241" s="9">
         <v>46232</v>
@@ -15255,7 +15278,7 @@
         <v>26</v>
       </c>
       <c r="N241" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="O241" s="10" t="s">
         <v>197</v>
@@ -15271,7 +15294,7 @@
     </row>
     <row r="242" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B242" s="5">
         <v>46162.56960513889</v>
@@ -15287,10 +15310,10 @@
         <v>26</v>
       </c>
       <c r="G242" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H242" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H242" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I242" s="5">
         <v>46232</v>
@@ -15308,10 +15331,10 @@
         <v>26</v>
       </c>
       <c r="N242" s="6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="O242" s="6" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P242" s="6" t="s">
         <v>26</v>
@@ -15324,7 +15347,7 @@
     </row>
     <row r="243" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A243" s="8" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B243" s="9">
         <v>46162.569612060186</v>
@@ -15340,10 +15363,10 @@
         <v>26</v>
       </c>
       <c r="G243" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H243" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H243" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I243" s="9">
         <v>46232</v>
@@ -15361,7 +15384,7 @@
         <v>26</v>
       </c>
       <c r="N243" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="O243" s="10" t="s">
         <v>197</v>
@@ -15377,7 +15400,7 @@
     </row>
     <row r="244" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B244" s="5">
         <v>46162.569619999995</v>
@@ -15393,10 +15416,10 @@
         <v>26</v>
       </c>
       <c r="G244" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H244" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H244" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I244" s="5">
         <v>46232</v>
@@ -15414,7 +15437,7 @@
         <v>26</v>
       </c>
       <c r="N244" s="6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="O244" s="6" t="s">
         <v>197</v>
@@ -15430,7 +15453,7 @@
     </row>
     <row r="245" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A245" s="8" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B245" s="9">
         <v>46162.569627812496</v>
@@ -15446,10 +15469,10 @@
         <v>26</v>
       </c>
       <c r="G245" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H245" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="H245" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="I245" s="9">
         <v>46232</v>
@@ -15467,7 +15490,7 @@
         <v>26</v>
       </c>
       <c r="N245" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="O245" s="10" t="s">
         <v>197</v>
@@ -15483,7 +15506,7 @@
     </row>
     <row r="246" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B246" s="5">
         <v>46162.569634513886</v>
@@ -15499,10 +15522,10 @@
         <v>26</v>
       </c>
       <c r="G246" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H246" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="H246" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="I246" s="5">
         <v>46232</v>
@@ -15520,7 +15543,7 @@
         <v>26</v>
       </c>
       <c r="N246" s="6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="O246" s="6" t="s">
         <v>197</v>
@@ -15536,7 +15559,7 @@
     </row>
     <row r="247" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A247" s="8" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B247" s="9">
         <v>46162.5591494213</v>
@@ -15546,7 +15569,7 @@
         <v>46162.664148020835</v>
       </c>
       <c r="E247" s="10" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F247" s="10" t="s">
         <v>25</v>
@@ -15570,7 +15593,7 @@
         <v>26</v>
       </c>
       <c r="O247" s="10" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="P247" s="10" t="s">
         <v>26</v>
@@ -15583,7 +15606,7 @@
     </row>
     <row r="248" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B248" s="5">
         <v>46162.559152800924</v>
@@ -15593,16 +15616,16 @@
         <v>46162.676061377315</v>
       </c>
       <c r="E248" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="F248" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G248" s="6" t="s">
         <v>509</v>
       </c>
-      <c r="F248" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G248" s="6" t="s">
+      <c r="H248" s="6" t="s">
         <v>510</v>
-      </c>
-      <c r="H248" s="6" t="s">
-        <v>511</v>
       </c>
       <c r="I248" s="5">
         <v>46233</v>
@@ -15620,13 +15643,13 @@
         <v>26</v>
       </c>
       <c r="N248" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="O248" s="6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="P248" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="Q248" s="5">
         <v>46233</v>
@@ -15646,7 +15669,7 @@
     </row>
     <row r="249" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A249" s="8" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B249" s="9">
         <v>46162.55915726852</v>
@@ -15656,7 +15679,7 @@
         <v>46197.69418131944</v>
       </c>
       <c r="E249" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F249" s="10" t="s">
         <v>26</v>
@@ -15683,13 +15706,13 @@
         <v>26</v>
       </c>
       <c r="N249" s="10" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="O249" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="P249" s="10" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="Q249" s="9">
         <v>46233</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -849,64 +849,64 @@
     <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
   </si>
   <si>
+    <t>1214969466610550</t>
+  </si>
+  <si>
+    <t>OT 4324- ZVN 1-7-37/2 ,check planos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armado,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
+    <t>1214969379260053</t>
+  </si>
+  <si>
+    <t>1214969379260073</t>
+  </si>
+  <si>
+    <t>OT 4324- ZVN 1-7-37/2 ,Armado</t>
+  </si>
+  <si>
+    <t>1214969379268441</t>
+  </si>
+  <si>
+    <t>1214969335531196</t>
+  </si>
+  <si>
+    <t>Armado,OT 4325- ZVN 1-7-63/2</t>
+  </si>
+  <si>
+    <t>1214969047720343</t>
+  </si>
+  <si>
+    <t>1214969047720344</t>
+  </si>
+  <si>
+    <t>1214969047720345</t>
+  </si>
+  <si>
+    <t>1214969047720346</t>
+  </si>
+  <si>
+    <t>1214969047720347</t>
+  </si>
+  <si>
+    <t>1214969047720348</t>
+  </si>
+  <si>
+    <t>1214969047720349</t>
+  </si>
+  <si>
+    <t>1214969335531211</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4325- ZVN 1-7-63/2</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214969466610550</t>
-  </si>
-  <si>
-    <t>OT 4324- ZVN 1-7-37/2 ,check planos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armado,OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t>1214969379260053</t>
-  </si>
-  <si>
-    <t>1214969379260073</t>
-  </si>
-  <si>
-    <t>OT 4324- ZVN 1-7-37/2 ,Armado</t>
-  </si>
-  <si>
-    <t>1214969379268441</t>
-  </si>
-  <si>
-    <t>1214969335531196</t>
-  </si>
-  <si>
-    <t>Armado,OT 4325- ZVN 1-7-63/2</t>
-  </si>
-  <si>
-    <t>1214969047720343</t>
-  </si>
-  <si>
-    <t>1214969047720344</t>
-  </si>
-  <si>
-    <t>1214969047720345</t>
-  </si>
-  <si>
-    <t>1214969047720346</t>
-  </si>
-  <si>
-    <t>1214969047720347</t>
-  </si>
-  <si>
-    <t>1214969047720348</t>
-  </si>
-  <si>
-    <t>1214969047720349</t>
-  </si>
-  <si>
-    <t>1214969335531211</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4325- ZVN 1-7-63/2</t>
   </si>
   <si>
     <t>1214969379273832</t>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46216.16904840278</v>
+        <v>46217.173818703704</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>255</v>
@@ -6967,8 +6967,8 @@
       <c r="R84" s="5">
         <v>46216</v>
       </c>
-      <c r="S84" s="12" t="s">
-        <v>257</v>
+      <c r="S84" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
@@ -6979,7 +6979,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B85" s="9">
         <v>46162.558626620375</v>
@@ -7019,10 +7019,10 @@
         <v>255</v>
       </c>
       <c r="O85" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="P85" s="10" t="s">
         <v>259</v>
-      </c>
-      <c r="P85" s="10" t="s">
-        <v>260</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -7032,7 +7032,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B86" s="5">
         <v>46162.55863280092</v>
@@ -7072,10 +7072,10 @@
         <v>255</v>
       </c>
       <c r="O86" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="P86" s="6" t="s">
         <v>259</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>260</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -7085,7 +7085,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B87" s="9">
         <v>46162.55863850695</v>
@@ -7125,10 +7125,10 @@
         <v>255</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -7138,7 +7138,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B88" s="5">
         <v>46162.558644247685</v>
@@ -7178,10 +7178,10 @@
         <v>255</v>
       </c>
       <c r="O88" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="P88" s="6" t="s">
         <v>259</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>260</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7191,7 +7191,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B89" s="9">
         <v>46162.55864990741</v>
@@ -7234,7 +7234,7 @@
         <v>197</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -7244,7 +7244,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B90" s="5">
         <v>46162.56148016204</v>
@@ -7297,7 +7297,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B91" s="9">
         <v>46162.561489201384</v>
@@ -7350,7 +7350,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B92" s="5">
         <v>46162.56149930556</v>
@@ -7403,7 +7403,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B93" s="9">
         <v>46162.561507199076</v>
@@ -7456,7 +7456,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B94" s="5">
         <v>46162.56151613426</v>
@@ -7509,7 +7509,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B95" s="9">
         <v>46162.56152413195</v>
@@ -7562,7 +7562,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B96" s="5">
         <v>46162.56153119213</v>
@@ -7615,17 +7615,17 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B97" s="9">
         <v>46162.55865439815</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46210.17988293982</v>
+        <v>46217.168480266206</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7655,7 +7655,7 @@
         <v>228</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>228</v>
@@ -7667,7 +7667,7 @@
         <v>46217</v>
       </c>
       <c r="S97" s="12" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="T97" s="10">
         <v>0</v>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46198.7933840162</v>
+        <v>46217.16848263889</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>191</v>
@@ -7715,10 +7715,10 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>278</v>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46198.79338457176</v>
+        <v>46217.168484050926</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>191</v>
@@ -7768,10 +7768,10 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>280</v>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46198.79337287037</v>
+        <v>46217.16847319444</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>191</v>
@@ -7821,10 +7821,10 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>282</v>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46198.793388391205</v>
+        <v>46217.16847716435</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>191</v>
@@ -7874,10 +7874,10 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>284</v>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46162.67376247685</v>
+        <v>46217.168485312504</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>197</v>
@@ -7927,7 +7927,7 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>197</v>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46162.67376181713</v>
+        <v>46217.16846244213</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>197</v>
@@ -7980,7 +7980,7 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O103" s="10" t="s">
         <v>197</v>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46162.67376091435</v>
+        <v>46217.16846439815</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>197</v>
@@ -8033,7 +8033,7 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>289</v>
@@ -8056,7 +8056,7 @@
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46162.67376023148</v>
+        <v>46217.16846583333</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>197</v>
@@ -8086,7 +8086,7 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O105" s="10" t="s">
         <v>197</v>
@@ -8109,7 +8109,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46162.67375957176</v>
+        <v>46217.16846726852</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>197</v>
@@ -8139,7 +8139,7 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>197</v>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46162.67375887731</v>
+        <v>46217.16846878472</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>197</v>
@@ -8192,7 +8192,7 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O107" s="10" t="s">
         <v>197</v>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46162.67375819445</v>
+        <v>46217.168470358796</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>197</v>
@@ -8245,7 +8245,7 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>197</v>
@@ -8268,7 +8268,7 @@
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46162.67375751157</v>
+        <v>46217.16847178241</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>197</v>
@@ -8298,7 +8298,7 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O109" s="10" t="s">
         <v>197</v>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46216.544257754635</v>
+        <v>46217.19024513889</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>313</v>
@@ -8717,8 +8717,8 @@
       <c r="R116" s="5">
         <v>46224</v>
       </c>
-      <c r="S116" s="7" t="s">
-        <v>55</v>
+      <c r="S116" s="12" t="s">
+        <v>276</v>
       </c>
       <c r="T116" s="6">
         <v>0</v>
@@ -9405,7 +9405,7 @@
         <v>310</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P129" s="10" t="s">
         <v>310</v>
@@ -9417,7 +9417,7 @@
         <v>46219</v>
       </c>
       <c r="S129" s="12" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="T129" s="10">
         <v>0</v>
@@ -10092,7 +10092,7 @@
         <v>46220</v>
       </c>
       <c r="S142" s="12" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="T142" s="6">
         <v>0</v>
@@ -10791,7 +10791,7 @@
         <v>46223</v>
       </c>
       <c r="S155" s="12" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="T155" s="10">
         <v>0</v>
@@ -11445,7 +11445,7 @@
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46162.67399393518</v>
+        <v>46217.19024570602</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>399</v>
@@ -11489,8 +11489,8 @@
       <c r="R168" s="5">
         <v>46224</v>
       </c>
-      <c r="S168" s="7" t="s">
-        <v>55</v>
+      <c r="S168" s="12" t="s">
+        <v>276</v>
       </c>
       <c r="T168" s="6">
         <v>0</v>
@@ -14225,7 +14225,7 @@
         <v>434</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P221" s="10" t="s">
         <v>434</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -648,6 +648,9 @@
     <t xml:space="preserve">OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1214969335458375</t>
   </si>
   <si>
@@ -904,9 +907,6 @@
   </si>
   <si>
     <t>OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4325- ZVN 1-7-63/2</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214969379273832</t>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46162.671697337966</v>
+        <v>46218.17936890046</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -5103,8 +5103,8 @@
       <c r="R50" s="5">
         <v>46225</v>
       </c>
-      <c r="S50" s="7" t="s">
-        <v>55</v>
+      <c r="S50" s="12" t="s">
+        <v>190</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -5115,7 +5115,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B51" s="9">
         <v>46162.5584890162</v>
@@ -5125,7 +5125,7 @@
         <v>46191.68638508102</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -5153,10 +5153,10 @@
         <v>186</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -5166,7 +5166,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B52" s="5">
         <v>46162.558492951386</v>
@@ -5176,7 +5176,7 @@
         <v>46191.68638201389</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -5204,10 +5204,10 @@
         <v>186</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -5217,7 +5217,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B53" s="9">
         <v>46162.55849660879</v>
@@ -5227,7 +5227,7 @@
         <v>46191.68637913195</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -5255,10 +5255,10 @@
         <v>186</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -5268,7 +5268,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B54" s="5">
         <v>46162.55849916667</v>
@@ -5278,7 +5278,7 @@
         <v>46191.68637614584</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -5306,10 +5306,10 @@
         <v>186</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5319,7 +5319,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B55" s="9">
         <v>46162.55850175926</v>
@@ -5329,7 +5329,7 @@
         <v>46191.6863727662</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -5357,10 +5357,10 @@
         <v>186</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B56" s="5">
         <v>46162.56211614583</v>
@@ -5380,7 +5380,7 @@
         <v>46191.686369641204</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -5408,7 +5408,7 @@
         <v>186</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -5421,7 +5421,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B57" s="9">
         <v>46162.56212396991</v>
@@ -5431,7 +5431,7 @@
         <v>46191.68636637731</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
@@ -5459,10 +5459,10 @@
         <v>186</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5472,7 +5472,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B58" s="5">
         <v>46162.56213497685</v>
@@ -5482,7 +5482,7 @@
         <v>46191.686363761575</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -5510,10 +5510,10 @@
         <v>186</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5523,7 +5523,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B59" s="9">
         <v>46162.562155057865</v>
@@ -5533,7 +5533,7 @@
         <v>46191.6863608912</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -5561,7 +5561,7 @@
         <v>186</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>26</v>
@@ -5574,7 +5574,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B60" s="5">
         <v>46162.562163055554</v>
@@ -5584,7 +5584,7 @@
         <v>46191.68635278935</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -5612,7 +5612,7 @@
         <v>186</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5625,7 +5625,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B61" s="9">
         <v>46162.56217104167</v>
@@ -5635,7 +5635,7 @@
         <v>46191.68635209491</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -5663,7 +5663,7 @@
         <v>186</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5676,7 +5676,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B62" s="5">
         <v>46162.562178935186</v>
@@ -5686,7 +5686,7 @@
         <v>46191.686351412034</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5714,10 +5714,10 @@
         <v>186</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5727,7 +5727,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B63" s="9">
         <v>46162.55850443287</v>
@@ -5739,7 +5739,7 @@
         <v>46216.608532638886</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>25</v>
@@ -5763,7 +5763,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>26</v>
@@ -5780,7 +5780,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B64" s="5">
         <v>46162.558507546295</v>
@@ -5792,16 +5792,16 @@
         <v>46216.60235340278</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I64" s="5">
         <v>46203</v>
@@ -5819,13 +5819,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>137</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q64" s="5">
         <v>46203</v>
@@ -5845,7 +5845,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B65" s="9">
         <v>46162.5585121412</v>
@@ -5857,7 +5857,7 @@
         <v>46216.603024375</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5884,13 +5884,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q65" s="9">
         <v>46204</v>
@@ -5910,7 +5910,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B66" s="5">
         <v>46162.558518645834</v>
@@ -5922,16 +5922,16 @@
         <v>46216.60332174768</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I66" s="5">
         <v>46203</v>
@@ -5949,13 +5949,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>145</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q66" s="5">
         <v>46203</v>
@@ -5975,7 +5975,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B67" s="9">
         <v>46162.55852324074</v>
@@ -5987,7 +5987,7 @@
         <v>46216.603370682875</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -6014,13 +6014,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q67" s="9">
         <v>46204</v>
@@ -6040,7 +6040,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B68" s="5">
         <v>46162.5585274537</v>
@@ -6052,16 +6052,16 @@
         <v>46216.60848061343</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I68" s="5">
         <v>46203</v>
@@ -6079,13 +6079,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>167</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q68" s="5">
         <v>46203</v>
@@ -6105,7 +6105,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B69" s="9">
         <v>46162.558531400464</v>
@@ -6117,7 +6117,7 @@
         <v>46216.60852013889</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -6144,13 +6144,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q69" s="9">
         <v>46204</v>
@@ -6170,7 +6170,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B70" s="5">
         <v>46162.55853556713</v>
@@ -6180,7 +6180,7 @@
         <v>46162.61139740741</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -6204,7 +6204,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -6217,7 +6217,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B71" s="9">
         <v>46162.558538067125</v>
@@ -6227,16 +6227,16 @@
         <v>46210.17224337963</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I71" s="9">
         <v>46205</v>
@@ -6254,13 +6254,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q71" s="9">
         <v>46205</v>
@@ -6280,7 +6280,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B72" s="5">
         <v>46162.558542557876</v>
@@ -6290,16 +6290,16 @@
         <v>46216.60851978009</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I72" s="5">
         <v>46205</v>
@@ -6317,13 +6317,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6333,7 +6333,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B73" s="9">
         <v>46162.558548402776</v>
@@ -6343,16 +6343,16 @@
         <v>46216.608520821756</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I73" s="9">
         <v>46205</v>
@@ -6370,13 +6370,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -6386,7 +6386,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B74" s="5">
         <v>46162.55855412037</v>
@@ -6396,16 +6396,16 @@
         <v>46216.608521828704</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I74" s="5">
         <v>46205</v>
@@ -6423,13 +6423,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6439,7 +6439,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B75" s="9">
         <v>46162.558560000005</v>
@@ -6449,16 +6449,16 @@
         <v>46216.6085178125</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I75" s="9">
         <v>46205</v>
@@ -6476,13 +6476,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6492,7 +6492,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B76" s="5">
         <v>46162.558565671294</v>
@@ -6502,16 +6502,16 @@
         <v>46216.60851880787</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I76" s="5">
         <v>46205</v>
@@ -6529,13 +6529,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6545,7 +6545,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B77" s="9">
         <v>46162.56018778935</v>
@@ -6555,16 +6555,16 @@
         <v>46216.60851089121</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I77" s="9">
         <v>46205</v>
@@ -6582,13 +6582,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6598,7 +6598,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B78" s="5">
         <v>46162.560207789356</v>
@@ -6608,16 +6608,16 @@
         <v>46216.60851201389</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I78" s="5">
         <v>46205</v>
@@ -6635,13 +6635,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6651,7 +6651,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B79" s="9">
         <v>46162.5602175463</v>
@@ -6661,16 +6661,16 @@
         <v>46216.608512997685</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I79" s="9">
         <v>46205</v>
@@ -6688,13 +6688,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6704,7 +6704,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B80" s="5">
         <v>46162.56022641204</v>
@@ -6714,16 +6714,16 @@
         <v>46216.608513900464</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I80" s="5">
         <v>46205</v>
@@ -6741,13 +6741,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6757,7 +6757,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B81" s="9">
         <v>46162.56023459491</v>
@@ -6767,16 +6767,16 @@
         <v>46216.60851494213</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I81" s="9">
         <v>46205</v>
@@ -6794,13 +6794,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6810,7 +6810,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B82" s="5">
         <v>46162.56024284722</v>
@@ -6820,16 +6820,16 @@
         <v>46216.6085158912</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I82" s="5">
         <v>46205</v>
@@ -6847,13 +6847,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6863,7 +6863,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B83" s="9">
         <v>46162.560250625</v>
@@ -6873,16 +6873,16 @@
         <v>46216.60851681713</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I83" s="9">
         <v>46205</v>
@@ -6900,13 +6900,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6916,7 +6916,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B84" s="5">
         <v>46162.55862063657</v>
@@ -6926,16 +6926,16 @@
         <v>46217.173818703704</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I84" s="5">
         <v>46210</v>
@@ -6953,13 +6953,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q84" s="5">
         <v>46210</v>
@@ -6979,7 +6979,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B85" s="9">
         <v>46162.558626620375</v>
@@ -6989,16 +6989,16 @@
         <v>46216.16902931713</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I85" s="9">
         <v>46210</v>
@@ -7016,13 +7016,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -7032,7 +7032,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B86" s="5">
         <v>46162.55863280092</v>
@@ -7042,16 +7042,16 @@
         <v>46216.169044270835</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I86" s="5">
         <v>46210</v>
@@ -7069,13 +7069,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -7085,7 +7085,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B87" s="9">
         <v>46162.55863850695</v>
@@ -7095,16 +7095,16 @@
         <v>46216.16904583333</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I87" s="9">
         <v>46210</v>
@@ -7122,13 +7122,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -7138,7 +7138,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B88" s="5">
         <v>46162.558644247685</v>
@@ -7148,16 +7148,16 @@
         <v>46216.1690471412</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I88" s="5">
         <v>46210</v>
@@ -7175,13 +7175,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7191,7 +7191,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B89" s="9">
         <v>46162.55864990741</v>
@@ -7201,16 +7201,16 @@
         <v>46216.16904278935</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I89" s="9">
         <v>46210</v>
@@ -7228,13 +7228,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -7244,7 +7244,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B90" s="5">
         <v>46162.56148016204</v>
@@ -7254,16 +7254,16 @@
         <v>46216.169030324076</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I90" s="5">
         <v>46210</v>
@@ -7281,13 +7281,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7297,7 +7297,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B91" s="9">
         <v>46162.561489201384</v>
@@ -7307,16 +7307,16 @@
         <v>46216.169031840276</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I91" s="9">
         <v>46210</v>
@@ -7334,10 +7334,10 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P91" s="10" t="s">
         <v>26</v>
@@ -7350,7 +7350,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B92" s="5">
         <v>46162.56149930556</v>
@@ -7360,16 +7360,16 @@
         <v>46216.16903329861</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I92" s="5">
         <v>46210</v>
@@ -7387,13 +7387,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7403,7 +7403,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B93" s="9">
         <v>46162.561507199076</v>
@@ -7413,16 +7413,16 @@
         <v>46216.16903479167</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I93" s="9">
         <v>46210</v>
@@ -7440,13 +7440,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7456,7 +7456,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B94" s="5">
         <v>46162.56151613426</v>
@@ -7466,16 +7466,16 @@
         <v>46216.16903612269</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I94" s="5">
         <v>46210</v>
@@ -7493,13 +7493,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7509,7 +7509,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B95" s="9">
         <v>46162.56152413195</v>
@@ -7519,16 +7519,16 @@
         <v>46216.16903741898</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I95" s="9">
         <v>46210</v>
@@ -7546,13 +7546,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7562,7 +7562,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B96" s="5">
         <v>46162.56153119213</v>
@@ -7572,16 +7572,16 @@
         <v>46216.16903872685</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I96" s="5">
         <v>46210</v>
@@ -7599,13 +7599,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7615,17 +7615,17 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B97" s="9">
         <v>46162.55865439815</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46217.168480266206</v>
+        <v>46218.20591833333</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7652,13 +7652,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q97" s="9">
         <v>46217</v>
@@ -7666,8 +7666,8 @@
       <c r="R97" s="9">
         <v>46217</v>
       </c>
-      <c r="S97" s="12" t="s">
-        <v>276</v>
+      <c r="S97" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T97" s="10">
         <v>0</v>
@@ -7688,7 +7688,7 @@
         <v>46217.16848263889</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7715,10 +7715,10 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>278</v>
@@ -7741,7 +7741,7 @@
         <v>46217.168484050926</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7768,10 +7768,10 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>280</v>
@@ -7794,7 +7794,7 @@
         <v>46217.16847319444</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7821,10 +7821,10 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>282</v>
@@ -7847,7 +7847,7 @@
         <v>46217.16847716435</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7874,10 +7874,10 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>284</v>
@@ -7900,7 +7900,7 @@
         <v>46217.168485312504</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7927,10 +7927,10 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>286</v>
@@ -7953,7 +7953,7 @@
         <v>46217.16846244213</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7980,13 +7980,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -8006,7 +8006,7 @@
         <v>46217.16846439815</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -8033,13 +8033,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>289</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -8059,7 +8059,7 @@
         <v>46217.16846583333</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -8086,13 +8086,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -8112,7 +8112,7 @@
         <v>46217.16846726852</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -8139,13 +8139,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8165,7 +8165,7 @@
         <v>46217.16846878472</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -8192,13 +8192,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -8218,7 +8218,7 @@
         <v>46217.168470358796</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8245,13 +8245,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8271,7 +8271,7 @@
         <v>46217.16847178241</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -8298,13 +8298,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8324,7 +8324,7 @@
         <v>46216.54541798611</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>25</v>
@@ -8379,10 +8379,10 @@
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I111" s="9">
         <v>46161</v>
@@ -8400,7 +8400,7 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O111" s="10" t="s">
         <v>114</v>
@@ -8444,10 +8444,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I112" s="5">
         <v>46161</v>
@@ -8465,7 +8465,7 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>105</v>
@@ -8507,10 +8507,10 @@
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I113" s="9">
         <v>46196</v>
@@ -8528,7 +8528,7 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O113" s="10" t="s">
         <v>123</v>
@@ -8572,10 +8572,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I114" s="5">
         <v>46232</v>
@@ -8593,7 +8593,7 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>155</v>
@@ -8718,7 +8718,7 @@
         <v>46224</v>
       </c>
       <c r="S116" s="12" t="s">
-        <v>276</v>
+        <v>190</v>
       </c>
       <c r="T116" s="6">
         <v>0</v>
@@ -8739,7 +8739,7 @@
         <v>46216.544258368056</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8792,7 +8792,7 @@
         <v>46216.54425895833</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8845,7 +8845,7 @@
         <v>46162.67425633102</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8875,7 +8875,7 @@
         <v>313</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P119" s="10" t="s">
         <v>319</v>
@@ -8898,7 +8898,7 @@
         <v>46162.674253379635</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8928,7 +8928,7 @@
         <v>313</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>319</v>
@@ -8951,7 +8951,7 @@
         <v>46162.67425</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8981,10 +8981,10 @@
         <v>313</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -9004,7 +9004,7 @@
         <v>46162.67424702546</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -9034,10 +9034,10 @@
         <v>313</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -9057,7 +9057,7 @@
         <v>46162.67424429399</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -9087,10 +9087,10 @@
         <v>313</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -9110,7 +9110,7 @@
         <v>46162.674233321755</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -9140,10 +9140,10 @@
         <v>313</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9163,7 +9163,7 @@
         <v>46162.67423263889</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -9193,10 +9193,10 @@
         <v>313</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -9216,7 +9216,7 @@
         <v>46162.674231944446</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9246,10 +9246,10 @@
         <v>313</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9269,7 +9269,7 @@
         <v>46162.674231261575</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -9299,10 +9299,10 @@
         <v>313</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9322,7 +9322,7 @@
         <v>46162.67423060186</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9352,10 +9352,10 @@
         <v>313</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9405,7 +9405,7 @@
         <v>310</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P129" s="10" t="s">
         <v>310</v>
@@ -9417,7 +9417,7 @@
         <v>46219</v>
       </c>
       <c r="S129" s="12" t="s">
-        <v>276</v>
+        <v>190</v>
       </c>
       <c r="T129" s="10">
         <v>0</v>
@@ -9438,7 +9438,7 @@
         <v>46216.545420497685</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9489,7 +9489,7 @@
         <v>46216.54541923611</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9540,7 +9540,7 @@
         <v>46216.54542087963</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9591,7 +9591,7 @@
         <v>46216.545421400464</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9642,7 +9642,7 @@
         <v>46162.67438523148</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9670,7 +9670,7 @@
         <v>330</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>341</v>
@@ -9693,7 +9693,7 @@
         <v>46216.545414016204</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9724,7 +9724,7 @@
         <v>343</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9744,7 +9744,7 @@
         <v>46216.54541466435</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9775,7 +9775,7 @@
         <v>345</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9795,7 +9795,7 @@
         <v>46216.54541517361</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9826,7 +9826,7 @@
         <v>343</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9846,7 +9846,7 @@
         <v>46216.545415636574</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9897,7 +9897,7 @@
         <v>46216.54541619213</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -9928,7 +9928,7 @@
         <v>343</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9948,7 +9948,7 @@
         <v>46216.545416747686</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9979,7 +9979,7 @@
         <v>351</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9999,7 +9999,7 @@
         <v>46216.54541722222</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -10030,7 +10030,7 @@
         <v>351</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -10080,7 +10080,7 @@
         <v>310</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>310</v>
@@ -10092,7 +10092,7 @@
         <v>46220</v>
       </c>
       <c r="S142" s="12" t="s">
-        <v>276</v>
+        <v>190</v>
       </c>
       <c r="T142" s="6">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>46216.545412060186</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -10166,7 +10166,7 @@
         <v>46216.54541274306</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -10219,7 +10219,7 @@
         <v>46216.54541334491</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -10272,7 +10272,7 @@
         <v>46216.545413935186</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10325,7 +10325,7 @@
         <v>46162.674524965274</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -10355,7 +10355,7 @@
         <v>354</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P147" s="10" t="s">
         <v>364</v>
@@ -10378,7 +10378,7 @@
         <v>46216.54540832176</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10411,7 +10411,7 @@
         <v>366</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10431,7 +10431,7 @@
         <v>46162.67451787037</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -10461,10 +10461,10 @@
         <v>354</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10484,7 +10484,7 @@
         <v>46216.54540890046</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10517,7 +10517,7 @@
         <v>366</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10570,7 +10570,7 @@
         <v>366</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10590,7 +10590,7 @@
         <v>46216.545409976854</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10623,7 +10623,7 @@
         <v>366</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10643,7 +10643,7 @@
         <v>46216.54541050926</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10676,7 +10676,7 @@
         <v>366</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q153" s="10"/>
       <c r="R153" s="10"/>
@@ -10696,7 +10696,7 @@
         <v>46216.545411099534</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10729,7 +10729,7 @@
         <v>366</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10791,7 +10791,7 @@
         <v>46223</v>
       </c>
       <c r="S155" s="12" t="s">
-        <v>276</v>
+        <v>190</v>
       </c>
       <c r="T155" s="10">
         <v>0</v>
@@ -10812,7 +10812,7 @@
         <v>46198.7933762037</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10865,7 +10865,7 @@
         <v>46198.79337655092</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
@@ -10918,7 +10918,7 @@
         <v>46198.793389375</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10971,7 +10971,7 @@
         <v>46198.79338491899</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
@@ -11024,7 +11024,7 @@
         <v>46162.674682349534</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -11054,7 +11054,7 @@
         <v>374</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P160" s="6" t="s">
         <v>385</v>
@@ -11077,7 +11077,7 @@
         <v>46162.674678888885</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
@@ -11130,7 +11130,7 @@
         <v>46162.67467586805</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -11163,7 +11163,7 @@
         <v>387</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11183,7 +11183,7 @@
         <v>46162.67467314815</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
@@ -11236,7 +11236,7 @@
         <v>46162.67467030093</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11289,7 +11289,7 @@
         <v>46162.67466239583</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
@@ -11342,7 +11342,7 @@
         <v>46162.674661655095</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11395,7 +11395,7 @@
         <v>46162.67466097222</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
@@ -11428,7 +11428,7 @@
         <v>387</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q167" s="10"/>
       <c r="R167" s="10"/>
@@ -11478,7 +11478,7 @@
         <v>310</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P168" s="6" t="s">
         <v>310</v>
@@ -11490,7 +11490,7 @@
         <v>46224</v>
       </c>
       <c r="S168" s="12" t="s">
-        <v>276</v>
+        <v>190</v>
       </c>
       <c r="T168" s="6">
         <v>0</v>
@@ -11511,7 +11511,7 @@
         <v>46162.67483585648</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
@@ -11539,7 +11539,7 @@
         <v>399</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P169" s="10" t="s">
         <v>401</v>
@@ -11562,7 +11562,7 @@
         <v>46162.674832847224</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11590,7 +11590,7 @@
         <v>399</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P170" s="6" t="s">
         <v>401</v>
@@ -11613,7 +11613,7 @@
         <v>46162.67482962963</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11641,7 +11641,7 @@
         <v>399</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P171" s="10" t="s">
         <v>404</v>
@@ -11664,7 +11664,7 @@
         <v>46162.67482693287</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11692,7 +11692,7 @@
         <v>399</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P172" s="6" t="s">
         <v>404</v>
@@ -11715,7 +11715,7 @@
         <v>46162.67482414352</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
@@ -11743,7 +11743,7 @@
         <v>399</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P173" s="10" t="s">
         <v>407</v>
@@ -11766,7 +11766,7 @@
         <v>46162.67482128472</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
@@ -11794,7 +11794,7 @@
         <v>399</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P174" s="6" t="s">
         <v>26</v>
@@ -11817,7 +11817,7 @@
         <v>46162.67481818287</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
@@ -11845,10 +11845,10 @@
         <v>399</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q175" s="10"/>
       <c r="R175" s="10"/>
@@ -11868,7 +11868,7 @@
         <v>46162.674815543985</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
@@ -11896,7 +11896,7 @@
         <v>399</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P176" s="6" t="s">
         <v>26</v>
@@ -11919,7 +11919,7 @@
         <v>46162.674812743055</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
@@ -11947,7 +11947,7 @@
         <v>399</v>
       </c>
       <c r="O177" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P177" s="10" t="s">
         <v>26</v>
@@ -11970,7 +11970,7 @@
         <v>46162.67480497685</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
@@ -11998,7 +11998,7 @@
         <v>399</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P178" s="6" t="s">
         <v>26</v>
@@ -12021,7 +12021,7 @@
         <v>46162.674804317125</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
@@ -12049,7 +12049,7 @@
         <v>399</v>
       </c>
       <c r="O179" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P179" s="10" t="s">
         <v>26</v>
@@ -12072,7 +12072,7 @@
         <v>46162.674803587965</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
@@ -12100,10 +12100,10 @@
         <v>399</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -12186,7 +12186,7 @@
         <v>46162.675084849536</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
@@ -12214,7 +12214,7 @@
         <v>416</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P182" s="6" t="s">
         <v>419</v>
@@ -12237,7 +12237,7 @@
         <v>46162.67508193287</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>26</v>
@@ -12265,7 +12265,7 @@
         <v>416</v>
       </c>
       <c r="O183" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P183" s="10" t="s">
         <v>419</v>
@@ -12288,7 +12288,7 @@
         <v>46162.67507869213</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
@@ -12316,7 +12316,7 @@
         <v>416</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P184" s="6" t="s">
         <v>422</v>
@@ -12339,7 +12339,7 @@
         <v>46162.67507611111</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
@@ -12367,7 +12367,7 @@
         <v>416</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P185" s="10" t="s">
         <v>419</v>
@@ -12390,7 +12390,7 @@
         <v>46162.6750730787</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
@@ -12418,7 +12418,7 @@
         <v>416</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P186" s="6" t="s">
         <v>425</v>
@@ -12441,7 +12441,7 @@
         <v>46162.675070150464</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
@@ -12469,7 +12469,7 @@
         <v>416</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P187" s="10" t="s">
         <v>26</v>
@@ -12492,7 +12492,7 @@
         <v>46162.6750674537</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12520,7 +12520,7 @@
         <v>416</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P188" s="6" t="s">
         <v>391</v>
@@ -12543,7 +12543,7 @@
         <v>46162.67506488426</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
@@ -12571,10 +12571,10 @@
         <v>416</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12594,7 +12594,7 @@
         <v>46162.67506164352</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12622,10 +12622,10 @@
         <v>416</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12645,7 +12645,7 @@
         <v>46162.67505446759</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
@@ -12673,10 +12673,10 @@
         <v>416</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12696,7 +12696,7 @@
         <v>46162.675053750005</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -12724,10 +12724,10 @@
         <v>416</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12747,7 +12747,7 @@
         <v>46162.67505302084</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>26</v>
@@ -12775,10 +12775,10 @@
         <v>416</v>
       </c>
       <c r="O193" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P193" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q193" s="10"/>
       <c r="R193" s="10"/>
@@ -12908,7 +12908,7 @@
         <v>46162.67538505787</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
@@ -12936,7 +12936,7 @@
         <v>437</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P196" s="6" t="s">
         <v>442</v>
@@ -12959,7 +12959,7 @@
         <v>46162.675382534726</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>26</v>
@@ -12987,7 +12987,7 @@
         <v>437</v>
       </c>
       <c r="O197" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P197" s="10" t="s">
         <v>442</v>
@@ -13010,7 +13010,7 @@
         <v>46162.67537990741</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
@@ -13038,7 +13038,7 @@
         <v>437</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P198" s="6" t="s">
         <v>442</v>
@@ -13061,7 +13061,7 @@
         <v>46162.67537715277</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>26</v>
@@ -13089,7 +13089,7 @@
         <v>437</v>
       </c>
       <c r="O199" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P199" s="10" t="s">
         <v>442</v>
@@ -13112,7 +13112,7 @@
         <v>46162.675374178245</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
@@ -13140,7 +13140,7 @@
         <v>437</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P200" s="6" t="s">
         <v>447</v>
@@ -13163,7 +13163,7 @@
         <v>46162.675371296296</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
@@ -13191,7 +13191,7 @@
         <v>437</v>
       </c>
       <c r="O201" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P201" s="10" t="s">
         <v>391</v>
@@ -13214,7 +13214,7 @@
         <v>46162.675368321754</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
@@ -13242,7 +13242,7 @@
         <v>437</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P202" s="6" t="s">
         <v>26</v>
@@ -13265,7 +13265,7 @@
         <v>46162.67536565972</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
@@ -13293,10 +13293,10 @@
         <v>437</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P203" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q203" s="10"/>
       <c r="R203" s="10"/>
@@ -13316,7 +13316,7 @@
         <v>46162.67536296297</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
@@ -13344,10 +13344,10 @@
         <v>437</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13367,7 +13367,7 @@
         <v>46162.67535506944</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
@@ -13395,10 +13395,10 @@
         <v>437</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q205" s="10"/>
       <c r="R205" s="10"/>
@@ -13418,7 +13418,7 @@
         <v>46162.67535439815</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
@@ -13446,10 +13446,10 @@
         <v>437</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13469,7 +13469,7 @@
         <v>46162.67535373842</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
@@ -13497,10 +13497,10 @@
         <v>437</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q207" s="10"/>
       <c r="R207" s="10"/>
@@ -13550,7 +13550,7 @@
         <v>434</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P208" s="6" t="s">
         <v>434</v>
@@ -13583,7 +13583,7 @@
         <v>46162.67559398148</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
@@ -13611,7 +13611,7 @@
         <v>456</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P209" s="10" t="s">
         <v>458</v>
@@ -13634,7 +13634,7 @@
         <v>46162.67559118055</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
@@ -13662,7 +13662,7 @@
         <v>456</v>
       </c>
       <c r="O210" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P210" s="6" t="s">
         <v>458</v>
@@ -13685,7 +13685,7 @@
         <v>46162.675588391205</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>26</v>
@@ -13713,7 +13713,7 @@
         <v>456</v>
       </c>
       <c r="O211" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P211" s="10" t="s">
         <v>458</v>
@@ -13736,7 +13736,7 @@
         <v>46162.67558560186</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
@@ -13764,7 +13764,7 @@
         <v>456</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P212" s="6" t="s">
         <v>458</v>
@@ -13787,7 +13787,7 @@
         <v>46162.67558284722</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>26</v>
@@ -13815,7 +13815,7 @@
         <v>456</v>
       </c>
       <c r="O213" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P213" s="10" t="s">
         <v>463</v>
@@ -13838,7 +13838,7 @@
         <v>46162.6755797338</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
@@ -13866,7 +13866,7 @@
         <v>456</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P214" s="6" t="s">
         <v>26</v>
@@ -13889,7 +13889,7 @@
         <v>46162.675576967595</v>
       </c>
       <c r="E215" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F215" s="10" t="s">
         <v>26</v>
@@ -13917,10 +13917,10 @@
         <v>456</v>
       </c>
       <c r="O215" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P215" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q215" s="10"/>
       <c r="R215" s="10"/>
@@ -13940,7 +13940,7 @@
         <v>46162.67557431713</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
@@ -13968,7 +13968,7 @@
         <v>456</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P216" s="6" t="s">
         <v>467</v>
@@ -13991,7 +13991,7 @@
         <v>46162.67557162037</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>26</v>
@@ -14019,10 +14019,10 @@
         <v>456</v>
       </c>
       <c r="O217" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P217" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q217" s="10"/>
       <c r="R217" s="10"/>
@@ -14042,7 +14042,7 @@
         <v>46162.67556375</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
@@ -14070,10 +14070,10 @@
         <v>456</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P218" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q218" s="6"/>
       <c r="R218" s="6"/>
@@ -14093,7 +14093,7 @@
         <v>46162.675563020835</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>26</v>
@@ -14121,10 +14121,10 @@
         <v>456</v>
       </c>
       <c r="O219" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P219" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q219" s="10"/>
       <c r="R219" s="10"/>
@@ -14144,7 +14144,7 @@
         <v>46162.67556230324</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
@@ -14172,10 +14172,10 @@
         <v>456</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P220" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q220" s="6"/>
       <c r="R220" s="6"/>
@@ -14201,10 +14201,10 @@
         <v>26</v>
       </c>
       <c r="G221" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H221" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I221" s="9">
         <v>46231</v>
@@ -14225,7 +14225,7 @@
         <v>434</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P221" s="10" t="s">
         <v>434</v>
@@ -14258,16 +14258,16 @@
         <v>46162.67579450231</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H222" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I222" s="6"/>
       <c r="J222" s="5">
@@ -14286,7 +14286,7 @@
         <v>473</v>
       </c>
       <c r="O222" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P222" s="6" t="s">
         <v>475</v>
@@ -14309,16 +14309,16 @@
         <v>46162.6757915162</v>
       </c>
       <c r="E223" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G223" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H223" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I223" s="10"/>
       <c r="J223" s="9">
@@ -14337,7 +14337,7 @@
         <v>473</v>
       </c>
       <c r="O223" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P223" s="10" t="s">
         <v>475</v>
@@ -14360,16 +14360,16 @@
         <v>46162.67578863426</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H224" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I224" s="6"/>
       <c r="J224" s="5">
@@ -14388,7 +14388,7 @@
         <v>473</v>
       </c>
       <c r="O224" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P224" s="6" t="s">
         <v>478</v>
@@ -14411,16 +14411,16 @@
         <v>46162.67578590278</v>
       </c>
       <c r="E225" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F225" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G225" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H225" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I225" s="10"/>
       <c r="J225" s="9">
@@ -14439,7 +14439,7 @@
         <v>473</v>
       </c>
       <c r="O225" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P225" s="10" t="s">
         <v>478</v>
@@ -14462,16 +14462,16 @@
         <v>46162.67578289352</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F226" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H226" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I226" s="6"/>
       <c r="J226" s="5">
@@ -14490,7 +14490,7 @@
         <v>473</v>
       </c>
       <c r="O226" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P226" s="6" t="s">
         <v>481</v>
@@ -14513,16 +14513,16 @@
         <v>46162.67577962963</v>
       </c>
       <c r="E227" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F227" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G227" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H227" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I227" s="10"/>
       <c r="J227" s="9">
@@ -14541,10 +14541,10 @@
         <v>473</v>
       </c>
       <c r="O227" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P227" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q227" s="10"/>
       <c r="R227" s="10"/>
@@ -14564,16 +14564,16 @@
         <v>46162.67577695602</v>
       </c>
       <c r="E228" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F228" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G228" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H228" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I228" s="6"/>
       <c r="J228" s="5">
@@ -14592,10 +14592,10 @@
         <v>473</v>
       </c>
       <c r="O228" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P228" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q228" s="6"/>
       <c r="R228" s="6"/>
@@ -14621,10 +14621,10 @@
         <v>26</v>
       </c>
       <c r="G229" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H229" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I229" s="10"/>
       <c r="J229" s="9">
@@ -14643,10 +14643,10 @@
         <v>473</v>
       </c>
       <c r="O229" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P229" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q229" s="10"/>
       <c r="R229" s="10"/>
@@ -14666,16 +14666,16 @@
         <v>46162.67577162037</v>
       </c>
       <c r="E230" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F230" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G230" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H230" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I230" s="6"/>
       <c r="J230" s="5">
@@ -14694,10 +14694,10 @@
         <v>473</v>
       </c>
       <c r="O230" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P230" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q230" s="6"/>
       <c r="R230" s="6"/>
@@ -14717,16 +14717,16 @@
         <v>46162.67576392361</v>
       </c>
       <c r="E231" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F231" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G231" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H231" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I231" s="10"/>
       <c r="J231" s="9">
@@ -14745,10 +14745,10 @@
         <v>473</v>
       </c>
       <c r="O231" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P231" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q231" s="10"/>
       <c r="R231" s="10"/>
@@ -14768,16 +14768,16 @@
         <v>46162.67576322917</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F232" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G232" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H232" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I232" s="6"/>
       <c r="J232" s="5">
@@ -14796,10 +14796,10 @@
         <v>473</v>
       </c>
       <c r="O232" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P232" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q232" s="6"/>
       <c r="R232" s="6"/>
@@ -14819,16 +14819,16 @@
         <v>46162.67576252315</v>
       </c>
       <c r="E233" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F233" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G233" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H233" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I233" s="10"/>
       <c r="J233" s="9">
@@ -14847,10 +14847,10 @@
         <v>473</v>
       </c>
       <c r="O233" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P233" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q233" s="10"/>
       <c r="R233" s="10"/>
@@ -14876,10 +14876,10 @@
         <v>26</v>
       </c>
       <c r="G234" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H234" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I234" s="5">
         <v>46232</v>
@@ -14900,7 +14900,7 @@
         <v>434</v>
       </c>
       <c r="O234" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P234" s="6" t="s">
         <v>491</v>
@@ -14933,16 +14933,16 @@
         <v>46162.676026875</v>
       </c>
       <c r="E235" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F235" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G235" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H235" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I235" s="9">
         <v>46232</v>
@@ -14963,7 +14963,7 @@
         <v>490</v>
       </c>
       <c r="O235" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P235" s="10" t="s">
         <v>490</v>
@@ -14986,16 +14986,16 @@
         <v>46162.67602255787</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F236" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G236" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H236" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I236" s="5">
         <v>46232</v>
@@ -15016,7 +15016,7 @@
         <v>490</v>
       </c>
       <c r="O236" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P236" s="6" t="s">
         <v>490</v>
@@ -15039,16 +15039,16 @@
         <v>46162.676019108796</v>
       </c>
       <c r="E237" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F237" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G237" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H237" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I237" s="9">
         <v>46232</v>
@@ -15069,7 +15069,7 @@
         <v>490</v>
       </c>
       <c r="O237" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P237" s="10" t="s">
         <v>490</v>
@@ -15092,16 +15092,16 @@
         <v>46162.67601616898</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F238" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G238" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H238" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I238" s="5">
         <v>46232</v>
@@ -15122,7 +15122,7 @@
         <v>490</v>
       </c>
       <c r="O238" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P238" s="6" t="s">
         <v>490</v>
@@ -15145,16 +15145,16 @@
         <v>46162.676013275464</v>
       </c>
       <c r="E239" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F239" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G239" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H239" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I239" s="9">
         <v>46232</v>
@@ -15175,7 +15175,7 @@
         <v>490</v>
       </c>
       <c r="O239" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P239" s="10" t="s">
         <v>490</v>
@@ -15198,16 +15198,16 @@
         <v>46162.67600972222</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F240" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G240" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H240" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I240" s="5">
         <v>46232</v>
@@ -15228,7 +15228,7 @@
         <v>490</v>
       </c>
       <c r="O240" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P240" s="6" t="s">
         <v>26</v>
@@ -15251,16 +15251,16 @@
         <v>46162.676007002316</v>
       </c>
       <c r="E241" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F241" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G241" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H241" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I241" s="9">
         <v>46232</v>
@@ -15281,7 +15281,7 @@
         <v>490</v>
       </c>
       <c r="O241" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P241" s="10" t="s">
         <v>26</v>
@@ -15304,16 +15304,16 @@
         <v>46162.67600369213</v>
       </c>
       <c r="E242" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F242" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G242" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H242" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I242" s="5">
         <v>46232</v>
@@ -15357,16 +15357,16 @@
         <v>46162.67599591435</v>
       </c>
       <c r="E243" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F243" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G243" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H243" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I243" s="9">
         <v>46232</v>
@@ -15387,7 +15387,7 @@
         <v>490</v>
       </c>
       <c r="O243" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P243" s="10" t="s">
         <v>26</v>
@@ -15410,16 +15410,16 @@
         <v>46162.67599258102</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F244" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G244" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H244" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I244" s="5">
         <v>46232</v>
@@ -15440,7 +15440,7 @@
         <v>490</v>
       </c>
       <c r="O244" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P244" s="6" t="s">
         <v>26</v>
@@ -15463,16 +15463,16 @@
         <v>46162.675991412034</v>
       </c>
       <c r="E245" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F245" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G245" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H245" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I245" s="9">
         <v>46232</v>
@@ -15493,7 +15493,7 @@
         <v>490</v>
       </c>
       <c r="O245" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P245" s="10" t="s">
         <v>26</v>
@@ -15516,16 +15516,16 @@
         <v>46162.675990613425</v>
       </c>
       <c r="E246" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F246" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G246" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H246" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I246" s="5">
         <v>46232</v>
@@ -15546,7 +15546,7 @@
         <v>490</v>
       </c>
       <c r="O246" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P246" s="6" t="s">
         <v>26</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -11971,7 +11971,7 @@
       </c>
       <c r="C181" s="10"/>
       <c r="D181" s="9">
-        <v>46162.673987789356</v>
+        <v>46219.17072790509</v>
       </c>
       <c r="E181" s="10" t="s">
         <v>413</v>
@@ -12013,8 +12013,8 @@
       <c r="R181" s="9">
         <v>46226</v>
       </c>
-      <c r="S181" s="7" t="s">
-        <v>55</v>
+      <c r="S181" s="12" t="s">
+        <v>187</v>
       </c>
       <c r="T181" s="10">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -9327,7 +9327,7 @@
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46212.180082453706</v>
+        <v>46220.18406796297</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>327</v>
@@ -9369,8 +9369,8 @@
       <c r="R129" s="9">
         <v>46219</v>
       </c>
-      <c r="S129" s="12" t="s">
-        <v>187</v>
+      <c r="S129" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T129" s="10">
         <v>0</v>
@@ -12667,7 +12667,7 @@
       </c>
       <c r="C195" s="10"/>
       <c r="D195" s="9">
-        <v>46162.67540229167</v>
+        <v>46220.19238578704</v>
       </c>
       <c r="E195" s="10" t="s">
         <v>434</v>
@@ -12711,8 +12711,8 @@
       <c r="R195" s="9">
         <v>46227</v>
       </c>
-      <c r="S195" s="7" t="s">
-        <v>55</v>
+      <c r="S195" s="12" t="s">
+        <v>187</v>
       </c>
       <c r="T195" s="10">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -9976,7 +9976,7 @@
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46213.173677557876</v>
+        <v>46221.20048677083</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>351</v>
@@ -10018,8 +10018,8 @@
       <c r="R142" s="5">
         <v>46220</v>
       </c>
-      <c r="S142" s="12" t="s">
-        <v>187</v>
+      <c r="S142" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T142" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -528,6 +528,9 @@
     <t>Generacion OC Fabricación Externa OT 4324 4325,Fabricación estructura proveedor externo OT 4324 4325</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1214969287605824</t>
   </si>
   <si>
@@ -640,9 +643,6 @@
   </si>
   <si>
     <t xml:space="preserve">OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214969335458375</t>
@@ -4404,7 +4404,7 @@
         <v>46209.612930856485</v>
       </c>
       <c r="D39" s="9">
-        <v>46216.544503425925</v>
+        <v>46224.198430289354</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>146</v>
@@ -4448,8 +4448,8 @@
       <c r="R39" s="9">
         <v>46231</v>
       </c>
-      <c r="S39" s="7" t="s">
-        <v>55</v>
+      <c r="S39" s="12" t="s">
+        <v>150</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>
@@ -4460,7 +4460,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46162.558437569445</v>
@@ -4505,7 +4505,7 @@
         <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4515,7 +4515,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B41" s="9">
         <v>46162.55844153935</v>
@@ -4527,7 +4527,7 @@
         <v>46209.612886620365</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
@@ -4560,7 +4560,7 @@
         <v>89</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4570,7 +4570,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46162.55844576389</v>
@@ -4582,16 +4582,16 @@
         <v>46216.54443384259</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46230</v>
@@ -4612,7 +4612,7 @@
         <v>146</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4625,7 +4625,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B43" s="9">
         <v>46162.55844833334</v>
@@ -4637,7 +4637,7 @@
         <v>46209.81470094908</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
@@ -4667,7 +4667,7 @@
         <v>91</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4690,7 +4690,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46162.55845114583</v>
@@ -4729,13 +4729,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4745,7 +4745,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B45" s="9">
         <v>46162.55845520833</v>
@@ -4757,7 +4757,7 @@
         <v>46209.81467782408</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -4784,13 +4784,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>86</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4800,7 +4800,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46162.55817767361</v>
@@ -4812,7 +4812,7 @@
         <v>46210.528923819445</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4836,7 +4836,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4853,7 +4853,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B47" s="9">
         <v>46162.55845957176</v>
@@ -4865,16 +4865,16 @@
         <v>46197.67690475694</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I47" s="9">
         <v>46160</v>
@@ -4892,13 +4892,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>61</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="9">
         <v>46160</v>
@@ -4918,7 +4918,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46162.55846439815</v>
@@ -4930,16 +4930,16 @@
         <v>46198.79333422454</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I48" s="5">
         <v>46176</v>
@@ -4957,13 +4957,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="5">
         <v>46176</v>
@@ -4983,7 +4983,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B49" s="9">
         <v>46162.55847024306</v>
@@ -5001,10 +5001,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -5020,13 +5020,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="9">
         <v>46185</v>
@@ -5046,7 +5046,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46162.55848571759</v>
@@ -5056,16 +5056,16 @@
         <v>46218.17936890046</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I50" s="5">
         <v>46225</v>
@@ -5083,10 +5083,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -5098,7 +5098,7 @@
         <v>46225</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -5125,10 +5125,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -5144,7 +5144,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O51" s="10" t="s">
         <v>190</v>
@@ -5176,10 +5176,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -5195,7 +5195,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>190</v>
@@ -5227,10 +5227,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
@@ -5246,7 +5246,7 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>190</v>
@@ -5278,10 +5278,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -5297,7 +5297,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>190</v>
@@ -5329,10 +5329,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -5348,7 +5348,7 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>196</v>
@@ -5380,10 +5380,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -5399,7 +5399,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>196</v>
@@ -5431,10 +5431,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="9">
@@ -5450,7 +5450,7 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>196</v>
@@ -5482,10 +5482,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -5501,7 +5501,7 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>196</v>
@@ -5533,10 +5533,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="9">
@@ -5552,7 +5552,7 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O59" s="10" t="s">
         <v>196</v>
@@ -5584,10 +5584,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5603,7 +5603,7 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>196</v>
@@ -5635,10 +5635,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="9">
@@ -5654,7 +5654,7 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O61" s="10" t="s">
         <v>196</v>
@@ -5686,10 +5686,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I62" s="6"/>
       <c r="J62" s="5">
@@ -5705,7 +5705,7 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>196</v>
@@ -5857,10 +5857,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I65" s="9">
         <v>46204</v>
@@ -5987,10 +5987,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I67" s="9">
         <v>46204</v>
@@ -6076,7 +6076,7 @@
         <v>205</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>223</v>
@@ -6117,10 +6117,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I69" s="9">
         <v>46204</v>
@@ -7625,10 +7625,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I97" s="9">
         <v>46217</v>
@@ -7688,10 +7688,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I98" s="5">
         <v>46217</v>
@@ -7741,10 +7741,10 @@
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I99" s="9">
         <v>46217</v>
@@ -7794,10 +7794,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I100" s="5">
         <v>46217</v>
@@ -7847,10 +7847,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I101" s="9">
         <v>46217</v>
@@ -7900,10 +7900,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I102" s="5">
         <v>46217</v>
@@ -7953,10 +7953,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I103" s="9">
         <v>46217</v>
@@ -8006,10 +8006,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I104" s="5">
         <v>46217</v>
@@ -8059,10 +8059,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I105" s="9">
         <v>46217</v>
@@ -8112,10 +8112,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I106" s="5">
         <v>46217</v>
@@ -8165,10 +8165,10 @@
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I107" s="9">
         <v>46217</v>
@@ -8218,10 +8218,10 @@
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I108" s="5">
         <v>46217</v>
@@ -8271,10 +8271,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I109" s="9">
         <v>46217</v>
@@ -8590,7 +8590,7 @@
         <v>205</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>306</v>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46223.57990936343</v>
+        <v>46224.25044768519</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>311</v>
@@ -8712,7 +8712,7 @@
         <v>46224</v>
       </c>
       <c r="S116" s="12" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="T116" s="6">
         <v>0</v>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46223.57886836806</v>
+        <v>46224.25040153935</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>190</v>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46223.5788674537</v>
+        <v>46224.25040292824</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>190</v>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46223.57886079861</v>
+        <v>46224.25044962963</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>190</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46223.57886005787</v>
+        <v>46224.25045101852</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>190</v>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46223.57885931713</v>
+        <v>46224.25040421296</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>196</v>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46223.57885866898</v>
+        <v>46224.25042715278</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>196</v>
@@ -9048,7 +9048,7 @@
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46223.57885796296</v>
+        <v>46224.2504290625</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>196</v>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46223.57885731482</v>
+        <v>46224.250430555556</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>196</v>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46223.57885670139</v>
+        <v>46224.25043193287</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>196</v>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46223.578856064814</v>
+        <v>46224.250433402776</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>196</v>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46223.578855416665</v>
+        <v>46224.25043480324</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>196</v>
@@ -9313,7 +9313,7 @@
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46223.57885478009</v>
+        <v>46224.25043630787</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>196</v>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="C155" s="10"/>
       <c r="D155" s="9">
-        <v>46223.579907418985</v>
+        <v>46224.18423814815</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>372</v>
@@ -10784,8 +10784,8 @@
       <c r="R155" s="9">
         <v>46223</v>
       </c>
-      <c r="S155" s="12" t="s">
-        <v>188</v>
+      <c r="S155" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T155" s="10">
         <v>0</v>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46223.57990668982</v>
+        <v>46224.25045393519</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>397</v>
@@ -11484,7 +11484,7 @@
         <v>46224</v>
       </c>
       <c r="S168" s="12" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="T168" s="6">
         <v>0</v>
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C169" s="10"/>
       <c r="D169" s="9">
-        <v>46223.5796616088</v>
+        <v>46224.25045532407</v>
       </c>
       <c r="E169" s="10" t="s">
         <v>190</v>
@@ -11553,7 +11553,7 @@
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46223.57966096065</v>
+        <v>46224.25039887731</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>190</v>
@@ -11604,7 +11604,7 @@
       </c>
       <c r="C171" s="10"/>
       <c r="D171" s="9">
-        <v>46223.57966033564</v>
+        <v>46224.250400185185</v>
       </c>
       <c r="E171" s="10" t="s">
         <v>190</v>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46223.579659675925</v>
+        <v>46224.25039688658</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>190</v>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="C173" s="10"/>
       <c r="D173" s="9">
-        <v>46223.57965892361</v>
+        <v>46224.25045253472</v>
       </c>
       <c r="E173" s="10" t="s">
         <v>196</v>
@@ -11757,7 +11757,7 @@
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46223.57965828704</v>
+        <v>46224.25043752315</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>196</v>
@@ -11808,7 +11808,7 @@
       </c>
       <c r="C175" s="10"/>
       <c r="D175" s="9">
-        <v>46223.579657615745</v>
+        <v>46224.25043901621</v>
       </c>
       <c r="E175" s="10" t="s">
         <v>196</v>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46223.57965688658</v>
+        <v>46224.25044046296</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>196</v>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="C177" s="10"/>
       <c r="D177" s="9">
-        <v>46223.57965625</v>
+        <v>46224.2504419676</v>
       </c>
       <c r="E177" s="10" t="s">
         <v>196</v>
@@ -11961,7 +11961,7 @@
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46223.57965560185</v>
+        <v>46224.25044340278</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>196</v>
@@ -12012,7 +12012,7 @@
       </c>
       <c r="C179" s="10"/>
       <c r="D179" s="9">
-        <v>46223.579655</v>
+        <v>46224.25044509259</v>
       </c>
       <c r="E179" s="10" t="s">
         <v>196</v>
@@ -12063,7 +12063,7 @@
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46223.57965436342</v>
+        <v>46224.25044643518</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>196</v>
@@ -12159,7 +12159,7 @@
         <v>46226</v>
       </c>
       <c r="S181" s="12" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="T181" s="10">
         <v>0</v>
@@ -12881,7 +12881,7 @@
         <v>46227</v>
       </c>
       <c r="S195" s="12" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="T195" s="10">
         <v>0</v>
@@ -13556,7 +13556,7 @@
         <v>46230</v>
       </c>
       <c r="S208" s="12" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="T208" s="6">
         <v>0</v>
@@ -14186,7 +14186,7 @@
       </c>
       <c r="C221" s="10"/>
       <c r="D221" s="9">
-        <v>46162.67579302083</v>
+        <v>46224.198430335644</v>
       </c>
       <c r="E221" s="10" t="s">
         <v>471</v>
@@ -14230,8 +14230,8 @@
       <c r="R221" s="9">
         <v>46231</v>
       </c>
-      <c r="S221" s="7" t="s">
-        <v>55</v>
+      <c r="S221" s="12" t="s">
+        <v>150</v>
       </c>
       <c r="T221" s="10">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46217.16846439815</v>
+        <v>46224.87647666667</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>196</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -5053,7 +5053,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46218.17936890046</v>
+        <v>46225.16841621528</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46191.68638508102</v>
+        <v>46225.16841835648</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>190</v>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46191.68638201389</v>
+        <v>46225.16841996528</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>190</v>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46191.68637913195</v>
+        <v>46225.168421215276</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>190</v>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46191.68637614584</v>
+        <v>46225.16838393519</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46191.6863727662</v>
+        <v>46225.16838541666</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>196</v>
@@ -5371,7 +5371,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46191.686369641204</v>
+        <v>46225.16840149305</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>196</v>
@@ -5422,7 +5422,7 @@
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46191.68636637731</v>
+        <v>46225.16840322917</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>196</v>
@@ -5473,7 +5473,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46191.686363761575</v>
+        <v>46225.16840447916</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>196</v>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46191.6863608912</v>
+        <v>46225.16840631944</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>196</v>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46191.68635278935</v>
+        <v>46225.1684090625</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>196</v>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46191.68635209491</v>
+        <v>46225.168411701394</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>196</v>
@@ -5677,7 +5677,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46191.686351412034</v>
+        <v>46225.16841293982</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>196</v>
@@ -8557,7 +8557,7 @@
         <v>46216.54425189814</v>
       </c>
       <c r="D114" s="5">
-        <v>46216.544359340274</v>
+        <v>46225.18669188657</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>305</v>
@@ -8601,8 +8601,8 @@
       <c r="R114" s="5">
         <v>46232</v>
       </c>
-      <c r="S114" s="7" t="s">
-        <v>55</v>
+      <c r="S114" s="12" t="s">
+        <v>150</v>
       </c>
       <c r="T114" s="6">
         <v>1</v>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46224.25044768519</v>
+        <v>46225.185239872684</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>311</v>
@@ -8711,8 +8711,8 @@
       <c r="R116" s="5">
         <v>46224</v>
       </c>
-      <c r="S116" s="12" t="s">
-        <v>150</v>
+      <c r="S116" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T116" s="6">
         <v>0</v>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46224.25045393519</v>
+        <v>46225.18524023148</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>397</v>
@@ -11483,8 +11483,8 @@
       <c r="R168" s="5">
         <v>46224</v>
       </c>
-      <c r="S168" s="12" t="s">
-        <v>150</v>
+      <c r="S168" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T168" s="6">
         <v>0</v>
@@ -14861,7 +14861,7 @@
       </c>
       <c r="C234" s="6"/>
       <c r="D234" s="5">
-        <v>46162.6758584375</v>
+        <v>46225.186692812495</v>
       </c>
       <c r="E234" s="6" t="s">
         <v>488</v>
@@ -14905,8 +14905,8 @@
       <c r="R234" s="5">
         <v>46232</v>
       </c>
-      <c r="S234" s="7" t="s">
-        <v>55</v>
+      <c r="S234" s="12" t="s">
+        <v>150</v>
       </c>
       <c r="T234" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -5056,7 +5056,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46225.16841621528</v>
+        <v>46226.20215001157</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -5100,8 +5100,8 @@
       <c r="R50" s="5">
         <v>46225</v>
       </c>
-      <c r="S50" s="12" t="s">
-        <v>151</v>
+      <c r="S50" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="C181" s="10"/>
       <c r="D181" s="9">
-        <v>46223.57990600694</v>
+        <v>46226.16815395834</v>
       </c>
       <c r="E181" s="10" t="s">
         <v>415</v>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46223.57981173611</v>
+        <v>46226.16815751157</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>191</v>
@@ -12265,7 +12265,7 @@
       </c>
       <c r="C183" s="10"/>
       <c r="D183" s="9">
-        <v>46223.57981109954</v>
+        <v>46226.16815899305</v>
       </c>
       <c r="E183" s="10" t="s">
         <v>191</v>
@@ -12316,7 +12316,7 @@
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46223.57981048611</v>
+        <v>46226.16815614583</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>191</v>
@@ -12367,7 +12367,7 @@
       </c>
       <c r="C185" s="10"/>
       <c r="D185" s="9">
-        <v>46223.57980986111</v>
+        <v>46226.16816035879</v>
       </c>
       <c r="E185" s="10" t="s">
         <v>191</v>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46223.57980917824</v>
+        <v>46226.16816185185</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>197</v>
@@ -12469,7 +12469,7 @@
       </c>
       <c r="C187" s="10"/>
       <c r="D187" s="9">
-        <v>46223.579808553244</v>
+        <v>46226.16814340278</v>
       </c>
       <c r="E187" s="10" t="s">
         <v>197</v>
@@ -12520,7 +12520,7 @@
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46223.57980792824</v>
+        <v>46226.16814550926</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>197</v>
@@ -12571,7 +12571,7 @@
       </c>
       <c r="C189" s="10"/>
       <c r="D189" s="9">
-        <v>46223.579807118054</v>
+        <v>46226.168146909724</v>
       </c>
       <c r="E189" s="10" t="s">
         <v>197</v>
@@ -12622,7 +12622,7 @@
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46223.57980648148</v>
+        <v>46226.168148275465</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>197</v>
@@ -12673,7 +12673,7 @@
       </c>
       <c r="C191" s="10"/>
       <c r="D191" s="9">
-        <v>46223.57980582176</v>
+        <v>46226.16814969908</v>
       </c>
       <c r="E191" s="10" t="s">
         <v>197</v>
@@ -12724,7 +12724,7 @@
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46223.57980519676</v>
+        <v>46226.16815109954</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>197</v>
@@ -12775,7 +12775,7 @@
       </c>
       <c r="C193" s="10"/>
       <c r="D193" s="9">
-        <v>46223.579804560184</v>
+        <v>46226.16815254629</v>
       </c>
       <c r="E193" s="10" t="s">
         <v>197</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -12151,7 +12151,7 @@
       </c>
       <c r="C181" s="10"/>
       <c r="D181" s="9">
-        <v>46226.16815395834</v>
+        <v>46227.200147048614</v>
       </c>
       <c r="E181" s="10" t="s">
         <v>415</v>
@@ -12195,8 +12195,8 @@
       <c r="R181" s="9">
         <v>46226</v>
       </c>
-      <c r="S181" s="12" t="s">
-        <v>151</v>
+      <c r="S181" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T181" s="10">
         <v>0</v>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="C195" s="10"/>
       <c r="D195" s="9">
-        <v>46220.19238578704</v>
+        <v>46228.19288883102</v>
       </c>
       <c r="E195" s="10" t="s">
         <v>436</v>
@@ -12917,8 +12917,8 @@
       <c r="R195" s="9">
         <v>46227</v>
       </c>
-      <c r="S195" s="12" t="s">
-        <v>151</v>
+      <c r="S195" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T195" s="10">
         <v>0</v>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46162.67538505787</v>
+        <v>46227.16884697917</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>191</v>
@@ -12987,7 +12987,7 @@
       </c>
       <c r="C197" s="10"/>
       <c r="D197" s="9">
-        <v>46162.675382534726</v>
+        <v>46227.16885321759</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>191</v>
@@ -13038,7 +13038,7 @@
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46162.67537990741</v>
+        <v>46227.16885833333</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>191</v>
@@ -13089,7 +13089,7 @@
       </c>
       <c r="C199" s="10"/>
       <c r="D199" s="9">
-        <v>46162.67537715277</v>
+        <v>46227.16885959491</v>
       </c>
       <c r="E199" s="10" t="s">
         <v>191</v>
@@ -13140,7 +13140,7 @@
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46162.675374178245</v>
+        <v>46227.168854675925</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>197</v>
@@ -13191,7 +13191,7 @@
       </c>
       <c r="C201" s="10"/>
       <c r="D201" s="9">
-        <v>46162.675371296296</v>
+        <v>46227.168836944446</v>
       </c>
       <c r="E201" s="10" t="s">
         <v>197</v>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46162.675368321754</v>
+        <v>46227.16883850694</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>197</v>
@@ -13293,7 +13293,7 @@
       </c>
       <c r="C203" s="10"/>
       <c r="D203" s="9">
-        <v>46162.67536565972</v>
+        <v>46227.168839861115</v>
       </c>
       <c r="E203" s="10" t="s">
         <v>197</v>
@@ -13344,7 +13344,7 @@
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46162.67536296297</v>
+        <v>46227.168841273146</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>197</v>
@@ -13395,7 +13395,7 @@
       </c>
       <c r="C205" s="10"/>
       <c r="D205" s="9">
-        <v>46162.67535506944</v>
+        <v>46227.16884255787</v>
       </c>
       <c r="E205" s="10" t="s">
         <v>197</v>
@@ -13446,7 +13446,7 @@
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46162.67535439815</v>
+        <v>46227.168843796295</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>197</v>
@@ -13497,7 +13497,7 @@
       </c>
       <c r="C207" s="10"/>
       <c r="D207" s="9">
-        <v>46162.67535373842</v>
+        <v>46227.16884491898</v>
       </c>
       <c r="E207" s="10" t="s">
         <v>197</v>
@@ -13548,7 +13548,7 @@
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46223.58015545139</v>
+        <v>46230.16873222222</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>455</v>
@@ -13611,7 +13611,7 @@
       </c>
       <c r="C209" s="10"/>
       <c r="D209" s="9">
-        <v>46223.580075879625</v>
+        <v>46230.16873420139</v>
       </c>
       <c r="E209" s="10" t="s">
         <v>191</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46223.58007527778</v>
+        <v>46230.16873547454</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>191</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C211" s="10"/>
       <c r="D211" s="9">
-        <v>46223.58007462963</v>
+        <v>46230.16873686343</v>
       </c>
       <c r="E211" s="10" t="s">
         <v>191</v>
@@ -13764,7 +13764,7 @@
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46223.5800740625</v>
+        <v>46230.16873802083</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>191</v>
@@ -13815,7 +13815,7 @@
       </c>
       <c r="C213" s="10"/>
       <c r="D213" s="9">
-        <v>46223.58007347222</v>
+        <v>46230.168739155095</v>
       </c>
       <c r="E213" s="10" t="s">
         <v>197</v>
@@ -13866,7 +13866,7 @@
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46223.580072881945</v>
+        <v>46230.16872133102</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>197</v>
@@ -13917,7 +13917,7 @@
       </c>
       <c r="C215" s="10"/>
       <c r="D215" s="9">
-        <v>46223.58007225694</v>
+        <v>46230.16872302083</v>
       </c>
       <c r="E215" s="10" t="s">
         <v>197</v>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46223.58007167824</v>
+        <v>46230.168724675925</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>197</v>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="C217" s="10"/>
       <c r="D217" s="9">
-        <v>46223.58007108796</v>
+        <v>46230.16872583333</v>
       </c>
       <c r="E217" s="10" t="s">
         <v>197</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46223.58007049769</v>
+        <v>46230.168726979166</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>197</v>
@@ -14121,7 +14121,7 @@
       </c>
       <c r="C219" s="10"/>
       <c r="D219" s="9">
-        <v>46223.580069895834</v>
+        <v>46230.168728055556</v>
       </c>
       <c r="E219" s="10" t="s">
         <v>197</v>
@@ -14172,7 +14172,7 @@
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46223.58006928241</v>
+        <v>46230.16872912037</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>197</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -13548,7 +13548,7 @@
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46230.16873222222</v>
+        <v>46231.180388402776</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>455</v>
@@ -13592,8 +13592,8 @@
       <c r="R208" s="5">
         <v>46230</v>
       </c>
-      <c r="S208" s="12" t="s">
-        <v>151</v>
+      <c r="S208" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T208" s="6">
         <v>0</v>
@@ -14223,7 +14223,7 @@
       </c>
       <c r="C221" s="10"/>
       <c r="D221" s="9">
-        <v>46224.198430335644</v>
+        <v>46231.168253888885</v>
       </c>
       <c r="E221" s="10" t="s">
         <v>472</v>
@@ -14286,7 +14286,7 @@
       </c>
       <c r="C222" s="6"/>
       <c r="D222" s="5">
-        <v>46162.67579450231</v>
+        <v>46231.168255868055</v>
       </c>
       <c r="E222" s="6" t="s">
         <v>191</v>
@@ -14337,7 +14337,7 @@
       </c>
       <c r="C223" s="10"/>
       <c r="D223" s="9">
-        <v>46162.6757915162</v>
+        <v>46231.16824994213</v>
       </c>
       <c r="E223" s="10" t="s">
         <v>191</v>
@@ -14388,7 +14388,7 @@
       </c>
       <c r="C224" s="6"/>
       <c r="D224" s="5">
-        <v>46162.67578863426</v>
+        <v>46231.168251111114</v>
       </c>
       <c r="E224" s="6" t="s">
         <v>191</v>
@@ -14439,7 +14439,7 @@
       </c>
       <c r="C225" s="10"/>
       <c r="D225" s="9">
-        <v>46162.67578590278</v>
+        <v>46231.168252511576</v>
       </c>
       <c r="E225" s="10" t="s">
         <v>191</v>
@@ -14490,7 +14490,7 @@
       </c>
       <c r="C226" s="6"/>
       <c r="D226" s="5">
-        <v>46162.67578289352</v>
+        <v>46231.16825728009</v>
       </c>
       <c r="E226" s="6" t="s">
         <v>197</v>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="C227" s="10"/>
       <c r="D227" s="9">
-        <v>46162.67577962963</v>
+        <v>46231.16824121527</v>
       </c>
       <c r="E227" s="10" t="s">
         <v>197</v>
@@ -14592,7 +14592,7 @@
       </c>
       <c r="C228" s="6"/>
       <c r="D228" s="5">
-        <v>46162.67577695602</v>
+        <v>46231.16824241898</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>197</v>
@@ -14643,7 +14643,7 @@
       </c>
       <c r="C229" s="10"/>
       <c r="D229" s="9">
-        <v>46162.67577410879</v>
+        <v>46231.16824366898</v>
       </c>
       <c r="E229" s="10" t="s">
         <v>466</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C230" s="6"/>
       <c r="D230" s="5">
-        <v>46162.67577162037</v>
+        <v>46231.168244733795</v>
       </c>
       <c r="E230" s="6" t="s">
         <v>197</v>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="C231" s="10"/>
       <c r="D231" s="9">
-        <v>46162.67576392361</v>
+        <v>46231.16824633101</v>
       </c>
       <c r="E231" s="10" t="s">
         <v>197</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="C232" s="6"/>
       <c r="D232" s="5">
-        <v>46162.67576322917</v>
+        <v>46231.16824753472</v>
       </c>
       <c r="E232" s="6" t="s">
         <v>197</v>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="C233" s="10"/>
       <c r="D233" s="9">
-        <v>46162.67576252315</v>
+        <v>46231.16824866898</v>
       </c>
       <c r="E233" s="10" t="s">
         <v>197</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -531,475 +531,475 @@
     <t>Generacion OC Fabricación Externa OT 4324 4325,Fabricación estructura proveedor externo OT 4324 4325</t>
   </si>
   <si>
+    <t>1214969287605824</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4324 4325,Fabricación estructura proveedor externo OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969287605839</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Recepcion fabricación externa ,Fabricación Externa  OT 4324 4325,Control de calidad fabricación externa  OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969466515947</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1214969466515957</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4324 4325,Fabricación Mecanizado OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969466515967</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4324 4325,Fabricación Mecanizado OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969335445666</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado,Mecanizado OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969284200803</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214969335445681</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214969466529004</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos motor proveedor OT 4324 4325</t>
+  </si>
+  <si>
+    <t>check planos,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>1214969379162030</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,Propuesta Mecanizado OT 4324 4325,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,Propuesta Fabricación externa  OT 4324 4325,propuesta Corte Laser OT 4324 4325,Propuesta Corte plasma  OT 4324 4325,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
+    <t>1214969335458365</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
+    <t>1214969335458375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">check pruebas FAT,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
+    <t>1214969335458385</t>
+  </si>
+  <si>
+    <t>1214969379177095</t>
+  </si>
+  <si>
+    <t>1214969379177100</t>
+  </si>
+  <si>
+    <t>1214969379177105</t>
+  </si>
+  <si>
+    <t>OT 4325- ZVN 1-7-63/2</t>
+  </si>
+  <si>
+    <t>1214969047720357</t>
+  </si>
+  <si>
+    <t>1214969047720358</t>
+  </si>
+  <si>
+    <t>1214969047720359</t>
+  </si>
+  <si>
+    <t>1214969047720360</t>
+  </si>
+  <si>
+    <t>1214969047720361</t>
+  </si>
+  <si>
+    <t>1214969047720362</t>
+  </si>
+  <si>
+    <t>1214969047720363</t>
+  </si>
+  <si>
+    <t>1214969379177110</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214969287656726</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214969287656746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Recepcion materiales corte laser,Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,Bodega:,OT 4324- ZVN 1-7-37/2 ,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
+    <t>1214969287656971</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1214969287656991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
+    <t>1214969287665511</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1214969287665526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
+    <t>1214969504173515</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,Armado,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1214969504173525</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
+    <t>1214969379214241</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparación Materiales,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
+    <t>1214969379214266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>OT 4324- ZVN 1-7-37/2 ,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1214969466635588</t>
+  </si>
+  <si>
+    <t>1214969287690629</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado,Control de calidad corte laser ,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1214969335506636</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,OT 4325- ZVN 1-7-63/2</t>
+  </si>
+  <si>
+    <t>1214969047720336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Mecanizado,Control de calidad Corte plasma,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214969047720337</t>
+  </si>
+  <si>
+    <t>1214969047720338</t>
+  </si>
+  <si>
+    <t>1214969047720339</t>
+  </si>
+  <si>
+    <t>1214969047720340</t>
+  </si>
+  <si>
+    <t>1214969047720341</t>
+  </si>
+  <si>
+    <t>1214969047720342</t>
+  </si>
+  <si>
+    <t>1214969466610535</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
+    <t>1214969466610550</t>
+  </si>
+  <si>
+    <t>OT 4324- ZVN 1-7-37/2 ,check planos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armado,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
+    <t>1214969379260053</t>
+  </si>
+  <si>
+    <t>1214969379260073</t>
+  </si>
+  <si>
+    <t>OT 4324- ZVN 1-7-37/2 ,Armado</t>
+  </si>
+  <si>
+    <t>1214969379268441</t>
+  </si>
+  <si>
+    <t>1214969335531196</t>
+  </si>
+  <si>
+    <t>Armado,OT 4325- ZVN 1-7-63/2</t>
+  </si>
+  <si>
+    <t>1214969047720343</t>
+  </si>
+  <si>
+    <t>1214969047720344</t>
+  </si>
+  <si>
+    <t>1214969047720345</t>
+  </si>
+  <si>
+    <t>1214969047720346</t>
+  </si>
+  <si>
+    <t>1214969047720347</t>
+  </si>
+  <si>
+    <t>1214969047720348</t>
+  </si>
+  <si>
+    <t>1214969047720349</t>
+  </si>
+  <si>
+    <t>1214969335531211</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4325- ZVN 1-7-63/2</t>
+  </si>
+  <si>
+    <t>1214969379273832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revestimiento,Control de calidad Armado,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
+    <t>1214969379273852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Armado,Revestimiento,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
+    <t>1214969287798323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Armado,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
+    <t>1214969287798343</t>
+  </si>
+  <si>
+    <t>OT 4324- ZVN 1-7-37/2 ,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214969504264934</t>
+  </si>
+  <si>
+    <t>Revestimiento,Control de calidad Armado,OT 4325- ZVN 1-7-63/2</t>
+  </si>
+  <si>
+    <t>1214969047720350</t>
+  </si>
+  <si>
+    <t>1214969047720351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT7 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214969047720352</t>
+  </si>
+  <si>
+    <t>1214969047720353</t>
+  </si>
+  <si>
+    <t>1214969047720354</t>
+  </si>
+  <si>
+    <t>1214969047720355</t>
+  </si>
+  <si>
+    <t>1214969047720356</t>
+  </si>
+  <si>
+    <t>1214969287809049</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete,Recepcion Alabe,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1214969287809059</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT  4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,Bodega:,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
+    <t>1214969287819630</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,Bodega:,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
+    <t>1214969287819650</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,Bodega:,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
+    <t>1214969379310795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revestimiento,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214969287605824</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4324 4325,Fabricación estructura proveedor externo OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969287605839</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Recepcion fabricación externa ,Fabricación Externa  OT 4324 4325,Control de calidad fabricación externa  OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969466515947</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1214969466515957</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4324 4325,Fabricación Mecanizado OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969466515967</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4324 4325,Fabricación Mecanizado OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969335445666</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado,Mecanizado OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969284200803</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214969335445681</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214969466529004</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos motor proveedor OT 4324 4325</t>
-  </si>
-  <si>
-    <t>check planos,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>1214969379162030</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,Propuesta Mecanizado OT 4324 4325,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,Propuesta Fabricación externa  OT 4324 4325,propuesta Corte Laser OT 4324 4325,Propuesta Corte plasma  OT 4324 4325,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t>1214969335458365</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t>1214969335458375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">check pruebas FAT,OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t>1214969335458385</t>
-  </si>
-  <si>
-    <t>1214969379177095</t>
-  </si>
-  <si>
-    <t>1214969379177100</t>
-  </si>
-  <si>
-    <t>1214969379177105</t>
-  </si>
-  <si>
-    <t>OT 4325- ZVN 1-7-63/2</t>
-  </si>
-  <si>
-    <t>1214969047720357</t>
-  </si>
-  <si>
-    <t>1214969047720358</t>
-  </si>
-  <si>
-    <t>1214969047720359</t>
-  </si>
-  <si>
-    <t>1214969047720360</t>
-  </si>
-  <si>
-    <t>1214969047720361</t>
-  </si>
-  <si>
-    <t>1214969047720362</t>
-  </si>
-  <si>
-    <t>1214969047720363</t>
-  </si>
-  <si>
-    <t>1214969379177110</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214969287656726</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214969287656746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Recepcion materiales corte laser,Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,Bodega:,OT 4324- ZVN 1-7-37/2 ,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t>1214969287656971</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1214969287656991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t>1214969287665511</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1214969287665526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t>1214969504173515</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,Armado,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1214969504173525</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t>1214969379214241</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preparación Materiales,OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t>1214969379214266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>OT 4324- ZVN 1-7-37/2 ,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1214969466635588</t>
-  </si>
-  <si>
-    <t>1214969287690629</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado,Control de calidad corte laser ,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1214969335506636</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,OT 4325- ZVN 1-7-63/2</t>
-  </si>
-  <si>
-    <t>1214969047720336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Mecanizado,Control de calidad Corte plasma,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214969047720337</t>
-  </si>
-  <si>
-    <t>1214969047720338</t>
-  </si>
-  <si>
-    <t>1214969047720339</t>
-  </si>
-  <si>
-    <t>1214969047720340</t>
-  </si>
-  <si>
-    <t>1214969047720341</t>
-  </si>
-  <si>
-    <t>1214969047720342</t>
-  </si>
-  <si>
-    <t>1214969466610535</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t>1214969466610550</t>
-  </si>
-  <si>
-    <t>OT 4324- ZVN 1-7-37/2 ,check planos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armado,OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t>1214969379260053</t>
-  </si>
-  <si>
-    <t>1214969379260073</t>
-  </si>
-  <si>
-    <t>OT 4324- ZVN 1-7-37/2 ,Armado</t>
-  </si>
-  <si>
-    <t>1214969379268441</t>
-  </si>
-  <si>
-    <t>1214969335531196</t>
-  </si>
-  <si>
-    <t>Armado,OT 4325- ZVN 1-7-63/2</t>
-  </si>
-  <si>
-    <t>1214969047720343</t>
-  </si>
-  <si>
-    <t>1214969047720344</t>
-  </si>
-  <si>
-    <t>1214969047720345</t>
-  </si>
-  <si>
-    <t>1214969047720346</t>
-  </si>
-  <si>
-    <t>1214969047720347</t>
-  </si>
-  <si>
-    <t>1214969047720348</t>
-  </si>
-  <si>
-    <t>1214969047720349</t>
-  </si>
-  <si>
-    <t>1214969335531211</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4325- ZVN 1-7-63/2</t>
-  </si>
-  <si>
-    <t>1214969379273832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revestimiento,Control de calidad Armado,OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t>1214969379273852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Armado,Revestimiento,OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t>1214969287798323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Armado,OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t>1214969287798343</t>
-  </si>
-  <si>
-    <t>OT 4324- ZVN 1-7-37/2 ,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214969504264934</t>
-  </si>
-  <si>
-    <t>Revestimiento,Control de calidad Armado,OT 4325- ZVN 1-7-63/2</t>
-  </si>
-  <si>
-    <t>1214969047720350</t>
-  </si>
-  <si>
-    <t>1214969047720351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT7 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214969047720352</t>
-  </si>
-  <si>
-    <t>1214969047720353</t>
-  </si>
-  <si>
-    <t>1214969047720354</t>
-  </si>
-  <si>
-    <t>1214969047720355</t>
-  </si>
-  <si>
-    <t>1214969047720356</t>
-  </si>
-  <si>
-    <t>1214969287809049</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete,Recepcion Alabe,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1214969287809059</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT  4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,Bodega:,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t>1214969287819630</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,Bodega:,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t>1214969287819650</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,Bodega:,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t>1214969379310795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revestimiento,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
   </si>
   <si>
     <t>1214969379310810</t>
@@ -4407,7 +4407,7 @@
         <v>46209.612930856485</v>
       </c>
       <c r="D39" s="9">
-        <v>46224.198430289354</v>
+        <v>46232.17963666667</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>147</v>
@@ -4451,8 +4451,8 @@
       <c r="R39" s="9">
         <v>46231</v>
       </c>
-      <c r="S39" s="12" t="s">
-        <v>151</v>
+      <c r="S39" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>
@@ -4463,7 +4463,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46162.558437569445</v>
@@ -4508,7 +4508,7 @@
         <v>89</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B41" s="9">
         <v>46162.55844153935</v>
@@ -4530,7 +4530,7 @@
         <v>46209.612886620365</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
@@ -4563,7 +4563,7 @@
         <v>90</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4573,7 +4573,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46162.55844576389</v>
@@ -4585,16 +4585,16 @@
         <v>46216.54443384259</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I42" s="5">
         <v>46230</v>
@@ -4615,7 +4615,7 @@
         <v>147</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4628,7 +4628,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B43" s="9">
         <v>46162.55844833334</v>
@@ -4640,7 +4640,7 @@
         <v>46209.81470094908</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
@@ -4670,7 +4670,7 @@
         <v>92</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4693,7 +4693,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46162.55845114583</v>
@@ -4732,13 +4732,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4748,7 +4748,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B45" s="9">
         <v>46162.55845520833</v>
@@ -4760,7 +4760,7 @@
         <v>46209.81467782408</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -4787,13 +4787,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>87</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4803,7 +4803,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46162.55817767361</v>
@@ -4815,7 +4815,7 @@
         <v>46210.528923819445</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4839,7 +4839,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4856,7 +4856,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B47" s="9">
         <v>46162.55845957176</v>
@@ -4868,16 +4868,16 @@
         <v>46197.67690475694</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>174</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>175</v>
       </c>
       <c r="I47" s="9">
         <v>46160</v>
@@ -4895,13 +4895,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>61</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="9">
         <v>46160</v>
@@ -4921,7 +4921,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46162.55846439815</v>
@@ -4933,16 +4933,16 @@
         <v>46198.79333422454</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46176</v>
@@ -4960,13 +4960,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46176</v>
@@ -4986,7 +4986,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B49" s="9">
         <v>46162.55847024306</v>
@@ -5004,10 +5004,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -5023,13 +5023,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="9">
         <v>46185</v>
@@ -5049,7 +5049,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46162.55848571759</v>
@@ -5059,16 +5059,16 @@
         <v>46226.20215001157</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46225</v>
@@ -5086,10 +5086,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -5112,7 +5112,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
         <v>46162.5584890162</v>
@@ -5122,16 +5122,16 @@
         <v>46225.16841835648</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -5147,13 +5147,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O51" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="P51" s="10" t="s">
         <v>191</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>192</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46162.558492951386</v>
@@ -5173,16 +5173,16 @@
         <v>46225.16841996528</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -5198,13 +5198,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="P52" s="6" t="s">
         <v>191</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>192</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -5214,7 +5214,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B53" s="9">
         <v>46162.55849660879</v>
@@ -5224,16 +5224,16 @@
         <v>46225.168421215276</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
@@ -5249,13 +5249,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -5265,7 +5265,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B54" s="5">
         <v>46162.55849916667</v>
@@ -5275,16 +5275,16 @@
         <v>46225.16838393519</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -5300,13 +5300,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5316,7 +5316,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B55" s="9">
         <v>46162.55850175926</v>
@@ -5326,16 +5326,16 @@
         <v>46225.16838541666</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -5351,13 +5351,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5367,7 +5367,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B56" s="5">
         <v>46162.56211614583</v>
@@ -5377,16 +5377,16 @@
         <v>46225.16840149305</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -5402,10 +5402,10 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -5418,7 +5418,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B57" s="9">
         <v>46162.56212396991</v>
@@ -5428,16 +5428,16 @@
         <v>46225.16840322917</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="9">
@@ -5453,13 +5453,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5469,7 +5469,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B58" s="5">
         <v>46162.56213497685</v>
@@ -5479,16 +5479,16 @@
         <v>46225.16840447916</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -5504,13 +5504,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5520,7 +5520,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B59" s="9">
         <v>46162.562155057865</v>
@@ -5530,16 +5530,16 @@
         <v>46225.16840631944</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="9">
@@ -5555,10 +5555,10 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>26</v>
@@ -5571,7 +5571,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B60" s="5">
         <v>46162.562163055554</v>
@@ -5581,16 +5581,16 @@
         <v>46225.1684090625</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5606,10 +5606,10 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5622,7 +5622,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B61" s="9">
         <v>46162.56217104167</v>
@@ -5632,16 +5632,16 @@
         <v>46225.168411701394</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="9">
@@ -5657,10 +5657,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5673,7 +5673,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B62" s="5">
         <v>46162.562178935186</v>
@@ -5683,16 +5683,16 @@
         <v>46225.16841293982</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I62" s="6"/>
       <c r="J62" s="5">
@@ -5708,13 +5708,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5724,7 +5724,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B63" s="9">
         <v>46162.55850443287</v>
@@ -5736,7 +5736,7 @@
         <v>46216.608532638886</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>25</v>
@@ -5760,7 +5760,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>26</v>
@@ -5777,7 +5777,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B64" s="5">
         <v>46162.558507546295</v>
@@ -5789,16 +5789,16 @@
         <v>46216.60235340278</v>
       </c>
       <c r="E64" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G64" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="F64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G64" s="6" t="s">
+      <c r="H64" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I64" s="5">
         <v>46203</v>
@@ -5816,13 +5816,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>136</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q64" s="5">
         <v>46203</v>
@@ -5842,7 +5842,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B65" s="9">
         <v>46162.5585121412</v>
@@ -5854,16 +5854,16 @@
         <v>46216.603024375</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I65" s="9">
         <v>46204</v>
@@ -5881,13 +5881,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O65" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="P65" s="10" t="s">
         <v>215</v>
-      </c>
-      <c r="P65" s="10" t="s">
-        <v>216</v>
       </c>
       <c r="Q65" s="9">
         <v>46204</v>
@@ -5907,7 +5907,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B66" s="5">
         <v>46162.558518645834</v>
@@ -5919,16 +5919,16 @@
         <v>46216.60332174768</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I66" s="5">
         <v>46203</v>
@@ -5946,13 +5946,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>144</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q66" s="5">
         <v>46203</v>
@@ -5972,7 +5972,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B67" s="9">
         <v>46162.55852324074</v>
@@ -5984,16 +5984,16 @@
         <v>46216.603370682875</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I67" s="9">
         <v>46204</v>
@@ -6011,13 +6011,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q67" s="9">
         <v>46204</v>
@@ -6037,7 +6037,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B68" s="5">
         <v>46162.5585274537</v>
@@ -6049,16 +6049,16 @@
         <v>46216.60848061343</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I68" s="5">
         <v>46203</v>
@@ -6076,13 +6076,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Q68" s="5">
         <v>46203</v>
@@ -6102,7 +6102,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B69" s="9">
         <v>46162.558531400464</v>
@@ -6114,16 +6114,16 @@
         <v>46216.60852013889</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I69" s="9">
         <v>46204</v>
@@ -6141,13 +6141,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q69" s="9">
         <v>46204</v>
@@ -6167,7 +6167,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B70" s="5">
         <v>46162.55853556713</v>
@@ -6177,7 +6177,7 @@
         <v>46225.81140046296</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -6201,7 +6201,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -6214,7 +6214,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B71" s="9">
         <v>46162.558538067125</v>
@@ -6226,16 +6226,16 @@
         <v>46225.81140453704</v>
       </c>
       <c r="E71" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="F71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="F71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="10" t="s">
+      <c r="H71" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I71" s="9">
         <v>46205</v>
@@ -6253,13 +6253,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q71" s="9">
         <v>46205</v>
@@ -6279,7 +6279,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B72" s="5">
         <v>46162.558542557876</v>
@@ -6291,16 +6291,16 @@
         <v>46225.81138166667</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="I72" s="5">
         <v>46205</v>
@@ -6318,13 +6318,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O72" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="P72" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="P72" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6334,7 +6334,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B73" s="9">
         <v>46162.558548402776</v>
@@ -6346,16 +6346,16 @@
         <v>46225.81137240741</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I73" s="9">
         <v>46205</v>
@@ -6373,13 +6373,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O73" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="P73" s="10" t="s">
         <v>239</v>
-      </c>
-      <c r="P73" s="10" t="s">
-        <v>240</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -6389,7 +6389,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B74" s="5">
         <v>46162.55855412037</v>
@@ -6401,16 +6401,16 @@
         <v>46225.81136013889</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="I74" s="5">
         <v>46205</v>
@@ -6428,13 +6428,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6444,7 +6444,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B75" s="9">
         <v>46162.558560000005</v>
@@ -6456,16 +6456,16 @@
         <v>46225.81133931713</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I75" s="9">
         <v>46205</v>
@@ -6483,13 +6483,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6499,7 +6499,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B76" s="5">
         <v>46162.558565671294</v>
@@ -6511,16 +6511,16 @@
         <v>46225.811349282405</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="I76" s="5">
         <v>46205</v>
@@ -6538,13 +6538,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6554,7 +6554,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B77" s="9">
         <v>46162.56018778935</v>
@@ -6566,16 +6566,16 @@
         <v>46225.81131902778</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H77" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I77" s="9">
         <v>46205</v>
@@ -6593,13 +6593,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6609,7 +6609,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B78" s="5">
         <v>46162.560207789356</v>
@@ -6621,16 +6621,16 @@
         <v>46225.81130854167</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="I78" s="5">
         <v>46205</v>
@@ -6648,13 +6648,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6664,7 +6664,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B79" s="9">
         <v>46162.5602175463</v>
@@ -6676,16 +6676,16 @@
         <v>46225.81129936343</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I79" s="9">
         <v>46205</v>
@@ -6703,13 +6703,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6719,7 +6719,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B80" s="5">
         <v>46162.56022641204</v>
@@ -6731,16 +6731,16 @@
         <v>46225.81129182871</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="I80" s="5">
         <v>46205</v>
@@ -6758,13 +6758,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6774,7 +6774,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B81" s="9">
         <v>46162.56023459491</v>
@@ -6786,16 +6786,16 @@
         <v>46225.81128357639</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I81" s="9">
         <v>46205</v>
@@ -6813,13 +6813,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6829,7 +6829,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B82" s="5">
         <v>46162.56024284722</v>
@@ -6841,16 +6841,16 @@
         <v>46225.811274074076</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="I82" s="5">
         <v>46205</v>
@@ -6868,13 +6868,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6884,7 +6884,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B83" s="9">
         <v>46162.560250625</v>
@@ -6896,16 +6896,16 @@
         <v>46225.811265509255</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I83" s="9">
         <v>46205</v>
@@ -6923,13 +6923,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6939,7 +6939,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B84" s="5">
         <v>46162.55862063657</v>
@@ -6949,16 +6949,16 @@
         <v>46225.81192504629</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="I84" s="5">
         <v>46210</v>
@@ -6976,13 +6976,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q84" s="5">
         <v>46210</v>
@@ -7002,7 +7002,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B85" s="9">
         <v>46162.558626620375</v>
@@ -7012,16 +7012,16 @@
         <v>46225.81138908565</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H85" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I85" s="9">
         <v>46210</v>
@@ -7039,13 +7039,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O85" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="P85" s="10" t="s">
         <v>258</v>
-      </c>
-      <c r="P85" s="10" t="s">
-        <v>259</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -7055,7 +7055,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B86" s="5">
         <v>46162.55863280092</v>
@@ -7065,16 +7065,16 @@
         <v>46225.81137782407</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="I86" s="5">
         <v>46210</v>
@@ -7092,13 +7092,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O86" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="P86" s="6" t="s">
         <v>258</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>259</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -7108,7 +7108,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B87" s="9">
         <v>46162.55863850695</v>
@@ -7118,16 +7118,16 @@
         <v>46225.81136515047</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H87" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I87" s="9">
         <v>46210</v>
@@ -7145,13 +7145,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -7161,7 +7161,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B88" s="5">
         <v>46162.558644247685</v>
@@ -7171,16 +7171,16 @@
         <v>46225.811345740745</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="I88" s="5">
         <v>46210</v>
@@ -7198,13 +7198,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O88" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="P88" s="6" t="s">
         <v>258</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>259</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7214,7 +7214,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B89" s="9">
         <v>46162.55864990741</v>
@@ -7224,16 +7224,16 @@
         <v>46225.811355625</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I89" s="9">
         <v>46210</v>
@@ -7251,13 +7251,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -7267,7 +7267,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B90" s="5">
         <v>46162.56148016204</v>
@@ -7277,16 +7277,16 @@
         <v>46225.81132334491</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="I90" s="5">
         <v>46210</v>
@@ -7304,13 +7304,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7320,7 +7320,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B91" s="9">
         <v>46162.561489201384</v>
@@ -7330,16 +7330,16 @@
         <v>46225.81131275463</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H91" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I91" s="9">
         <v>46210</v>
@@ -7357,10 +7357,10 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P91" s="10" t="s">
         <v>26</v>
@@ -7373,7 +7373,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B92" s="5">
         <v>46162.56149930556</v>
@@ -7383,16 +7383,16 @@
         <v>46225.81130295139</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="I92" s="5">
         <v>46210</v>
@@ -7410,13 +7410,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7426,7 +7426,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B93" s="9">
         <v>46162.561507199076</v>
@@ -7436,16 +7436,16 @@
         <v>46225.81129587963</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H93" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I93" s="9">
         <v>46210</v>
@@ -7463,13 +7463,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7479,7 +7479,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B94" s="5">
         <v>46162.56151613426</v>
@@ -7489,16 +7489,16 @@
         <v>46225.81128686343</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="I94" s="5">
         <v>46210</v>
@@ -7516,13 +7516,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7532,7 +7532,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B95" s="9">
         <v>46162.56152413195</v>
@@ -7542,16 +7542,16 @@
         <v>46225.81127690972</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H95" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I95" s="9">
         <v>46210</v>
@@ -7569,13 +7569,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7585,7 +7585,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B96" s="5">
         <v>46162.56153119213</v>
@@ -7595,16 +7595,16 @@
         <v>46225.81127016204</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="I96" s="5">
         <v>46210</v>
@@ -7622,13 +7622,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7638,7 +7638,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B97" s="9">
         <v>46162.55865439815</v>
@@ -7648,16 +7648,16 @@
         <v>46218.20591833333</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H97" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I97" s="9">
         <v>46217</v>
@@ -7675,13 +7675,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q97" s="9">
         <v>46217</v>
@@ -7701,7 +7701,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B98" s="5">
         <v>46162.55865909722</v>
@@ -7711,16 +7711,16 @@
         <v>46217.16848263889</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I98" s="5">
         <v>46217</v>
@@ -7738,13 +7738,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7754,7 +7754,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B99" s="9">
         <v>46162.55866501157</v>
@@ -7764,16 +7764,16 @@
         <v>46217.168484050926</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H99" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I99" s="9">
         <v>46217</v>
@@ -7791,13 +7791,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7807,7 +7807,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B100" s="5">
         <v>46162.55867084491</v>
@@ -7817,16 +7817,16 @@
         <v>46217.16847319444</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I100" s="5">
         <v>46217</v>
@@ -7844,13 +7844,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7860,7 +7860,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B101" s="9">
         <v>46162.558676597226</v>
@@ -7870,16 +7870,16 @@
         <v>46217.16847716435</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I101" s="9">
         <v>46217</v>
@@ -7897,13 +7897,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7913,7 +7913,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B102" s="5">
         <v>46162.55868239583</v>
@@ -7923,16 +7923,16 @@
         <v>46217.168485312504</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I102" s="5">
         <v>46217</v>
@@ -7950,13 +7950,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7966,7 +7966,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B103" s="9">
         <v>46162.56176834491</v>
@@ -7976,16 +7976,16 @@
         <v>46217.16846244213</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H103" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I103" s="9">
         <v>46217</v>
@@ -8003,13 +8003,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -8019,7 +8019,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B104" s="5">
         <v>46162.56177670139</v>
@@ -8029,16 +8029,16 @@
         <v>46224.87647666667</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I104" s="5">
         <v>46217</v>
@@ -8056,13 +8056,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -8072,7 +8072,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B105" s="9">
         <v>46162.56178474537</v>
@@ -8082,16 +8082,16 @@
         <v>46217.16846583333</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H105" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I105" s="9">
         <v>46217</v>
@@ -8109,13 +8109,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -8125,7 +8125,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B106" s="5">
         <v>46162.56179298611</v>
@@ -8135,16 +8135,16 @@
         <v>46217.16846726852</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I106" s="5">
         <v>46217</v>
@@ -8162,13 +8162,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8178,7 +8178,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B107" s="9">
         <v>46162.5618009375</v>
@@ -8188,16 +8188,16 @@
         <v>46217.16846878472</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H107" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I107" s="9">
         <v>46217</v>
@@ -8215,13 +8215,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -8231,7 +8231,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B108" s="5">
         <v>46162.56180909723</v>
@@ -8241,16 +8241,16 @@
         <v>46217.168470358796</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H108" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I108" s="5">
         <v>46217</v>
@@ -8268,13 +8268,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8284,7 +8284,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B109" s="9">
         <v>46162.56181716435</v>
@@ -8294,16 +8294,16 @@
         <v>46217.16847178241</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H109" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I109" s="9">
         <v>46217</v>
@@ -8321,13 +8321,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8337,7 +8337,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B110" s="5">
         <v>46162.55868650463</v>
@@ -8349,7 +8349,7 @@
         <v>46225.87275534723</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>25</v>
@@ -8373,7 +8373,7 @@
         <v>26</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>26</v>
@@ -8390,7 +8390,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B111" s="9">
         <v>46162.55869006945</v>
@@ -8402,16 +8402,16 @@
         <v>46216.54541784722</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H111" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H111" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I111" s="9">
         <v>46161</v>
@@ -8429,13 +8429,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O111" s="10" t="s">
         <v>113</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q111" s="9">
         <v>46161</v>
@@ -8455,7 +8455,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B112" s="5">
         <v>46162.558696921296</v>
@@ -8467,16 +8467,16 @@
         <v>46216.54542513889</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H112" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I112" s="5">
         <v>46161</v>
@@ -8494,13 +8494,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>104</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q112" s="5">
         <v>46161</v>
@@ -8520,7 +8520,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B113" s="9">
         <v>46162.55870284722</v>
@@ -8532,16 +8532,16 @@
         <v>46225.87107724537</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H113" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H113" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I113" s="9">
         <v>46196</v>
@@ -8559,13 +8559,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O113" s="10" t="s">
         <v>122</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q113" s="9">
         <v>46196</v>
@@ -8585,7 +8585,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B114" s="5">
         <v>46162.55870962963</v>
@@ -8597,16 +8597,16 @@
         <v>46225.18669188657</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H114" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I114" s="5">
         <v>46232</v>
@@ -8624,13 +8624,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q114" s="5">
         <v>46232</v>
@@ -8639,7 +8639,7 @@
         <v>46232</v>
       </c>
       <c r="S114" s="12" t="s">
-        <v>151</v>
+        <v>307</v>
       </c>
       <c r="T114" s="6">
         <v>1</v>
@@ -8770,7 +8770,7 @@
         <v>46224.25040153935</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8823,7 +8823,7 @@
         <v>46224.25040292824</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8876,7 +8876,7 @@
         <v>46224.25044962963</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8906,7 +8906,7 @@
         <v>312</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P119" s="10" t="s">
         <v>318</v>
@@ -8929,7 +8929,7 @@
         <v>46224.25045101852</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8959,7 +8959,7 @@
         <v>312</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>318</v>
@@ -8982,7 +8982,7 @@
         <v>46224.25040421296</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -9012,10 +9012,10 @@
         <v>312</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -9035,7 +9035,7 @@
         <v>46224.25042715278</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -9065,10 +9065,10 @@
         <v>312</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -9088,7 +9088,7 @@
         <v>46224.2504290625</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -9118,10 +9118,10 @@
         <v>312</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -9141,7 +9141,7 @@
         <v>46224.250430555556</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -9171,10 +9171,10 @@
         <v>312</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9194,7 +9194,7 @@
         <v>46224.25043193287</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -9224,10 +9224,10 @@
         <v>312</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -9247,7 +9247,7 @@
         <v>46224.250433402776</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9277,10 +9277,10 @@
         <v>312</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9300,7 +9300,7 @@
         <v>46224.25043480324</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -9330,10 +9330,10 @@
         <v>312</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9353,7 +9353,7 @@
         <v>46224.25043630787</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9383,10 +9383,10 @@
         <v>312</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9436,7 +9436,7 @@
         <v>309</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P129" s="10" t="s">
         <v>309</v>
@@ -9469,7 +9469,7 @@
         <v>46223.57901649305</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9520,7 +9520,7 @@
         <v>46223.57901584491</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9571,7 +9571,7 @@
         <v>46223.57901519676</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9622,7 +9622,7 @@
         <v>46223.57901452546</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9673,7 +9673,7 @@
         <v>46223.579013888884</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9701,7 +9701,7 @@
         <v>329</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>340</v>
@@ -9724,7 +9724,7 @@
         <v>46223.579013229166</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9755,7 +9755,7 @@
         <v>342</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9775,7 +9775,7 @@
         <v>46223.579012546295</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9806,7 +9806,7 @@
         <v>344</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9826,7 +9826,7 @@
         <v>46223.579011875</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9857,7 +9857,7 @@
         <v>342</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9877,7 +9877,7 @@
         <v>46223.57901104167</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9928,7 +9928,7 @@
         <v>46223.57901035879</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -9959,7 +9959,7 @@
         <v>342</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9979,7 +9979,7 @@
         <v>46223.579009733796</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -10010,7 +10010,7 @@
         <v>350</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -10030,7 +10030,7 @@
         <v>46223.57900907408</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -10061,7 +10061,7 @@
         <v>350</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -10111,7 +10111,7 @@
         <v>309</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>309</v>
@@ -10144,7 +10144,7 @@
         <v>46223.57929469907</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -10197,7 +10197,7 @@
         <v>46223.57929405093</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -10250,7 +10250,7 @@
         <v>46223.5792933912</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -10303,7 +10303,7 @@
         <v>46223.579292766204</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10356,7 +10356,7 @@
         <v>46223.57929214121</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -10386,7 +10386,7 @@
         <v>353</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P147" s="10" t="s">
         <v>363</v>
@@ -10409,7 +10409,7 @@
         <v>46223.5792915162</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10442,7 +10442,7 @@
         <v>365</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10462,7 +10462,7 @@
         <v>46223.57929087963</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -10492,10 +10492,10 @@
         <v>353</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10515,7 +10515,7 @@
         <v>46223.57929026621</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10548,7 +10548,7 @@
         <v>365</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10601,7 +10601,7 @@
         <v>365</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10621,7 +10621,7 @@
         <v>46223.57928883102</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10654,7 +10654,7 @@
         <v>365</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10674,7 +10674,7 @@
         <v>46223.57928822917</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10707,7 +10707,7 @@
         <v>365</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q153" s="10"/>
       <c r="R153" s="10"/>
@@ -10727,7 +10727,7 @@
         <v>46223.579287615736</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10760,7 +10760,7 @@
         <v>365</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10843,7 +10843,7 @@
         <v>46225.87106959491</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10896,7 +10896,7 @@
         <v>46225.87107101852</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
@@ -10949,7 +10949,7 @@
         <v>46225.87107528935</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -11002,7 +11002,7 @@
         <v>46225.87107458334</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
@@ -11055,7 +11055,7 @@
         <v>46223.57947667824</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -11085,7 +11085,7 @@
         <v>373</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P160" s="6" t="s">
         <v>384</v>
@@ -11108,7 +11108,7 @@
         <v>46225.87106449074</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
@@ -11161,7 +11161,7 @@
         <v>46225.87106525463</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -11194,7 +11194,7 @@
         <v>386</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11214,7 +11214,7 @@
         <v>46225.871065949075</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
@@ -11267,7 +11267,7 @@
         <v>46225.8710666088</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11320,7 +11320,7 @@
         <v>46225.87106722222</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
@@ -11373,7 +11373,7 @@
         <v>46225.87106789352</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11426,7 +11426,7 @@
         <v>46225.87106853009</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
@@ -11459,7 +11459,7 @@
         <v>386</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q167" s="10"/>
       <c r="R167" s="10"/>
@@ -11509,7 +11509,7 @@
         <v>309</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P168" s="6" t="s">
         <v>309</v>
@@ -11542,7 +11542,7 @@
         <v>46224.25045532407</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
@@ -11570,7 +11570,7 @@
         <v>398</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P169" s="10" t="s">
         <v>400</v>
@@ -11593,7 +11593,7 @@
         <v>46224.25039887731</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11621,7 +11621,7 @@
         <v>398</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P170" s="6" t="s">
         <v>400</v>
@@ -11644,7 +11644,7 @@
         <v>46224.250400185185</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11672,7 +11672,7 @@
         <v>398</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P171" s="10" t="s">
         <v>403</v>
@@ -11695,7 +11695,7 @@
         <v>46224.25039688658</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11723,7 +11723,7 @@
         <v>398</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P172" s="6" t="s">
         <v>403</v>
@@ -11746,7 +11746,7 @@
         <v>46224.25045253472</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
@@ -11774,7 +11774,7 @@
         <v>398</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P173" s="10" t="s">
         <v>406</v>
@@ -11797,7 +11797,7 @@
         <v>46224.25043752315</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
@@ -11825,7 +11825,7 @@
         <v>398</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P174" s="6" t="s">
         <v>26</v>
@@ -11848,7 +11848,7 @@
         <v>46224.25043901621</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
@@ -11876,10 +11876,10 @@
         <v>398</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q175" s="10"/>
       <c r="R175" s="10"/>
@@ -11899,7 +11899,7 @@
         <v>46224.25044046296</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
@@ -11927,7 +11927,7 @@
         <v>398</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P176" s="6" t="s">
         <v>26</v>
@@ -11950,7 +11950,7 @@
         <v>46224.2504419676</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
@@ -11978,7 +11978,7 @@
         <v>398</v>
       </c>
       <c r="O177" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P177" s="10" t="s">
         <v>26</v>
@@ -12001,7 +12001,7 @@
         <v>46224.25044340278</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
@@ -12029,7 +12029,7 @@
         <v>398</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P178" s="6" t="s">
         <v>26</v>
@@ -12052,7 +12052,7 @@
         <v>46224.25044509259</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
@@ -12080,7 +12080,7 @@
         <v>398</v>
       </c>
       <c r="O179" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P179" s="10" t="s">
         <v>26</v>
@@ -12103,7 +12103,7 @@
         <v>46224.25044643518</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
@@ -12131,10 +12131,10 @@
         <v>398</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -12217,7 +12217,7 @@
         <v>46226.16815751157</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
@@ -12245,7 +12245,7 @@
         <v>415</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P182" s="6" t="s">
         <v>418</v>
@@ -12268,7 +12268,7 @@
         <v>46226.16815899305</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>26</v>
@@ -12296,7 +12296,7 @@
         <v>415</v>
       </c>
       <c r="O183" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P183" s="10" t="s">
         <v>418</v>
@@ -12319,7 +12319,7 @@
         <v>46226.16815614583</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
@@ -12347,7 +12347,7 @@
         <v>415</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P184" s="6" t="s">
         <v>421</v>
@@ -12370,7 +12370,7 @@
         <v>46226.16816035879</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
@@ -12398,7 +12398,7 @@
         <v>415</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P185" s="10" t="s">
         <v>418</v>
@@ -12421,7 +12421,7 @@
         <v>46226.16816185185</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
@@ -12449,7 +12449,7 @@
         <v>415</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P186" s="6" t="s">
         <v>424</v>
@@ -12472,7 +12472,7 @@
         <v>46226.16814340278</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
@@ -12500,7 +12500,7 @@
         <v>415</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P187" s="10" t="s">
         <v>26</v>
@@ -12523,7 +12523,7 @@
         <v>46226.16814550926</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12551,7 +12551,7 @@
         <v>415</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P188" s="6" t="s">
         <v>390</v>
@@ -12574,7 +12574,7 @@
         <v>46226.168146909724</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
@@ -12602,10 +12602,10 @@
         <v>415</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12625,7 +12625,7 @@
         <v>46226.168148275465</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12653,10 +12653,10 @@
         <v>415</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12676,7 +12676,7 @@
         <v>46226.16814969908</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
@@ -12704,10 +12704,10 @@
         <v>415</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12727,7 +12727,7 @@
         <v>46226.16815109954</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -12755,10 +12755,10 @@
         <v>415</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12778,7 +12778,7 @@
         <v>46226.16815254629</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>26</v>
@@ -12806,10 +12806,10 @@
         <v>415</v>
       </c>
       <c r="O193" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P193" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q193" s="10"/>
       <c r="R193" s="10"/>
@@ -12939,7 +12939,7 @@
         <v>46227.16884697917</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
@@ -12967,7 +12967,7 @@
         <v>436</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P196" s="6" t="s">
         <v>441</v>
@@ -12990,7 +12990,7 @@
         <v>46227.16885321759</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>26</v>
@@ -13018,7 +13018,7 @@
         <v>436</v>
       </c>
       <c r="O197" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P197" s="10" t="s">
         <v>441</v>
@@ -13041,7 +13041,7 @@
         <v>46227.16885833333</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
@@ -13069,7 +13069,7 @@
         <v>436</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P198" s="6" t="s">
         <v>441</v>
@@ -13092,7 +13092,7 @@
         <v>46227.16885959491</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>26</v>
@@ -13120,7 +13120,7 @@
         <v>436</v>
       </c>
       <c r="O199" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P199" s="10" t="s">
         <v>441</v>
@@ -13143,7 +13143,7 @@
         <v>46227.168854675925</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
@@ -13171,7 +13171,7 @@
         <v>436</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P200" s="6" t="s">
         <v>446</v>
@@ -13194,7 +13194,7 @@
         <v>46227.168836944446</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
@@ -13222,7 +13222,7 @@
         <v>436</v>
       </c>
       <c r="O201" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P201" s="10" t="s">
         <v>390</v>
@@ -13245,7 +13245,7 @@
         <v>46227.16883850694</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
@@ -13273,7 +13273,7 @@
         <v>436</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P202" s="6" t="s">
         <v>26</v>
@@ -13296,7 +13296,7 @@
         <v>46227.168839861115</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
@@ -13324,10 +13324,10 @@
         <v>436</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P203" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q203" s="10"/>
       <c r="R203" s="10"/>
@@ -13347,7 +13347,7 @@
         <v>46227.168841273146</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
@@ -13375,10 +13375,10 @@
         <v>436</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13398,7 +13398,7 @@
         <v>46227.16884255787</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
@@ -13426,10 +13426,10 @@
         <v>436</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q205" s="10"/>
       <c r="R205" s="10"/>
@@ -13449,7 +13449,7 @@
         <v>46227.168843796295</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
@@ -13477,10 +13477,10 @@
         <v>436</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13500,7 +13500,7 @@
         <v>46227.16884491898</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
@@ -13528,10 +13528,10 @@
         <v>436</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q207" s="10"/>
       <c r="R207" s="10"/>
@@ -13581,7 +13581,7 @@
         <v>433</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P208" s="6" t="s">
         <v>433</v>
@@ -13614,7 +13614,7 @@
         <v>46230.16873420139</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
@@ -13642,7 +13642,7 @@
         <v>455</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P209" s="10" t="s">
         <v>457</v>
@@ -13665,7 +13665,7 @@
         <v>46230.16873547454</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
@@ -13693,7 +13693,7 @@
         <v>455</v>
       </c>
       <c r="O210" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P210" s="6" t="s">
         <v>457</v>
@@ -13716,7 +13716,7 @@
         <v>46230.16873686343</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>26</v>
@@ -13744,7 +13744,7 @@
         <v>455</v>
       </c>
       <c r="O211" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P211" s="10" t="s">
         <v>457</v>
@@ -13767,7 +13767,7 @@
         <v>46230.16873802083</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
@@ -13795,7 +13795,7 @@
         <v>455</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P212" s="6" t="s">
         <v>457</v>
@@ -13818,7 +13818,7 @@
         <v>46230.168739155095</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>26</v>
@@ -13846,7 +13846,7 @@
         <v>455</v>
       </c>
       <c r="O213" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P213" s="10" t="s">
         <v>462</v>
@@ -13869,7 +13869,7 @@
         <v>46230.16872133102</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
@@ -13897,7 +13897,7 @@
         <v>455</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P214" s="6" t="s">
         <v>26</v>
@@ -13920,7 +13920,7 @@
         <v>46230.16872302083</v>
       </c>
       <c r="E215" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F215" s="10" t="s">
         <v>26</v>
@@ -13948,10 +13948,10 @@
         <v>455</v>
       </c>
       <c r="O215" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P215" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q215" s="10"/>
       <c r="R215" s="10"/>
@@ -13971,7 +13971,7 @@
         <v>46230.168724675925</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
@@ -13999,7 +13999,7 @@
         <v>455</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P216" s="6" t="s">
         <v>466</v>
@@ -14022,7 +14022,7 @@
         <v>46230.16872583333</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>26</v>
@@ -14050,10 +14050,10 @@
         <v>455</v>
       </c>
       <c r="O217" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P217" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q217" s="10"/>
       <c r="R217" s="10"/>
@@ -14073,7 +14073,7 @@
         <v>46230.168726979166</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
@@ -14101,10 +14101,10 @@
         <v>455</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P218" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q218" s="6"/>
       <c r="R218" s="6"/>
@@ -14124,7 +14124,7 @@
         <v>46230.168728055556</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>26</v>
@@ -14152,10 +14152,10 @@
         <v>455</v>
       </c>
       <c r="O219" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P219" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q219" s="10"/>
       <c r="R219" s="10"/>
@@ -14175,7 +14175,7 @@
         <v>46230.16872912037</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
@@ -14203,10 +14203,10 @@
         <v>455</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P220" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q220" s="6"/>
       <c r="R220" s="6"/>
@@ -14223,7 +14223,7 @@
       </c>
       <c r="C221" s="10"/>
       <c r="D221" s="9">
-        <v>46231.168253888885</v>
+        <v>46232.179640358794</v>
       </c>
       <c r="E221" s="10" t="s">
         <v>472</v>
@@ -14232,10 +14232,10 @@
         <v>26</v>
       </c>
       <c r="G221" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H221" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="H221" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I221" s="9">
         <v>46231</v>
@@ -14256,7 +14256,7 @@
         <v>433</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P221" s="10" t="s">
         <v>433</v>
@@ -14267,8 +14267,8 @@
       <c r="R221" s="9">
         <v>46231</v>
       </c>
-      <c r="S221" s="12" t="s">
-        <v>151</v>
+      <c r="S221" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T221" s="10">
         <v>0</v>
@@ -14289,16 +14289,16 @@
         <v>46231.168255868055</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H222" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="H222" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="I222" s="6"/>
       <c r="J222" s="5">
@@ -14317,7 +14317,7 @@
         <v>472</v>
       </c>
       <c r="O222" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P222" s="6" t="s">
         <v>474</v>
@@ -14340,16 +14340,16 @@
         <v>46231.16824994213</v>
       </c>
       <c r="E223" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G223" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H223" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="H223" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I223" s="10"/>
       <c r="J223" s="9">
@@ -14368,7 +14368,7 @@
         <v>472</v>
       </c>
       <c r="O223" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P223" s="10" t="s">
         <v>474</v>
@@ -14391,16 +14391,16 @@
         <v>46231.168251111114</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H224" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="H224" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="I224" s="6"/>
       <c r="J224" s="5">
@@ -14419,7 +14419,7 @@
         <v>472</v>
       </c>
       <c r="O224" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P224" s="6" t="s">
         <v>477</v>
@@ -14442,16 +14442,16 @@
         <v>46231.168252511576</v>
       </c>
       <c r="E225" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F225" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G225" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H225" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="H225" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I225" s="10"/>
       <c r="J225" s="9">
@@ -14470,7 +14470,7 @@
         <v>472</v>
       </c>
       <c r="O225" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P225" s="10" t="s">
         <v>477</v>
@@ -14493,16 +14493,16 @@
         <v>46231.16825728009</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F226" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H226" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="H226" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="I226" s="6"/>
       <c r="J226" s="5">
@@ -14521,7 +14521,7 @@
         <v>472</v>
       </c>
       <c r="O226" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P226" s="6" t="s">
         <v>480</v>
@@ -14544,16 +14544,16 @@
         <v>46231.16824121527</v>
       </c>
       <c r="E227" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F227" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G227" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H227" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="H227" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I227" s="10"/>
       <c r="J227" s="9">
@@ -14572,10 +14572,10 @@
         <v>472</v>
       </c>
       <c r="O227" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P227" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q227" s="10"/>
       <c r="R227" s="10"/>
@@ -14595,16 +14595,16 @@
         <v>46231.16824241898</v>
       </c>
       <c r="E228" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F228" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G228" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H228" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="H228" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="I228" s="6"/>
       <c r="J228" s="5">
@@ -14623,10 +14623,10 @@
         <v>472</v>
       </c>
       <c r="O228" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P228" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q228" s="6"/>
       <c r="R228" s="6"/>
@@ -14652,10 +14652,10 @@
         <v>26</v>
       </c>
       <c r="G229" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H229" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="H229" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I229" s="10"/>
       <c r="J229" s="9">
@@ -14674,10 +14674,10 @@
         <v>472</v>
       </c>
       <c r="O229" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P229" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q229" s="10"/>
       <c r="R229" s="10"/>
@@ -14697,16 +14697,16 @@
         <v>46231.168244733795</v>
       </c>
       <c r="E230" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F230" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G230" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H230" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="H230" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="I230" s="6"/>
       <c r="J230" s="5">
@@ -14725,10 +14725,10 @@
         <v>472</v>
       </c>
       <c r="O230" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P230" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q230" s="6"/>
       <c r="R230" s="6"/>
@@ -14748,16 +14748,16 @@
         <v>46231.16824633101</v>
       </c>
       <c r="E231" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F231" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G231" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H231" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="H231" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I231" s="10"/>
       <c r="J231" s="9">
@@ -14776,10 +14776,10 @@
         <v>472</v>
       </c>
       <c r="O231" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P231" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q231" s="10"/>
       <c r="R231" s="10"/>
@@ -14799,16 +14799,16 @@
         <v>46231.16824753472</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F232" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G232" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H232" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="H232" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="I232" s="6"/>
       <c r="J232" s="5">
@@ -14827,10 +14827,10 @@
         <v>472</v>
       </c>
       <c r="O232" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P232" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q232" s="6"/>
       <c r="R232" s="6"/>
@@ -14850,16 +14850,16 @@
         <v>46231.16824866898</v>
       </c>
       <c r="E233" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F233" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G233" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H233" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="H233" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I233" s="10"/>
       <c r="J233" s="9">
@@ -14878,10 +14878,10 @@
         <v>472</v>
       </c>
       <c r="O233" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P233" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q233" s="10"/>
       <c r="R233" s="10"/>
@@ -14898,7 +14898,7 @@
       </c>
       <c r="C234" s="6"/>
       <c r="D234" s="5">
-        <v>46225.186692812495</v>
+        <v>46232.168207395836</v>
       </c>
       <c r="E234" s="6" t="s">
         <v>489</v>
@@ -14907,10 +14907,10 @@
         <v>26</v>
       </c>
       <c r="G234" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H234" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="H234" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="I234" s="5">
         <v>46232</v>
@@ -14931,7 +14931,7 @@
         <v>433</v>
       </c>
       <c r="O234" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P234" s="6" t="s">
         <v>490</v>
@@ -14943,7 +14943,7 @@
         <v>46232</v>
       </c>
       <c r="S234" s="12" t="s">
-        <v>151</v>
+        <v>307</v>
       </c>
       <c r="T234" s="6">
         <v>0</v>
@@ -14961,19 +14961,19 @@
       </c>
       <c r="C235" s="10"/>
       <c r="D235" s="9">
-        <v>46162.676026875</v>
+        <v>46232.16820975694</v>
       </c>
       <c r="E235" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F235" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G235" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H235" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="H235" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I235" s="9">
         <v>46232</v>
@@ -14994,7 +14994,7 @@
         <v>489</v>
       </c>
       <c r="O235" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P235" s="10" t="s">
         <v>489</v>
@@ -15014,19 +15014,19 @@
       </c>
       <c r="C236" s="6"/>
       <c r="D236" s="5">
-        <v>46162.67602255787</v>
+        <v>46232.16820384259</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F236" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G236" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H236" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="H236" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="I236" s="5">
         <v>46232</v>
@@ -15047,7 +15047,7 @@
         <v>489</v>
       </c>
       <c r="O236" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P236" s="6" t="s">
         <v>489</v>
@@ -15067,19 +15067,19 @@
       </c>
       <c r="C237" s="10"/>
       <c r="D237" s="9">
-        <v>46162.676019108796</v>
+        <v>46232.16820505787</v>
       </c>
       <c r="E237" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F237" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G237" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H237" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="H237" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I237" s="9">
         <v>46232</v>
@@ -15100,7 +15100,7 @@
         <v>489</v>
       </c>
       <c r="O237" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P237" s="10" t="s">
         <v>489</v>
@@ -15120,19 +15120,19 @@
       </c>
       <c r="C238" s="6"/>
       <c r="D238" s="5">
-        <v>46162.67601616898</v>
+        <v>46232.168206180555</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F238" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G238" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H238" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="H238" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="I238" s="5">
         <v>46232</v>
@@ -15153,7 +15153,7 @@
         <v>489</v>
       </c>
       <c r="O238" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P238" s="6" t="s">
         <v>489</v>
@@ -15173,19 +15173,19 @@
       </c>
       <c r="C239" s="10"/>
       <c r="D239" s="9">
-        <v>46162.676013275464</v>
+        <v>46232.16820247685</v>
       </c>
       <c r="E239" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F239" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G239" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H239" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="H239" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I239" s="9">
         <v>46232</v>
@@ -15206,7 +15206,7 @@
         <v>489</v>
       </c>
       <c r="O239" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P239" s="10" t="s">
         <v>489</v>
@@ -15226,19 +15226,19 @@
       </c>
       <c r="C240" s="6"/>
       <c r="D240" s="5">
-        <v>46162.67600972222</v>
+        <v>46232.168191261575</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F240" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G240" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H240" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="H240" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="I240" s="5">
         <v>46232</v>
@@ -15259,7 +15259,7 @@
         <v>489</v>
       </c>
       <c r="O240" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P240" s="6" t="s">
         <v>26</v>
@@ -15279,19 +15279,19 @@
       </c>
       <c r="C241" s="10"/>
       <c r="D241" s="9">
-        <v>46162.676007002316</v>
+        <v>46232.1681928125</v>
       </c>
       <c r="E241" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F241" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G241" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H241" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="H241" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I241" s="9">
         <v>46232</v>
@@ -15312,7 +15312,7 @@
         <v>489</v>
       </c>
       <c r="O241" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P241" s="10" t="s">
         <v>26</v>
@@ -15332,19 +15332,19 @@
       </c>
       <c r="C242" s="6"/>
       <c r="D242" s="5">
-        <v>46162.67600369213</v>
+        <v>46232.16819405093</v>
       </c>
       <c r="E242" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F242" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G242" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H242" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="H242" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="I242" s="5">
         <v>46232</v>
@@ -15385,19 +15385,19 @@
       </c>
       <c r="C243" s="10"/>
       <c r="D243" s="9">
-        <v>46162.67599591435</v>
+        <v>46232.168195289356</v>
       </c>
       <c r="E243" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F243" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G243" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H243" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="H243" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I243" s="9">
         <v>46232</v>
@@ -15418,7 +15418,7 @@
         <v>489</v>
       </c>
       <c r="O243" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P243" s="10" t="s">
         <v>26</v>
@@ -15438,19 +15438,19 @@
       </c>
       <c r="C244" s="6"/>
       <c r="D244" s="5">
-        <v>46162.67599258102</v>
+        <v>46232.16819645833</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F244" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G244" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H244" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="H244" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="I244" s="5">
         <v>46232</v>
@@ -15471,7 +15471,7 @@
         <v>489</v>
       </c>
       <c r="O244" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P244" s="6" t="s">
         <v>26</v>
@@ -15491,19 +15491,19 @@
       </c>
       <c r="C245" s="10"/>
       <c r="D245" s="9">
-        <v>46162.675991412034</v>
+        <v>46232.16819769676</v>
       </c>
       <c r="E245" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F245" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G245" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H245" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="H245" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="I245" s="9">
         <v>46232</v>
@@ -15524,7 +15524,7 @@
         <v>489</v>
       </c>
       <c r="O245" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P245" s="10" t="s">
         <v>26</v>
@@ -15544,19 +15544,19 @@
       </c>
       <c r="C246" s="6"/>
       <c r="D246" s="5">
-        <v>46162.675990613425</v>
+        <v>46232.1681990162</v>
       </c>
       <c r="E246" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F246" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G246" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H246" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="H246" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="I246" s="5">
         <v>46232</v>
@@ -15577,7 +15577,7 @@
         <v>489</v>
       </c>
       <c r="O246" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P246" s="6" t="s">
         <v>26</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2845" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2845" uniqueCount="511">
   <si>
     <t xml:space="preserve">50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT 4324 4325 </t>
   </si>
@@ -997,9 +997,6 @@
   </si>
   <si>
     <t xml:space="preserve">Revestimiento,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214969379310810</t>
@@ -8594,7 +8591,7 @@
         <v>46216.54425189814</v>
       </c>
       <c r="D114" s="5">
-        <v>46225.18669188657</v>
+        <v>46233.17925828704</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>305</v>
@@ -8638,8 +8635,8 @@
       <c r="R114" s="5">
         <v>46232</v>
       </c>
-      <c r="S114" s="12" t="s">
-        <v>307</v>
+      <c r="S114" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T114" s="6">
         <v>1</v>
@@ -8650,7 +8647,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B115" s="9">
         <v>46162.55871869213</v>
@@ -8660,7 +8657,7 @@
         <v>46162.64775322917</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>25</v>
@@ -8684,7 +8681,7 @@
         <v>26</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>26</v>
@@ -8697,7 +8694,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B116" s="5">
         <v>46162.55872223379</v>
@@ -8707,7 +8704,7 @@
         <v>46225.185239872684</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8734,13 +8731,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q116" s="5">
         <v>46218</v>
@@ -8760,7 +8757,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B117" s="9">
         <v>46162.55873068287</v>
@@ -8797,10 +8794,10 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P117" s="10" t="s">
         <v>26</v>
@@ -8813,7 +8810,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B118" s="5">
         <v>46162.558735011575</v>
@@ -8850,10 +8847,10 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>26</v>
@@ -8866,7 +8863,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B119" s="9">
         <v>46162.55873951389</v>
@@ -8903,13 +8900,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O119" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8919,7 +8916,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B120" s="5">
         <v>46162.55874386574</v>
@@ -8956,13 +8953,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8972,7 +8969,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B121" s="9">
         <v>46162.55874813657</v>
@@ -9009,7 +9006,7 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O121" s="10" t="s">
         <v>196</v>
@@ -9025,7 +9022,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B122" s="5">
         <v>46162.56516702546</v>
@@ -9062,7 +9059,7 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>196</v>
@@ -9078,7 +9075,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B123" s="9">
         <v>46162.56517383102</v>
@@ -9115,7 +9112,7 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O123" s="10" t="s">
         <v>196</v>
@@ -9131,7 +9128,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B124" s="5">
         <v>46162.565181134254</v>
@@ -9168,7 +9165,7 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>196</v>
@@ -9184,7 +9181,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B125" s="9">
         <v>46162.565189201385</v>
@@ -9221,7 +9218,7 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O125" s="10" t="s">
         <v>196</v>
@@ -9237,7 +9234,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B126" s="5">
         <v>46162.56519680556</v>
@@ -9274,7 +9271,7 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>196</v>
@@ -9290,7 +9287,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B127" s="9">
         <v>46162.565205590276</v>
@@ -9327,7 +9324,7 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O127" s="10" t="s">
         <v>196</v>
@@ -9343,7 +9340,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B128" s="5">
         <v>46162.565212013884</v>
@@ -9380,7 +9377,7 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>196</v>
@@ -9396,7 +9393,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B129" s="9">
         <v>46162.558751550925</v>
@@ -9406,7 +9403,7 @@
         <v>46223.5799087037</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -9433,13 +9430,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O129" s="10" t="s">
         <v>274</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q129" s="9">
         <v>46219</v>
@@ -9459,7 +9456,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B130" s="5">
         <v>46162.558756238424</v>
@@ -9494,13 +9491,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O130" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="P130" s="6" t="s">
         <v>331</v>
-      </c>
-      <c r="P130" s="6" t="s">
-        <v>332</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9510,7 +9507,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B131" s="9">
         <v>46162.55876204861</v>
@@ -9545,13 +9542,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9561,7 +9558,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B132" s="5">
         <v>46162.55876745371</v>
@@ -9596,13 +9593,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O132" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="P132" s="6" t="s">
         <v>336</v>
-      </c>
-      <c r="P132" s="6" t="s">
-        <v>337</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9612,7 +9609,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B133" s="9">
         <v>46162.558773888886</v>
@@ -9647,13 +9644,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O133" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="P133" s="10" t="s">
         <v>336</v>
-      </c>
-      <c r="P133" s="10" t="s">
-        <v>337</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9663,7 +9660,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B134" s="5">
         <v>46162.558827430556</v>
@@ -9698,13 +9695,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>196</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9714,7 +9711,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B135" s="9">
         <v>46162.565477233795</v>
@@ -9749,10 +9746,10 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P135" s="10" t="s">
         <v>196</v>
@@ -9765,7 +9762,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B136" s="5">
         <v>46162.56548539352</v>
@@ -9800,10 +9797,10 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>196</v>
@@ -9816,7 +9813,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B137" s="9">
         <v>46162.56549420139</v>
@@ -9851,10 +9848,10 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P137" s="10" t="s">
         <v>196</v>
@@ -9867,7 +9864,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B138" s="5">
         <v>46162.56549981482</v>
@@ -9902,13 +9899,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9918,7 +9915,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B139" s="9">
         <v>46162.565507719904</v>
@@ -9953,10 +9950,10 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P139" s="10" t="s">
         <v>196</v>
@@ -9969,7 +9966,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B140" s="5">
         <v>46162.56551637732</v>
@@ -10004,10 +10001,10 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>196</v>
@@ -10020,7 +10017,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B141" s="9">
         <v>46162.56598206019</v>
@@ -10055,10 +10052,10 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="P141" s="10" t="s">
         <v>196</v>
@@ -10071,7 +10068,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B142" s="5">
         <v>46162.55883354167</v>
@@ -10081,7 +10078,7 @@
         <v>46223.57990805556</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -10108,13 +10105,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>255</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q142" s="5">
         <v>46220</v>
@@ -10134,7 +10131,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B143" s="9">
         <v>46162.55883898148</v>
@@ -10171,13 +10168,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -10187,7 +10184,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B144" s="5">
         <v>46162.55884618056</v>
@@ -10224,13 +10221,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10240,7 +10237,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B145" s="9">
         <v>46162.55885335648</v>
@@ -10277,13 +10274,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -10293,7 +10290,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B146" s="5">
         <v>46162.558860624995</v>
@@ -10330,13 +10327,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10346,7 +10343,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B147" s="9">
         <v>46162.558867395834</v>
@@ -10383,13 +10380,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="O147" s="10" t="s">
         <v>196</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10399,7 +10396,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B148" s="5">
         <v>46162.566146365745</v>
@@ -10436,10 +10433,10 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>196</v>
@@ -10452,7 +10449,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B149" s="9">
         <v>46162.566153101856</v>
@@ -10489,7 +10486,7 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="O149" s="10" t="s">
         <v>196</v>
@@ -10505,7 +10502,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B150" s="5">
         <v>46162.56617111111</v>
@@ -10542,10 +10539,10 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>196</v>
@@ -10558,7 +10555,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B151" s="9">
         <v>46162.56618105324</v>
@@ -10568,7 +10565,7 @@
         <v>46223.57928965278</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
@@ -10595,10 +10592,10 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="P151" s="10" t="s">
         <v>196</v>
@@ -10611,7 +10608,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B152" s="5">
         <v>46162.56618987268</v>
@@ -10648,10 +10645,10 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="P152" s="6" t="s">
         <v>196</v>
@@ -10664,7 +10661,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B153" s="9">
         <v>46162.56620271991</v>
@@ -10701,10 +10698,10 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="P153" s="10" t="s">
         <v>196</v>
@@ -10717,7 +10714,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B154" s="5">
         <v>46162.56620673611</v>
@@ -10754,10 +10751,10 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="P154" s="6" t="s">
         <v>196</v>
@@ -10770,7 +10767,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B155" s="9">
         <v>46162.558871574074</v>
@@ -10780,7 +10777,7 @@
         <v>46224.18423814815</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -10807,13 +10804,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q155" s="9">
         <v>46223</v>
@@ -10833,7 +10830,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B156" s="5">
         <v>46162.55887622685</v>
@@ -10870,13 +10867,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O156" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="P156" s="6" t="s">
         <v>376</v>
-      </c>
-      <c r="P156" s="6" t="s">
-        <v>377</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10886,7 +10883,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B157" s="9">
         <v>46162.55888300926</v>
@@ -10923,13 +10920,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O157" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="P157" s="10" t="s">
         <v>376</v>
-      </c>
-      <c r="P157" s="10" t="s">
-        <v>377</v>
       </c>
       <c r="Q157" s="10"/>
       <c r="R157" s="10"/>
@@ -10939,7 +10936,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B158" s="5">
         <v>46162.558892581015</v>
@@ -10976,13 +10973,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10992,7 +10989,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B159" s="9">
         <v>46162.55889858796</v>
@@ -11029,13 +11026,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P159" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q159" s="10"/>
       <c r="R159" s="10"/>
@@ -11045,7 +11042,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B160" s="5">
         <v>46162.558904618054</v>
@@ -11082,13 +11079,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O160" s="6" t="s">
         <v>196</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -11098,7 +11095,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B161" s="9">
         <v>46162.566379375</v>
@@ -11135,13 +11132,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O161" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="P161" s="10" t="s">
         <v>386</v>
-      </c>
-      <c r="P161" s="10" t="s">
-        <v>387</v>
       </c>
       <c r="Q161" s="10"/>
       <c r="R161" s="10"/>
@@ -11151,7 +11148,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B162" s="5">
         <v>46162.56638695602</v>
@@ -11188,10 +11185,10 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="P162" s="6" t="s">
         <v>196</v>
@@ -11204,7 +11201,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B163" s="9">
         <v>46162.56639532407</v>
@@ -11241,13 +11238,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -11257,7 +11254,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B164" s="5">
         <v>46162.56640418981</v>
@@ -11294,13 +11291,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O164" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="P164" s="6" t="s">
         <v>392</v>
-      </c>
-      <c r="P164" s="6" t="s">
-        <v>393</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11310,7 +11307,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B165" s="9">
         <v>46162.56641240741</v>
@@ -11347,13 +11344,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -11363,7 +11360,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B166" s="5">
         <v>46162.56642033564</v>
@@ -11400,13 +11397,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="Q166" s="6"/>
       <c r="R166" s="6"/>
@@ -11416,7 +11413,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B167" s="9">
         <v>46162.566427708334</v>
@@ -11453,10 +11450,10 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="P167" s="10" t="s">
         <v>196</v>
@@ -11469,7 +11466,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B168" s="5">
         <v>46162.558908946754</v>
@@ -11479,7 +11476,7 @@
         <v>46225.18524023148</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11506,13 +11503,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O168" s="6" t="s">
         <v>255</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q168" s="5">
         <v>46224</v>
@@ -11532,7 +11529,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B169" s="9">
         <v>46162.55891369213</v>
@@ -11567,13 +11564,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O169" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P169" s="10" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q169" s="10"/>
       <c r="R169" s="10"/>
@@ -11583,7 +11580,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B170" s="5">
         <v>46162.55891930556</v>
@@ -11618,13 +11615,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O170" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
@@ -11634,7 +11631,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B171" s="9">
         <v>46162.558924930556</v>
@@ -11669,13 +11666,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O171" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q171" s="10"/>
       <c r="R171" s="10"/>
@@ -11685,7 +11682,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B172" s="5">
         <v>46162.55893104167</v>
@@ -11720,13 +11717,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O172" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11736,7 +11733,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B173" s="9">
         <v>46162.55893646991</v>
@@ -11771,13 +11768,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O173" s="10" t="s">
         <v>196</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11787,7 +11784,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B174" s="5">
         <v>46162.567320891205</v>
@@ -11822,7 +11819,7 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O174" s="6" t="s">
         <v>196</v>
@@ -11838,7 +11835,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B175" s="9">
         <v>46162.567330034726</v>
@@ -11873,7 +11870,7 @@
         <v>26</v>
       </c>
       <c r="N175" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O175" s="10" t="s">
         <v>196</v>
@@ -11889,7 +11886,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B176" s="5">
         <v>46162.567337685185</v>
@@ -11924,7 +11921,7 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O176" s="6" t="s">
         <v>196</v>
@@ -11940,7 +11937,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B177" s="9">
         <v>46162.567344166666</v>
@@ -11975,7 +11972,7 @@
         <v>26</v>
       </c>
       <c r="N177" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O177" s="10" t="s">
         <v>196</v>
@@ -11991,7 +11988,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B178" s="5">
         <v>46162.56735135417</v>
@@ -12026,7 +12023,7 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O178" s="6" t="s">
         <v>196</v>
@@ -12042,7 +12039,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B179" s="9">
         <v>46162.5673590625</v>
@@ -12077,7 +12074,7 @@
         <v>26</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O179" s="10" t="s">
         <v>196</v>
@@ -12093,7 +12090,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B180" s="5">
         <v>46162.567366284726</v>
@@ -12128,7 +12125,7 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O180" s="6" t="s">
         <v>196</v>
@@ -12144,7 +12141,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B181" s="9">
         <v>46162.558941678246</v>
@@ -12154,7 +12151,7 @@
         <v>46227.200147048614</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>26</v>
@@ -12181,13 +12178,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O181" s="10" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="P181" s="10" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Q181" s="9">
         <v>46226</v>
@@ -12207,7 +12204,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B182" s="5">
         <v>46162.5589471875</v>
@@ -12242,13 +12239,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="O182" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -12258,7 +12255,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B183" s="9">
         <v>46162.55895184028</v>
@@ -12293,13 +12290,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="10" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="O183" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P183" s="10" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Q183" s="10"/>
       <c r="R183" s="10"/>
@@ -12309,7 +12306,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B184" s="5">
         <v>46162.55895655093</v>
@@ -12344,13 +12341,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="O184" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12360,7 +12357,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B185" s="9">
         <v>46162.5589959375</v>
@@ -12395,13 +12392,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="10" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="O185" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -12411,7 +12408,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B186" s="5">
         <v>46162.55900136574</v>
@@ -12446,13 +12443,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="O186" s="6" t="s">
         <v>196</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12462,7 +12459,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B187" s="9">
         <v>46162.56759152778</v>
@@ -12497,7 +12494,7 @@
         <v>26</v>
       </c>
       <c r="N187" s="10" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="O187" s="10" t="s">
         <v>196</v>
@@ -12513,7 +12510,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B188" s="5">
         <v>46162.56759846065</v>
@@ -12548,13 +12545,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="O188" s="6" t="s">
         <v>196</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12564,7 +12561,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B189" s="9">
         <v>46162.56760671297</v>
@@ -12599,7 +12596,7 @@
         <v>26</v>
       </c>
       <c r="N189" s="10" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="O189" s="10" t="s">
         <v>196</v>
@@ -12615,7 +12612,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B190" s="5">
         <v>46162.56761416666</v>
@@ -12650,7 +12647,7 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="O190" s="6" t="s">
         <v>196</v>
@@ -12666,7 +12663,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B191" s="9">
         <v>46162.56762221065</v>
@@ -12701,7 +12698,7 @@
         <v>26</v>
       </c>
       <c r="N191" s="10" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="O191" s="10" t="s">
         <v>196</v>
@@ -12717,7 +12714,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B192" s="5">
         <v>46162.56762855324</v>
@@ -12752,7 +12749,7 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="O192" s="6" t="s">
         <v>196</v>
@@ -12768,7 +12765,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B193" s="9">
         <v>46162.56763415509</v>
@@ -12803,7 +12800,7 @@
         <v>26</v>
       </c>
       <c r="N193" s="10" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="O193" s="10" t="s">
         <v>196</v>
@@ -12819,7 +12816,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B194" s="5">
         <v>46162.55900565972</v>
@@ -12829,7 +12826,7 @@
         <v>46162.663939108796</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>25</v>
@@ -12853,7 +12850,7 @@
         <v>26</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="P194" s="6" t="s">
         <v>26</v>
@@ -12866,7 +12863,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B195" s="9">
         <v>46162.55900940972</v>
@@ -12876,16 +12873,16 @@
         <v>46228.19288883102</v>
       </c>
       <c r="E195" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="F195" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G195" s="10" t="s">
         <v>436</v>
       </c>
-      <c r="F195" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G195" s="10" t="s">
+      <c r="H195" s="10" t="s">
         <v>437</v>
-      </c>
-      <c r="H195" s="10" t="s">
-        <v>438</v>
       </c>
       <c r="I195" s="9">
         <v>46227</v>
@@ -12903,13 +12900,13 @@
         <v>26</v>
       </c>
       <c r="N195" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O195" s="10" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P195" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="Q195" s="9">
         <v>46227</v>
@@ -12929,7 +12926,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B196" s="5">
         <v>46162.559015023144</v>
@@ -12945,10 +12942,10 @@
         <v>26</v>
       </c>
       <c r="G196" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="H196" s="6" t="s">
         <v>437</v>
-      </c>
-      <c r="H196" s="6" t="s">
-        <v>438</v>
       </c>
       <c r="I196" s="6"/>
       <c r="J196" s="5">
@@ -12964,13 +12961,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O196" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -12980,7 +12977,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B197" s="9">
         <v>46162.55901939815</v>
@@ -12996,10 +12993,10 @@
         <v>26</v>
       </c>
       <c r="G197" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="H197" s="10" t="s">
         <v>437</v>
-      </c>
-      <c r="H197" s="10" t="s">
-        <v>438</v>
       </c>
       <c r="I197" s="10"/>
       <c r="J197" s="9">
@@ -13015,13 +13012,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="10" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O197" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P197" s="10" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q197" s="10"/>
       <c r="R197" s="10"/>
@@ -13031,7 +13028,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B198" s="5">
         <v>46162.55902388888</v>
@@ -13047,10 +13044,10 @@
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="H198" s="6" t="s">
         <v>437</v>
-      </c>
-      <c r="H198" s="6" t="s">
-        <v>438</v>
       </c>
       <c r="I198" s="6"/>
       <c r="J198" s="5">
@@ -13066,13 +13063,13 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O198" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q198" s="6"/>
       <c r="R198" s="6"/>
@@ -13082,7 +13079,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B199" s="9">
         <v>46162.559028090276</v>
@@ -13098,10 +13095,10 @@
         <v>26</v>
       </c>
       <c r="G199" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="H199" s="10" t="s">
         <v>437</v>
-      </c>
-      <c r="H199" s="10" t="s">
-        <v>438</v>
       </c>
       <c r="I199" s="10"/>
       <c r="J199" s="9">
@@ -13117,13 +13114,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="10" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O199" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P199" s="10" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q199" s="10"/>
       <c r="R199" s="10"/>
@@ -13133,7 +13130,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B200" s="5">
         <v>46162.559032060184</v>
@@ -13149,10 +13146,10 @@
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="H200" s="6" t="s">
         <v>437</v>
-      </c>
-      <c r="H200" s="6" t="s">
-        <v>438</v>
       </c>
       <c r="I200" s="6"/>
       <c r="J200" s="5">
@@ -13168,13 +13165,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O200" s="6" t="s">
         <v>196</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -13184,7 +13181,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B201" s="9">
         <v>46162.56847083333</v>
@@ -13200,10 +13197,10 @@
         <v>26</v>
       </c>
       <c r="G201" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="H201" s="10" t="s">
         <v>437</v>
-      </c>
-      <c r="H201" s="10" t="s">
-        <v>438</v>
       </c>
       <c r="I201" s="10"/>
       <c r="J201" s="9">
@@ -13219,13 +13216,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="10" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O201" s="10" t="s">
         <v>196</v>
       </c>
       <c r="P201" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="Q201" s="10"/>
       <c r="R201" s="10"/>
@@ -13235,7 +13232,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B202" s="5">
         <v>46162.5684778588</v>
@@ -13251,10 +13248,10 @@
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="H202" s="6" t="s">
         <v>437</v>
-      </c>
-      <c r="H202" s="6" t="s">
-        <v>438</v>
       </c>
       <c r="I202" s="6"/>
       <c r="J202" s="5">
@@ -13270,7 +13267,7 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O202" s="6" t="s">
         <v>196</v>
@@ -13286,7 +13283,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B203" s="9">
         <v>46162.56848583333</v>
@@ -13302,10 +13299,10 @@
         <v>26</v>
       </c>
       <c r="G203" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="H203" s="10" t="s">
         <v>437</v>
-      </c>
-      <c r="H203" s="10" t="s">
-        <v>438</v>
       </c>
       <c r="I203" s="10"/>
       <c r="J203" s="9">
@@ -13321,7 +13318,7 @@
         <v>26</v>
       </c>
       <c r="N203" s="10" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O203" s="10" t="s">
         <v>196</v>
@@ -13337,7 +13334,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B204" s="5">
         <v>46162.56849315972</v>
@@ -13353,10 +13350,10 @@
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="H204" s="6" t="s">
         <v>437</v>
-      </c>
-      <c r="H204" s="6" t="s">
-        <v>438</v>
       </c>
       <c r="I204" s="6"/>
       <c r="J204" s="5">
@@ -13372,7 +13369,7 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O204" s="6" t="s">
         <v>196</v>
@@ -13388,7 +13385,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B205" s="9">
         <v>46162.568499120374</v>
@@ -13404,10 +13401,10 @@
         <v>26</v>
       </c>
       <c r="G205" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="H205" s="10" t="s">
         <v>437</v>
-      </c>
-      <c r="H205" s="10" t="s">
-        <v>438</v>
       </c>
       <c r="I205" s="10"/>
       <c r="J205" s="9">
@@ -13423,7 +13420,7 @@
         <v>26</v>
       </c>
       <c r="N205" s="10" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O205" s="10" t="s">
         <v>196</v>
@@ -13439,7 +13436,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B206" s="5">
         <v>46162.568507013886</v>
@@ -13455,10 +13452,10 @@
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="H206" s="6" t="s">
         <v>437</v>
-      </c>
-      <c r="H206" s="6" t="s">
-        <v>438</v>
       </c>
       <c r="I206" s="6"/>
       <c r="J206" s="5">
@@ -13474,7 +13471,7 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O206" s="6" t="s">
         <v>196</v>
@@ -13490,7 +13487,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B207" s="9">
         <v>46162.56851576389</v>
@@ -13506,10 +13503,10 @@
         <v>26</v>
       </c>
       <c r="G207" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="H207" s="10" t="s">
         <v>437</v>
-      </c>
-      <c r="H207" s="10" t="s">
-        <v>438</v>
       </c>
       <c r="I207" s="10"/>
       <c r="J207" s="9">
@@ -13525,7 +13522,7 @@
         <v>26</v>
       </c>
       <c r="N207" s="10" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O207" s="10" t="s">
         <v>196</v>
@@ -13541,7 +13538,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B208" s="5">
         <v>46162.559035983795</v>
@@ -13551,7 +13548,7 @@
         <v>46231.180388402776</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
@@ -13578,13 +13575,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O208" s="6" t="s">
         <v>255</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="Q208" s="5">
         <v>46230</v>
@@ -13604,7 +13601,7 @@
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B209" s="9">
         <v>46162.559040057866</v>
@@ -13639,13 +13636,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="10" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="O209" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P209" s="10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Q209" s="10"/>
       <c r="R209" s="10"/>
@@ -13655,7 +13652,7 @@
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B210" s="5">
         <v>46162.559044305555</v>
@@ -13690,13 +13687,13 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="O210" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P210" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Q210" s="6"/>
       <c r="R210" s="6"/>
@@ -13706,7 +13703,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B211" s="9">
         <v>46162.55904842593</v>
@@ -13741,13 +13738,13 @@
         <v>26</v>
       </c>
       <c r="N211" s="10" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="O211" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P211" s="10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Q211" s="10"/>
       <c r="R211" s="10"/>
@@ -13757,7 +13754,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B212" s="5">
         <v>46162.55905241898</v>
@@ -13792,13 +13789,13 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="O212" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P212" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Q212" s="6"/>
       <c r="R212" s="6"/>
@@ -13808,7 +13805,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B213" s="9">
         <v>46162.55905643519</v>
@@ -13843,13 +13840,13 @@
         <v>26</v>
       </c>
       <c r="N213" s="10" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="O213" s="10" t="s">
         <v>196</v>
       </c>
       <c r="P213" s="10" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="Q213" s="10"/>
       <c r="R213" s="10"/>
@@ -13859,7 +13856,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B214" s="5">
         <v>46162.568794328705</v>
@@ -13894,7 +13891,7 @@
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="O214" s="6" t="s">
         <v>196</v>
@@ -13910,7 +13907,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B215" s="9">
         <v>46162.56880138889</v>
@@ -13945,7 +13942,7 @@
         <v>26</v>
       </c>
       <c r="N215" s="10" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="O215" s="10" t="s">
         <v>196</v>
@@ -13961,7 +13958,7 @@
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B216" s="5">
         <v>46162.56880807871</v>
@@ -13996,13 +13993,13 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="O216" s="6" t="s">
         <v>196</v>
       </c>
       <c r="P216" s="6" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Q216" s="6"/>
       <c r="R216" s="6"/>
@@ -14012,7 +14009,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B217" s="9">
         <v>46162.56881548611</v>
@@ -14047,7 +14044,7 @@
         <v>26</v>
       </c>
       <c r="N217" s="10" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="O217" s="10" t="s">
         <v>196</v>
@@ -14063,7 +14060,7 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B218" s="5">
         <v>46162.56882248842</v>
@@ -14098,7 +14095,7 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="O218" s="6" t="s">
         <v>196</v>
@@ -14114,7 +14111,7 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B219" s="9">
         <v>46162.56882971065</v>
@@ -14149,7 +14146,7 @@
         <v>26</v>
       </c>
       <c r="N219" s="10" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="O219" s="10" t="s">
         <v>196</v>
@@ -14165,7 +14162,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B220" s="5">
         <v>46162.56883761574</v>
@@ -14200,7 +14197,7 @@
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="O220" s="6" t="s">
         <v>196</v>
@@ -14216,7 +14213,7 @@
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B221" s="9">
         <v>46162.559060671294</v>
@@ -14226,7 +14223,7 @@
         <v>46232.179640358794</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
@@ -14253,13 +14250,13 @@
         <v>26</v>
       </c>
       <c r="N221" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O221" s="10" t="s">
         <v>274</v>
       </c>
       <c r="P221" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="Q221" s="9">
         <v>46231</v>
@@ -14279,7 +14276,7 @@
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B222" s="5">
         <v>46162.55906472223</v>
@@ -14314,13 +14311,13 @@
         <v>26</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="O222" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P222" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="Q222" s="6"/>
       <c r="R222" s="6"/>
@@ -14330,7 +14327,7 @@
     </row>
     <row r="223" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" s="8" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B223" s="9">
         <v>46162.55907236111</v>
@@ -14365,13 +14362,13 @@
         <v>26</v>
       </c>
       <c r="N223" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="O223" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P223" s="10" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="Q223" s="10"/>
       <c r="R223" s="10"/>
@@ -14381,7 +14378,7 @@
     </row>
     <row r="224" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B224" s="5">
         <v>46162.55907862268</v>
@@ -14416,13 +14413,13 @@
         <v>26</v>
       </c>
       <c r="N224" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="O224" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P224" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q224" s="6"/>
       <c r="R224" s="6"/>
@@ -14432,7 +14429,7 @@
     </row>
     <row r="225" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" s="8" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B225" s="9">
         <v>46162.55908304398</v>
@@ -14467,13 +14464,13 @@
         <v>26</v>
       </c>
       <c r="N225" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="O225" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P225" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q225" s="10"/>
       <c r="R225" s="10"/>
@@ -14483,7 +14480,7 @@
     </row>
     <row r="226" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B226" s="5">
         <v>46162.55908719907</v>
@@ -14518,13 +14515,13 @@
         <v>26</v>
       </c>
       <c r="N226" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="O226" s="6" t="s">
         <v>196</v>
       </c>
       <c r="P226" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Q226" s="6"/>
       <c r="R226" s="6"/>
@@ -14534,7 +14531,7 @@
     </row>
     <row r="227" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" s="8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B227" s="9">
         <v>46162.56901232639</v>
@@ -14569,7 +14566,7 @@
         <v>26</v>
       </c>
       <c r="N227" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="O227" s="10" t="s">
         <v>196</v>
@@ -14585,7 +14582,7 @@
     </row>
     <row r="228" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B228" s="5">
         <v>46162.569018888884</v>
@@ -14620,7 +14617,7 @@
         <v>26</v>
       </c>
       <c r="N228" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="O228" s="6" t="s">
         <v>196</v>
@@ -14636,7 +14633,7 @@
     </row>
     <row r="229" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" s="8" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B229" s="9">
         <v>46162.56902688657</v>
@@ -14646,7 +14643,7 @@
         <v>46231.16824366898</v>
       </c>
       <c r="E229" s="10" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F229" s="10" t="s">
         <v>26</v>
@@ -14671,7 +14668,7 @@
         <v>26</v>
       </c>
       <c r="N229" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="O229" s="10" t="s">
         <v>196</v>
@@ -14687,7 +14684,7 @@
     </row>
     <row r="230" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B230" s="5">
         <v>46162.56903291667</v>
@@ -14722,7 +14719,7 @@
         <v>26</v>
       </c>
       <c r="N230" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="O230" s="6" t="s">
         <v>196</v>
@@ -14738,7 +14735,7 @@
     </row>
     <row r="231" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A231" s="8" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B231" s="9">
         <v>46162.56903989583</v>
@@ -14773,7 +14770,7 @@
         <v>26</v>
       </c>
       <c r="N231" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="O231" s="10" t="s">
         <v>196</v>
@@ -14789,7 +14786,7 @@
     </row>
     <row r="232" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B232" s="5">
         <v>46162.56904635417</v>
@@ -14824,7 +14821,7 @@
         <v>26</v>
       </c>
       <c r="N232" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="O232" s="6" t="s">
         <v>196</v>
@@ -14840,7 +14837,7 @@
     </row>
     <row r="233" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B233" s="9">
         <v>46162.56905347222</v>
@@ -14875,7 +14872,7 @@
         <v>26</v>
       </c>
       <c r="N233" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="O233" s="10" t="s">
         <v>196</v>
@@ -14891,17 +14888,17 @@
     </row>
     <row r="234" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B234" s="5">
         <v>46162.559091284726</v>
       </c>
       <c r="C234" s="6"/>
       <c r="D234" s="5">
-        <v>46232.168207395836</v>
+        <v>46233.179258923614</v>
       </c>
       <c r="E234" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F234" s="6" t="s">
         <v>26</v>
@@ -14928,13 +14925,13 @@
         <v>26</v>
       </c>
       <c r="N234" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O234" s="6" t="s">
         <v>255</v>
       </c>
       <c r="P234" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="Q234" s="5">
         <v>46232</v>
@@ -14942,8 +14939,8 @@
       <c r="R234" s="5">
         <v>46232</v>
       </c>
-      <c r="S234" s="12" t="s">
-        <v>307</v>
+      <c r="S234" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T234" s="6">
         <v>0</v>
@@ -14954,7 +14951,7 @@
     </row>
     <row r="235" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A235" s="8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B235" s="9">
         <v>46162.55909613426</v>
@@ -14991,13 +14988,13 @@
         <v>26</v>
       </c>
       <c r="N235" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O235" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P235" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Q235" s="10"/>
       <c r="R235" s="10"/>
@@ -15007,7 +15004,7 @@
     </row>
     <row r="236" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B236" s="5">
         <v>46162.55910012731</v>
@@ -15044,13 +15041,13 @@
         <v>26</v>
       </c>
       <c r="N236" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O236" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P236" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Q236" s="6"/>
       <c r="R236" s="6"/>
@@ -15060,7 +15057,7 @@
     </row>
     <row r="237" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A237" s="8" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B237" s="9">
         <v>46162.55910407407</v>
@@ -15097,13 +15094,13 @@
         <v>26</v>
       </c>
       <c r="N237" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O237" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P237" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Q237" s="10"/>
       <c r="R237" s="10"/>
@@ -15113,7 +15110,7 @@
     </row>
     <row r="238" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B238" s="5">
         <v>46162.559108125</v>
@@ -15150,13 +15147,13 @@
         <v>26</v>
       </c>
       <c r="N238" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O238" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P238" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Q238" s="6"/>
       <c r="R238" s="6"/>
@@ -15166,7 +15163,7 @@
     </row>
     <row r="239" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A239" s="8" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B239" s="9">
         <v>46162.55914409722</v>
@@ -15203,13 +15200,13 @@
         <v>26</v>
       </c>
       <c r="N239" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O239" s="10" t="s">
         <v>196</v>
       </c>
       <c r="P239" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Q239" s="10"/>
       <c r="R239" s="10"/>
@@ -15219,7 +15216,7 @@
     </row>
     <row r="240" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B240" s="5">
         <v>46162.56958915509</v>
@@ -15256,7 +15253,7 @@
         <v>26</v>
       </c>
       <c r="N240" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O240" s="6" t="s">
         <v>196</v>
@@ -15272,7 +15269,7 @@
     </row>
     <row r="241" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A241" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B241" s="9">
         <v>46162.56959587963</v>
@@ -15309,7 +15306,7 @@
         <v>26</v>
       </c>
       <c r="N241" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O241" s="10" t="s">
         <v>196</v>
@@ -15325,7 +15322,7 @@
     </row>
     <row r="242" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B242" s="5">
         <v>46162.56960513889</v>
@@ -15362,10 +15359,10 @@
         <v>26</v>
       </c>
       <c r="N242" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O242" s="6" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P242" s="6" t="s">
         <v>26</v>
@@ -15378,7 +15375,7 @@
     </row>
     <row r="243" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A243" s="8" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B243" s="9">
         <v>46162.569612060186</v>
@@ -15415,7 +15412,7 @@
         <v>26</v>
       </c>
       <c r="N243" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O243" s="10" t="s">
         <v>196</v>
@@ -15431,7 +15428,7 @@
     </row>
     <row r="244" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B244" s="5">
         <v>46162.569619999995</v>
@@ -15468,7 +15465,7 @@
         <v>26</v>
       </c>
       <c r="N244" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O244" s="6" t="s">
         <v>196</v>
@@ -15484,7 +15481,7 @@
     </row>
     <row r="245" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A245" s="8" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B245" s="9">
         <v>46162.569627812496</v>
@@ -15521,7 +15518,7 @@
         <v>26</v>
       </c>
       <c r="N245" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O245" s="10" t="s">
         <v>196</v>
@@ -15537,7 +15534,7 @@
     </row>
     <row r="246" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B246" s="5">
         <v>46162.569634513886</v>
@@ -15574,7 +15571,7 @@
         <v>26</v>
       </c>
       <c r="N246" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O246" s="6" t="s">
         <v>196</v>
@@ -15590,7 +15587,7 @@
     </row>
     <row r="247" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A247" s="8" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B247" s="9">
         <v>46162.5591494213</v>
@@ -15600,7 +15597,7 @@
         <v>46162.664148020835</v>
       </c>
       <c r="E247" s="10" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F247" s="10" t="s">
         <v>25</v>
@@ -15624,7 +15621,7 @@
         <v>26</v>
       </c>
       <c r="O247" s="10" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="P247" s="10" t="s">
         <v>26</v>
@@ -15637,7 +15634,7 @@
     </row>
     <row r="248" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B248" s="5">
         <v>46162.559152800924</v>
@@ -15647,16 +15644,16 @@
         <v>46162.676061377315</v>
       </c>
       <c r="E248" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="F248" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G248" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="F248" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G248" s="6" t="s">
+      <c r="H248" s="6" t="s">
         <v>508</v>
-      </c>
-      <c r="H248" s="6" t="s">
-        <v>509</v>
       </c>
       <c r="I248" s="5">
         <v>46233</v>
@@ -15674,13 +15671,13 @@
         <v>26</v>
       </c>
       <c r="N248" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="O248" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="P248" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="Q248" s="5">
         <v>46233</v>
@@ -15700,7 +15697,7 @@
     </row>
     <row r="249" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A249" s="8" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B249" s="9">
         <v>46162.55915726852</v>
@@ -15710,7 +15707,7 @@
         <v>46197.69418131944</v>
       </c>
       <c r="E249" s="10" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F249" s="10" t="s">
         <v>26</v>
@@ -15737,13 +15734,13 @@
         <v>26</v>
       </c>
       <c r="N249" s="10" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="O249" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="P249" s="10" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="Q249" s="9">
         <v>46233</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2845" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2845" uniqueCount="512">
   <si>
     <t xml:space="preserve">50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT 4324 4325 </t>
   </si>
@@ -1603,6 +1603,9 @@
   </si>
   <si>
     <t>nicolas.tello@zitron.com</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1214969504634475</t>
@@ -15641,7 +15644,7 @@
       </c>
       <c r="C248" s="6"/>
       <c r="D248" s="5">
-        <v>46162.676061377315</v>
+        <v>46234.18541615741</v>
       </c>
       <c r="E248" s="6" t="s">
         <v>506</v>
@@ -15685,8 +15688,8 @@
       <c r="R248" s="5">
         <v>46241</v>
       </c>
-      <c r="S248" s="7" t="s">
-        <v>55</v>
+      <c r="S248" s="12" t="s">
+        <v>509</v>
       </c>
       <c r="T248" s="6">
         <v>0</v>
@@ -15697,17 +15700,17 @@
     </row>
     <row r="249" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A249" s="8" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B249" s="9">
         <v>46162.55915726852</v>
       </c>
       <c r="C249" s="10"/>
       <c r="D249" s="9">
-        <v>46197.69418131944</v>
+        <v>46234.18541615741</v>
       </c>
       <c r="E249" s="10" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F249" s="10" t="s">
         <v>26</v>
@@ -15748,8 +15751,8 @@
       <c r="R249" s="9">
         <v>46241</v>
       </c>
-      <c r="S249" s="7" t="s">
-        <v>55</v>
+      <c r="S249" s="12" t="s">
+        <v>509</v>
       </c>
       <c r="T249" s="10">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -8704,7 +8704,7 @@
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46225.185239872684</v>
+        <v>46237.54090622685</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>311</v>
@@ -8754,8 +8754,8 @@
       <c r="T116" s="6">
         <v>0</v>
       </c>
-      <c r="U116" s="11" t="s">
-        <v>102</v>
+      <c r="U116" s="12" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
@@ -9403,7 +9403,7 @@
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46223.5799087037</v>
+        <v>46237.54094651621</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>328</v>
@@ -9453,8 +9453,8 @@
       <c r="T129" s="10">
         <v>0</v>
       </c>
-      <c r="U129" s="11" t="s">
-        <v>102</v>
+      <c r="U129" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -15644,7 +15644,7 @@
       </c>
       <c r="C248" s="6"/>
       <c r="D248" s="5">
-        <v>46234.18541615741</v>
+        <v>46241.16861545139</v>
       </c>
       <c r="E248" s="6" t="s">
         <v>506</v>
@@ -15707,7 +15707,7 @@
       </c>
       <c r="C249" s="10"/>
       <c r="D249" s="9">
-        <v>46234.18541615741</v>
+        <v>46241.16861770833</v>
       </c>
       <c r="E249" s="10" t="s">
         <v>511</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2845" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2845" uniqueCount="511">
   <si>
     <t xml:space="preserve">50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT 4324 4325 </t>
   </si>
@@ -1603,9 +1603,6 @@
   </si>
   <si>
     <t>nicolas.tello@zitron.com</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214969504634475</t>
@@ -15644,7 +15641,7 @@
       </c>
       <c r="C248" s="6"/>
       <c r="D248" s="5">
-        <v>46241.16861545139</v>
+        <v>46242.19780203704</v>
       </c>
       <c r="E248" s="6" t="s">
         <v>506</v>
@@ -15688,8 +15685,8 @@
       <c r="R248" s="5">
         <v>46241</v>
       </c>
-      <c r="S248" s="12" t="s">
-        <v>509</v>
+      <c r="S248" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T248" s="6">
         <v>0</v>
@@ -15700,17 +15697,17 @@
     </row>
     <row r="249" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A249" s="8" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B249" s="9">
         <v>46162.55915726852</v>
       </c>
       <c r="C249" s="10"/>
       <c r="D249" s="9">
-        <v>46241.16861770833</v>
+        <v>46242.197801365735</v>
       </c>
       <c r="E249" s="10" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F249" s="10" t="s">
         <v>26</v>
@@ -15751,8 +15748,8 @@
       <c r="R249" s="9">
         <v>46241</v>
       </c>
-      <c r="S249" s="12" t="s">
-        <v>509</v>
+      <c r="S249" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T249" s="10">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -200,9 +200,6 @@
     <t>Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
     <t>1214969379007271</t>
   </si>
   <si>
@@ -358,6 +355,9 @@
   </si>
   <si>
     <t>rodete OT 4324 4325,Materiales corte Laser OT 4324 4325,Alabe OT 4324 4325,Motor OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1214969466331129</t>
@@ -2615,9 +2615,11 @@
       <c r="B10" s="5">
         <v>46162.55816482639</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="5">
+        <v>46247.666494467594</v>
+      </c>
       <c r="D10" s="5">
-        <v>46197.69419108796</v>
+        <v>46247.66651185185</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2652,14 +2654,16 @@
       <c r="Q10" s="6"/>
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="12" t="s">
-        <v>48</v>
+      <c r="T10" s="6">
+        <v>1</v>
+      </c>
+      <c r="U10" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B11" s="9">
         <v>46162.55824909722</v>
@@ -2671,16 +2675,16 @@
         <v>46197.69418131944</v>
       </c>
       <c r="E11" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="10" t="s">
+      <c r="H11" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>52</v>
       </c>
       <c r="I11" s="9">
         <v>46149</v>
@@ -2692,7 +2696,7 @@
         <v>26</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M11" s="10" t="s">
         <v>26</v>
@@ -2704,7 +2708,7 @@
         <v>40</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q11" s="9">
         <v>46149</v>
@@ -2713,7 +2717,7 @@
         <v>46150</v>
       </c>
       <c r="S11" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T11" s="10">
         <v>1</v>
@@ -2724,7 +2728,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B12" s="5">
         <v>46162.55825447917</v>
@@ -2736,16 +2740,16 @@
         <v>46197.69418155093</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="I12" s="5">
         <v>46149</v>
@@ -2757,7 +2761,7 @@
         <v>26</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>26</v>
@@ -2769,7 +2773,7 @@
         <v>40</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q12" s="5">
         <v>46149</v>
@@ -2778,7 +2782,7 @@
         <v>46150</v>
       </c>
       <c r="S12" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T12" s="6">
         <v>1</v>
@@ -2789,7 +2793,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13" s="9">
         <v>46162.55825988426</v>
@@ -2801,16 +2805,16 @@
         <v>46197.6941815162</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>52</v>
       </c>
       <c r="I13" s="9">
         <v>46149</v>
@@ -2822,7 +2826,7 @@
         <v>26</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M13" s="10" t="s">
         <v>26</v>
@@ -2834,7 +2838,7 @@
         <v>40</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q13" s="9">
         <v>46149</v>
@@ -2843,7 +2847,7 @@
         <v>46157</v>
       </c>
       <c r="S13" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T13" s="10">
         <v>1</v>
@@ -2854,7 +2858,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B14" s="5">
         <v>46162.55816920139</v>
@@ -2866,7 +2870,7 @@
         <v>46209.56174483796</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>25</v>
@@ -2890,7 +2894,7 @@
         <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>26</v>
@@ -2907,7 +2911,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B15" s="9">
         <v>46162.55827298611</v>
@@ -2919,16 +2923,16 @@
         <v>46198.683943310185</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>52</v>
       </c>
       <c r="I15" s="9">
         <v>46153</v>
@@ -2946,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Q15" s="9">
         <v>46153</v>
@@ -2961,7 +2965,7 @@
         <v>46154</v>
       </c>
       <c r="S15" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T15" s="10">
         <v>1</v>
@@ -2972,7 +2976,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B16" s="5">
         <v>46162.55827819444</v>
@@ -2984,16 +2988,16 @@
         <v>46209.56277344907</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="I16" s="5">
         <v>46153</v>
@@ -3011,13 +3015,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q16" s="5">
         <v>46153</v>
@@ -3026,7 +3030,7 @@
         <v>46154</v>
       </c>
       <c r="S16" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T16" s="6">
         <v>1</v>
@@ -3037,7 +3041,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B17" s="9">
         <v>46162.55828362268</v>
@@ -3049,16 +3053,16 @@
         <v>46223.578627152776</v>
       </c>
       <c r="E17" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="10" t="s">
+      <c r="H17" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I17" s="9">
         <v>46153</v>
@@ -3076,13 +3080,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q17" s="9">
         <v>46153</v>
@@ -3091,7 +3095,7 @@
         <v>46154</v>
       </c>
       <c r="S17" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T17" s="10">
         <v>1</v>
@@ -3102,7 +3106,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B18" s="5">
         <v>46162.55828883102</v>
@@ -3114,16 +3118,16 @@
         <v>46223.578623622685</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I18" s="5">
         <v>46188</v>
@@ -3141,13 +3145,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O18" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P18" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="Q18" s="5">
         <v>46188</v>
@@ -3167,7 +3171,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B19" s="9">
         <v>46162.55829380787</v>
@@ -3179,16 +3183,16 @@
         <v>46223.578619988424</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H19" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I19" s="9">
         <v>46188</v>
@@ -3206,13 +3210,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q19" s="9">
         <v>46188</v>
@@ -3232,7 +3236,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B20" s="5">
         <v>46162.55829782407</v>
@@ -3244,16 +3248,16 @@
         <v>46223.578616377315</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I20" s="5">
         <v>46188</v>
@@ -3271,13 +3275,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q20" s="5">
         <v>46188</v>
@@ -3297,7 +3301,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B21" s="9">
         <v>46162.558301446756</v>
@@ -3309,16 +3313,16 @@
         <v>46223.57861149305</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H21" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I21" s="9">
         <v>46188</v>
@@ -3336,13 +3340,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q21" s="9">
         <v>46188</v>
@@ -3362,7 +3366,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B22" s="5">
         <v>46162.55817344907</v>
@@ -3372,7 +3376,7 @@
         <v>46209.81432671296</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -3396,7 +3400,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -3406,7 +3410,7 @@
       <c r="S22" s="6"/>
       <c r="T22" s="6"/>
       <c r="U22" s="12" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -3450,13 +3454,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>98</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q23" s="9">
         <v>46155</v>
@@ -3465,7 +3469,7 @@
         <v>46160</v>
       </c>
       <c r="S23" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T23" s="10">
         <v>1</v>
@@ -3518,7 +3522,7 @@
         <v>95</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>101</v>
@@ -3526,7 +3530,7 @@
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
@@ -3587,7 +3591,7 @@
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
@@ -3637,13 +3641,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>108</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q26" s="5">
         <v>46155</v>
@@ -3652,7 +3656,7 @@
         <v>46160</v>
       </c>
       <c r="S26" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T26" s="6">
         <v>1</v>
@@ -3705,7 +3709,7 @@
         <v>107</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>111</v>
@@ -3713,7 +3717,7 @@
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
@@ -3774,7 +3778,7 @@
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
@@ -3824,13 +3828,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>117</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q29" s="9">
         <v>46155</v>
@@ -3892,7 +3896,7 @@
         <v>116</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>120</v>
@@ -3900,7 +3904,7 @@
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
@@ -3961,7 +3965,7 @@
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
@@ -4022,7 +4026,7 @@
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
@@ -4072,13 +4076,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O33" s="10" t="s">
         <v>131</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q33" s="9">
         <v>46190</v>
@@ -4140,7 +4144,7 @@
         <v>128</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>134</v>
@@ -4148,7 +4152,7 @@
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
@@ -4209,7 +4213,7 @@
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
       <c r="S35" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
@@ -4259,7 +4263,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>140</v>
@@ -4297,7 +4301,7 @@
         <v>46209.81440909722</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
@@ -4327,7 +4331,7 @@
         <v>139</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>142</v>
@@ -4382,7 +4386,7 @@
         <v>139</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>145</v>
@@ -4434,7 +4438,7 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>150</v>
@@ -4472,7 +4476,7 @@
         <v>46209.612079687504</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
@@ -4502,7 +4506,7 @@
         <v>147</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>152</v>
@@ -4557,7 +4561,7 @@
         <v>147</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>155</v>
@@ -4664,7 +4668,7 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>162</v>
@@ -4702,7 +4706,7 @@
         <v>46209.814638090276</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
@@ -4732,7 +4736,7 @@
         <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>164</v>
@@ -4787,7 +4791,7 @@
         <v>161</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>167</v>
@@ -4895,7 +4899,7 @@
         <v>169</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>175</v>
@@ -4995,7 +4999,7 @@
         <v>46198.793379675924</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
@@ -8441,7 +8445,7 @@
         <v>46161</v>
       </c>
       <c r="S111" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T111" s="10">
         <v>1</v>
@@ -8506,7 +8510,7 @@
         <v>46161</v>
       </c>
       <c r="S112" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T112" s="6">
         <v>1</v>
@@ -8710,10 +8714,10 @@
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H116" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I116" s="5">
         <v>46218</v>
@@ -8752,7 +8756,7 @@
         <v>0</v>
       </c>
       <c r="U116" s="12" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
@@ -8773,10 +8777,10 @@
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H117" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H117" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I117" s="9">
         <v>46218</v>
@@ -8826,10 +8830,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H118" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I118" s="5">
         <v>46218</v>
@@ -8879,10 +8883,10 @@
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H119" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H119" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I119" s="9">
         <v>46218</v>
@@ -8932,10 +8936,10 @@
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H120" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I120" s="5">
         <v>46218</v>
@@ -8985,10 +8989,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H121" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H121" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I121" s="9">
         <v>46218</v>
@@ -9038,10 +9042,10 @@
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H122" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I122" s="5">
         <v>46218</v>
@@ -9091,10 +9095,10 @@
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H123" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H123" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I123" s="9">
         <v>46218</v>
@@ -9144,10 +9148,10 @@
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H124" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I124" s="5">
         <v>46218</v>
@@ -9197,10 +9201,10 @@
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H125" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H125" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I125" s="9">
         <v>46218</v>
@@ -9250,10 +9254,10 @@
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H126" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I126" s="5">
         <v>46218</v>
@@ -9303,10 +9307,10 @@
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H127" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H127" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I127" s="9">
         <v>46218</v>
@@ -9356,10 +9360,10 @@
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H128" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I128" s="5">
         <v>46218</v>
@@ -9409,10 +9413,10 @@
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H129" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H129" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I129" s="9">
         <v>46219</v>
@@ -9472,10 +9476,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H130" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -9523,10 +9527,10 @@
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H131" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H131" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I131" s="10"/>
       <c r="J131" s="9">
@@ -9574,10 +9578,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H132" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9625,10 +9629,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H133" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H133" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I133" s="10"/>
       <c r="J133" s="9">
@@ -9676,10 +9680,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H134" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9727,10 +9731,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H135" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H135" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I135" s="10"/>
       <c r="J135" s="9">
@@ -9778,10 +9782,10 @@
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H136" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9829,10 +9833,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H137" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H137" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I137" s="10"/>
       <c r="J137" s="9">
@@ -9880,10 +9884,10 @@
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H138" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9931,10 +9935,10 @@
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H139" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H139" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I139" s="10"/>
       <c r="J139" s="9">
@@ -9982,10 +9986,10 @@
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H140" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I140" s="6"/>
       <c r="J140" s="5">
@@ -10033,10 +10037,10 @@
         <v>26</v>
       </c>
       <c r="G141" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H141" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H141" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I141" s="10"/>
       <c r="J141" s="9">
@@ -10084,10 +10088,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H142" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I142" s="5">
         <v>46220</v>
@@ -10147,10 +10151,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H143" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H143" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I143" s="9">
         <v>46220</v>
@@ -10200,10 +10204,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H144" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I144" s="5">
         <v>46220</v>
@@ -10253,10 +10257,10 @@
         <v>26</v>
       </c>
       <c r="G145" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H145" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H145" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I145" s="9">
         <v>46220</v>
@@ -10306,10 +10310,10 @@
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H146" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I146" s="5">
         <v>46220</v>
@@ -10359,10 +10363,10 @@
         <v>26</v>
       </c>
       <c r="G147" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H147" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H147" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I147" s="9">
         <v>46220</v>
@@ -10412,10 +10416,10 @@
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H148" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I148" s="5">
         <v>46220</v>
@@ -10465,10 +10469,10 @@
         <v>26</v>
       </c>
       <c r="G149" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H149" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H149" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I149" s="9">
         <v>46220</v>
@@ -10518,10 +10522,10 @@
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H150" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H150" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I150" s="5">
         <v>46220</v>
@@ -10571,10 +10575,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H151" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H151" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I151" s="9">
         <v>46220</v>
@@ -10624,10 +10628,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H152" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H152" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I152" s="5">
         <v>46220</v>
@@ -10677,10 +10681,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H153" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H153" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I153" s="9">
         <v>46220</v>
@@ -10730,10 +10734,10 @@
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H154" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H154" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I154" s="5">
         <v>46220</v>
@@ -10783,10 +10787,10 @@
         <v>26</v>
       </c>
       <c r="G155" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H155" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H155" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I155" s="9">
         <v>46223</v>
@@ -10846,10 +10850,10 @@
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H156" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H156" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I156" s="5">
         <v>46223</v>
@@ -10899,10 +10903,10 @@
         <v>26</v>
       </c>
       <c r="G157" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H157" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H157" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I157" s="9">
         <v>46223</v>
@@ -10952,10 +10956,10 @@
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H158" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H158" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I158" s="5">
         <v>46223</v>
@@ -11005,10 +11009,10 @@
         <v>26</v>
       </c>
       <c r="G159" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H159" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H159" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I159" s="9">
         <v>46223</v>
@@ -11058,10 +11062,10 @@
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H160" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H160" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I160" s="5">
         <v>46223</v>
@@ -11111,10 +11115,10 @@
         <v>26</v>
       </c>
       <c r="G161" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H161" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H161" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I161" s="9">
         <v>46223</v>
@@ -11164,10 +11168,10 @@
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H162" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H162" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I162" s="5">
         <v>46223</v>
@@ -11217,10 +11221,10 @@
         <v>26</v>
       </c>
       <c r="G163" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H163" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H163" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I163" s="9">
         <v>46223</v>
@@ -11270,10 +11274,10 @@
         <v>26</v>
       </c>
       <c r="G164" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H164" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H164" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I164" s="5">
         <v>46223</v>
@@ -11323,10 +11327,10 @@
         <v>26</v>
       </c>
       <c r="G165" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H165" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H165" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I165" s="9">
         <v>46223</v>
@@ -11376,10 +11380,10 @@
         <v>26</v>
       </c>
       <c r="G166" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H166" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H166" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I166" s="5">
         <v>46223</v>
@@ -11429,10 +11433,10 @@
         <v>26</v>
       </c>
       <c r="G167" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H167" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H167" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I167" s="9">
         <v>46223</v>
@@ -11482,10 +11486,10 @@
         <v>26</v>
       </c>
       <c r="G168" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H168" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H168" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I168" s="5">
         <v>46224</v>
@@ -11545,10 +11549,10 @@
         <v>26</v>
       </c>
       <c r="G169" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H169" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H169" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I169" s="10"/>
       <c r="J169" s="9">
@@ -11596,10 +11600,10 @@
         <v>26</v>
       </c>
       <c r="G170" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H170" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H170" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I170" s="6"/>
       <c r="J170" s="5">
@@ -11647,10 +11651,10 @@
         <v>26</v>
       </c>
       <c r="G171" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H171" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H171" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I171" s="10"/>
       <c r="J171" s="9">
@@ -11698,10 +11702,10 @@
         <v>26</v>
       </c>
       <c r="G172" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H172" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H172" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I172" s="6"/>
       <c r="J172" s="5">
@@ -11749,10 +11753,10 @@
         <v>26</v>
       </c>
       <c r="G173" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H173" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H173" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I173" s="10"/>
       <c r="J173" s="9">
@@ -11800,10 +11804,10 @@
         <v>26</v>
       </c>
       <c r="G174" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H174" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H174" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I174" s="6"/>
       <c r="J174" s="5">
@@ -11851,10 +11855,10 @@
         <v>26</v>
       </c>
       <c r="G175" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H175" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H175" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I175" s="10"/>
       <c r="J175" s="9">
@@ -11902,10 +11906,10 @@
         <v>26</v>
       </c>
       <c r="G176" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H176" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H176" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I176" s="6"/>
       <c r="J176" s="5">
@@ -11953,10 +11957,10 @@
         <v>26</v>
       </c>
       <c r="G177" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H177" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H177" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I177" s="10"/>
       <c r="J177" s="9">
@@ -12004,10 +12008,10 @@
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H178" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H178" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I178" s="6"/>
       <c r="J178" s="5">
@@ -12055,10 +12059,10 @@
         <v>26</v>
       </c>
       <c r="G179" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H179" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H179" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I179" s="10"/>
       <c r="J179" s="9">
@@ -12106,10 +12110,10 @@
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H180" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H180" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I180" s="6"/>
       <c r="J180" s="5">
@@ -12157,10 +12161,10 @@
         <v>26</v>
       </c>
       <c r="G181" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H181" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H181" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I181" s="9">
         <v>46226</v>
@@ -12220,10 +12224,10 @@
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H182" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H182" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I182" s="6"/>
       <c r="J182" s="5">
@@ -12271,10 +12275,10 @@
         <v>26</v>
       </c>
       <c r="G183" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H183" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H183" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I183" s="10"/>
       <c r="J183" s="9">
@@ -12322,10 +12326,10 @@
         <v>26</v>
       </c>
       <c r="G184" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H184" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H184" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I184" s="6"/>
       <c r="J184" s="5">
@@ -12373,10 +12377,10 @@
         <v>26</v>
       </c>
       <c r="G185" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H185" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H185" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I185" s="10"/>
       <c r="J185" s="9">
@@ -12424,10 +12428,10 @@
         <v>26</v>
       </c>
       <c r="G186" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H186" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H186" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I186" s="6"/>
       <c r="J186" s="5">
@@ -12475,10 +12479,10 @@
         <v>26</v>
       </c>
       <c r="G187" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H187" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H187" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I187" s="10"/>
       <c r="J187" s="9">
@@ -12526,10 +12530,10 @@
         <v>26</v>
       </c>
       <c r="G188" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H188" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H188" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I188" s="6"/>
       <c r="J188" s="5">
@@ -12577,10 +12581,10 @@
         <v>26</v>
       </c>
       <c r="G189" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H189" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H189" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I189" s="10"/>
       <c r="J189" s="9">
@@ -12628,10 +12632,10 @@
         <v>26</v>
       </c>
       <c r="G190" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H190" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H190" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I190" s="6"/>
       <c r="J190" s="5">
@@ -12679,10 +12683,10 @@
         <v>26</v>
       </c>
       <c r="G191" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H191" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H191" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I191" s="10"/>
       <c r="J191" s="9">
@@ -12730,10 +12734,10 @@
         <v>26</v>
       </c>
       <c r="G192" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H192" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H192" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I192" s="6"/>
       <c r="J192" s="5">
@@ -12781,10 +12785,10 @@
         <v>26</v>
       </c>
       <c r="G193" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H193" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H193" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I193" s="10"/>
       <c r="J193" s="9">
@@ -13554,10 +13558,10 @@
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H208" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H208" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I208" s="5">
         <v>46230</v>
@@ -13617,10 +13621,10 @@
         <v>26</v>
       </c>
       <c r="G209" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H209" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H209" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I209" s="10"/>
       <c r="J209" s="9">
@@ -13668,10 +13672,10 @@
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H210" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H210" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I210" s="6"/>
       <c r="J210" s="5">
@@ -13719,10 +13723,10 @@
         <v>26</v>
       </c>
       <c r="G211" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H211" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H211" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I211" s="10"/>
       <c r="J211" s="9">
@@ -13770,10 +13774,10 @@
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H212" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H212" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I212" s="6"/>
       <c r="J212" s="5">
@@ -13821,10 +13825,10 @@
         <v>26</v>
       </c>
       <c r="G213" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H213" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H213" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I213" s="10"/>
       <c r="J213" s="9">
@@ -13872,10 +13876,10 @@
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H214" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H214" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I214" s="6"/>
       <c r="J214" s="5">
@@ -13923,10 +13927,10 @@
         <v>26</v>
       </c>
       <c r="G215" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H215" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H215" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I215" s="10"/>
       <c r="J215" s="9">
@@ -13974,10 +13978,10 @@
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H216" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H216" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I216" s="6"/>
       <c r="J216" s="5">
@@ -14025,10 +14029,10 @@
         <v>26</v>
       </c>
       <c r="G217" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H217" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H217" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I217" s="10"/>
       <c r="J217" s="9">
@@ -14076,10 +14080,10 @@
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H218" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H218" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I218" s="6"/>
       <c r="J218" s="5">
@@ -14127,10 +14131,10 @@
         <v>26</v>
       </c>
       <c r="G219" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H219" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H219" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="I219" s="10"/>
       <c r="J219" s="9">
@@ -14178,10 +14182,10 @@
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H220" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H220" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I220" s="6"/>
       <c r="J220" s="5">
@@ -15713,10 +15717,10 @@
         <v>26</v>
       </c>
       <c r="G249" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H249" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="H249" s="10" t="s">
-        <v>52</v>
       </c>
       <c r="I249" s="9">
         <v>46233</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2845" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2846" uniqueCount="511">
   <si>
     <t xml:space="preserve">50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT 4324 4325 </t>
   </si>
@@ -357,292 +357,292 @@
     <t>rodete OT 4324 4325,Materiales corte Laser OT 4324 4325,Alabe OT 4324 4325,Motor OT 4324 4325</t>
   </si>
   <si>
+    <t>1214969466331129</t>
+  </si>
+  <si>
+    <t>Alabe OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe OT 4324 4325,Generación OC Alabe OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969379038319</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe OT 4324 4325,Alabe OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1214969379038337</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Alabe OT 4324 4325,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214969287532633</t>
+  </si>
+  <si>
+    <t>rodete OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete OT 4324 4325,Fabricación Rodete OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969287532648</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete OT 4324 4325</t>
+  </si>
+  <si>
+    <t>rodete OT 4324 4325,Fabricación Rodete OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969503994817</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete,rodete OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969504007335</t>
+  </si>
+  <si>
+    <t>Motor OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Generación OC motor OT 4324 4325,Fabricación motor OT 4324 4325,Planos motor proveedor OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969504007350</t>
+  </si>
+  <si>
+    <t>Generación OC motor OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Motor OT 4324 4325,Fabricación motor OT 4324 4325,Planos motor proveedor OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969504023948</t>
+  </si>
+  <si>
+    <t>Fabricación motor OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Recepcion motor,Motor OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969504023966</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Motor OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969335368176</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser  OT 4324 4325,Generación OC materiales corte Laser OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969335368191</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser  OT 4324 4325,Materiales corte Laser OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969379077262</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser  OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Materiales corte Laser OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969379077280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales Corte Plasma OT 4324 4325 </t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  OT 4324 4325,Fabricación Corte Plasma  OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969287605397</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma OT 4324 4325 ,Fabricación Corte Plasma  OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969287605412</t>
+  </si>
+  <si>
+    <t>Fabricación Corte Plasma  OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma OT 4324 4325 ,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>1214969287605814</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4324 4325,Fabricación estructura proveedor externo OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969287605824</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4324 4325,Fabricación estructura proveedor externo OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969287605839</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Recepcion fabricación externa ,Fabricación Externa  OT 4324 4325,Control de calidad fabricación externa  OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969466515947</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1214969466515957</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4324 4325,Fabricación Mecanizado OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969466515967</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4324 4325,Fabricación Mecanizado OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969335445666</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4324 4325</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado,Mecanizado OT 4324 4325</t>
+  </si>
+  <si>
+    <t>1214969284200803</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214969335445681</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214969466529004</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos motor proveedor OT 4324 4325</t>
+  </si>
+  <si>
+    <t>check planos,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>1214969379162030</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,Propuesta Mecanizado OT 4324 4325,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,Propuesta Fabricación externa  OT 4324 4325,propuesta Corte Laser OT 4324 4325,Propuesta Corte plasma  OT 4324 4325,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
+    <t>1214969335458365</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1214969466331129</t>
-  </si>
-  <si>
-    <t>Alabe OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe OT 4324 4325,Generación OC Alabe OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969379038319</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe OT 4324 4325,Alabe OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1214969379038337</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Alabe OT 4324 4325,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214969287532633</t>
-  </si>
-  <si>
-    <t>rodete OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete OT 4324 4325,Fabricación Rodete OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969287532648</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete OT 4324 4325</t>
-  </si>
-  <si>
-    <t>rodete OT 4324 4325,Fabricación Rodete OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969503994817</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete,rodete OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969504007335</t>
-  </si>
-  <si>
-    <t>Motor OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Generación OC motor OT 4324 4325,Fabricación motor OT 4324 4325,Planos motor proveedor OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969504007350</t>
-  </si>
-  <si>
-    <t>Generación OC motor OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Motor OT 4324 4325,Fabricación motor OT 4324 4325,Planos motor proveedor OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969504023948</t>
-  </si>
-  <si>
-    <t>Fabricación motor OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Recepcion motor,Motor OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969504023966</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Motor OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969335368176</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser  OT 4324 4325,Generación OC materiales corte Laser OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969335368191</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser  OT 4324 4325,Materiales corte Laser OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969379077262</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser  OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Materiales corte Laser OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969379077280</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales Corte Plasma OT 4324 4325 </t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  OT 4324 4325,Fabricación Corte Plasma  OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969287605397</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma OT 4324 4325 ,Fabricación Corte Plasma  OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969287605412</t>
-  </si>
-  <si>
-    <t>Fabricación Corte Plasma  OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma OT 4324 4325 ,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>1214969287605814</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4324 4325,Fabricación estructura proveedor externo OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969287605824</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4324 4325,Fabricación estructura proveedor externo OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969287605839</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Recepcion fabricación externa ,Fabricación Externa  OT 4324 4325,Control de calidad fabricación externa  OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969466515947</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1214969466515957</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4324 4325,Fabricación Mecanizado OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969466515967</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4324 4325,Fabricación Mecanizado OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969335445666</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4324 4325</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado,Mecanizado OT 4324 4325</t>
-  </si>
-  <si>
-    <t>1214969284200803</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214969335445681</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214969466529004</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos motor proveedor OT 4324 4325</t>
-  </si>
-  <si>
-    <t>check planos,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>1214969379162030</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4325- ZVN 1-7-63/2,OT 4324- ZVN 1-7-37/2 ,Propuesta Mecanizado OT 4324 4325,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,Propuesta Fabricación externa  OT 4324 4325,propuesta Corte Laser OT 4324 4325,Propuesta Corte plasma  OT 4324 4325,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
-  </si>
-  <si>
-    <t>1214969335458365</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 </t>
   </si>
   <si>
     <t>1214969335458375</t>
@@ -3371,9 +3371,11 @@
       <c r="B22" s="5">
         <v>46162.55817344907</v>
       </c>
-      <c r="C22" s="6"/>
+      <c r="C22" s="5">
+        <v>46247.81442592593</v>
+      </c>
       <c r="D22" s="5">
-        <v>46209.81432671296</v>
+        <v>46247.81443989583</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -3408,14 +3410,16 @@
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
       <c r="S22" s="6"/>
-      <c r="T22" s="6"/>
-      <c r="U22" s="12" t="s">
-        <v>93</v>
+      <c r="T22" s="6">
+        <v>1</v>
+      </c>
+      <c r="U22" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B23" s="9">
         <v>46162.558305694445</v>
@@ -3427,16 +3431,16 @@
         <v>46209.563062939815</v>
       </c>
       <c r="E23" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="10" t="s">
+      <c r="H23" s="10" t="s">
         <v>96</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>97</v>
       </c>
       <c r="I23" s="9">
         <v>46155</v>
@@ -3457,7 +3461,7 @@
         <v>91</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>91</v>
@@ -3480,7 +3484,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B24" s="5">
         <v>46162.55831018518</v>
@@ -3492,16 +3496,16 @@
         <v>46209.56210862269</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="I24" s="5">
         <v>46155</v>
@@ -3519,13 +3523,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>70</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -3536,12 +3540,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B25" s="9">
         <v>46162.55831479166</v>
@@ -3553,16 +3557,16 @@
         <v>46209.56214238426</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>96</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>97</v>
       </c>
       <c r="I25" s="9">
         <v>46157</v>
@@ -3580,13 +3584,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3597,12 +3601,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B26" s="5">
         <v>46162.558319710646</v>
@@ -3614,16 +3618,16 @@
         <v>46209.563100486106</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="I26" s="5">
         <v>46155</v>
@@ -3644,7 +3648,7 @@
         <v>91</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>91</v>
@@ -3667,7 +3671,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B27" s="9">
         <v>46162.55832415509</v>
@@ -3679,16 +3683,16 @@
         <v>46198.68464270834</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>96</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>97</v>
       </c>
       <c r="I27" s="9">
         <v>46155</v>
@@ -3706,13 +3710,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>73</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3723,12 +3727,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46162.5583337037</v>
@@ -3740,16 +3744,16 @@
         <v>46198.68468228009</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="I28" s="5">
         <v>46157</v>
@@ -3767,13 +3771,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3784,12 +3788,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B29" s="9">
         <v>46162.55833876158</v>
@@ -3801,16 +3805,16 @@
         <v>46198.684341354165</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>96</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>97</v>
       </c>
       <c r="I29" s="9">
         <v>46155</v>
@@ -3831,7 +3835,7 @@
         <v>91</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P29" s="10" t="s">
         <v>91</v>
@@ -3854,7 +3858,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46162.5583437037</v>
@@ -3866,16 +3870,16 @@
         <v>46198.684137696764</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="I30" s="5">
         <v>46155</v>
@@ -3893,13 +3897,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3910,12 +3914,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B31" s="9">
         <v>46162.55834872685</v>
@@ -3927,16 +3931,16 @@
         <v>46198.68430833334</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>96</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>97</v>
       </c>
       <c r="I31" s="9">
         <v>46167</v>
@@ -3954,13 +3958,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3971,12 +3975,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46162.558353518514</v>
@@ -3988,16 +3992,16 @@
         <v>46198.68417709491</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="I32" s="5">
         <v>46167</v>
@@ -4015,13 +4019,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -4032,12 +4036,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B33" s="9">
         <v>46162.558358229166</v>
@@ -4049,16 +4053,16 @@
         <v>46209.81431997685</v>
       </c>
       <c r="E33" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="10" t="s">
+      <c r="H33" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>130</v>
       </c>
       <c r="I33" s="9">
         <v>46190</v>
@@ -4079,7 +4083,7 @@
         <v>91</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>91</v>
@@ -4102,7 +4106,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
         <v>46162.5583628125</v>
@@ -4114,16 +4118,16 @@
         <v>46209.814146226854</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="I34" s="5">
         <v>46190</v>
@@ -4141,13 +4145,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -4158,12 +4162,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B35" s="9">
         <v>46162.55841275463</v>
@@ -4175,16 +4179,16 @@
         <v>46209.8142920949</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>130</v>
       </c>
       <c r="I35" s="9">
         <v>46192</v>
@@ -4202,13 +4206,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -4219,12 +4223,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B36" s="5">
         <v>46162.558418622684</v>
@@ -4236,16 +4240,16 @@
         <v>46209.81449996528</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="I36" s="5">
         <v>46190</v>
@@ -4266,7 +4270,7 @@
         <v>91</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -4289,7 +4293,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B37" s="9">
         <v>46162.558422118054</v>
@@ -4307,10 +4311,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>130</v>
       </c>
       <c r="I37" s="9">
         <v>46190</v>
@@ -4328,13 +4332,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>82</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -4344,7 +4348,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46162.558426400465</v>
@@ -4356,16 +4360,16 @@
         <v>46209.81446026621</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="I38" s="5">
         <v>46161</v>
@@ -4383,13 +4387,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>83</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -4399,7 +4403,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B39" s="9">
         <v>46162.55843366898</v>
@@ -4411,16 +4415,16 @@
         <v>46232.17963666667</v>
       </c>
       <c r="E39" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>148</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>149</v>
       </c>
       <c r="I39" s="9">
         <v>46190</v>
@@ -4441,7 +4445,7 @@
         <v>91</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -4464,7 +4468,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B40" s="5">
         <v>46162.558437569445</v>
@@ -4482,10 +4486,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46190</v>
@@ -4503,13 +4507,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4519,7 +4523,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B41" s="9">
         <v>46162.55844153935</v>
@@ -4531,16 +4535,16 @@
         <v>46209.612886620365</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>148</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>149</v>
       </c>
       <c r="I41" s="9">
         <v>46199</v>
@@ -4558,13 +4562,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>89</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4574,7 +4578,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46162.55844576389</v>
@@ -4586,16 +4590,16 @@
         <v>46216.54443384259</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46230</v>
@@ -4613,10 +4617,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4629,7 +4633,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B43" s="9">
         <v>46162.55844833334</v>
@@ -4641,16 +4645,16 @@
         <v>46209.81470094908</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>130</v>
       </c>
       <c r="I43" s="9">
         <v>46190</v>
@@ -4671,7 +4675,7 @@
         <v>91</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4694,7 +4698,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46162.55845114583</v>
@@ -4712,10 +4716,10 @@
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="I44" s="5">
         <v>46190</v>
@@ -4733,13 +4737,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4749,7 +4753,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B45" s="9">
         <v>46162.55845520833</v>
@@ -4761,16 +4765,16 @@
         <v>46209.81467782408</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>130</v>
       </c>
       <c r="I45" s="9">
         <v>46192</v>
@@ -4788,13 +4792,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>86</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4804,7 +4808,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46162.55817767361</v>
@@ -4816,7 +4820,7 @@
         <v>46210.528923819445</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4840,7 +4844,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4857,7 +4861,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B47" s="9">
         <v>46162.55845957176</v>
@@ -4869,16 +4873,16 @@
         <v>46197.67690475694</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="I47" s="9">
         <v>46160</v>
@@ -4896,13 +4900,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q47" s="9">
         <v>46160</v>
@@ -4922,7 +4926,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B48" s="5">
         <v>46162.55846439815</v>
@@ -4934,16 +4938,16 @@
         <v>46198.79333422454</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="I48" s="5">
         <v>46176</v>
@@ -4961,13 +4965,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="Q48" s="5">
         <v>46176</v>
@@ -4987,7 +4991,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B49" s="9">
         <v>46162.55847024306</v>
@@ -5005,10 +5009,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>181</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>182</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -5024,13 +5028,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q49" s="9">
         <v>46185</v>
@@ -5050,26 +5054,28 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5">
         <v>46162.55848571759</v>
       </c>
-      <c r="C50" s="6"/>
+      <c r="C50" s="5">
+        <v>46247.81199479167</v>
+      </c>
       <c r="D50" s="5">
-        <v>46226.20215001157</v>
+        <v>46247.813050763885</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I50" s="5">
         <v>46225</v>
@@ -5087,10 +5093,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -5105,10 +5111,10 @@
         <v>33</v>
       </c>
       <c r="T50" s="6">
-        <v>0</v>
-      </c>
-      <c r="U50" s="11" t="s">
-        <v>102</v>
+        <v>1</v>
+      </c>
+      <c r="U50" s="12" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -5118,9 +5124,11 @@
       <c r="B51" s="9">
         <v>46162.5584890162</v>
       </c>
-      <c r="C51" s="10"/>
+      <c r="C51" s="9">
+        <v>46247.81167303241</v>
+      </c>
       <c r="D51" s="9">
-        <v>46225.16841835648</v>
+        <v>46247.814428935184</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>190</v>
@@ -5129,10 +5137,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>186</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>187</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -5148,7 +5156,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O51" s="10" t="s">
         <v>190</v>
@@ -5169,9 +5177,11 @@
       <c r="B52" s="5">
         <v>46162.558492951386</v>
       </c>
-      <c r="C52" s="6"/>
+      <c r="C52" s="5">
+        <v>46247.81303396991</v>
+      </c>
       <c r="D52" s="5">
-        <v>46225.16841996528</v>
+        <v>46247.81442918981</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>190</v>
@@ -5180,10 +5190,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -5199,7 +5209,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>190</v>
@@ -5220,9 +5230,11 @@
       <c r="B53" s="9">
         <v>46162.55849660879</v>
       </c>
-      <c r="C53" s="10"/>
+      <c r="C53" s="9">
+        <v>46247.814462696755</v>
+      </c>
       <c r="D53" s="9">
-        <v>46225.168421215276</v>
+        <v>46247.81446421296</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>190</v>
@@ -5231,10 +5243,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>186</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>187</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
@@ -5250,7 +5262,7 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>190</v>
@@ -5271,9 +5283,11 @@
       <c r="B54" s="5">
         <v>46162.55849916667</v>
       </c>
-      <c r="C54" s="6"/>
+      <c r="C54" s="5">
+        <v>46247.81451542824</v>
+      </c>
       <c r="D54" s="5">
-        <v>46225.16838393519</v>
+        <v>46247.81452064815</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -5282,10 +5296,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -5301,7 +5315,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>190</v>
@@ -5322,9 +5336,11 @@
       <c r="B55" s="9">
         <v>46162.55850175926</v>
       </c>
-      <c r="C55" s="10"/>
+      <c r="C55" s="9">
+        <v>46247.81451621528</v>
+      </c>
       <c r="D55" s="9">
-        <v>46225.16838541666</v>
+        <v>46247.81452103009</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>196</v>
@@ -5333,10 +5349,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>186</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>187</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -5352,7 +5368,7 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>196</v>
@@ -5373,9 +5389,11 @@
       <c r="B56" s="5">
         <v>46162.56211614583</v>
       </c>
-      <c r="C56" s="6"/>
+      <c r="C56" s="5">
+        <v>46247.81451681713</v>
+      </c>
       <c r="D56" s="5">
-        <v>46225.16840149305</v>
+        <v>46247.81452143518</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>196</v>
@@ -5384,10 +5402,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -5403,7 +5421,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>196</v>
@@ -5424,9 +5442,11 @@
       <c r="B57" s="9">
         <v>46162.56212396991</v>
       </c>
-      <c r="C57" s="10"/>
+      <c r="C57" s="9">
+        <v>46247.814517210645</v>
+      </c>
       <c r="D57" s="9">
-        <v>46225.16840322917</v>
+        <v>46247.81452175926</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>196</v>
@@ -5435,10 +5455,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>186</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>187</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="9">
@@ -5454,7 +5474,7 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>196</v>
@@ -5475,9 +5495,11 @@
       <c r="B58" s="5">
         <v>46162.56213497685</v>
       </c>
-      <c r="C58" s="6"/>
+      <c r="C58" s="5">
+        <v>46247.814517743056</v>
+      </c>
       <c r="D58" s="5">
-        <v>46225.16840447916</v>
+        <v>46247.81452204861</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>196</v>
@@ -5486,10 +5508,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -5505,7 +5527,7 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>196</v>
@@ -5526,9 +5548,11 @@
       <c r="B59" s="9">
         <v>46162.562155057865</v>
       </c>
-      <c r="C59" s="10"/>
+      <c r="C59" s="9">
+        <v>46247.814518263884</v>
+      </c>
       <c r="D59" s="9">
-        <v>46225.16840631944</v>
+        <v>46247.81452231482</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>196</v>
@@ -5537,10 +5561,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>186</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>187</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="9">
@@ -5556,7 +5580,7 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O59" s="10" t="s">
         <v>196</v>
@@ -5577,9 +5601,11 @@
       <c r="B60" s="5">
         <v>46162.562163055554</v>
       </c>
-      <c r="C60" s="6"/>
+      <c r="C60" s="5">
+        <v>46247.81451863426</v>
+      </c>
       <c r="D60" s="5">
-        <v>46225.1684090625</v>
+        <v>46247.81452263889</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>196</v>
@@ -5588,10 +5614,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5607,7 +5633,7 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>196</v>
@@ -5628,9 +5654,11 @@
       <c r="B61" s="9">
         <v>46162.56217104167</v>
       </c>
-      <c r="C61" s="10"/>
+      <c r="C61" s="9">
+        <v>46247.81451899305</v>
+      </c>
       <c r="D61" s="9">
-        <v>46225.168411701394</v>
+        <v>46247.81452295139</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>196</v>
@@ -5639,10 +5667,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>186</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>187</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="9">
@@ -5658,7 +5686,7 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O61" s="10" t="s">
         <v>196</v>
@@ -5679,9 +5707,11 @@
       <c r="B62" s="5">
         <v>46162.562178935186</v>
       </c>
-      <c r="C62" s="6"/>
+      <c r="C62" s="5">
+        <v>46247.81451936343</v>
+      </c>
       <c r="D62" s="5">
-        <v>46225.16841293982</v>
+        <v>46247.81452326389</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>196</v>
@@ -5690,10 +5720,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I62" s="6"/>
       <c r="J62" s="5">
@@ -5709,7 +5739,7 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>196</v>
@@ -5820,7 +5850,7 @@
         <v>205</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>211</v>
@@ -5861,10 +5891,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I65" s="9">
         <v>46204</v>
@@ -5950,7 +5980,7 @@
         <v>205</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>218</v>
@@ -5991,10 +6021,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I67" s="9">
         <v>46204</v>
@@ -6080,7 +6110,7 @@
         <v>205</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>223</v>
@@ -6121,10 +6151,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I69" s="9">
         <v>46204</v>
@@ -6173,9 +6203,11 @@
       <c r="B70" s="5">
         <v>46162.55853556713</v>
       </c>
-      <c r="C70" s="6"/>
+      <c r="C70" s="5">
+        <v>46247.81526716435</v>
+      </c>
       <c r="D70" s="5">
-        <v>46225.81140046296</v>
+        <v>46247.81528174768</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>227</v>
@@ -6210,8 +6242,12 @@
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
       <c r="S70" s="6"/>
-      <c r="T70" s="6"/>
-      <c r="U70" s="6"/>
+      <c r="T70" s="6">
+        <v>1</v>
+      </c>
+      <c r="U70" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
@@ -6945,9 +6981,11 @@
       <c r="B84" s="5">
         <v>46162.55862063657</v>
       </c>
-      <c r="C84" s="6"/>
+      <c r="C84" s="5">
+        <v>46247.81329474537</v>
+      </c>
       <c r="D84" s="5">
-        <v>46225.81192504629</v>
+        <v>46247.813307812496</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>254</v>
@@ -6995,10 +7033,10 @@
         <v>33</v>
       </c>
       <c r="T84" s="6">
-        <v>0</v>
-      </c>
-      <c r="U84" s="11" t="s">
-        <v>102</v>
+        <v>1</v>
+      </c>
+      <c r="U84" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -7008,9 +7046,11 @@
       <c r="B85" s="9">
         <v>46162.558626620375</v>
       </c>
-      <c r="C85" s="10"/>
+      <c r="C85" s="9">
+        <v>46247.81326572917</v>
+      </c>
       <c r="D85" s="9">
-        <v>46225.81138908565</v>
+        <v>46247.813273101856</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>190</v>
@@ -7061,9 +7101,11 @@
       <c r="B86" s="5">
         <v>46162.55863280092</v>
       </c>
-      <c r="C86" s="6"/>
+      <c r="C86" s="5">
+        <v>46247.81326645833</v>
+      </c>
       <c r="D86" s="5">
-        <v>46225.81137782407</v>
+        <v>46247.81327356481</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>190</v>
@@ -7114,9 +7156,11 @@
       <c r="B87" s="9">
         <v>46162.55863850695</v>
       </c>
-      <c r="C87" s="10"/>
+      <c r="C87" s="9">
+        <v>46247.81326702546</v>
+      </c>
       <c r="D87" s="9">
-        <v>46225.81136515047</v>
+        <v>46247.813274050925</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>190</v>
@@ -7167,9 +7211,11 @@
       <c r="B88" s="5">
         <v>46162.558644247685</v>
       </c>
-      <c r="C88" s="6"/>
+      <c r="C88" s="5">
+        <v>46247.81326759259</v>
+      </c>
       <c r="D88" s="5">
-        <v>46225.811345740745</v>
+        <v>46247.81327449074</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>190</v>
@@ -7220,9 +7266,11 @@
       <c r="B89" s="9">
         <v>46162.55864990741</v>
       </c>
-      <c r="C89" s="10"/>
+      <c r="C89" s="9">
+        <v>46247.81326810185</v>
+      </c>
       <c r="D89" s="9">
-        <v>46225.811355625</v>
+        <v>46247.81327490741</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>196</v>
@@ -7273,9 +7321,11 @@
       <c r="B90" s="5">
         <v>46162.56148016204</v>
       </c>
-      <c r="C90" s="6"/>
+      <c r="C90" s="5">
+        <v>46247.813268680555</v>
+      </c>
       <c r="D90" s="5">
-        <v>46225.81132334491</v>
+        <v>46247.81327533565</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>196</v>
@@ -7326,9 +7376,11 @@
       <c r="B91" s="9">
         <v>46162.561489201384</v>
       </c>
-      <c r="C91" s="10"/>
+      <c r="C91" s="9">
+        <v>46247.81326920139</v>
+      </c>
       <c r="D91" s="9">
-        <v>46225.81131275463</v>
+        <v>46247.81327569444</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>196</v>
@@ -7379,9 +7431,11 @@
       <c r="B92" s="5">
         <v>46162.56149930556</v>
       </c>
-      <c r="C92" s="6"/>
+      <c r="C92" s="5">
+        <v>46247.813269606486</v>
+      </c>
       <c r="D92" s="5">
-        <v>46225.81130295139</v>
+        <v>46247.81327605324</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>196</v>
@@ -7432,9 +7486,11 @@
       <c r="B93" s="9">
         <v>46162.561507199076</v>
       </c>
-      <c r="C93" s="10"/>
+      <c r="C93" s="9">
+        <v>46247.81327021991</v>
+      </c>
       <c r="D93" s="9">
-        <v>46225.81129587963</v>
+        <v>46247.81327640046</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>196</v>
@@ -7485,9 +7541,11 @@
       <c r="B94" s="5">
         <v>46162.56151613426</v>
       </c>
-      <c r="C94" s="6"/>
+      <c r="C94" s="5">
+        <v>46247.813270729166</v>
+      </c>
       <c r="D94" s="5">
-        <v>46225.81128686343</v>
+        <v>46247.813276747685</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>196</v>
@@ -7538,9 +7596,11 @@
       <c r="B95" s="9">
         <v>46162.56152413195</v>
       </c>
-      <c r="C95" s="10"/>
+      <c r="C95" s="9">
+        <v>46247.81327126158</v>
+      </c>
       <c r="D95" s="9">
-        <v>46225.81127690972</v>
+        <v>46247.81327708333</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>196</v>
@@ -7591,9 +7651,11 @@
       <c r="B96" s="5">
         <v>46162.56153119213</v>
       </c>
-      <c r="C96" s="6"/>
+      <c r="C96" s="5">
+        <v>46247.813271747684</v>
+      </c>
       <c r="D96" s="5">
-        <v>46225.81127016204</v>
+        <v>46247.81327741898</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>196</v>
@@ -7644,9 +7706,11 @@
       <c r="B97" s="9">
         <v>46162.55865439815</v>
       </c>
-      <c r="C97" s="10"/>
+      <c r="C97" s="9">
+        <v>46247.81345563657</v>
+      </c>
       <c r="D97" s="9">
-        <v>46218.20591833333</v>
+        <v>46247.815585648146</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>273</v>
@@ -7655,10 +7719,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H97" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I97" s="9">
         <v>46217</v>
@@ -7694,10 +7758,10 @@
         <v>33</v>
       </c>
       <c r="T97" s="10">
-        <v>0</v>
-      </c>
-      <c r="U97" s="11" t="s">
-        <v>102</v>
+        <v>1</v>
+      </c>
+      <c r="U97" s="12" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7707,9 +7771,11 @@
       <c r="B98" s="5">
         <v>46162.55865909722</v>
       </c>
-      <c r="C98" s="6"/>
+      <c r="C98" s="5">
+        <v>46247.81341994213</v>
+      </c>
       <c r="D98" s="5">
-        <v>46217.16848263889</v>
+        <v>46247.81342832176</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>190</v>
@@ -7718,10 +7784,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I98" s="5">
         <v>46217</v>
@@ -7760,9 +7826,11 @@
       <c r="B99" s="9">
         <v>46162.55866501157</v>
       </c>
-      <c r="C99" s="10"/>
+      <c r="C99" s="9">
+        <v>46247.81342078703</v>
+      </c>
       <c r="D99" s="9">
-        <v>46217.168484050926</v>
+        <v>46247.813428761576</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>190</v>
@@ -7771,10 +7839,10 @@
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H99" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I99" s="9">
         <v>46217</v>
@@ -7813,9 +7881,11 @@
       <c r="B100" s="5">
         <v>46162.55867084491</v>
       </c>
-      <c r="C100" s="6"/>
+      <c r="C100" s="5">
+        <v>46247.81342143519</v>
+      </c>
       <c r="D100" s="5">
-        <v>46217.16847319444</v>
+        <v>46247.81342914352</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>190</v>
@@ -7824,10 +7894,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I100" s="5">
         <v>46217</v>
@@ -7866,9 +7936,11 @@
       <c r="B101" s="9">
         <v>46162.558676597226</v>
       </c>
-      <c r="C101" s="10"/>
+      <c r="C101" s="9">
+        <v>46247.81342208333</v>
+      </c>
       <c r="D101" s="9">
-        <v>46217.16847716435</v>
+        <v>46247.813429490736</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>190</v>
@@ -7877,10 +7949,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I101" s="9">
         <v>46217</v>
@@ -7919,9 +7991,11 @@
       <c r="B102" s="5">
         <v>46162.55868239583</v>
       </c>
-      <c r="C102" s="6"/>
+      <c r="C102" s="5">
+        <v>46247.81342266204</v>
+      </c>
       <c r="D102" s="5">
-        <v>46217.168485312504</v>
+        <v>46247.81342986111</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>196</v>
@@ -7930,10 +8004,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I102" s="5">
         <v>46217</v>
@@ -7972,9 +8046,11 @@
       <c r="B103" s="9">
         <v>46162.56176834491</v>
       </c>
-      <c r="C103" s="10"/>
+      <c r="C103" s="9">
+        <v>46247.81342333333</v>
+      </c>
       <c r="D103" s="9">
-        <v>46217.16846244213</v>
+        <v>46247.813430208334</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>196</v>
@@ -7983,10 +8059,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H103" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I103" s="9">
         <v>46217</v>
@@ -8025,9 +8101,11 @@
       <c r="B104" s="5">
         <v>46162.56177670139</v>
       </c>
-      <c r="C104" s="6"/>
+      <c r="C104" s="5">
+        <v>46247.813423935186</v>
+      </c>
       <c r="D104" s="5">
-        <v>46224.87647666667</v>
+        <v>46247.81343056713</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>196</v>
@@ -8036,10 +8114,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I104" s="5">
         <v>46217</v>
@@ -8078,9 +8156,11 @@
       <c r="B105" s="9">
         <v>46162.56178474537</v>
       </c>
-      <c r="C105" s="10"/>
+      <c r="C105" s="9">
+        <v>46247.81342449074</v>
+      </c>
       <c r="D105" s="9">
-        <v>46217.16846583333</v>
+        <v>46247.81343096065</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>196</v>
@@ -8089,10 +8169,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H105" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I105" s="9">
         <v>46217</v>
@@ -8131,9 +8211,11 @@
       <c r="B106" s="5">
         <v>46162.56179298611</v>
       </c>
-      <c r="C106" s="6"/>
+      <c r="C106" s="5">
+        <v>46247.8134250463</v>
+      </c>
       <c r="D106" s="5">
-        <v>46217.16846726852</v>
+        <v>46247.813431284725</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>196</v>
@@ -8142,10 +8224,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I106" s="5">
         <v>46217</v>
@@ -8184,9 +8266,11 @@
       <c r="B107" s="9">
         <v>46162.5618009375</v>
       </c>
-      <c r="C107" s="10"/>
+      <c r="C107" s="9">
+        <v>46247.813425636574</v>
+      </c>
       <c r="D107" s="9">
-        <v>46217.16846878472</v>
+        <v>46247.81343163195</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>196</v>
@@ -8195,10 +8279,10 @@
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H107" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I107" s="9">
         <v>46217</v>
@@ -8237,9 +8321,11 @@
       <c r="B108" s="5">
         <v>46162.56180909723</v>
       </c>
-      <c r="C108" s="6"/>
+      <c r="C108" s="5">
+        <v>46247.8134262963</v>
+      </c>
       <c r="D108" s="5">
-        <v>46217.168470358796</v>
+        <v>46247.81343196759</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>196</v>
@@ -8248,10 +8334,10 @@
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H108" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I108" s="5">
         <v>46217</v>
@@ -8290,9 +8376,11 @@
       <c r="B109" s="9">
         <v>46162.56181716435</v>
       </c>
-      <c r="C109" s="10"/>
+      <c r="C109" s="9">
+        <v>46247.81342679398</v>
+      </c>
       <c r="D109" s="9">
-        <v>46217.16847178241</v>
+        <v>46247.81343231481</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>196</v>
@@ -8301,10 +8389,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H109" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I109" s="9">
         <v>46217</v>
@@ -8433,7 +8521,7 @@
         <v>205</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>297</v>
@@ -8498,7 +8586,7 @@
         <v>205</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>300</v>
@@ -8563,7 +8651,7 @@
         <v>205</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>303</v>
@@ -8628,7 +8716,7 @@
         <v>205</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>306</v>
@@ -8658,7 +8746,7 @@
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46162.64775322917</v>
+        <v>46247.81444270833</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>308</v>
@@ -8703,9 +8791,11 @@
       <c r="B116" s="5">
         <v>46162.55872223379</v>
       </c>
-      <c r="C116" s="6"/>
+      <c r="C116" s="5">
+        <v>46247.813576307875</v>
+      </c>
       <c r="D116" s="5">
-        <v>46237.54090622685</v>
+        <v>46247.815586412034</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>311</v>
@@ -8753,10 +8843,10 @@
         <v>33</v>
       </c>
       <c r="T116" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U116" s="12" t="s">
-        <v>93</v>
+        <v>188</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
@@ -8766,9 +8856,11 @@
       <c r="B117" s="9">
         <v>46162.55873068287</v>
       </c>
-      <c r="C117" s="10"/>
+      <c r="C117" s="9">
+        <v>46247.813550949075</v>
+      </c>
       <c r="D117" s="9">
-        <v>46224.25040153935</v>
+        <v>46247.8155793287</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>190</v>
@@ -8819,9 +8911,11 @@
       <c r="B118" s="5">
         <v>46162.558735011575</v>
       </c>
-      <c r="C118" s="6"/>
+      <c r="C118" s="5">
+        <v>46247.81355158565</v>
+      </c>
       <c r="D118" s="5">
-        <v>46224.25040292824</v>
+        <v>46247.81355893519</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>190</v>
@@ -8872,9 +8966,11 @@
       <c r="B119" s="9">
         <v>46162.55873951389</v>
       </c>
-      <c r="C119" s="10"/>
+      <c r="C119" s="9">
+        <v>46247.81355201389</v>
+      </c>
       <c r="D119" s="9">
-        <v>46224.25044962963</v>
+        <v>46247.81355928241</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>190</v>
@@ -8925,9 +9021,11 @@
       <c r="B120" s="5">
         <v>46162.55874386574</v>
       </c>
-      <c r="C120" s="6"/>
+      <c r="C120" s="5">
+        <v>46247.813552638894</v>
+      </c>
       <c r="D120" s="5">
-        <v>46224.25045101852</v>
+        <v>46247.81355965278</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>190</v>
@@ -8978,9 +9076,11 @@
       <c r="B121" s="9">
         <v>46162.55874813657</v>
       </c>
-      <c r="C121" s="10"/>
+      <c r="C121" s="9">
+        <v>46247.813553252316</v>
+      </c>
       <c r="D121" s="9">
-        <v>46224.25040421296</v>
+        <v>46247.813559988426</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>196</v>
@@ -9031,9 +9131,11 @@
       <c r="B122" s="5">
         <v>46162.56516702546</v>
       </c>
-      <c r="C122" s="6"/>
+      <c r="C122" s="5">
+        <v>46247.81355381945</v>
+      </c>
       <c r="D122" s="5">
-        <v>46224.25042715278</v>
+        <v>46247.81356034722</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>196</v>
@@ -9084,9 +9186,11 @@
       <c r="B123" s="9">
         <v>46162.56517383102</v>
       </c>
-      <c r="C123" s="10"/>
+      <c r="C123" s="9">
+        <v>46247.813554374996</v>
+      </c>
       <c r="D123" s="9">
-        <v>46224.2504290625</v>
+        <v>46247.813560740746</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>196</v>
@@ -9137,9 +9241,11 @@
       <c r="B124" s="5">
         <v>46162.565181134254</v>
       </c>
-      <c r="C124" s="6"/>
+      <c r="C124" s="5">
+        <v>46247.81355496528</v>
+      </c>
       <c r="D124" s="5">
-        <v>46224.250430555556</v>
+        <v>46247.81356108796</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>196</v>
@@ -9190,9 +9296,11 @@
       <c r="B125" s="9">
         <v>46162.565189201385</v>
       </c>
-      <c r="C125" s="10"/>
+      <c r="C125" s="9">
+        <v>46247.81355553241</v>
+      </c>
       <c r="D125" s="9">
-        <v>46224.25043193287</v>
+        <v>46247.813561435185</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>196</v>
@@ -9243,9 +9351,11 @@
       <c r="B126" s="5">
         <v>46162.56519680556</v>
       </c>
-      <c r="C126" s="6"/>
+      <c r="C126" s="5">
+        <v>46247.81355611111</v>
+      </c>
       <c r="D126" s="5">
-        <v>46224.250433402776</v>
+        <v>46247.81356178241</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>196</v>
@@ -9296,9 +9406,11 @@
       <c r="B127" s="9">
         <v>46162.565205590276</v>
       </c>
-      <c r="C127" s="10"/>
+      <c r="C127" s="9">
+        <v>46247.81355662037</v>
+      </c>
       <c r="D127" s="9">
-        <v>46224.25043480324</v>
+        <v>46247.813562129624</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>196</v>
@@ -9349,9 +9461,11 @@
       <c r="B128" s="5">
         <v>46162.565212013884</v>
       </c>
-      <c r="C128" s="6"/>
+      <c r="C128" s="5">
+        <v>46247.81355717593</v>
+      </c>
       <c r="D128" s="5">
-        <v>46224.25043630787</v>
+        <v>46247.81356247685</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>196</v>
@@ -9402,9 +9516,11 @@
       <c r="B129" s="9">
         <v>46162.558751550925</v>
       </c>
-      <c r="C129" s="10"/>
+      <c r="C129" s="9">
+        <v>46247.81391107639</v>
+      </c>
       <c r="D129" s="9">
-        <v>46237.54094651621</v>
+        <v>46247.81393420139</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>328</v>
@@ -9452,7 +9568,7 @@
         <v>33</v>
       </c>
       <c r="T129" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U129" s="7" t="s">
         <v>27</v>
@@ -9465,9 +9581,11 @@
       <c r="B130" s="5">
         <v>46162.558756238424</v>
       </c>
-      <c r="C130" s="6"/>
+      <c r="C130" s="5">
+        <v>46247.81387784722</v>
+      </c>
       <c r="D130" s="5">
-        <v>46223.57901649305</v>
+        <v>46247.81388666667</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>190</v>
@@ -9516,9 +9634,11 @@
       <c r="B131" s="9">
         <v>46162.55876204861</v>
       </c>
-      <c r="C131" s="10"/>
+      <c r="C131" s="9">
+        <v>46247.813878773144</v>
+      </c>
       <c r="D131" s="9">
-        <v>46223.57901584491</v>
+        <v>46247.81388728009</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>190</v>
@@ -9567,9 +9687,11 @@
       <c r="B132" s="5">
         <v>46162.55876745371</v>
       </c>
-      <c r="C132" s="6"/>
+      <c r="C132" s="5">
+        <v>46247.81387945602</v>
+      </c>
       <c r="D132" s="5">
-        <v>46223.57901519676</v>
+        <v>46247.81388778935</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>190</v>
@@ -9618,9 +9740,11 @@
       <c r="B133" s="9">
         <v>46162.558773888886</v>
       </c>
-      <c r="C133" s="10"/>
+      <c r="C133" s="9">
+        <v>46247.813880104164</v>
+      </c>
       <c r="D133" s="9">
-        <v>46223.57901452546</v>
+        <v>46247.81388819445</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>190</v>
@@ -9669,9 +9793,11 @@
       <c r="B134" s="5">
         <v>46162.558827430556</v>
       </c>
-      <c r="C134" s="6"/>
+      <c r="C134" s="5">
+        <v>46247.81388079861</v>
+      </c>
       <c r="D134" s="5">
-        <v>46223.579013888884</v>
+        <v>46247.81388861111</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>196</v>
@@ -9720,9 +9846,11 @@
       <c r="B135" s="9">
         <v>46162.565477233795</v>
       </c>
-      <c r="C135" s="10"/>
+      <c r="C135" s="9">
+        <v>46247.81388153935</v>
+      </c>
       <c r="D135" s="9">
-        <v>46223.579013229166</v>
+        <v>46247.81388916667</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>196</v>
@@ -9771,9 +9899,11 @@
       <c r="B136" s="5">
         <v>46162.56548539352</v>
       </c>
-      <c r="C136" s="6"/>
+      <c r="C136" s="5">
+        <v>46247.81388210648</v>
+      </c>
       <c r="D136" s="5">
-        <v>46223.579012546295</v>
+        <v>46247.81388960648</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>196</v>
@@ -9822,9 +9952,11 @@
       <c r="B137" s="9">
         <v>46162.56549420139</v>
       </c>
-      <c r="C137" s="10"/>
+      <c r="C137" s="9">
+        <v>46247.81388266204</v>
+      </c>
       <c r="D137" s="9">
-        <v>46223.579011875</v>
+        <v>46247.81389002315</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>196</v>
@@ -9873,9 +10005,11 @@
       <c r="B138" s="5">
         <v>46162.56549981482</v>
       </c>
-      <c r="C138" s="6"/>
+      <c r="C138" s="5">
+        <v>46247.81388327546</v>
+      </c>
       <c r="D138" s="5">
-        <v>46223.57901104167</v>
+        <v>46247.81389039352</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>196</v>
@@ -9924,9 +10058,11 @@
       <c r="B139" s="9">
         <v>46162.565507719904</v>
       </c>
-      <c r="C139" s="10"/>
+      <c r="C139" s="9">
+        <v>46247.813883842595</v>
+      </c>
       <c r="D139" s="9">
-        <v>46223.57901035879</v>
+        <v>46247.81389078704</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>196</v>
@@ -9975,9 +10111,11 @@
       <c r="B140" s="5">
         <v>46162.56551637732</v>
       </c>
-      <c r="C140" s="6"/>
+      <c r="C140" s="5">
+        <v>46247.813884421295</v>
+      </c>
       <c r="D140" s="5">
-        <v>46223.579009733796</v>
+        <v>46247.813891157406</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>196</v>
@@ -10026,9 +10164,11 @@
       <c r="B141" s="9">
         <v>46162.56598206019</v>
       </c>
-      <c r="C141" s="10"/>
+      <c r="C141" s="9">
+        <v>46247.8138850463</v>
+      </c>
       <c r="D141" s="9">
-        <v>46223.57900907408</v>
+        <v>46247.81389152778</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>196</v>
@@ -10077,9 +10217,11 @@
       <c r="B142" s="5">
         <v>46162.55883354167</v>
       </c>
-      <c r="C142" s="6"/>
+      <c r="C142" s="5">
+        <v>46247.814077731484</v>
+      </c>
       <c r="D142" s="5">
-        <v>46223.57990805556</v>
+        <v>46247.81409195602</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>352</v>
@@ -10127,10 +10269,10 @@
         <v>33</v>
       </c>
       <c r="T142" s="6">
-        <v>0</v>
-      </c>
-      <c r="U142" s="11" t="s">
-        <v>102</v>
+        <v>1</v>
+      </c>
+      <c r="U142" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
@@ -10140,9 +10282,11 @@
       <c r="B143" s="9">
         <v>46162.55883898148</v>
       </c>
-      <c r="C143" s="10"/>
+      <c r="C143" s="9">
+        <v>46247.81404020834</v>
+      </c>
       <c r="D143" s="9">
-        <v>46223.57929469907</v>
+        <v>46247.81405185185</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>190</v>
@@ -10193,9 +10337,11 @@
       <c r="B144" s="5">
         <v>46162.55884618056</v>
       </c>
-      <c r="C144" s="6"/>
+      <c r="C144" s="5">
+        <v>46247.81404131945</v>
+      </c>
       <c r="D144" s="5">
-        <v>46223.57929405093</v>
+        <v>46247.81405244213</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>190</v>
@@ -10246,9 +10392,11 @@
       <c r="B145" s="9">
         <v>46162.55885335648</v>
       </c>
-      <c r="C145" s="10"/>
+      <c r="C145" s="9">
+        <v>46247.814042314814</v>
+      </c>
       <c r="D145" s="9">
-        <v>46223.5792933912</v>
+        <v>46247.81405292824</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>190</v>
@@ -10299,9 +10447,11 @@
       <c r="B146" s="5">
         <v>46162.558860624995</v>
       </c>
-      <c r="C146" s="6"/>
+      <c r="C146" s="5">
+        <v>46247.81404347222</v>
+      </c>
       <c r="D146" s="5">
-        <v>46223.579292766204</v>
+        <v>46247.814053379625</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>190</v>
@@ -10352,9 +10502,11 @@
       <c r="B147" s="9">
         <v>46162.558867395834</v>
       </c>
-      <c r="C147" s="10"/>
+      <c r="C147" s="9">
+        <v>46247.81404434028</v>
+      </c>
       <c r="D147" s="9">
-        <v>46223.57929214121</v>
+        <v>46247.81405421296</v>
       </c>
       <c r="E147" s="10" t="s">
         <v>196</v>
@@ -10405,9 +10557,11 @@
       <c r="B148" s="5">
         <v>46162.566146365745</v>
       </c>
-      <c r="C148" s="6"/>
+      <c r="C148" s="5">
+        <v>46247.81404521991</v>
+      </c>
       <c r="D148" s="5">
-        <v>46223.5792915162</v>
+        <v>46247.814054664355</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>196</v>
@@ -10458,9 +10612,11 @@
       <c r="B149" s="9">
         <v>46162.566153101856</v>
       </c>
-      <c r="C149" s="10"/>
+      <c r="C149" s="9">
+        <v>46247.814045949075</v>
+      </c>
       <c r="D149" s="9">
-        <v>46223.57929087963</v>
+        <v>46247.81405508102</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>196</v>
@@ -10511,9 +10667,11 @@
       <c r="B150" s="5">
         <v>46162.56617111111</v>
       </c>
-      <c r="C150" s="6"/>
+      <c r="C150" s="5">
+        <v>46247.81404670139</v>
+      </c>
       <c r="D150" s="5">
-        <v>46223.57929026621</v>
+        <v>46247.814055509254</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>196</v>
@@ -10564,9 +10722,11 @@
       <c r="B151" s="9">
         <v>46162.56618105324</v>
       </c>
-      <c r="C151" s="10"/>
+      <c r="C151" s="9">
+        <v>46247.81404748843</v>
+      </c>
       <c r="D151" s="9">
-        <v>46223.57928965278</v>
+        <v>46247.81405601852</v>
       </c>
       <c r="E151" s="10" t="s">
         <v>346</v>
@@ -10617,9 +10777,11 @@
       <c r="B152" s="5">
         <v>46162.56618987268</v>
       </c>
-      <c r="C152" s="6"/>
+      <c r="C152" s="5">
+        <v>46247.814048263885</v>
+      </c>
       <c r="D152" s="5">
-        <v>46223.57928883102</v>
+        <v>46247.81405644676</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>196</v>
@@ -10670,9 +10832,11 @@
       <c r="B153" s="9">
         <v>46162.56620271991</v>
       </c>
-      <c r="C153" s="10"/>
+      <c r="C153" s="9">
+        <v>46247.81404895833</v>
+      </c>
       <c r="D153" s="9">
-        <v>46223.57928822917</v>
+        <v>46247.81405685185</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>196</v>
@@ -10723,9 +10887,11 @@
       <c r="B154" s="5">
         <v>46162.56620673611</v>
       </c>
-      <c r="C154" s="6"/>
+      <c r="C154" s="5">
+        <v>46247.81404971065</v>
+      </c>
       <c r="D154" s="5">
-        <v>46223.579287615736</v>
+        <v>46247.81405725694</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>196</v>
@@ -10776,9 +10942,11 @@
       <c r="B155" s="9">
         <v>46162.558871574074</v>
       </c>
-      <c r="C155" s="10"/>
+      <c r="C155" s="9">
+        <v>46247.814219699074</v>
+      </c>
       <c r="D155" s="9">
-        <v>46224.18423814815</v>
+        <v>46247.814231689816</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>372</v>
@@ -10826,10 +10994,10 @@
         <v>33</v>
       </c>
       <c r="T155" s="10">
-        <v>0</v>
-      </c>
-      <c r="U155" s="11" t="s">
-        <v>102</v>
+        <v>1</v>
+      </c>
+      <c r="U155" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
@@ -10839,9 +11007,11 @@
       <c r="B156" s="5">
         <v>46162.55887622685</v>
       </c>
-      <c r="C156" s="6"/>
+      <c r="C156" s="5">
+        <v>46247.81418356481</v>
+      </c>
       <c r="D156" s="5">
-        <v>46225.87106959491</v>
+        <v>46247.81419292824</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>190</v>
@@ -10892,9 +11062,11 @@
       <c r="B157" s="9">
         <v>46162.55888300926</v>
       </c>
-      <c r="C157" s="10"/>
+      <c r="C157" s="9">
+        <v>46247.814184456016</v>
+      </c>
       <c r="D157" s="9">
-        <v>46225.87107101852</v>
+        <v>46247.81419348379</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>190</v>
@@ -10945,9 +11117,11 @@
       <c r="B158" s="5">
         <v>46162.558892581015</v>
       </c>
-      <c r="C158" s="6"/>
+      <c r="C158" s="5">
+        <v>46247.814185104166</v>
+      </c>
       <c r="D158" s="5">
-        <v>46225.87107528935</v>
+        <v>46247.81419395833</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>190</v>
@@ -10998,9 +11172,11 @@
       <c r="B159" s="9">
         <v>46162.55889858796</v>
       </c>
-      <c r="C159" s="10"/>
+      <c r="C159" s="9">
+        <v>46247.81418613426</v>
+      </c>
       <c r="D159" s="9">
-        <v>46225.87107458334</v>
+        <v>46247.814194398146</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>190</v>
@@ -11051,9 +11227,11 @@
       <c r="B160" s="5">
         <v>46162.558904618054</v>
       </c>
-      <c r="C160" s="6"/>
+      <c r="C160" s="5">
+        <v>46247.81418677083</v>
+      </c>
       <c r="D160" s="5">
-        <v>46223.57947667824</v>
+        <v>46247.81419479167</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>196</v>
@@ -11104,9 +11282,11 @@
       <c r="B161" s="9">
         <v>46162.566379375</v>
       </c>
-      <c r="C161" s="10"/>
+      <c r="C161" s="9">
+        <v>46247.81418747685</v>
+      </c>
       <c r="D161" s="9">
-        <v>46225.87106449074</v>
+        <v>46247.81419527778</v>
       </c>
       <c r="E161" s="10" t="s">
         <v>196</v>
@@ -11157,9 +11337,11 @@
       <c r="B162" s="5">
         <v>46162.56638695602</v>
       </c>
-      <c r="C162" s="6"/>
+      <c r="C162" s="5">
+        <v>46247.81418810185</v>
+      </c>
       <c r="D162" s="5">
-        <v>46225.87106525463</v>
+        <v>46247.814195659725</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>196</v>
@@ -11210,9 +11392,11 @@
       <c r="B163" s="9">
         <v>46162.56639532407</v>
       </c>
-      <c r="C163" s="10"/>
+      <c r="C163" s="9">
+        <v>46247.814188749995</v>
+      </c>
       <c r="D163" s="9">
-        <v>46225.871065949075</v>
+        <v>46247.81419597223</v>
       </c>
       <c r="E163" s="10" t="s">
         <v>196</v>
@@ -11263,9 +11447,11 @@
       <c r="B164" s="5">
         <v>46162.56640418981</v>
       </c>
-      <c r="C164" s="6"/>
+      <c r="C164" s="5">
+        <v>46247.81418947916</v>
+      </c>
       <c r="D164" s="5">
-        <v>46225.8710666088</v>
+        <v>46247.81419634259</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>196</v>
@@ -11316,9 +11502,11 @@
       <c r="B165" s="9">
         <v>46162.56641240741</v>
       </c>
-      <c r="C165" s="10"/>
+      <c r="C165" s="9">
+        <v>46247.81419010417</v>
+      </c>
       <c r="D165" s="9">
-        <v>46225.87106722222</v>
+        <v>46247.81419680556</v>
       </c>
       <c r="E165" s="10" t="s">
         <v>196</v>
@@ -11369,9 +11557,11 @@
       <c r="B166" s="5">
         <v>46162.56642033564</v>
       </c>
-      <c r="C166" s="6"/>
+      <c r="C166" s="5">
+        <v>46247.81419077546</v>
+      </c>
       <c r="D166" s="5">
-        <v>46225.87106789352</v>
+        <v>46247.8141971875</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>196</v>
@@ -11422,9 +11612,11 @@
       <c r="B167" s="9">
         <v>46162.566427708334</v>
       </c>
-      <c r="C167" s="10"/>
+      <c r="C167" s="9">
+        <v>46247.81419138889</v>
+      </c>
       <c r="D167" s="9">
-        <v>46225.87106853009</v>
+        <v>46247.814197569445</v>
       </c>
       <c r="E167" s="10" t="s">
         <v>196</v>
@@ -11475,9 +11667,11 @@
       <c r="B168" s="5">
         <v>46162.558908946754</v>
       </c>
-      <c r="C168" s="6"/>
+      <c r="C168" s="5">
+        <v>46247.81443539352</v>
+      </c>
       <c r="D168" s="5">
-        <v>46225.18524023148</v>
+        <v>46247.814451053244</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>397</v>
@@ -11525,10 +11719,10 @@
         <v>33</v>
       </c>
       <c r="T168" s="6">
-        <v>0</v>
-      </c>
-      <c r="U168" s="11" t="s">
-        <v>102</v>
+        <v>1</v>
+      </c>
+      <c r="U168" s="12" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
@@ -11538,9 +11732,11 @@
       <c r="B169" s="9">
         <v>46162.55891369213</v>
       </c>
-      <c r="C169" s="10"/>
+      <c r="C169" s="9">
+        <v>46247.81438027778</v>
+      </c>
       <c r="D169" s="9">
-        <v>46224.25045532407</v>
+        <v>46247.81440623842</v>
       </c>
       <c r="E169" s="10" t="s">
         <v>190</v>
@@ -11589,9 +11785,11 @@
       <c r="B170" s="5">
         <v>46162.55891930556</v>
       </c>
-      <c r="C170" s="6"/>
+      <c r="C170" s="5">
+        <v>46247.81438157408</v>
+      </c>
       <c r="D170" s="5">
-        <v>46224.25039887731</v>
+        <v>46247.814408680555</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>190</v>
@@ -11640,9 +11838,11 @@
       <c r="B171" s="9">
         <v>46162.558924930556</v>
       </c>
-      <c r="C171" s="10"/>
+      <c r="C171" s="9">
+        <v>46247.81438563658</v>
+      </c>
       <c r="D171" s="9">
-        <v>46224.250400185185</v>
+        <v>46247.81441115741</v>
       </c>
       <c r="E171" s="10" t="s">
         <v>190</v>
@@ -11691,9 +11891,11 @@
       <c r="B172" s="5">
         <v>46162.55893104167</v>
       </c>
-      <c r="C172" s="6"/>
+      <c r="C172" s="5">
+        <v>46247.81438819444</v>
+      </c>
       <c r="D172" s="5">
-        <v>46224.25039688658</v>
+        <v>46247.814413726854</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>190</v>
@@ -11742,9 +11944,11 @@
       <c r="B173" s="9">
         <v>46162.55893646991</v>
       </c>
-      <c r="C173" s="10"/>
+      <c r="C173" s="9">
+        <v>46247.814390625004</v>
+      </c>
       <c r="D173" s="9">
-        <v>46224.25045253472</v>
+        <v>46247.814415127315</v>
       </c>
       <c r="E173" s="10" t="s">
         <v>196</v>
@@ -11793,9 +11997,11 @@
       <c r="B174" s="5">
         <v>46162.567320891205</v>
       </c>
-      <c r="C174" s="6"/>
+      <c r="C174" s="5">
+        <v>46247.81439159722</v>
+      </c>
       <c r="D174" s="5">
-        <v>46224.25043752315</v>
+        <v>46247.81441560185</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>196</v>
@@ -11844,9 +12050,11 @@
       <c r="B175" s="9">
         <v>46162.567330034726</v>
       </c>
-      <c r="C175" s="10"/>
+      <c r="C175" s="9">
+        <v>46247.81439208333</v>
+      </c>
       <c r="D175" s="9">
-        <v>46224.25043901621</v>
+        <v>46247.814415995366</v>
       </c>
       <c r="E175" s="10" t="s">
         <v>196</v>
@@ -11895,9 +12103,11 @@
       <c r="B176" s="5">
         <v>46162.567337685185</v>
       </c>
-      <c r="C176" s="6"/>
+      <c r="C176" s="5">
+        <v>46247.8143928125</v>
+      </c>
       <c r="D176" s="5">
-        <v>46224.25044046296</v>
+        <v>46247.81441644676</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>196</v>
@@ -11946,9 +12156,11 @@
       <c r="B177" s="9">
         <v>46162.567344166666</v>
       </c>
-      <c r="C177" s="10"/>
+      <c r="C177" s="9">
+        <v>46247.814393692126</v>
+      </c>
       <c r="D177" s="9">
-        <v>46224.2504419676</v>
+        <v>46247.8144168287</v>
       </c>
       <c r="E177" s="10" t="s">
         <v>196</v>
@@ -11997,9 +12209,11 @@
       <c r="B178" s="5">
         <v>46162.56735135417</v>
       </c>
-      <c r="C178" s="6"/>
+      <c r="C178" s="5">
+        <v>46247.814394710644</v>
+      </c>
       <c r="D178" s="5">
-        <v>46224.25044340278</v>
+        <v>46247.81441721065</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>196</v>
@@ -12048,9 +12262,11 @@
       <c r="B179" s="9">
         <v>46162.5673590625</v>
       </c>
-      <c r="C179" s="10"/>
+      <c r="C179" s="9">
+        <v>46247.81439590278</v>
+      </c>
       <c r="D179" s="9">
-        <v>46224.25044509259</v>
+        <v>46247.814417581016</v>
       </c>
       <c r="E179" s="10" t="s">
         <v>196</v>
@@ -12099,9 +12315,11 @@
       <c r="B180" s="5">
         <v>46162.567366284726</v>
       </c>
-      <c r="C180" s="6"/>
+      <c r="C180" s="5">
+        <v>46247.81439731481</v>
+      </c>
       <c r="D180" s="5">
-        <v>46224.25044643518</v>
+        <v>46247.8144181713</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>196</v>
@@ -12203,7 +12421,7 @@
         <v>0</v>
       </c>
       <c r="U181" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
@@ -12215,7 +12433,7 @@
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46226.16815751157</v>
+        <v>46247.81168096064</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>190</v>
@@ -12266,7 +12484,7 @@
       </c>
       <c r="C183" s="10"/>
       <c r="D183" s="9">
-        <v>46226.16815899305</v>
+        <v>46247.81304408565</v>
       </c>
       <c r="E183" s="10" t="s">
         <v>190</v>
@@ -12317,7 +12535,7 @@
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46226.16815614583</v>
+        <v>46247.81446768518</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>190</v>
@@ -12368,7 +12586,7 @@
       </c>
       <c r="C185" s="10"/>
       <c r="D185" s="9">
-        <v>46226.16816035879</v>
+        <v>46247.814529201394</v>
       </c>
       <c r="E185" s="10" t="s">
         <v>190</v>
@@ -12419,7 +12637,7 @@
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46226.16816185185</v>
+        <v>46247.814529525465</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>196</v>
@@ -12470,7 +12688,7 @@
       </c>
       <c r="C187" s="10"/>
       <c r="D187" s="9">
-        <v>46226.16814340278</v>
+        <v>46247.81420626157</v>
       </c>
       <c r="E187" s="10" t="s">
         <v>196</v>
@@ -12521,7 +12739,7 @@
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46226.16814550926</v>
+        <v>46247.814529386575</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>196</v>
@@ -12572,7 +12790,7 @@
       </c>
       <c r="C189" s="10"/>
       <c r="D189" s="9">
-        <v>46226.168146909724</v>
+        <v>46247.81452946759</v>
       </c>
       <c r="E189" s="10" t="s">
         <v>196</v>
@@ -12623,7 +12841,7 @@
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46226.168148275465</v>
+        <v>46247.81420597222</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>196</v>
@@ -12674,7 +12892,7 @@
       </c>
       <c r="C191" s="10"/>
       <c r="D191" s="9">
-        <v>46226.16814969908</v>
+        <v>46247.81420606481</v>
       </c>
       <c r="E191" s="10" t="s">
         <v>196</v>
@@ -12725,7 +12943,7 @@
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46226.16815109954</v>
+        <v>46247.81420664352</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>196</v>
@@ -12776,7 +12994,7 @@
       </c>
       <c r="C193" s="10"/>
       <c r="D193" s="9">
-        <v>46226.16815254629</v>
+        <v>46247.81452969907</v>
       </c>
       <c r="E193" s="10" t="s">
         <v>196</v>
@@ -12925,7 +13143,7 @@
         <v>0</v>
       </c>
       <c r="U195" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
@@ -13192,7 +13410,7 @@
       </c>
       <c r="C201" s="10"/>
       <c r="D201" s="9">
-        <v>46227.168836944446</v>
+        <v>46247.81420716435</v>
       </c>
       <c r="E201" s="10" t="s">
         <v>196</v>
@@ -13600,7 +13818,7 @@
         <v>0</v>
       </c>
       <c r="U208" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
@@ -14275,7 +14493,7 @@
         <v>0</v>
       </c>
       <c r="U221" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
@@ -14950,7 +15168,7 @@
         <v>0</v>
       </c>
       <c r="U234" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="235" spans="1:21" x14ac:dyDescent="0.25">
@@ -15696,7 +15914,7 @@
         <v>0</v>
       </c>
       <c r="U248" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="249" spans="1:21" x14ac:dyDescent="0.25">
@@ -15759,7 +15977,7 @@
         <v>0</v>
       </c>
       <c r="U249" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -2359,7 +2359,7 @@
         <v>46175.87405894676</v>
       </c>
       <c r="D6" s="5">
-        <v>46213.766980995366</v>
+        <v>46248.93024659722</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -6207,7 +6207,7 @@
         <v>46247.81526716435</v>
       </c>
       <c r="D70" s="5">
-        <v>46247.81528174768</v>
+        <v>46249.01801238426</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>227</v>
@@ -8795,7 +8795,7 @@
         <v>46247.813576307875</v>
       </c>
       <c r="D116" s="5">
-        <v>46247.815586412034</v>
+        <v>46249.00406114583</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>311</v>
@@ -9520,7 +9520,7 @@
         <v>46247.81391107639</v>
       </c>
       <c r="D129" s="9">
-        <v>46247.81393420139</v>
+        <v>46249.00408576389</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>328</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -6207,7 +6207,7 @@
         <v>46247.81526716435</v>
       </c>
       <c r="D70" s="5">
-        <v>46249.01801238426</v>
+        <v>46260.58255684028</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>227</v>
@@ -7710,7 +7710,7 @@
         <v>46247.81345563657</v>
       </c>
       <c r="D97" s="9">
-        <v>46247.815585648146</v>
+        <v>46260.58260415509</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>273</v>
@@ -7724,12 +7724,8 @@
       <c r="H97" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="I97" s="9">
-        <v>46217</v>
-      </c>
-      <c r="J97" s="9">
-        <v>46217</v>
-      </c>
+      <c r="I97" s="10"/>
+      <c r="J97" s="10"/>
       <c r="K97" s="10" t="s">
         <v>26</v>
       </c>
@@ -7760,8 +7756,8 @@
       <c r="T97" s="10">
         <v>1</v>
       </c>
-      <c r="U97" s="12" t="s">
-        <v>188</v>
+      <c r="U97" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -8795,7 +8791,7 @@
         <v>46247.813576307875</v>
       </c>
       <c r="D116" s="5">
-        <v>46249.00406114583</v>
+        <v>46260.58267778935</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>311</v>
@@ -8845,8 +8841,8 @@
       <c r="T116" s="6">
         <v>1</v>
       </c>
-      <c r="U116" s="12" t="s">
-        <v>188</v>
+      <c r="U116" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
@@ -11671,7 +11667,7 @@
         <v>46247.81443539352</v>
       </c>
       <c r="D168" s="5">
-        <v>46247.814451053244</v>
+        <v>46260.5827024537</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>397</v>
@@ -11721,8 +11717,8 @@
       <c r="T168" s="6">
         <v>1</v>
       </c>
-      <c r="U168" s="12" t="s">
-        <v>188</v>
+      <c r="U168" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
@@ -12370,7 +12366,7 @@
       </c>
       <c r="C181" s="10"/>
       <c r="D181" s="9">
-        <v>46227.200147048614</v>
+        <v>46260.582717916666</v>
       </c>
       <c r="E181" s="10" t="s">
         <v>414</v>
@@ -12420,8 +12416,8 @@
       <c r="T181" s="10">
         <v>0</v>
       </c>
-      <c r="U181" s="11" t="s">
-        <v>101</v>
+      <c r="U181" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
@@ -13767,7 +13763,7 @@
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46231.180388402776</v>
+        <v>46260.58276497685</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>454</v>
@@ -13817,8 +13813,8 @@
       <c r="T208" s="6">
         <v>0</v>
       </c>
-      <c r="U208" s="11" t="s">
-        <v>101</v>
+      <c r="U208" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
@@ -14442,7 +14438,7 @@
       </c>
       <c r="C221" s="10"/>
       <c r="D221" s="9">
-        <v>46232.179640358794</v>
+        <v>46260.58278292824</v>
       </c>
       <c r="E221" s="10" t="s">
         <v>471</v>
@@ -14492,8 +14488,8 @@
       <c r="T221" s="10">
         <v>0</v>
       </c>
-      <c r="U221" s="11" t="s">
-        <v>101</v>
+      <c r="U221" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
@@ -15117,7 +15113,7 @@
       </c>
       <c r="C234" s="6"/>
       <c r="D234" s="5">
-        <v>46233.179258923614</v>
+        <v>46260.58282258102</v>
       </c>
       <c r="E234" s="6" t="s">
         <v>488</v>
@@ -15167,8 +15163,8 @@
       <c r="T234" s="6">
         <v>0</v>
       </c>
-      <c r="U234" s="11" t="s">
-        <v>101</v>
+      <c r="U234" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="235" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2846" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2848" uniqueCount="511">
   <si>
     <t xml:space="preserve">50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT 4324 4325 </t>
   </si>
@@ -8740,9 +8740,11 @@
       <c r="B115" s="9">
         <v>46162.55871869213</v>
       </c>
-      <c r="C115" s="10"/>
+      <c r="C115" s="9">
+        <v>46260.842362800926</v>
+      </c>
       <c r="D115" s="9">
-        <v>46247.81444270833</v>
+        <v>46260.842380243055</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>308</v>
@@ -8777,8 +8779,12 @@
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
       <c r="S115" s="10"/>
-      <c r="T115" s="10"/>
-      <c r="U115" s="10"/>
+      <c r="T115" s="10">
+        <v>1</v>
+      </c>
+      <c r="U115" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
@@ -12364,9 +12370,11 @@
       <c r="B181" s="9">
         <v>46162.558941678246</v>
       </c>
-      <c r="C181" s="10"/>
+      <c r="C181" s="9">
+        <v>46260.8403359375</v>
+      </c>
       <c r="D181" s="9">
-        <v>46260.582717916666</v>
+        <v>46260.840349652775</v>
       </c>
       <c r="E181" s="10" t="s">
         <v>414</v>
@@ -12414,7 +12422,7 @@
         <v>33</v>
       </c>
       <c r="T181" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U181" s="7" t="s">
         <v>27</v>
@@ -12427,9 +12435,11 @@
       <c r="B182" s="5">
         <v>46162.5589471875</v>
       </c>
-      <c r="C182" s="6"/>
+      <c r="C182" s="5">
+        <v>46260.840305439815</v>
+      </c>
       <c r="D182" s="5">
-        <v>46247.81168096064</v>
+        <v>46260.84031221065</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>190</v>
@@ -12478,9 +12488,11 @@
       <c r="B183" s="9">
         <v>46162.55895184028</v>
       </c>
-      <c r="C183" s="10"/>
+      <c r="C183" s="9">
+        <v>46260.84030618056</v>
+      </c>
       <c r="D183" s="9">
-        <v>46247.81304408565</v>
+        <v>46260.84031262732</v>
       </c>
       <c r="E183" s="10" t="s">
         <v>190</v>
@@ -12529,9 +12541,11 @@
       <c r="B184" s="5">
         <v>46162.55895655093</v>
       </c>
-      <c r="C184" s="6"/>
+      <c r="C184" s="5">
+        <v>46260.84030671296</v>
+      </c>
       <c r="D184" s="5">
-        <v>46247.81446768518</v>
+        <v>46260.84031303241</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>190</v>
@@ -12580,9 +12594,11 @@
       <c r="B185" s="9">
         <v>46162.5589959375</v>
       </c>
-      <c r="C185" s="10"/>
+      <c r="C185" s="9">
+        <v>46260.8403072338</v>
+      </c>
       <c r="D185" s="9">
-        <v>46247.814529201394</v>
+        <v>46260.84031342593</v>
       </c>
       <c r="E185" s="10" t="s">
         <v>190</v>
@@ -12631,9 +12647,11 @@
       <c r="B186" s="5">
         <v>46162.55900136574</v>
       </c>
-      <c r="C186" s="6"/>
+      <c r="C186" s="5">
+        <v>46260.84030773148</v>
+      </c>
       <c r="D186" s="5">
-        <v>46247.814529525465</v>
+        <v>46260.840313796296</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>196</v>
@@ -12682,9 +12700,11 @@
       <c r="B187" s="9">
         <v>46162.56759152778</v>
       </c>
-      <c r="C187" s="10"/>
+      <c r="C187" s="9">
+        <v>46260.84030829861</v>
+      </c>
       <c r="D187" s="9">
-        <v>46247.81420626157</v>
+        <v>46260.840314166664</v>
       </c>
       <c r="E187" s="10" t="s">
         <v>196</v>
@@ -12733,9 +12753,11 @@
       <c r="B188" s="5">
         <v>46162.56759846065</v>
       </c>
-      <c r="C188" s="6"/>
+      <c r="C188" s="5">
+        <v>46260.840308645835</v>
+      </c>
       <c r="D188" s="5">
-        <v>46247.814529386575</v>
+        <v>46260.840314456014</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>196</v>
@@ -12784,9 +12806,11 @@
       <c r="B189" s="9">
         <v>46162.56760671297</v>
       </c>
-      <c r="C189" s="10"/>
+      <c r="C189" s="9">
+        <v>46260.840309085645</v>
+      </c>
       <c r="D189" s="9">
-        <v>46247.81452946759</v>
+        <v>46260.84031474537</v>
       </c>
       <c r="E189" s="10" t="s">
         <v>196</v>
@@ -12835,9 +12859,11 @@
       <c r="B190" s="5">
         <v>46162.56761416666</v>
       </c>
-      <c r="C190" s="6"/>
+      <c r="C190" s="5">
+        <v>46260.84030952546</v>
+      </c>
       <c r="D190" s="5">
-        <v>46247.81420597222</v>
+        <v>46260.8403150463</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>196</v>
@@ -12886,9 +12912,11 @@
       <c r="B191" s="9">
         <v>46162.56762221065</v>
       </c>
-      <c r="C191" s="10"/>
+      <c r="C191" s="9">
+        <v>46260.84030996528</v>
+      </c>
       <c r="D191" s="9">
-        <v>46247.81420606481</v>
+        <v>46260.84031534722</v>
       </c>
       <c r="E191" s="10" t="s">
         <v>196</v>
@@ -12937,9 +12965,11 @@
       <c r="B192" s="5">
         <v>46162.56762855324</v>
       </c>
-      <c r="C192" s="6"/>
+      <c r="C192" s="5">
+        <v>46260.840310405096</v>
+      </c>
       <c r="D192" s="5">
-        <v>46247.81420664352</v>
+        <v>46260.84031564815</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>196</v>
@@ -12988,9 +13018,11 @@
       <c r="B193" s="9">
         <v>46162.56763415509</v>
       </c>
-      <c r="C193" s="10"/>
+      <c r="C193" s="9">
+        <v>46260.84031090278</v>
+      </c>
       <c r="D193" s="9">
-        <v>46247.81452969907</v>
+        <v>46260.84031596065</v>
       </c>
       <c r="E193" s="10" t="s">
         <v>196</v>
@@ -13039,9 +13071,11 @@
       <c r="B194" s="5">
         <v>46162.55900565972</v>
       </c>
-      <c r="C194" s="6"/>
+      <c r="C194" s="5">
+        <v>46260.84237268519</v>
+      </c>
       <c r="D194" s="5">
-        <v>46162.663939108796</v>
+        <v>46260.84238768519</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>432</v>
@@ -13076,8 +13110,12 @@
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
       <c r="S194" s="6"/>
-      <c r="T194" s="6"/>
-      <c r="U194" s="6"/>
+      <c r="T194" s="6">
+        <v>1</v>
+      </c>
+      <c r="U194" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
@@ -13086,9 +13124,11 @@
       <c r="B195" s="9">
         <v>46162.55900940972</v>
       </c>
-      <c r="C195" s="10"/>
+      <c r="C195" s="9">
+        <v>46260.84146768518</v>
+      </c>
       <c r="D195" s="9">
-        <v>46228.19288883102</v>
+        <v>46260.842270486115</v>
       </c>
       <c r="E195" s="10" t="s">
         <v>435</v>
@@ -13136,10 +13176,10 @@
         <v>33</v>
       </c>
       <c r="T195" s="10">
-        <v>0</v>
-      </c>
-      <c r="U195" s="11" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U195" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
@@ -13149,9 +13189,11 @@
       <c r="B196" s="5">
         <v>46162.559015023144</v>
       </c>
-      <c r="C196" s="6"/>
+      <c r="C196" s="5">
+        <v>46260.84143572916</v>
+      </c>
       <c r="D196" s="5">
-        <v>46227.16884697917</v>
+        <v>46260.841442986115</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>190</v>
@@ -13200,9 +13242,11 @@
       <c r="B197" s="9">
         <v>46162.55901939815</v>
       </c>
-      <c r="C197" s="10"/>
+      <c r="C197" s="9">
+        <v>46260.84143648148</v>
+      </c>
       <c r="D197" s="9">
-        <v>46227.16885321759</v>
+        <v>46260.841443391204</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>190</v>
@@ -13251,9 +13295,11 @@
       <c r="B198" s="5">
         <v>46162.55902388888</v>
       </c>
-      <c r="C198" s="6"/>
+      <c r="C198" s="5">
+        <v>46260.84143702546</v>
+      </c>
       <c r="D198" s="5">
-        <v>46227.16885833333</v>
+        <v>46260.84144372685</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>190</v>
@@ -13302,9 +13348,11 @@
       <c r="B199" s="9">
         <v>46162.559028090276</v>
       </c>
-      <c r="C199" s="10"/>
+      <c r="C199" s="9">
+        <v>46260.841437662035</v>
+      </c>
       <c r="D199" s="9">
-        <v>46227.16885959491</v>
+        <v>46260.84144405092</v>
       </c>
       <c r="E199" s="10" t="s">
         <v>190</v>
@@ -13353,9 +13401,11 @@
       <c r="B200" s="5">
         <v>46162.559032060184</v>
       </c>
-      <c r="C200" s="6"/>
+      <c r="C200" s="5">
+        <v>46260.841438240735</v>
+      </c>
       <c r="D200" s="5">
-        <v>46227.168854675925</v>
+        <v>46260.841444363425</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>196</v>
@@ -13404,9 +13454,11 @@
       <c r="B201" s="9">
         <v>46162.56847083333</v>
       </c>
-      <c r="C201" s="10"/>
+      <c r="C201" s="9">
+        <v>46260.84143883102</v>
+      </c>
       <c r="D201" s="9">
-        <v>46247.81420716435</v>
+        <v>46260.841444687496</v>
       </c>
       <c r="E201" s="10" t="s">
         <v>196</v>
@@ -13455,9 +13507,11 @@
       <c r="B202" s="5">
         <v>46162.5684778588</v>
       </c>
-      <c r="C202" s="6"/>
+      <c r="C202" s="5">
+        <v>46260.84143927084</v>
+      </c>
       <c r="D202" s="5">
-        <v>46227.16883850694</v>
+        <v>46260.84144502315</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>196</v>
@@ -13506,9 +13560,11 @@
       <c r="B203" s="9">
         <v>46162.56848583333</v>
       </c>
-      <c r="C203" s="10"/>
+      <c r="C203" s="9">
+        <v>46260.841439641204</v>
+      </c>
       <c r="D203" s="9">
-        <v>46227.168839861115</v>
+        <v>46260.84144534722</v>
       </c>
       <c r="E203" s="10" t="s">
         <v>196</v>
@@ -13557,9 +13613,11 @@
       <c r="B204" s="5">
         <v>46162.56849315972</v>
       </c>
-      <c r="C204" s="6"/>
+      <c r="C204" s="5">
+        <v>46260.84144013889</v>
+      </c>
       <c r="D204" s="5">
-        <v>46227.168841273146</v>
+        <v>46260.841445659724</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>196</v>
@@ -13608,9 +13666,11 @@
       <c r="B205" s="9">
         <v>46162.568499120374</v>
       </c>
-      <c r="C205" s="10"/>
+      <c r="C205" s="9">
+        <v>46260.84144070602</v>
+      </c>
       <c r="D205" s="9">
-        <v>46227.16884255787</v>
+        <v>46260.841445972226</v>
       </c>
       <c r="E205" s="10" t="s">
         <v>196</v>
@@ -13659,9 +13719,11 @@
       <c r="B206" s="5">
         <v>46162.568507013886</v>
       </c>
-      <c r="C206" s="6"/>
+      <c r="C206" s="5">
+        <v>46260.84144125</v>
+      </c>
       <c r="D206" s="5">
-        <v>46227.168843796295</v>
+        <v>46260.8414462963</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>196</v>
@@ -13710,9 +13772,11 @@
       <c r="B207" s="9">
         <v>46162.56851576389</v>
       </c>
-      <c r="C207" s="10"/>
+      <c r="C207" s="9">
+        <v>46260.84144177083</v>
+      </c>
       <c r="D207" s="9">
-        <v>46227.16884491898</v>
+        <v>46260.84144658565</v>
       </c>
       <c r="E207" s="10" t="s">
         <v>196</v>
@@ -13761,9 +13825,11 @@
       <c r="B208" s="5">
         <v>46162.559035983795</v>
       </c>
-      <c r="C208" s="6"/>
+      <c r="C208" s="5">
+        <v>46260.84109861111</v>
+      </c>
       <c r="D208" s="5">
-        <v>46260.58276497685</v>
+        <v>46260.841111863425</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>454</v>
@@ -13811,7 +13877,7 @@
         <v>33</v>
       </c>
       <c r="T208" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U208" s="7" t="s">
         <v>27</v>
@@ -13824,9 +13890,11 @@
       <c r="B209" s="9">
         <v>46162.559040057866</v>
       </c>
-      <c r="C209" s="10"/>
+      <c r="C209" s="9">
+        <v>46260.84042487269</v>
+      </c>
       <c r="D209" s="9">
-        <v>46230.16873420139</v>
+        <v>46260.84145730324</v>
       </c>
       <c r="E209" s="10" t="s">
         <v>190</v>
@@ -13875,9 +13943,11 @@
       <c r="B210" s="5">
         <v>46162.559044305555</v>
       </c>
-      <c r="C210" s="6"/>
+      <c r="C210" s="5">
+        <v>46260.84047520833</v>
+      </c>
       <c r="D210" s="5">
-        <v>46230.16873547454</v>
+        <v>46260.84145716435</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>190</v>
@@ -13926,9 +13996,11 @@
       <c r="B211" s="9">
         <v>46162.55904842593</v>
       </c>
-      <c r="C211" s="10"/>
+      <c r="C211" s="9">
+        <v>46260.840525775464</v>
+      </c>
       <c r="D211" s="9">
-        <v>46230.16873686343</v>
+        <v>46260.84145767361</v>
       </c>
       <c r="E211" s="10" t="s">
         <v>190</v>
@@ -13977,9 +14049,11 @@
       <c r="B212" s="5">
         <v>46162.55905241898</v>
       </c>
-      <c r="C212" s="6"/>
+      <c r="C212" s="5">
+        <v>46260.8405772338</v>
+      </c>
       <c r="D212" s="5">
-        <v>46230.16873802083</v>
+        <v>46260.84145756945</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>190</v>
@@ -14028,9 +14102,11 @@
       <c r="B213" s="9">
         <v>46162.55905643519</v>
       </c>
-      <c r="C213" s="10"/>
+      <c r="C213" s="9">
+        <v>46260.840634189815</v>
+      </c>
       <c r="D213" s="9">
-        <v>46230.168739155095</v>
+        <v>46260.84145674769</v>
       </c>
       <c r="E213" s="10" t="s">
         <v>196</v>
@@ -14079,9 +14155,11 @@
       <c r="B214" s="5">
         <v>46162.568794328705</v>
       </c>
-      <c r="C214" s="6"/>
+      <c r="C214" s="5">
+        <v>46260.840720671295</v>
+      </c>
       <c r="D214" s="5">
-        <v>46230.16872133102</v>
+        <v>46260.84145472222</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>196</v>
@@ -14130,9 +14208,11 @@
       <c r="B215" s="9">
         <v>46162.56880138889</v>
       </c>
-      <c r="C215" s="10"/>
+      <c r="C215" s="9">
+        <v>46260.84078269676</v>
+      </c>
       <c r="D215" s="9">
-        <v>46230.16872302083</v>
+        <v>46260.84078416666</v>
       </c>
       <c r="E215" s="10" t="s">
         <v>196</v>
@@ -14181,9 +14261,11 @@
       <c r="B216" s="5">
         <v>46162.56880807871</v>
       </c>
-      <c r="C216" s="6"/>
+      <c r="C216" s="5">
+        <v>46260.840797384255</v>
+      </c>
       <c r="D216" s="5">
-        <v>46230.168724675925</v>
+        <v>46260.84145471065</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>196</v>
@@ -14232,9 +14314,11 @@
       <c r="B217" s="9">
         <v>46162.56881548611</v>
       </c>
-      <c r="C217" s="10"/>
+      <c r="C217" s="9">
+        <v>46260.84091443287</v>
+      </c>
       <c r="D217" s="9">
-        <v>46230.16872583333</v>
+        <v>46260.84145452546</v>
       </c>
       <c r="E217" s="10" t="s">
         <v>196</v>
@@ -14283,9 +14367,11 @@
       <c r="B218" s="5">
         <v>46162.56882248842</v>
       </c>
-      <c r="C218" s="6"/>
+      <c r="C218" s="5">
+        <v>46260.840975949075</v>
+      </c>
       <c r="D218" s="5">
-        <v>46230.168726979166</v>
+        <v>46260.84145447917</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>196</v>
@@ -14334,9 +14420,11 @@
       <c r="B219" s="9">
         <v>46162.56882971065</v>
       </c>
-      <c r="C219" s="10"/>
+      <c r="C219" s="9">
+        <v>46260.841025381946</v>
+      </c>
       <c r="D219" s="9">
-        <v>46230.168728055556</v>
+        <v>46260.84145458334</v>
       </c>
       <c r="E219" s="10" t="s">
         <v>196</v>
@@ -14385,9 +14473,11 @@
       <c r="B220" s="5">
         <v>46162.56883761574</v>
       </c>
-      <c r="C220" s="6"/>
+      <c r="C220" s="5">
+        <v>46260.84108528935</v>
+      </c>
       <c r="D220" s="5">
-        <v>46230.16872912037</v>
+        <v>46260.84145449074</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>196</v>
@@ -14436,9 +14526,11 @@
       <c r="B221" s="9">
         <v>46162.559060671294</v>
       </c>
-      <c r="C221" s="10"/>
+      <c r="C221" s="9">
+        <v>46260.84163928241</v>
+      </c>
       <c r="D221" s="9">
-        <v>46260.58278292824</v>
+        <v>46260.842270891204</v>
       </c>
       <c r="E221" s="10" t="s">
         <v>471</v>
@@ -14486,7 +14578,7 @@
         <v>33</v>
       </c>
       <c r="T221" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U221" s="7" t="s">
         <v>27</v>
@@ -14499,9 +14591,11 @@
       <c r="B222" s="5">
         <v>46162.55906472223</v>
       </c>
-      <c r="C222" s="6"/>
+      <c r="C222" s="5">
+        <v>46260.841611111115</v>
+      </c>
       <c r="D222" s="5">
-        <v>46231.168255868055</v>
+        <v>46260.8416187963</v>
       </c>
       <c r="E222" s="6" t="s">
         <v>190</v>
@@ -14550,9 +14644,11 @@
       <c r="B223" s="9">
         <v>46162.55907236111</v>
       </c>
-      <c r="C223" s="10"/>
+      <c r="C223" s="9">
+        <v>46260.841611909724</v>
+      </c>
       <c r="D223" s="9">
-        <v>46231.16824994213</v>
+        <v>46260.84161920139</v>
       </c>
       <c r="E223" s="10" t="s">
         <v>190</v>
@@ -14601,9 +14697,11 @@
       <c r="B224" s="5">
         <v>46162.55907862268</v>
       </c>
-      <c r="C224" s="6"/>
+      <c r="C224" s="5">
+        <v>46260.841612488424</v>
+      </c>
       <c r="D224" s="5">
-        <v>46231.168251111114</v>
+        <v>46260.841619548606</v>
       </c>
       <c r="E224" s="6" t="s">
         <v>190</v>
@@ -14652,9 +14750,11 @@
       <c r="B225" s="9">
         <v>46162.55908304398</v>
       </c>
-      <c r="C225" s="10"/>
+      <c r="C225" s="9">
+        <v>46260.84161309028</v>
+      </c>
       <c r="D225" s="9">
-        <v>46231.168252511576</v>
+        <v>46260.841619872685</v>
       </c>
       <c r="E225" s="10" t="s">
         <v>190</v>
@@ -14703,9 +14803,11 @@
       <c r="B226" s="5">
         <v>46162.55908719907</v>
       </c>
-      <c r="C226" s="6"/>
+      <c r="C226" s="5">
+        <v>46260.84161369213</v>
+      </c>
       <c r="D226" s="5">
-        <v>46231.16825728009</v>
+        <v>46260.841620266205</v>
       </c>
       <c r="E226" s="6" t="s">
         <v>196</v>
@@ -14754,9 +14856,11 @@
       <c r="B227" s="9">
         <v>46162.56901232639</v>
       </c>
-      <c r="C227" s="10"/>
+      <c r="C227" s="9">
+        <v>46260.841614317134</v>
+      </c>
       <c r="D227" s="9">
-        <v>46231.16824121527</v>
+        <v>46260.84162060185</v>
       </c>
       <c r="E227" s="10" t="s">
         <v>196</v>
@@ -14805,9 +14909,11 @@
       <c r="B228" s="5">
         <v>46162.569018888884</v>
       </c>
-      <c r="C228" s="6"/>
+      <c r="C228" s="5">
+        <v>46260.84161481481</v>
+      </c>
       <c r="D228" s="5">
-        <v>46231.16824241898</v>
+        <v>46260.84162091435</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>196</v>
@@ -14856,9 +14962,11 @@
       <c r="B229" s="9">
         <v>46162.56902688657</v>
       </c>
-      <c r="C229" s="10"/>
+      <c r="C229" s="9">
+        <v>46260.8416153125</v>
+      </c>
       <c r="D229" s="9">
-        <v>46231.16824366898</v>
+        <v>46260.841621238425</v>
       </c>
       <c r="E229" s="10" t="s">
         <v>465</v>
@@ -14907,9 +15015,11 @@
       <c r="B230" s="5">
         <v>46162.56903291667</v>
       </c>
-      <c r="C230" s="6"/>
+      <c r="C230" s="5">
+        <v>46260.84161585648</v>
+      </c>
       <c r="D230" s="5">
-        <v>46231.168244733795</v>
+        <v>46260.84162153935</v>
       </c>
       <c r="E230" s="6" t="s">
         <v>196</v>
@@ -14958,9 +15068,11 @@
       <c r="B231" s="9">
         <v>46162.56903989583</v>
       </c>
-      <c r="C231" s="10"/>
+      <c r="C231" s="9">
+        <v>46260.841616412035</v>
+      </c>
       <c r="D231" s="9">
-        <v>46231.16824633101</v>
+        <v>46260.841621851854</v>
       </c>
       <c r="E231" s="10" t="s">
         <v>196</v>
@@ -15009,9 +15121,11 @@
       <c r="B232" s="5">
         <v>46162.56904635417</v>
       </c>
-      <c r="C232" s="6"/>
+      <c r="C232" s="5">
+        <v>46260.84161694444</v>
+      </c>
       <c r="D232" s="5">
-        <v>46231.16824753472</v>
+        <v>46260.841622175925</v>
       </c>
       <c r="E232" s="6" t="s">
         <v>196</v>
@@ -15060,9 +15174,11 @@
       <c r="B233" s="9">
         <v>46162.56905347222</v>
       </c>
-      <c r="C233" s="10"/>
+      <c r="C233" s="9">
+        <v>46260.841617453705</v>
+      </c>
       <c r="D233" s="9">
-        <v>46231.16824866898</v>
+        <v>46260.8416225</v>
       </c>
       <c r="E233" s="10" t="s">
         <v>196</v>
@@ -15111,9 +15227,11 @@
       <c r="B234" s="5">
         <v>46162.559091284726</v>
       </c>
-      <c r="C234" s="6"/>
+      <c r="C234" s="5">
+        <v>46260.84175015046</v>
+      </c>
       <c r="D234" s="5">
-        <v>46260.58282258102</v>
+        <v>46260.84227121528</v>
       </c>
       <c r="E234" s="6" t="s">
         <v>488</v>
@@ -15161,7 +15279,7 @@
         <v>33</v>
       </c>
       <c r="T234" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U234" s="7" t="s">
         <v>27</v>
@@ -15174,9 +15292,11 @@
       <c r="B235" s="9">
         <v>46162.55909613426</v>
       </c>
-      <c r="C235" s="10"/>
+      <c r="C235" s="9">
+        <v>46260.84171793982</v>
+      </c>
       <c r="D235" s="9">
-        <v>46232.16820975694</v>
+        <v>46260.84172601852</v>
       </c>
       <c r="E235" s="10" t="s">
         <v>190</v>
@@ -15227,9 +15347,11 @@
       <c r="B236" s="5">
         <v>46162.55910012731</v>
       </c>
-      <c r="C236" s="6"/>
+      <c r="C236" s="5">
+        <v>46260.84171893519</v>
+      </c>
       <c r="D236" s="5">
-        <v>46232.16820384259</v>
+        <v>46260.84172645833</v>
       </c>
       <c r="E236" s="6" t="s">
         <v>190</v>
@@ -15280,9 +15402,11 @@
       <c r="B237" s="9">
         <v>46162.55910407407</v>
       </c>
-      <c r="C237" s="10"/>
+      <c r="C237" s="9">
+        <v>46260.84171957176</v>
+      </c>
       <c r="D237" s="9">
-        <v>46232.16820505787</v>
+        <v>46260.84172680556</v>
       </c>
       <c r="E237" s="10" t="s">
         <v>190</v>
@@ -15333,9 +15457,11 @@
       <c r="B238" s="5">
         <v>46162.559108125</v>
       </c>
-      <c r="C238" s="6"/>
+      <c r="C238" s="5">
+        <v>46260.841720324075</v>
+      </c>
       <c r="D238" s="5">
-        <v>46232.168206180555</v>
+        <v>46260.84172719908</v>
       </c>
       <c r="E238" s="6" t="s">
         <v>190</v>
@@ -15386,9 +15512,11 @@
       <c r="B239" s="9">
         <v>46162.55914409722</v>
       </c>
-      <c r="C239" s="10"/>
+      <c r="C239" s="9">
+        <v>46260.841721006946</v>
+      </c>
       <c r="D239" s="9">
-        <v>46232.16820247685</v>
+        <v>46260.84172768518</v>
       </c>
       <c r="E239" s="10" t="s">
         <v>196</v>
@@ -15439,9 +15567,11 @@
       <c r="B240" s="5">
         <v>46162.56958915509</v>
       </c>
-      <c r="C240" s="6"/>
+      <c r="C240" s="5">
+        <v>46260.84172166667</v>
+      </c>
       <c r="D240" s="5">
-        <v>46232.168191261575</v>
+        <v>46260.84172805556</v>
       </c>
       <c r="E240" s="6" t="s">
         <v>196</v>
@@ -15492,9 +15622,11 @@
       <c r="B241" s="9">
         <v>46162.56959587963</v>
       </c>
-      <c r="C241" s="10"/>
+      <c r="C241" s="9">
+        <v>46260.841722094905</v>
+      </c>
       <c r="D241" s="9">
-        <v>46232.1681928125</v>
+        <v>46260.84172848379</v>
       </c>
       <c r="E241" s="10" t="s">
         <v>196</v>
@@ -15545,9 +15677,11 @@
       <c r="B242" s="5">
         <v>46162.56960513889</v>
       </c>
-      <c r="C242" s="6"/>
+      <c r="C242" s="5">
+        <v>46260.84172266204</v>
+      </c>
       <c r="D242" s="5">
-        <v>46232.16819405093</v>
+        <v>46260.84172884259</v>
       </c>
       <c r="E242" s="6" t="s">
         <v>196</v>
@@ -15598,9 +15732,11 @@
       <c r="B243" s="9">
         <v>46162.569612060186</v>
       </c>
-      <c r="C243" s="10"/>
+      <c r="C243" s="9">
+        <v>46260.84172306713</v>
+      </c>
       <c r="D243" s="9">
-        <v>46232.168195289356</v>
+        <v>46260.84172914352</v>
       </c>
       <c r="E243" s="10" t="s">
         <v>196</v>
@@ -15651,9 +15787,11 @@
       <c r="B244" s="5">
         <v>46162.569619999995</v>
       </c>
-      <c r="C244" s="6"/>
+      <c r="C244" s="5">
+        <v>46260.8417234838</v>
+      </c>
       <c r="D244" s="5">
-        <v>46232.16819645833</v>
+        <v>46260.84172946759</v>
       </c>
       <c r="E244" s="6" t="s">
         <v>196</v>
@@ -15704,9 +15842,11 @@
       <c r="B245" s="9">
         <v>46162.569627812496</v>
       </c>
-      <c r="C245" s="10"/>
+      <c r="C245" s="9">
+        <v>46260.84172391203</v>
+      </c>
       <c r="D245" s="9">
-        <v>46232.16819769676</v>
+        <v>46260.84172982639</v>
       </c>
       <c r="E245" s="10" t="s">
         <v>196</v>
@@ -15757,9 +15897,11 @@
       <c r="B246" s="5">
         <v>46162.569634513886</v>
       </c>
-      <c r="C246" s="6"/>
+      <c r="C246" s="5">
+        <v>46260.841724363425</v>
+      </c>
       <c r="D246" s="5">
-        <v>46232.1681990162</v>
+        <v>46260.84173019676</v>
       </c>
       <c r="E246" s="6" t="s">
         <v>196</v>
@@ -15859,7 +16001,7 @@
       </c>
       <c r="C248" s="6"/>
       <c r="D248" s="5">
-        <v>46242.19780203704</v>
+        <v>46260.84177113426</v>
       </c>
       <c r="E248" s="6" t="s">
         <v>506</v>
@@ -15909,8 +16051,8 @@
       <c r="T248" s="6">
         <v>0</v>
       </c>
-      <c r="U248" s="11" t="s">
-        <v>101</v>
+      <c r="U248" s="12" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="249" spans="1:21" x14ac:dyDescent="0.25">
@@ -15922,7 +16064,7 @@
       </c>
       <c r="C249" s="10"/>
       <c r="D249" s="9">
-        <v>46242.197801365735</v>
+        <v>46260.84177142361</v>
       </c>
       <c r="E249" s="10" t="s">
         <v>510</v>
@@ -15972,8 +16114,8 @@
       <c r="T249" s="10">
         <v>0</v>
       </c>
-      <c r="U249" s="11" t="s">
-        <v>101</v>
+      <c r="U249" s="12" t="s">
+        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4324-4325.xlsx
@@ -2619,7 +2619,7 @@
         <v>46247.666494467594</v>
       </c>
       <c r="D10" s="5">
-        <v>46247.66651185185</v>
+        <v>46264.276712349536</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
